--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D2FFB1-6459-4848-8350-2FEFA28B1038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BA8DCB-B176-46CA-BF9F-AE1782149AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="454">
   <si>
     <t>Canal</t>
   </si>
@@ -160,9 +160,6 @@
     <t>Criterio</t>
   </si>
   <si>
-    <t>Zapotlán</t>
-  </si>
-  <si>
     <t>Muy positivo</t>
   </si>
   <si>
@@ -184,9 +181,6 @@
     <t>Gobernador</t>
   </si>
   <si>
-    <t>Ixmiquilpan</t>
-  </si>
-  <si>
     <t>Redacción</t>
   </si>
   <si>
@@ -199,18 +193,12 @@
     <t>Negativo</t>
   </si>
   <si>
-    <t>Opinión</t>
-  </si>
-  <si>
     <t>Interior</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>Columnista</t>
-  </si>
-  <si>
     <t>SSPH</t>
   </si>
   <si>
@@ -235,9 +223,6 @@
     <t>Positivo</t>
   </si>
   <si>
-    <t>Segobh</t>
-  </si>
-  <si>
     <t>Neutro</t>
   </si>
   <si>
@@ -250,18 +235,12 @@
     <t>Saderh</t>
   </si>
   <si>
-    <t>Reportaje</t>
-  </si>
-  <si>
     <t>El Universal Hidalgo</t>
   </si>
   <si>
     <t>Lorena Rosas</t>
   </si>
   <si>
-    <t>Erika Gutiérrez</t>
-  </si>
-  <si>
     <t>Estatal</t>
   </si>
   <si>
@@ -277,9 +256,6 @@
     <t>Milenio Hidalgo</t>
   </si>
   <si>
-    <t>Teodoro Santos</t>
-  </si>
-  <si>
     <t>Semarnath</t>
   </si>
   <si>
@@ -301,12 +277,6 @@
     <t>Al Día Noticias</t>
   </si>
   <si>
-    <t>Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>Alma Leticia Sánchez</t>
-  </si>
-  <si>
     <t>Lourdes Naranjo</t>
   </si>
   <si>
@@ -322,9 +292,6 @@
     <t>Módulos</t>
   </si>
   <si>
-    <t>Ana Luisa Vega</t>
-  </si>
-  <si>
     <t>Secundaria</t>
   </si>
   <si>
@@ -334,21 +301,6 @@
     <t>Tiraje</t>
   </si>
   <si>
-    <t>Sipdus</t>
-  </si>
-  <si>
-    <t>Pág. 03</t>
-  </si>
-  <si>
-    <t>Pág. 04</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo</t>
-  </si>
-  <si>
-    <t>Berenice Gamboa</t>
-  </si>
-  <si>
     <t>Impresiones locales</t>
   </si>
   <si>
@@ -361,1120 +313,1102 @@
     <t>Carmen Hernández</t>
   </si>
   <si>
-    <t>Óscar Javier González Hernández</t>
-  </si>
-  <si>
-    <t>Polos del Bienestar</t>
-  </si>
-  <si>
-    <t>Regiones 04</t>
-  </si>
-  <si>
-    <t>Alerta De Fraude</t>
-  </si>
-  <si>
-    <t>Fernanda Huerta</t>
-  </si>
-  <si>
     <t>Gustavo Vargas</t>
   </si>
   <si>
-    <t>Rosalía Maldonado</t>
-  </si>
-  <si>
-    <t>Regional 14</t>
-  </si>
-  <si>
     <t>Apoyo A Jóvenes</t>
   </si>
   <si>
     <t>Impulso a las artes</t>
   </si>
   <si>
-    <t>Regreso A Clases</t>
-  </si>
-  <si>
-    <t>Capacitación sanitaria</t>
-  </si>
-  <si>
-    <t>Pág. 02</t>
-  </si>
-  <si>
-    <t>Cobertura educativa</t>
-  </si>
-  <si>
-    <t>Protección ambiental</t>
-  </si>
-  <si>
-    <t>Pág. 17</t>
-  </si>
-  <si>
-    <t>Local 5</t>
-  </si>
-  <si>
-    <t>Local 7</t>
-  </si>
-  <si>
-    <t>Secretaría del Trabajo y Previsión Social de Hidalgo, PGJEH</t>
-  </si>
-  <si>
-    <t>Asistencia social</t>
-  </si>
-  <si>
-    <t>Robo a comercio</t>
-  </si>
-  <si>
-    <t>03A</t>
-  </si>
-  <si>
-    <t>06B</t>
-  </si>
-  <si>
-    <t>07B</t>
-  </si>
-  <si>
-    <t>08C</t>
-  </si>
-  <si>
-    <t>09C</t>
-  </si>
-  <si>
-    <t>Cuotas escolares</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez</t>
-  </si>
-  <si>
-    <t>Pág. 05</t>
-  </si>
-  <si>
-    <t>Otorgan la toma de nota a nueva representante del SUTSMMR</t>
-  </si>
-  <si>
-    <t>La STPSH formalizó la toma de nota a favor de Citlali Islas Vargas como nueva secretaria general del sindicato del ayuntamiento de Mineral de la Reforma (SUTSMMR), destrabando un litigio legal de amparo que inició a finales de 2025.</t>
-  </si>
-  <si>
-    <t>Toma de protesta</t>
-  </si>
-  <si>
-    <t>La Secretaría del Trabajo avaló formalmente la nueva dirigencia de Citlali Islas al frente de los 244 trabajadores del sindicato municipal de la Reforma.</t>
-  </si>
-  <si>
-    <t>STPSH, Ayuntamiento de Mineral de la Reforma, Tribunal de Arbitraje de Hidalgo</t>
-  </si>
-  <si>
-    <t>Citlali Islas Vargas, Óscar Javier González Hernández, Matilde Espinosa Bustamante</t>
-  </si>
-  <si>
-    <t>Se suman 8 municipios de Hidalgo a la ZMVM</t>
-  </si>
-  <si>
-    <t>A partir del martes entró en vigor el decreto de incorporación de ocho municipios de Hidalgo (incluyendo Tula, Tizayuca, Tepeji y Atitalaquia) a la Zona Metropolitana del Valle de México para coordinar el desarrollo territorial ordenado.</t>
-  </si>
-  <si>
     <t>ZMVM</t>
   </si>
   <si>
-    <t>Ocho municipios industriales hidalguenses se integraron formalmente a la Zona Metropolitana del Valle de México tras la publicación del decreto del DOF.</t>
-  </si>
-  <si>
-    <t>Diario Oficial de la Federación, Gobiernos de Hidalgo, CDMX y Edomex</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Claudia Sheinbaum Pardo, Alfredo del Mazo</t>
-  </si>
-  <si>
-    <t>SEPH ve a Hidalgo listo para cobertura total a nivel medio superior</t>
-  </si>
-  <si>
-    <t>El secretario de Educación, Natividad Castrejón, aseguró que la entidad está preparada para dar cobertura del 100% a la matrícula de bachillerato en el periodo 2027-2028 apoyados en nuevas escuelas y sin exámenes punitivos.</t>
-  </si>
-  <si>
-    <t>Pág. 06</t>
-  </si>
-  <si>
-    <t>Hidalgo planea garantizar espacios escolares para la totalidad de egresados de secundaria en el ciclo 2027-2028 bajo la política Mi Derecho, Mi Lugar.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, SEP Federal, CBTis</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, Daniel Fragoso Torres</t>
-  </si>
-  <si>
-    <t>Llama Castrejón a no castigar por falta de pago en cuotas escolares</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez reiteró que las cuotas anuales de mantenimiento son aportaciones voluntarias definidas por consensos de padres y bajo ninguna circunstancia se podrá condicionar la entrega de documentos o clases por impagos.</t>
-  </si>
-  <si>
-    <t>La SEPH prohibió la aplicación de medidas punitivas o retención de certificados escolares a familias que omitan el pago de cuotas voluntarias.</t>
-  </si>
-  <si>
-    <t>Alista Menchaca su 4° Informe de Gobierno</t>
-  </si>
-  <si>
-    <t>En una gira por la localidad de Tlatzintla, en el municipio de Molango, el gobernador Julio Menchaca Salazar confirmó que presentará su Cuarto Informe el 4 de septiembre, descartando eventos regionales e indicando que se expondrá a la calificación social.</t>
-  </si>
-  <si>
-    <t>Molango</t>
-  </si>
-  <si>
-    <t>Informe De Gobierno</t>
-  </si>
-  <si>
-    <t>El titular del Ejecutivo estatal perfila la presentación de su reporte de labores para el 4 de septiembre, contemplándose la visita de la presidencia de México.</t>
-  </si>
-  <si>
-    <t>Salomón Hernández</t>
-  </si>
-  <si>
-    <t>Gobierno de México, Gobierno del Estado de Hidalgo, Ayuntamiento de Molango</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Isabel Ramírez Mercado, Claudia Sheinbaum Pardo</t>
-  </si>
-  <si>
-    <t>Destinan 8.27 mdp a puente de Tlatzintla</t>
-  </si>
-  <si>
-    <t>Acompañado por el delegado de la SICT, el gobernador Julio Menchaca anunció una inversión de 8.27 mdp para rehabilitar el puente vehicular Tetipanchalco de Tlatzintla, afectado por tormentas, con un período de ejecución técnica de 153 días.</t>
-  </si>
-  <si>
     <t>Obras De Infraestructura</t>
   </si>
   <si>
-    <t>El gobierno y la SICT anunciaron la reconstrucción de accesos y gaviones de contención del puente afectado en la Sierra Alta de Hidalgo.</t>
-  </si>
-  <si>
-    <t>SICT federal, Gobierno de Hidalgo</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Pablo Octavio Olvera Sánchez</t>
-  </si>
-  <si>
-    <t>Tulancingo busca reducir riesgos por agroquímicos</t>
-  </si>
-  <si>
-    <t>La Secretaría del Campo de Tulancingo e inspectores de Senasica instruyeron a 30 comercios agrícolas de Santa Ana Hueytlalpan sobre la disposición final y triple lavado de envases vacíos de fertilizantes para evitar contaminación hídrica.</t>
-  </si>
-  <si>
-    <t>Politics 08</t>
-  </si>
-  <si>
-    <t>Autoridades del sector agrícola promovieron talleres sobre el uso responsable de insumos agroquímicos de alto riesgo en zonas de invernaderos en Tulancingo.</t>
-  </si>
-  <si>
-    <t>Secretaría del Campo de Tulancingo, Senasica, Dirección de Reglamentos</t>
-  </si>
-  <si>
-    <t>Hugo Flores Jiménez, Noé Ríos Argüelles</t>
-  </si>
-  <si>
-    <t>Regiones 05</t>
-  </si>
-  <si>
-    <t>Regiones 06</t>
-  </si>
-  <si>
-    <t>Fraudes laborales dejan 39 denuncias de hidalguenses</t>
-  </si>
-  <si>
-    <t>El titular de la STPSH, Óscar González, alertó que al menos 39 personas han denunciado formalmente a redes delictivas que ofrecen plazas fraudulentas de hasta 30 dólares la hora en EE. UU. y suplantan la identidad física de la secretaría.</t>
-  </si>
-  <si>
-    <t>La Secretaría del Trabajo canalizó denuncias penales de 39 hidalguenses estafados con supuestos empleos en el extranjero mediante páginas apócrifas de internet.</t>
-  </si>
-  <si>
-    <t>Van 51 asesinatos de mujeres; solo dos feminicidios</t>
-  </si>
-  <si>
-    <t>Cifras del SESNSP revelan que de enero a julio se registraron 51 asesinatos violentos de mujeres en Hidalgo, de los cuales únicamente dos carpetas se iniciaron e investigan bajo el protocolo de feminicidio.</t>
-  </si>
-  <si>
-    <t>Feminicidio</t>
-  </si>
-  <si>
-    <t>Hidalgo figura entre las tres entidades con menor tasa de carpetas por feminicidio a pesar del reporte acumulado de 51 homicidios de mujeres.</t>
-  </si>
-  <si>
-    <t>SESNSP, Procuraduría General de Justicia del Estado</t>
-  </si>
-  <si>
-    <t>Reunirá Raíces de Hidalgo a 87 comunidades de 28 municipios</t>
-  </si>
-  <si>
-    <t>La secretaria Elizabeth Quintanar informó que el viernes se llevará a cabo el Encuentro Estatal de Turismo Comunitario "Raíces de Hidalgo" en la Hacienda Tepozotlán de Epazoyucan, reuniendo a más de 60 experiencias ancestrales.</t>
-  </si>
-  <si>
-    <t>Regiones 07</t>
-  </si>
-  <si>
-    <t>Turismo Comunitario</t>
-  </si>
-  <si>
-    <t>La Secretaría de Turismo de Hidalgo coordinó un festival cultural interactivo para exhibir la gastronomía, medicina y artesanía tradicional de 28 demarcaciones.</t>
-  </si>
-  <si>
     <t>Turismo</t>
   </si>
   <si>
-    <t>Secretaría de Turismo, Hacienda Tepozotlán</t>
-  </si>
-  <si>
-    <t>Elizabeth Quintanar Gómez</t>
-  </si>
-  <si>
-    <t>Sin cifras: turismo negro en Hidalgo</t>
-  </si>
-  <si>
-    <t>Elizabeth Quintanar Gómez admitió la afluencia de personas en el Castillo del Diablo de Pachuca promovida por el líder de la Santa Muerte, Óscar Pelcastre, señalando que son contabilizados simplemente como visitantes generales de comercios.</t>
-  </si>
-  <si>
-    <t>Segmentos especializados</t>
-  </si>
-  <si>
-    <t>Sectur Hidalgo reconoció el fenómeno del turismo negro en Pachuca, aclarando la carencia de estadísticas oficiales específicas para viajeros rituales.</t>
-  </si>
-  <si>
-    <t>Secretaría de Turismo</t>
-  </si>
-  <si>
-    <t>Elizabeth Quintanar Gómez, Óscar el Perro Pelcastre</t>
-  </si>
-  <si>
-    <t>Niñas y niños conocen labor policial</t>
-  </si>
-  <si>
-    <t>El DIF Municipal de El Arenal, presidido por Alma Marín, coordinó visitas educativas de menores en el Centro de Formación Profesional para enseñar sobre la legalidad y erradicar prejuicios hacia los servidores públicos de seguridad.</t>
-  </si>
-  <si>
-    <t>El Arenal</t>
-  </si>
-  <si>
-    <t>Prevención del delito</t>
-  </si>
-  <si>
-    <t>La institución del DIF municipal de El Arenal llevó a cabo recorridos infantiles de proximidad social con elementos del área de Prevención del Delito.</t>
-  </si>
-  <si>
-    <t>DIF Municipal de El Arenal, SIPINNA, PILARES, Área de Prevención del Delito</t>
-  </si>
-  <si>
-    <t>Alma Marín</t>
-  </si>
-  <si>
-    <t>DIF Tulancingo invita a sumarse a programa de apadrinamiento</t>
-  </si>
-  <si>
-    <t>El Patronato del DIF Tulancingo invitó a sumarse al programa de recaudación "Amigos del Corazón" para subsidiar tratamientos de niños con problemas neuronales en la Unidad de Rehabilitación, reportando 10 apadrinados en curso.</t>
-  </si>
-  <si>
-    <t>La presidenta del patronato de Tulancingo convocó al programa de padrinazgo neuronal tras entregar más de mil 730 apoyos médicos en colonias vulnerables.</t>
-  </si>
-  <si>
-    <t>DIF municipal de Tulancingo, UBR</t>
-  </si>
-  <si>
-    <t>Jessica Garrido Cázarez</t>
-  </si>
-  <si>
-    <t>Invita a conocer las especies de hongos</t>
-  </si>
-  <si>
-    <t>El Parque Ecológico Cubitos abrirá sus puertas los días 27 y 28 de agosto para la primera edición de "Hongosto PEC", un evento diseñado para acercar a la población al conocimiento de los hongos, su importancia ecológica y la producción de setas comestibles.</t>
-  </si>
-  <si>
-    <t>La Semarnath organizará el festival cultural y educativo "Hongosto PEC" en el Parque Ecológico Cubitos para promover el conocimiento ambiental y el cultivo de setas.</t>
-  </si>
-  <si>
-    <t>Semarnath, Parque Ecológico Cubitos</t>
-  </si>
-  <si>
-    <t>Suma Hidalgo más de 7 mil casos de diabetes</t>
-  </si>
-  <si>
-    <t>Registros epidemiológicos estatales de salud revelan que en lo que va de 2026 Hidalgo acumula mil casos nuevos de diabetes mellitus por mes, alcanzando un total de 7,747 pacientes bajo tratamiento, lo que sitúa a este padecimiento como una de las causas principales de muerte y de discapacidad en adultos mayores.</t>
-  </si>
-  <si>
-    <t>Prevención De Enfermedades</t>
-  </si>
-  <si>
-    <t>Hidalgo reporta un promedio de casi mil diagnósticos mensuales de diabetes mellitus, encendiendo alarmas de salud pública en adultos de la entidad.</t>
-  </si>
-  <si>
-    <t>Maximiliano Pérez</t>
-  </si>
-  <si>
-    <t>Secretaría de Salud de Hidalgo, Inapam, OMS, Ensanut 2023</t>
-  </si>
-  <si>
-    <t>Produce el estado más de 15 toneladas de tuna</t>
-  </si>
-  <si>
-    <t>La Secretaría de Agricultura y Desarrollo Rural federal reportó que Hidalgo se sitúa entre los cinco productores principales de tuna del país, con una cosecha estimada de 15,949 toneladas sobre 44,527 hectáreas cultivadas en 2025, generando una derrama económica superior a los dos mil millones de pesos.</t>
-  </si>
-  <si>
     <t>Producción agrícola</t>
   </si>
   <si>
-    <t>La Saderh reportó que Hidalgo aportó un volumen de más de 15 mil toneladas de tuna en el mercado nacional durante el ciclo productivo evaluado.</t>
-  </si>
-  <si>
-    <t>Secretaría de Agricultura y Desarrollo Rural, Saderh</t>
-  </si>
-  <si>
-    <t>La educación como verdadera causa</t>
-  </si>
-  <si>
-    <t>Columna de opinión de Nuvia Mayorga Delgado que reflexiona sobre las deficiencias, la deserción escolar y los altos índices de violencia en las escuelas mexicanas, analizando críticamente el modelo educativo de la actual administración e instando a fortalecer los valores familiares.</t>
-  </si>
-  <si>
-    <t>Mejora educativa</t>
-  </si>
-  <si>
-    <t>La columnista Nuvia Mayorga critica los rezagos educativos, la inseguridad y los retos socioemocionales de la matrícula escolar de nivel básico.</t>
-  </si>
-  <si>
-    <t>Nuvia Mayorga Delgado</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública, Inegi, SNTE</t>
-  </si>
-  <si>
-    <t>Nuvia Mayorga Delgado, Aurelio Nuño</t>
-  </si>
-  <si>
-    <t>Hasta mil 650 pesos se gastan el uniformes</t>
-  </si>
-  <si>
-    <t>Padres de familia acuden a los puestos de uniformes escolares instalados en el centro de Pachuca de cara al regreso a clases del 31 de agosto, reportando un desembolso promedio de entre 560 y mil 650 pesos por alumno para adquirir prendas escolares y uniformes deportivos.</t>
-  </si>
-  <si>
-    <t>Padres de familia de Pachuca reportan gastos de hasta mil 650 pesos para la compra de uniformes escolares de educación básica ante la proximidad del ciclo escolar.</t>
-  </si>
-  <si>
     <t>Sonia Nochebuena</t>
   </si>
   <si>
-    <t>Sonia Nochebuena, Everardo Márquez</t>
-  </si>
-  <si>
-    <t>Hospital del Niño brinda atención a bajo costo</t>
-  </si>
-  <si>
-    <t>El Hospital del Niño DIF Hidalgo destacó las ventajas de su infraestructura y laboratorios clínicos al ofrecer estudios de laboratorio, rayos X, tomografías y resonancias magnéticas a costos hasta 25% menores que laboratorios comerciales, con el fin de beneficiar la economía familiar.</t>
-  </si>
-  <si>
-    <t>Atención médica</t>
-  </si>
-  <si>
-    <t>El centro hospitalario infantil de Pachuca promueve análisis de imagenología y laboratorio clínico especializados con tarifas subsidiadas para la población.</t>
-  </si>
-  <si>
-    <t>Hospital del Niño DIF, Sistema DIF Hidalgo</t>
-  </si>
-  <si>
-    <t>Hidalgo implementará Mi derecho, mi lugar en 2027</t>
-  </si>
-  <si>
-    <t>La SEPH informó que para el ciclo escolar 2027-2028 se implementará en la entidad el modelo "Mi derecho, mi lugar", un mecanismo de asignación automatizada de planteles para educación media superior que eliminará el examen de ingreso en la Zona Metropolitana del Valle de México.</t>
-  </si>
-  <si>
-    <t>Hidalgo adoptará el sistema federal de asignación educativa de bachillerato en 2027, garantizando gratuidad y acceso a egresados de secundaria.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Comipems, Gobierno Federal</t>
-  </si>
-  <si>
-    <t>Existen libros para personas con ceguera</t>
-  </si>
-  <si>
-    <t>La Dirección de Educación Especial de la SEPH coordina la entrega gratuita de libros escolares adaptados en sistema Braille y formato Macrotipo para alumnos con discapacidad visual o baja visión que cursan la educación básica en escuelas públicas regulares y de educación especial.</t>
-  </si>
-  <si>
-    <t>Inclusión</t>
-  </si>
-  <si>
-    <t>La SEPH promueve la distribución gratuita de materiales didácticos especializados en sistema Braille y Macrotipo para estudiantes con debilidad visual.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Dirección de Educación Especial</t>
-  </si>
-  <si>
-    <t>Habilitan registro para vales de la SEPH</t>
-  </si>
-  <si>
-    <t>A partir del 25 de agosto de 2026, la SEPH habilitó la plataforma digital para el registro de beneficiarios del programa de vales escolares de uniformes, calzado y útiles, aplicable a alumnos de escuelas públicas hidalguenses para el inicio de clases.</t>
-  </si>
-  <si>
-    <t>Paquete de apoyos escolares</t>
-  </si>
-  <si>
-    <t>La SEPH formalizó el arranque del registro en línea de tutores y alumnos para el canje oficial del paquete de útiles y uniformes escolares gratuitos.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Sistema de Registro de Alumnos</t>
-  </si>
-  <si>
     <t>Hidalgo</t>
   </si>
   <si>
-    <t>Perspectiva Histórica: La tuza como patrimonio biocultural</t>
-  </si>
-  <si>
-    <t>Ensayo histórico-antropológico que analiza el valor semántico, sociocultural e identitario de la tuza como parte fundamental de la memoria biocultural, su vinculación con el subsuelo y con la vida minera de Pachuca y de Real del Monte.</t>
-  </si>
-  <si>
-    <t>Patrimonio biocultural</t>
-  </si>
-  <si>
-    <t>Artículo que reflexiona sobre el valor ecológico, histórico y cultural de la tuza, instando a preservar su hábitat más allá del uso deportivo del término.</t>
-  </si>
-  <si>
-    <t>Estephany Espinosa</t>
-  </si>
-  <si>
-    <t>Suman $105 millones invertidos en Lolotla</t>
-  </si>
-  <si>
-    <t>El mandatario hidalguense acudió a Lolotla como parte de las Rutas de la Transformación para constatar apoyos y obras camineras por un monto acumulado de 105 mdp ejecutados de 2022 a 2026 para remediar los estragos de la vaguada monzónica.</t>
-  </si>
-  <si>
-    <t>Lolotla</t>
-  </si>
-  <si>
-    <t>El titular del Ejecutivo estatal formalizó la entrega de equipamiento productivo y vientres ovinos a 475 productores damnificados de la Sierra Alta.</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Secretaría de Bienestar</t>
-  </si>
-  <si>
-    <t>Formalizan incorporación de ocho municipios de Hidalgo a la ZMVM</t>
-  </si>
-  <si>
-    <t>El Diario Oficial de la Federación publicó la ampliación formal del Consejo Metropolitano, incorporando a ocho municipios de Hidalgo (como Tula, Tepeji y Atitalaquia) para unificar la planeación de vialidades, medio ambiente y servicios urbanos.</t>
-  </si>
-  <si>
-    <t>Hidalgo formalizó la integración de ocho demarcaciones del sur a la Zona Metropolitana del Valle de México para coordinar el ordenamiento territorial.</t>
-  </si>
-  <si>
-    <t>Sedatu, Gobierno de Hidalgo, CDMX, Edomex, Morelos, Consejo de Desarrollo Metropolitano</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Claudia Sheinbaum Pardo</t>
-  </si>
-  <si>
-    <t>Un vehículo del servicio público chocó con una motocicleta</t>
-  </si>
-  <si>
-    <t>Ayer por la mañana se registró un accidente vial sobre la México-Pachuca a la altura de Acayuca, Zapotlán, donde un colectivo de pasaje impactó a una motocicleta al retornar, tomándose conocimiento del seguro sin reportar heridas graves.</t>
-  </si>
-  <si>
-    <t>Accidente de Transporte Público</t>
-  </si>
-  <si>
-    <t>Unidades de la Guardia Nacional y de Semot supervisaron la colisión de una colectiva de ruta contra una motocicleta en Zapotlán de Juárez.</t>
-  </si>
-  <si>
-    <t>Semot</t>
-  </si>
-  <si>
-    <t>Semot, STCH, Guardia Nacional</t>
-  </si>
-  <si>
-    <t>Hidalgo, sexto lugar nacional en violaciones</t>
-  </si>
-  <si>
-    <t>Reporte del SESNSP devela que el estado acumuló 533 carpetas por el delito de violación de enero a julio (60 de ellas en julio), posicionando a Hidalgo en la sexta posición del país. Suman 4 mil 847 querellas por violencia familiar.</t>
-  </si>
-  <si>
-    <t>Hidalgo concentra altos índices nacionales de violación y lesiones de género, señalando el Congreso del Estado que secretarios comparecerán en octubre.</t>
-  </si>
-  <si>
-    <t>SESNSP, Procuraduría General de Justicia del Estado de Hidalgo, Congreso local</t>
-  </si>
-  <si>
-    <t>Mónica Reyes Martínez</t>
-  </si>
-  <si>
-    <t>La mitad de oficiales de la PIBEH aprobó sus evaluaciones de control y confianza</t>
-  </si>
-  <si>
-    <t>El comisionado Francisco Martínez Gómez reconoció que la corporación registra entre 40% y 50% de evaluaciones de control aprobadas, atribuyendo las bajas estadísticas a la alta rotación voluntaria del personal de nuevo ingreso.</t>
-  </si>
-  <si>
-    <t>Control de confianza</t>
-  </si>
-  <si>
-    <t>La Policía Industrial Bancaria estatal reportó que menos de la mitad de su fuerza de 3,300 guardias e inspectores posee certificaciones vigentes del C3.</t>
-  </si>
-  <si>
-    <t>PIBEH, C3, Secretaría de Seguridad Pública, Inegi</t>
-  </si>
-  <si>
-    <t>Francisco Martínez Gómez</t>
-  </si>
-  <si>
-    <t>REPORTAN AFLUENCIA DE 80% EN BALNEARIOS</t>
-  </si>
-  <si>
-    <t>José Luis Castro Gómez, director de la Asociación de Balnearios de Hidalgo, previó un balance excelente de 80% de hospedaje en Ixmiquilpan gracias a la festividad de Jalpan, aunque el Mundial de fútbol restó volumen de paseantes.</t>
-  </si>
-  <si>
-    <t>Pág. 09</t>
-  </si>
-  <si>
     <t>Afluencia Turística</t>
   </si>
   <si>
-    <t>Los 15 balnearios y centros ecológicos de Ixmiquilpan promediaron un 80% de cupo vacacional, estimándose una importante derrama gastronómica de Canirac.</t>
-  </si>
-  <si>
-    <t>Asociación de Balnearios de Hidalgo, Secretaría de Turismo, Canirac</t>
-  </si>
-  <si>
-    <t>José Luis Castro Gómez, Elizabeth Quintanar Gómez, María Elena Carballal</t>
-  </si>
-  <si>
-    <t>Invierten casi $150 millones en infraestructura turística</t>
-  </si>
-  <si>
-    <t>La Sectur de Hidalgo reportó que la iniciativa privada de cabañas, glamping y restaurantes inyectó 149.8 mdp en los últimos cuatro años, presentándose el PPOT para consolidar la certificación de prestadores de servicios.</t>
-  </si>
-  <si>
-    <t>Infraestructura Turística</t>
-  </si>
-  <si>
-    <t>Sectur Hidalgo devela inversiones de 149 mdp de prestadores de servicios turísticos y promueve regulaciones especiales de hospedaje en plataformas.</t>
-  </si>
-  <si>
-    <t>Secretaría de Turismo de Hidalgo, PPOT</t>
-  </si>
-  <si>
-    <t>Jorge Ortiz, Elizabeth Quintanar Gómez</t>
-  </si>
-  <si>
-    <t>SSPH celebra golpe a cártel; hay reserva sobre detenciones</t>
-  </si>
-  <si>
-    <t>El titular de la SSPH, Salvador Cruz Neri, reconoció que las detenciones de 20 integrantes del CJNG en operativos coordinados federales se manejan bajo reserva. Celebró la intervención del Gabinete de Seguridad Nacional pero aclaró que localmente solo reciben avisos.</t>
-  </si>
-  <si>
-    <t>El titular de la policía de Hidalgo reconoció que la corporación local no recibe información táctica detallada previa sobre los cateos federales contra células del CJNG.</t>
-  </si>
-  <si>
     <t>Nathali González</t>
   </si>
   <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Gabinete de Seguridad federal, Sedena, Semar, FGR, Guardia Nacional</t>
-  </si>
-  <si>
-    <t>Salvador Cruz Neri, Omar García Harfuch, Arturo Gómez Canales</t>
-  </si>
-  <si>
-    <t>Formalizan ampliación de la ZMVM por ser zona clave</t>
-  </si>
-  <si>
-    <t>El DOF publicó la Declaratoria de Modificación de la Zona Metropolitana del Valle de México. El decreto formaliza la adhesión de ocho municipios de Hidalgo (como Tula, Tepeji, Tizayuca y Tlaxcoapan) a las 16 alcaldías de la CDMX y 59 del Edomex.</t>
-  </si>
-  <si>
-    <t>Hidalgo incorporó formalmente ocho municipios conurbados del sur a la planeación territorial, de movilidad y de servicios del Valle de México tras publicarse el decreto federal.</t>
-  </si>
-  <si>
-    <t>Sedatu federal, Consejo de Desarrollo Metropolitano, Gobiernos de Hidalgo, CDMX, Edomex y Morelos</t>
-  </si>
-  <si>
-    <t>Perfilan sedes para Polos de Bienestar en Tula y Sahagún</t>
-  </si>
-  <si>
-    <t>Tras la cancelación del Polo de Desarrollo en Tlaxcoapan, el gobernador Julio Menchaca Salazar garantizó las gestiones para abrir dos nuevos polos en Tula (foco logístico) y Ciudad Sahagún, mientras progresa la Reserva Zapotlán ($10,100 mdp y 910 hectáreas) para manufactura avanzada, farmacéutica y logística.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca gestiona ante la federación la creación de dos nuevos Polos del Bienestar en Tula de Allende y Ciudad Sahagún, mientras avanza la obra de la Reserva Zapotlán.</t>
-  </si>
-  <si>
-    <t>Secretaría de Economía, SICT, Sedeco</t>
-  </si>
-  <si>
-    <t>Miriam Avilés</t>
-  </si>
-  <si>
-    <t>Calzado Escolar Gratuito: Programa de Apoyo a Estudiantes</t>
-  </si>
-  <si>
-    <t>Campaña del gobierno estatal que publica los cuatro pasos del canje de calzado escolar del programa Altagracia Mercado: Paso 1 (Talla del menor), Paso 2 y 3 (Inscripción y vale digital en padresdefamilia.seph.gob.mx) y Paso 4 (Entrega desde el primer día de clases).</t>
-  </si>
-  <si>
     <t>Boletín</t>
   </si>
   <si>
-    <t>La SEPH y el gobierno de Hidalgo publicaron las reglas de operación y los cuatro pasos para el canje de vales de calzado escolar gratuito para el ciclo 2026-2027.</t>
-  </si>
-  <si>
     <t>Comunicado gubernamental</t>
   </si>
   <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Secretaría de Bienestar</t>
-  </si>
-  <si>
-    <t>Altagracia Mercado</t>
-  </si>
-  <si>
-    <t>Llama la SEPH a moderar cuotas en los planteles</t>
-  </si>
-  <si>
-    <t>Ante el inicio de las inscripciones del ciclo escolar 2026-2027 y el reporte de cuotas de entre 600 y 800 pesos, el secretario Natividad Castrejón aclaró que son aportaciones voluntarias de comités de padres y sugirió fijarlas por familia y no por estudiante para mitigar la carga.</t>
-  </si>
-  <si>
-    <t>La SEPH aclaró que las cuotas escolares son voluntarias y recomendó a los comités de padres de familia establecer cuotas por familia y no por estudiante.</t>
-  </si>
-  <si>
-    <t>02.ESTADO</t>
-  </si>
-  <si>
-    <t>Estiman operación completa del Polo de Bienestar en Zapotlán en siete años</t>
-  </si>
-  <si>
-    <t>La operación total del Polo de Desarrollo Económico para el Bienestar (Podecobi) de Zapotlán se estima que se alcance en siete años, de acuerdo con Germán Ahumada Alduncin, director ejecutivo de DEWA, empresa que desarrollará el proyecto. La primera etapa incluye dos naves con una inversión de 10 mil 100 millones de pesos, operando en 18 meses.</t>
-  </si>
-  <si>
-    <t>DEWA estima consolidar el Polo de Bienestar Zapotlán en un plazo de siete años, proyectando el inicio de operaciones de las dos primeras naves en 18 meses.</t>
-  </si>
-  <si>
-    <t>Secretaría de Desarrollo Económico, Cooperativa Cruz Azul</t>
-  </si>
-  <si>
-    <t>Germán Ahumada Alduncin</t>
-  </si>
-  <si>
-    <t>03.ESTADO</t>
-  </si>
-  <si>
-    <t>Infraestructura turística de Hidalgo acumula 149 mdp de inversión privada</t>
-  </si>
-  <si>
-    <t>En los últimos cuatro años, la infraestructura turística de Hidalgo ha concentrado 149 millones 850 mil pesos de inversión privada, de acuerdo con la Dirección de Inteligencia y Política Turística. El director de Planificación y Evaluación, Jorge Ortiz, y la secretaria de Turismo, Elizabeth Quintanar, indicaron que los proyectos incluyen desde ampliaciones hasta nuevos desarrollos.</t>
-  </si>
-  <si>
-    <t>Sectur Hidalgo reportó una captación de más de 149 mdp en inversión turística privada de 2022 a 2026, señalando un déficit vacacional en el corredor de la montaña.</t>
-  </si>
-  <si>
-    <t>Secretaría de Turismo de Hidalgo</t>
-  </si>
-  <si>
-    <t>Elizabeth Quintanar Gómez, Jorge Ortiz</t>
-  </si>
-  <si>
-    <t>Caen cuatro por robo a mano armada a negocios en La Reforma</t>
-  </si>
-  <si>
-    <t>Elementos de la SSPH detuvieron a cuatro sujetos relacionados con el robo a mano armada de negocios en el fraccionamiento Chavarría y la localidad de Palma Gorda, en Mineral de la Reforma. Se les decomisaron dos armas cortas (una hechiza y una de plástico) y una motocicleta con reporte de robo.</t>
-  </si>
-  <si>
-    <t>SSPH detuvo a cuatro presuntos asaltantes en Mineral de la Reforma implicados en asaltos armados a una panadería de Chavarría y un domicilio de Palma Gorda.</t>
-  </si>
-  <si>
     <t>Marco Cerón</t>
   </si>
   <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Ministerio Público</t>
-  </si>
-  <si>
-    <t>Instala SSH Comité Estatal de Partería</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo (SSH) instaló el Comité Estatal de Partería, conformado por 11 miembros permanentes y ocho invitados especiales, para fortalecer la coordinación interinstitucional, promoviendo una atención segura, respetuosa y con enfoque de derechos humanos en salud materna. Hidalgo cuenta con 301 parteras tradicionales y se integró la Licenciatura en la UT de Tulancingo.</t>
-  </si>
-  <si>
     <t>Salud materna</t>
   </si>
   <si>
-    <t>La SSH instaló el Comité Estatal de Partería para optimizar la salud materna y neonatal con un enfoque permanente de derechos humanos.</t>
-  </si>
-  <si>
-    <t>SSH, Copriseh, IMSS, ISSSTE, IMSS Bienestar, Pemex, INPI</t>
-  </si>
-  <si>
-    <t>Vanesa Escalante Arroyo, Diana Reyes Gómez, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Entrega Cultura más de 4 mdp en apoyos de 4 programas</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura estatal entregó apoyos económicos e instrumentos musicales en 38 municipios de Hidalgo mediante cuatro programas de fomento artístico por 4.35 mdp. El programa Semilleros Creativos concentró la mayor parte con 1.8 mdp en beneficio de 129 menores que recibieron 275 instrumentos.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura ejerció 4.35 mdp en cuatro programas para la entrega de instrumentos musicales y financiamientos de creadores en 38 municipios.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura de Hidalgo, Secretaría de Contraloría, Cecultah</t>
-  </si>
-  <si>
-    <t>Neyda Naranjo Baltazar, Julio Menchaca Salazar, Álvaro Bardales Ramírez, César Aurelio Monroy Vega, Tadeo Torres Torres</t>
-  </si>
-  <si>
-    <t>Julio Menchaca respalda la transformación de Lolotla con más de 105 millones de pesos</t>
-  </si>
-  <si>
-    <t>En las Rutas de la Transformación, el gobernador Julio Menchaca entregó apoyos productivos avícolas, agrícolas, ovinos y porcinos a 475 productores de Lolotla por un valor de 4 mdp, junto con canastas alimentarias de la Sebiso y el DIF Hidalgo para mil 219 familias, además de dar seguimiento a obras camineras por 105 mdp.</t>
-  </si>
-  <si>
-    <t>Ruta de la Transformación</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca formalizó apoyos agrícolas de la Saderh, canastas del DIF y obras públicas camineras por un monto de 105 mdp en Lolotla.</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado, Saderh, DIFH, Sipdus</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Claudia Sheinbaum Pardo, Napoleón González Pérez, Ricardo Alvizo Contreras, Alejandro Sánchez García, María Díaz Bustos</t>
-  </si>
-  <si>
-    <t>Inhjuve inicia oficialmente inscripción presencial de los programas Transformando Emprendedores y Embajadores Juventud 2026</t>
-  </si>
-  <si>
-    <t>El Inhjuve y la Sebiso abrieron el periodo de registro presencial y cotejo de documentos de las segundas convocatorias de los programas "Transformando Emprendedores" (apoyo de hasta 20 mil pesos para proyectos productivos de jóvenes de 18 a 29 años) y "Embajadores Juventud" (apoyo de hasta 12 mil pesos en cuatro entregas) en Pachuca.</t>
-  </si>
-  <si>
-    <t>La Sebiso y el Inhjuve iniciaron el registro presencial de los programas de apoyo económico Transformando Emprendedores y Embajadores Juventud 2026.</t>
-  </si>
-  <si>
-    <t>Secretaría de Bienestar e Inclusión Social, Instituto Hidalguense de la Juventud (Inhjuve)</t>
-  </si>
-  <si>
-    <t>Ricardo Olvera Molina</t>
-  </si>
-  <si>
-    <t>Con transparencia y buen uso del gasto público, rinde el presupuesto de gobierno para atender necesidades</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar encabezó las acciones de reconstrucción vial y abasto de agua en Molango de Escamilla tras los estragos de la vaguada monzónica. Se anunció que la SICT federal invertirá 8.27 mdp en la reconstrucción del puente Tetipanchalco de Naopa en beneficio de siete comunidades.</t>
-  </si>
-  <si>
-    <t>La SICT federal y el gobierno de Hidalgo coordinan la reconstrucción vial de Molango, incluyendo la obra de 8.27 mdp en el puente Tetipanchalco.</t>
-  </si>
-  <si>
-    <t>Gobierno de México, Gobierno de Hidalgo, Centro SICT, CEAA</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Pablo Octavio Olvera Sánchez, Juan Carlos Chávez González, María Isabel Ramírez Mercado</t>
-  </si>
-  <si>
-    <t>Hidalgo inicia Programa de Profesionalización y certificación 2026</t>
-  </si>
-  <si>
-    <t>La Secretaría de Turismo presentó el Programa de Profesionalización y Certificación Turística 2026 para elevar la calidad de los servicios en la entidad. Se impartirán 40 cursos prácticos en 21 municipios sobre hospitalidad, salvamento acuático, IA aplicada y turismo sustentable para más de 22 mil prestadores de servicios.</t>
-  </si>
-  <si>
-    <t>Capacitación turística</t>
-  </si>
-  <si>
-    <t>La Secturh de Hidalgo puso en marcha la Academia Permanente de Capacitación turística que impartirá 40 cursos prácticos en 21 municipios.</t>
-  </si>
-  <si>
-    <t>Secretaría de Turismo de Hidalgo (Secturh)</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Elizabeth Quintanar Gómez, Salvador Navarrete Zorrilla, Carlos Llaca Castelán</t>
-  </si>
-  <si>
-    <t>Entregan Manual de Organización y la Operación de Corredor Artesanal</t>
-  </si>
-  <si>
-    <t>La Comisión Estatal para el Desarrollo Sostenible de los Pueblos Indígenas (CEDSPI) entregó el Manual de Organización y Operación del Corredor Artesanal de La Rinconada, en Tasquillo, regulando horarios, higiene, seguridad y rotación de espacios para artesanos locales. Se prevé la entrega de 22 paradores artesanales con manuales este año.</t>
-  </si>
-  <si>
-    <t>Tasquillo</t>
-  </si>
-  <si>
-    <t>Apoyo a artesanos</t>
-  </si>
-  <si>
-    <t>La CEDSPI entregó la normativa de administración del Corredor Artesanal de Tasquillo, proyectándose la entrega de 22 paradores regulados este año.</t>
-  </si>
-  <si>
-    <t>CEDSPI, Unidad de Planeación y Prospectiva (Uplaph), Ayuntamiento de Tasquillo, Comité Administrativo</t>
-  </si>
-  <si>
-    <t>Andrés Rivera Rosales</t>
-  </si>
-  <si>
-    <t>Encabeza Natividad Castrejón el arranque de la Campaña Boteo Teletón 2026 en la SEPH</t>
-  </si>
-  <si>
-    <t>La SEPH dio inicio oficial a la Campaña Boteo Teletón 2026 en la comunidad educativa estatal con el lema 'Por eso te quiero Teletón'. El secretario Natividad Castrejón llamó a directivos y alumnos a sumarse a favor de la inclusión de personas con discapacidad, recordando que en la colecta anterior se reunieron más de 3.29 mdp.</t>
-  </si>
-  <si>
-    <t>La SEPH arrancó las brigadas escolares de recolección de donativos del Boteo Teletón 2026, buscando rebasar el récord previo de 3.29 mdp.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo (SEPH), Fundación Teletón, CRIT Hidalgo, Unidad de Promoción Voluntaria de la SEPH</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, Julio Menchaca Salazar, Agustín Lagunas Oseguera, Virginia Hurtado Salinas</t>
-  </si>
-  <si>
-    <t>UNFPA-IHM coordinan “Diálogo Intersectorial” para atención de violencia</t>
-  </si>
-  <si>
-    <t>El UNFPA México y el Instituto Hidalguense de las Mujeres (IHM) organizaron la reunión virtual "Diálogo Intersectorial" para la región Molango, con el fin de consolidar el modelo de atención y protección local para mujeres víctimas de violencia. Se analizaron abusos y barreras tradicionales en la Sierra.</t>
-  </si>
-  <si>
-    <t>Violencia De Género</t>
-  </si>
-  <si>
-    <t>UNFPA y el IHM sostuvieron un diálogo intersectorial en Molango para atender incidencias de violencia de género y erradicar barreras culturales de la sierra.</t>
-  </si>
-  <si>
-    <t>UNFPA, Instituto Hidalguense de las Mujeres (IHM), Policía Violeta, IMSS Bienestar, CECyTEH, SEPH, PGJEH, CDHEH, CEAV, Comisión de Búsqueda de Personas</t>
-  </si>
-  <si>
-    <t>Katya Gabriela Hernández Pérez, Angélica Ramírez Dávila</t>
-  </si>
-  <si>
-    <t>Moderniza Caasim la infraestructura de tipo hidráulica en San Agustín Tlaxiaca</t>
-  </si>
-  <si>
-    <t>Con el objetivo de mejorar el abasto de agua potable en San Agustín Tlaxiaca, la Caasim modernizó la infraestructura mediante la sustitución de 934 metros de tuberías en la colonia Santa Catarina, beneficiando las condiciones operativas de suministro para más de 120 mil habitantes.</t>
-  </si>
-  <si>
-    <t>San Agustín Tlaxiaca</t>
-  </si>
-  <si>
-    <t>Infraestructura Hidráulica</t>
-  </si>
-  <si>
-    <t>La Caasim modernizó la red hidráulica de Santa Catarina en San Agustín Tlaxiaca, sustituyendo tuberías para optimizar el abasto de agua.</t>
-  </si>
-  <si>
-    <t>Caasim, Gobierno de Hidalgo</t>
-  </si>
-  <si>
-    <t>Contraloría fortalece vigilancia institucional durante entrega de poyos</t>
-  </si>
-  <si>
-    <t>La Contraloría del Estado de Hidalgo desplegó brigadas de acompañamiento y fiscalización ciudadana durante la entrega de programas sociales en municipios de la Sierra Alta (como Lolotla, Molango y Tlanchinol), garantizando la transparencia de recursos que superan los 18 mdp.</t>
-  </si>
-  <si>
-    <t>Vigilancia del gasto público</t>
-  </si>
-  <si>
-    <t>La Contraloría supervisó la entrega correcta de apoyos económicos del programa de Bienestar y de Madres Trabajadoras en la Sierra Alta de Hidalgo.</t>
-  </si>
-  <si>
-    <t>Contraloría</t>
-  </si>
-  <si>
-    <t>Secretaría de Contraloría del Estado de Hidalgo, Órganos de Control y Vigilancia, Sebiso</t>
-  </si>
-  <si>
-    <t>Briseyda Torres</t>
-  </si>
-  <si>
-    <t>José José Sinfónico llega a Gota de Plata con Orquesta Sinfónica del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura invita al concierto José José Sinfónico: Homenaje al Príncipe de la Canción de la OSEH el jueves 17 de septiembre en el Auditorio Gota de Plata de Pachuca. Se presentarán solistas destacados como Armando Gómez Martínez, Julio Trejo y David Argel Cruz.</t>
-  </si>
-  <si>
     <t>Evento Cultural</t>
   </si>
   <si>
-    <t>La Orquesta Sinfónica de Hidalgo (OSEH) ofrecerá un homenaje a José José el 17 de septiembre con la participación de reconocidos intérpretes.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura del Estado de Hidalgo, Orquesta Sinfónica del Estado de Hidalgo (OSEH), Cecultah</t>
-  </si>
-  <si>
-    <t>Armando Gómez Martínez, Julio Trejo, David Argel Cruz Ortega, Jjuncoreano, Héctor Javier Reyes Bonilla</t>
-  </si>
-  <si>
-    <t>Universidad Digital mantiene abierta Convocatoria 2026-II</t>
-  </si>
-  <si>
-    <t>La UNIDEH mantiene abierta su Convocatoria 2026-II para cursar licenciaturas en Gestión Empresarial, Software y Turismo Alternativo, así como maestrías y doctorados virtuales. El registro de aspirantes permanecerá vigente hasta el 1 de octubre.</t>
-  </si>
-  <si>
-    <t>Convocatoria de ingreso</t>
-  </si>
-  <si>
-    <t>La UNIDEH mantiene abierta su segunda convocatoria del año para cursar programas de licenciatura, maestría y doctorado en modalidad completamente virtual.</t>
-  </si>
-  <si>
-    <t>Universidad Digital del Estado de Hidalgo (UNIDEH)</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Sebiso gestionó 20 espacios para personas artesanas en Feria de San Agustín Metzquititlán 2026</t>
-  </si>
-  <si>
-    <t>La Dirección de Fomento Artesanal de la Sebiso obtuvo 20 espacios comerciales gratuitos de venta en la Feria de San Agustín Metzquititlán 2026 para artesanos locales. Suman 450 espacios coordinados este año en ferias estatales y vecinas para incentivar el comercio de artesanías.</t>
-  </si>
-  <si>
-    <t>Metzquititlán</t>
-  </si>
-  <si>
-    <t>Impulso a artesanos</t>
-  </si>
-  <si>
-    <t>La Sebiso y el ayuntamiento local coordinaron la apertura de 20 espacios comerciales sin costo para exhibir artesanía hidalguense en la Feria de Metzquititlán.</t>
-  </si>
-  <si>
-    <t>Secretaría de Bienestar e Inclusión Social (Sebiso), Dirección General de Fomento Artesanal, Ayuntamiento de San Agustín Metzquititlán</t>
-  </si>
-  <si>
-    <t>Ricardo Gómez Moreno, Nora Aidhé Luciano Martínez</t>
-  </si>
-  <si>
-    <t>Universidad Digital mantiene abierta su Convocatoria 2026-II</t>
-  </si>
-  <si>
-    <t>La Universidad Digital del Estado de Hidalgo (UNIDEH) mantiene abierta su Convocatoria 2026-II, para este segundo periodo de ingreso se oferta la Licenciatura en Gestión Empresarial y de Proyectos, Ingeniería de Software y Licenciatura en Turismo Alternativo, así como las Maestrías en Enseñanza de las Ciencias y en Derechos Humanos, además del Doctorado en Investigación e Intervención para la Innovación Educativa.</t>
-  </si>
-  <si>
-    <t>La UNIDEH mantiene abierta su segunda convocatoria para licenciaturas, maestrías y doctorados virtuales con fecha límite al 1 de octubre.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, UNIDEH</t>
-  </si>
-  <si>
-    <t>Instalan Comité de Partería en la entidad</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo (SSH) instaló el Comité Estatal de Partería, integrado por 11 miembros permanentes y ocho invitados especiales, con el propósito de fortalecer la coordinación interinstitucional en favor de la salud materna y neonatal.</t>
-  </si>
-  <si>
-    <t>La SSH instaló el Comité Estatal de Partería con 11 miembros de diversas instituciones para coordinar estrategias de atención con enfoque de derechos humanos.</t>
-  </si>
-  <si>
-    <t>Secretaría de Salud de Hidalgo, Universidad Tecnológica de Tulancingo</t>
-  </si>
-  <si>
-    <t>Diana Reyes Gómez</t>
-  </si>
-  <si>
-    <t>Exigen que Ordenamiento Ecológico se apegue a derecho</t>
-  </si>
-  <si>
-    <t>La organización ambientalista Biofutura, exigió a las autoridades municipales y estatales que el Programa de Ordenamiento Ecológico Local Participativo (POELP) se apegue a derecho y proteja a Pachuca. Señalan que cuatro áreas clave, como el refugio de la tuza, quedaron desprotegidas.</t>
-  </si>
-  <si>
-    <t>Biofutura denunció la existencia de serios errores en el POELP de Pachuca, exigiendo que se protejan zonas de refugio ecológico y corredores urbanos.</t>
-  </si>
-  <si>
-    <t>Semarnath, Ayuntamiento de Pachuca, Biofutura</t>
-  </si>
-  <si>
-    <t>Mineral de la Reforma cumple en rendición de cuentas</t>
-  </si>
-  <si>
-    <t>El Ayuntamiento de Mineral de la Reforma obtuvo una calificación del 100 por ciento correspondiente al segundo trimestre del Índice Municipal de Rendición de Cuentas del Ejercicio Fiscal 2026 emitido por la ASEH.</t>
-  </si>
-  <si>
-    <t>Rendición de cuentas</t>
-  </si>
-  <si>
-    <t>Mineral de la Reforma destacó entre las 20 alcaldías con evaluación perfecta de la ASEH en el cumplimiento de Cuenta Pública y avance de gestión financiera.</t>
-  </si>
-  <si>
-    <t>Auditoría Superior del Estado de Hidalgo, Ayuntamiento de Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>Entregan apoyos a mujeres rurales y pequeños productores</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar encabezó en Lolotla la entrega de equipamiento acuícola, avícola, vientres ovinos y porcinos a 475 productores de la Sierra Alta por un valor de 4.06 mdp, constatando el avance de obras camineras por 105 mdp.</t>
-  </si>
-  <si>
-    <t>El mandatario Julio Menchaca formalizó apoyos productivos y supervisó la conectividad vial de Lolotla a diez meses del impacto de la vaguada monzónica.</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Secretaría de Bienestar, Saderh</t>
-  </si>
-  <si>
-    <t>Modernizan infraestructura en San Agustín Tlaxiaca</t>
-  </si>
-  <si>
-    <t>Con el objetivo de mejorar el servicio de agua potable, la Caasim llevó a cabo la modernización hidráulica y sustitución de 934 metros de tuberías en la colonia Santa Catarina, extendiendo la vida útil de la red en beneficio de 120 mil habitantes.</t>
-  </si>
-  <si>
-    <t>Sustitución de tubería</t>
-  </si>
-  <si>
-    <t>Caasim rehabilitó la red de conducción en San Agustín Tlaxiaca para optimizar las condiciones operativas y el abasto regular de agua potable.</t>
-  </si>
-  <si>
-    <t>Comisión de Agua y Alcantarillado de Sistemas Intermunicipales, Sipdus</t>
-  </si>
-  <si>
-    <t>Con buen uso del gasto público, rinde el presupuesto: JMS</t>
-  </si>
-  <si>
-    <t>Durante una gira de reconstrucción municipal en Molango, el gobernador Julio Menchaca supervisó obras de agua y de caminos por un acumulado de 149 mdp, destacando que el Centro SICT federal destinará 8.27 mdp en reconstruir el puente Tetipanchalco de Naopa.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca coordinó con el Centro SICT Hidalgo la reconstrucción del puente colapsado en Molango, proyectando su conclusión para finales de este año.</t>
-  </si>
-  <si>
-    <t>Gobierno de México, Centro SICT Hidalgo, Sipdus</t>
-  </si>
-  <si>
-    <t>Atracaban negocios en Mineral de la Reforma y ya los atraparon</t>
-  </si>
-  <si>
-    <t>Operativos preventivos coordinados de la SSPH y policías locales de Mineral de la Reforma lograron el arresto de dos asaltantes armados en una panadería de Chavarría y dos hombres más robando refacciones en un depósito de Palma Gorda.</t>
-  </si>
-  <si>
-    <t>Acciones del Mando Coordinado en Mineral de la Reforma permitieron el arresto de cuatro delincuentes armados y la recuperación de vehículos y mercancía.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Mando Coordinado municipal</t>
-  </si>
-  <si>
-    <t>Patrulla derrapa y vuelca en Felipe Ángeles; 2 agentes heridos</t>
-  </si>
-  <si>
-    <t>Una patrulla de la Policía Industrial Bancaria de Hidalgo (PIBEH) derrapó debido al asfalto mojado, colisionando contra un poste y volcando sobre el bulevar Felipe Ángeles de Pachuca, frente a las instalaciones de la Procuraduría estatal.</t>
-  </si>
-  <si>
-    <t>Accidente de patrulla</t>
-  </si>
-  <si>
-    <t>Dos oficiales de la PIBEH resultaron lesionados de gravedad tras registrarse una fuerte volcadura policial en la capital del estado.</t>
-  </si>
-  <si>
-    <t>Policía Industrial Bancaria de Hidalgo, Procuraduría General de Justicia</t>
-  </si>
-  <si>
-    <t>Estados de México disputan visitantes; buscan contener impacto de violencia</t>
-  </si>
-  <si>
-    <t>Reportaje nacional sobre las estrategias aplicadas en Jalisco, Morelos, Sinaloa, Aguascalientes y Michoacán para blindar su reputación turística frente a hechos delictivos y alertas norteamericanas, diversificando sus mercados y reforzando comités de vigilancia.</t>
-  </si>
-  <si>
-    <t>Destinos turísticos mexicanos compiten por captar congresos y grandes convenciones mediante esquemas especiales de promoción y control de seguridad.</t>
-  </si>
-  <si>
-    <t>Secretaría de Turismo federal, Gobiernos Estatales</t>
-  </si>
-  <si>
-    <t>Miguel Andrés Hernández, Fernanda Gaxiola, Verónica González, Alejandra Osuna, Alfonso Márquez, Nemesio Oseguera Cervantes</t>
-  </si>
-  <si>
-    <t>Entra en vigor nueva delimitación de la Zona Metropolitana del Valle de México</t>
-  </si>
-  <si>
-    <t>A partir de este miércoles entra en vigencia formal el decreto que incorpora a ocho municipios de Hidalgo a la Zona Metropolitana del Valle de México. Aunque se prevén mayores inversiones y proyectos, activistas señalan la necesidad urgente de resolver retos de contaminación y delincuencia como en Tizayuca.</t>
-  </si>
-  <si>
-    <t>Ocho municipios del sur de Hidalgo se integraron formalmente a la ZMVM, trayendo consigo desafíos de desarrollo urbano, movilidad y seguridad.</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Consejo de Desarrollo Metropolitano</t>
+    <t>Luis Godínez</t>
+  </si>
+  <si>
+    <t>Centros para los migrantes recibirán 2.5 mdp cada uno</t>
+  </si>
+  <si>
+    <t>El DIF Hidalgo destinará recursos federales de aproximadamente 2.5 millones de pesos por sede para restaurar y operar centros de atención a migrantes. El titular del organismo, Ricardo Enrique Alvizo Contreras, señaló que ante la baja afluencia momentánea de movilidad migratoria, los espacios albergarán temporalmente a 62 artesanos que visitarán Huejutla y a unos 160 que acudirán a la Feria de Pachuca.</t>
+  </si>
+  <si>
+    <t>Apoyo A Migrantes</t>
+  </si>
+  <si>
+    <t>El DIF Hidalgo destinará recursos federales de 2.5 mdp por sede para rehabilitar centros de migración, habilitándolos temporalmente como albergues para artesanos locales.</t>
+  </si>
+  <si>
+    <t>Sistema DIF Hidalgo, Secretaría de Cultura</t>
+  </si>
+  <si>
+    <t>Ricardo Enrique Alvizo Contreras</t>
+  </si>
+  <si>
+    <t>“Cada quien responde por su trayectoria”: Julio Menchaca</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar deslindó su responsabilidad frente a la designación de Adán Augusto López Hernández como coordinador electoral de Morena en la cuarta circunscripción, tras los señalamientos contra el tabasqueño sobre su presunta relación con el grupo delictivo La Barredora. "Cada quien tiene que responder por su trayectoria y yo no puedo ser aval de nadie más que mío", precisó.</t>
+  </si>
+  <si>
+    <t>Trabajo partidista</t>
+  </si>
+  <si>
+    <t>El gobernador de Hidalgo evitó respaldar la trayectoria del senador Adán Augusto López tras críticas de la oposición por supuestas relaciones delictivas.</t>
+  </si>
+  <si>
+    <t>Morena</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Adán Augusto López Hernández</t>
+  </si>
+  <si>
+    <t>Buscan incorporar 30 municipios a la ZMVM</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar anunció que buscarán que se concrete la incorporación de 30 demarcaciones del estado a la Zona Metropolitana del Valle de México (ZMVM) para unificar planes de urbanismo, servicios y medio ambiente, tras celebrarse la entrada en vigor del decreto federal que sumó a ocho municipios del sur.</t>
+  </si>
+  <si>
+    <t>Hidalgo impulsará la adhesión de 30 municipios a la Zona Metropolitana del Valle de México tras oficializarse la incorporación de ocho demarcaciones del sur.</t>
+  </si>
+  <si>
+    <t>Diario Oficial de la Federación, Sedatu, Gobiernos de Hidalgo, CDMX y Edomex</t>
+  </si>
+  <si>
+    <t>Citnova destina $50 millones para entrega de 220 becas</t>
+  </si>
+  <si>
+    <t>El director del Citnova, Francisco Patiño Cardona, informó la entrega de 220 apoyos educativos para posgrados y proyectos en la entidad con un presupuesto de 50 millones de pesos. Consiste en 115 becas de posgrado nacionales (15 mil pesos al mes) y en el extranjero (36 mil pesos al mes), así como 105 apoyos del Fondo Hidalgo para desarrollos de impacto social.</t>
+  </si>
+  <si>
+    <t>Becas</t>
+  </si>
+  <si>
+    <t>Citnova canalizó una bolsa presupuestal de 50 mdp para financiar 220 becas de posgrado y proyectos de innovación científica en beneficio del desarrollo local.</t>
+  </si>
+  <si>
+    <t>Consejo de Ciencia, Tecnología e Innovación de Hidalgo</t>
+  </si>
+  <si>
+    <t>Francisco Patiño Cardona</t>
+  </si>
+  <si>
+    <t>Salvador Cruz se pronuncia ante muertes</t>
+  </si>
+  <si>
+    <t>El titular de la SSPH, Salvador Cruz Neri, informó que se les dota de atención médica prioritaria a los presos de la entidad ante el registro de decesos relacionados con enfermedades crónicas e incidencias de suicidios en el penal de Tulancingo y Tula. Explicó que se abrieron carpetas de investigación correspondientes ante la PGJEH.</t>
+  </si>
+  <si>
+    <t>Deficiencias Ceresos</t>
+  </si>
+  <si>
+    <t>El secretario de Seguridad, Salvador Cruz Neri, informó que se dio intervención a la PGJEH tras registrarse decesos de internos en los penales locales.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, PGJEH</t>
+  </si>
+  <si>
+    <t>Salvador Cruz Neri</t>
+  </si>
+  <si>
+    <t>Comercializa China obsidiana de Hidalgo</t>
+  </si>
+  <si>
+    <t>Francisco Patiño Cardona, titular del Citnova, reveló el plagio y comercialización en aeropuertos internacionales de máscaras chinas con obsidiana del Nopalillo, Epazoyucan, por hasta 40 mil pesos, frente al costo artesanal local de 5 mil pesos. Explicó que se investiga la morfología a nivel atómico para patentar la huella molecular de la roca.</t>
+  </si>
+  <si>
+    <t>Epazoyucan</t>
+  </si>
+  <si>
+    <t>Registro de patente</t>
+  </si>
+  <si>
+    <t>El Citnova identificó la imitación tecnológica de artesanías locales de obsidiana por productores chinos, iniciando gestiones de laboratorio para patentar el mineral.</t>
+  </si>
+  <si>
+    <t>Huejutla</t>
+  </si>
+  <si>
+    <t>Vinculan a proceso a 7 por retención del edil de San Salvador</t>
+  </si>
+  <si>
+    <t>El juez penal de los Juzgados de Pachuca vinculó a proceso a siete personas (Carmela, Arely, Silvia, Rubén, Justino, Isaías y Rubén) acusadas de privación de la libertad, daños y lesiones dolosas en agravio del alcalde Norberto Martínez Corona. Continuarán el proceso con resguardo domiciliario cautelar por los próximos tres meses.</t>
+  </si>
+  <si>
+    <t>San Salvador</t>
+  </si>
+  <si>
+    <t>Vinculación A Proceso</t>
+  </si>
+  <si>
+    <t>La fiscalía obtuvo auto de vinculación a proceso y prisión domiciliaria provisional para siete pobladores implicados en agresiones y la retención del edil.</t>
+  </si>
+  <si>
+    <t>Juzgados Penales de Pachuca, Procuraduría General de Justicia del Estado, Ayuntamiento de San Salvador</t>
+  </si>
+  <si>
+    <t>Norberto Martínez Corona, Carmela, Arely, Silvia, Rubén, Justino, Isaías</t>
+  </si>
+  <si>
+    <t>Van por sueldos dignos para personal de la UBR</t>
+  </si>
+  <si>
+    <t>La alcaldesa de Tulancingo, Lorena García Cázares, y el DIF Hidalgo acordaron la entrega en comodato de la nueva sede de la UBR al organismo asistencial estatal. Se coordinan modificaciones a la Ley de Ingresos municipal para garantizar sueldos dignos e incrementar tarifas equitativas y retener neurólogos de alto perfil.</t>
+  </si>
+  <si>
+    <t>Rehabilitación UBR</t>
+  </si>
+  <si>
+    <t>La alcaldía de Tulancingo acordó ceder la operación del centro rehabilitador neuronal al DIF estatal para subsanar los bajos salarios.</t>
+  </si>
+  <si>
+    <t>Sistema DIF Hidalgo, Ayuntamiento de Tulancingo, UBR</t>
+  </si>
+  <si>
+    <t>Lorena García Cázares, Edda Vite Ramos</t>
+  </si>
+  <si>
+    <t>Tulancingo emprende una campaña de recuperación y saneamiento forestal</t>
+  </si>
+  <si>
+    <t>La Secretaría del Campo de Tulancingo, encabezada por Hugo Flores Jiménez, y la Conafor iniciaron podas de saneamiento forestal contra la plaga del gusano descortezador. Se plantaron 500 pinos Montezumae en el parque El Camaleón (parte de una donación de 2 mil pinos) para reforestar ejidos críticos como Tulancingo y límites de Acaxochitlán.</t>
+  </si>
+  <si>
+    <t>Saneamiento forestal</t>
+  </si>
+  <si>
+    <t>La Secretaría del Campo municipal e inspectores de Conafor ejecutan barridos químicos y podas técnicas para detener el avance del gusano descortezador.</t>
+  </si>
+  <si>
+    <t>Comisión Nacional Forestal, Secretaría del Campo municipal, Asociación de Silvicultores</t>
+  </si>
+  <si>
+    <t>Hugo Flores Jiménez, Arturo Gómez Canales</t>
+  </si>
+  <si>
+    <t>DIF Huejutla reconoce a adultos mayores</t>
+  </si>
+  <si>
+    <t>El DIF de Huejutla coordinó jornadas recreativas para más de 300 adscritos al CAAM en la celebración de la Semana del Adulto Mayor. Kristel Rodríguez Flores lideró las actividades físicas de envejecimiento activo de cara a la celebración del 28 de agosto, además de ofrecerles un desayuno y obsequios tradicionales.</t>
+  </si>
+  <si>
+    <t>Apoyo a adultos mayores</t>
+  </si>
+  <si>
+    <t>El Sistema DIF de Huejutla organizó jornadas lúdicas de salud e integración para conmemorar el Día de los Adultos Mayores.</t>
+  </si>
+  <si>
+    <t>Sistema DIF Huejutla, Ayuntamiento municipal, CAAM</t>
+  </si>
+  <si>
+    <t>Kristel Rodríguez Flores</t>
+  </si>
+  <si>
+    <t>IHE prepara ciclo escolar 2026-2027</t>
+  </si>
+  <si>
+    <t>En representación de Natividad Castrejón Valdez, la coordinadora de educación básica Nancy Adriana León Vite encabezó los trabajos del Consejo Técnico Escolar (CTE) del IHE. Se definieron los programas pedagógicos de la Guía Operativa, los maratones de lectura y los programas de contención emocional del ciclo 2026-2027.</t>
+  </si>
+  <si>
+    <t>Capacitación docente</t>
+  </si>
+  <si>
+    <t>La subsecretaria de educación básica lideró el diseño de planes de seguridad escolar y prevención del maltrato infantil con directivos.</t>
+  </si>
+  <si>
+    <t>Instituto Hidalguense de Educación, Dirección General de Educación Básica</t>
+  </si>
+  <si>
+    <t>Nancy Adriana León Vite, Natividad Castrejón Valdez</t>
+  </si>
+  <si>
+    <t>Nueva plaza comercial en el sur de Pachuca</t>
+  </si>
+  <si>
+    <t>En diciembre de 2026 podría ser la apertura de la nueva plaza comercial Paseo Bonfil, ubicada en el bulevar Ramón G. Bonfil, al sur de Pachuca, de acuerdo con trabajadores de la obra. El diseño está a cargo de Metagrama Diseño Arquitectónico. Albergará marcas como Banregio, Home Store, Promoda, Coppel, un Walmart Supercenter y un gimnasio. Se prevé generar 345 empleos directos e indirectos.</t>
+  </si>
+  <si>
+    <t>Desarrollo Urbano</t>
+  </si>
+  <si>
+    <t>Se proyecta para diciembre de 2026 la apertura de la plaza comercial Paseo Bonfil en el sur de Pachuca, estimándose la generación de 345 empleos.</t>
+  </si>
+  <si>
+    <t>Ayuntamiento de Pachuca</t>
+  </si>
+  <si>
+    <t>La obesidad infantil en México no se detiene, pese a sellos</t>
+  </si>
+  <si>
+    <t>En 2017 México tenía 10 millones de niños y adolescentes con sobrepeso y obesidad, una de las tasas más altas del mundo. Se hizo el etiquetado frontal, se reguló la comida chatarra de las escuelas, se regularon los anuncios. Sin embargo, para 2025 la cifra alcanzó los 11.4 millones, según datos de la ENSANUT, UNICEF y OMS.</t>
+  </si>
+  <si>
+    <t>Obesidad infantil</t>
+  </si>
+  <si>
+    <t>A pesar de la implementación de sellos de advertencia y regulaciones publicitarias, la obesidad infantil en México aumentó a 11.4 millones en 2025.</t>
+  </si>
+  <si>
+    <t>ENSANUT, UNICEF, OMS</t>
+  </si>
+  <si>
+    <t>Niega Cruz Neri fallas en penales de Hidalgo</t>
+  </si>
+  <si>
+    <t>El titular de la Secretaría de Seguridad Pública de Hidalgo (SSPH), Salvador Cruz Neri, negó que existan fallas de seguridad en los penales del estado tras los decesos de internos reportados en Tulancingo e Ixmiquilpan, aclarando que cada caso es investigado. Explicó que cuando un interno requiere atención médica es trasladado a un hospital. Por otra parte, señaló que el rezago en profesionalización policial reportado por el INEGI no refleja el estatus real porque corresponden al 26.9% de policías con Certificado Único Policial (CUP).</t>
+  </si>
+  <si>
+    <t>El titular de la SSPH, Salvador Cruz Neri, rechazó la existencia de fallas sistemáticas en los Ceresos y justificó las métricas de certificación policial.</t>
+  </si>
+  <si>
+    <t>Blanca Soriano</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, INEGI, PGJEH</t>
+  </si>
+  <si>
+    <t>Salvador Cruz Neri, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Inaugura Menchaca cuartel de Policía</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar inauguró el nuevo cuartel de la Policía Estatal en la colonia Cubitos de Pachuca, con una inversión superior a 22 millones de pesos. El inmueble albergará a 86 graduados de la academia y contará con tres unidades especializadas (Grupo Táctico, Vialidad Metropolitana y Medidas de Protección). El secretario de Obras Públicas, Alejandro Sánchez García, refirió que la obra forma parte de la dignificación del parque vehicular e inmobiliario estatal.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca inauguró el nuevo Cuartel de la Policía Estatal en Cubitos, el cual contó con una inversión de 22 millones de pesos.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Sipdus</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Salvador Cruz Neri, Alejandro Sánchez García, Julio César Meléndez Coria</t>
+  </si>
+  <si>
+    <t>Los Centros Gerontológicos están a tu disposición</t>
+  </si>
+  <si>
+    <t>Campaña oficial del Sistema DIF Hidalgo y la Secretaría de Bienestar para difundir los servicios que ofrecen los Centros Gerontológicos Integrales para personas mayores de 60 años. Incluye servicios de salud (medicina, odontología, enfermería, nutrición), atención psicológica, talleres de convivencia (manualidades, pintura, karaoke) y terapia física.</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo difundió la red de atención y terapias gratuitas que ofrecen sus Centros Gerontológicos Integrales para adultos mayores.</t>
+  </si>
+  <si>
+    <t>Sistema DIF Hidalgo, Secretaría de Bienestar e Inclusión Social</t>
+  </si>
+  <si>
+    <t>Geriátricos, opción para adultos mayores</t>
+  </si>
+  <si>
+    <t>Encontrar un espacio adecuado para el cuidado de adultos mayores es una creciente necesidad en Pachuca. La Fundación de Beneficencia María Domínguez Viuda de Álvarez, en Parque Hidalgo, ofrece servicios de estancia diurna y permanente para personas mayores de 65 años. Cuenta con servicios de salud, alimentación y terapias físicas con un costo promedio de 8 mil 500 pesos.</t>
+  </si>
+  <si>
+    <t>Atención adultos mayores</t>
+  </si>
+  <si>
+    <t>La Casa de Descanso Vida en Pachuca promueve esquemas de estancia gerontológica subsidiada con servicios integrales de terapia y de nutrición.</t>
+  </si>
+  <si>
+    <t>Sistema DIF Hidalgo, Fundación de Beneficencia María Domínguez Viuda de Álvarez</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos, María Domínguez Viuda de Álvarez</t>
+  </si>
+  <si>
+    <t>Tus emociones no giran al azar, tú puedes manejarlas</t>
+  </si>
+  <si>
+    <t>Campaña oficial institucional de la SEPH y el IHE orientada a promover la salud mental de los estudiantes de educación básica y media superior mediante el reconocimiento, manejo y gestión de las emociones de manera saludable. Pone a disposición canales de contacto de la Dirección General de Acompañamiento Socioemocional y Educativo.</t>
+  </si>
+  <si>
+    <t>Educación socioemocional</t>
+  </si>
+  <si>
+    <t>La SEPH y el IHE promueven el programa permanente de educación socioemocional en las escuelas públicas hidalguenses.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Instituto Hidalguense de Educación (IHE)</t>
+  </si>
+  <si>
+    <t>En hidalgo se hablará de panteones y rituales</t>
+  </si>
+  <si>
+    <t>En el Auditorio Salvador Toscano del Centro INAH Hidalgo y en el Auditorio Abundio Martínez del Centro de las Artes de Hidalgo, se realizará el Décimo Coloquio Internacional de Historia del 9 al 11 de septiembre. El evento reunirá a especialistas de seis países (Argentina, Colombia, Guatemala, Perú, España, México) para analizar el patrimonio funerario y su valor histórico.</t>
+  </si>
+  <si>
+    <t>Hidalgo será sede del Décimo Coloquio Internacional de Historia que reunirá a expertos de seis países para debatir sobre el patrimonio funerario.</t>
+  </si>
+  <si>
+    <t>Centro INAH Hidalgo, Secretaría de Cultura de Hidalgo, Cecultah</t>
+  </si>
+  <si>
+    <t>Manuel Villarruel Vázquez, Neyda Naranjo Baltazar</t>
+  </si>
+  <si>
+    <t>Reciben apoyos para fortalecer negocios</t>
+  </si>
+  <si>
+    <t>En el Foro del Centro de Atención Infantil (CAI) Pitahayas de Pachuca, se realizó la entrega del apoyo mil del Sistema DIF Hidalgo, consistente en máquinas de coser, hornos y herramientas para repostería a personas de 16 municipios. El proyecto con una inversión de 1.96 mdp busca que los beneficiarios consoliden un autoempleo y sean autosuficientes.</t>
+  </si>
+  <si>
+    <t>Apoyo a emprendedores</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo entregó el apoyo productivo número mil de la administración para fomentar el autoempleo en 16 municipios.</t>
+  </si>
+  <si>
+    <t>Sistema DIF Hidalgo, Centro de Rehabilitación Integral Hidalgo (CRIH)</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos, Hector Villafuentes</t>
+  </si>
+  <si>
+    <t>Aguas termales brindan alivio en el cuerpo</t>
+  </si>
+  <si>
+    <t>Cada fin de semana, miles de turistas de diferentes partes del país visitan los balnearios de aguas termales en el Valle del Mezquital. Betsabé Atalia Sierra García, egresada de Ciencias de la Tierra de la UNAM, detalló que estas aguas, al encontrarse a temperaturas superiores a los 36°C, disuelven minerales y alivian dolores musculares, asma y rinitis.</t>
+  </si>
+  <si>
+    <t>Valle del Mezquital</t>
+  </si>
+  <si>
+    <t>Turistas del centro del país abarrotan los balnearios de aguas termales en el Mezquital, atraídos por sus facultades terapéuticas.</t>
+  </si>
+  <si>
+    <t>Omar Santiago</t>
+  </si>
+  <si>
+    <t>UNAM, Secretaría de Turismo de Hidalgo</t>
+  </si>
+  <si>
+    <t>Betsabé Atalia Sierra García</t>
+  </si>
+  <si>
+    <t>Escasez de Chinicuil incrementa el precio</t>
+  </si>
+  <si>
+    <t>Recolectores de chinicuil en el Valle del Mezquital reportan baja cosecha de la larva de color rosado debido al uso de aguas de riego que afectan las pencas del maguey. Antonio Cruz, recolector, explicó que la escasez ha provocado que el kilo del insecto alcance los dos mil pesos y la canasta de sardina los 550 pesos.</t>
+  </si>
+  <si>
+    <t>La escasez de la larva comestible de chinicuil por el uso de aguas residuales disparó su precio de venta en el Valle del Mezquital.</t>
+  </si>
+  <si>
+    <t>Asociación de Silvicultores</t>
+  </si>
+  <si>
+    <t>Antonio Cruz</t>
+  </si>
+  <si>
+    <t>Entrega el estado 50 mdp en becas y apoyos</t>
+  </si>
+  <si>
+    <t>El gobierno del estado adjudicó apoyos por un valor global de 50 mdp en beneficio de 220 investigadores y becarios hidalguenses, como parte de los programas Fondo Hidalgo y Becas de Excelencia coordinados por el Citnova. Hidalgo cuenta actualmente con 812 miembros del SNI.</t>
+  </si>
+  <si>
+    <t>Impulso a ciencia y tecnología</t>
+  </si>
+  <si>
+    <t>Hidalgo consolidó la entrega de estímulos científicos a 220 investigadores locales, proyectando alcanzar los mil 250 especialistas acreditados al cierre del sexenio.</t>
+  </si>
+  <si>
+    <t>Citnova, Sistema Nacional de Investigadores</t>
+  </si>
+  <si>
+    <t>“Subestación eléctrica, clave para atraer industria”</t>
+  </si>
+  <si>
+    <t>El delegado federal de la Secretaría de Economía reconoció que la escasez de capacidad energética representa un obstáculo primario para la inversión en Tulancingo, por lo que sostendrá encuentros técnicos con personal de la CFE y Sedeco para detonar el proyecto de una nueva subestación.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Economía y el gobierno de Hidalgo coordinan estudios para fundamentar la construcción de una nueva subestación eléctrica en la región de Tulancingo.</t>
+  </si>
+  <si>
+    <t>Mirely Santos</t>
+  </si>
+  <si>
+    <t>Comisión Federal de Electricidad, Secretaría de Desarrollo Económico, Secretaría de Energía</t>
+  </si>
+  <si>
+    <t>Pedro Canales Vega</t>
+  </si>
+  <si>
+    <t>El Citnova prepara una nueva denuncia por más irregularidades</t>
+  </si>
+  <si>
+    <t>El Citnova prepara otra querella penal contra exservidores públicos de la pasada administración, tras interponer previamente una denuncia por la compra irregular e inoperante de una planta piloto para la producción de vacunas con valor de 21 mdp.</t>
+  </si>
+  <si>
+    <t>Denuncias</t>
+  </si>
+  <si>
+    <t>El Consejo de Ciencia y Tecnología dará a conocer nuevos expedientes de corrupción en la adquisición de infraestructura científica el próximo 9 de septiembre.</t>
+  </si>
+  <si>
+    <t>Citnova, PGJEH</t>
+  </si>
+  <si>
+    <t>El último timbre del ciclo... también puede ser el PRIMERO para el reciclaje</t>
+  </si>
+  <si>
+    <t>Campaña institucional orientada al acopio y reciclaje de materiales escolares en desuso (libros, libretas, revistas) recolectados en el Parque Ecológico Cubitos del 20 de julio al 30 de agosto, para evitar el desperdicio y promover la conservación ecológica.</t>
+  </si>
+  <si>
+    <t>Cultura de reciclaje</t>
+  </si>
+  <si>
+    <t>La Semarnath promueve el programa estatal de recolección de celulosa y papel escolar usado para fomentar la sostenibilidad en el retorno a clases.</t>
+  </si>
+  <si>
+    <t>Parque Ecológico Cubitos, Secretaría de Medio Ambiente de Hidalgo</t>
+  </si>
+  <si>
+    <t>Entregan apoyos productivos por $6.8 millones en dos municipios</t>
+  </si>
+  <si>
+    <t>La Saderh entregó insumos agrícolas, vientres ovinos, desbrozadoras, semillas e hijuelos de maguey a 546 productores ganaderos y ejidales de Tepeji del Río ($4.8 mdp) y Tlahuelilpan ($2.0 mdp) de forma directa.</t>
+  </si>
+  <si>
+    <t>Apoyo Al Agro</t>
+  </si>
+  <si>
+    <t>La Saderh Hidalgo ejecutó una inversión agropecuaria coordinada para tecnificar y reactivar la capacidad productiva del campo en la región de Tula.</t>
+  </si>
+  <si>
+    <t>Saderh de Hidalgo</t>
+  </si>
+  <si>
+    <t>Napoleón González Pérez</t>
+  </si>
+  <si>
+    <t>En riesgo por huachicol, más de 20 municipios</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar advirtió sobre el peligro latente e incendios en zonas urbanas por tomas clandestinas en 20 municipios del estado. El anuncio se dio al inaugurar el cuartel policial de Cubitos de Pachuca con valor de 22 mdp.</t>
+  </si>
+  <si>
+    <t>Robo de hidrocarburo</t>
+  </si>
+  <si>
+    <t>El titular del Ejecutivo estatal alertó que el huachicol constituye una seria amenaza civil y ordenó el despliegue del Ejército y Guardia Nacional para blindar ductos.</t>
+  </si>
+  <si>
+    <t>FGR, Guardia Nacional, Sedena, SSPH, Gabinete de Seguridad</t>
+  </si>
+  <si>
+    <t>Detienen a seis sujetos en posesión de armas durante un operativo</t>
+  </si>
+  <si>
+    <t>La SSPH, el Ejército y la Guardia Nacional desplegaron un operativo coordinado en Tecozautla, logrando detener a seis personas y decomisar nueve armas de fuego de grueso calibre, cartuchos útiles, chalecos y ponchallantas.</t>
+  </si>
+  <si>
+    <t>Tecozautla</t>
+  </si>
+  <si>
+    <t>Estrategia de seguridad</t>
+  </si>
+  <si>
+    <t>Fuerzas coordinadas del Mando Único asestaron un golpe táctico en la Sierra Gorda al desarmar y arrestar a un grupo armado en Tecozautla.</t>
+  </si>
+  <si>
+    <t>SSPH, Defensa, Guardia Nacional</t>
+  </si>
+  <si>
+    <t>Vinculan a detenidos por agredir a alcalde</t>
+  </si>
+  <si>
+    <t>Un juez de control vinculó a proceso a siete personas (cuatro hombres y tres mujeres) bajo los cargos de robo, lesiones dolosas y privación ilegal de la libertad cometidos en agravio del alcalde de San Salvador, Norberto Martínez Cruz, imponiéndose prisión domiciliaria preventiva.</t>
+  </si>
+  <si>
+    <t>La PGJEH formalizó la vinculación judicial de siete comuneros implicados en la retención y agresiones físicas perpetradas contra el edil en días pasados.</t>
+  </si>
+  <si>
+    <t>Juzgados de Pachuca, Procuraduría General de Justicia de Hidalgo</t>
+  </si>
+  <si>
+    <t>Norberto Martínez Cruz, Jesús Anim Ope Islas, Carmela, Arely, Silvia, Rubén, Justino, Isaías</t>
+  </si>
+  <si>
+    <t>Capturan a cinco involucrados en distribución de estupefacientes en Tolcayuca</t>
+  </si>
+  <si>
+    <t>Mediante dos cateos conjuntos de la SSPH, PGJEH y Sedena en la Felipe Ángeles de Tolcayuca, se clausuraron dos predios dedicados al narcomenudeo, capturando a cinco hombres (uno de ellos menor) con 756 dosis de cristal y marihuana.</t>
+  </si>
+  <si>
+    <t>Tolcayuca</t>
+  </si>
+  <si>
+    <t>Combate Al Narcomenudeo</t>
+  </si>
+  <si>
+    <t>El Mando Coordinado desmanteló dos bodegas de almacenamiento de narcóticos en Tolcayuca tras un operativo de inteligencia operativa.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, PGJEH, Sedena, Ministerio Público</t>
+  </si>
+  <si>
+    <t>Alejandro Reyes</t>
+  </si>
+  <si>
+    <t>Se combate a todos los delincuentes: Cruz Neri</t>
+  </si>
+  <si>
+    <t>El secretario de Seguridad Pública de Hidalgo, Salvador Cruz Neri, señaló que no se puede confirmar la presencia del Cártel Jalisco Nueva Generación (CJNG) en Hidalgo, luego de que autoridades federales detuvieran a 20 presuntos integrantes de este grupo delictivo en operativos coordinados en Hidalgo, Jalisco y Michoacán. Indicó que se combate a todos los grupos de la delincuencia que pretenden operar en la entidad.</t>
+  </si>
+  <si>
+    <t>El titular de la SSPH, Salvador Cruz Neri, rechazó confirmar operaciones activas del CJNG en el estado, afirmando que se detiene de forma general a todas las células criminales.</t>
+  </si>
+  <si>
+    <t>SSPH, Gobierno del Estado de Hidalgo, FGR, Guardia Nacional</t>
+  </si>
+  <si>
+    <t>Festejan a más de 300 abuelitos en Huejutla</t>
+  </si>
+  <si>
+    <t>El DIF municipal de Huejutla, presidido por Kristel Rodríguez Flores, organizó un convivio especial de conmemoración para más de 300 adultos mayores adscritos al Centro de Atención del Adulto Mayor (CAAM) en la víspera del Día del Adulto Mayor. Las actividades lúdicas forman parte de programas permanentes de envejecimiento activo.</t>
+  </si>
+  <si>
+    <t>El DIF de Huejutla festejó a más de 300 adultos mayores del CAAM con actividades culturales y recreativas para conmemorar el Día del Adulto Mayor.</t>
+  </si>
+  <si>
+    <t>Sistema DIF Huejutla, CAAM</t>
+  </si>
+  <si>
+    <t>Abren apoyos para jóvenes emprendedores</t>
+  </si>
+  <si>
+    <t>La Sebiso y el Inhjuve iniciaron el periodo de registro para recibir apoyos económicos del programa Transformando Emprendedores 2026, con montos de hasta 20 mil pesos para proyectos productivos, y Embajadores Juventud, con un subsidio de hasta 12 mil pesos.</t>
+  </si>
+  <si>
+    <t>El Inhjuve y la Sebiso abrieron la ventanilla presencial de recepción de solicitudes de los programas de apoyo al emprendimiento y capacitación de jóvenes.</t>
+  </si>
+  <si>
+    <t>Inhjuve, Secretaría de Bienestar e Inclusión Social</t>
+  </si>
+  <si>
+    <t>Hidalgo impulsa formación musical infantil</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura estatal distribuyó 275 instrumentos musicales para el programa federal de Semilleros Creativos de cinco municipios. La entrega forma parte de una inversión acumulada de 4 millones 351 mil pesos destinados a creadores de 38 demarcaciones.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura de Hidalgo ejerció 4.35 mdp en apoyos a creadores y dotó de 275 instrumentos a menores del programa Semilleros Creativos.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura de Hidalgo, Semilleros Creativos</t>
+  </si>
+  <si>
+    <t>Buscan reducir las muertes maternas en Hidalgo</t>
+  </si>
+  <si>
+    <t>Ante el registro de cinco defunciones de mujeres embarazadas en Hidalgo durante la semana epidemiológica 32, el sector salud estatal impulsará y coordinará trabajos con parteras tradicionales a través del Comité Estatal de Partería.</t>
+  </si>
+  <si>
+    <t>Las autoridades sanitarias de Hidalgo instalaron el Comité de Partería para contrarrestar los índices epidemiológicos de decesos gestacionales en la entidad.</t>
+  </si>
+  <si>
+    <t>Secretaría de Salud de Hidalgo</t>
+  </si>
+  <si>
+    <t>Sierra Alta recibe 11 mdp en apoyos</t>
+  </si>
+  <si>
+    <t>Ocho municipios de la Sierra Alta de Hidalgo recibieron apoyos estatales por un monto acumulado de 11 millones 110 mil pesos dirigidos a personas cuidadoras, madres trabajadoras y familias rurales a través de Sebiso, concentrando Bienestar y Desarrollo la mayor porción del subsidio con 7.87 mdp.</t>
+  </si>
+  <si>
+    <t>Sierra Alta</t>
+  </si>
+  <si>
+    <t>Programas Del Bienestar</t>
+  </si>
+  <si>
+    <t>La Secretaría de Bienestar de Hidalgo canalizó 11 mdp en subsidios de programas sociales para reactivar la economía familiar en ocho alcaldías serranas.</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar e Inclusión Social</t>
+  </si>
+  <si>
+    <t>Llevan prevención de salud a comunidades en el estado</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo intensificó las actividades de medicina y prevención comunitaria mediante la red de Promotores de la Salud, quienes recorren colonias impartiendo pláticas y proporcionando herramientas para mejorar hábitos de vida.</t>
+  </si>
+  <si>
+    <t>Promoción De La Salud</t>
+  </si>
+  <si>
+    <t>Los Promotores de la Salud de la SSH redoblaron recorridos rurales de proximidad sanitaria para orientar hábitos alimenticios y prevenir padecimientos crónicos.</t>
+  </si>
+  <si>
+    <t>Secretaría de Salud de Hidalgo, Promotores de la Salud</t>
+  </si>
+  <si>
+    <t>Impulsa DIF estatal economía de familias vulnerables con entrega de proyectos productivos</t>
+  </si>
+  <si>
+    <t>El Centro de Asistencia Infantil Comunitario (CAIC) de Pachuca fue sede de la entrega de 32 proyectos productivos a familias de 16 municipios, con el objetivo de fortalecer su economía. El evento estuvo encabezado por la presidenta del Patronato del Sistema DIF Hidalgo, Edda Vite Ramos, destacando una inversión de 1 millón 962 mil 626.44 pesos, sumando 287 proyectos entregados durante la administración para emprendimientos de estética, cocina, carpintería, entre otros.</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo coordinó la entrega de 32 proyectos productivos a familias de 16 municipios para incentivar el autoempleo local.</t>
+  </si>
+  <si>
+    <t>Sistema DIF Hidalgo, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos</t>
+  </si>
+  <si>
+    <t>Inauguran Cuartel de Policía Estatal en Cubitos; invierten 22 mdp</t>
+  </si>
+  <si>
+    <t>Con una inversión de 22 millones 325 mil 60 pesos y en una superficie de terreno de mil 550 metros cuadrados, el gobernador Julio Menchaca Salazar encabezó la inauguración del Cuartel de Policía Estatal de Cubitos, así como la toma de protesta de 116 egresados del Instituto de Formación Profesional. El secretario de Seguridad, Salvador Cruz Neri, señaló que el espacio cuenta con equipo de medidas de protección para atender a las víctimas del delito.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca inauguró el nuevo Cuartel de la Policía Estatal de Cubitos en Pachuca, ejecutado con una inversión de 22.3 mdp.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública, Instituto de Formación Profesional, Gobierno del Estado</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Salvador Cruz Neri</t>
+  </si>
+  <si>
+    <t>Detienen a presuntos narcomenudistas en Tolcayuca; hay un menor involucrado</t>
+  </si>
+  <si>
+    <t>Elementos de la SSPH detuvieron en Tolcayuca a cinco sujetos, entre ellos un menor de edad, dedicados a la distribución de droga, logrando el aseguramiento de dos inmuebles, una motocicleta, 593 dosis de mariguana, 163 de cristal, una báscula y tres teléfonos móviles en la col. Felipe Ángeles.</t>
+  </si>
+  <si>
+    <t>La SSPH desarticuló una célula de narcomenudeo en Tolcayuca al asegurar a cinco implicados con más de 750 dosis de sustancias.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Sedena, Procuraduría General de Justicia del Estado</t>
+  </si>
+  <si>
+    <t>Destaca Edda Vite Ramos la verdadera importancia de generar oportunidades</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo entregó 32 proyectos productivos de autoempleo (máquinas de coser, equipamiento para alimentos y repostería) a familias con personas con discapacidad de 16 municipios, con una inversión de 1 millón 962 mil 626.44 pesos, acumulando 287 proyectos productivos y más de 11.8 mdp ejecutados en la presente gestión.</t>
+  </si>
+  <si>
+    <t>La presidenta del DIF estatal, Edda Vite, formalizó la entrega de 32 financiamientos productivos de autoempleo para promover la inclusión laboral de personas con discapacidad.</t>
+  </si>
+  <si>
+    <t>Sistema DIF Hidalgo, Centros de Rehabilitación Integral de Hidalgo (CRIH), DIF Municipales</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos, Héctor Alberto Villa Fuentes, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Estudiantes del ITESA desarrollan prototipos de go-karts eléctricos</t>
+  </si>
+  <si>
+    <t>Estudiantes de octavo semestre de Ingeniería en Sistemas Automotrices de ITESA fabricaron dos prototipos funcionales de go-karts 100% eléctricos como parte de su formación en electromovilidad, integrando conocimientos de diseño y potencia automotriz bajo el Plan México y el proyecto federal Olinia.</t>
+  </si>
+  <si>
+    <t>Innovación tecnológica</t>
+  </si>
+  <si>
+    <t>Alumnos de ITESA desarrollaron dos vehículos eléctricos ligeros apegados al Plan México y a los programas nacionales para incentivar la manufactura de electromovilidad.</t>
+  </si>
+  <si>
+    <t>Instituto Tecnológico Superior del Oriente del Estado de Hidalgo (ITESA), Academia de Sistemas Automotrices, Secretaría de Educación Pública de Hidalgo</t>
+  </si>
+  <si>
+    <t>Joshio Guadalupe García Acosta, Diego Armando Reyes Cruz, Yonatan Castillo Morales, Aldair Muñoz Martínez, Brandon Domínguez Escorcia, Brandon Rodríguez Cruz, Diego Islas Franco, Dylan Alexander Blancas Carreto, Monserrat Ramírez Jasso, Julio César Hernández Munguía, Guillermo Álvarez Jiménez, Miguel Ángel Lazcano Zavala, Brayan Meneses Mentado, Jeremi Misael Acosta Mateo, Guillermo Canceco Fiel, Bryan Herrera Olvera, Edwin Romero Castelán, Efraín Pacheco Escobedo, Adolfo Lagos Franco Hernández, Saúl Sánchez Cruz</t>
+  </si>
+  <si>
+    <t>Consolida Gobierno de Hidalgo estrategia de impulso a producciones audiovisuales y liderazgo en locaciones</t>
+  </si>
+  <si>
+    <t>La Secretaría de Turismo reportó que Hidalgo ha albergado más de 95 producciones audiovisuales durante la actual administración. Elizabeth Quintanar organizó el foro especializado "Hidalgo en Escena" para captar filmaciones, y alista un recorrido de localización del 7 al 9 de septiembre.</t>
+  </si>
+  <si>
+    <t>Promoción turística</t>
+  </si>
+  <si>
+    <t>La Secturh promueve a la entidad como un escenario estratégico de rodaje de cine y de publicidad, acumulando 95 proyectos fílmicos consolidados.</t>
+  </si>
+  <si>
+    <t>Secretaría de Turismo de Hidalgo (Secturh), Comisión Mexicana de Filmaciones (Comefilm), Ayuntamiento de Zempoala, Ayuntamiento de Metztitlán</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Elizabeth Quintanar Gómez, Diana Álvarez Segoviano, Gabriel Vargas Godínez, María de la Luz Rodríguez Hernández</t>
+  </si>
+  <si>
+    <t>Estado de Hidalgo será sede del 10º Coloquio Internacional “Historia y Costumbres Funerarias”</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura estatal y el Centro INAH Hidalgo organizan el Décimo Coloquio de costumbres y patrimonio funerario del 9 al 11 de septiembre en Pachuca, reuniendo unas 50 ponencias de especialistas de cinco países que abordarán el valor social de los cementerios históricos.</t>
+  </si>
+  <si>
+    <t>Pachuca albergará el encuentro internacional de historia funeraria con expertos de Argentina, Brasil, Colombia, Guatemala, Perú y México.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura del Estado de Hidalgo, Centro INAH Hidalgo, Icomos Mexicano, Red Iberoamericana de Valoración y Gestión de Cementerios Patrimoniales, UNAM, UAM, Amigos Protectores del Panteón Inglés</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo Baltazar, Ethel Herrera Moreno, Manuel Villarruel Vázquez, Luis Francisco Sánchez Fonseca</t>
+  </si>
+  <si>
+    <t>Julio Menchaca inaugura Cuartel en Pachuca de Soto de la Policía Estatal Cubitos</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar entregó de forma oficial el Cuartel Policial de Cubitos, Pachuca, el cual con una inversión de 22 millones 235 mil 60 pesos dotará de infraestructura, servicio médico y site de monitoreo a tres divisiones policiales operativas.</t>
+  </si>
+  <si>
+    <t>El titular del Ejecutivo inauguró el nuevo complejo de la policía estatal y acompañó la toma de protesta de 116 graduados de la academia.</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Secretaría de Seguridad Pública de Hidalgo, Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (Sipdus), Instituto de Formación Profesional</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Salvador Cruz Neri, Alejandro Sánchez García</t>
+  </si>
+  <si>
+    <t>Actualiza CCLEH todos sus servicios con el portal “Registro de Poderes”</t>
+  </si>
+  <si>
+    <t>El Centro de Conciliación Laboral de Hidalgo (CCLEH) habilitó la plataforma poderes.ccleh.gob.mx para facilitar la inscripción y consulta en línea de poderes notariales del sector empresarial, mejorando la seguridad, transparencia y agilizando las audiencias.</t>
+  </si>
+  <si>
+    <t>Innovación pública</t>
+  </si>
+  <si>
+    <t>La Secretaría del Trabajo e Hidalgo implementaron un portal digital que disminuye tiempos y elimina el uso de papel en procesos conciliatorios de empresas.</t>
+  </si>
+  <si>
+    <t>Centro de Conciliación Laboral del Estado de Hidalgo (CCLEH), Secretaría del Trabajo y Previsión Social de Hidalgo</t>
+  </si>
+  <si>
+    <t>Mariela Valero Mota</t>
+  </si>
+  <si>
+    <t>Concluye con gran éxito Curso de Envejecimiento Saludable en Tlaxcoapan</t>
+  </si>
+  <si>
+    <t>El IAAMEH concluyó con éxito el Curso Hidalgo de Envejecimiento Saludable tras tres meses de capacitación lúdica a 58 adultos mayores en Tlaxcoapan, entregando de forma complementaria 11 constancias de educación básica respaldadas por el IHEA.</t>
+  </si>
+  <si>
+    <t>Tlaxcoapan</t>
+  </si>
+  <si>
+    <t>El organismo IAAMEH certificó a 58 personas de la tercera edad en envejecimiento activo y coordinó la entrega de certificados escolares en Tlaxcoapan.</t>
+  </si>
+  <si>
+    <t>Instituto para la Atención de las y los Adultos Mayores del Estado de Hidalgo (IAAMEH), Instituto Hidalguense de Educación para Adultos (IHEA), Casa de Día Tlaxcoapan</t>
+  </si>
+  <si>
+    <t>Penélope Apodaca Sinsel</t>
+  </si>
+  <si>
+    <t>Digitalizar trámites genera rápidamente mayor confianza en la ciudadanía</t>
+  </si>
+  <si>
+    <t>El titular de la Unidad de Planeación y Prospectiva, Miguel Ángel Tello Vargas, develo que la digitalización y simplificación de más de 900 trámites estatales bajo el Ruts disminuye requisitos innecesarios y abona a la trazabilidad institucional.</t>
+  </si>
+  <si>
+    <t>Simplificación de trámites</t>
+  </si>
+  <si>
+    <t>La Uplaph acelera el programa de gobierno digital en el estado, incorporando de manera gradual a dependencias y a los 84 cabildos en la plataforma RUTS.</t>
+  </si>
+  <si>
+    <t>Unidad de Planeación y Prospectiva de Hidalgo (Uplaph), Agencia de Transformación Digital y Telecomunicaciones (ATDT), Registro Único de Trámites y Servicios (RUTS)</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Tello Vargas</t>
+  </si>
+  <si>
+    <t>Base de Operaciones Interinstitucionales (BOI), asegura a grupo generador de violencia en Tecozautla</t>
+  </si>
+  <si>
+    <t>Fuerzas operativas del BOM (SSPH, Defensa, Guardia Nacional y policía municipal) capturaron en Tecozautla a seis masculinos a bordo de camionetas robadas, incautándoles un arsenal de 9 armas, 446 cartuchos, chalecos antibalas, 120 ponchallantas y narcóticos.</t>
+  </si>
+  <si>
+    <t>Un operativo de fuerzas coordinadas desarmó y arrestó a seis presuntos delincuentes implicados en narcomenudeo y posesión de material bélico en Tecozautla.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Secretaría de la Defensa Nacional, Guardia Nacional, Policía Municipal de Tecozautla, Ministerio Público</t>
+  </si>
+  <si>
+    <t>SSPH detiene 5 presuntos involucrados en distribución de droga en Tolcayuca</t>
+  </si>
+  <si>
+    <t>La SSPH, el Ejército y la Procuraduría desarticularon dos fincas identificadas como almacén y punto de comercio de droga en la colonia Felipe Ángeles en Tolcayuca, deteniendo a cinco individuos con 756 dosis de mariguana y cristal.</t>
+  </si>
+  <si>
+    <t>Autoridades asestaron un golpe al narcomenudeo en Tolcayuca tras ejecutar cateos coordinados que permitieron el arresto de cinco implicados.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Secretaría de la Defensa Nacional, Procuraduría General de Justicia del Estado, Ministerio Público</t>
+  </si>
+  <si>
+    <t>Oscar Raúl Pérez</t>
+  </si>
+  <si>
+    <t>Celebra la UPN 48 años de formar profesionales</t>
+  </si>
+  <si>
+    <t>La Universidad Pedagógica Nacional (UPN) conmemoró 48 años de contribuir a la profesionalización del magisterio y a la formación de especialistas en el campo educativo en México. En la entidad, la directora Marisol Vite destacó el crecimiento de la matrícula y la infraestructura.</t>
+  </si>
+  <si>
+    <t>Aniversario Universidades</t>
+  </si>
+  <si>
+    <t>La UPN-Hidalgo conmemoró el decreto de fundación de la institución, resaltando el incremento de su oferta de licenciaturas y posgrados académicos.</t>
+  </si>
+  <si>
+    <t>Universidad Pedagógica Nacional Hidalgo (UPN-H), Sección 15 del SNTE</t>
+  </si>
+  <si>
+    <t>Marisol Vite Vargas, Benigno Sánchez Naranjo, José López Portillo</t>
+  </si>
+  <si>
+    <t>“Yo no puedo ser aval de nadie”: Julio Menchaca</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar precisó que no será aval de la trayectoria de Adán Augusto López tras los señalamientos en su contra por presuntos vínculos delictivos en Tabasco. Sostuvo que mantiene una amistad con él pero cada quien debe responder por sus actos.</t>
+  </si>
+  <si>
+    <t>El gobernador aclaró que su plática con Adán Augusto López se dio bajo una relación institucional y de amistad, pero deslindó su trayectoria delictiva personal.</t>
+  </si>
+  <si>
+    <t>Gobernador del Estado de Hidalgo, Morena, Senado de la República</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Adán Augusto López Hernández, Hernán Bermúdez Requena</t>
+  </si>
+  <si>
+    <t>Tula</t>
+  </si>
+  <si>
+    <t>Aseguran a generadores de violencia</t>
+  </si>
+  <si>
+    <t>La Base de Operaciones Interinstitucionales (BOM) detuvo en Tecozautla a seis hombres a bordo de dos camionetas robadas, incautándoles un arsenal de 9 armas (6 largas y 3 cortas), 22 cargadores, 446 cartuchos, chalecos, 120 ponchallantas y dosis de mariguana y cristal.</t>
+  </si>
+  <si>
+    <t>Fuerzas federales y del Mando Coordinado estatal detuvieron en Tecozautla a seis asaltantes armados en posesión de armas de fuego de grueso calibre y ponchallantas.</t>
+  </si>
+  <si>
+    <t>Base de Operaciones Mixtas (BOM), SSPH, Defensa, Guardia Nacional, Policía Municipal de Tecozautla, Ministerio Público</t>
+  </si>
+  <si>
+    <t>Menchaca se reúne con Adán tras su nombramiento como coordinador</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar confirmó haber recibido la semana pasada al senador Adán Augusto López Hernández, tras ser designado coordinador de Morena en la cuarta circunscripción. Respecto a los presuntos nexos del tabasqueño con la organización "La Barredora", Menchaca deslindó responsabilidades afirmando que cada quien debe responder por su trayectoria personal.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca se reunió con Adán Augusto López tras su nombramiento como coordinador de Morena, deslindándose de sus antecedentes personales.</t>
+  </si>
+  <si>
+    <t>Adela Garmez</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Morena, Senado de la República</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Adán Augusto López Hernández, Ariadna Montiel, Marco Antonio Rico Mercado, Cuauhtémoc Ochoa</t>
+  </si>
+  <si>
+    <t>Detenidos dicen pertenecer a cárteles, pero no se ha podido comprobar: Neri</t>
+  </si>
+  <si>
+    <t>El comisionado Salvador Cruz Neri señaló que algunos detenidos en la entidad refieren pertenecer a bandas criminales nacionales como el CJNG para infundir temor, sin que se acredite su pertenencia real. Asimismo, justificó que el 90% de la policía estatal posee el CUP, aclarando que el Inegi incluyó a la PIBEH intramuros en el rezago.</t>
+  </si>
+  <si>
+    <t>El titular de la SSPH, Salvador Cruz Neri, rechazó confirmar la presencia formal del CJNG en el estado y defendió el índice de acreditación policial local.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Inegi, FGR, CJNG, PIBEH</t>
+  </si>
+  <si>
+    <t>Abren nuevo cuartel para la Policía Estatal en Cubitos</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar inauguró las instalaciones del nuevo cuartel policial en la col. Cubitos de Pachuca, ejecutado con una inversión de 22.3 mdp sobre una superficie de 1,550 m2. El inmueble albergará a 116 egresados de la academia estatal y contará con un site especializado de videovigilancia.</t>
+  </si>
+  <si>
+    <t>El mandatario Julio Menchaca formalizó el nuevo cuartel policial de Cubitos, proyectado como un complejo táctico funcional para la operación metropolitana.</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Secretaría de Seguridad Pública de Hidalgo, Sipdus, Instituto de Formación Profesional</t>
+  </si>
+  <si>
+    <t>Crece desnutrición severa; mujeres, las más afectadas</t>
+  </si>
+  <si>
+    <t>El boletín epidemiológico de la Secretaría de Salud federal devela un repunte del 50% en los diagnósticos hidalguenses de desnutrición severa en 2026, acumulando 129 casos frente a los 86 reportados el año anterior. El sexo femenino concentra la mayor incidencia con 71 querellas.</t>
+  </si>
+  <si>
+    <t>Vigilancia Epidemiológica</t>
+  </si>
+  <si>
+    <t>Estudios federales revelan que la desnutrición severa creció a 129 casos anuales en Hidalgo, afectando prioritariamente a la población femenina.</t>
+  </si>
+  <si>
+    <t>Secretaría de Salud federal, Dirección General de Epidemiología</t>
+  </si>
+  <si>
+    <t>Hidalgo suma tres muertes por covid-19 en una semana</t>
+  </si>
+  <si>
+    <t>El estado de Hidalgo registró tres decesos adicionales por covid-19 en el último reporte semanal, alcanzando un acumulado de 12 fallecimientos en lo que va del 2026. Esto posiciona a Hidalgo en la primera posición del país por decesos derivados de este virus.</t>
+  </si>
+  <si>
+    <t>Covid 19</t>
+  </si>
+  <si>
+    <t>Hidalgo lidera la tasa nacional de letalidad por covid-19 en el año tras confirmarse 12 decesos, concentrando el 23.5% de las muertes del país.</t>
+  </si>
+  <si>
+    <t>Entrega DIFH casi 2 mdp en proyectos productivos</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo formalizó la entrega de equipamiento y herramientas productivas a 32 familias vulnerables de 16 municipios que asisten a personas con discapacidad. La inversión superó el millón 962 mil pesos y contempla un riguroso acompañamiento de tres años para garantizar la viabilidad.</t>
+  </si>
+  <si>
+    <t>Apoyo a personas con discapacidad</t>
+  </si>
+  <si>
+    <t>El DIF estatal entregó 32 proyectos de repostería, costura y alimentos para impulsar la autosuficiencia económica de familias de escasos recursos.</t>
+  </si>
+  <si>
+    <t>Socorro Ávila</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>IHE consolida planeación académica para el nuevo ciclo escolar 2026-2027</t>
+  </si>
+  <si>
+    <t>La coordinación de educación básica coordinó los trabajos intensivos del Consejo Técnico Escolar para delinear los ejes operativos y de seguridad del ciclo 2026-2027. Se revisaron las campañas de lectura, la Guía de Funcionamiento y la estrategia de educación socioemocional El Emocionario.</t>
+  </si>
+  <si>
+    <t>Autoridades de educación básica articularon las estrategias académicas y de prevención del maltrato infantil del nuevo periodo escolar.</t>
+  </si>
+  <si>
+    <t>Nancy Adriana León Vite, Leobardo Cano Albarrán, Grissel Martínez Aguilar, Claudia Huerta Ruiz, Samuel Nava Alcántara, Aurorita Fernanda Reyes</t>
+  </si>
+  <si>
+    <t>Tula: crecen lesiones y la violencia familiar</t>
+  </si>
+  <si>
+    <t>Estudios del SESNSP revelan que de enero a julio el delito de lesiones en Tula de Allende se incrementó un 31.6% en comparación anual, contabilizando 225 carpetas. El ilícito de violencia familiar aumentó 10.6% con 146 investigaciones, posicionándose como la problemática de mayor incidencia local.</t>
+  </si>
+  <si>
+    <t>El SESNSP reportó un aumento del 31% en agresiones dolosas y de violencia familiar en Tula, aunque se registró una reducción en robos y homicidios.</t>
+  </si>
+  <si>
+    <t>Joselyn Sánchez</t>
+  </si>
+  <si>
+    <t>Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública, Procuraduría General de Justicia del Estado, SSPH</t>
+  </si>
+  <si>
+    <t>Destina gobierno 50 mdp en becas y fondos para la ciencia e innovación</t>
+  </si>
+  <si>
+    <t>El director del Citnova, Francisco Patiño Cardona, detalló los apoyos asignados del Fondo Hidalgo 2026, consistentes en una inversión de 50 mdp. La bolsa canalizará 25 mdp para 105 investigaciones de alto impacto y otros 25 mdp para el financiamiento de 115 becas de maestría y doctorado.</t>
+  </si>
+  <si>
+    <t>El Citnova formalizó apoyos económicos científicos de posgrado y de investigación aplicada para 220 especialistas hidalguenses.</t>
+  </si>
+  <si>
+    <t>Consejo de Ciencia, Tecnología e Innovación de Hidalgo, Gobierno del Estado</t>
+  </si>
+  <si>
+    <t>Menchaca reserva su opinión ante la llegada de Adán</t>
+  </si>
+  <si>
+    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, evitó fijar una postura sobre la designación de Adán Augusto López Hernández como coordinador de Morena en la cuarta circunscripción electoral para los comicios de 2027. Al ser cuestionado sobre las imputaciones contra el tabasqueño por supuestos nexos con el grupo delictivo 'La Barredora' de Tabasco, el mandatario estatal respondió que cada persona debe hacerse responsable de su trayectoria personal.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca se reservó de emitir comentarios sobre el nombramiento de Adán Augusto López en Morena, indicando que cada quien es responsable de sus actos.</t>
+  </si>
+  <si>
+    <t>Erick Perales</t>
+  </si>
+  <si>
+    <t>Morena, Gobierno del Estado de Hidalgo, Senado de la República</t>
+  </si>
+  <si>
+    <t>Vinculan a proceso a 7 por conflicto en La Flor</t>
+  </si>
+  <si>
+    <t>La PGJEH obtuvo la vinculación a proceso y resguardo domiciliario temporal por tres meses de investigación complementaria contra siete pobladores (J. C. A., I. A. H., R. A. L., R. S. B., S. N. M., A. C. B. y C. H. B.) acusados de privación ilegal de la libertad, lesiones, robo y daño en propiedad. Los hechos ocurrieron el 18 y 19 de agosto en la comunidad de La Flor, San Salvador, tras retener por la fuerza al alcalde y a regidores del cabildo, dejando 10 policías estatales lesionados.</t>
+  </si>
+  <si>
+    <t>La procuraduría estatal vinculó judicialmente a proceso a siete pobladores implicados en disturbios violentos y en la retención del cabildo municipal en San Salvador.</t>
+  </si>
+  <si>
+    <t>Procuraduría General de Justicia del Estado de Hidalgo, Secretaría de Seguridad Pública de Hidalgo, Ayuntamiento de San Salvador</t>
+  </si>
+  <si>
+    <t>J. C. A., I. A. H., R. A. L., R. S. B., S. N. M., A. C. B., C. H. B.</t>
+  </si>
+  <si>
+    <t>Invierten 22 mdp en el cuartel de Cubitos</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar inauguró el nuevo cuartel de la Policía Estatal en Cubitos, Pachuca, construido con un presupuesto de 22 millones 235 mil 60 pesos. El espacio albergará las divisiones de Vialidad Metropolitana, Grupo Táctico y Medidas de Protección para acercar los servicios de auxilio. Durante la ceremonia, 116 nuevos cadetes de la corporación rindieron protesta tras acumular mil horas de profesionalización.</t>
+  </si>
+  <si>
+    <t>El mandatario estatal inauguró el complejo táctico de Cubitos y dio la bienvenida a 116 cadetes profesionales para robustecer las brigadas de auxilio y seguridad.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Gobierno del Estado de Hidalgo, Instituto de Formación Profesional</t>
+  </si>
+  <si>
+    <t>Detenciones en Tecozautla da indicio de grupo criminal</t>
+  </si>
+  <si>
+    <t>La SSPH indaga la incursión de bandas criminales de otros estados tras arrestar a seis hombres armados que circulaban en dos vehículos con reporte de robo en Tecozautla, decomisándoles un arsenal de nueve armas de fuego, equipo balístico y 120 ponchallantas. Asimismo, el comisionado Salvador Cruz Neri confirmó la detención preventiva de un objetivo de interés federal prioritario en Pachuca.</t>
+  </si>
+  <si>
+    <t>SSPH y fuerzas operativas detuvieron en Tecozautla a seis civiles procedentes de otras entidades en posesión de fusiles de asalto y equipo táctico.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Secretaría de la Defensa Nacional, Guardia Nacional</t>
   </si>
 </sst>
 </file>
@@ -1598,8 +1532,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}" name="Tabla1" displayName="Tabla1" ref="A1:AJ64" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ64" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}" name="Tabla1" displayName="Tabla1" ref="A1:AJ68" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ68" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{D3CF0D4E-B6F9-44AC-AB4F-0535BBEB6872}" uniqueName="Canal" name="Canal">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
@@ -2031,7 +1965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DBE5F67-B229-448F-97D5-0E5E46CD1702}">
-  <dimension ref="A1:AJ64"/>
+  <dimension ref="A1:AJ68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -2183,28 +2117,28 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="F2" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G2" t="s">
-        <v>97</v>
+        <v>46261</v>
+      </c>
+      <c r="G2">
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="I2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -2213,75 +2147,75 @@
         <v>13262</v>
       </c>
       <c r="T2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W2" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="X2" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="Y2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="Z2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AD2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="AG2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH2" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="AI2" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="AJ2" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="F3" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G3" t="s">
-        <v>132</v>
+        <v>46261</v>
+      </c>
+      <c r="G3">
+        <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -2290,75 +2224,75 @@
         <v>13262</v>
       </c>
       <c r="T3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W3" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="X3" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="Y3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA3">
         <v>20</v>
       </c>
       <c r="AB3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF3" t="s">
         <v>41</v>
       </c>
-      <c r="AD3" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF3" t="s">
+      <c r="AG3" t="s">
         <v>42</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AH3" t="s">
         <v>43</v>
       </c>
-      <c r="AH3" t="s">
-        <v>44</v>
-      </c>
       <c r="AI3" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="AJ3" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="F4" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G4" t="s">
-        <v>147</v>
+        <v>46261</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
       </c>
       <c r="H4" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -2367,75 +2301,75 @@
         <v>13262</v>
       </c>
       <c r="T4" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W4" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="X4" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="Y4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF4" t="s">
         <v>41</v>
       </c>
-      <c r="AD4" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>103</v>
-      </c>
       <c r="AG4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH4" t="s">
         <v>43</v>
       </c>
-      <c r="AH4" t="s">
-        <v>56</v>
-      </c>
       <c r="AI4" t="s">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="AJ4" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
         <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="F5" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G5" t="s">
-        <v>147</v>
+        <v>46261</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -2444,75 +2378,75 @@
         <v>13262</v>
       </c>
       <c r="T5" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W5" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="X5" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="Y5" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB5" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="AD5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF5" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="AG5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH5" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="AI5" t="s">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="AJ5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
         <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="E6" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="F6" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G6" t="s">
-        <v>106</v>
+        <v>46261</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>156</v>
+        <v>64</v>
       </c>
       <c r="I6" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -2521,75 +2455,75 @@
         <v>13262</v>
       </c>
       <c r="T6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W6" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="X6" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="Y6" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA6">
         <v>20</v>
       </c>
       <c r="AB6" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF6" t="s">
         <v>41</v>
       </c>
-      <c r="AD6" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>159</v>
-      </c>
       <c r="AG6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AI6" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="AJ6" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
         <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="E7" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="F7" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G7" t="s">
-        <v>106</v>
+        <v>46261</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="I7" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -2598,75 +2532,75 @@
         <v>13262</v>
       </c>
       <c r="T7" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W7" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="X7" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="Y7" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA7">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AB7" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF7" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="AG7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH7" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="AI7" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="AJ7" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
         <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="E8" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="F8" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G8" t="s">
-        <v>170</v>
+        <v>46261</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
       </c>
       <c r="H8" t="s">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="I8" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -2675,75 +2609,75 @@
         <v>13262</v>
       </c>
       <c r="T8" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W8" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="X8" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="Y8" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA8">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB8" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC8" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="AD8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF8" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="AG8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH8" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="AI8" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="AJ8" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
         <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="E9" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="F9" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G9" t="s">
-        <v>175</v>
+        <v>46261</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -2752,75 +2686,75 @@
         <v>13262</v>
       </c>
       <c r="T9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W9" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="X9" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="Y9" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA9">
         <v>15</v>
       </c>
       <c r="AB9" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD9" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF9" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="AG9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH9" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="AI9" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="AJ9" t="s">
-        <v>104</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
         <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="F10" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G10" t="s">
-        <v>175</v>
+        <v>46261</v>
+      </c>
+      <c r="G10">
+        <v>7</v>
       </c>
       <c r="H10" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -2829,75 +2763,75 @@
         <v>13262</v>
       </c>
       <c r="T10" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W10" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="X10" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="Y10" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z10" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA10">
         <v>20</v>
       </c>
       <c r="AB10" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF10" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AG10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH10" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="AI10" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="AJ10" t="s">
-        <v>48</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
         <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="E11" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="F11" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G11" t="s">
-        <v>186</v>
+        <v>46261</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
       </c>
       <c r="H11" t="s">
-        <v>71</v>
+        <v>138</v>
       </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -2906,75 +2840,75 @@
         <v>13262</v>
       </c>
       <c r="T11" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W11" t="s">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="X11" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="Y11" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA11">
         <v>15</v>
       </c>
       <c r="AB11" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC11" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="AD11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF11" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="AG11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH11" t="s">
-        <v>189</v>
+        <v>54</v>
       </c>
       <c r="AI11" t="s">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="AJ11" t="s">
-        <v>191</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
         <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="E12" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="F12" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G12" t="s">
-        <v>186</v>
+        <v>46261</v>
+      </c>
+      <c r="G12">
+        <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I12" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2983,75 +2917,75 @@
         <v>13262</v>
       </c>
       <c r="T12" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W12" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="X12" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="Y12" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA12">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AB12" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC12" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="AD12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH12" t="s">
         <v>52</v>
       </c>
-      <c r="AF12" t="s">
-        <v>57</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>189</v>
-      </c>
       <c r="AI12" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="AJ12" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="E13" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="F13" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G13" t="s">
-        <v>170</v>
+        <v>46261</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
       </c>
       <c r="H13" t="s">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="I13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -3060,75 +2994,75 @@
         <v>13262</v>
       </c>
       <c r="T13" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W13" t="s">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="X13" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="Y13" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="Z13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB13" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC13" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF13" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AG13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH13" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="AI13" t="s">
-        <v>203</v>
+        <v>174</v>
       </c>
       <c r="AJ13" t="s">
-        <v>204</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D14" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="E14" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="F14" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G14" t="s">
-        <v>174</v>
+        <v>46261</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
       </c>
       <c r="H14" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I14" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -3137,75 +3071,75 @@
         <v>13262</v>
       </c>
       <c r="T14" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W14" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="X14" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="Y14" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="Z14" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB14" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF14" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="AG14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="AI14" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="AJ14" t="s">
-        <v>209</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="F15" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -3214,75 +3148,75 @@
         <v>13262</v>
       </c>
       <c r="T15" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W15" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="X15" t="s">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="Y15" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z15" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AA15">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB15" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC15" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="AD15" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF15" t="s">
-        <v>108</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH15" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="AI15" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="AJ15" t="s">
-        <v>108</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
       <c r="E16" t="s">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="F16" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G16">
         <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -3291,75 +3225,75 @@
         <v>13262</v>
       </c>
       <c r="T16" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W16" t="s">
-        <v>216</v>
+        <v>92</v>
       </c>
       <c r="X16" t="s">
-        <v>217</v>
+        <v>188</v>
       </c>
       <c r="Y16" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z16" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA16">
+        <v>24</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC16" t="s">
         <v>40</v>
       </c>
-      <c r="AA16">
-        <v>30</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>41</v>
-      </c>
       <c r="AD16" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF16" t="s">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH16" t="s">
         <v>43</v>
       </c>
-      <c r="AH16" t="s">
-        <v>59</v>
-      </c>
       <c r="AI16" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="AJ16" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="E17" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="F17" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I17" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -3368,75 +3302,78 @@
         <v>13262</v>
       </c>
       <c r="T17" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V17" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="W17" t="s">
-        <v>222</v>
+        <v>160</v>
       </c>
       <c r="X17" t="s">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="Y17" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="Z17" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA17">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB17" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD17" t="s">
-        <v>52</v>
+        <v>40</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>100</v>
       </c>
       <c r="AF17" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AG17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH17" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="AI17" t="s">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="AJ17" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="E18" t="s">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="F18" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H18" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -3445,75 +3382,75 @@
         <v>13262</v>
       </c>
       <c r="T18" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V18" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="W18" t="s">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="X18" t="s">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="Y18" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="Z18" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB18" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC18" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD18" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF18" t="s">
-        <v>229</v>
+        <v>88</v>
       </c>
       <c r="AG18" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="AH18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AI18" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="AJ18" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="E19" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="F19" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H19" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I19" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -3522,75 +3459,78 @@
         <v>13262</v>
       </c>
       <c r="T19" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V19" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="W19" t="s">
-        <v>114</v>
+        <v>203</v>
       </c>
       <c r="X19" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="Y19" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="Z19" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AA19">
         <v>20</v>
       </c>
       <c r="AB19" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD19" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>100</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH19" t="s">
         <v>52</v>
       </c>
-      <c r="AF19" t="s">
-        <v>235</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>56</v>
-      </c>
       <c r="AI19" t="s">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c r="AJ19" t="s">
-        <v>236</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="E20" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="F20" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H20" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I20" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -3599,75 +3539,75 @@
         <v>13262</v>
       </c>
       <c r="T20" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W20" t="s">
-        <v>239</v>
+        <v>103</v>
       </c>
       <c r="X20" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="Y20" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z20" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA20">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB20" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD20" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF20" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="AG20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH20" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="AI20" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="AJ20" t="s">
-        <v>109</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="E21" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="F21" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H21" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="I21" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -3676,75 +3616,75 @@
         <v>13262</v>
       </c>
       <c r="T21" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W21" t="s">
-        <v>117</v>
+        <v>213</v>
       </c>
       <c r="X21" t="s">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="Y21" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z21" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA21">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB21" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF21" t="s">
-        <v>235</v>
+        <v>88</v>
       </c>
       <c r="AG21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AI21" t="s">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="AJ21" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="E22" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="F22" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G22">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H22" t="s">
-        <v>71</v>
+        <v>219</v>
       </c>
       <c r="I22" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -3753,75 +3693,75 @@
         <v>13262</v>
       </c>
       <c r="T22" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W22" t="s">
-        <v>248</v>
+        <v>97</v>
       </c>
       <c r="X22" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
       <c r="Y22" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z22" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA22">
         <v>15</v>
       </c>
       <c r="AB22" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD22" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF22" t="s">
-        <v>110</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH22" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="AI22" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="AJ22" t="s">
-        <v>110</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="E23" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="F23" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G23" t="s">
-        <v>111</v>
+        <v>46261</v>
+      </c>
+      <c r="G23">
+        <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>71</v>
+        <v>219</v>
       </c>
       <c r="I23" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="R23">
         <v>1</v>
@@ -3830,75 +3770,75 @@
         <v>13262</v>
       </c>
       <c r="T23" t="s">
+        <v>83</v>
+      </c>
+      <c r="V23" t="s">
+        <v>38</v>
+      </c>
+      <c r="W23" t="s">
         <v>94</v>
       </c>
-      <c r="V23" t="s">
-        <v>39</v>
-      </c>
-      <c r="W23" t="s">
-        <v>253</v>
-      </c>
       <c r="X23" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="Y23" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA23">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB23" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC23" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD23" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF23" t="s">
-        <v>110</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AI23" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="AJ23" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="E24" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="F24" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G24" t="s">
-        <v>97</v>
+        <v>46261</v>
+      </c>
+      <c r="G24">
+        <v>4</v>
       </c>
       <c r="H24" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I24" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -3907,75 +3847,75 @@
         <v>13262</v>
       </c>
       <c r="T24" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V24" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="W24" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="X24" t="s">
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="Y24" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="Z24" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA24">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="AB24" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC24" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD24" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF24" t="s">
-        <v>261</v>
+        <v>76</v>
       </c>
       <c r="AG24" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="AH24" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="AI24" t="s">
-        <v>48</v>
+        <v>233</v>
       </c>
       <c r="AJ24" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D25" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="E25" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="F25" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G25" t="s">
-        <v>132</v>
+        <v>46261</v>
+      </c>
+      <c r="G25">
+        <v>4</v>
       </c>
       <c r="H25" t="s">
-        <v>264</v>
+        <v>56</v>
       </c>
       <c r="I25" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="R25">
         <v>1</v>
@@ -3984,75 +3924,75 @@
         <v>13262</v>
       </c>
       <c r="T25" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W25" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="X25" t="s">
-        <v>265</v>
+        <v>236</v>
       </c>
       <c r="Y25" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z25" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA25">
+        <v>15</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC25" t="s">
         <v>40</v>
       </c>
-      <c r="AA25">
-        <v>20</v>
-      </c>
-      <c r="AB25" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC25" t="s">
-        <v>41</v>
-      </c>
       <c r="AD25" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF25" t="s">
-        <v>46</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH25" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="AJ25" t="s">
-        <v>87</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="E26" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="F26" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G26" t="s">
-        <v>132</v>
+        <v>46261</v>
+      </c>
+      <c r="G26">
+        <v>4</v>
       </c>
       <c r="H26" t="s">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="I26" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="R26">
         <v>1</v>
@@ -4061,75 +4001,75 @@
         <v>13262</v>
       </c>
       <c r="T26" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W26" t="s">
-        <v>141</v>
+        <v>242</v>
       </c>
       <c r="X26" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="Y26" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z26" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA26">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB26" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC26" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="AD26" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF26" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="AG26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH26" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="AI26" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="AJ26" t="s">
-        <v>271</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="E27" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="F27" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G27" t="s">
-        <v>147</v>
+        <v>46261</v>
+      </c>
+      <c r="G27">
+        <v>6</v>
       </c>
       <c r="H27" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="I27" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="R27">
         <v>1</v>
@@ -4138,75 +4078,78 @@
         <v>13262</v>
       </c>
       <c r="T27" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V27" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="W27" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="X27" t="s">
-        <v>275</v>
+        <v>248</v>
       </c>
       <c r="Y27" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="Z27" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA27">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AB27" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC27" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD27" t="s">
-        <v>52</v>
+        <v>40</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>100</v>
       </c>
       <c r="AF27" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>249</v>
+      </c>
+      <c r="AJ27" t="s">
         <v>46</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH27" t="s">
-        <v>276</v>
-      </c>
-      <c r="AI27" t="s">
-        <v>277</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="E28" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="F28" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G28" t="s">
-        <v>147</v>
+        <v>46261</v>
+      </c>
+      <c r="G28">
+        <v>6</v>
       </c>
       <c r="H28" t="s">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="I28" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="R28">
         <v>1</v>
@@ -4215,75 +4158,75 @@
         <v>13262</v>
       </c>
       <c r="T28" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W28" t="s">
-        <v>102</v>
+        <v>252</v>
       </c>
       <c r="X28" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="Y28" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z28" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA28">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB28" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD28" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF28" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="AG28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH28" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="AI28" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="AJ28" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="E29" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="F29" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G29" t="s">
-        <v>147</v>
+        <v>46261</v>
+      </c>
+      <c r="G29">
+        <v>7</v>
       </c>
       <c r="H29" t="s">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="I29" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -4292,75 +4235,75 @@
         <v>13262</v>
       </c>
       <c r="T29" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V29" t="s">
+        <v>38</v>
+      </c>
+      <c r="W29" t="s">
+        <v>258</v>
+      </c>
+      <c r="X29" t="s">
+        <v>259</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z29" t="s">
         <v>39</v>
       </c>
-      <c r="W29" t="s">
-        <v>285</v>
-      </c>
-      <c r="X29" t="s">
-        <v>286</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>51</v>
-      </c>
       <c r="AA29">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AB29" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD29" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF29" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="AG29" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH29" t="s">
         <v>43</v>
       </c>
-      <c r="AH29" t="s">
-        <v>54</v>
-      </c>
       <c r="AI29" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="AJ29" t="s">
-        <v>288</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="E30" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
       <c r="F30" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G30" t="s">
-        <v>291</v>
+        <v>46261</v>
+      </c>
+      <c r="G30">
+        <v>7</v>
       </c>
       <c r="H30" t="s">
-        <v>45</v>
+        <v>263</v>
       </c>
       <c r="I30" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="R30">
         <v>1</v>
@@ -4369,75 +4312,75 @@
         <v>13262</v>
       </c>
       <c r="T30" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W30" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="X30" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="Y30" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z30" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA30">
         <v>20</v>
       </c>
       <c r="AB30" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD30" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF30" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="AG30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH30" t="s">
-        <v>189</v>
+        <v>50</v>
       </c>
       <c r="AI30" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="AJ30" t="s">
-        <v>295</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D31" t="s">
-        <v>296</v>
+        <v>267</v>
       </c>
       <c r="E31" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="F31" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G31" t="s">
-        <v>291</v>
+        <v>46261</v>
+      </c>
+      <c r="G31">
+        <v>9</v>
       </c>
       <c r="H31" t="s">
-        <v>256</v>
+        <v>141</v>
       </c>
       <c r="I31" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -4446,75 +4389,75 @@
         <v>13262</v>
       </c>
       <c r="T31" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W31" t="s">
-        <v>298</v>
+        <v>142</v>
       </c>
       <c r="X31" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="Y31" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z31" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA31">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB31" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD31" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF31" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="AG31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH31" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="AI31" t="s">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AJ31" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D32" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="E32" t="s">
-        <v>303</v>
+        <v>273</v>
       </c>
       <c r="F32" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G32" t="s">
-        <v>97</v>
+        <v>46261</v>
+      </c>
+      <c r="G32">
+        <v>9</v>
       </c>
       <c r="H32" t="s">
-        <v>71</v>
+        <v>274</v>
       </c>
       <c r="I32" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="R32">
         <v>1</v>
@@ -4523,75 +4466,75 @@
         <v>13262</v>
       </c>
       <c r="T32" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W32" t="s">
-        <v>101</v>
+        <v>275</v>
       </c>
       <c r="X32" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="Y32" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z32" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA32">
         <v>15</v>
       </c>
       <c r="AB32" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD32" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF32" t="s">
-        <v>305</v>
+        <v>44</v>
       </c>
       <c r="AG32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH32" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="AI32" t="s">
-        <v>306</v>
+        <v>277</v>
       </c>
       <c r="AJ32" t="s">
-        <v>307</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s">
-        <v>308</v>
+        <v>279</v>
       </c>
       <c r="E33" t="s">
-        <v>309</v>
+        <v>280</v>
       </c>
       <c r="F33" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G33" t="s">
-        <v>119</v>
+        <v>46261</v>
+      </c>
+      <c r="G33">
+        <v>2</v>
       </c>
       <c r="H33" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="I33" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -4600,75 +4543,75 @@
         <v>13262</v>
       </c>
       <c r="T33" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W33" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
       <c r="X33" t="s">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="Y33" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z33" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA33">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB33" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC33" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AD33" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF33" t="s">
-        <v>305</v>
+        <v>278</v>
       </c>
       <c r="AG33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH33" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AI33" t="s">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="AJ33" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="E34" t="s">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="F34" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G34" t="s">
-        <v>116</v>
+        <v>46261</v>
+      </c>
+      <c r="G34">
+        <v>10</v>
       </c>
       <c r="H34" t="s">
-        <v>71</v>
+        <v>138</v>
       </c>
       <c r="I34" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -4677,75 +4620,75 @@
         <v>13262</v>
       </c>
       <c r="T34" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W34" t="s">
-        <v>105</v>
+        <v>160</v>
       </c>
       <c r="X34" t="s">
-        <v>314</v>
+        <v>285</v>
       </c>
       <c r="Y34" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z34" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA34">
+        <v>15</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC34" t="s">
         <v>40</v>
       </c>
-      <c r="AB34" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC34" t="s">
-        <v>41</v>
-      </c>
       <c r="AD34" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF34" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="AG34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH34" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="AI34" t="s">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="AJ34" t="s">
-        <v>87</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D35" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="E35" t="s">
-        <v>318</v>
+        <v>288</v>
       </c>
       <c r="F35" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G35" t="s">
-        <v>120</v>
+        <v>46261</v>
+      </c>
+      <c r="G35">
+        <v>10</v>
       </c>
       <c r="H35" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="I35" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R35">
         <v>1</v>
@@ -4754,78 +4697,72 @@
         <v>13262</v>
       </c>
       <c r="T35" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V35" t="s">
-        <v>319</v>
+        <v>38</v>
       </c>
       <c r="W35" t="s">
-        <v>253</v>
+        <v>89</v>
       </c>
       <c r="X35" t="s">
-        <v>320</v>
+        <v>289</v>
       </c>
       <c r="Y35" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="Z35" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA35">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AB35" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC35" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="AD35" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE35" t="s">
-        <v>321</v>
+        <v>49</v>
       </c>
       <c r="AF35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AH35" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="AI35" t="s">
-        <v>322</v>
-      </c>
-      <c r="AJ35" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D36" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
       <c r="E36" t="s">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="F36" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G36" t="s">
-        <v>121</v>
+        <v>46261</v>
+      </c>
+      <c r="G36">
+        <v>10</v>
       </c>
       <c r="H36" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="I36" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -4834,75 +4771,72 @@
         <v>13262</v>
       </c>
       <c r="T36" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W36" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="X36" t="s">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="Y36" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="Z36" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA36">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AB36" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC36" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="AD36" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF36" t="s">
-        <v>316</v>
+        <v>44</v>
       </c>
       <c r="AG36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH36" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="AI36" t="s">
-        <v>98</v>
-      </c>
-      <c r="AJ36" t="s">
-        <v>131</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="D37" t="s">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="E37" t="s">
-        <v>329</v>
+        <v>296</v>
       </c>
       <c r="F37" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G37" t="s">
-        <v>327</v>
+        <v>46261</v>
+      </c>
+      <c r="G37">
+        <v>10</v>
       </c>
       <c r="H37" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="I37" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -4911,75 +4845,72 @@
         <v>13262</v>
       </c>
       <c r="T37" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W37" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="X37" t="s">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="Y37" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="Z37" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA37">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB37" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC37" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="AD37" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF37" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="AG37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH37" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="AI37" t="s">
-        <v>331</v>
-      </c>
-      <c r="AJ37" t="s">
-        <v>332</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B38" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="D38" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
       <c r="E38" t="s">
-        <v>335</v>
+        <v>300</v>
       </c>
       <c r="F38" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G38" t="s">
-        <v>333</v>
+        <v>46261</v>
+      </c>
+      <c r="G38">
+        <v>10</v>
       </c>
       <c r="H38" t="s">
-        <v>71</v>
+        <v>301</v>
       </c>
       <c r="I38" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R38">
         <v>1</v>
@@ -4988,75 +4919,72 @@
         <v>13262</v>
       </c>
       <c r="T38" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W38" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="X38" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="Y38" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="Z38" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA38">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB38" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC38" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="AD38" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF38" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="AG38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH38" t="s">
-        <v>189</v>
+        <v>65</v>
       </c>
       <c r="AI38" t="s">
-        <v>337</v>
-      </c>
-      <c r="AJ38" t="s">
-        <v>338</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="D39" t="s">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="E39" t="s">
-        <v>340</v>
+        <v>306</v>
       </c>
       <c r="F39" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G39" t="s">
-        <v>333</v>
+        <v>46261</v>
+      </c>
+      <c r="G39">
+        <v>10</v>
       </c>
       <c r="H39" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I39" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="R39">
         <v>1</v>
@@ -5065,75 +4993,72 @@
         <v>13262</v>
       </c>
       <c r="T39" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W39" t="s">
-        <v>124</v>
+        <v>307</v>
       </c>
       <c r="X39" t="s">
-        <v>341</v>
+        <v>308</v>
       </c>
       <c r="Y39" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="Z39" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA39">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB39" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC39" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="AD39" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF39" t="s">
-        <v>342</v>
+        <v>44</v>
       </c>
       <c r="AG39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AH39" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AI39" t="s">
-        <v>343</v>
-      </c>
-      <c r="AJ39" t="s">
-        <v>48</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="D40" t="s">
-        <v>344</v>
+        <v>310</v>
       </c>
       <c r="E40" t="s">
-        <v>345</v>
+        <v>311</v>
       </c>
       <c r="F40" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G40">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H40" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="I40" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R40">
         <v>1</v>
@@ -5142,75 +5067,75 @@
         <v>13262</v>
       </c>
       <c r="T40" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W40" t="s">
-        <v>346</v>
+        <v>213</v>
       </c>
       <c r="X40" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="Y40" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z40" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA40">
         <v>20</v>
       </c>
       <c r="AB40" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC40" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD40" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF40" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="AG40" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH40" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="AI40" t="s">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="AJ40" t="s">
-        <v>349</v>
+        <v>314</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="D41" t="s">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="E41" t="s">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="F41" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G41">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H41" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="I41" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -5219,75 +5144,75 @@
         <v>13262</v>
       </c>
       <c r="T41" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W41" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="X41" t="s">
-        <v>352</v>
+        <v>317</v>
       </c>
       <c r="Y41" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z41" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA41">
         <v>24</v>
       </c>
       <c r="AB41" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD41" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF41" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="AG41" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH41" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="AI41" t="s">
-        <v>353</v>
+        <v>318</v>
       </c>
       <c r="AJ41" t="s">
-        <v>354</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="E42" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
       <c r="F42" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G42">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H42" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="I42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R42">
         <v>1</v>
@@ -5296,75 +5221,72 @@
         <v>13262</v>
       </c>
       <c r="T42" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W42" t="s">
-        <v>357</v>
+        <v>275</v>
       </c>
       <c r="X42" t="s">
-        <v>358</v>
+        <v>322</v>
       </c>
       <c r="Y42" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z42" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA42">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB42" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC42" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD42" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF42" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="AG42" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH42" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AI42" t="s">
-        <v>359</v>
-      </c>
-      <c r="AJ42" t="s">
-        <v>360</v>
+        <v>323</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D43" t="s">
+        <v>324</v>
+      </c>
+      <c r="E43" t="s">
+        <v>325</v>
+      </c>
+      <c r="F43" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G43">
+        <v>7</v>
+      </c>
+      <c r="H43" t="s">
         <v>64</v>
       </c>
-      <c r="B43" t="s">
-        <v>79</v>
-      </c>
-      <c r="D43" t="s">
-        <v>361</v>
-      </c>
-      <c r="E43" t="s">
-        <v>362</v>
-      </c>
-      <c r="F43" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G43">
-        <v>10</v>
-      </c>
-      <c r="H43" t="s">
-        <v>71</v>
-      </c>
       <c r="I43" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="R43">
         <v>1</v>
@@ -5373,75 +5295,75 @@
         <v>13262</v>
       </c>
       <c r="T43" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W43" t="s">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="X43" t="s">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="Y43" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z43" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA43">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AB43" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC43" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD43" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF43" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG43" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AH43" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="AI43" t="s">
-        <v>364</v>
+        <v>327</v>
       </c>
       <c r="AJ43" t="s">
-        <v>365</v>
+        <v>328</v>
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" t="s">
+        <v>71</v>
+      </c>
+      <c r="D44" t="s">
+        <v>329</v>
+      </c>
+      <c r="E44" t="s">
+        <v>330</v>
+      </c>
+      <c r="F44" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G44">
+        <v>8</v>
+      </c>
+      <c r="H44" t="s">
         <v>64</v>
       </c>
-      <c r="B44" t="s">
-        <v>79</v>
-      </c>
-      <c r="D44" t="s">
-        <v>366</v>
-      </c>
-      <c r="E44" t="s">
-        <v>367</v>
-      </c>
-      <c r="F44" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G44">
-        <v>11</v>
-      </c>
-      <c r="H44" t="s">
-        <v>156</v>
-      </c>
       <c r="I44" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R44">
         <v>1</v>
@@ -5450,75 +5372,75 @@
         <v>13262</v>
       </c>
       <c r="T44" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W44" t="s">
-        <v>164</v>
+        <v>331</v>
       </c>
       <c r="X44" t="s">
-        <v>368</v>
+        <v>332</v>
       </c>
       <c r="Y44" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z44" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA44">
         <v>20</v>
       </c>
       <c r="AB44" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC44" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF44" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG44" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH44" t="s">
         <v>52</v>
       </c>
-      <c r="AD44" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF44" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG44" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH44" t="s">
-        <v>44</v>
-      </c>
       <c r="AI44" t="s">
-        <v>369</v>
+        <v>333</v>
       </c>
       <c r="AJ44" t="s">
-        <v>370</v>
+        <v>334</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" t="s">
+        <v>71</v>
+      </c>
+      <c r="D45" t="s">
+        <v>335</v>
+      </c>
+      <c r="E45" t="s">
+        <v>336</v>
+      </c>
+      <c r="F45" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G45">
+        <v>9</v>
+      </c>
+      <c r="H45" t="s">
         <v>64</v>
       </c>
-      <c r="B45" t="s">
-        <v>79</v>
-      </c>
-      <c r="D45" t="s">
-        <v>371</v>
-      </c>
-      <c r="E45" t="s">
-        <v>372</v>
-      </c>
-      <c r="F45" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G45">
-        <v>12</v>
-      </c>
-      <c r="H45" t="s">
-        <v>71</v>
-      </c>
       <c r="I45" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -5527,75 +5449,75 @@
         <v>13262</v>
       </c>
       <c r="T45" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W45" t="s">
-        <v>373</v>
+        <v>337</v>
       </c>
       <c r="X45" t="s">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="Y45" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA45">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB45" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC45" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD45" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AH45" t="s">
-        <v>189</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s">
-        <v>375</v>
+        <v>339</v>
       </c>
       <c r="AJ45" t="s">
-        <v>376</v>
+        <v>340</v>
       </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B46" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D46" t="s">
-        <v>377</v>
+        <v>341</v>
       </c>
       <c r="E46" t="s">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="F46" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G46">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H46" t="s">
-        <v>379</v>
+        <v>51</v>
       </c>
       <c r="I46" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R46">
         <v>1</v>
@@ -5604,75 +5526,75 @@
         <v>13262</v>
       </c>
       <c r="T46" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W46" t="s">
-        <v>380</v>
+        <v>103</v>
       </c>
       <c r="X46" t="s">
-        <v>381</v>
+        <v>343</v>
       </c>
       <c r="Y46" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z46" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA46">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB46" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC46" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD46" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF46" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG46" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AH46" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AI46" t="s">
-        <v>382</v>
+        <v>344</v>
       </c>
       <c r="AJ46" t="s">
-        <v>383</v>
+        <v>345</v>
       </c>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D47" t="s">
-        <v>384</v>
+        <v>346</v>
       </c>
       <c r="E47" t="s">
-        <v>385</v>
+        <v>347</v>
       </c>
       <c r="F47" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G47">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H47" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="I47" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="R47">
         <v>1</v>
@@ -5681,75 +5603,75 @@
         <v>13262</v>
       </c>
       <c r="T47" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W47" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="X47" t="s">
-        <v>386</v>
+        <v>348</v>
       </c>
       <c r="Y47" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z47" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA47">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AB47" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC47" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD47" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF47" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG47" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AH47" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="AI47" t="s">
-        <v>387</v>
+        <v>349</v>
       </c>
       <c r="AJ47" t="s">
-        <v>388</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" t="s">
+        <v>71</v>
+      </c>
+      <c r="D48" t="s">
+        <v>351</v>
+      </c>
+      <c r="E48" t="s">
+        <v>352</v>
+      </c>
+      <c r="F48" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G48">
+        <v>11</v>
+      </c>
+      <c r="H48" t="s">
         <v>64</v>
       </c>
-      <c r="B48" t="s">
-        <v>79</v>
-      </c>
-      <c r="D48" t="s">
-        <v>389</v>
-      </c>
-      <c r="E48" t="s">
-        <v>390</v>
-      </c>
-      <c r="F48" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G48">
-        <v>14</v>
-      </c>
-      <c r="H48" t="s">
-        <v>156</v>
-      </c>
       <c r="I48" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="R48">
         <v>1</v>
@@ -5758,75 +5680,75 @@
         <v>13262</v>
       </c>
       <c r="T48" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V48" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W48" t="s">
-        <v>391</v>
+        <v>353</v>
       </c>
       <c r="X48" t="s">
-        <v>392</v>
+        <v>354</v>
       </c>
       <c r="Y48" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z48" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA48">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB48" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC48" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD48" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF48" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG48" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AH48" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="AI48" t="s">
-        <v>393</v>
+        <v>355</v>
       </c>
       <c r="AJ48" t="s">
-        <v>394</v>
+        <v>356</v>
       </c>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D49" t="s">
-        <v>395</v>
+        <v>357</v>
       </c>
       <c r="E49" t="s">
-        <v>396</v>
+        <v>358</v>
       </c>
       <c r="F49" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G49">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H49" t="s">
-        <v>397</v>
+        <v>359</v>
       </c>
       <c r="I49" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="R49">
         <v>1</v>
@@ -5835,75 +5757,75 @@
         <v>13262</v>
       </c>
       <c r="T49" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W49" t="s">
-        <v>398</v>
+        <v>160</v>
       </c>
       <c r="X49" t="s">
-        <v>399</v>
+        <v>360</v>
       </c>
       <c r="Y49" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z49" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA49">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB49" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC49" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD49" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AH49" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AI49" t="s">
-        <v>400</v>
+        <v>361</v>
       </c>
       <c r="AJ49" t="s">
-        <v>87</v>
+        <v>362</v>
       </c>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>59</v>
+      </c>
+      <c r="B50" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" t="s">
+        <v>363</v>
+      </c>
+      <c r="E50" t="s">
+        <v>364</v>
+      </c>
+      <c r="F50" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G50">
+        <v>12</v>
+      </c>
+      <c r="H50" t="s">
         <v>64</v>
       </c>
-      <c r="B50" t="s">
-        <v>79</v>
-      </c>
-      <c r="D50" t="s">
-        <v>401</v>
-      </c>
-      <c r="E50" t="s">
-        <v>402</v>
-      </c>
-      <c r="F50" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G50">
-        <v>15</v>
-      </c>
-      <c r="H50" t="s">
-        <v>71</v>
-      </c>
       <c r="I50" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R50">
         <v>1</v>
@@ -5912,75 +5834,75 @@
         <v>13262</v>
       </c>
       <c r="T50" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W50" t="s">
-        <v>403</v>
+        <v>365</v>
       </c>
       <c r="X50" t="s">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="Y50" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z50" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA50">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB50" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC50" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD50" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AH50" t="s">
-        <v>405</v>
+        <v>72</v>
       </c>
       <c r="AI50" t="s">
-        <v>406</v>
+        <v>367</v>
       </c>
       <c r="AJ50" t="s">
-        <v>407</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B51" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D51" t="s">
-        <v>408</v>
+        <v>369</v>
       </c>
       <c r="E51" t="s">
-        <v>409</v>
+        <v>370</v>
       </c>
       <c r="F51" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G51">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H51" t="s">
-        <v>55</v>
+        <v>263</v>
       </c>
       <c r="I51" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="R51">
         <v>1</v>
@@ -5989,75 +5911,72 @@
         <v>13262</v>
       </c>
       <c r="T51" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W51" t="s">
-        <v>410</v>
+        <v>264</v>
       </c>
       <c r="X51" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="Y51" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z51" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA51">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB51" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC51" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD51" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF51" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG51" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AH51" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="AI51" t="s">
-        <v>412</v>
-      </c>
-      <c r="AJ51" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D52" t="s">
-        <v>414</v>
+        <v>373</v>
       </c>
       <c r="E52" t="s">
-        <v>415</v>
+        <v>374</v>
       </c>
       <c r="F52" s="1">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="G52">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H52" t="s">
-        <v>71</v>
+        <v>274</v>
       </c>
       <c r="I52" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="R52">
         <v>1</v>
@@ -6066,75 +5985,72 @@
         <v>13262</v>
       </c>
       <c r="T52" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V52" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W52" t="s">
-        <v>416</v>
+        <v>275</v>
       </c>
       <c r="X52" t="s">
-        <v>417</v>
+        <v>375</v>
       </c>
       <c r="Y52" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z52" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA52">
         <v>15</v>
       </c>
       <c r="AB52" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC52" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD52" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF52" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG52" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AH52" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="AI52" t="s">
-        <v>418</v>
-      </c>
-      <c r="AJ52" t="s">
-        <v>419</v>
+        <v>376</v>
       </c>
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" t="s">
+        <v>73</v>
+      </c>
+      <c r="D53" t="s">
+        <v>378</v>
+      </c>
+      <c r="E53" t="s">
+        <v>379</v>
+      </c>
+      <c r="F53" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G53">
+        <v>5</v>
+      </c>
+      <c r="H53" t="s">
         <v>64</v>
       </c>
-      <c r="B53" t="s">
-        <v>79</v>
-      </c>
-      <c r="D53" t="s">
-        <v>420</v>
-      </c>
-      <c r="E53" t="s">
-        <v>421</v>
-      </c>
-      <c r="F53" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G53">
-        <v>16</v>
-      </c>
-      <c r="H53" t="s">
-        <v>422</v>
-      </c>
       <c r="I53" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R53">
         <v>1</v>
@@ -6143,75 +6059,75 @@
         <v>13262</v>
       </c>
       <c r="T53" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W53" t="s">
-        <v>423</v>
+        <v>380</v>
       </c>
       <c r="X53" t="s">
-        <v>424</v>
+        <v>381</v>
       </c>
       <c r="Y53" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="Z53" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA53">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB53" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC53" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF53" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG53" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH53" t="s">
         <v>52</v>
       </c>
-      <c r="AD53" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF53" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG53" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH53" t="s">
-        <v>72</v>
-      </c>
       <c r="AI53" t="s">
-        <v>425</v>
+        <v>382</v>
       </c>
       <c r="AJ53" t="s">
-        <v>426</v>
+        <v>383</v>
       </c>
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>84</v>
+      </c>
+      <c r="B54" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54" t="s">
+        <v>384</v>
+      </c>
+      <c r="E54" t="s">
+        <v>385</v>
+      </c>
+      <c r="F54" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G54">
+        <v>5</v>
+      </c>
+      <c r="H54" t="s">
         <v>64</v>
       </c>
-      <c r="B54" t="s">
-        <v>81</v>
-      </c>
-      <c r="D54" t="s">
-        <v>427</v>
-      </c>
-      <c r="E54" t="s">
-        <v>428</v>
-      </c>
-      <c r="F54" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G54" t="s">
-        <v>125</v>
-      </c>
-      <c r="H54" t="s">
-        <v>71</v>
-      </c>
       <c r="I54" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="R54">
         <v>1</v>
@@ -6220,75 +6136,75 @@
         <v>13262</v>
       </c>
       <c r="T54" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W54" t="s">
-        <v>416</v>
+        <v>113</v>
       </c>
       <c r="X54" t="s">
-        <v>429</v>
+        <v>386</v>
       </c>
       <c r="Y54" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z54" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA54">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AB54" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC54" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD54" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF54" t="s">
-        <v>46</v>
+        <v>377</v>
       </c>
       <c r="AG54" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH54" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="AI54" t="s">
-        <v>430</v>
+        <v>387</v>
       </c>
       <c r="AJ54" t="s">
-        <v>48</v>
+        <v>388</v>
       </c>
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="B55" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D55" t="s">
-        <v>431</v>
+        <v>390</v>
       </c>
       <c r="E55" t="s">
-        <v>432</v>
+        <v>391</v>
       </c>
       <c r="F55" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G55" t="s">
-        <v>125</v>
+        <v>46261</v>
+      </c>
+      <c r="G55">
+        <v>9</v>
       </c>
       <c r="H55" t="s">
-        <v>71</v>
+        <v>263</v>
       </c>
       <c r="I55" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="R55">
         <v>1</v>
@@ -6297,75 +6213,75 @@
         <v>13262</v>
       </c>
       <c r="T55" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V55" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W55" t="s">
-        <v>346</v>
+        <v>264</v>
       </c>
       <c r="X55" t="s">
-        <v>433</v>
+        <v>392</v>
       </c>
       <c r="Y55" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z55" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA55">
         <v>20</v>
       </c>
       <c r="AB55" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD55" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF55" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG55" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH55" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI55" t="s">
+        <v>393</v>
+      </c>
+      <c r="AJ55" t="s">
         <v>46</v>
-      </c>
-      <c r="AG55" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH55" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI55" t="s">
-        <v>434</v>
-      </c>
-      <c r="AJ55" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>59</v>
+      </c>
+      <c r="B56" t="s">
+        <v>67</v>
+      </c>
+      <c r="D56" t="s">
+        <v>394</v>
+      </c>
+      <c r="E56" t="s">
+        <v>395</v>
+      </c>
+      <c r="F56" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+      <c r="H56" t="s">
         <v>64</v>
       </c>
-      <c r="B56" t="s">
-        <v>81</v>
-      </c>
-      <c r="D56" t="s">
-        <v>436</v>
-      </c>
-      <c r="E56" t="s">
-        <v>437</v>
-      </c>
-      <c r="F56" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G56" t="s">
-        <v>125</v>
-      </c>
-      <c r="H56" t="s">
-        <v>55</v>
-      </c>
       <c r="I56" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -6374,75 +6290,75 @@
         <v>13262</v>
       </c>
       <c r="T56" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V56" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W56" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="X56" t="s">
-        <v>438</v>
+        <v>396</v>
       </c>
       <c r="Y56" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z56" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA56">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB56" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD56" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF56" t="s">
-        <v>91</v>
+        <v>397</v>
       </c>
       <c r="AG56" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH56" t="s">
         <v>43</v>
       </c>
-      <c r="AH56" t="s">
-        <v>77</v>
-      </c>
       <c r="AI56" t="s">
-        <v>439</v>
+        <v>398</v>
       </c>
       <c r="AJ56" t="s">
-        <v>48</v>
+        <v>399</v>
       </c>
     </row>
     <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" t="s">
+        <v>67</v>
+      </c>
+      <c r="D57" t="s">
+        <v>400</v>
+      </c>
+      <c r="E57" t="s">
+        <v>401</v>
+      </c>
+      <c r="F57" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G57">
+        <v>3</v>
+      </c>
+      <c r="H57" t="s">
         <v>64</v>
       </c>
-      <c r="B57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D57" t="s">
-        <v>440</v>
-      </c>
-      <c r="E57" t="s">
-        <v>441</v>
-      </c>
-      <c r="F57" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G57" t="s">
-        <v>126</v>
-      </c>
-      <c r="H57" t="s">
-        <v>84</v>
-      </c>
       <c r="I57" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="R57">
         <v>1</v>
@@ -6451,75 +6367,75 @@
         <v>13262</v>
       </c>
       <c r="T57" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W57" t="s">
-        <v>442</v>
+        <v>85</v>
       </c>
       <c r="X57" t="s">
-        <v>443</v>
+        <v>402</v>
       </c>
       <c r="Y57" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="Z57" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA57">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AB57" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD57" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF57" t="s">
-        <v>46</v>
+        <v>397</v>
       </c>
       <c r="AG57" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH57" t="s">
-        <v>405</v>
+        <v>50</v>
       </c>
       <c r="AI57" t="s">
-        <v>444</v>
+        <v>403</v>
       </c>
       <c r="AJ57" t="s">
-        <v>48</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D58" t="s">
-        <v>445</v>
+        <v>404</v>
       </c>
       <c r="E58" t="s">
-        <v>446</v>
+        <v>405</v>
       </c>
       <c r="F58" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G58" t="s">
-        <v>127</v>
+        <v>46261</v>
+      </c>
+      <c r="G58">
+        <v>3</v>
       </c>
       <c r="H58" t="s">
-        <v>264</v>
+        <v>51</v>
       </c>
       <c r="I58" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="R58">
         <v>1</v>
@@ -6528,75 +6444,75 @@
         <v>13262</v>
       </c>
       <c r="T58" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W58" t="s">
-        <v>357</v>
+        <v>92</v>
       </c>
       <c r="X58" t="s">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="Y58" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z58" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA58">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB58" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC58" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD58" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF58" t="s">
-        <v>46</v>
+        <v>397</v>
       </c>
       <c r="AG58" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH58" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AI58" t="s">
-        <v>448</v>
+        <v>407</v>
       </c>
       <c r="AJ58" t="s">
-        <v>271</v>
+        <v>350</v>
       </c>
     </row>
     <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" t="s">
+        <v>67</v>
+      </c>
+      <c r="D59" t="s">
+        <v>408</v>
+      </c>
+      <c r="E59" t="s">
+        <v>409</v>
+      </c>
+      <c r="F59" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G59">
+        <v>4</v>
+      </c>
+      <c r="H59" t="s">
         <v>64</v>
       </c>
-      <c r="B59" t="s">
-        <v>81</v>
-      </c>
-      <c r="D59" t="s">
-        <v>449</v>
-      </c>
-      <c r="E59" t="s">
-        <v>450</v>
-      </c>
-      <c r="F59" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G59" t="s">
-        <v>127</v>
-      </c>
-      <c r="H59" t="s">
-        <v>397</v>
-      </c>
       <c r="I59" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="R59">
         <v>1</v>
@@ -6605,75 +6521,75 @@
         <v>13262</v>
       </c>
       <c r="T59" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V59" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W59" t="s">
-        <v>451</v>
+        <v>410</v>
       </c>
       <c r="X59" t="s">
-        <v>452</v>
+        <v>411</v>
       </c>
       <c r="Y59" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="Z59" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA59">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB59" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC59" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="AD59" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF59" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG59" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH59" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI59" t="s">
+        <v>412</v>
+      </c>
+      <c r="AJ59" t="s">
         <v>46</v>
-      </c>
-      <c r="AG59" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH59" t="s">
-        <v>95</v>
-      </c>
-      <c r="AI59" t="s">
-        <v>453</v>
-      </c>
-      <c r="AJ59" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" t="s">
+        <v>413</v>
+      </c>
+      <c r="E60" t="s">
+        <v>414</v>
+      </c>
+      <c r="F60" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G60">
+        <v>4</v>
+      </c>
+      <c r="H60" t="s">
         <v>64</v>
       </c>
-      <c r="B60" t="s">
-        <v>81</v>
-      </c>
-      <c r="D60" t="s">
-        <v>454</v>
-      </c>
-      <c r="E60" t="s">
-        <v>455</v>
-      </c>
-      <c r="F60" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G60" t="s">
-        <v>127</v>
-      </c>
-      <c r="H60" t="s">
-        <v>156</v>
-      </c>
       <c r="I60" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="R60">
         <v>1</v>
@@ -6682,75 +6598,75 @@
         <v>13262</v>
       </c>
       <c r="T60" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V60" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W60" t="s">
-        <v>164</v>
+        <v>415</v>
       </c>
       <c r="X60" t="s">
-        <v>456</v>
+        <v>416</v>
       </c>
       <c r="Y60" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z60" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA60">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB60" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD60" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF60" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG60" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH60" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI60" t="s">
+        <v>412</v>
+      </c>
+      <c r="AJ60" t="s">
         <v>46</v>
-      </c>
-      <c r="AG60" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH60" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI60" t="s">
-        <v>457</v>
-      </c>
-      <c r="AJ60" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="61" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>67</v>
+      </c>
+      <c r="D61" t="s">
+        <v>417</v>
+      </c>
+      <c r="E61" t="s">
+        <v>418</v>
+      </c>
+      <c r="F61" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G61">
+        <v>17</v>
+      </c>
+      <c r="H61" t="s">
         <v>64</v>
       </c>
-      <c r="B61" t="s">
-        <v>81</v>
-      </c>
-      <c r="D61" t="s">
-        <v>458</v>
-      </c>
-      <c r="E61" t="s">
-        <v>459</v>
-      </c>
-      <c r="F61" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G61" t="s">
-        <v>128</v>
-      </c>
-      <c r="H61" t="s">
-        <v>84</v>
-      </c>
       <c r="I61" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R61">
         <v>1</v>
@@ -6759,75 +6675,75 @@
         <v>13262</v>
       </c>
       <c r="T61" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W61" t="s">
-        <v>124</v>
+        <v>419</v>
       </c>
       <c r="X61" t="s">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="Y61" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z61" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA61">
         <v>20</v>
       </c>
       <c r="AB61" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC61" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD61" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF61" t="s">
-        <v>46</v>
+        <v>421</v>
       </c>
       <c r="AG61" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AH61" t="s">
         <v>54</v>
       </c>
       <c r="AI61" t="s">
-        <v>461</v>
+        <v>313</v>
       </c>
       <c r="AJ61" t="s">
-        <v>48</v>
+        <v>422</v>
       </c>
     </row>
     <row r="62" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>59</v>
+      </c>
+      <c r="B62" t="s">
+        <v>67</v>
+      </c>
+      <c r="D62" t="s">
+        <v>423</v>
+      </c>
+      <c r="E62" t="s">
+        <v>424</v>
+      </c>
+      <c r="F62" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G62">
+        <v>17</v>
+      </c>
+      <c r="H62" t="s">
         <v>64</v>
       </c>
-      <c r="B62" t="s">
-        <v>81</v>
-      </c>
-      <c r="D62" t="s">
-        <v>462</v>
-      </c>
-      <c r="E62" t="s">
-        <v>463</v>
-      </c>
-      <c r="F62" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G62" t="s">
-        <v>128</v>
-      </c>
-      <c r="H62" t="s">
-        <v>55</v>
-      </c>
       <c r="I62" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="R62">
         <v>1</v>
@@ -6836,75 +6752,78 @@
         <v>13262</v>
       </c>
       <c r="T62" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V62" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="W62" t="s">
-        <v>464</v>
+        <v>166</v>
       </c>
       <c r="X62" t="s">
-        <v>465</v>
+        <v>425</v>
       </c>
       <c r="Y62" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="Z62" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA62">
         <v>15</v>
       </c>
       <c r="AB62" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD62" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE62" t="s">
+        <v>100</v>
+      </c>
+      <c r="AF62" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG62" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH62" t="s">
         <v>52</v>
       </c>
-      <c r="AF62" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG62" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH62" t="s">
-        <v>54</v>
-      </c>
       <c r="AI62" t="s">
-        <v>466</v>
+        <v>168</v>
       </c>
       <c r="AJ62" t="s">
-        <v>48</v>
+        <v>426</v>
       </c>
     </row>
     <row r="63" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D63" t="s">
-        <v>467</v>
+        <v>427</v>
       </c>
       <c r="E63" t="s">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="F63" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G63" t="s">
-        <v>129</v>
+        <v>46261</v>
+      </c>
+      <c r="G63">
+        <v>18</v>
       </c>
       <c r="H63" t="s">
-        <v>71</v>
+        <v>389</v>
       </c>
       <c r="I63" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="R63">
         <v>1</v>
@@ -6913,75 +6832,75 @@
         <v>13262</v>
       </c>
       <c r="T63" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V63" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="W63" t="s">
-        <v>292</v>
+        <v>86</v>
       </c>
       <c r="X63" t="s">
-        <v>469</v>
+        <v>429</v>
       </c>
       <c r="Y63" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="Z63" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA63">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB63" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AC63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD63" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AF63" t="s">
+        <v>430</v>
+      </c>
+      <c r="AG63" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI63" t="s">
+        <v>431</v>
+      </c>
+      <c r="AJ63" t="s">
         <v>46</v>
-      </c>
-      <c r="AG63" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH63" t="s">
-        <v>189</v>
-      </c>
-      <c r="AI63" t="s">
-        <v>470</v>
-      </c>
-      <c r="AJ63" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="64" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>59</v>
+      </c>
+      <c r="B64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D64" t="s">
+        <v>432</v>
+      </c>
+      <c r="E64" t="s">
+        <v>433</v>
+      </c>
+      <c r="F64" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G64">
+        <v>18</v>
+      </c>
+      <c r="H64" t="s">
         <v>64</v>
       </c>
-      <c r="B64" t="s">
-        <v>83</v>
-      </c>
-      <c r="D64" t="s">
-        <v>472</v>
-      </c>
-      <c r="E64" t="s">
-        <v>473</v>
-      </c>
-      <c r="F64" s="1">
-        <v>46260</v>
-      </c>
-      <c r="G64" t="s">
-        <v>96</v>
-      </c>
-      <c r="H64" t="s">
-        <v>71</v>
-      </c>
       <c r="I64" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="R64">
         <v>1</v>
@@ -6990,49 +6909,357 @@
         <v>13262</v>
       </c>
       <c r="T64" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V64" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W64" t="s">
+        <v>231</v>
+      </c>
+      <c r="X64" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA64">
+        <v>20</v>
+      </c>
+      <c r="AB64" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC64" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD64" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF64" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG64" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH64" t="s">
+        <v>72</v>
+      </c>
+      <c r="AI64" t="s">
+        <v>435</v>
+      </c>
+      <c r="AJ64" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>59</v>
+      </c>
+      <c r="B65" t="s">
+        <v>75</v>
+      </c>
+      <c r="D65" t="s">
+        <v>436</v>
+      </c>
+      <c r="E65" t="s">
+        <v>437</v>
+      </c>
+      <c r="F65" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G65">
+        <v>3</v>
+      </c>
+      <c r="H65" t="s">
+        <v>96</v>
+      </c>
+      <c r="I65" t="s">
+        <v>58</v>
+      </c>
+      <c r="R65">
+        <v>1</v>
+      </c>
+      <c r="S65">
+        <v>13262</v>
+      </c>
+      <c r="T65" t="s">
+        <v>83</v>
+      </c>
+      <c r="V65" t="s">
+        <v>38</v>
+      </c>
+      <c r="W65" t="s">
+        <v>113</v>
+      </c>
+      <c r="X65" t="s">
+        <v>438</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA65">
+        <v>30</v>
+      </c>
+      <c r="AB65" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD65" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF65" t="s">
+        <v>439</v>
+      </c>
+      <c r="AG65" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH65" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI65" t="s">
+        <v>440</v>
+      </c>
+      <c r="AJ65" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" t="s">
+        <v>75</v>
+      </c>
+      <c r="D66" t="s">
+        <v>441</v>
+      </c>
+      <c r="E66" t="s">
+        <v>442</v>
+      </c>
+      <c r="F66" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G66">
+        <v>2</v>
+      </c>
+      <c r="H66" t="s">
         <v>141</v>
       </c>
-      <c r="X64" t="s">
-        <v>474</v>
-      </c>
-      <c r="Y64" t="s">
+      <c r="I66" t="s">
+        <v>47</v>
+      </c>
+      <c r="R66">
+        <v>1</v>
+      </c>
+      <c r="S66">
+        <v>13262</v>
+      </c>
+      <c r="T66" t="s">
+        <v>83</v>
+      </c>
+      <c r="V66" t="s">
+        <v>38</v>
+      </c>
+      <c r="W66" t="s">
+        <v>142</v>
+      </c>
+      <c r="X66" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA66">
+        <v>20</v>
+      </c>
+      <c r="AB66" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC66" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF66" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG66" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH66" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI66" t="s">
+        <v>444</v>
+      </c>
+      <c r="AJ66" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>59</v>
+      </c>
+      <c r="B67" t="s">
+        <v>75</v>
+      </c>
+      <c r="D67" t="s">
+        <v>446</v>
+      </c>
+      <c r="E67" t="s">
+        <v>447</v>
+      </c>
+      <c r="F67" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G67">
+        <v>4</v>
+      </c>
+      <c r="H67" t="s">
+        <v>51</v>
+      </c>
+      <c r="I67" t="s">
+        <v>37</v>
+      </c>
+      <c r="R67">
+        <v>1</v>
+      </c>
+      <c r="S67">
+        <v>13262</v>
+      </c>
+      <c r="T67" t="s">
+        <v>83</v>
+      </c>
+      <c r="V67" t="s">
+        <v>38</v>
+      </c>
+      <c r="W67" t="s">
         <v>92</v>
       </c>
-      <c r="Z64" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA64">
-        <v>15</v>
-      </c>
-      <c r="AB64" t="s">
-        <v>90</v>
-      </c>
-      <c r="AC64" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD64" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF64" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG64" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH64" t="s">
+      <c r="X67" t="s">
+        <v>448</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA67">
+        <v>24</v>
+      </c>
+      <c r="AB67" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD67" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF67" t="s">
         <v>44</v>
       </c>
-      <c r="AI64" t="s">
-        <v>475</v>
-      </c>
-      <c r="AJ64" t="s">
+      <c r="AG67" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH67" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI67" t="s">
+        <v>449</v>
+      </c>
+      <c r="AJ67" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>59</v>
+      </c>
+      <c r="B68" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" t="s">
+        <v>450</v>
+      </c>
+      <c r="E68" t="s">
+        <v>451</v>
+      </c>
+      <c r="F68" s="1">
+        <v>46261</v>
+      </c>
+      <c r="G68">
+        <v>5</v>
+      </c>
+      <c r="H68" t="s">
+        <v>263</v>
+      </c>
+      <c r="I68" t="s">
+        <v>57</v>
+      </c>
+      <c r="R68">
+        <v>1</v>
+      </c>
+      <c r="S68">
+        <v>13262</v>
+      </c>
+      <c r="T68" t="s">
+        <v>83</v>
+      </c>
+      <c r="V68" t="s">
+        <v>38</v>
+      </c>
+      <c r="W68" t="s">
+        <v>264</v>
+      </c>
+      <c r="X68" t="s">
+        <v>452</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z68" t="s">
         <v>48</v>
+      </c>
+      <c r="AA68">
+        <v>20</v>
+      </c>
+      <c r="AB68" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC68" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD68" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF68" t="s">
+        <v>439</v>
+      </c>
+      <c r="AG68" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH68" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI68" t="s">
+        <v>453</v>
+      </c>
+      <c r="AJ68" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BA8DCB-B176-46CA-BF9F-AE1782149AB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B3E42C-1BC6-4E0D-8545-03F284AC25B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="465">
   <si>
     <t>Canal</t>
   </si>
@@ -166,9 +166,6 @@
     <t>Noticia</t>
   </si>
   <si>
-    <t>Portada</t>
-  </si>
-  <si>
     <t>Sí</t>
   </si>
   <si>
@@ -211,9 +208,6 @@
     <t>Lizania Zavala</t>
   </si>
   <si>
-    <t>DIFH</t>
-  </si>
-  <si>
     <t>SSH</t>
   </si>
   <si>
@@ -232,9 +226,6 @@
     <t>El Sol de Hidalgo</t>
   </si>
   <si>
-    <t>Saderh</t>
-  </si>
-  <si>
     <t>El Universal Hidalgo</t>
   </si>
   <si>
@@ -256,9 +247,6 @@
     <t>Milenio Hidalgo</t>
   </si>
   <si>
-    <t>Semarnath</t>
-  </si>
-  <si>
     <t>Veida Martínez Miranda</t>
   </si>
   <si>
@@ -283,9 +271,6 @@
     <t>Julio Menchaca Salazar</t>
   </si>
   <si>
-    <t>Sedeco</t>
-  </si>
-  <si>
     <t>Cabeza</t>
   </si>
   <si>
@@ -295,9 +280,6 @@
     <t>Secundaria</t>
   </si>
   <si>
-    <t>María Antonieta Islas</t>
-  </si>
-  <si>
     <t>Tiraje</t>
   </si>
   <si>
@@ -313,1102 +295,1153 @@
     <t>Carmen Hernández</t>
   </si>
   <si>
-    <t>Gustavo Vargas</t>
-  </si>
-  <si>
-    <t>Apoyo A Jóvenes</t>
-  </si>
-  <si>
-    <t>Impulso a las artes</t>
-  </si>
-  <si>
-    <t>ZMVM</t>
-  </si>
-  <si>
     <t>Obras De Infraestructura</t>
   </si>
   <si>
     <t>Turismo</t>
   </si>
   <si>
-    <t>Producción agrícola</t>
-  </si>
-  <si>
     <t>Sonia Nochebuena</t>
   </si>
   <si>
     <t>Hidalgo</t>
   </si>
   <si>
-    <t>Afluencia Turística</t>
-  </si>
-  <si>
-    <t>Nathali González</t>
-  </si>
-  <si>
     <t>Boletín</t>
   </si>
   <si>
     <t>Comunicado gubernamental</t>
   </si>
   <si>
-    <t>Marco Cerón</t>
-  </si>
-  <si>
-    <t>Salud materna</t>
-  </si>
-  <si>
     <t>Evento Cultural</t>
   </si>
   <si>
-    <t>Luis Godínez</t>
-  </si>
-  <si>
-    <t>Centros para los migrantes recibirán 2.5 mdp cada uno</t>
-  </si>
-  <si>
-    <t>El DIF Hidalgo destinará recursos federales de aproximadamente 2.5 millones de pesos por sede para restaurar y operar centros de atención a migrantes. El titular del organismo, Ricardo Enrique Alvizo Contreras, señaló que ante la baja afluencia momentánea de movilidad migratoria, los espacios albergarán temporalmente a 62 artesanos que visitarán Huejutla y a unos 160 que acudirán a la Feria de Pachuca.</t>
-  </si>
-  <si>
-    <t>Apoyo A Migrantes</t>
-  </si>
-  <si>
-    <t>El DIF Hidalgo destinará recursos federales de 2.5 mdp por sede para rehabilitar centros de migración, habilitándolos temporalmente como albergues para artesanos locales.</t>
-  </si>
-  <si>
-    <t>Sistema DIF Hidalgo, Secretaría de Cultura</t>
-  </si>
-  <si>
-    <t>Ricardo Enrique Alvizo Contreras</t>
-  </si>
-  <si>
-    <t>“Cada quien responde por su trayectoria”: Julio Menchaca</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar deslindó su responsabilidad frente a la designación de Adán Augusto López Hernández como coordinador electoral de Morena en la cuarta circunscripción, tras los señalamientos contra el tabasqueño sobre su presunta relación con el grupo delictivo La Barredora. "Cada quien tiene que responder por su trayectoria y yo no puedo ser aval de nadie más que mío", precisó.</t>
-  </si>
-  <si>
-    <t>Trabajo partidista</t>
-  </si>
-  <si>
-    <t>El gobernador de Hidalgo evitó respaldar la trayectoria del senador Adán Augusto López tras críticas de la oposición por supuestas relaciones delictivas.</t>
-  </si>
-  <si>
-    <t>Morena</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Adán Augusto López Hernández</t>
-  </si>
-  <si>
-    <t>Buscan incorporar 30 municipios a la ZMVM</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar anunció que buscarán que se concrete la incorporación de 30 demarcaciones del estado a la Zona Metropolitana del Valle de México (ZMVM) para unificar planes de urbanismo, servicios y medio ambiente, tras celebrarse la entrada en vigor del decreto federal que sumó a ocho municipios del sur.</t>
-  </si>
-  <si>
-    <t>Hidalgo impulsará la adhesión de 30 municipios a la Zona Metropolitana del Valle de México tras oficializarse la incorporación de ocho demarcaciones del sur.</t>
-  </si>
-  <si>
-    <t>Diario Oficial de la Federación, Sedatu, Gobiernos de Hidalgo, CDMX y Edomex</t>
-  </si>
-  <si>
-    <t>Citnova destina $50 millones para entrega de 220 becas</t>
-  </si>
-  <si>
-    <t>El director del Citnova, Francisco Patiño Cardona, informó la entrega de 220 apoyos educativos para posgrados y proyectos en la entidad con un presupuesto de 50 millones de pesos. Consiste en 115 becas de posgrado nacionales (15 mil pesos al mes) y en el extranjero (36 mil pesos al mes), así como 105 apoyos del Fondo Hidalgo para desarrollos de impacto social.</t>
-  </si>
-  <si>
-    <t>Becas</t>
-  </si>
-  <si>
-    <t>Citnova canalizó una bolsa presupuestal de 50 mdp para financiar 220 becas de posgrado y proyectos de innovación científica en beneficio del desarrollo local.</t>
-  </si>
-  <si>
-    <t>Consejo de Ciencia, Tecnología e Innovación de Hidalgo</t>
-  </si>
-  <si>
-    <t>Francisco Patiño Cardona</t>
-  </si>
-  <si>
-    <t>Salvador Cruz se pronuncia ante muertes</t>
-  </si>
-  <si>
-    <t>El titular de la SSPH, Salvador Cruz Neri, informó que se les dota de atención médica prioritaria a los presos de la entidad ante el registro de decesos relacionados con enfermedades crónicas e incidencias de suicidios en el penal de Tulancingo y Tula. Explicó que se abrieron carpetas de investigación correspondientes ante la PGJEH.</t>
-  </si>
-  <si>
-    <t>Deficiencias Ceresos</t>
-  </si>
-  <si>
-    <t>El secretario de Seguridad, Salvador Cruz Neri, informó que se dio intervención a la PGJEH tras registrarse decesos de internos en los penales locales.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, PGJEH</t>
-  </si>
-  <si>
     <t>Salvador Cruz Neri</t>
   </si>
   <si>
-    <t>Comercializa China obsidiana de Hidalgo</t>
-  </si>
-  <si>
-    <t>Francisco Patiño Cardona, titular del Citnova, reveló el plagio y comercialización en aeropuertos internacionales de máscaras chinas con obsidiana del Nopalillo, Epazoyucan, por hasta 40 mil pesos, frente al costo artesanal local de 5 mil pesos. Explicó que se investiga la morfología a nivel atómico para patentar la huella molecular de la roca.</t>
-  </si>
-  <si>
-    <t>Epazoyucan</t>
-  </si>
-  <si>
-    <t>Registro de patente</t>
-  </si>
-  <si>
-    <t>El Citnova identificó la imitación tecnológica de artesanías locales de obsidiana por productores chinos, iniciando gestiones de laboratorio para patentar el mineral.</t>
-  </si>
-  <si>
     <t>Huejutla</t>
   </si>
   <si>
-    <t>Vinculan a proceso a 7 por retención del edil de San Salvador</t>
-  </si>
-  <si>
-    <t>El juez penal de los Juzgados de Pachuca vinculó a proceso a siete personas (Carmela, Arely, Silvia, Rubén, Justino, Isaías y Rubén) acusadas de privación de la libertad, daños y lesiones dolosas en agravio del alcalde Norberto Martínez Corona. Continuarán el proceso con resguardo domiciliario cautelar por los próximos tres meses.</t>
-  </si>
-  <si>
-    <t>San Salvador</t>
-  </si>
-  <si>
-    <t>Vinculación A Proceso</t>
-  </si>
-  <si>
-    <t>La fiscalía obtuvo auto de vinculación a proceso y prisión domiciliaria provisional para siete pobladores implicados en agresiones y la retención del edil.</t>
-  </si>
-  <si>
-    <t>Juzgados Penales de Pachuca, Procuraduría General de Justicia del Estado, Ayuntamiento de San Salvador</t>
-  </si>
-  <si>
-    <t>Norberto Martínez Corona, Carmela, Arely, Silvia, Rubén, Justino, Isaías</t>
-  </si>
-  <si>
-    <t>Van por sueldos dignos para personal de la UBR</t>
-  </si>
-  <si>
-    <t>La alcaldesa de Tulancingo, Lorena García Cázares, y el DIF Hidalgo acordaron la entrega en comodato de la nueva sede de la UBR al organismo asistencial estatal. Se coordinan modificaciones a la Ley de Ingresos municipal para garantizar sueldos dignos e incrementar tarifas equitativas y retener neurólogos de alto perfil.</t>
-  </si>
-  <si>
-    <t>Rehabilitación UBR</t>
-  </si>
-  <si>
-    <t>La alcaldía de Tulancingo acordó ceder la operación del centro rehabilitador neuronal al DIF estatal para subsanar los bajos salarios.</t>
-  </si>
-  <si>
-    <t>Sistema DIF Hidalgo, Ayuntamiento de Tulancingo, UBR</t>
-  </si>
-  <si>
-    <t>Lorena García Cázares, Edda Vite Ramos</t>
-  </si>
-  <si>
-    <t>Tulancingo emprende una campaña de recuperación y saneamiento forestal</t>
-  </si>
-  <si>
-    <t>La Secretaría del Campo de Tulancingo, encabezada por Hugo Flores Jiménez, y la Conafor iniciaron podas de saneamiento forestal contra la plaga del gusano descortezador. Se plantaron 500 pinos Montezumae en el parque El Camaleón (parte de una donación de 2 mil pinos) para reforestar ejidos críticos como Tulancingo y límites de Acaxochitlán.</t>
-  </si>
-  <si>
-    <t>Saneamiento forestal</t>
-  </si>
-  <si>
-    <t>La Secretaría del Campo municipal e inspectores de Conafor ejecutan barridos químicos y podas técnicas para detener el avance del gusano descortezador.</t>
-  </si>
-  <si>
-    <t>Comisión Nacional Forestal, Secretaría del Campo municipal, Asociación de Silvicultores</t>
-  </si>
-  <si>
-    <t>Hugo Flores Jiménez, Arturo Gómez Canales</t>
-  </si>
-  <si>
-    <t>DIF Huejutla reconoce a adultos mayores</t>
-  </si>
-  <si>
-    <t>El DIF de Huejutla coordinó jornadas recreativas para más de 300 adscritos al CAAM en la celebración de la Semana del Adulto Mayor. Kristel Rodríguez Flores lideró las actividades físicas de envejecimiento activo de cara a la celebración del 28 de agosto, además de ofrecerles un desayuno y obsequios tradicionales.</t>
-  </si>
-  <si>
     <t>Apoyo a adultos mayores</t>
   </si>
   <si>
-    <t>El Sistema DIF de Huejutla organizó jornadas lúdicas de salud e integración para conmemorar el Día de los Adultos Mayores.</t>
-  </si>
-  <si>
-    <t>Sistema DIF Huejutla, Ayuntamiento municipal, CAAM</t>
-  </si>
-  <si>
-    <t>Kristel Rodríguez Flores</t>
-  </si>
-  <si>
-    <t>IHE prepara ciclo escolar 2026-2027</t>
-  </si>
-  <si>
-    <t>En representación de Natividad Castrejón Valdez, la coordinadora de educación básica Nancy Adriana León Vite encabezó los trabajos del Consejo Técnico Escolar (CTE) del IHE. Se definieron los programas pedagógicos de la Guía Operativa, los maratones de lectura y los programas de contención emocional del ciclo 2026-2027.</t>
-  </si>
-  <si>
     <t>Capacitación docente</t>
   </si>
   <si>
-    <t>La subsecretaria de educación básica lideró el diseño de planes de seguridad escolar y prevención del maltrato infantil con directivos.</t>
-  </si>
-  <si>
-    <t>Instituto Hidalguense de Educación, Dirección General de Educación Básica</t>
-  </si>
-  <si>
-    <t>Nancy Adriana León Vite, Natividad Castrejón Valdez</t>
-  </si>
-  <si>
-    <t>Nueva plaza comercial en el sur de Pachuca</t>
-  </si>
-  <si>
-    <t>En diciembre de 2026 podría ser la apertura de la nueva plaza comercial Paseo Bonfil, ubicada en el bulevar Ramón G. Bonfil, al sur de Pachuca, de acuerdo con trabajadores de la obra. El diseño está a cargo de Metagrama Diseño Arquitectónico. Albergará marcas como Banregio, Home Store, Promoda, Coppel, un Walmart Supercenter y un gimnasio. Se prevé generar 345 empleos directos e indirectos.</t>
-  </si>
-  <si>
     <t>Desarrollo Urbano</t>
   </si>
   <si>
-    <t>Se proyecta para diciembre de 2026 la apertura de la plaza comercial Paseo Bonfil en el sur de Pachuca, estimándose la generación de 345 empleos.</t>
-  </si>
-  <si>
-    <t>Ayuntamiento de Pachuca</t>
-  </si>
-  <si>
-    <t>La obesidad infantil en México no se detiene, pese a sellos</t>
-  </si>
-  <si>
-    <t>En 2017 México tenía 10 millones de niños y adolescentes con sobrepeso y obesidad, una de las tasas más altas del mundo. Se hizo el etiquetado frontal, se reguló la comida chatarra de las escuelas, se regularon los anuncios. Sin embargo, para 2025 la cifra alcanzó los 11.4 millones, según datos de la ENSANUT, UNICEF y OMS.</t>
-  </si>
-  <si>
-    <t>Obesidad infantil</t>
-  </si>
-  <si>
-    <t>A pesar de la implementación de sellos de advertencia y regulaciones publicitarias, la obesidad infantil en México aumentó a 11.4 millones en 2025.</t>
-  </si>
-  <si>
-    <t>ENSANUT, UNICEF, OMS</t>
-  </si>
-  <si>
-    <t>Niega Cruz Neri fallas en penales de Hidalgo</t>
-  </si>
-  <si>
-    <t>El titular de la Secretaría de Seguridad Pública de Hidalgo (SSPH), Salvador Cruz Neri, negó que existan fallas de seguridad en los penales del estado tras los decesos de internos reportados en Tulancingo e Ixmiquilpan, aclarando que cada caso es investigado. Explicó que cuando un interno requiere atención médica es trasladado a un hospital. Por otra parte, señaló que el rezago en profesionalización policial reportado por el INEGI no refleja el estatus real porque corresponden al 26.9% de policías con Certificado Único Policial (CUP).</t>
-  </si>
-  <si>
-    <t>El titular de la SSPH, Salvador Cruz Neri, rechazó la existencia de fallas sistemáticas en los Ceresos y justificó las métricas de certificación policial.</t>
-  </si>
-  <si>
-    <t>Blanca Soriano</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, INEGI, PGJEH</t>
-  </si>
-  <si>
-    <t>Salvador Cruz Neri, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Inaugura Menchaca cuartel de Policía</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar inauguró el nuevo cuartel de la Policía Estatal en la colonia Cubitos de Pachuca, con una inversión superior a 22 millones de pesos. El inmueble albergará a 86 graduados de la academia y contará con tres unidades especializadas (Grupo Táctico, Vialidad Metropolitana y Medidas de Protección). El secretario de Obras Públicas, Alejandro Sánchez García, refirió que la obra forma parte de la dignificación del parque vehicular e inmobiliario estatal.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca inauguró el nuevo Cuartel de la Policía Estatal en Cubitos, el cual contó con una inversión de 22 millones de pesos.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Sipdus</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Salvador Cruz Neri, Alejandro Sánchez García, Julio César Meléndez Coria</t>
-  </si>
-  <si>
-    <t>Los Centros Gerontológicos están a tu disposición</t>
-  </si>
-  <si>
-    <t>Campaña oficial del Sistema DIF Hidalgo y la Secretaría de Bienestar para difundir los servicios que ofrecen los Centros Gerontológicos Integrales para personas mayores de 60 años. Incluye servicios de salud (medicina, odontología, enfermería, nutrición), atención psicológica, talleres de convivencia (manualidades, pintura, karaoke) y terapia física.</t>
-  </si>
-  <si>
-    <t>El Sistema DIF Hidalgo difundió la red de atención y terapias gratuitas que ofrecen sus Centros Gerontológicos Integrales para adultos mayores.</t>
-  </si>
-  <si>
-    <t>Sistema DIF Hidalgo, Secretaría de Bienestar e Inclusión Social</t>
-  </si>
-  <si>
-    <t>Geriátricos, opción para adultos mayores</t>
-  </si>
-  <si>
-    <t>Encontrar un espacio adecuado para el cuidado de adultos mayores es una creciente necesidad en Pachuca. La Fundación de Beneficencia María Domínguez Viuda de Álvarez, en Parque Hidalgo, ofrece servicios de estancia diurna y permanente para personas mayores de 65 años. Cuenta con servicios de salud, alimentación y terapias físicas con un costo promedio de 8 mil 500 pesos.</t>
-  </si>
-  <si>
-    <t>Atención adultos mayores</t>
-  </si>
-  <si>
-    <t>La Casa de Descanso Vida en Pachuca promueve esquemas de estancia gerontológica subsidiada con servicios integrales de terapia y de nutrición.</t>
-  </si>
-  <si>
-    <t>Sistema DIF Hidalgo, Fundación de Beneficencia María Domínguez Viuda de Álvarez</t>
-  </si>
-  <si>
-    <t>Edda Vite Ramos, María Domínguez Viuda de Álvarez</t>
-  </si>
-  <si>
-    <t>Tus emociones no giran al azar, tú puedes manejarlas</t>
-  </si>
-  <si>
-    <t>Campaña oficial institucional de la SEPH y el IHE orientada a promover la salud mental de los estudiantes de educación básica y media superior mediante el reconocimiento, manejo y gestión de las emociones de manera saludable. Pone a disposición canales de contacto de la Dirección General de Acompañamiento Socioemocional y Educativo.</t>
-  </si>
-  <si>
-    <t>Educación socioemocional</t>
-  </si>
-  <si>
-    <t>La SEPH y el IHE promueven el programa permanente de educación socioemocional en las escuelas públicas hidalguenses.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Instituto Hidalguense de Educación (IHE)</t>
-  </si>
-  <si>
-    <t>En hidalgo se hablará de panteones y rituales</t>
-  </si>
-  <si>
-    <t>En el Auditorio Salvador Toscano del Centro INAH Hidalgo y en el Auditorio Abundio Martínez del Centro de las Artes de Hidalgo, se realizará el Décimo Coloquio Internacional de Historia del 9 al 11 de septiembre. El evento reunirá a especialistas de seis países (Argentina, Colombia, Guatemala, Perú, España, México) para analizar el patrimonio funerario y su valor histórico.</t>
-  </si>
-  <si>
-    <t>Hidalgo será sede del Décimo Coloquio Internacional de Historia que reunirá a expertos de seis países para debatir sobre el patrimonio funerario.</t>
-  </si>
-  <si>
-    <t>Centro INAH Hidalgo, Secretaría de Cultura de Hidalgo, Cecultah</t>
-  </si>
-  <si>
-    <t>Manuel Villarruel Vázquez, Neyda Naranjo Baltazar</t>
-  </si>
-  <si>
-    <t>Reciben apoyos para fortalecer negocios</t>
-  </si>
-  <si>
-    <t>En el Foro del Centro de Atención Infantil (CAI) Pitahayas de Pachuca, se realizó la entrega del apoyo mil del Sistema DIF Hidalgo, consistente en máquinas de coser, hornos y herramientas para repostería a personas de 16 municipios. El proyecto con una inversión de 1.96 mdp busca que los beneficiarios consoliden un autoempleo y sean autosuficientes.</t>
-  </si>
-  <si>
-    <t>Apoyo a emprendedores</t>
-  </si>
-  <si>
-    <t>El Sistema DIF Hidalgo entregó el apoyo productivo número mil de la administración para fomentar el autoempleo en 16 municipios.</t>
-  </si>
-  <si>
-    <t>Sistema DIF Hidalgo, Centro de Rehabilitación Integral Hidalgo (CRIH)</t>
-  </si>
-  <si>
-    <t>Edda Vite Ramos, Hector Villafuentes</t>
-  </si>
-  <si>
-    <t>Aguas termales brindan alivio en el cuerpo</t>
-  </si>
-  <si>
-    <t>Cada fin de semana, miles de turistas de diferentes partes del país visitan los balnearios de aguas termales en el Valle del Mezquital. Betsabé Atalia Sierra García, egresada de Ciencias de la Tierra de la UNAM, detalló que estas aguas, al encontrarse a temperaturas superiores a los 36°C, disuelven minerales y alivian dolores musculares, asma y rinitis.</t>
-  </si>
-  <si>
-    <t>Valle del Mezquital</t>
-  </si>
-  <si>
-    <t>Turistas del centro del país abarrotan los balnearios de aguas termales en el Mezquital, atraídos por sus facultades terapéuticas.</t>
-  </si>
-  <si>
-    <t>Omar Santiago</t>
-  </si>
-  <si>
-    <t>UNAM, Secretaría de Turismo de Hidalgo</t>
-  </si>
-  <si>
-    <t>Betsabé Atalia Sierra García</t>
-  </si>
-  <si>
-    <t>Escasez de Chinicuil incrementa el precio</t>
-  </si>
-  <si>
-    <t>Recolectores de chinicuil en el Valle del Mezquital reportan baja cosecha de la larva de color rosado debido al uso de aguas de riego que afectan las pencas del maguey. Antonio Cruz, recolector, explicó que la escasez ha provocado que el kilo del insecto alcance los dos mil pesos y la canasta de sardina los 550 pesos.</t>
-  </si>
-  <si>
-    <t>La escasez de la larva comestible de chinicuil por el uso de aguas residuales disparó su precio de venta en el Valle del Mezquital.</t>
-  </si>
-  <si>
-    <t>Asociación de Silvicultores</t>
-  </si>
-  <si>
-    <t>Antonio Cruz</t>
-  </si>
-  <si>
-    <t>Entrega el estado 50 mdp en becas y apoyos</t>
-  </si>
-  <si>
-    <t>El gobierno del estado adjudicó apoyos por un valor global de 50 mdp en beneficio de 220 investigadores y becarios hidalguenses, como parte de los programas Fondo Hidalgo y Becas de Excelencia coordinados por el Citnova. Hidalgo cuenta actualmente con 812 miembros del SNI.</t>
-  </si>
-  <si>
-    <t>Impulso a ciencia y tecnología</t>
-  </si>
-  <si>
-    <t>Hidalgo consolidó la entrega de estímulos científicos a 220 investigadores locales, proyectando alcanzar los mil 250 especialistas acreditados al cierre del sexenio.</t>
-  </si>
-  <si>
-    <t>Citnova, Sistema Nacional de Investigadores</t>
-  </si>
-  <si>
-    <t>“Subestación eléctrica, clave para atraer industria”</t>
-  </si>
-  <si>
-    <t>El delegado federal de la Secretaría de Economía reconoció que la escasez de capacidad energética representa un obstáculo primario para la inversión en Tulancingo, por lo que sostendrá encuentros técnicos con personal de la CFE y Sedeco para detonar el proyecto de una nueva subestación.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Economía y el gobierno de Hidalgo coordinan estudios para fundamentar la construcción de una nueva subestación eléctrica en la región de Tulancingo.</t>
-  </si>
-  <si>
     <t>Mirely Santos</t>
   </si>
   <si>
-    <t>Comisión Federal de Electricidad, Secretaría de Desarrollo Económico, Secretaría de Energía</t>
-  </si>
-  <si>
-    <t>Pedro Canales Vega</t>
-  </si>
-  <si>
-    <t>El Citnova prepara una nueva denuncia por más irregularidades</t>
-  </si>
-  <si>
-    <t>El Citnova prepara otra querella penal contra exservidores públicos de la pasada administración, tras interponer previamente una denuncia por la compra irregular e inoperante de una planta piloto para la producción de vacunas con valor de 21 mdp.</t>
-  </si>
-  <si>
-    <t>Denuncias</t>
-  </si>
-  <si>
-    <t>El Consejo de Ciencia y Tecnología dará a conocer nuevos expedientes de corrupción en la adquisición de infraestructura científica el próximo 9 de septiembre.</t>
-  </si>
-  <si>
-    <t>Citnova, PGJEH</t>
-  </si>
-  <si>
-    <t>El último timbre del ciclo... también puede ser el PRIMERO para el reciclaje</t>
-  </si>
-  <si>
-    <t>Campaña institucional orientada al acopio y reciclaje de materiales escolares en desuso (libros, libretas, revistas) recolectados en el Parque Ecológico Cubitos del 20 de julio al 30 de agosto, para evitar el desperdicio y promover la conservación ecológica.</t>
-  </si>
-  <si>
-    <t>Cultura de reciclaje</t>
-  </si>
-  <si>
-    <t>La Semarnath promueve el programa estatal de recolección de celulosa y papel escolar usado para fomentar la sostenibilidad en el retorno a clases.</t>
-  </si>
-  <si>
-    <t>Parque Ecológico Cubitos, Secretaría de Medio Ambiente de Hidalgo</t>
-  </si>
-  <si>
-    <t>Entregan apoyos productivos por $6.8 millones en dos municipios</t>
-  </si>
-  <si>
-    <t>La Saderh entregó insumos agrícolas, vientres ovinos, desbrozadoras, semillas e hijuelos de maguey a 546 productores ganaderos y ejidales de Tepeji del Río ($4.8 mdp) y Tlahuelilpan ($2.0 mdp) de forma directa.</t>
-  </si>
-  <si>
-    <t>Apoyo Al Agro</t>
-  </si>
-  <si>
-    <t>La Saderh Hidalgo ejecutó una inversión agropecuaria coordinada para tecnificar y reactivar la capacidad productiva del campo en la región de Tula.</t>
-  </si>
-  <si>
-    <t>Saderh de Hidalgo</t>
-  </si>
-  <si>
-    <t>Napoleón González Pérez</t>
-  </si>
-  <si>
-    <t>En riesgo por huachicol, más de 20 municipios</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar advirtió sobre el peligro latente e incendios en zonas urbanas por tomas clandestinas en 20 municipios del estado. El anuncio se dio al inaugurar el cuartel policial de Cubitos de Pachuca con valor de 22 mdp.</t>
-  </si>
-  <si>
     <t>Robo de hidrocarburo</t>
   </si>
   <si>
-    <t>El titular del Ejecutivo estatal alertó que el huachicol constituye una seria amenaza civil y ordenó el despliegue del Ejército y Guardia Nacional para blindar ductos.</t>
-  </si>
-  <si>
-    <t>FGR, Guardia Nacional, Sedena, SSPH, Gabinete de Seguridad</t>
-  </si>
-  <si>
-    <t>Detienen a seis sujetos en posesión de armas durante un operativo</t>
-  </si>
-  <si>
-    <t>La SSPH, el Ejército y la Guardia Nacional desplegaron un operativo coordinado en Tecozautla, logrando detener a seis personas y decomisar nueve armas de fuego de grueso calibre, cartuchos útiles, chalecos y ponchallantas.</t>
-  </si>
-  <si>
-    <t>Tecozautla</t>
-  </si>
-  <si>
-    <t>Estrategia de seguridad</t>
-  </si>
-  <si>
-    <t>Fuerzas coordinadas del Mando Único asestaron un golpe táctico en la Sierra Gorda al desarmar y arrestar a un grupo armado en Tecozautla.</t>
-  </si>
-  <si>
-    <t>SSPH, Defensa, Guardia Nacional</t>
-  </si>
-  <si>
-    <t>Vinculan a detenidos por agredir a alcalde</t>
-  </si>
-  <si>
-    <t>Un juez de control vinculó a proceso a siete personas (cuatro hombres y tres mujeres) bajo los cargos de robo, lesiones dolosas y privación ilegal de la libertad cometidos en agravio del alcalde de San Salvador, Norberto Martínez Cruz, imponiéndose prisión domiciliaria preventiva.</t>
-  </si>
-  <si>
-    <t>La PGJEH formalizó la vinculación judicial de siete comuneros implicados en la retención y agresiones físicas perpetradas contra el edil en días pasados.</t>
-  </si>
-  <si>
-    <t>Juzgados de Pachuca, Procuraduría General de Justicia de Hidalgo</t>
-  </si>
-  <si>
-    <t>Norberto Martínez Cruz, Jesús Anim Ope Islas, Carmela, Arely, Silvia, Rubén, Justino, Isaías</t>
-  </si>
-  <si>
-    <t>Capturan a cinco involucrados en distribución de estupefacientes en Tolcayuca</t>
-  </si>
-  <si>
-    <t>Mediante dos cateos conjuntos de la SSPH, PGJEH y Sedena en la Felipe Ángeles de Tolcayuca, se clausuraron dos predios dedicados al narcomenudeo, capturando a cinco hombres (uno de ellos menor) con 756 dosis de cristal y marihuana.</t>
-  </si>
-  <si>
-    <t>Tolcayuca</t>
-  </si>
-  <si>
-    <t>Combate Al Narcomenudeo</t>
-  </si>
-  <si>
-    <t>El Mando Coordinado desmanteló dos bodegas de almacenamiento de narcóticos en Tolcayuca tras un operativo de inteligencia operativa.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, PGJEH, Sedena, Ministerio Público</t>
-  </si>
-  <si>
     <t>Alejandro Reyes</t>
   </si>
   <si>
-    <t>Se combate a todos los delincuentes: Cruz Neri</t>
-  </si>
-  <si>
-    <t>El secretario de Seguridad Pública de Hidalgo, Salvador Cruz Neri, señaló que no se puede confirmar la presencia del Cártel Jalisco Nueva Generación (CJNG) en Hidalgo, luego de que autoridades federales detuvieran a 20 presuntos integrantes de este grupo delictivo en operativos coordinados en Hidalgo, Jalisco y Michoacán. Indicó que se combate a todos los grupos de la delincuencia que pretenden operar en la entidad.</t>
-  </si>
-  <si>
-    <t>El titular de la SSPH, Salvador Cruz Neri, rechazó confirmar operaciones activas del CJNG en el estado, afirmando que se detiene de forma general a todas las células criminales.</t>
-  </si>
-  <si>
-    <t>SSPH, Gobierno del Estado de Hidalgo, FGR, Guardia Nacional</t>
-  </si>
-  <si>
-    <t>Festejan a más de 300 abuelitos en Huejutla</t>
-  </si>
-  <si>
-    <t>El DIF municipal de Huejutla, presidido por Kristel Rodríguez Flores, organizó un convivio especial de conmemoración para más de 300 adultos mayores adscritos al Centro de Atención del Adulto Mayor (CAAM) en la víspera del Día del Adulto Mayor. Las actividades lúdicas forman parte de programas permanentes de envejecimiento activo.</t>
-  </si>
-  <si>
-    <t>El DIF de Huejutla festejó a más de 300 adultos mayores del CAAM con actividades culturales y recreativas para conmemorar el Día del Adulto Mayor.</t>
-  </si>
-  <si>
-    <t>Sistema DIF Huejutla, CAAM</t>
-  </si>
-  <si>
-    <t>Abren apoyos para jóvenes emprendedores</t>
-  </si>
-  <si>
-    <t>La Sebiso y el Inhjuve iniciaron el periodo de registro para recibir apoyos económicos del programa Transformando Emprendedores 2026, con montos de hasta 20 mil pesos para proyectos productivos, y Embajadores Juventud, con un subsidio de hasta 12 mil pesos.</t>
-  </si>
-  <si>
-    <t>El Inhjuve y la Sebiso abrieron la ventanilla presencial de recepción de solicitudes de los programas de apoyo al emprendimiento y capacitación de jóvenes.</t>
-  </si>
-  <si>
-    <t>Inhjuve, Secretaría de Bienestar e Inclusión Social</t>
-  </si>
-  <si>
-    <t>Hidalgo impulsa formación musical infantil</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura estatal distribuyó 275 instrumentos musicales para el programa federal de Semilleros Creativos de cinco municipios. La entrega forma parte de una inversión acumulada de 4 millones 351 mil pesos destinados a creadores de 38 demarcaciones.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura de Hidalgo ejerció 4.35 mdp en apoyos a creadores y dotó de 275 instrumentos a menores del programa Semilleros Creativos.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura de Hidalgo, Semilleros Creativos</t>
-  </si>
-  <si>
-    <t>Buscan reducir las muertes maternas en Hidalgo</t>
-  </si>
-  <si>
-    <t>Ante el registro de cinco defunciones de mujeres embarazadas en Hidalgo durante la semana epidemiológica 32, el sector salud estatal impulsará y coordinará trabajos con parteras tradicionales a través del Comité Estatal de Partería.</t>
-  </si>
-  <si>
-    <t>Las autoridades sanitarias de Hidalgo instalaron el Comité de Partería para contrarrestar los índices epidemiológicos de decesos gestacionales en la entidad.</t>
-  </si>
-  <si>
-    <t>Secretaría de Salud de Hidalgo</t>
-  </si>
-  <si>
-    <t>Sierra Alta recibe 11 mdp en apoyos</t>
-  </si>
-  <si>
-    <t>Ocho municipios de la Sierra Alta de Hidalgo recibieron apoyos estatales por un monto acumulado de 11 millones 110 mil pesos dirigidos a personas cuidadoras, madres trabajadoras y familias rurales a través de Sebiso, concentrando Bienestar y Desarrollo la mayor porción del subsidio con 7.87 mdp.</t>
-  </si>
-  <si>
-    <t>Sierra Alta</t>
-  </si>
-  <si>
-    <t>Programas Del Bienestar</t>
-  </si>
-  <si>
-    <t>La Secretaría de Bienestar de Hidalgo canalizó 11 mdp en subsidios de programas sociales para reactivar la economía familiar en ocho alcaldías serranas.</t>
-  </si>
-  <si>
-    <t>Secretaría de Bienestar e Inclusión Social</t>
-  </si>
-  <si>
-    <t>Llevan prevención de salud a comunidades en el estado</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo intensificó las actividades de medicina y prevención comunitaria mediante la red de Promotores de la Salud, quienes recorren colonias impartiendo pláticas y proporcionando herramientas para mejorar hábitos de vida.</t>
-  </si>
-  <si>
-    <t>Promoción De La Salud</t>
-  </si>
-  <si>
-    <t>Los Promotores de la Salud de la SSH redoblaron recorridos rurales de proximidad sanitaria para orientar hábitos alimenticios y prevenir padecimientos crónicos.</t>
-  </si>
-  <si>
-    <t>Secretaría de Salud de Hidalgo, Promotores de la Salud</t>
-  </si>
-  <si>
-    <t>Impulsa DIF estatal economía de familias vulnerables con entrega de proyectos productivos</t>
-  </si>
-  <si>
-    <t>El Centro de Asistencia Infantil Comunitario (CAIC) de Pachuca fue sede de la entrega de 32 proyectos productivos a familias de 16 municipios, con el objetivo de fortalecer su economía. El evento estuvo encabezado por la presidenta del Patronato del Sistema DIF Hidalgo, Edda Vite Ramos, destacando una inversión de 1 millón 962 mil 626.44 pesos, sumando 287 proyectos entregados durante la administración para emprendimientos de estética, cocina, carpintería, entre otros.</t>
-  </si>
-  <si>
-    <t>El Sistema DIF Hidalgo coordinó la entrega de 32 proyectos productivos a familias de 16 municipios para incentivar el autoempleo local.</t>
-  </si>
-  <si>
-    <t>Sistema DIF Hidalgo, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Edda Vite Ramos</t>
-  </si>
-  <si>
-    <t>Inauguran Cuartel de Policía Estatal en Cubitos; invierten 22 mdp</t>
-  </si>
-  <si>
-    <t>Con una inversión de 22 millones 325 mil 60 pesos y en una superficie de terreno de mil 550 metros cuadrados, el gobernador Julio Menchaca Salazar encabezó la inauguración del Cuartel de Policía Estatal de Cubitos, así como la toma de protesta de 116 egresados del Instituto de Formación Profesional. El secretario de Seguridad, Salvador Cruz Neri, señaló que el espacio cuenta con equipo de medidas de protección para atender a las víctimas del delito.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca inauguró el nuevo Cuartel de la Policía Estatal de Cubitos en Pachuca, ejecutado con una inversión de 22.3 mdp.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública, Instituto de Formación Profesional, Gobierno del Estado</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Salvador Cruz Neri</t>
-  </si>
-  <si>
-    <t>Detienen a presuntos narcomenudistas en Tolcayuca; hay un menor involucrado</t>
-  </si>
-  <si>
-    <t>Elementos de la SSPH detuvieron en Tolcayuca a cinco sujetos, entre ellos un menor de edad, dedicados a la distribución de droga, logrando el aseguramiento de dos inmuebles, una motocicleta, 593 dosis de mariguana, 163 de cristal, una báscula y tres teléfonos móviles en la col. Felipe Ángeles.</t>
-  </si>
-  <si>
-    <t>La SSPH desarticuló una célula de narcomenudeo en Tolcayuca al asegurar a cinco implicados con más de 750 dosis de sustancias.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Sedena, Procuraduría General de Justicia del Estado</t>
-  </si>
-  <si>
-    <t>Destaca Edda Vite Ramos la verdadera importancia de generar oportunidades</t>
-  </si>
-  <si>
-    <t>El Sistema DIF Hidalgo entregó 32 proyectos productivos de autoempleo (máquinas de coser, equipamiento para alimentos y repostería) a familias con personas con discapacidad de 16 municipios, con una inversión de 1 millón 962 mil 626.44 pesos, acumulando 287 proyectos productivos y más de 11.8 mdp ejecutados en la presente gestión.</t>
-  </si>
-  <si>
-    <t>La presidenta del DIF estatal, Edda Vite, formalizó la entrega de 32 financiamientos productivos de autoempleo para promover la inclusión laboral de personas con discapacidad.</t>
-  </si>
-  <si>
-    <t>Sistema DIF Hidalgo, Centros de Rehabilitación Integral de Hidalgo (CRIH), DIF Municipales</t>
-  </si>
-  <si>
-    <t>Edda Vite Ramos, Héctor Alberto Villa Fuentes, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Estudiantes del ITESA desarrollan prototipos de go-karts eléctricos</t>
-  </si>
-  <si>
-    <t>Estudiantes de octavo semestre de Ingeniería en Sistemas Automotrices de ITESA fabricaron dos prototipos funcionales de go-karts 100% eléctricos como parte de su formación en electromovilidad, integrando conocimientos de diseño y potencia automotriz bajo el Plan México y el proyecto federal Olinia.</t>
-  </si>
-  <si>
-    <t>Innovación tecnológica</t>
-  </si>
-  <si>
-    <t>Alumnos de ITESA desarrollaron dos vehículos eléctricos ligeros apegados al Plan México y a los programas nacionales para incentivar la manufactura de electromovilidad.</t>
-  </si>
-  <si>
-    <t>Instituto Tecnológico Superior del Oriente del Estado de Hidalgo (ITESA), Academia de Sistemas Automotrices, Secretaría de Educación Pública de Hidalgo</t>
-  </si>
-  <si>
-    <t>Joshio Guadalupe García Acosta, Diego Armando Reyes Cruz, Yonatan Castillo Morales, Aldair Muñoz Martínez, Brandon Domínguez Escorcia, Brandon Rodríguez Cruz, Diego Islas Franco, Dylan Alexander Blancas Carreto, Monserrat Ramírez Jasso, Julio César Hernández Munguía, Guillermo Álvarez Jiménez, Miguel Ángel Lazcano Zavala, Brayan Meneses Mentado, Jeremi Misael Acosta Mateo, Guillermo Canceco Fiel, Bryan Herrera Olvera, Edwin Romero Castelán, Efraín Pacheco Escobedo, Adolfo Lagos Franco Hernández, Saúl Sánchez Cruz</t>
-  </si>
-  <si>
-    <t>Consolida Gobierno de Hidalgo estrategia de impulso a producciones audiovisuales y liderazgo en locaciones</t>
-  </si>
-  <si>
-    <t>La Secretaría de Turismo reportó que Hidalgo ha albergado más de 95 producciones audiovisuales durante la actual administración. Elizabeth Quintanar organizó el foro especializado "Hidalgo en Escena" para captar filmaciones, y alista un recorrido de localización del 7 al 9 de septiembre.</t>
-  </si>
-  <si>
-    <t>Promoción turística</t>
-  </si>
-  <si>
-    <t>La Secturh promueve a la entidad como un escenario estratégico de rodaje de cine y de publicidad, acumulando 95 proyectos fílmicos consolidados.</t>
-  </si>
-  <si>
-    <t>Secretaría de Turismo de Hidalgo (Secturh), Comisión Mexicana de Filmaciones (Comefilm), Ayuntamiento de Zempoala, Ayuntamiento de Metztitlán</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Elizabeth Quintanar Gómez, Diana Álvarez Segoviano, Gabriel Vargas Godínez, María de la Luz Rodríguez Hernández</t>
-  </si>
-  <si>
-    <t>Estado de Hidalgo será sede del 10º Coloquio Internacional “Historia y Costumbres Funerarias”</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura estatal y el Centro INAH Hidalgo organizan el Décimo Coloquio de costumbres y patrimonio funerario del 9 al 11 de septiembre en Pachuca, reuniendo unas 50 ponencias de especialistas de cinco países que abordarán el valor social de los cementerios históricos.</t>
-  </si>
-  <si>
-    <t>Pachuca albergará el encuentro internacional de historia funeraria con expertos de Argentina, Brasil, Colombia, Guatemala, Perú y México.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura del Estado de Hidalgo, Centro INAH Hidalgo, Icomos Mexicano, Red Iberoamericana de Valoración y Gestión de Cementerios Patrimoniales, UNAM, UAM, Amigos Protectores del Panteón Inglés</t>
-  </si>
-  <si>
-    <t>Neyda Naranjo Baltazar, Ethel Herrera Moreno, Manuel Villarruel Vázquez, Luis Francisco Sánchez Fonseca</t>
-  </si>
-  <si>
-    <t>Julio Menchaca inaugura Cuartel en Pachuca de Soto de la Policía Estatal Cubitos</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar entregó de forma oficial el Cuartel Policial de Cubitos, Pachuca, el cual con una inversión de 22 millones 235 mil 60 pesos dotará de infraestructura, servicio médico y site de monitoreo a tres divisiones policiales operativas.</t>
-  </si>
-  <si>
-    <t>El titular del Ejecutivo inauguró el nuevo complejo de la policía estatal y acompañó la toma de protesta de 116 graduados de la academia.</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Secretaría de Seguridad Pública de Hidalgo, Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (Sipdus), Instituto de Formación Profesional</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Salvador Cruz Neri, Alejandro Sánchez García</t>
-  </si>
-  <si>
-    <t>Actualiza CCLEH todos sus servicios con el portal “Registro de Poderes”</t>
-  </si>
-  <si>
-    <t>El Centro de Conciliación Laboral de Hidalgo (CCLEH) habilitó la plataforma poderes.ccleh.gob.mx para facilitar la inscripción y consulta en línea de poderes notariales del sector empresarial, mejorando la seguridad, transparencia y agilizando las audiencias.</t>
-  </si>
-  <si>
-    <t>Innovación pública</t>
-  </si>
-  <si>
-    <t>La Secretaría del Trabajo e Hidalgo implementaron un portal digital que disminuye tiempos y elimina el uso de papel en procesos conciliatorios de empresas.</t>
-  </si>
-  <si>
-    <t>Centro de Conciliación Laboral del Estado de Hidalgo (CCLEH), Secretaría del Trabajo y Previsión Social de Hidalgo</t>
-  </si>
-  <si>
-    <t>Mariela Valero Mota</t>
-  </si>
-  <si>
-    <t>Concluye con gran éxito Curso de Envejecimiento Saludable en Tlaxcoapan</t>
-  </si>
-  <si>
-    <t>El IAAMEH concluyó con éxito el Curso Hidalgo de Envejecimiento Saludable tras tres meses de capacitación lúdica a 58 adultos mayores en Tlaxcoapan, entregando de forma complementaria 11 constancias de educación básica respaldadas por el IHEA.</t>
-  </si>
-  <si>
     <t>Tlaxcoapan</t>
   </si>
   <si>
-    <t>El organismo IAAMEH certificó a 58 personas de la tercera edad en envejecimiento activo y coordinó la entrega de certificados escolares en Tlaxcoapan.</t>
-  </si>
-  <si>
-    <t>Instituto para la Atención de las y los Adultos Mayores del Estado de Hidalgo (IAAMEH), Instituto Hidalguense de Educación para Adultos (IHEA), Casa de Día Tlaxcoapan</t>
-  </si>
-  <si>
-    <t>Penélope Apodaca Sinsel</t>
-  </si>
-  <si>
-    <t>Digitalizar trámites genera rápidamente mayor confianza en la ciudadanía</t>
-  </si>
-  <si>
-    <t>El titular de la Unidad de Planeación y Prospectiva, Miguel Ángel Tello Vargas, develo que la digitalización y simplificación de más de 900 trámites estatales bajo el Ruts disminuye requisitos innecesarios y abona a la trazabilidad institucional.</t>
-  </si>
-  <si>
-    <t>Simplificación de trámites</t>
-  </si>
-  <si>
-    <t>La Uplaph acelera el programa de gobierno digital en el estado, incorporando de manera gradual a dependencias y a los 84 cabildos en la plataforma RUTS.</t>
-  </si>
-  <si>
-    <t>Unidad de Planeación y Prospectiva de Hidalgo (Uplaph), Agencia de Transformación Digital y Telecomunicaciones (ATDT), Registro Único de Trámites y Servicios (RUTS)</t>
-  </si>
-  <si>
     <t>Miguel Ángel Tello Vargas</t>
   </si>
   <si>
-    <t>Base de Operaciones Interinstitucionales (BOI), asegura a grupo generador de violencia en Tecozautla</t>
-  </si>
-  <si>
-    <t>Fuerzas operativas del BOM (SSPH, Defensa, Guardia Nacional y policía municipal) capturaron en Tecozautla a seis masculinos a bordo de camionetas robadas, incautándoles un arsenal de 9 armas, 446 cartuchos, chalecos antibalas, 120 ponchallantas y narcóticos.</t>
-  </si>
-  <si>
-    <t>Un operativo de fuerzas coordinadas desarmó y arrestó a seis presuntos delincuentes implicados en narcomenudeo y posesión de material bélico en Tecozautla.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Secretaría de la Defensa Nacional, Guardia Nacional, Policía Municipal de Tecozautla, Ministerio Público</t>
-  </si>
-  <si>
-    <t>SSPH detiene 5 presuntos involucrados en distribución de droga en Tolcayuca</t>
-  </si>
-  <si>
-    <t>La SSPH, el Ejército y la Procuraduría desarticularon dos fincas identificadas como almacén y punto de comercio de droga en la colonia Felipe Ángeles en Tolcayuca, deteniendo a cinco individuos con 756 dosis de mariguana y cristal.</t>
-  </si>
-  <si>
-    <t>Autoridades asestaron un golpe al narcomenudeo en Tolcayuca tras ejecutar cateos coordinados que permitieron el arresto de cinco implicados.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Secretaría de la Defensa Nacional, Procuraduría General de Justicia del Estado, Ministerio Público</t>
-  </si>
-  <si>
-    <t>Oscar Raúl Pérez</t>
-  </si>
-  <si>
-    <t>Celebra la UPN 48 años de formar profesionales</t>
-  </si>
-  <si>
-    <t>La Universidad Pedagógica Nacional (UPN) conmemoró 48 años de contribuir a la profesionalización del magisterio y a la formación de especialistas en el campo educativo en México. En la entidad, la directora Marisol Vite destacó el crecimiento de la matrícula y la infraestructura.</t>
-  </si>
-  <si>
-    <t>Aniversario Universidades</t>
-  </si>
-  <si>
-    <t>La UPN-Hidalgo conmemoró el decreto de fundación de la institución, resaltando el incremento de su oferta de licenciaturas y posgrados académicos.</t>
-  </si>
-  <si>
-    <t>Universidad Pedagógica Nacional Hidalgo (UPN-H), Sección 15 del SNTE</t>
-  </si>
-  <si>
-    <t>Marisol Vite Vargas, Benigno Sánchez Naranjo, José López Portillo</t>
-  </si>
-  <si>
-    <t>“Yo no puedo ser aval de nadie”: Julio Menchaca</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar precisó que no será aval de la trayectoria de Adán Augusto López tras los señalamientos en su contra por presuntos vínculos delictivos en Tabasco. Sostuvo que mantiene una amistad con él pero cada quien debe responder por sus actos.</t>
-  </si>
-  <si>
-    <t>El gobernador aclaró que su plática con Adán Augusto López se dio bajo una relación institucional y de amistad, pero deslindó su trayectoria delictiva personal.</t>
-  </si>
-  <si>
-    <t>Gobernador del Estado de Hidalgo, Morena, Senado de la República</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Adán Augusto López Hernández, Hernán Bermúdez Requena</t>
-  </si>
-  <si>
     <t>Tula</t>
   </si>
   <si>
-    <t>Aseguran a generadores de violencia</t>
-  </si>
-  <si>
-    <t>La Base de Operaciones Interinstitucionales (BOM) detuvo en Tecozautla a seis hombres a bordo de dos camionetas robadas, incautándoles un arsenal de 9 armas (6 largas y 3 cortas), 22 cargadores, 446 cartuchos, chalecos, 120 ponchallantas y dosis de mariguana y cristal.</t>
-  </si>
-  <si>
-    <t>Fuerzas federales y del Mando Coordinado estatal detuvieron en Tecozautla a seis asaltantes armados en posesión de armas de fuego de grueso calibre y ponchallantas.</t>
-  </si>
-  <si>
-    <t>Base de Operaciones Mixtas (BOM), SSPH, Defensa, Guardia Nacional, Policía Municipal de Tecozautla, Ministerio Público</t>
-  </si>
-  <si>
-    <t>Menchaca se reúne con Adán tras su nombramiento como coordinador</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar confirmó haber recibido la semana pasada al senador Adán Augusto López Hernández, tras ser designado coordinador de Morena en la cuarta circunscripción. Respecto a los presuntos nexos del tabasqueño con la organización "La Barredora", Menchaca deslindó responsabilidades afirmando que cada quien debe responder por su trayectoria personal.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca se reunió con Adán Augusto López tras su nombramiento como coordinador de Morena, deslindándose de sus antecedentes personales.</t>
-  </si>
-  <si>
     <t>Adela Garmez</t>
   </si>
   <si>
-    <t>Gobierno del Estado de Hidalgo, Morena, Senado de la República</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Adán Augusto López Hernández, Ariadna Montiel, Marco Antonio Rico Mercado, Cuauhtémoc Ochoa</t>
-  </si>
-  <si>
-    <t>Detenidos dicen pertenecer a cárteles, pero no se ha podido comprobar: Neri</t>
-  </si>
-  <si>
-    <t>El comisionado Salvador Cruz Neri señaló que algunos detenidos en la entidad refieren pertenecer a bandas criminales nacionales como el CJNG para infundir temor, sin que se acredite su pertenencia real. Asimismo, justificó que el 90% de la policía estatal posee el CUP, aclarando que el Inegi incluyó a la PIBEH intramuros en el rezago.</t>
-  </si>
-  <si>
-    <t>El titular de la SSPH, Salvador Cruz Neri, rechazó confirmar la presencia formal del CJNG en el estado y defendió el índice de acreditación policial local.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Inegi, FGR, CJNG, PIBEH</t>
-  </si>
-  <si>
-    <t>Abren nuevo cuartel para la Policía Estatal en Cubitos</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar inauguró las instalaciones del nuevo cuartel policial en la col. Cubitos de Pachuca, ejecutado con una inversión de 22.3 mdp sobre una superficie de 1,550 m2. El inmueble albergará a 116 egresados de la academia estatal y contará con un site especializado de videovigilancia.</t>
-  </si>
-  <si>
-    <t>El mandatario Julio Menchaca formalizó el nuevo cuartel policial de Cubitos, proyectado como un complejo táctico funcional para la operación metropolitana.</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Secretaría de Seguridad Pública de Hidalgo, Sipdus, Instituto de Formación Profesional</t>
-  </si>
-  <si>
-    <t>Crece desnutrición severa; mujeres, las más afectadas</t>
-  </si>
-  <si>
-    <t>El boletín epidemiológico de la Secretaría de Salud federal devela un repunte del 50% en los diagnósticos hidalguenses de desnutrición severa en 2026, acumulando 129 casos frente a los 86 reportados el año anterior. El sexo femenino concentra la mayor incidencia con 71 querellas.</t>
-  </si>
-  <si>
-    <t>Vigilancia Epidemiológica</t>
-  </si>
-  <si>
-    <t>Estudios federales revelan que la desnutrición severa creció a 129 casos anuales en Hidalgo, afectando prioritariamente a la población femenina.</t>
-  </si>
-  <si>
-    <t>Secretaría de Salud federal, Dirección General de Epidemiología</t>
-  </si>
-  <si>
-    <t>Hidalgo suma tres muertes por covid-19 en una semana</t>
-  </si>
-  <si>
-    <t>El estado de Hidalgo registró tres decesos adicionales por covid-19 en el último reporte semanal, alcanzando un acumulado de 12 fallecimientos en lo que va del 2026. Esto posiciona a Hidalgo en la primera posición del país por decesos derivados de este virus.</t>
-  </si>
-  <si>
-    <t>Covid 19</t>
-  </si>
-  <si>
-    <t>Hidalgo lidera la tasa nacional de letalidad por covid-19 en el año tras confirmarse 12 decesos, concentrando el 23.5% de las muertes del país.</t>
-  </si>
-  <si>
-    <t>Entrega DIFH casi 2 mdp en proyectos productivos</t>
-  </si>
-  <si>
-    <t>El Sistema DIF Hidalgo formalizó la entrega de equipamiento y herramientas productivas a 32 familias vulnerables de 16 municipios que asisten a personas con discapacidad. La inversión superó el millón 962 mil pesos y contempla un riguroso acompañamiento de tres años para garantizar la viabilidad.</t>
-  </si>
-  <si>
-    <t>Apoyo a personas con discapacidad</t>
-  </si>
-  <si>
-    <t>El DIF estatal entregó 32 proyectos de repostería, costura y alimentos para impulsar la autosuficiencia económica de familias de escasos recursos.</t>
-  </si>
-  <si>
-    <t>Socorro Ávila</t>
-  </si>
-  <si>
-    <t>Edda Vite Ramos, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>IHE consolida planeación académica para el nuevo ciclo escolar 2026-2027</t>
-  </si>
-  <si>
-    <t>La coordinación de educación básica coordinó los trabajos intensivos del Consejo Técnico Escolar para delinear los ejes operativos y de seguridad del ciclo 2026-2027. Se revisaron las campañas de lectura, la Guía de Funcionamiento y la estrategia de educación socioemocional El Emocionario.</t>
-  </si>
-  <si>
-    <t>Autoridades de educación básica articularon las estrategias académicas y de prevención del maltrato infantil del nuevo periodo escolar.</t>
-  </si>
-  <si>
-    <t>Nancy Adriana León Vite, Leobardo Cano Albarrán, Grissel Martínez Aguilar, Claudia Huerta Ruiz, Samuel Nava Alcántara, Aurorita Fernanda Reyes</t>
-  </si>
-  <si>
-    <t>Tula: crecen lesiones y la violencia familiar</t>
-  </si>
-  <si>
-    <t>Estudios del SESNSP revelan que de enero a julio el delito de lesiones en Tula de Allende se incrementó un 31.6% en comparación anual, contabilizando 225 carpetas. El ilícito de violencia familiar aumentó 10.6% con 146 investigaciones, posicionándose como la problemática de mayor incidencia local.</t>
-  </si>
-  <si>
-    <t>El SESNSP reportó un aumento del 31% en agresiones dolosas y de violencia familiar en Tula, aunque se registró una reducción en robos y homicidios.</t>
-  </si>
-  <si>
-    <t>Joselyn Sánchez</t>
-  </si>
-  <si>
-    <t>Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública, Procuraduría General de Justicia del Estado, SSPH</t>
-  </si>
-  <si>
-    <t>Destina gobierno 50 mdp en becas y fondos para la ciencia e innovación</t>
-  </si>
-  <si>
-    <t>El director del Citnova, Francisco Patiño Cardona, detalló los apoyos asignados del Fondo Hidalgo 2026, consistentes en una inversión de 50 mdp. La bolsa canalizará 25 mdp para 105 investigaciones de alto impacto y otros 25 mdp para el financiamiento de 115 becas de maestría y doctorado.</t>
-  </si>
-  <si>
-    <t>El Citnova formalizó apoyos económicos científicos de posgrado y de investigación aplicada para 220 especialistas hidalguenses.</t>
-  </si>
-  <si>
-    <t>Consejo de Ciencia, Tecnología e Innovación de Hidalgo, Gobierno del Estado</t>
-  </si>
-  <si>
-    <t>Menchaca reserva su opinión ante la llegada de Adán</t>
-  </si>
-  <si>
-    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, evitó fijar una postura sobre la designación de Adán Augusto López Hernández como coordinador de Morena en la cuarta circunscripción electoral para los comicios de 2027. Al ser cuestionado sobre las imputaciones contra el tabasqueño por supuestos nexos con el grupo delictivo 'La Barredora' de Tabasco, el mandatario estatal respondió que cada persona debe hacerse responsable de su trayectoria personal.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca se reservó de emitir comentarios sobre el nombramiento de Adán Augusto López en Morena, indicando que cada quien es responsable de sus actos.</t>
-  </si>
-  <si>
     <t>Erick Perales</t>
   </si>
   <si>
-    <t>Morena, Gobierno del Estado de Hidalgo, Senado de la República</t>
-  </si>
-  <si>
-    <t>Vinculan a proceso a 7 por conflicto en La Flor</t>
-  </si>
-  <si>
-    <t>La PGJEH obtuvo la vinculación a proceso y resguardo domiciliario temporal por tres meses de investigación complementaria contra siete pobladores (J. C. A., I. A. H., R. A. L., R. S. B., S. N. M., A. C. B. y C. H. B.) acusados de privación ilegal de la libertad, lesiones, robo y daño en propiedad. Los hechos ocurrieron el 18 y 19 de agosto en la comunidad de La Flor, San Salvador, tras retener por la fuerza al alcalde y a regidores del cabildo, dejando 10 policías estatales lesionados.</t>
-  </si>
-  <si>
-    <t>La procuraduría estatal vinculó judicialmente a proceso a siete pobladores implicados en disturbios violentos y en la retención del cabildo municipal en San Salvador.</t>
-  </si>
-  <si>
-    <t>Procuraduría General de Justicia del Estado de Hidalgo, Secretaría de Seguridad Pública de Hidalgo, Ayuntamiento de San Salvador</t>
-  </si>
-  <si>
-    <t>J. C. A., I. A. H., R. A. L., R. S. B., S. N. M., A. C. B., C. H. B.</t>
-  </si>
-  <si>
-    <t>Invierten 22 mdp en el cuartel de Cubitos</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar inauguró el nuevo cuartel de la Policía Estatal en Cubitos, Pachuca, construido con un presupuesto de 22 millones 235 mil 60 pesos. El espacio albergará las divisiones de Vialidad Metropolitana, Grupo Táctico y Medidas de Protección para acercar los servicios de auxilio. Durante la ceremonia, 116 nuevos cadetes de la corporación rindieron protesta tras acumular mil horas de profesionalización.</t>
-  </si>
-  <si>
-    <t>El mandatario estatal inauguró el complejo táctico de Cubitos y dio la bienvenida a 116 cadetes profesionales para robustecer las brigadas de auxilio y seguridad.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Gobierno del Estado de Hidalgo, Instituto de Formación Profesional</t>
-  </si>
-  <si>
-    <t>Detenciones en Tecozautla da indicio de grupo criminal</t>
-  </si>
-  <si>
-    <t>La SSPH indaga la incursión de bandas criminales de otros estados tras arrestar a seis hombres armados que circulaban en dos vehículos con reporte de robo en Tecozautla, decomisándoles un arsenal de nueve armas de fuego, equipo balístico y 120 ponchallantas. Asimismo, el comisionado Salvador Cruz Neri confirmó la detención preventiva de un objetivo de interés federal prioritario en Pachuca.</t>
-  </si>
-  <si>
-    <t>SSPH y fuerzas operativas detuvieron en Tecozautla a seis civiles procedentes de otras entidades en posesión de fusiles de asalto y equipo táctico.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Secretaría de la Defensa Nacional, Guardia Nacional</t>
+    <t>Trabajan en protocolo de protección a docentes</t>
+  </si>
+  <si>
+    <t>El titular de la SEPH, Natividad Castrejón Valdez, confirmó que en coordinación con el SNTE y el Congreso local, trabajan en un documento para equilibrar el derecho de las infancias y la protección de los docentes ante quejas o demandas por presunta violencia escolar. El funcionario reconoció la obligación de separar temporalmente a maestros de sus funciones ante quejas, pero señaló que existen cientos de casos en los que no corresponden a los hechos, como ocurrió en Zapotlán con dos trabajadores acusados de violación que resultaron inocentes de lo que calificó como una "injuria".</t>
+  </si>
+  <si>
+    <t>Violencia Escolar</t>
+  </si>
+  <si>
+    <t>La SEPH, el SNTE y el Congreso local elaboran un protocolo de mediación para proteger a los docentes frente a denuncias infundadas de violencia escolar, garantizando a la vez el interés superior de la niñez.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Sindicato Nacional de Trabajadores de la Educación, Congreso del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez</t>
+  </si>
+  <si>
+    <t>Suman siete vinculados con grupos criminales</t>
+  </si>
+  <si>
+    <t>Con la aprehensión de Jorge Luis N., alias "Koki", presunto líder de Pueblo Unido y vinculado con La Barredora, en la autopista México-Pachuca, se acumulan en Hidalgo al menos siete detenciones clave de integrantes de grupos criminales nacionales desde 2025. El recuento incluye a K. G. R. C. "El Kenny" (grupo San Luis Rey) capturado en mayo en Tizayuca; R. E. R. M. "El Chelelo" (líder de Los Solas) capturado en Tula; María de los Ángeles N. y Samantha N. (viuda e hija del líder del Cártel de Tláhuac, El Ojos) detenidas en Pachuca; Juan Miguel N. "El Pajarraco" (Guerreros Unidos, vinculado al caso Ayotzinapa) capturado en junio; y Axel Esli N. (La Unión Tepito) capturado en enero en la capital.</t>
+  </si>
+  <si>
+    <t>Reportaje</t>
+  </si>
+  <si>
+    <t>Tras la captura de Jorge Luis N. "El Koki", un recuento de Criterio revela que desde 2025 se han registrado siete arrestos clave en Hidalgo de integrantes de grupos como La Barredora, La Unión Tepito, el Cártel de Tláhuac y Guerreros Unidos.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Procuraduría General de Justicia del Estado de Hidalgo, Fiscalía General de Justicia de la Ciudad de México</t>
+  </si>
+  <si>
+    <t>Jorge Luis N (Koki), Ulises N (Pinto), K. G. R. C. (El Kenny), R. E. R. M. (El Chelelo), María de los Ángeles N, Samantha N, Felipe de Jesús Pérez Luna (El Ojos), Juan Miguel N (El Pajarraco), Axel Esli N</t>
+  </si>
+  <si>
+    <t>Aumentan los delitos en Villa de Tezontepec</t>
+  </si>
+  <si>
+    <t>La PGJEH inició 15 carpetas de investigación en el municipio de Villa de Tezontepec durante el mes de julio de 2026, principalmente por delitos de lesiones dolosas (cuatro carpetas) y violencia familiar (dos denuncias), de acuerdo con datos publicados por el SESNSP. Adicionalmente, el Ministerio Público recibió una denuncia por homicidio doloso cometido con arma de fuego, una carpeta por privación ilegal de la libertad, una indagatoria por discriminación, una por narcomenudeo, una por amenazas y otra por delitos cometidos por servidores públicos.</t>
+  </si>
+  <si>
+    <t>Villa de Tezontepec</t>
+  </si>
+  <si>
+    <t>Datos del SESNSP revelan que en julio de 2026 se iniciaron 15 carpetas de investigación en Villa de Tezontepec, registrándose un repunte en delitos como lesiones dolosas, violencia familiar, homicidio y privación ilegal de la libertad.</t>
+  </si>
+  <si>
+    <t>Procuraduría General de Justicia del Estado de Hidalgo, Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública, Ministerio Público</t>
+  </si>
+  <si>
+    <t>SUTSMP elegirá nueva dirigencia el 5 de septiembre entre 2 planillas</t>
+  </si>
+  <si>
+    <t>El Sindicato Único de Trabajadores al Servicio del Municipio de Pachuca (SUTSMP) realizará el próximo 5 de septiembre las elecciones para renovar su dirigencia entre dos planillas validadas por el Comité Electoral por cumplir con todos los requisitos. Las planillas son la verde ("Por un sindicato para todos", encabezada por Pablo Anaya García) y la azul ("Unidad y democracia sindical", con Irma María de Jesús López Arroyo para la Secretaría General). El secretario del Trabajo estatal, Óscar Javier González Hernández, informó que la dependencia dará acompañamiento al proceso del sindicato, que cuenta con más de mil 390 agremiados.</t>
+  </si>
+  <si>
+    <t>SUTSMP</t>
+  </si>
+  <si>
+    <t>El Sindicato Único de Trabajadores al Servicio del Municipio de Pachuca renovará su dirigencia el 5 de septiembre con la participación de las planillas verde y azul, contando con el acompañamiento de la STPSH para garantizar el apego a la norma.</t>
+  </si>
+  <si>
+    <t>Secretaría del Trabajo y Previsión Social de Hidalgo, Sindicato Único de Trabajadores al Servicio del Municipio de Pachuca, Comité Electoral del SUTSMP</t>
+  </si>
+  <si>
+    <t>Óscar Javier González Hernández, Pablo Anaya García, Irma María de Jesús López Arroyo</t>
+  </si>
+  <si>
+    <t>Carril derecho de Las Torres lleva un 29%</t>
+  </si>
+  <si>
+    <t>La reconstrucción con concreto hidráulico en el carril derecho del bulevar Las Torres, al sur de Pachuca, presenta un avance del 29 por ciento, reportó la Sipdus. Los trabajos actualmente se concentran del kilómetro 0+500 al 0+450 e incorporan obras de drenaje, zampeado y juntas de dilatación en el puente del Río de las Avenidas. La obra fue adjudicada a Ahufe Materiales para la Construcción por un monto de 289 millones 519 mil 74 pesos, iniciada el 22 de mayo con fecha estimada de entrega para el primer trimestre de 2027.</t>
+  </si>
+  <si>
+    <t>Pavimentación hidráulica</t>
+  </si>
+  <si>
+    <t>La Sipdus reportó un avance del 29% en la reconstrucción con concreto hidráulico del carril derecho del bulevar Las Torres, obra que implicará una inversión de 289.5 mdp y concluirá en el primer trimestre de 2027.</t>
+  </si>
+  <si>
+    <t>Sipdus</t>
+  </si>
+  <si>
+    <t>Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible</t>
+  </si>
+  <si>
+    <t>Siete filmes se estrenarán en Pachuca</t>
+  </si>
+  <si>
+    <t>La 30ª edición del Tour de Cine Francés 2026 se presentará en Pachuca del 10 al 23 de septiembre de 2026 en las salas de Cinépolis Galerías y VIP Galerías Pachuca. La vocera del certamen, Sofía Llorente, destacó en entrevista que este festival busca estrechar lazos generacionales y formar audiencias. Las siete películas europeas que integran el programa oficial son: Abandonado, El Camino, El Crimen del 3er Piso, El Desconocido del Gran Arco, La Copia Perfecta, Me Encontraste, y Solo una ilusión. Los pases de Cinebono están a la venta desde el 25 de agosto por un costo de 220 pesos.</t>
+  </si>
+  <si>
+    <t>La edición 30 del Tour de Cine Francés llegará a Cinépolis Pachuca del 10 al 23 de septiembre de 2026 con el estreno de siete largometrajes europeos, ofreciendo esquemas de abono preferencial para el público local.</t>
+  </si>
+  <si>
+    <t>Cinépolis, Secretaría de Cultura de Hidalgo</t>
+  </si>
+  <si>
+    <t>Sofía Llorente</t>
+  </si>
+  <si>
+    <t>La Sinfónica de Hidalgo revivirá la música de José José</t>
+  </si>
+  <si>
+    <t>La Orquesta Sinfónica del Estado de Hidalgo (OSEH) ofrecerá un emotivo homenaje al legado artístico de José José "El Príncipe de la Canción" en el Auditorio Gota de Plata de Pachuca. El espectáculo se llevará a cabo el próximo jueves 17 de septiembre de 2026 a las 19:00 horas, combinando nostalgias y arreglos de tipo sinfónico para revivir los himnos románticos de José Rómulo Sosa Ortiz, quien acumuló más de 120 millones de discos vendidos a nivel internacional.</t>
+  </si>
+  <si>
+    <t>Concierto Sinfónico</t>
+  </si>
+  <si>
+    <t>La Orquesta Sinfónica del Estado de Hidalgo presentará un concierto de homenaje sinfónico a José José en el Auditorio Gota de Plata el próximo 17 de septiembre de 2026.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura del Estado de Hidalgo, Orquesta Sinfónica del Estado de Hidalgo, Auditorio Gota de Plata, Parque Cultural Hidalguense</t>
+  </si>
+  <si>
+    <t>José José (José Rómulo Sosa Ortiz)</t>
+  </si>
+  <si>
+    <t>Anuncia alza salarial de 12% a docentes</t>
+  </si>
+  <si>
+    <t>El secretario general del SNTE, Alfonso Cepeda Salas, anunció en Hidalgo el aumento salarial del 12% a docentes, tras la entrega en Pachuca de estímulos por años de servicio, de 20 a 50 años de antigüedad. Detalló que se logró un despegue salarial de 12.7% entre personal de apoyo y docentes. Acompañado por el secretario de la Sección 15, Said Vargas Sáenz, y el titular de la SEPH, Natividad Castrejón Valdez, explicó que este incremento forma parte del Pliego Nacional de Demandas 2026.</t>
+  </si>
+  <si>
+    <t>Aumento salarial</t>
+  </si>
+  <si>
+    <t>El dirigente nacional del SNTE, Alfonso Cepeda, anunció en Hidalgo un incremento salarial del 12% a docentes, gestionado bajo el Pliego Nacional de Demandas 2026.</t>
+  </si>
+  <si>
+    <t>Sindicato Nacional de Trabajadores de la Educación, Sección 15 del SNTE, Secretaría de Educación Pública de Hidalgo</t>
+  </si>
+  <si>
+    <t>Alfonso Cepeda Salas, Said Vargas Sáenz, Natividad Castrejón Valdez</t>
+  </si>
+  <si>
+    <t>Unidades Médicas Servicio Gratuito</t>
+  </si>
+  <si>
+    <t>Campaña oficial del Gobierno del Estado de Hidalgo, la Secretaría del Despacho del Gobernador y Petróleos Mexicanos (Pemex) para invitar a la ciudadanía a aprovechar las Unidades Médicas que brindan atención integral gratuita de salud en diversas comunidades. Se ofrecen servicios especializados de ultrasonidos, medicamentos, electrocardiogramas, toma de peso, talla, glucosa, triglicéridos y colesterol, además de consultas de medicina general, nutricional y odontológica, en horario de 8:30 a 16:00 horas.</t>
+  </si>
+  <si>
+    <t>Unidad Médica Móvil</t>
+  </si>
+  <si>
+    <t>Pemex y el Despacho del Gobernador promueven las jornadas gratuitas de salud mediante unidades médicas móviles equipadas con ultrasonidos, consultas generales y laboratorios.</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Secretaría del Despacho del Gobernador, Petróleos Mexicanos</t>
+  </si>
+  <si>
+    <t>Bienestar no vigila descuentos de INAPAM</t>
+  </si>
+  <si>
+    <t>El delegado de Programas para el Desarrollo de Hidalgo, Abraham Mendoza Zenteno, admitió públicamente que la Secretaría de Bienestar federal no cuenta con atribuciones legales para vigilar que los concesionarios y las empresas de transporte privado respeten el descuento obligatorio del 50% para adultos mayores poseedores de la credencial del INAPAM. El funcionario reconoció la falta de supervisión directa a los prestadores de servicios tras constantes reclamos ciudadanos.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Bienestar reconoció la inoperancia para fiscalizar y obligar a concesionarios del transporte hidalguense a cumplir con los descuentos de tarjetas INAPAM.</t>
+  </si>
+  <si>
+    <t>Alma Leticia Sánchez</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar, Instituto Nacional de las Personas Adultas Mayores (INAPAM)</t>
+  </si>
+  <si>
+    <t>Abraham Mendoza Zenteno</t>
+  </si>
+  <si>
+    <t>Datos Generales: Epic Traverse</t>
+  </si>
+  <si>
+    <t>Anuncio promocional del evento de aventura de deportes extremos 'Epic Traverse' a desarrollarse del 23 al 25 de octubre de 2026 en el estado de Hidalgo. Con la participación de 150 competidores equipados con vestimenta deportiva, se desarrollará un recorrido de aproximadamente dos días iniciando a las 6:00 horas, el cual abarca 9 municipios: Mineral del Chico, Atotonilco el Grande, Actopan, Santiago de Anaya, Cardonal, Metztitlán, Ixmiquilpan, Tasquillo y Zimapán.</t>
+  </si>
+  <si>
+    <t>Turismo Deportivo</t>
+  </si>
+  <si>
+    <t>Promoción del reto 'Epic Traverse' en Hidalgo para octubre de 2026, convocando a 150 atletas de alto rendimiento a recorrer senderos de 9 municipios del estado.</t>
+  </si>
+  <si>
+    <t>Anuncio oficial</t>
+  </si>
+  <si>
+    <t>Secretaría de Turismo de Hidalgo</t>
+  </si>
+  <si>
+    <t>Adultos mayores deben ejercitarse</t>
+  </si>
+  <si>
+    <t>El Instituto Hidalguense del Deporte (Inhide) emitió una serie de recomendaciones para invitar a las personas adultas mayores a realizar actividad física de manera constante, señalando que la práctica cotidiana de ejercicio representa una herramienta fundamental para favorecer el envejecimiento activo, ayudándoles a preservar su movilidad, independencia y calidad de vida integral.</t>
+  </si>
+  <si>
+    <t>Envejecimiento saludable</t>
+  </si>
+  <si>
+    <t>El Inhide recomendó implementar rutinas de ejercicio diario para personas adultas mayores como medida preventiva de preservación motriz y envejecimiento activo.</t>
+  </si>
+  <si>
+    <t>Instituto Hidalguense del Deporte</t>
+  </si>
+  <si>
+    <t>Encabeza Hidalgo las muertes por Covid-19</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud federal y la Dirección General de Epidemiología informaron que el estado de Hidalgo alcanzó 12 muertes acumuladas por Covid-19 en lo que va del año, colocándose como el primer lugar nacional de mortalidad en el país. El reporte indicó un acumulado de 162 casos positivos, registrándose tres fallecimientos y ocho nuevos contagios confirmados durante la tercera semana de agosto. Hidalgo concentra el 23.5 por ciento de los decesos reportados a nivel nacional.</t>
+  </si>
+  <si>
+    <t>Mortalidad Covid-19</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud federal confirma que Hidalgo encabeza el índice nacional de mortalidad por Covid-19, sumando 12 muertes asociadas al virus en el transcurso del año.</t>
+  </si>
+  <si>
+    <t>Secretaría de Salud federal, Dirección General de Epidemiología, Secretaría de Salud de Hidalgo</t>
+  </si>
+  <si>
+    <t>El estado tiene déficit de 4 mil operadores de maquinaria</t>
+  </si>
+  <si>
+    <t>El secretario del Trabajo de Hidalgo, Óscar Javier González Hernández, informó que el sector productivo estatal presenta una escasez aproximada de 4 mil operadores de maquinaria pesada (como soldadores, técnicos en construcción y operadores de trascabos), perfiles que alcanzan salarios de hasta 30 mil pesos mensuales debido a la alta especialización. Ante ello, la STPSH y el Icathi capacitan a interesados en simuladores móviles con escenarios virtuales. Durante la inauguración de la Feria del Empleo se ofertaron 800 vacantes.</t>
+  </si>
+  <si>
+    <t>Mano de obra especializada</t>
+  </si>
+  <si>
+    <t>La Secretaría del Trabajo local reportó un déficit de 4 mil plazas de operadores de maquinaria pesada, impulsando programas virtuales de adiestramiento técnico mediante el Icathi.</t>
+  </si>
+  <si>
+    <t>Secretaría del Trabajo y Previsión Social de Hidalgo, Instituto de Capacitación para el Trabajo de Hidalgo (Icathi)</t>
+  </si>
+  <si>
+    <t>Óscar Javier González Hernández</t>
+  </si>
+  <si>
+    <t>Tula: sí se puede</t>
+  </si>
+  <si>
+    <t>Columna de opinión del contralor estatal Álvaro Bardales que aborda la histórica problemática de contaminación ambiental y descargas residuales sobre el río Tula. Resalta que, de cara al cuarto informe del gobernador Julio Menchaca Salazar, la Comisión Estatal del Agua y Alcantarillado (CEAA) ejecutó una trascendental obra de infraestructura de más de 34 kilómetros de colectores que beneficiará a 120 mil habitantes, conduciendo las aguas residuales hacia la termoeléctrica de CFE para su tratamiento y uso industrial.</t>
+  </si>
+  <si>
+    <t>Opinión</t>
+  </si>
+  <si>
+    <t>Saneamiento ambiental río Tula</t>
+  </si>
+  <si>
+    <t>Álvaro Bardales destaca el impacto ecológico de la red de colectores hídricos en Tula, que captará residuos de 120 mil pobladores para ser tratados y reutilizados por CFE.</t>
+  </si>
+  <si>
+    <t>Álvaro Bardales</t>
+  </si>
+  <si>
+    <t>Columnista</t>
+  </si>
+  <si>
+    <t>Contraloría</t>
+  </si>
+  <si>
+    <t>Comisión Estatal del Agua y Alcantarillado (CEAA), Comisión Federal de Electricidad (CFE), Gobierno del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Álvaro Bardales, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Invertirán 225 millones de pesos para Jacala</t>
+  </si>
+  <si>
+    <t>Durante su gira de trabajo por la sierra de Jacala de Ledezma, en el marco de las Rutas de la Transformación, el gobernador Julio Menchaca Salazar informó una inversión de 225 mdp coordinada con la federación para restaurar caminos y puentes afectados por la vaguada monzónica. El titular federal de la SICT, Pablo Octavio Olvera Sánchez, detalló la reconstrucción de 8 caminos ejidales de conectividad y la edificación de los puentes de La Palma (91.28 metros) y Quetzalapa (110 metros).</t>
+  </si>
+  <si>
+    <t>Jacala</t>
+  </si>
+  <si>
+    <t>Reconstrucción carretera por lluvias</t>
+  </si>
+  <si>
+    <t>El Gobierno del Estado y la federación inyectarán un presupuesto de 225 mdp en Jacala para rehabilitar la red de caminos y puentes colapsados por los meteoros climatológicos.</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Secretaría de Infraestructura, Comunicaciones y Transportes (SICT)</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Pablo Octavio Olvera Sánchez</t>
+  </si>
+  <si>
+    <t>Firman convenio para mapeo de las expresiones rituales estatales</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura de Hidalgo, bajo la dirección de Neyda Naranjo Baltazar, y el Ciesas, representado por Francisco Fernández de Castro Santos, firmaron un convenio general de colaboración científica para instrumentar la 'Cartografía Ritual del Estado de Hidalgo'. El proyecto combinará la investigación etnográfica con tecnologías y sistemas de información geográfica geoespaciales para documentar y conservar el patrimonio y folclor intangible de las comunidades de la entidad.</t>
+  </si>
+  <si>
+    <t>Conservación del patrimonio tradicional</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura y el Ciesas signaron una agenda académica para mapear digitalmente las expresiones rituales hidalguenses mediante sistemas geográficos.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura del Estado de Hidalgo, Centro de Investigaciones y Estudios Superiores en Antropología Social (Ciesas)</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo Baltazar, Francisco Fernández de Castro Santos</t>
+  </si>
+  <si>
+    <t>Artesanos, con espacios gratuitos en la feria 2026</t>
+  </si>
+  <si>
+    <t>El titular de la Secretaría de Bienestar e Inclusión Social (Sebiso), Ricardo Gómez Moreno, dio a conocer que más de 130 artesanos de Hidalgo dispondrán de stands completamente gratuitos en el Pabellón Artesanal y Gastronómico de la Feria de Pachuca 2026 (del 24 de septiembre al 18 de octubre). Asimismo, con el propósito de facilitar la participación y mitigar los costos de creadores del Mezquital, la Huasteca y Otomí-Tepehua, el DIF Estatal les proporcionará hospedaje sin costo en sus albergues.</t>
+  </si>
+  <si>
+    <t>Fomento artesanal regional</t>
+  </si>
+  <si>
+    <t>La Sebiso otorgará espacios exentos de pago a 130 artesanos hidalguenses en el pabellón comercial de la Feria de Pachuca, coordinando subsidios de hospedaje con el DIFH.</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar e Inclusión Social, Sistema DIF Hidalgo, Feria San Francisco Pachuca 2026</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno</t>
+  </si>
+  <si>
+    <t>Las familias recurren a compras de última hora por el regreso a clases</t>
+  </si>
+  <si>
+    <t>De cara al inicio del ciclo escolar 2026-2027 programado para el lunes 31 de agosto, familias hidalguenses efectúan compras de última hora este fin de semana para adquirir libretas, mochilas y uniformes. Madres como Yareli Gómez explicaron que esperaron el cobro de la quincena para mitigar gastos que se sitúan entre los 2 mil y los 10 mil pesos en colegios públicos y privados. La SEPH prevé la reincorporación de 650 mil estudiantes, efectuándose la inauguración oficial en la Secundaria General 2.</t>
+  </si>
+  <si>
+    <t>Economía familiar regreso a clases</t>
+  </si>
+  <si>
+    <t>Padres de familia saturan comercios papeleros de Pachuca por compras escolares tardías ante el inminente inicio de cursos de 650 mil alumnos de educación básica.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo (SEPH)</t>
+  </si>
+  <si>
+    <t>Yareli Gómez</t>
+  </si>
+  <si>
+    <t>Asegura SEPH cobertura total en escuelas, tras protestas en Tizayuca</t>
+  </si>
+  <si>
+    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, garantizó que el 100 por ciento de los alumnos de educación básica en el estado tienen asegurado un espacio en planteles públicos. Respondió así a las recientes protestas de padres de familia en Tizayuca, quienes reportaban un déficit de 300 lugares en primarias y secundarias. Explicó que ante crecimientos demográficos severos se activan protocolos para canalizar matrículas a las opciones escolares de mayor proximidad.</t>
+  </si>
+  <si>
+    <t>Tizayuca</t>
+  </si>
+  <si>
+    <t>Garantía de matrícula básica</t>
+  </si>
+  <si>
+    <t>El titular de la SEPH disipó temores vecinales y garantizó que se solventó la saturación de inscripciones en el fraccionamiento Héroes de Tizayuca ofreciendo planteles alternos.</t>
+  </si>
+  <si>
+    <t>Protesta personal de hospital de Zimapán</t>
+  </si>
+  <si>
+    <t>Trabajadores eventuales y de base del hospital general de Zimapán realizaron una manifestación pacífica en las instalaciones médicas para exigir certeza laboral, incremento salarial y su incorporación al esquema de federalización. Señalaron que el pasado 30 de junio entregaron una petición formal sin recibir respuesta tras cumplirse el plazo. Asimismo, expusieron que laboran en condiciones precarias ante la escasez de insumos, medicamentos, estudios clínicos y especialistas de salud.</t>
+  </si>
+  <si>
+    <t>Zimapán</t>
+  </si>
+  <si>
+    <t>Protesta y carencias hospitalarias</t>
+  </si>
+  <si>
+    <t>Trabajadores del hospital de Zimapán protestaron en demanda de certeza laboral y federalización de plazas, exponiendo desabasto crítico de insumos y medicamentos.</t>
+  </si>
+  <si>
+    <t>Erika Gutiérrez</t>
+  </si>
+  <si>
+    <t>Secretaría de Salud de Hidalgo, Hospital de Zimapán, IMSS-Bienestar</t>
+  </si>
+  <si>
+    <t>La rehabilitación de la biblioteca Sor Juana, en Tulancingo, en 2027</t>
+  </si>
+  <si>
+    <t>La secretaria de Cultura de Hidalgo, Neyda Naranjo Baltazar, informó que hay un proyecto aprobado para rehabilitar estructuralmente el techo y remodelar las instalaciones de la biblioteca Sor Juana Inés de la Cruz en el centro de Tulancingo, así como la biblioteca central Ricardo Garibay de Pachuca. Sin embargo, aclaró que, tras celebrar mesas de planeación con la Secretaría de Hacienda local, la asignación y ejecución de los recursos iniciará formalmente en el presupuesto del ejercicio fiscal 2027.</t>
+  </si>
+  <si>
+    <t>Remodelación de recintos culturales</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura postergó para el año 2027 los trabajos de reconstrucción de techumbre de la biblioteca Sor Juana de Tulancingo por calendarización de Hacienda.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura de Hidalgo, Secretaría de Hacienda de Hidalgo, Biblioteca Sor Juana Inés de la Cruz, Biblioteca Central Ricardo Garibay</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo Baltazar</t>
+  </si>
+  <si>
+    <t>Ante llegada del tren, presentan propuesta de crecimiento urbano</t>
+  </si>
+  <si>
+    <t>Pachuca y Mineral de la Reforma publicaron en el Periódico Oficial del estado (POEH) el Programa Parcial de Desarrollo Urbano, el cual considera, entre otras cosas, una propuesta de estructura urbana, vial y de accesibilidad a la estación del Tren México-Pachuca (tramo AIFA-Pachuca). El esquema considera dos centros urbanos estratégicos, cinco centros de barrio, zonas de densificación vertical en Venta Prieta, Las Águilas y El Chacón, un circuito ciclista para movilidad activa, un Fondo Municipal de Infraestructura Verde y un sistema metropolitano de monitoreo de zonas de riesgo de inundación.</t>
+  </si>
+  <si>
+    <t>Pachuca y Mineral de la Reforma publicaron el Programa Parcial de Desarrollo Urbano, contemplando estructura vial y de accesibilidad para la estación del Tren México-Pachuca.</t>
+  </si>
+  <si>
+    <t>Sipdus, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Reconocen a más de mil docentes por hasta 50 años de servicio</t>
+  </si>
+  <si>
+    <t>Un total de mil 912 docentes de Hidalgo fueron reconocidos por sus años de servicio en el sector educativo con estímulos y medallas por cumplir de 20 a 50 años de trayectoria. El acto fue encabezado por el dirigente nacional del SNTE, Alfonso Cepeda Salas; el líder de la Sección 15, Said Vargas Sáenz, y el titular de la SEPH, Natividad Castrejón Valdez, quienes destacaron los incrementos salariales y de prestaciones logrados durante sus gestiones. Además, se anunció que la elección para renovar la dirigencia de la Sección XV podría posponerse hasta después de los comicios locales de 2027.</t>
+  </si>
+  <si>
+    <t>Reconocimiento</t>
+  </si>
+  <si>
+    <t>Un total de mil 912 docentes hidalguenses de la Sección 15 del SNTE fueron reconocidos con estímulos y medallas por hasta 50 años de servicio, destacándose mejoras salariales.</t>
+  </si>
+  <si>
+    <t>Dulce Castillo</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Sindicato Nacional de Trabajadores de la Educación, Sección 15 del SNTE</t>
+  </si>
+  <si>
+    <t>Balcón Político: Hidalgo, entre inversiones millonarias e informalidad</t>
+  </si>
+  <si>
+    <t>Columna de análisis económico que confronta los 21 mil mdp en anuncios de inversión estatales y los 145 mil mdp consolidados en cuatro años por Julio Menchaca frente a las cifras del INEGI que devela una informalidad laboral del 72% en el estado, sumándose 31 mil personas al sector informal y registrándose pérdidas de empleos en la agricultura y restaurantes.</t>
+  </si>
+  <si>
+    <t>Informalidad laboral</t>
+  </si>
+  <si>
+    <t>Carlos Camacho contrasta el auge de inversiones por 145 mil mdp en Hidalgo frente a una tasa del 72% de informalidad laboral que afecta a un millón de hidalguenses.</t>
+  </si>
+  <si>
+    <t>Carlos Camacho</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Instituto Nacional de Estadística y Geografía, Cooperativa Cruz Azul</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Carlos Camacho</t>
+  </si>
+  <si>
+    <t>Más de 130 artesanos participarán en pabellón de Feria de San Francisco</t>
+  </si>
+  <si>
+    <t>El titular de la Sebiso, Ricardo Gómez Moreno, dio a conocer los resultados de la asignación gratuita de espacios para el Pabellón Artesanal y Gastronómico de la Feria San Francisco Pachuca 2026 (del 24 de septiembre al 18 de octubre), beneficiando a más de 130 artesanos de las regiones del Mezquital, Otomí-Tepehua, la Huasteca, la Sierra y los valles de Pachuca y Tulancingo. Se coordinará hospedaje gratuito con los albergues del DIF estatal.</t>
+  </si>
+  <si>
+    <t>Apoyo a artesanos</t>
+  </si>
+  <si>
+    <t>La Sebiso otorgará espacios gratuitos en la Feria de Pachuca a más de 130 artesanos regionales, quienes recibirán hospedaje subsidiado mediante el DIFH.</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar e Inclusión Social, Sistema DIF Hidalgo, Patronato de la Feria San Francisco Pachuca 2026</t>
+  </si>
+  <si>
+    <t>Atacan a balazos casa en Tlamaco; van 2 agresiones</t>
+  </si>
+  <si>
+    <t>Una casa habitación de la comunidad de Tlamaco, municipio de Atitalaquia, fue atacada con arma de fuego la noche del miércoles, sin que se reportaran personas muertas o heridas, ni detenidos. De acuerdo con fuentes de la Secretaría de Seguridad Pública municipal, el ataque ocurrió minutos después de las 22:00 horas, luego de que vecinos reportaran primero una explosión y posteriormente detonaciones de arma de fuego. Al llegar al lugar, elementos policiales localizaron una vivienda de dos pisos con impactos de bala dirigidos hacia una ventana del segundo piso, cuyos vidrios quedaron destruidos. También se reportó que vecinos vieron varias camionetas con personas armadas en la zona.</t>
+  </si>
+  <si>
+    <t>Atitalaquia</t>
+  </si>
+  <si>
+    <t>Ataque Armado</t>
+  </si>
+  <si>
+    <t>Una vivienda en la comunidad de Tlamaco, Atitalaquia, fue atacada a balazos por sujetos armados a bordo de camionetas, lo que movilizó a la policía local sin reportarse heridos.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Procuraduría General de Justicia de Hidalgo, Guardia Nacional</t>
+  </si>
+  <si>
+    <t>Destinan 178 mdp a obras y movilidad en La Misión</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar encabezó su quinta gira de trabajo en La Misión, como parte del programa Rutas de la Transformación para la Reconstrucción, donde informó sobre las acciones para reparar los daños ocasionados por la vaguada monzónica y restablecer la movilidad en la región. Durante la jornada se dio a conocer que el Gobierno de México, a través de la SICT, invertirá más de 178 millones de pesos para la reconstrucción de 24 caminos y un puente peatonal en el municipio, beneficiando a diversas localidades.</t>
+  </si>
+  <si>
+    <t>La Misión</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca anunció una inversión de 178 mdp por parte de la SICT federal para reconstruir 24 caminos y un puente peatonal afectados por las lluvias en La Misión.</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Secretaría de Infraestructura, Comunicaciones y Transportes (SICT), Comisión Estatal del Agua y Alcantarillado (CEAA)</t>
+  </si>
+  <si>
+    <t>Dan 115.7 mdp a caminos de Jacala</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar visitó Jacala de Ledezma para concluir la actual etapa del programa Rutas de la Transformación para la Reconstrucción, donde informó que se destinan más de 225 millones de pesos para atender los caminos dañados por las lluvias. Del monto total, el Gobierno de México aportará más de 115.7 millones de pesos para la modernización del camino Jacala-Quetzalapa, pavimentaciones y construcción de sistemas de agua potable en beneficio de comunidades de la región serrana.</t>
+  </si>
+  <si>
+    <t>Rehabilitación carretera</t>
+  </si>
+  <si>
+    <t>En su visita a Jacala, el gobernador Julio Menchaca detalló que la federación aportará 115.7 mdp para reconstruir ocho caminos ejidales y dos puentes colapsados por meteoros climatológicos.</t>
+  </si>
+  <si>
+    <t>Más de 130 artesanos estarán en pabellón</t>
+  </si>
+  <si>
+    <t>La Secretaría de Bienestar e Inclusión Social de Hidalgo (Sebiso) informó que más de 130 artesanos participarán en la Feria San Francisco Pachuca 2026, la cual se realizará del 24 de septiembre al 18 de octubre de 2026. El titular de la dependencia, Ricardo Gómez Moreno, señaló que los espacios serán gratuitos para favorecer la comercialización de sus piezas y productos sin intermediarios. Por su parte, el Sistema DIFH ofrecerá hospedaje gratuito en sus albergues para artesanos procedentes de regiones distantes.</t>
+  </si>
+  <si>
+    <t>La Sebiso y el DIF estatal otorgarán espacios comerciales y hospedaje gratuito a más de 130 artesanos de Hidalgo que participarán en el pabellón de la Feria de Pachuca 2026.</t>
+  </si>
+  <si>
+    <t>Epic Traverse Hidalgo</t>
+  </si>
+  <si>
+    <t>Anuncio promocional del reto deportivo de aventura extrema Epic Traverse, que se llevará a cabo del 23 al 25 de octubre de 2026 en el estado de Hidalgo. Convocará a 150 competidores con equipamiento de vestimenta deportiva para realizar un recorrido de aproximadamente dos días con inicio a las 6:00 h, cruzando los municipios de Mineral del Chico, Atotonilco El Grande, Actopan, Santiago de Anaya, Cardonal, Metztitlán, Ixmiquilpan, Tasquillo y Zimapán.</t>
+  </si>
+  <si>
+    <t>Se promueve el evento de deportes de aventura Epic Traverse en Hidalgo, convocando a 150 atletas a realizar un trayecto extremo que recorrerá nueve demarcaciones del estado.</t>
+  </si>
+  <si>
+    <t>Hidalgo incorpora ocho municipios a la ZMVM</t>
+  </si>
+  <si>
+    <t>La Zona Metropolitana del Valle de México (ZMVM) oficializó la incorporación de ocho municipios de Hidalgo (Atitalaquia, Atotonilco de Tula, Tepeji del Río, Tizayuca, Tlaxcoapan, Tolcayuca, Tula de Allende y Villa de Tezontepec) y uno de Morelos a su esquema de planeación metropolitana. La modificación, publicada en el Diario Oficial de la Federación, permitirá la articulación conjunta de políticas de movilidad, vivienda, medio ambiente, infraestructura y desarrollo urbano sostenible entre las entidades federativas, sin que los municipios pierdan su autonomía.</t>
+  </si>
+  <si>
+    <t>La ZMVM oficializó la anexión de ocho ayuntamientos de Hidalgo a su área de planeación metropolitana, facilitando la coordinación de infraestructura y servicios sin lesionar su autonomía.</t>
+  </si>
+  <si>
+    <t>Francisco Villeda</t>
+  </si>
+  <si>
+    <t>Secretaría de Desarrollo Agrario, Territorial y Urbano (Sedatu), Consejo de Desarrollo Metropolitano, Gobiernos estatales de Hidalgo, Edomex y Morelos</t>
+  </si>
+  <si>
+    <t>Clara Brugada Molina, Delfina Gómez Álvarez, Margarita González Saravia, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>PODE COBI detona industria médica</t>
+  </si>
+  <si>
+    <t>El titular de la Unidad de Planeación y Prospectiva de Hidalgo (Uplaph), Miguel Ángel Tello Vargas, develo que el Polo de Desarrollo Económico para el Bienestar (PODE COBI) en Zapotlán de Juárez detonará de manera significativa el crecimiento y consolidación de la industria médica, química y farmacéutica en la entidad, aprovechando su ubicación e infraestructura de conectividad con la zona metropolitana.</t>
+  </si>
+  <si>
+    <t>Zapotlán</t>
+  </si>
+  <si>
+    <t>Polos del Bienestar</t>
+  </si>
+  <si>
+    <t>La Uplaph prevé un alto auge industrial químico y farmacéutico en el estado a partir de la detonación de la infraestructura del Polo de Desarrollo PODE COBI en Zapotlán.</t>
+  </si>
+  <si>
+    <t>Unidad de Planeación y Prospectiva de Hidalgo (Uplaph), Gobierno del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Apoyan a personas cuidadoras</t>
+  </si>
+  <si>
+    <t>La Secretaría de Bienestar e Inclusión Social de Hidalgo (Sebiso), a través de la Dirección General de Inclusión, inició la entrega de subsidios del programa de apoyo económico a personas cuidadoras de personas con discapacidad severa. El programa, impulsado por el gobernador Julio Menchaca, tiene por objeto brindar un soporte monetario a quienes dedican de tiempo completo su labor al cuidado familiar en municipios como Tlaxcoapan.</t>
+  </si>
+  <si>
+    <t>Apoyo a personas cuidadoras</t>
+  </si>
+  <si>
+    <t>La Sebiso hidalguense formalizó la dispersión de apoyos de los programas del Bienestar enfocados a respaldar económicamente la labor de personas cuidadoras en Tlaxcoapan.</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Dirección General de Inclusión para las Personas con Discapacidad</t>
+  </si>
+  <si>
+    <t>Reconocen trayectoria de más de mil trabajadores</t>
+  </si>
+  <si>
+    <t>El titular de la SEPH, Natividad Castrejón Valdez, el líder nacional del SNTE, Alfonso Cepeda Salas, y el dirigente estatal de la Sección 15, Said Vargas Sáenz, presidieron un emotivo evento para reconocer y entregar estímulos a mil 912 trabajadores y docentes de la educación por sus años de servicio, destacando el profesionalismo, disciplina y compromiso con la enseñanza de la niñez en Hidalgo.</t>
+  </si>
+  <si>
+    <t>La SEPH y las cúpulas del SNTE entregaron medallas y estímulos por trayectoria de servicio a mil 912 trabajadores magisteriales en Pachuca.</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, Alfonso Cepeda Salas, Said Vargas Sáenz</t>
+  </si>
+  <si>
+    <t>Fortalece la SEPH formación docente</t>
+  </si>
+  <si>
+    <t>La Secretaría de Educación Pública de Hidalgo (SEPH) fortalece la actualización y capacitación del personal docente mediante los Ejercicios Integradores del Aprendizaje (EIA). Esta estrategia permite evaluar y orientar las prácticas de enseñanza en el aula para responder a las necesidades específicas de las comunidades escolares y consolidar los preceptos del modelo pedagógico oficial.</t>
+  </si>
+  <si>
+    <t>La SEPH implementó talleres de capacitación docente bajo el esquema de Ejercicios Integradores para robustecer la planeación académica en las aulas.</t>
+  </si>
+  <si>
+    <t>Ofrecen 700 empleos para los jóvenes</t>
+  </si>
+  <si>
+    <t>Con la participación de 25 empresas y una oferta de 700 plazas laborales, se llevó a cabo la Feria Nacional de Empleo para las Juventudes 2026 en Mineral de la Reforma, informó el titular de la STPSH, Oscar Javier González Hernández. El funcionario puntualizó que esta feria busca acercar opciones laborales formales y dignas, con salarios competitivos, para mitigar los índices de desocupación en el sector joven.</t>
+  </si>
+  <si>
+    <t>Mineral de la Reforma</t>
+  </si>
+  <si>
+    <t>Feria De Empleo</t>
+  </si>
+  <si>
+    <t>La Secretaría del Trabajo de Hidalgo inauguró una feria de empleo juvenil en Mineral de la Reforma con una oferta inicial de 700 vacantes y 25 firmas participantes.</t>
+  </si>
+  <si>
+    <t>Secretaría del Trabajo y Previsión Social de Hidalgo (STPSH), Instituto de Capacitación para el Trabajo (Icathi)</t>
+  </si>
+  <si>
+    <t>Oscar Javier González Hernández</t>
+  </si>
+  <si>
+    <t>Hidalgo registró una tasa de desocupación de 2.2 por ciento</t>
+  </si>
+  <si>
+    <t>El titular de la Secretaría del Trabajo y Previsión Social de Hidalgo (STPSH), Oscar Javier González Hernández, informó que el estado registró una tasa de desocupación de 2.2 por ciento durante el segundo trimestre de 2026, de acuerdo con los indicadores más recientes de la Encuesta Nacional de Ocupación y Empleo (ENOE) elaborada por el Inegi. Esto representa un descenso de 0.5 puntos porcentuales en comparación anual.</t>
+  </si>
+  <si>
+    <t>Tasa de desocupación</t>
+  </si>
+  <si>
+    <t>La STPSH reportó que Hidalgo registró una tasa de desocupación del 2.2% al cierre del segundo trimestre de 2026, de acuerdo con la ENOE del Inegi.</t>
+  </si>
+  <si>
+    <t>Secretaría del Trabajo y Previsión Social de Hidalgo, Instituto Nacional de Estadística y Geografía (Inegi)</t>
+  </si>
+  <si>
+    <t>CULTURA: La Celestina</t>
+  </si>
+  <si>
+    <t>En el marco de la inauguración del 2.º Festival Internacional Sor Juana Inés de la Cruz: Escena Barroca, la obra dramática 'La Celestina' (De mujeres y brujas) se presentará hoy en Pachuca a las 18:00 horas, promoviendo el acceso a la cultura barroca y las artes teatrales.</t>
+  </si>
+  <si>
+    <t>La obra escénica 'La Celestina' se presentará en Pachuca a las 18:00 horas en el arranque de la segunda edición del Festival Escena Barroca.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura del Estado de Hidalgo, Consejo Estatal para las Culturas y las Artes</t>
+  </si>
+  <si>
+    <t>FOTOGRAFÍA: La Muestra PECDA</t>
+  </si>
+  <si>
+    <t>La Muestra PECDA Hidalgo 2025 de artes visuales entra en su última semana de exhibición de artes teatrales y de fotografía en Pachuca. En este contexto, este jueves se presentará la puesta en escena 'Historias de la luna para el viento' en el foro del Teatro Romo de Vivar.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura anunció el cierre de la muestra del estímulo PECDA con la función teatral 'Historias de la luna para el viento' en el Teatro Romo de Vivar.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura del Estado de Hidalgo, Teatro Guillermo Romo de Vivar, PECDA</t>
+  </si>
+  <si>
+    <t>Por conflicto de propiedad, SEPH negocia terreno de escuela en Tezontepec</t>
+  </si>
+  <si>
+    <t>El área jurídica de la SEPH atiende el conflicto de propiedad de una escuela de educación media superior en Tezontepec de Aldama, cuyo terreno cuenta con un particular que obtuvo una resolución favorable en un juicio. El predio está valuado entre 10 y 12 mdp, y el edificio en 40 mdp. El secretario Natividad Castrejón Valdez informó que se busca un acuerdo de negociación antes de heredar el problema a la siguiente administración.</t>
+  </si>
+  <si>
+    <t>Tezontepec de Aldama</t>
+  </si>
+  <si>
+    <t>Conflicto predio escolar</t>
+  </si>
+  <si>
+    <t>La SEPH busca un acuerdo de negociación con un particular que acreditó la propiedad del predio donde opera un plantel escolar en Tezontepec de Aldama.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo</t>
+  </si>
+  <si>
+    <t>Concluye Menchaca primera etapa de Rutas para la Reconstrucción; continuarán tras Cuarto Informe</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar concluyó en Jacala de Ledezma la primera etapa de las Rutas de la Transformación para la Reconstrucción, donde dio cuenta de obras y acciones por más de 225 mdp para atender daños de la vaguada monzónica. Anunció que la federación aportará 115.7 mdp para reconstruir ocho caminos que comunican a comunidades como La Palma, Quetzalapa y El Aguaje. Adelantó que las Rutas continuarán tras rendir su informe de gobierno.</t>
+  </si>
+  <si>
+    <t>Rutas de la Reconstrucción</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca concluyó la primera fase de las Rutas de la Reconstrucción con obras por 225 mdp para resarcir daños pluviales en Jacala.</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Secretaría de Infraestructura, Comunicaciones y Transportes</t>
+  </si>
+  <si>
+    <t>Con protocolo buscan proteger a docentes ante denuncias “falsas”</t>
+  </si>
+  <si>
+    <t>El secretario de Educación Pública, Natividad Castrejón Valdez, señaló que la iniciativa conjunta con el Congreso local, el SNTE nacional y la Sección 15 busca proteger los derechos de los maestros expuestos a sanciones inmerecidas por denuncias falsas de violencia escolar. Aclaró que aunque se tiene la obligación de separar preventivamente al docente ante quejas, se busca evitar la vulnerabilidad de los profesores cuando las acusaciones resultan ser falsas, citando un caso previo en Zapotlán.</t>
+  </si>
+  <si>
+    <t>La SEPH, el Congreso y el SNTE alistan un protocolo para proteger los derechos de maestros ante quejas o falsas acusaciones de violencia escolar.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Congreso del Estado de Hidalgo, Sindicato Nacional de Trabajadores de la Educación, Sección 15 del SNTE</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, Alfonso Cepeda Salas</t>
+  </si>
+  <si>
+    <t>Desarrollan estudiantes hidalguenses prototipos de go-karts eléctricos</t>
+  </si>
+  <si>
+    <t>Alumnos de octavo semestre de Ingeniería en Sistemas Automotrices del ITESA diseñaron y construyeron dos prototipos funcionales de go-karts 100% eléctricos como parte de su especialidad de electromovilidad. El coordinador del proyecto, Joshio Guadalupe García Acosta, destacó que este desarrollo está alineado con las metas del Plan México y de la estrategia federal Olinia para impulsar vehículos eléctricos de manufactura nacional.</t>
+  </si>
+  <si>
+    <t>Apan</t>
+  </si>
+  <si>
+    <t>Plan México</t>
+  </si>
+  <si>
+    <t>Estudiantes de Ingeniería de Sistemas Automotrices de ITESA ensamblaron dos prototipos de go-karts eléctricos alineados con los objetivos del Plan México.</t>
+  </si>
+  <si>
+    <t>Instituto Tecnológico Superior del Oriente del Estado de Hidalgo, Secretaría de Educación Pública de Hidalgo</t>
+  </si>
+  <si>
+    <t>Joshio Guadalupe García Acosta</t>
+  </si>
+  <si>
+    <t>Espejeando: Presentación de la orquesta sinfónica del Estado de Hidalgo en la catedral de Huejutla / Retorno de vacacionistas / Xantolo</t>
+  </si>
+  <si>
+    <t>Columna de opinión que aborda diversos temas locales de la Huasteca: 1) El éxito de la presentación de la Orquesta Sinfónica en la catedral de Huejutla y la descentralización de la cultura promovida por Neyda Naranjo. 2) La expectativa del ayuntamiento para el último Xantolo de la actual administración. 3) El retorno de vacacionistas por el regreso a clases que reactivará el comercio de calzado y útiles.</t>
+  </si>
+  <si>
+    <t>Temas varios</t>
+  </si>
+  <si>
+    <t>Trascendidos que destacan la presentación de la orquesta sinfónica en la catedral de Huejutla, las expectativas por el Xantolo y la reactivación comercial por el regreso a clases.</t>
+  </si>
+  <si>
+    <t>Perseo</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura de Hidalgo, Ayuntamiento de Huejutla</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo Baltazar, Genaro Zuviri González</t>
+  </si>
+  <si>
+    <t>Desde Jacala Julio Menchaca concluye Rutas para la Reconstrucción</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca concluyó la etapa de las Rutas de la Transformación para la Reconstrucción en Jacala de Ledezma, reportando obras por más de 225 mdp para atender daños pluviales. Destacó el respaldo del gobierno federal de Claudia Sheinbaum con 115.7 mdp para reconstruir 8 caminos y puentes. Alejandro Sánchez (Sipdus) anunció puentes sobre el río Amajac; CEAA y Conagua informaron sobre rehabilitación de agua.</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (Sipdus), Comisión Estatal del Agua y Alcantarillado (CEAA), Centro SICT en Hidalgo, Comisión Nacional del Agua (Conagua), Ayuntamiento de Jacala</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Claudia Sheinbaum Pardo, Pablo Octavio Olvera Sánchez, Alejandro Sánchez García, Juan Carlos Chávez González, Kendra Martínez Sánchez</t>
+  </si>
+  <si>
+    <t>Sebiso hace entrega de tarjetas a domicilio a personas cuidadoras</t>
+  </si>
+  <si>
+    <t>La Secretaría de Bienestar e Inclusión Social (Sebiso) inició la entrega de tarjetas de apoyo económico de 10 mil pesos para personas cuidadoras de personas con discapacidad severa. Debido a las limitaciones de movilidad, se programaron 89 visitas domiciliarias en municipios como San Felipe Orizatlán, Huejutla, Jacala y La Misión.</t>
+  </si>
+  <si>
+    <t>La Sebiso hidalguense formalizó la dispersión de apoyos de los programas del Bienestar enfocados a respaldar económicamente la labor de personas cuidadoras.</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar e Inclusión Social, Dirección General de Inclusión para las Personas con Discapacidad, Servidores del Pueblo</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Ricardo Gómez Moreno, Alfonso Hayyim Flores Barrera, Jorge Miguel García Vázquez</t>
+  </si>
+  <si>
+    <t>Realizan en Mineral de la Reforma Feria Nacional de Empleo para las Juventudes</t>
+  </si>
+  <si>
+    <t>Con la participación de 25 empresas y 700 plazas ofertadas, se llevó a cabo la Feria Nacional de Empleo para las Juventudes 2026 en el municipio de Mineral de la Reforma. El titular de la STPSH, Oscar Javier González Hernández, informó que al segundo trimestre de 2026, la tasa de desocupación se ubicó en 2.2 por ciento, 0.5 puntos porcentuales por debajo de la media nacional. Se firmó un convenio de colaboración con la UNID para elevar la empleabilidad.</t>
+  </si>
+  <si>
+    <t>La Secretaría del Trabajo de Hidalgo inauguró una feria de empleo juvenil en Mineral de la Reforma con una oferta de 700 vacantes y 25 firmas participantes.</t>
+  </si>
+  <si>
+    <t>Secretaría del Trabajo y Previsión Social de Hidalgo, Ayuntamiento de Mineral de la Reforma, Instituto de Capacitación para el Trabajo del Estado de Hidalgo (Icathi)</t>
+  </si>
+  <si>
+    <t>Oscar Javier González Hernández, Eduardo Medécigo Rubio, Sergio Arturo Hernández Echagaray, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Atendemos cada rincón de Hidalgo; hay obra en los 84 municipios: Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar encabezó una gira de trabajo en el municipio de La Misión, donde dio cuenta de las obras y acciones realizadas para atender las afectaciones pluviales y recuperar la movilidad de la zona. Se destacó que la SICT federal destinará más de 178 mdp para reconstruir 24 caminos y un puente peatonal. Desde 2023 se han invertido más de 80 mdp estatales en obras locales.</t>
+  </si>
+  <si>
+    <t>El mandatario estatal reportó obras estatales por más de 80 mdp y una inversión de la SICT federal de 178 mdp para reconstruir 24 caminos dañados en La Misión.</t>
+  </si>
+  <si>
+    <t>Gobierno de Hidalgo, Secretaría de Infraestructura, Comunicaciones y Transportes (SICT), Comisión Estatal del Agua y Alcantarillado (CEAA), Ayuntamiento de La Misión</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Pablo Octavio Olvera Sánchez, Ibsan Israel Villeda Villeda</t>
+  </si>
+  <si>
+    <t>Obra La Celestina llega a Pachuca con el 2º Festival Internacional</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura de Hidalgo, en colaboración con el Centro Cultural Helénico y El Claustro de Sor Juana, presentará en Pachuca dos actividades del 2º Festival Internacional Sor Juana Inés de la Cruz: Escena Barroca. El viernes 28 de agosto a las 18:00 horas se escenificará 'La Celestina. De mujeres y brujas' en el Teatro Romo de Vivar, y el sábado 29 se impartirá el taller 'El bululú contemporáneo' en el Ferrocarril.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura del Estado de Hidalgo, Centro Cultural Helénico, El Claustro de Sor Juana</t>
+  </si>
+  <si>
+    <t>Jesús Torres, Carol Delgado</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura y CIESAS firman convenio para mapear expresiones rituales de Hidalgo</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura de Hidalgo y el CIESAS firmaron un convenio general de colaboración académica y científica para instrumentar el proyecto 'Cartografía Ritual del Estado de Hidalgo', que combinará la investigación documental y de campo con tecnologías de Sistemas de Información Geográfica geoespaciales para documentar las tradiciones de las diez regiones geoculturales.</t>
+  </si>
+  <si>
+    <t>Conservación del Patrimonio Cultural</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura y el Ciesas firmaron un convenio académico y de georreferenciación para mapear digitalmente las expresiones rituales hidalguenses.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura del Estado de Hidalgo, Centro de Investigaciones y Estudios Superiores en Antropología Social (CIESAS), Centro INAH Hidalgo, ProSIG-CSH</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo Baltazar, Francisco Fernández de Castro Santos, Manuel Villarruel Vázquez, Deborah Monroy Magaldi, Luis Francisco Sánchez Fonseca, Antonio Escobar Ohmstede, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Llega Muestra PECDA a su última semana con teatro, fotografía y artes visuales</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura de Hidalgo invitó a la última semana de actividades de la Muestra del Programa de Estímulos a la Creación y Desarrollo Artístico (PECDA) Hidalgo 2025. Los eventos se desarrollarán hasta el 31 de agosto, incluyendo representaciones de teatro en el Teatro Romo de Vivar, exposiciones fotográficas en el Ferrocarril y artes visuales en el Centro de Cultura Digital.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura anunció el cierre de la muestra del estímulo PECDA con funciones teatrales, de fotografía y artes visuales en diversos recintos de Pachuca.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura del Estado de Hidalgo, Teatro Guillermo Romo de Vivar, Centro Cultural del Ferrocarril, Centro de Cultura Digital, PECDA</t>
+  </si>
+  <si>
+    <t>Fátima Carrillo Marrodán, Jéssica Miriam Mejía Domínguez, Mariana Castillo Monterrubio, Andrea Natalia Arriaga Pájaro, Fabrizio Otamendi Servín</t>
+  </si>
+  <si>
+    <t>Avanzan proyectos de infraestructura vial y de conectividad en aeropuerto AIFA</t>
+  </si>
+  <si>
+    <t>En el marco de la Mesa de Trabajo en Materia de Movilidad y Conectividad 2026 del AIFA, se presentaron propuestas de infraestructura clave como la conexión vial Zumpango-AIFA, el ramal Arco Norte-Paseo del Bicentenario, y los avances de la planeación para la extensión del Tren Suburbano hacia la ciudad de Pachuca, buscando fortalecer la conectividad metropolitana.</t>
+  </si>
+  <si>
+    <t>Edomex</t>
+  </si>
+  <si>
+    <t>Se presentaron proyectos metropolitanos de infraestructura vial y ferroviaria de conectividad con el AIFA, incluyendo el ramal a Pachuca.</t>
+  </si>
+  <si>
+    <t>Secretaría de Turismo de Hidalgo (Secturh), Secretaría de Movilidad y Transporte (Semot), Secretaría de Desarrollo Agrario, Territorial y Urbano (Sedatu), Comisión Consultiva del AIFA</t>
+  </si>
+  <si>
+    <t>Isidoro Pastor Román, Elizabeth Quintanar Gómez, Lyzbeth Robles Gutiérrez</t>
+  </si>
+  <si>
+    <t>SEPH y SNTE reconocen trayectoria de mil 912 trabajadores de la educación</t>
+  </si>
+  <si>
+    <t>En representación del gobernador, el titular de la SEPH, Natividad Castrejón Valdez, junto con el dirigente nacional del SNTE, Alfonso Cepeda Salas, y el secretario general de la Sección 15, Said Vargas Sáenz, entregaron estímulos y medallas por 20, 25, 30, 40 y 50 años de servicio a mil 912 trabajadores de la educación hidalguenses, refrendando el compromiso con el magisterio.</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, Alfonso Zepeda Salas, Said Vargas Sáenz, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Más de 130 hidalguenses participarán en el pabellón artesanal y gastronómico de la Feria de San Francisco Pachuca 2026</t>
+  </si>
+  <si>
+    <t>La Secretaría de Bienestar e Inclusión Social de Hidalgo (Sebiso) dio a conocer los resultados de la segunda asignación de espacios para el Pabellón Artesanal y Gastronómico de la Feria San Francisco Pachuca 2026, beneficiando a más de 130 artesanos regionales con stands gratuitos y hospedaje coordinado con el DIF estatal.</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>En Zapotlán se impulsará industria médica y farmacéutica</t>
+  </si>
+  <si>
+    <t>El titular de la Unidad de Planeación y Prospectiva (Uplaph), Miguel Ángel Tello Vargas, develo que el Polo de Desarrollo Económico para el Bienestar (Podeco) en Zapotlán de Juárez impulsará la industria médica y farmacéutica hacia 2040, aprovechando el potencial de conectividad regional y la millonaria inversión de 10 mil 106 mdp de la firma DEWA.</t>
+  </si>
+  <si>
+    <t>La Uplaph prevé un alto auge industrial químico y farmacéutico en el estado a partir de la detonación de la infraestructura del Polo de Desarrollo Podeco en Zapotlán.</t>
+  </si>
+  <si>
+    <t>Unidad de Planeación y Prospectiva de Hidalgo (Uplaph), Gobierno del Estado de Hidalgo, Gobierno de México</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Tello Vargas, Claudia Sheinbaum Pardo, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Banda Sinfónica de Hidalgo Estará en Tlanchinol</t>
+  </si>
+  <si>
+    <t>El alcalde de Tlanchinol, Gabino Hernández Vite, extendió la invitación a disfrutar del concierto gratuito que ofrecerá la Banda Sinfónica del Estado de Hidalgo este viernes a las 15:00 horas en la parroquia de San Agustín, un evento coordinado de la mano de la Secretaría de Cultura para acercar las expresiones culturales a las regiones.</t>
+  </si>
+  <si>
+    <t>Tlanchinol</t>
+  </si>
+  <si>
+    <t>El municipio de Tlanchinol será sede del concierto de la Banda Sinfónica del Estado de Hidalgo en la Parroquia de San Agustín para descentralizar los eventos artísticos.</t>
+  </si>
+  <si>
+    <t>Ángel Osiris Castillo García</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura de Gobierno del Estado de Hidalgo, Ayuntamiento de Tlanchinol</t>
+  </si>
+  <si>
+    <t>Gabino Hernández Vite, Neyda Naranjo Baltazar</t>
+  </si>
+  <si>
+    <t>SSPH aseguró dos personas con hidrocarburo de procedencia ilícita en Ixmiquilpan</t>
+  </si>
+  <si>
+    <t>Elementos de la SSPH junto con el Mando Coordinado de Ixmiquilpan aseguraron en el barrio de Santa Ana a dos personas que transportaban un cargamento ilícito de aproximadamente 1,200 litros de hidrocarburo de Pemex, distribuidos en 19 garrafones en el área de carga de una camioneta pick-up. Quedaron a disposición de la FGR en Tula de Allende.</t>
+  </si>
+  <si>
+    <t>Ixmiquilpan</t>
+  </si>
+  <si>
+    <t>Fuerzas de seguridad y el Mando Coordinado incautaron 1,200 litros de combustible ilícito en Ixmiquilpan y arrestaron a dos personas involucradas.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Mando Coordinado de Ixmiquilpan, Fiscalía General de la República (FGR)</t>
+  </si>
+  <si>
+    <t>Dese por enterado: Israel Félix va con todo / Condolencias a Guadarrama / Aplazan elecciones Sección XV / Regularán bacheo en Pachuca</t>
+  </si>
+  <si>
+    <t>Trascendidos locales que analizan: 1) La campaña política contra el alcalde de Mineral de la Reforma, Eduardo Medécigo, y las intenciones de Israel Félix de posicionar a Shaida Lozada para 2027. 2) Condolencias para José Guadarrama por el deceso de su hermana Aseneth. 3) El posible aplazamiento de las elecciones en la Sección XV del SNTE en Hidalgo para evitar interferencias con los comicios de 2027, lo cual daría un respiro a Said Vargas. 4) El anuncio del secretario de Obras Públicas de Pachuca, Francisco Lugo Espinosa, sobre la regulación del bacheo por parte de particulares.</t>
+  </si>
+  <si>
+    <t>Trascendidos políticos sobre campañas contra Eduardo Medécigo, el virtual aplazamiento electoral en el SNTE de Said Vargas y la nueva regulación del bacheo particular en Pachuca.</t>
+  </si>
+  <si>
+    <t>Dese por enterado</t>
+  </si>
+  <si>
+    <t>Sindicato Nacional de Trabajadores de la Educación, Ayuntamiento de Pachuca, Ayuntamiento de Mineral de la Reforma</t>
+  </si>
+  <si>
+    <t>Eduardo Medécigo Rubio, Israel Félix Soto, Shaida Lozada Martínez, José Guadarrama Márquez, Aseneth Guadarrama Márquez, Alfonso Cepeda Salas, Said Vargas Sáenz, Francisco Lugo Espinosa</t>
+  </si>
+  <si>
+    <t>Más de 130 hidalguenses participarán en pabellón artesanal</t>
+  </si>
+  <si>
+    <t>La Secretaría de Bienestar e Inclusión Social (Sebiso) publicó los resultados de la segunda etapa de asignación de espacios gratuitos para el Pabellón Artesanal y Gastronómico de la Feria San Francisco Pachuca 2026 (del 24 de septiembre al 18 de octubre). El titular Ricardo Gómez Moreno destacó que el objetivo es promover la venta directa sin intermediarios. Se coordinará hospedaje gratuito para expositores distantes mediante el DIF estatal.</t>
+  </si>
+  <si>
+    <t>La Sebiso otorgará stands comerciales gratuitos en el pabellón de la Feria de Pachuca a más de 130 artesanos, facilitando hospedaje sin costo a través del DIFH.</t>
+  </si>
+  <si>
+    <t>Vidas dedicadas a la docencia</t>
+  </si>
+  <si>
+    <t>En un evento protocolario con cena y música celebrado en el salón Veravia de Pachuca, se entregaron estímulos y medallas oficiales de la Casa de Moneda de México a mil 212 docentes de Hidalgo por cumplir trayectorias de 20 a 50 años de servicio en el magisterio básico, en un acto encabezado por el titular de la SEPH, Natividad Castrejón Valdez, en representación del gobernador Julio Menchaca.</t>
+  </si>
+  <si>
+    <t>La SEPH coordinó la entrega de estímulos monetarios y medallas conmemorativas por años de antigüedad laboral a mil 212 profesores de educación básica.</t>
+  </si>
+  <si>
+    <t>Catalina Hermosillo Durán</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Sindicato Nacional de Trabajadores de la Educación</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Con operativos permanentes mejoran la seguridad en regiones del Estado</t>
+  </si>
+  <si>
+    <t>La SSPH emitió un comunicado para ratificar que mantiene desplegados operativos policiales de manera permanente durante los 365 días del año en las distintas regiones de Hidalgo. Las brigadas realizan patrullajes de proximidad social, vigilancia activa y presencia preventiva, exhortando a reportar anomalías al 911 o 089.</t>
+  </si>
+  <si>
+    <t>Operativo de Seguridad</t>
+  </si>
+  <si>
+    <t>La SSPH reafirmó el despliegue permanente de patrullas y tareas de proximidad social en las regiones de Hidalgo para preservar la tranquilidad.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo</t>
+  </si>
+  <si>
+    <t>Impartieron una conferencia para evitar casos de extorsión</t>
+  </si>
+  <si>
+    <t>La Secretaría de Seguridad Ciudadana de Tizayuca organizó un curso de adiestramiento técnico para sus oficiales en materia de identificación, prevención y combate al delito de extorsión. El taller fue impartido de manera conjunta por Michael Emmanuel Ángeles y el agente Raúl Pimentel, especialistas de la Unidad Especializada en el Combate al Secuestro de la procuraduría estatal.</t>
+  </si>
+  <si>
+    <t>Prevención de Extorsión</t>
+  </si>
+  <si>
+    <t>La policía municipal de Tizayuca recibió capacitación por parte de la UECS de la procuraduría para contener delitos de extorsión telefónica.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Ciudadana de Tizayuca, Procuraduría General de Justicia del Estado de Hidalgo, Unidad Especializada en el Combate al Secuestro (UECS)</t>
+  </si>
+  <si>
+    <t>Michael Emmanuel Ángeles, Raúl Pimentel</t>
+  </si>
+  <si>
+    <t>Policía Estatal aseguró a 2 personas con combustible ilícito</t>
+  </si>
+  <si>
+    <t>Elementos de la SSPH y el Mando Coordinado de Ixmiquilpan interceptaron en el barrio de Santa Ana una camioneta pick-up cargada con 19 garrafones con capacidad de 50 y 60 litros. En total, se aseguraron mil 200 litros de hidrocarburo de procedencia ilícita y se detuvo a dos personas por no acreditar la documentación legal del combustible, quedando a disposición de la FGR en Tula.</t>
+  </si>
+  <si>
+    <t>La SSPH y policías locales decomisaron mil 200 litros de huachicol y detuvieron a dos hombres a bordo de una camioneta de carga en Ixmiquilpan.</t>
+  </si>
+  <si>
+    <t>A balazos perpetran violento crimen</t>
+  </si>
+  <si>
+    <t>En Huejutla de Reyes se registró una violenta ejecución armada en contra de un hombre de 25 años de edad, identificado de forma extraoficial como Jesús Gustavo L., originario de la región. La víctima viajaba a bordo de su vehículo cuando fue atacada con armas de fuego. Tras corroborarse que no contaba con signos vitales, la policía municipal acordonó la escena y la PGJEH inició las investigaciones periciales correspondientes.</t>
+  </si>
+  <si>
+    <t>Homicidios</t>
+  </si>
+  <si>
+    <t>Sujetos armados ejecutaron a un joven de 25 años al interior de su automóvil en Huejutla de Reyes, activándose las diligencias periciales de la procuraduría.</t>
+  </si>
+  <si>
+    <t>Procuraduría General de Justicia del Estado de Hidalgo, Policía Municipal de Huejutla de Reyes</t>
+  </si>
+  <si>
+    <t>Jesús Gustavo L</t>
+  </si>
+  <si>
+    <t>Buscan proteger a los docentes ante denuncias</t>
+  </si>
+  <si>
+    <t>La SEPH respaldó la reforma legal aprobada por el Congreso del Estado de Hidalgo que adiciona el artículo 117 Bis a la Ley de Educación estatal para garantizar la presunción de inocencia de maestros y personal administrativo. El secretario Natividad Castrejón Valdez explicó que trabajarán conjuntamente con los legisladores para definir la aplicación del protocolo, ya que actualmente la normativa obliga a la separación inmediata del cargo ante quejas, afectando injustamente a cientos de docentes cuyas denuncias resultan no corresponder con la realidad.</t>
+  </si>
+  <si>
+    <t>La SEPH respalda la reforma del Congreso para salvaguardar la presunción de inocencia de docentes hidalguenses y estructurar protocolos de mediación ante quejas infundadas.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Congreso del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Analizan reubicar escuela por litigio</t>
+  </si>
+  <si>
+    <t>La SEPH busca mediar un acuerdo armonioso con el legítimo propietario de un terreno en Tezontepec de Aldama donde se edificó, hace 40 años, un plantel de educación media superior tras una donación de buena fe. El secretario Natividad Castrejón Valdez informó que resolver el conflicto legal del predio costaría unos 10 millones de pesos, por lo que paralelamente se evalúa reubicar el plantel aprovechando la infraestructura disponible de educación básica en el municipio para resguardar la inversión física del edificio, la cual asciende a 40 millones de pesos.</t>
+  </si>
+  <si>
+    <t>El titular de la SEPH analiza alternativas de reubicación y negociaciones de indemnización por 10 mdp para solucionar la disputa de tierras de una preparatoria en Tezontepec.</t>
+  </si>
+  <si>
+    <t>Menchaca concluye con Rutas de Reconstrucción</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar formalizó el cierre de la actual fase de las Rutas de la Transformación para la Reconstrucción en Jacala de Ledezma, reportando inversiones por más de 225 millones de pesos asignadas a resarcir los daños por inundaciones de 2025. Destacó que el gobierno de Claudia Sheinbaum aportará 115.7 mdp federales para reconstruir ocho caminos que comunican poblados como Quetzalapa, La Palma y El Aguaje, mientras que la SICT ejecutará los puentes de La Palma (91.28 metros) y Quetzalapa (110 metros) sobre el río Amajac.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar concluyó en Jacala las Rutas de la Reconstrucción con un informe de obras carreteras por 225 mdp respaldado por la federación.</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible, Comisión Estatal del Agua y Alcantarillado, Centro SICT en Hidalgo, Comisión Nacional del Agua, Ayuntamiento de Jacala</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Claudia Sheinbaum Pardo, Pablo Octavio Olvera Sánchez, Kendra Martínez Sánchez, Juan Carlos Chávez González</t>
+  </si>
+  <si>
+    <t>Feria San Francisco abre espacios para artesanos</t>
+  </si>
+  <si>
+    <t>La Secretaría de Bienestar e Inclusión Social de Hidalgo (Sebiso) dio a conocer los resultados de la segunda fase de asignación de espacios del Pabellón Artesanal y Gastronómico de la Feria San Francisco Pachuca 2026, beneficiando a más de 130 artesanos de las regiones del Mezquital, la Huasteca, Sierra y Otomí-Tepehua. El titular Ricardo Gómez Moreno puntualizó que los locales serán completamente gratuitos para promover la comercialización directa, coordinándose con el DIF estatal hospedaje sin costo en sus albergues.</t>
+  </si>
+  <si>
+    <t>La Sebiso asignó espacios gratuitos en el pabellón comercial de la Feria de Pachuca a más de 130 artesanos, facilitando hospedaje sin costo mediante albergues del DIF.</t>
   </si>
 </sst>
 </file>
@@ -1532,8 +1565,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}" name="Tabla1" displayName="Tabla1" ref="A1:AJ68" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ68" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}" name="Tabla1" displayName="Tabla1" ref="A1:AJ70" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ70" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{D3CF0D4E-B6F9-44AC-AB4F-0535BBEB6872}" uniqueName="Canal" name="Canal">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
@@ -1965,7 +1998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DBE5F67-B229-448F-97D5-0E5E46CD1702}">
-  <dimension ref="A1:AJ68"/>
+  <dimension ref="A1:AJ70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -2117,28 +2150,28 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
         <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F2" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -2147,75 +2180,75 @@
         <v>13262</v>
       </c>
       <c r="T2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V2" t="s">
         <v>38</v>
       </c>
       <c r="W2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="X2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="Y2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA2">
         <v>20</v>
       </c>
       <c r="AB2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AD2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="AG2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AH2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="AI2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AJ2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
         <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F3" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -2224,75 +2257,75 @@
         <v>13262</v>
       </c>
       <c r="T3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V3" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="W3" t="s">
+        <v>79</v>
+      </c>
+      <c r="X3" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA3">
+        <v>30</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>113</v>
-      </c>
-      <c r="X3" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA3">
-        <v>20</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B4" t="s">
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F4" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="I4" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -2301,75 +2334,72 @@
         <v>13262</v>
       </c>
       <c r="T4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V4" t="s">
         <v>38</v>
       </c>
       <c r="W4" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="X4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Y4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AD4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG4" t="s">
         <v>41</v>
       </c>
-      <c r="AG4" t="s">
-        <v>42</v>
-      </c>
       <c r="AH4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AI4" t="s">
-        <v>120</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B5" t="s">
         <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F5" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -2378,75 +2408,75 @@
         <v>13262</v>
       </c>
       <c r="T5" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V5" t="s">
         <v>38</v>
       </c>
       <c r="W5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="X5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="Y5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA5">
         <v>20</v>
       </c>
       <c r="AB5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AD5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF5" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="AG5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AH5" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="AI5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AJ5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
         <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F6" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -2455,75 +2485,72 @@
         <v>13262</v>
       </c>
       <c r="T6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V6" t="s">
         <v>38</v>
       </c>
       <c r="W6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="Y6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA6">
         <v>20</v>
       </c>
       <c r="AB6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC6" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="AD6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG6" t="s">
         <v>41</v>
       </c>
-      <c r="AG6" t="s">
-        <v>42</v>
-      </c>
       <c r="AH6" t="s">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="AI6" t="s">
-        <v>131</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B7" t="s">
         <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F7" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>135</v>
+        <v>50</v>
       </c>
       <c r="I7" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -2532,75 +2559,75 @@
         <v>13262</v>
       </c>
       <c r="T7" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V7" t="s">
         <v>38</v>
       </c>
       <c r="W7" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="X7" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="Y7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF7" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="AG7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AH7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AI7" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="AJ7" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
         <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E8" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F8" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -2609,75 +2636,75 @@
         <v>13262</v>
       </c>
       <c r="T8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V8" t="s">
         <v>38</v>
       </c>
       <c r="W8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="X8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="Y8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA8">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AD8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF8" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="AG8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AH8" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="AI8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="AJ8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F9" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="I9" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -2686,75 +2713,75 @@
         <v>13262</v>
       </c>
       <c r="T9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V9" t="s">
         <v>38</v>
       </c>
       <c r="W9" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="X9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="Y9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA9">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AG9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AH9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="AI9" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="AJ9" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F10" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -2763,75 +2790,78 @@
         <v>13262</v>
       </c>
       <c r="T10" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V10" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="W10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="X10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="Y10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA10">
         <v>20</v>
       </c>
       <c r="AB10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD10" t="s">
-        <v>49</v>
+        <v>39</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>87</v>
       </c>
       <c r="AF10" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="AG10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AH10" t="s">
-        <v>61</v>
+        <v>152</v>
       </c>
       <c r="AI10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="AJ10" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E11" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F11" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -2840,75 +2870,75 @@
         <v>13262</v>
       </c>
       <c r="T11" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V11" t="s">
         <v>38</v>
       </c>
       <c r="W11" t="s">
-        <v>160</v>
+        <v>91</v>
       </c>
       <c r="X11" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="Y11" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA11">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB11" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC11" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="AD11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF11" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
       <c r="AG11" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AH11" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="AI11" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AJ11" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E12" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F12" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G12">
         <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2917,75 +2947,78 @@
         <v>13262</v>
       </c>
       <c r="T12" t="s">
+        <v>77</v>
+      </c>
+      <c r="V12" t="s">
+        <v>86</v>
+      </c>
+      <c r="W12" t="s">
+        <v>162</v>
+      </c>
+      <c r="X12" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA12">
+        <v>20</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>164</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH12" t="s">
         <v>83</v>
       </c>
-      <c r="V12" t="s">
-        <v>38</v>
-      </c>
-      <c r="W12" t="s">
-        <v>166</v>
-      </c>
-      <c r="X12" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA12">
-        <v>15</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC12" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH12" t="s">
-        <v>52</v>
-      </c>
       <c r="AI12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="AJ12" t="s">
-        <v>169</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E13" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F13" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -2994,75 +3027,78 @@
         <v>13262</v>
       </c>
       <c r="T13" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V13" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="W13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="X13" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="Y13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB13" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC13" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AD13" t="s">
-        <v>49</v>
+        <v>39</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>87</v>
       </c>
       <c r="AF13" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="AG13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AH13" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="AI13" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AJ13" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
         <v>59</v>
       </c>
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
       <c r="D14" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E14" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F14" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H14" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="I14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -3071,75 +3107,72 @@
         <v>13262</v>
       </c>
       <c r="T14" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V14" t="s">
         <v>38</v>
       </c>
       <c r="W14" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="X14" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="Y14" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="Z14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AB14" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF14" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="AG14" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AH14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AI14" t="s">
-        <v>179</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>46</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
         <v>59</v>
       </c>
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
       <c r="D15" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E15" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F15" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -3148,75 +3181,75 @@
         <v>13262</v>
       </c>
       <c r="T15" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V15" t="s">
         <v>38</v>
       </c>
       <c r="W15" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="X15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Y15" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA15">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB15" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AD15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF15" t="s">
-        <v>183</v>
+        <v>60</v>
       </c>
       <c r="AG15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AH15" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AI15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="AJ15" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" t="s">
         <v>59</v>
       </c>
-      <c r="B16" t="s">
-        <v>60</v>
-      </c>
       <c r="D16" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E16" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F16" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="I16" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -3225,75 +3258,75 @@
         <v>13262</v>
       </c>
       <c r="T16" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V16" t="s">
-        <v>38</v>
+        <v>184</v>
       </c>
       <c r="W16" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="X16" t="s">
+        <v>186</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA16">
+        <v>15</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>187</v>
+      </c>
+      <c r="AG16" t="s">
         <v>188</v>
       </c>
-      <c r="Y16" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA16">
-        <v>24</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>183</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>42</v>
-      </c>
       <c r="AH16" t="s">
-        <v>43</v>
+        <v>189</v>
       </c>
       <c r="AI16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AJ16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s">
         <v>59</v>
       </c>
-      <c r="B17" t="s">
-        <v>60</v>
-      </c>
       <c r="D17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F17" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>64</v>
+        <v>194</v>
       </c>
       <c r="I17" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -3302,78 +3335,75 @@
         <v>13262</v>
       </c>
       <c r="T17" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V17" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="W17" t="s">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="X17" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Y17" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="Z17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA17">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB17" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD17" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AF17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH17" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="AI17" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AJ17" t="s">
-        <v>46</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" t="s">
         <v>59</v>
       </c>
-      <c r="B18" t="s">
-        <v>60</v>
-      </c>
       <c r="D18" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E18" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F18" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -3382,75 +3412,75 @@
         <v>13262</v>
       </c>
       <c r="T18" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V18" t="s">
         <v>38</v>
       </c>
       <c r="W18" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="X18" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Y18" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA18">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB18" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF18" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="AG18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AH18" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="AI18" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AJ18" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" t="s">
         <v>59</v>
       </c>
-      <c r="B19" t="s">
-        <v>60</v>
-      </c>
       <c r="D19" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E19" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F19" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -3459,78 +3489,75 @@
         <v>13262</v>
       </c>
       <c r="T19" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V19" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="W19" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="X19" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Y19" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="Z19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA19">
         <v>20</v>
       </c>
       <c r="AB19" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD19" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AF19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH19" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="AI19" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="AJ19" t="s">
-        <v>46</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" t="s">
         <v>59</v>
       </c>
-      <c r="B20" t="s">
-        <v>60</v>
-      </c>
       <c r="D20" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E20" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F20" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -3539,75 +3566,75 @@
         <v>13262</v>
       </c>
       <c r="T20" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V20" t="s">
         <v>38</v>
       </c>
       <c r="W20" t="s">
-        <v>103</v>
+        <v>213</v>
       </c>
       <c r="X20" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Y20" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA20">
         <v>20</v>
       </c>
       <c r="AB20" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF20" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="AG20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AH20" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="AI20" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="AJ20" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
         <v>59</v>
       </c>
-      <c r="B21" t="s">
-        <v>60</v>
-      </c>
       <c r="D21" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E21" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F21" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H21" t="s">
-        <v>51</v>
+        <v>219</v>
       </c>
       <c r="I21" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -3616,75 +3643,75 @@
         <v>13262</v>
       </c>
       <c r="T21" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V21" t="s">
         <v>38</v>
       </c>
       <c r="W21" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="X21" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="Y21" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA21">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB21" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF21" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="AG21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AH21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="AI21" t="s">
         <v>215</v>
       </c>
       <c r="AJ21" t="s">
-        <v>216</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" t="s">
         <v>59</v>
       </c>
-      <c r="B22" t="s">
-        <v>60</v>
-      </c>
       <c r="D22" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E22" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F22" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G22">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H22" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="I22" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -3693,75 +3720,72 @@
         <v>13262</v>
       </c>
       <c r="T22" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V22" t="s">
         <v>38</v>
       </c>
       <c r="W22" t="s">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c r="X22" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="Y22" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA22">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB22" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF22" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="AG22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AH22" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="AI22" t="s">
-        <v>222</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" t="s">
         <v>59</v>
       </c>
-      <c r="B23" t="s">
-        <v>60</v>
-      </c>
       <c r="D23" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E23" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F23" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G23">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H23" t="s">
-        <v>219</v>
+        <v>54</v>
       </c>
       <c r="I23" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="R23">
         <v>1</v>
@@ -3770,75 +3794,75 @@
         <v>13262</v>
       </c>
       <c r="T23" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V23" t="s">
         <v>38</v>
       </c>
       <c r="W23" t="s">
+        <v>231</v>
+      </c>
+      <c r="X23" t="s">
+        <v>232</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA23">
+        <v>15</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF23" t="s">
         <v>94</v>
       </c>
-      <c r="X23" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA23">
-        <v>24</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC23" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>221</v>
-      </c>
       <c r="AG23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AH23" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="AI23" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="AJ23" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E24" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="F24" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H24" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I24" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -3847,75 +3871,75 @@
         <v>13262</v>
       </c>
       <c r="T24" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V24" t="s">
         <v>38</v>
       </c>
       <c r="W24" t="s">
-        <v>231</v>
+        <v>93</v>
       </c>
       <c r="X24" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="Y24" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA24">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AB24" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF24" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="AG24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AH24" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="AI24" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AJ24" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E25" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="F25" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G25">
         <v>4</v>
       </c>
       <c r="H25" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="I25" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="R25">
         <v>1</v>
@@ -3924,75 +3948,75 @@
         <v>13262</v>
       </c>
       <c r="T25" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V25" t="s">
         <v>38</v>
       </c>
       <c r="W25" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
       <c r="X25" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Y25" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA25">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB25" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF25" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="AG25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AH25" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="AI25" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="AJ25" t="s">
-        <v>239</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E26" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="F26" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G26">
         <v>4</v>
       </c>
       <c r="H26" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="I26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R26">
         <v>1</v>
@@ -4001,75 +4025,75 @@
         <v>13262</v>
       </c>
       <c r="T26" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V26" t="s">
-        <v>38</v>
+        <v>184</v>
       </c>
       <c r="W26" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="X26" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="Y26" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA26">
         <v>12</v>
       </c>
       <c r="AB26" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AD26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF26" t="s">
-        <v>76</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s">
+        <v>188</v>
+      </c>
+      <c r="AH26" t="s">
         <v>42</v>
       </c>
-      <c r="AH26" t="s">
-        <v>72</v>
-      </c>
       <c r="AI26" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AJ26" t="s">
-        <v>46</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="E27" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="F27" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G27">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R27">
         <v>1</v>
@@ -4078,78 +4102,75 @@
         <v>13262</v>
       </c>
       <c r="T27" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V27" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="W27" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="X27" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="Y27" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="Z27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA27">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD27" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE27" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AF27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH27" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="AI27" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AJ27" t="s">
-        <v>46</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D28" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="E28" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="F28" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G28">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>64</v>
+        <v>259</v>
       </c>
       <c r="I28" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R28">
         <v>1</v>
@@ -4158,75 +4179,75 @@
         <v>13262</v>
       </c>
       <c r="T28" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V28" t="s">
         <v>38</v>
       </c>
       <c r="W28" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="X28" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="Y28" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA28">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AB28" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD28" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH28" t="s">
         <v>49</v>
       </c>
-      <c r="AF28" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG28" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH28" t="s">
-        <v>61</v>
-      </c>
       <c r="AI28" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="AJ28" t="s">
-        <v>255</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D29" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E29" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="F29" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H29" t="s">
-        <v>64</v>
+        <v>265</v>
       </c>
       <c r="I29" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -4235,72 +4256,72 @@
         <v>13262</v>
       </c>
       <c r="T29" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V29" t="s">
         <v>38</v>
       </c>
       <c r="W29" t="s">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="X29" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="Y29" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z29" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA29">
+        <v>24</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC29" t="s">
         <v>39</v>
       </c>
-      <c r="AA29">
-        <v>30</v>
-      </c>
-      <c r="AB29" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>40</v>
-      </c>
       <c r="AD29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF29" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AG29" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH29" t="s">
         <v>42</v>
       </c>
-      <c r="AH29" t="s">
-        <v>43</v>
-      </c>
       <c r="AI29" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="AJ29" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D30" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="E30" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="F30" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G30">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H30" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="I30" t="s">
         <v>37</v>
@@ -4312,75 +4333,75 @@
         <v>13262</v>
       </c>
       <c r="T30" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V30" t="s">
         <v>38</v>
       </c>
       <c r="W30" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="X30" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="Y30" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA30">
         <v>20</v>
       </c>
       <c r="AB30" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF30" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AG30" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH30" t="s">
         <v>42</v>
       </c>
-      <c r="AH30" t="s">
-        <v>50</v>
-      </c>
       <c r="AI30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AJ30" t="s">
-        <v>132</v>
+        <v>198</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D31" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E31" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F31" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G31">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H31" t="s">
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="I31" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -4389,75 +4410,75 @@
         <v>13262</v>
       </c>
       <c r="T31" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V31" t="s">
         <v>38</v>
       </c>
       <c r="W31" t="s">
-        <v>142</v>
+        <v>254</v>
       </c>
       <c r="X31" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Y31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA31">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB31" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC31" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AD31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF31" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="AG31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AH31" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="AI31" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="AJ31" t="s">
-        <v>271</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D32" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E32" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F32" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H32" t="s">
-        <v>274</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R32">
         <v>1</v>
@@ -4466,75 +4487,78 @@
         <v>13262</v>
       </c>
       <c r="T32" t="s">
+        <v>77</v>
+      </c>
+      <c r="V32" t="s">
+        <v>86</v>
+      </c>
+      <c r="W32" t="s">
+        <v>162</v>
+      </c>
+      <c r="X32" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA32">
+        <v>20</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>87</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH32" t="s">
         <v>83</v>
       </c>
-      <c r="V32" t="s">
-        <v>38</v>
-      </c>
-      <c r="W32" t="s">
-        <v>275</v>
-      </c>
-      <c r="X32" t="s">
-        <v>276</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z32" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA32">
-        <v>15</v>
-      </c>
-      <c r="AB32" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH32" t="s">
-        <v>50</v>
-      </c>
       <c r="AI32" t="s">
-        <v>277</v>
+        <v>165</v>
       </c>
       <c r="AJ32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
+        <v>278</v>
+      </c>
+      <c r="E33" t="s">
         <v>279</v>
       </c>
-      <c r="E33" t="s">
-        <v>280</v>
-      </c>
       <c r="F33" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H33" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I33" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -4543,75 +4567,75 @@
         <v>13262</v>
       </c>
       <c r="T33" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V33" t="s">
         <v>38</v>
       </c>
       <c r="W33" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="X33" t="s">
+        <v>280</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA33">
+        <v>24</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF33" t="s">
         <v>281</v>
       </c>
-      <c r="Y33" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z33" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA33">
-        <v>15</v>
-      </c>
-      <c r="AB33" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC33" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD33" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>278</v>
-      </c>
       <c r="AG33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AH33" t="s">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="AI33" t="s">
         <v>282</v>
       </c>
       <c r="AJ33" t="s">
-        <v>132</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D34" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E34" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F34" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G34">
         <v>10</v>
       </c>
       <c r="H34" t="s">
-        <v>138</v>
+        <v>286</v>
       </c>
       <c r="I34" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -4620,75 +4644,75 @@
         <v>13262</v>
       </c>
       <c r="T34" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V34" t="s">
         <v>38</v>
       </c>
       <c r="W34" t="s">
-        <v>160</v>
+        <v>287</v>
       </c>
       <c r="X34" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Y34" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA34">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB34" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC34" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AD34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH34" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="AI34" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AJ34" t="s">
-        <v>163</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D35" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E35" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F35" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G35">
         <v>10</v>
       </c>
       <c r="H35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R35">
         <v>1</v>
@@ -4697,72 +4721,75 @@
         <v>13262</v>
       </c>
       <c r="T35" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V35" t="s">
         <v>38</v>
       </c>
       <c r="W35" t="s">
-        <v>89</v>
+        <v>292</v>
       </c>
       <c r="X35" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Y35" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="Z35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB35" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AD35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH35" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="AI35" t="s">
-        <v>290</v>
+        <v>294</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D36" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E36" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F36" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G36">
         <v>10</v>
       </c>
       <c r="H36" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="I36" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -4771,72 +4798,75 @@
         <v>13262</v>
       </c>
       <c r="T36" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V36" t="s">
         <v>38</v>
       </c>
       <c r="W36" t="s">
-        <v>90</v>
+        <v>241</v>
       </c>
       <c r="X36" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Y36" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="Z36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB36" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC36" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="AD36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH36" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="AI36" t="s">
-        <v>294</v>
+        <v>244</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D37" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E37" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F37" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G37">
         <v>10</v>
       </c>
       <c r="H37" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="I37" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -4845,72 +4875,75 @@
         <v>13262</v>
       </c>
       <c r="T37" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V37" t="s">
         <v>38</v>
       </c>
       <c r="W37" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="X37" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Y37" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="Z37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA37">
         <v>10</v>
       </c>
       <c r="AB37" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AD37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH37" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="AI37" t="s">
-        <v>298</v>
+        <v>215</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F38" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G38">
         <v>10</v>
       </c>
       <c r="H38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I38" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R38">
         <v>1</v>
@@ -4919,72 +4952,75 @@
         <v>13262</v>
       </c>
       <c r="T38" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V38" t="s">
         <v>38</v>
       </c>
       <c r="W38" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="X38" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Y38" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="Z38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA38">
         <v>10</v>
       </c>
       <c r="AB38" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AD38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH38" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AI38" t="s">
-        <v>304</v>
+        <v>307</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D39" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E39" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F39" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G39">
         <v>10</v>
       </c>
       <c r="H39" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I39" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R39">
         <v>1</v>
@@ -4993,72 +5029,75 @@
         <v>13262</v>
       </c>
       <c r="T39" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V39" t="s">
         <v>38</v>
       </c>
       <c r="W39" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="X39" t="s">
+        <v>312</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA39">
+        <v>6</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>313</v>
+      </c>
+      <c r="AJ39" t="s">
         <v>308</v>
-      </c>
-      <c r="Y39" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z39" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA39">
-        <v>10</v>
-      </c>
-      <c r="AB39" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC39" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD39" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF39" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG39" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH39" t="s">
-        <v>55</v>
-      </c>
-      <c r="AI39" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="D40" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E40" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F40" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R40">
         <v>1</v>
@@ -5067,75 +5106,75 @@
         <v>13262</v>
       </c>
       <c r="T40" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V40" t="s">
         <v>38</v>
       </c>
       <c r="W40" t="s">
-        <v>213</v>
+        <v>88</v>
       </c>
       <c r="X40" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Y40" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA40">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB40" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF40" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="AG40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AH40" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="AI40" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AJ40" t="s">
-        <v>314</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="D41" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E41" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F41" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I41" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -5144,75 +5183,75 @@
         <v>13262</v>
       </c>
       <c r="T41" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V41" t="s">
         <v>38</v>
       </c>
       <c r="W41" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="X41" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Y41" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA41">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB41" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF41" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG41" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH41" t="s">
         <v>70</v>
       </c>
-      <c r="AG41" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH41" t="s">
-        <v>43</v>
-      </c>
       <c r="AI41" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AJ41" t="s">
-        <v>319</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B42" t="s">
         <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E42" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F42" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42" t="s">
-        <v>274</v>
+        <v>324</v>
       </c>
       <c r="I42" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="R42">
         <v>1</v>
@@ -5221,69 +5260,72 @@
         <v>13262</v>
       </c>
       <c r="T42" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V42" t="s">
         <v>38</v>
       </c>
       <c r="W42" t="s">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="X42" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Y42" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA42">
         <v>15</v>
       </c>
       <c r="AB42" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF42" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="AG42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AH42" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AI42" t="s">
-        <v>323</v>
+        <v>327</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="D43" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E43" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F43" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G43">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H43" t="s">
-        <v>64</v>
+        <v>194</v>
       </c>
       <c r="I43" t="s">
         <v>37</v>
@@ -5295,75 +5337,75 @@
         <v>13262</v>
       </c>
       <c r="T43" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V43" t="s">
         <v>38</v>
       </c>
       <c r="W43" t="s">
-        <v>213</v>
+        <v>330</v>
       </c>
       <c r="X43" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Y43" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA43">
         <v>24</v>
       </c>
       <c r="AB43" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF43" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="AG43" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AH43" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="AI43" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="AJ43" t="s">
-        <v>328</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E44" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F44" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G44">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="I44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R44">
         <v>1</v>
@@ -5372,75 +5414,75 @@
         <v>13262</v>
       </c>
       <c r="T44" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V44" t="s">
         <v>38</v>
       </c>
       <c r="W44" t="s">
-        <v>331</v>
+        <v>104</v>
       </c>
       <c r="X44" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Y44" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA44">
         <v>20</v>
       </c>
       <c r="AB44" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC44" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AD44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF44" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="AG44" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AH44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AI44" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AJ44" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E45" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F45" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G45">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H45" t="s">
-        <v>64</v>
+        <v>340</v>
       </c>
       <c r="I45" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -5449,75 +5491,75 @@
         <v>13262</v>
       </c>
       <c r="T45" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V45" t="s">
         <v>38</v>
       </c>
       <c r="W45" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="X45" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Y45" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA45">
         <v>20</v>
       </c>
       <c r="AB45" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF45" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="AG45" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AH45" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="AI45" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AJ45" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D46" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E46" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F46" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G46">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H46" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="I46" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R46">
         <v>1</v>
@@ -5526,72 +5568,72 @@
         <v>13262</v>
       </c>
       <c r="T46" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V46" t="s">
-        <v>38</v>
+        <v>184</v>
       </c>
       <c r="W46" t="s">
-        <v>103</v>
+        <v>347</v>
       </c>
       <c r="X46" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="Y46" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA46">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB46" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC46" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AD46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF46" t="s">
-        <v>44</v>
+        <v>349</v>
       </c>
       <c r="AG46" t="s">
-        <v>44</v>
+        <v>188</v>
       </c>
       <c r="AH46" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="AI46" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="AJ46" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B47" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D47" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="E47" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="F47" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G47">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H47" t="s">
-        <v>51</v>
+        <v>194</v>
       </c>
       <c r="I47" t="s">
         <v>37</v>
@@ -5603,75 +5645,75 @@
         <v>13262</v>
       </c>
       <c r="T47" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V47" t="s">
         <v>38</v>
       </c>
       <c r="W47" t="s">
-        <v>92</v>
+        <v>330</v>
       </c>
       <c r="X47" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="Y47" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA47">
         <v>24</v>
       </c>
       <c r="AB47" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC47" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AI47" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="AJ47" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D48" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="E48" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="F48" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G48">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H48" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="I48" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R48">
         <v>1</v>
@@ -5680,75 +5722,75 @@
         <v>13262</v>
       </c>
       <c r="T48" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V48" t="s">
         <v>38</v>
       </c>
       <c r="W48" t="s">
-        <v>353</v>
+        <v>292</v>
       </c>
       <c r="X48" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="Y48" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA48">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB48" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH48" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="AI48" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="AJ48" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D49" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E49" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F49" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G49">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H49" t="s">
-        <v>359</v>
+        <v>304</v>
       </c>
       <c r="I49" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R49">
         <v>1</v>
@@ -5757,75 +5799,75 @@
         <v>13262</v>
       </c>
       <c r="T49" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V49" t="s">
         <v>38</v>
       </c>
       <c r="W49" t="s">
-        <v>160</v>
+        <v>305</v>
       </c>
       <c r="X49" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Y49" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA49">
         <v>20</v>
       </c>
       <c r="AB49" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC49" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG49" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH49" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AI49" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AJ49" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D50" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E50" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F50" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G50">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H50" t="s">
-        <v>64</v>
+        <v>265</v>
       </c>
       <c r="I50" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="R50">
         <v>1</v>
@@ -5834,75 +5876,75 @@
         <v>13262</v>
       </c>
       <c r="T50" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V50" t="s">
         <v>38</v>
       </c>
       <c r="W50" t="s">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="X50" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Y50" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA50">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AB50" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC50" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF50" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG50" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH50" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="AI50" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AJ50" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D51" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E51" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F51" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G51">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H51" t="s">
-        <v>263</v>
+        <v>50</v>
       </c>
       <c r="I51" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R51">
         <v>1</v>
@@ -5911,72 +5953,75 @@
         <v>13262</v>
       </c>
       <c r="T51" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V51" t="s">
         <v>38</v>
       </c>
       <c r="W51" t="s">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="X51" t="s">
-        <v>371</v>
+        <v>316</v>
       </c>
       <c r="Y51" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA51">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB51" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF51" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG51" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH51" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AI51" t="s">
-        <v>372</v>
+        <v>373</v>
+      </c>
+      <c r="AJ51" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D52" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E52" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F52" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G52">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H52" t="s">
-        <v>274</v>
+        <v>50</v>
       </c>
       <c r="I52" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R52">
         <v>1</v>
@@ -5985,72 +6030,75 @@
         <v>13262</v>
       </c>
       <c r="T52" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V52" t="s">
         <v>38</v>
       </c>
       <c r="W52" t="s">
-        <v>275</v>
+        <v>377</v>
       </c>
       <c r="X52" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Y52" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA52">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB52" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD52" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF52" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG52" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH52" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AI52" t="s">
-        <v>376</v>
+        <v>379</v>
+      </c>
+      <c r="AJ52" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="B53" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D53" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E53" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F53" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G53">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H53" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R53">
         <v>1</v>
@@ -6059,75 +6107,75 @@
         <v>13262</v>
       </c>
       <c r="T53" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V53" t="s">
         <v>38</v>
       </c>
       <c r="W53" t="s">
-        <v>380</v>
+        <v>88</v>
       </c>
       <c r="X53" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Y53" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="Z53" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA53">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AB53" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD53" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF53" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG53" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH53" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="AI53" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AJ53" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D54" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E54" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F54" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G54">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H54" t="s">
-        <v>64</v>
+        <v>388</v>
       </c>
       <c r="I54" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R54">
         <v>1</v>
@@ -6136,72 +6184,72 @@
         <v>13262</v>
       </c>
       <c r="T54" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V54" t="s">
         <v>38</v>
       </c>
       <c r="W54" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="X54" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Y54" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA54">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AB54" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC54" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AD54" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF54" t="s">
-        <v>377</v>
+        <v>43</v>
       </c>
       <c r="AG54" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AH54" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AJ54" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D55" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E55" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F55" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G55">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H55" t="s">
-        <v>263</v>
+        <v>50</v>
       </c>
       <c r="I55" t="s">
         <v>37</v>
@@ -6213,75 +6261,75 @@
         <v>13262</v>
       </c>
       <c r="T55" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V55" t="s">
         <v>38</v>
       </c>
       <c r="W55" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="X55" t="s">
-        <v>392</v>
+        <v>297</v>
       </c>
       <c r="Y55" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z55" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA55">
         <v>20</v>
       </c>
       <c r="AB55" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF55" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG55" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH55" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AI55" t="s">
-        <v>393</v>
+        <v>244</v>
       </c>
       <c r="AJ55" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B56" t="s">
         <v>67</v>
       </c>
       <c r="D56" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E56" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F56" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H56" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I56" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -6290,75 +6338,75 @@
         <v>13262</v>
       </c>
       <c r="T56" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V56" t="s">
         <v>38</v>
       </c>
       <c r="W56" t="s">
-        <v>113</v>
+        <v>254</v>
       </c>
       <c r="X56" t="s">
-        <v>396</v>
+        <v>255</v>
       </c>
       <c r="Y56" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA56">
         <v>20</v>
       </c>
       <c r="AB56" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC56" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD56" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF56" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG56" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH56" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI56" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ56" t="s">
         <v>397</v>
-      </c>
-      <c r="AG56" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH56" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI56" t="s">
-        <v>398</v>
-      </c>
-      <c r="AJ56" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B57" t="s">
         <v>67</v>
       </c>
       <c r="D57" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E57" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F57" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H57" t="s">
-        <v>64</v>
+        <v>286</v>
       </c>
       <c r="I57" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="R57">
         <v>1</v>
@@ -6367,75 +6415,75 @@
         <v>13262</v>
       </c>
       <c r="T57" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V57" t="s">
         <v>38</v>
       </c>
       <c r="W57" t="s">
-        <v>85</v>
+        <v>287</v>
       </c>
       <c r="X57" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="Y57" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA57">
         <v>15</v>
       </c>
       <c r="AB57" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC57" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AD57" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF57" t="s">
-        <v>397</v>
+        <v>43</v>
       </c>
       <c r="AG57" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AH57" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AI57" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AJ57" t="s">
-        <v>132</v>
+        <v>402</v>
       </c>
     </row>
     <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B58" t="s">
         <v>67</v>
       </c>
       <c r="D58" t="s">
+        <v>403</v>
+      </c>
+      <c r="E58" t="s">
         <v>404</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" s="1">
+        <v>46262</v>
+      </c>
+      <c r="G58">
+        <v>14</v>
+      </c>
+      <c r="H58" t="s">
         <v>405</v>
       </c>
-      <c r="F58" s="1">
-        <v>46261</v>
-      </c>
-      <c r="G58">
-        <v>3</v>
-      </c>
-      <c r="H58" t="s">
-        <v>51</v>
-      </c>
       <c r="I58" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R58">
         <v>1</v>
@@ -6444,75 +6492,75 @@
         <v>13262</v>
       </c>
       <c r="T58" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V58" t="s">
         <v>38</v>
       </c>
       <c r="W58" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="X58" t="s">
         <v>406</v>
       </c>
       <c r="Y58" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z58" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA58">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB58" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD58" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF58" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="AG58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AH58" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="AI58" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AJ58" t="s">
-        <v>350</v>
+        <v>409</v>
       </c>
     </row>
     <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B59" t="s">
         <v>67</v>
       </c>
       <c r="D59" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E59" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F59" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H59" t="s">
-        <v>64</v>
+        <v>412</v>
       </c>
       <c r="I59" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="R59">
         <v>1</v>
@@ -6521,75 +6569,72 @@
         <v>13262</v>
       </c>
       <c r="T59" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V59" t="s">
         <v>38</v>
       </c>
       <c r="W59" t="s">
-        <v>410</v>
+        <v>95</v>
       </c>
       <c r="X59" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Y59" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA59">
         <v>20</v>
       </c>
       <c r="AB59" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD59" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF59" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG59" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH59" t="s">
         <v>49</v>
       </c>
-      <c r="AF59" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG59" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH59" t="s">
-        <v>55</v>
-      </c>
       <c r="AI59" t="s">
-        <v>412</v>
-      </c>
-      <c r="AJ59" t="s">
-        <v>46</v>
+        <v>414</v>
       </c>
     </row>
     <row r="60" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D60" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E60" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F60" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H60" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="I60" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R60">
         <v>1</v>
@@ -6598,75 +6643,75 @@
         <v>13262</v>
       </c>
       <c r="T60" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V60" t="s">
-        <v>38</v>
+        <v>184</v>
       </c>
       <c r="W60" t="s">
-        <v>415</v>
+        <v>347</v>
       </c>
       <c r="X60" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Y60" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z60" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA60">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AB60" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC60" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AD60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF60" t="s">
-        <v>98</v>
+        <v>418</v>
       </c>
       <c r="AG60" t="s">
+        <v>188</v>
+      </c>
+      <c r="AH60" t="s">
         <v>42</v>
       </c>
-      <c r="AH60" t="s">
-        <v>55</v>
-      </c>
       <c r="AI60" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="AJ60" t="s">
-        <v>46</v>
+        <v>420</v>
       </c>
     </row>
     <row r="61" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B61" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D61" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E61" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F61" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G61">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H61" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I61" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R61">
         <v>1</v>
@@ -6675,75 +6720,75 @@
         <v>13262</v>
       </c>
       <c r="T61" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V61" t="s">
         <v>38</v>
       </c>
       <c r="W61" t="s">
-        <v>419</v>
+        <v>254</v>
       </c>
       <c r="X61" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="Y61" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA61">
         <v>20</v>
       </c>
       <c r="AB61" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD61" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF61" t="s">
-        <v>421</v>
+        <v>43</v>
       </c>
       <c r="AG61" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AH61" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="AI61" t="s">
-        <v>313</v>
+        <v>256</v>
       </c>
       <c r="AJ61" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
     </row>
     <row r="62" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B62" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D62" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E62" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F62" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G62">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H62" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I62" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="R62">
         <v>1</v>
@@ -6752,78 +6797,75 @@
         <v>13262</v>
       </c>
       <c r="T62" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V62" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="W62" t="s">
-        <v>166</v>
+        <v>241</v>
       </c>
       <c r="X62" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Y62" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="Z62" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA62">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB62" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC62" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD62" t="s">
-        <v>40</v>
-      </c>
-      <c r="AE62" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AF62" t="s">
-        <v>44</v>
+        <v>427</v>
       </c>
       <c r="AG62" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AH62" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AI62" t="s">
-        <v>168</v>
+        <v>428</v>
       </c>
       <c r="AJ62" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="63" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D63" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E63" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F63" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G63">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H63" t="s">
-        <v>389</v>
+        <v>85</v>
       </c>
       <c r="I63" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="R63">
         <v>1</v>
@@ -6832,75 +6874,75 @@
         <v>13262</v>
       </c>
       <c r="T63" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V63" t="s">
         <v>38</v>
       </c>
       <c r="W63" t="s">
-        <v>86</v>
+        <v>432</v>
       </c>
       <c r="X63" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="Y63" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z63" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA63">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB63" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD63" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF63" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG63" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH63" t="s">
         <v>49</v>
       </c>
-      <c r="AF63" t="s">
-        <v>430</v>
-      </c>
-      <c r="AG63" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH63" t="s">
-        <v>45</v>
-      </c>
       <c r="AI63" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AJ63" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B64" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D64" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E64" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="F64" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G64">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H64" t="s">
-        <v>64</v>
+        <v>219</v>
       </c>
       <c r="I64" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="R64">
         <v>1</v>
@@ -6909,75 +6951,75 @@
         <v>13262</v>
       </c>
       <c r="T64" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V64" t="s">
         <v>38</v>
       </c>
       <c r="W64" t="s">
-        <v>231</v>
+        <v>437</v>
       </c>
       <c r="X64" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="Y64" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Z64" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA64">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB64" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD64" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF64" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="AG64" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AH64" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="AI64" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AJ64" t="s">
-        <v>126</v>
+        <v>440</v>
       </c>
     </row>
     <row r="65" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D65" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="E65" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F65" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G65">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H65" t="s">
-        <v>96</v>
+        <v>412</v>
       </c>
       <c r="I65" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R65">
         <v>1</v>
@@ -6986,75 +7028,75 @@
         <v>13262</v>
       </c>
       <c r="T65" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V65" t="s">
         <v>38</v>
       </c>
       <c r="W65" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="X65" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="Y65" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA65">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AB65" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD65" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF65" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG65" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH65" t="s">
         <v>49</v>
       </c>
-      <c r="AF65" t="s">
-        <v>439</v>
-      </c>
-      <c r="AG65" t="s">
-        <v>42</v>
-      </c>
-      <c r="AH65" t="s">
-        <v>43</v>
-      </c>
       <c r="AI65" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="AJ65" t="s">
-        <v>116</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D66" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E66" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F66" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H66" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="I66" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R66">
         <v>1</v>
@@ -7063,75 +7105,75 @@
         <v>13262</v>
       </c>
       <c r="T66" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V66" t="s">
         <v>38</v>
       </c>
       <c r="W66" t="s">
-        <v>142</v>
+        <v>446</v>
       </c>
       <c r="X66" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="Y66" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z66" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA66">
         <v>20</v>
       </c>
       <c r="AB66" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AD66" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF66" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG66" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH66" t="s">
         <v>44</v>
       </c>
-      <c r="AG66" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH66" t="s">
-        <v>45</v>
-      </c>
       <c r="AI66" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="AJ66" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="67" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D67" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E67" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F67" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H67" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="I67" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R67">
         <v>1</v>
@@ -7140,75 +7182,75 @@
         <v>13262</v>
       </c>
       <c r="T67" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V67" t="s">
         <v>38</v>
       </c>
       <c r="W67" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="X67" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="Y67" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z67" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA67">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB67" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC67" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AD67" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF67" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="AG67" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AH67" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AI67" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AJ67" t="s">
-        <v>319</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B68" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D68" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E68" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="F68" s="1">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>263</v>
+        <v>324</v>
       </c>
       <c r="I68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R68">
         <v>1</v>
@@ -7217,49 +7259,203 @@
         <v>13262</v>
       </c>
       <c r="T68" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V68" t="s">
         <v>38</v>
       </c>
       <c r="W68" t="s">
-        <v>264</v>
+        <v>325</v>
       </c>
       <c r="X68" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="Y68" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="Z68" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA68">
         <v>20</v>
       </c>
       <c r="AB68" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AC68" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AD68" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AF68" t="s">
-        <v>439</v>
+        <v>43</v>
       </c>
       <c r="AG68" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH68" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI68" t="s">
+        <v>327</v>
+      </c>
+      <c r="AJ68" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>57</v>
+      </c>
+      <c r="B69" t="s">
+        <v>71</v>
+      </c>
+      <c r="D69" t="s">
+        <v>457</v>
+      </c>
+      <c r="E69" t="s">
+        <v>458</v>
+      </c>
+      <c r="F69" s="1">
+        <v>46262</v>
+      </c>
+      <c r="G69">
+        <v>4</v>
+      </c>
+      <c r="H69" t="s">
+        <v>194</v>
+      </c>
+      <c r="I69" t="s">
+        <v>37</v>
+      </c>
+      <c r="R69">
+        <v>1</v>
+      </c>
+      <c r="S69">
+        <v>13262</v>
+      </c>
+      <c r="T69" t="s">
+        <v>77</v>
+      </c>
+      <c r="V69" t="s">
+        <v>38</v>
+      </c>
+      <c r="W69" t="s">
+        <v>330</v>
+      </c>
+      <c r="X69" t="s">
+        <v>459</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA69">
+        <v>24</v>
+      </c>
+      <c r="AB69" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC69" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD69" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF69" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG69" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH69" t="s">
         <v>42</v>
       </c>
-      <c r="AH68" t="s">
+      <c r="AI69" t="s">
+        <v>460</v>
+      </c>
+      <c r="AJ69" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="70" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>57</v>
+      </c>
+      <c r="B70" t="s">
+        <v>71</v>
+      </c>
+      <c r="D70" t="s">
+        <v>462</v>
+      </c>
+      <c r="E70" t="s">
+        <v>463</v>
+      </c>
+      <c r="F70" s="1">
+        <v>46262</v>
+      </c>
+      <c r="G70">
+        <v>5</v>
+      </c>
+      <c r="H70" t="s">
         <v>50</v>
       </c>
-      <c r="AI68" t="s">
-        <v>453</v>
-      </c>
-      <c r="AJ68" t="s">
-        <v>132</v>
+      <c r="I70" t="s">
+        <v>37</v>
+      </c>
+      <c r="R70">
+        <v>1</v>
+      </c>
+      <c r="S70">
+        <v>13262</v>
+      </c>
+      <c r="T70" t="s">
+        <v>77</v>
+      </c>
+      <c r="V70" t="s">
+        <v>38</v>
+      </c>
+      <c r="W70" t="s">
+        <v>254</v>
+      </c>
+      <c r="X70" t="s">
+        <v>464</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA70">
+        <v>20</v>
+      </c>
+      <c r="AB70" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC70" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>48</v>
+      </c>
+      <c r="AF70" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG70" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH70" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI70" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ70" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B3E42C-1BC6-4E0D-8545-03F284AC25B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93289598-7255-46AE-8868-96116496E313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="425">
   <si>
     <t>Canal</t>
   </si>
@@ -205,9 +205,6 @@
     <t>SEPH</t>
   </si>
   <si>
-    <t>Lizania Zavala</t>
-  </si>
-  <si>
     <t>SSH</t>
   </si>
   <si>
@@ -220,27 +217,15 @@
     <t>Neutro</t>
   </si>
   <si>
-    <t>Impresos locales</t>
-  </si>
-  <si>
     <t>El Sol de Hidalgo</t>
   </si>
   <si>
     <t>El Universal Hidalgo</t>
   </si>
   <si>
-    <t>Lorena Rosas</t>
-  </si>
-  <si>
-    <t>Estatal</t>
-  </si>
-  <si>
     <t>Bienestar</t>
   </si>
   <si>
-    <t>STPSH</t>
-  </si>
-  <si>
     <t>La Jornada Hidalgo</t>
   </si>
   <si>
@@ -286,12 +271,6 @@
     <t>Impresiones locales</t>
   </si>
   <si>
-    <t>Crimen Organizado</t>
-  </si>
-  <si>
-    <t>Incidencia Delictiva</t>
-  </si>
-  <si>
     <t>Carmen Hernández</t>
   </si>
   <si>
@@ -301,1147 +280,1048 @@
     <t>Turismo</t>
   </si>
   <si>
-    <t>Sonia Nochebuena</t>
-  </si>
-  <si>
     <t>Hidalgo</t>
   </si>
   <si>
     <t>Boletín</t>
   </si>
   <si>
-    <t>Comunicado gubernamental</t>
-  </si>
-  <si>
-    <t>Evento Cultural</t>
-  </si>
-  <si>
     <t>Salvador Cruz Neri</t>
   </si>
   <si>
     <t>Huejutla</t>
   </si>
   <si>
-    <t>Apoyo a adultos mayores</t>
-  </si>
-  <si>
     <t>Capacitación docente</t>
   </si>
   <si>
     <t>Desarrollo Urbano</t>
   </si>
   <si>
-    <t>Mirely Santos</t>
-  </si>
-  <si>
-    <t>Robo de hidrocarburo</t>
-  </si>
-  <si>
     <t>Alejandro Reyes</t>
   </si>
   <si>
-    <t>Tlaxcoapan</t>
-  </si>
-  <si>
-    <t>Miguel Ángel Tello Vargas</t>
-  </si>
-  <si>
     <t>Tula</t>
   </si>
   <si>
-    <t>Adela Garmez</t>
-  </si>
-  <si>
     <t>Erick Perales</t>
   </si>
   <si>
-    <t>Trabajan en protocolo de protección a docentes</t>
-  </si>
-  <si>
-    <t>El titular de la SEPH, Natividad Castrejón Valdez, confirmó que en coordinación con el SNTE y el Congreso local, trabajan en un documento para equilibrar el derecho de las infancias y la protección de los docentes ante quejas o demandas por presunta violencia escolar. El funcionario reconoció la obligación de separar temporalmente a maestros de sus funciones ante quejas, pero señaló que existen cientos de casos en los que no corresponden a los hechos, como ocurrió en Zapotlán con dos trabajadores acusados de violación que resultaron inocentes de lo que calificó como una "injuria".</t>
-  </si>
-  <si>
     <t>Violencia Escolar</t>
   </si>
   <si>
-    <t>La SEPH, el SNTE y el Congreso local elaboran un protocolo de mediación para proteger a los docentes frente a denuncias infundadas de violencia escolar, garantizando a la vez el interés superior de la niñez.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Sindicato Nacional de Trabajadores de la Educación, Congreso del Estado de Hidalgo</t>
-  </si>
-  <si>
     <t>Natividad Castrejón Valdez</t>
   </si>
   <si>
-    <t>Suman siete vinculados con grupos criminales</t>
-  </si>
-  <si>
-    <t>Con la aprehensión de Jorge Luis N., alias "Koki", presunto líder de Pueblo Unido y vinculado con La Barredora, en la autopista México-Pachuca, se acumulan en Hidalgo al menos siete detenciones clave de integrantes de grupos criminales nacionales desde 2025. El recuento incluye a K. G. R. C. "El Kenny" (grupo San Luis Rey) capturado en mayo en Tizayuca; R. E. R. M. "El Chelelo" (líder de Los Solas) capturado en Tula; María de los Ángeles N. y Samantha N. (viuda e hija del líder del Cártel de Tláhuac, El Ojos) detenidas en Pachuca; Juan Miguel N. "El Pajarraco" (Guerreros Unidos, vinculado al caso Ayotzinapa) capturado en junio; y Axel Esli N. (La Unión Tepito) capturado en enero en la capital.</t>
-  </si>
-  <si>
-    <t>Reportaje</t>
-  </si>
-  <si>
-    <t>Tras la captura de Jorge Luis N. "El Koki", un recuento de Criterio revela que desde 2025 se han registrado siete arrestos clave en Hidalgo de integrantes de grupos como La Barredora, La Unión Tepito, el Cártel de Tláhuac y Guerreros Unidos.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Procuraduría General de Justicia del Estado de Hidalgo, Fiscalía General de Justicia de la Ciudad de México</t>
-  </si>
-  <si>
-    <t>Jorge Luis N (Koki), Ulises N (Pinto), K. G. R. C. (El Kenny), R. E. R. M. (El Chelelo), María de los Ángeles N, Samantha N, Felipe de Jesús Pérez Luna (El Ojos), Juan Miguel N (El Pajarraco), Axel Esli N</t>
-  </si>
-  <si>
-    <t>Aumentan los delitos en Villa de Tezontepec</t>
-  </si>
-  <si>
-    <t>La PGJEH inició 15 carpetas de investigación en el municipio de Villa de Tezontepec durante el mes de julio de 2026, principalmente por delitos de lesiones dolosas (cuatro carpetas) y violencia familiar (dos denuncias), de acuerdo con datos publicados por el SESNSP. Adicionalmente, el Ministerio Público recibió una denuncia por homicidio doloso cometido con arma de fuego, una carpeta por privación ilegal de la libertad, una indagatoria por discriminación, una por narcomenudeo, una por amenazas y otra por delitos cometidos por servidores públicos.</t>
-  </si>
-  <si>
-    <t>Villa de Tezontepec</t>
-  </si>
-  <si>
-    <t>Datos del SESNSP revelan que en julio de 2026 se iniciaron 15 carpetas de investigación en Villa de Tezontepec, registrándose un repunte en delitos como lesiones dolosas, violencia familiar, homicidio y privación ilegal de la libertad.</t>
-  </si>
-  <si>
-    <t>Procuraduría General de Justicia del Estado de Hidalgo, Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública, Ministerio Público</t>
-  </si>
-  <si>
-    <t>SUTSMP elegirá nueva dirigencia el 5 de septiembre entre 2 planillas</t>
-  </si>
-  <si>
-    <t>El Sindicato Único de Trabajadores al Servicio del Municipio de Pachuca (SUTSMP) realizará el próximo 5 de septiembre las elecciones para renovar su dirigencia entre dos planillas validadas por el Comité Electoral por cumplir con todos los requisitos. Las planillas son la verde ("Por un sindicato para todos", encabezada por Pablo Anaya García) y la azul ("Unidad y democracia sindical", con Irma María de Jesús López Arroyo para la Secretaría General). El secretario del Trabajo estatal, Óscar Javier González Hernández, informó que la dependencia dará acompañamiento al proceso del sindicato, que cuenta con más de mil 390 agremiados.</t>
-  </si>
-  <si>
-    <t>SUTSMP</t>
-  </si>
-  <si>
-    <t>El Sindicato Único de Trabajadores al Servicio del Municipio de Pachuca renovará su dirigencia el 5 de septiembre con la participación de las planillas verde y azul, contando con el acompañamiento de la STPSH para garantizar el apego a la norma.</t>
-  </si>
-  <si>
-    <t>Secretaría del Trabajo y Previsión Social de Hidalgo, Sindicato Único de Trabajadores al Servicio del Municipio de Pachuca, Comité Electoral del SUTSMP</t>
-  </si>
-  <si>
-    <t>Óscar Javier González Hernández, Pablo Anaya García, Irma María de Jesús López Arroyo</t>
-  </si>
-  <si>
-    <t>Carril derecho de Las Torres lleva un 29%</t>
-  </si>
-  <si>
-    <t>La reconstrucción con concreto hidráulico en el carril derecho del bulevar Las Torres, al sur de Pachuca, presenta un avance del 29 por ciento, reportó la Sipdus. Los trabajos actualmente se concentran del kilómetro 0+500 al 0+450 e incorporan obras de drenaje, zampeado y juntas de dilatación en el puente del Río de las Avenidas. La obra fue adjudicada a Ahufe Materiales para la Construcción por un monto de 289 millones 519 mil 74 pesos, iniciada el 22 de mayo con fecha estimada de entrega para el primer trimestre de 2027.</t>
-  </si>
-  <si>
-    <t>Pavimentación hidráulica</t>
-  </si>
-  <si>
-    <t>La Sipdus reportó un avance del 29% en la reconstrucción con concreto hidráulico del carril derecho del bulevar Las Torres, obra que implicará una inversión de 289.5 mdp y concluirá en el primer trimestre de 2027.</t>
-  </si>
-  <si>
     <t>Sipdus</t>
   </si>
   <si>
-    <t>Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible</t>
-  </si>
-  <si>
-    <t>Siete filmes se estrenarán en Pachuca</t>
-  </si>
-  <si>
-    <t>La 30ª edición del Tour de Cine Francés 2026 se presentará en Pachuca del 10 al 23 de septiembre de 2026 en las salas de Cinépolis Galerías y VIP Galerías Pachuca. La vocera del certamen, Sofía Llorente, destacó en entrevista que este festival busca estrechar lazos generacionales y formar audiencias. Las siete películas europeas que integran el programa oficial son: Abandonado, El Camino, El Crimen del 3er Piso, El Desconocido del Gran Arco, La Copia Perfecta, Me Encontraste, y Solo una ilusión. Los pases de Cinebono están a la venta desde el 25 de agosto por un costo de 220 pesos.</t>
-  </si>
-  <si>
-    <t>La edición 30 del Tour de Cine Francés llegará a Cinépolis Pachuca del 10 al 23 de septiembre de 2026 con el estreno de siete largometrajes europeos, ofreciendo esquemas de abono preferencial para el público local.</t>
-  </si>
-  <si>
-    <t>Cinépolis, Secretaría de Cultura de Hidalgo</t>
-  </si>
-  <si>
-    <t>Sofía Llorente</t>
-  </si>
-  <si>
-    <t>La Sinfónica de Hidalgo revivirá la música de José José</t>
-  </si>
-  <si>
-    <t>La Orquesta Sinfónica del Estado de Hidalgo (OSEH) ofrecerá un emotivo homenaje al legado artístico de José José "El Príncipe de la Canción" en el Auditorio Gota de Plata de Pachuca. El espectáculo se llevará a cabo el próximo jueves 17 de septiembre de 2026 a las 19:00 horas, combinando nostalgias y arreglos de tipo sinfónico para revivir los himnos románticos de José Rómulo Sosa Ortiz, quien acumuló más de 120 millones de discos vendidos a nivel internacional.</t>
-  </si>
-  <si>
-    <t>Concierto Sinfónico</t>
-  </si>
-  <si>
-    <t>La Orquesta Sinfónica del Estado de Hidalgo presentará un concierto de homenaje sinfónico a José José en el Auditorio Gota de Plata el próximo 17 de septiembre de 2026.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura del Estado de Hidalgo, Orquesta Sinfónica del Estado de Hidalgo, Auditorio Gota de Plata, Parque Cultural Hidalguense</t>
-  </si>
-  <si>
-    <t>José José (José Rómulo Sosa Ortiz)</t>
-  </si>
-  <si>
-    <t>Anuncia alza salarial de 12% a docentes</t>
-  </si>
-  <si>
-    <t>El secretario general del SNTE, Alfonso Cepeda Salas, anunció en Hidalgo el aumento salarial del 12% a docentes, tras la entrega en Pachuca de estímulos por años de servicio, de 20 a 50 años de antigüedad. Detalló que se logró un despegue salarial de 12.7% entre personal de apoyo y docentes. Acompañado por el secretario de la Sección 15, Said Vargas Sáenz, y el titular de la SEPH, Natividad Castrejón Valdez, explicó que este incremento forma parte del Pliego Nacional de Demandas 2026.</t>
-  </si>
-  <si>
-    <t>Aumento salarial</t>
-  </si>
-  <si>
-    <t>El dirigente nacional del SNTE, Alfonso Cepeda, anunció en Hidalgo un incremento salarial del 12% a docentes, gestionado bajo el Pliego Nacional de Demandas 2026.</t>
-  </si>
-  <si>
-    <t>Sindicato Nacional de Trabajadores de la Educación, Sección 15 del SNTE, Secretaría de Educación Pública de Hidalgo</t>
-  </si>
-  <si>
-    <t>Alfonso Cepeda Salas, Said Vargas Sáenz, Natividad Castrejón Valdez</t>
-  </si>
-  <si>
-    <t>Unidades Médicas Servicio Gratuito</t>
-  </si>
-  <si>
-    <t>Campaña oficial del Gobierno del Estado de Hidalgo, la Secretaría del Despacho del Gobernador y Petróleos Mexicanos (Pemex) para invitar a la ciudadanía a aprovechar las Unidades Médicas que brindan atención integral gratuita de salud en diversas comunidades. Se ofrecen servicios especializados de ultrasonidos, medicamentos, electrocardiogramas, toma de peso, talla, glucosa, triglicéridos y colesterol, además de consultas de medicina general, nutricional y odontológica, en horario de 8:30 a 16:00 horas.</t>
-  </si>
-  <si>
-    <t>Unidad Médica Móvil</t>
-  </si>
-  <si>
-    <t>Pemex y el Despacho del Gobernador promueven las jornadas gratuitas de salud mediante unidades médicas móviles equipadas con ultrasonidos, consultas generales y laboratorios.</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Secretaría del Despacho del Gobernador, Petróleos Mexicanos</t>
-  </si>
-  <si>
-    <t>Bienestar no vigila descuentos de INAPAM</t>
-  </si>
-  <si>
-    <t>El delegado de Programas para el Desarrollo de Hidalgo, Abraham Mendoza Zenteno, admitió públicamente que la Secretaría de Bienestar federal no cuenta con atribuciones legales para vigilar que los concesionarios y las empresas de transporte privado respeten el descuento obligatorio del 50% para adultos mayores poseedores de la credencial del INAPAM. El funcionario reconoció la falta de supervisión directa a los prestadores de servicios tras constantes reclamos ciudadanos.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Bienestar reconoció la inoperancia para fiscalizar y obligar a concesionarios del transporte hidalguense a cumplir con los descuentos de tarjetas INAPAM.</t>
-  </si>
-  <si>
     <t>Alma Leticia Sánchez</t>
   </si>
   <si>
-    <t>Secretaría de Bienestar, Instituto Nacional de las Personas Adultas Mayores (INAPAM)</t>
-  </si>
-  <si>
-    <t>Abraham Mendoza Zenteno</t>
-  </si>
-  <si>
-    <t>Datos Generales: Epic Traverse</t>
-  </si>
-  <si>
-    <t>Anuncio promocional del evento de aventura de deportes extremos 'Epic Traverse' a desarrollarse del 23 al 25 de octubre de 2026 en el estado de Hidalgo. Con la participación de 150 competidores equipados con vestimenta deportiva, se desarrollará un recorrido de aproximadamente dos días iniciando a las 6:00 horas, el cual abarca 9 municipios: Mineral del Chico, Atotonilco el Grande, Actopan, Santiago de Anaya, Cardonal, Metztitlán, Ixmiquilpan, Tasquillo y Zimapán.</t>
-  </si>
-  <si>
-    <t>Turismo Deportivo</t>
-  </si>
-  <si>
-    <t>Promoción del reto 'Epic Traverse' en Hidalgo para octubre de 2026, convocando a 150 atletas de alto rendimiento a recorrer senderos de 9 municipios del estado.</t>
-  </si>
-  <si>
-    <t>Anuncio oficial</t>
-  </si>
-  <si>
-    <t>Secretaría de Turismo de Hidalgo</t>
-  </si>
-  <si>
-    <t>Adultos mayores deben ejercitarse</t>
-  </si>
-  <si>
-    <t>El Instituto Hidalguense del Deporte (Inhide) emitió una serie de recomendaciones para invitar a las personas adultas mayores a realizar actividad física de manera constante, señalando que la práctica cotidiana de ejercicio representa una herramienta fundamental para favorecer el envejecimiento activo, ayudándoles a preservar su movilidad, independencia y calidad de vida integral.</t>
-  </si>
-  <si>
-    <t>Envejecimiento saludable</t>
-  </si>
-  <si>
-    <t>El Inhide recomendó implementar rutinas de ejercicio diario para personas adultas mayores como medida preventiva de preservación motriz y envejecimiento activo.</t>
-  </si>
-  <si>
-    <t>Instituto Hidalguense del Deporte</t>
-  </si>
-  <si>
-    <t>Encabeza Hidalgo las muertes por Covid-19</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud federal y la Dirección General de Epidemiología informaron que el estado de Hidalgo alcanzó 12 muertes acumuladas por Covid-19 en lo que va del año, colocándose como el primer lugar nacional de mortalidad en el país. El reporte indicó un acumulado de 162 casos positivos, registrándose tres fallecimientos y ocho nuevos contagios confirmados durante la tercera semana de agosto. Hidalgo concentra el 23.5 por ciento de los decesos reportados a nivel nacional.</t>
-  </si>
-  <si>
-    <t>Mortalidad Covid-19</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud federal confirma que Hidalgo encabeza el índice nacional de mortalidad por Covid-19, sumando 12 muertes asociadas al virus en el transcurso del año.</t>
-  </si>
-  <si>
-    <t>Secretaría de Salud federal, Dirección General de Epidemiología, Secretaría de Salud de Hidalgo</t>
-  </si>
-  <si>
-    <t>El estado tiene déficit de 4 mil operadores de maquinaria</t>
-  </si>
-  <si>
-    <t>El secretario del Trabajo de Hidalgo, Óscar Javier González Hernández, informó que el sector productivo estatal presenta una escasez aproximada de 4 mil operadores de maquinaria pesada (como soldadores, técnicos en construcción y operadores de trascabos), perfiles que alcanzan salarios de hasta 30 mil pesos mensuales debido a la alta especialización. Ante ello, la STPSH y el Icathi capacitan a interesados en simuladores móviles con escenarios virtuales. Durante la inauguración de la Feria del Empleo se ofertaron 800 vacantes.</t>
-  </si>
-  <si>
-    <t>Mano de obra especializada</t>
-  </si>
-  <si>
-    <t>La Secretaría del Trabajo local reportó un déficit de 4 mil plazas de operadores de maquinaria pesada, impulsando programas virtuales de adiestramiento técnico mediante el Icathi.</t>
-  </si>
-  <si>
-    <t>Secretaría del Trabajo y Previsión Social de Hidalgo, Instituto de Capacitación para el Trabajo de Hidalgo (Icathi)</t>
-  </si>
-  <si>
-    <t>Óscar Javier González Hernández</t>
-  </si>
-  <si>
-    <t>Tula: sí se puede</t>
-  </si>
-  <si>
-    <t>Columna de opinión del contralor estatal Álvaro Bardales que aborda la histórica problemática de contaminación ambiental y descargas residuales sobre el río Tula. Resalta que, de cara al cuarto informe del gobernador Julio Menchaca Salazar, la Comisión Estatal del Agua y Alcantarillado (CEAA) ejecutó una trascendental obra de infraestructura de más de 34 kilómetros de colectores que beneficiará a 120 mil habitantes, conduciendo las aguas residuales hacia la termoeléctrica de CFE para su tratamiento y uso industrial.</t>
-  </si>
-  <si>
     <t>Opinión</t>
   </si>
   <si>
-    <t>Saneamiento ambiental río Tula</t>
-  </si>
-  <si>
-    <t>Álvaro Bardales destaca el impacto ecológico de la red de colectores hídricos en Tula, que captará residuos de 120 mil pobladores para ser tratados y reutilizados por CFE.</t>
-  </si>
-  <si>
-    <t>Álvaro Bardales</t>
-  </si>
-  <si>
     <t>Columnista</t>
   </si>
   <si>
-    <t>Contraloría</t>
-  </si>
-  <si>
-    <t>Comisión Estatal del Agua y Alcantarillado (CEAA), Comisión Federal de Electricidad (CFE), Gobierno del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Álvaro Bardales, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Invertirán 225 millones de pesos para Jacala</t>
-  </si>
-  <si>
-    <t>Durante su gira de trabajo por la sierra de Jacala de Ledezma, en el marco de las Rutas de la Transformación, el gobernador Julio Menchaca Salazar informó una inversión de 225 mdp coordinada con la federación para restaurar caminos y puentes afectados por la vaguada monzónica. El titular federal de la SICT, Pablo Octavio Olvera Sánchez, detalló la reconstrucción de 8 caminos ejidales de conectividad y la edificación de los puentes de La Palma (91.28 metros) y Quetzalapa (110 metros).</t>
-  </si>
-  <si>
-    <t>Jacala</t>
-  </si>
-  <si>
-    <t>Reconstrucción carretera por lluvias</t>
-  </si>
-  <si>
-    <t>El Gobierno del Estado y la federación inyectarán un presupuesto de 225 mdp en Jacala para rehabilitar la red de caminos y puentes colapsados por los meteoros climatológicos.</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Secretaría de Infraestructura, Comunicaciones y Transportes (SICT)</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Pablo Octavio Olvera Sánchez</t>
-  </si>
-  <si>
-    <t>Firman convenio para mapeo de las expresiones rituales estatales</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura de Hidalgo, bajo la dirección de Neyda Naranjo Baltazar, y el Ciesas, representado por Francisco Fernández de Castro Santos, firmaron un convenio general de colaboración científica para instrumentar la 'Cartografía Ritual del Estado de Hidalgo'. El proyecto combinará la investigación etnográfica con tecnologías y sistemas de información geográfica geoespaciales para documentar y conservar el patrimonio y folclor intangible de las comunidades de la entidad.</t>
-  </si>
-  <si>
-    <t>Conservación del patrimonio tradicional</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura y el Ciesas signaron una agenda académica para mapear digitalmente las expresiones rituales hidalguenses mediante sistemas geográficos.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura del Estado de Hidalgo, Centro de Investigaciones y Estudios Superiores en Antropología Social (Ciesas)</t>
-  </si>
-  <si>
-    <t>Neyda Naranjo Baltazar, Francisco Fernández de Castro Santos</t>
-  </si>
-  <si>
-    <t>Artesanos, con espacios gratuitos en la feria 2026</t>
-  </si>
-  <si>
-    <t>El titular de la Secretaría de Bienestar e Inclusión Social (Sebiso), Ricardo Gómez Moreno, dio a conocer que más de 130 artesanos de Hidalgo dispondrán de stands completamente gratuitos en el Pabellón Artesanal y Gastronómico de la Feria de Pachuca 2026 (del 24 de septiembre al 18 de octubre). Asimismo, con el propósito de facilitar la participación y mitigar los costos de creadores del Mezquital, la Huasteca y Otomí-Tepehua, el DIF Estatal les proporcionará hospedaje sin costo en sus albergues.</t>
-  </si>
-  <si>
-    <t>Fomento artesanal regional</t>
-  </si>
-  <si>
-    <t>La Sebiso otorgará espacios exentos de pago a 130 artesanos hidalguenses en el pabellón comercial de la Feria de Pachuca, coordinando subsidios de hospedaje con el DIFH.</t>
-  </si>
-  <si>
-    <t>Secretaría de Bienestar e Inclusión Social, Sistema DIF Hidalgo, Feria San Francisco Pachuca 2026</t>
-  </si>
-  <si>
-    <t>Ricardo Gómez Moreno</t>
-  </si>
-  <si>
-    <t>Las familias recurren a compras de última hora por el regreso a clases</t>
-  </si>
-  <si>
-    <t>De cara al inicio del ciclo escolar 2026-2027 programado para el lunes 31 de agosto, familias hidalguenses efectúan compras de última hora este fin de semana para adquirir libretas, mochilas y uniformes. Madres como Yareli Gómez explicaron que esperaron el cobro de la quincena para mitigar gastos que se sitúan entre los 2 mil y los 10 mil pesos en colegios públicos y privados. La SEPH prevé la reincorporación de 650 mil estudiantes, efectuándose la inauguración oficial en la Secundaria General 2.</t>
-  </si>
-  <si>
-    <t>Economía familiar regreso a clases</t>
-  </si>
-  <si>
-    <t>Padres de familia saturan comercios papeleros de Pachuca por compras escolares tardías ante el inminente inicio de cursos de 650 mil alumnos de educación básica.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo (SEPH)</t>
-  </si>
-  <si>
-    <t>Yareli Gómez</t>
-  </si>
-  <si>
-    <t>Asegura SEPH cobertura total en escuelas, tras protestas en Tizayuca</t>
-  </si>
-  <si>
-    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, garantizó que el 100 por ciento de los alumnos de educación básica en el estado tienen asegurado un espacio en planteles públicos. Respondió así a las recientes protestas de padres de familia en Tizayuca, quienes reportaban un déficit de 300 lugares en primarias y secundarias. Explicó que ante crecimientos demográficos severos se activan protocolos para canalizar matrículas a las opciones escolares de mayor proximidad.</t>
-  </si>
-  <si>
     <t>Tizayuca</t>
   </si>
   <si>
-    <t>Garantía de matrícula básica</t>
-  </si>
-  <si>
-    <t>El titular de la SEPH disipó temores vecinales y garantizó que se solventó la saturación de inscripciones en el fraccionamiento Héroes de Tizayuca ofreciendo planteles alternos.</t>
-  </si>
-  <si>
-    <t>Protesta personal de hospital de Zimapán</t>
-  </si>
-  <si>
-    <t>Trabajadores eventuales y de base del hospital general de Zimapán realizaron una manifestación pacífica en las instalaciones médicas para exigir certeza laboral, incremento salarial y su incorporación al esquema de federalización. Señalaron que el pasado 30 de junio entregaron una petición formal sin recibir respuesta tras cumplirse el plazo. Asimismo, expusieron que laboran en condiciones precarias ante la escasez de insumos, medicamentos, estudios clínicos y especialistas de salud.</t>
-  </si>
-  <si>
-    <t>Zimapán</t>
-  </si>
-  <si>
-    <t>Protesta y carencias hospitalarias</t>
-  </si>
-  <si>
-    <t>Trabajadores del hospital de Zimapán protestaron en demanda de certeza laboral y federalización de plazas, exponiendo desabasto crítico de insumos y medicamentos.</t>
-  </si>
-  <si>
-    <t>Erika Gutiérrez</t>
-  </si>
-  <si>
-    <t>Secretaría de Salud de Hidalgo, Hospital de Zimapán, IMSS-Bienestar</t>
-  </si>
-  <si>
-    <t>La rehabilitación de la biblioteca Sor Juana, en Tulancingo, en 2027</t>
-  </si>
-  <si>
-    <t>La secretaria de Cultura de Hidalgo, Neyda Naranjo Baltazar, informó que hay un proyecto aprobado para rehabilitar estructuralmente el techo y remodelar las instalaciones de la biblioteca Sor Juana Inés de la Cruz en el centro de Tulancingo, así como la biblioteca central Ricardo Garibay de Pachuca. Sin embargo, aclaró que, tras celebrar mesas de planeación con la Secretaría de Hacienda local, la asignación y ejecución de los recursos iniciará formalmente en el presupuesto del ejercicio fiscal 2027.</t>
-  </si>
-  <si>
-    <t>Remodelación de recintos culturales</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura postergó para el año 2027 los trabajos de reconstrucción de techumbre de la biblioteca Sor Juana de Tulancingo por calendarización de Hacienda.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura de Hidalgo, Secretaría de Hacienda de Hidalgo, Biblioteca Sor Juana Inés de la Cruz, Biblioteca Central Ricardo Garibay</t>
-  </si>
-  <si>
-    <t>Neyda Naranjo Baltazar</t>
-  </si>
-  <si>
-    <t>Ante llegada del tren, presentan propuesta de crecimiento urbano</t>
-  </si>
-  <si>
-    <t>Pachuca y Mineral de la Reforma publicaron en el Periódico Oficial del estado (POEH) el Programa Parcial de Desarrollo Urbano, el cual considera, entre otras cosas, una propuesta de estructura urbana, vial y de accesibilidad a la estación del Tren México-Pachuca (tramo AIFA-Pachuca). El esquema considera dos centros urbanos estratégicos, cinco centros de barrio, zonas de densificación vertical en Venta Prieta, Las Águilas y El Chacón, un circuito ciclista para movilidad activa, un Fondo Municipal de Infraestructura Verde y un sistema metropolitano de monitoreo de zonas de riesgo de inundación.</t>
-  </si>
-  <si>
-    <t>Pachuca y Mineral de la Reforma publicaron el Programa Parcial de Desarrollo Urbano, contemplando estructura vial y de accesibilidad para la estación del Tren México-Pachuca.</t>
-  </si>
-  <si>
-    <t>Sipdus, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>Reconocen a más de mil docentes por hasta 50 años de servicio</t>
-  </si>
-  <si>
-    <t>Un total de mil 912 docentes de Hidalgo fueron reconocidos por sus años de servicio en el sector educativo con estímulos y medallas por cumplir de 20 a 50 años de trayectoria. El acto fue encabezado por el dirigente nacional del SNTE, Alfonso Cepeda Salas; el líder de la Sección 15, Said Vargas Sáenz, y el titular de la SEPH, Natividad Castrejón Valdez, quienes destacaron los incrementos salariales y de prestaciones logrados durante sus gestiones. Además, se anunció que la elección para renovar la dirigencia de la Sección XV podría posponerse hasta después de los comicios locales de 2027.</t>
-  </si>
-  <si>
-    <t>Reconocimiento</t>
-  </si>
-  <si>
-    <t>Un total de mil 912 docentes hidalguenses de la Sección 15 del SNTE fueron reconocidos con estímulos y medallas por hasta 50 años de servicio, destacándose mejoras salariales.</t>
-  </si>
-  <si>
     <t>Dulce Castillo</t>
   </si>
   <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Sindicato Nacional de Trabajadores de la Educación, Sección 15 del SNTE</t>
-  </si>
-  <si>
-    <t>Balcón Político: Hidalgo, entre inversiones millonarias e informalidad</t>
-  </si>
-  <si>
-    <t>Columna de análisis económico que confronta los 21 mil mdp en anuncios de inversión estatales y los 145 mil mdp consolidados en cuatro años por Julio Menchaca frente a las cifras del INEGI que devela una informalidad laboral del 72% en el estado, sumándose 31 mil personas al sector informal y registrándose pérdidas de empleos en la agricultura y restaurantes.</t>
-  </si>
-  <si>
-    <t>Informalidad laboral</t>
-  </si>
-  <si>
-    <t>Carlos Camacho contrasta el auge de inversiones por 145 mil mdp en Hidalgo frente a una tasa del 72% de informalidad laboral que afecta a un millón de hidalguenses.</t>
-  </si>
-  <si>
-    <t>Carlos Camacho</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Instituto Nacional de Estadística y Geografía, Cooperativa Cruz Azul</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Carlos Camacho</t>
-  </si>
-  <si>
-    <t>Más de 130 artesanos participarán en pabellón de Feria de San Francisco</t>
-  </si>
-  <si>
-    <t>El titular de la Sebiso, Ricardo Gómez Moreno, dio a conocer los resultados de la asignación gratuita de espacios para el Pabellón Artesanal y Gastronómico de la Feria San Francisco Pachuca 2026 (del 24 de septiembre al 18 de octubre), beneficiando a más de 130 artesanos de las regiones del Mezquital, Otomí-Tepehua, la Huasteca, la Sierra y los valles de Pachuca y Tulancingo. Se coordinará hospedaje gratuito con los albergues del DIF estatal.</t>
-  </si>
-  <si>
     <t>Apoyo a artesanos</t>
   </si>
   <si>
-    <t>La Sebiso otorgará espacios gratuitos en la Feria de Pachuca a más de 130 artesanos regionales, quienes recibirán hospedaje subsidiado mediante el DIFH.</t>
-  </si>
-  <si>
-    <t>Secretaría de Bienestar e Inclusión Social, Sistema DIF Hidalgo, Patronato de la Feria San Francisco Pachuca 2026</t>
-  </si>
-  <si>
-    <t>Atacan a balazos casa en Tlamaco; van 2 agresiones</t>
-  </si>
-  <si>
-    <t>Una casa habitación de la comunidad de Tlamaco, municipio de Atitalaquia, fue atacada con arma de fuego la noche del miércoles, sin que se reportaran personas muertas o heridas, ni detenidos. De acuerdo con fuentes de la Secretaría de Seguridad Pública municipal, el ataque ocurrió minutos después de las 22:00 horas, luego de que vecinos reportaran primero una explosión y posteriormente detonaciones de arma de fuego. Al llegar al lugar, elementos policiales localizaron una vivienda de dos pisos con impactos de bala dirigidos hacia una ventana del segundo piso, cuyos vidrios quedaron destruidos. También se reportó que vecinos vieron varias camionetas con personas armadas en la zona.</t>
-  </si>
-  <si>
-    <t>Atitalaquia</t>
-  </si>
-  <si>
     <t>Ataque Armado</t>
   </si>
   <si>
-    <t>Una vivienda en la comunidad de Tlamaco, Atitalaquia, fue atacada a balazos por sujetos armados a bordo de camionetas, lo que movilizó a la policía local sin reportarse heridos.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Procuraduría General de Justicia de Hidalgo, Guardia Nacional</t>
-  </si>
-  <si>
-    <t>Destinan 178 mdp a obras y movilidad en La Misión</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar encabezó su quinta gira de trabajo en La Misión, como parte del programa Rutas de la Transformación para la Reconstrucción, donde informó sobre las acciones para reparar los daños ocasionados por la vaguada monzónica y restablecer la movilidad en la región. Durante la jornada se dio a conocer que el Gobierno de México, a través de la SICT, invertirá más de 178 millones de pesos para la reconstrucción de 24 caminos y un puente peatonal en el municipio, beneficiando a diversas localidades.</t>
-  </si>
-  <si>
-    <t>La Misión</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca anunció una inversión de 178 mdp por parte de la SICT federal para reconstruir 24 caminos y un puente peatonal afectados por las lluvias en La Misión.</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Secretaría de Infraestructura, Comunicaciones y Transportes (SICT), Comisión Estatal del Agua y Alcantarillado (CEAA)</t>
-  </si>
-  <si>
-    <t>Dan 115.7 mdp a caminos de Jacala</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar visitó Jacala de Ledezma para concluir la actual etapa del programa Rutas de la Transformación para la Reconstrucción, donde informó que se destinan más de 225 millones de pesos para atender los caminos dañados por las lluvias. Del monto total, el Gobierno de México aportará más de 115.7 millones de pesos para la modernización del camino Jacala-Quetzalapa, pavimentaciones y construcción de sistemas de agua potable en beneficio de comunidades de la región serrana.</t>
-  </si>
-  <si>
-    <t>Rehabilitación carretera</t>
-  </si>
-  <si>
-    <t>En su visita a Jacala, el gobernador Julio Menchaca detalló que la federación aportará 115.7 mdp para reconstruir ocho caminos ejidales y dos puentes colapsados por meteoros climatológicos.</t>
-  </si>
-  <si>
-    <t>Más de 130 artesanos estarán en pabellón</t>
-  </si>
-  <si>
-    <t>La Secretaría de Bienestar e Inclusión Social de Hidalgo (Sebiso) informó que más de 130 artesanos participarán en la Feria San Francisco Pachuca 2026, la cual se realizará del 24 de septiembre al 18 de octubre de 2026. El titular de la dependencia, Ricardo Gómez Moreno, señaló que los espacios serán gratuitos para favorecer la comercialización de sus piezas y productos sin intermediarios. Por su parte, el Sistema DIFH ofrecerá hospedaje gratuito en sus albergues para artesanos procedentes de regiones distantes.</t>
-  </si>
-  <si>
-    <t>La Sebiso y el DIF estatal otorgarán espacios comerciales y hospedaje gratuito a más de 130 artesanos de Hidalgo que participarán en el pabellón de la Feria de Pachuca 2026.</t>
-  </si>
-  <si>
-    <t>Epic Traverse Hidalgo</t>
-  </si>
-  <si>
-    <t>Anuncio promocional del reto deportivo de aventura extrema Epic Traverse, que se llevará a cabo del 23 al 25 de octubre de 2026 en el estado de Hidalgo. Convocará a 150 competidores con equipamiento de vestimenta deportiva para realizar un recorrido de aproximadamente dos días con inicio a las 6:00 h, cruzando los municipios de Mineral del Chico, Atotonilco El Grande, Actopan, Santiago de Anaya, Cardonal, Metztitlán, Ixmiquilpan, Tasquillo y Zimapán.</t>
-  </si>
-  <si>
-    <t>Se promueve el evento de deportes de aventura Epic Traverse en Hidalgo, convocando a 150 atletas a realizar un trayecto extremo que recorrerá nueve demarcaciones del estado.</t>
-  </si>
-  <si>
-    <t>Hidalgo incorpora ocho municipios a la ZMVM</t>
-  </si>
-  <si>
-    <t>La Zona Metropolitana del Valle de México (ZMVM) oficializó la incorporación de ocho municipios de Hidalgo (Atitalaquia, Atotonilco de Tula, Tepeji del Río, Tizayuca, Tlaxcoapan, Tolcayuca, Tula de Allende y Villa de Tezontepec) y uno de Morelos a su esquema de planeación metropolitana. La modificación, publicada en el Diario Oficial de la Federación, permitirá la articulación conjunta de políticas de movilidad, vivienda, medio ambiente, infraestructura y desarrollo urbano sostenible entre las entidades federativas, sin que los municipios pierdan su autonomía.</t>
-  </si>
-  <si>
-    <t>La ZMVM oficializó la anexión de ocho ayuntamientos de Hidalgo a su área de planeación metropolitana, facilitando la coordinación de infraestructura y servicios sin lesionar su autonomía.</t>
-  </si>
-  <si>
-    <t>Francisco Villeda</t>
-  </si>
-  <si>
-    <t>Secretaría de Desarrollo Agrario, Territorial y Urbano (Sedatu), Consejo de Desarrollo Metropolitano, Gobiernos estatales de Hidalgo, Edomex y Morelos</t>
-  </si>
-  <si>
-    <t>Clara Brugada Molina, Delfina Gómez Álvarez, Margarita González Saravia, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>PODE COBI detona industria médica</t>
-  </si>
-  <si>
-    <t>El titular de la Unidad de Planeación y Prospectiva de Hidalgo (Uplaph), Miguel Ángel Tello Vargas, develo que el Polo de Desarrollo Económico para el Bienestar (PODE COBI) en Zapotlán de Juárez detonará de manera significativa el crecimiento y consolidación de la industria médica, química y farmacéutica en la entidad, aprovechando su ubicación e infraestructura de conectividad con la zona metropolitana.</t>
-  </si>
-  <si>
-    <t>Zapotlán</t>
-  </si>
-  <si>
-    <t>Polos del Bienestar</t>
-  </si>
-  <si>
-    <t>La Uplaph prevé un alto auge industrial químico y farmacéutico en el estado a partir de la detonación de la infraestructura del Polo de Desarrollo PODE COBI en Zapotlán.</t>
-  </si>
-  <si>
-    <t>Unidad de Planeación y Prospectiva de Hidalgo (Uplaph), Gobierno del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Apoyan a personas cuidadoras</t>
-  </si>
-  <si>
-    <t>La Secretaría de Bienestar e Inclusión Social de Hidalgo (Sebiso), a través de la Dirección General de Inclusión, inició la entrega de subsidios del programa de apoyo económico a personas cuidadoras de personas con discapacidad severa. El programa, impulsado por el gobernador Julio Menchaca, tiene por objeto brindar un soporte monetario a quienes dedican de tiempo completo su labor al cuidado familiar en municipios como Tlaxcoapan.</t>
-  </si>
-  <si>
-    <t>Apoyo a personas cuidadoras</t>
-  </si>
-  <si>
-    <t>La Sebiso hidalguense formalizó la dispersión de apoyos de los programas del Bienestar enfocados a respaldar económicamente la labor de personas cuidadoras en Tlaxcoapan.</t>
-  </si>
-  <si>
-    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Dirección General de Inclusión para las Personas con Discapacidad</t>
-  </si>
-  <si>
-    <t>Reconocen trayectoria de más de mil trabajadores</t>
-  </si>
-  <si>
-    <t>El titular de la SEPH, Natividad Castrejón Valdez, el líder nacional del SNTE, Alfonso Cepeda Salas, y el dirigente estatal de la Sección 15, Said Vargas Sáenz, presidieron un emotivo evento para reconocer y entregar estímulos a mil 912 trabajadores y docentes de la educación por sus años de servicio, destacando el profesionalismo, disciplina y compromiso con la enseñanza de la niñez en Hidalgo.</t>
-  </si>
-  <si>
-    <t>La SEPH y las cúpulas del SNTE entregaron medallas y estímulos por trayectoria de servicio a mil 912 trabajadores magisteriales en Pachuca.</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, Alfonso Cepeda Salas, Said Vargas Sáenz</t>
-  </si>
-  <si>
-    <t>Fortalece la SEPH formación docente</t>
-  </si>
-  <si>
-    <t>La Secretaría de Educación Pública de Hidalgo (SEPH) fortalece la actualización y capacitación del personal docente mediante los Ejercicios Integradores del Aprendizaje (EIA). Esta estrategia permite evaluar y orientar las prácticas de enseñanza en el aula para responder a las necesidades específicas de las comunidades escolares y consolidar los preceptos del modelo pedagógico oficial.</t>
-  </si>
-  <si>
-    <t>La SEPH implementó talleres de capacitación docente bajo el esquema de Ejercicios Integradores para robustecer la planeación académica en las aulas.</t>
-  </si>
-  <si>
-    <t>Ofrecen 700 empleos para los jóvenes</t>
-  </si>
-  <si>
-    <t>Con la participación de 25 empresas y una oferta de 700 plazas laborales, se llevó a cabo la Feria Nacional de Empleo para las Juventudes 2026 en Mineral de la Reforma, informó el titular de la STPSH, Oscar Javier González Hernández. El funcionario puntualizó que esta feria busca acercar opciones laborales formales y dignas, con salarios competitivos, para mitigar los índices de desocupación en el sector joven.</t>
-  </si>
-  <si>
-    <t>Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>Feria De Empleo</t>
-  </si>
-  <si>
-    <t>La Secretaría del Trabajo de Hidalgo inauguró una feria de empleo juvenil en Mineral de la Reforma con una oferta inicial de 700 vacantes y 25 firmas participantes.</t>
-  </si>
-  <si>
-    <t>Secretaría del Trabajo y Previsión Social de Hidalgo (STPSH), Instituto de Capacitación para el Trabajo (Icathi)</t>
-  </si>
-  <si>
-    <t>Oscar Javier González Hernández</t>
-  </si>
-  <si>
-    <t>Hidalgo registró una tasa de desocupación de 2.2 por ciento</t>
-  </si>
-  <si>
-    <t>El titular de la Secretaría del Trabajo y Previsión Social de Hidalgo (STPSH), Oscar Javier González Hernández, informó que el estado registró una tasa de desocupación de 2.2 por ciento durante el segundo trimestre de 2026, de acuerdo con los indicadores más recientes de la Encuesta Nacional de Ocupación y Empleo (ENOE) elaborada por el Inegi. Esto representa un descenso de 0.5 puntos porcentuales en comparación anual.</t>
-  </si>
-  <si>
-    <t>Tasa de desocupación</t>
-  </si>
-  <si>
-    <t>La STPSH reportó que Hidalgo registró una tasa de desocupación del 2.2% al cierre del segundo trimestre de 2026, de acuerdo con la ENOE del Inegi.</t>
-  </si>
-  <si>
-    <t>Secretaría del Trabajo y Previsión Social de Hidalgo, Instituto Nacional de Estadística y Geografía (Inegi)</t>
-  </si>
-  <si>
-    <t>CULTURA: La Celestina</t>
-  </si>
-  <si>
-    <t>En el marco de la inauguración del 2.º Festival Internacional Sor Juana Inés de la Cruz: Escena Barroca, la obra dramática 'La Celestina' (De mujeres y brujas) se presentará hoy en Pachuca a las 18:00 horas, promoviendo el acceso a la cultura barroca y las artes teatrales.</t>
-  </si>
-  <si>
-    <t>La obra escénica 'La Celestina' se presentará en Pachuca a las 18:00 horas en el arranque de la segunda edición del Festival Escena Barroca.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura del Estado de Hidalgo, Consejo Estatal para las Culturas y las Artes</t>
-  </si>
-  <si>
-    <t>FOTOGRAFÍA: La Muestra PECDA</t>
-  </si>
-  <si>
-    <t>La Muestra PECDA Hidalgo 2025 de artes visuales entra en su última semana de exhibición de artes teatrales y de fotografía en Pachuca. En este contexto, este jueves se presentará la puesta en escena 'Historias de la luna para el viento' en el foro del Teatro Romo de Vivar.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura anunció el cierre de la muestra del estímulo PECDA con la función teatral 'Historias de la luna para el viento' en el Teatro Romo de Vivar.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura del Estado de Hidalgo, Teatro Guillermo Romo de Vivar, PECDA</t>
-  </si>
-  <si>
-    <t>Por conflicto de propiedad, SEPH negocia terreno de escuela en Tezontepec</t>
-  </si>
-  <si>
-    <t>El área jurídica de la SEPH atiende el conflicto de propiedad de una escuela de educación media superior en Tezontepec de Aldama, cuyo terreno cuenta con un particular que obtuvo una resolución favorable en un juicio. El predio está valuado entre 10 y 12 mdp, y el edificio en 40 mdp. El secretario Natividad Castrejón Valdez informó que se busca un acuerdo de negociación antes de heredar el problema a la siguiente administración.</t>
-  </si>
-  <si>
-    <t>Tezontepec de Aldama</t>
-  </si>
-  <si>
-    <t>Conflicto predio escolar</t>
-  </si>
-  <si>
-    <t>La SEPH busca un acuerdo de negociación con un particular que acreditó la propiedad del predio donde opera un plantel escolar en Tezontepec de Aldama.</t>
-  </si>
-  <si>
     <t>Secretaría de Educación Pública de Hidalgo</t>
   </si>
   <si>
-    <t>Concluye Menchaca primera etapa de Rutas para la Reconstrucción; continuarán tras Cuarto Informe</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar concluyó en Jacala de Ledezma la primera etapa de las Rutas de la Transformación para la Reconstrucción, donde dio cuenta de obras y acciones por más de 225 mdp para atender daños de la vaguada monzónica. Anunció que la federación aportará 115.7 mdp para reconstruir ocho caminos que comunican a comunidades como La Palma, Quetzalapa y El Aguaje. Adelantó que las Rutas continuarán tras rendir su informe de gobierno.</t>
-  </si>
-  <si>
-    <t>Rutas de la Reconstrucción</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca concluyó la primera fase de las Rutas de la Reconstrucción con obras por 225 mdp para resarcir daños pluviales en Jacala.</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Secretaría de Infraestructura, Comunicaciones y Transportes</t>
-  </si>
-  <si>
-    <t>Con protocolo buscan proteger a docentes ante denuncias “falsas”</t>
-  </si>
-  <si>
-    <t>El secretario de Educación Pública, Natividad Castrejón Valdez, señaló que la iniciativa conjunta con el Congreso local, el SNTE nacional y la Sección 15 busca proteger los derechos de los maestros expuestos a sanciones inmerecidas por denuncias falsas de violencia escolar. Aclaró que aunque se tiene la obligación de separar preventivamente al docente ante quejas, se busca evitar la vulnerabilidad de los profesores cuando las acusaciones resultan ser falsas, citando un caso previo en Zapotlán.</t>
-  </si>
-  <si>
-    <t>La SEPH, el Congreso y el SNTE alistan un protocolo para proteger los derechos de maestros ante quejas o falsas acusaciones de violencia escolar.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Congreso del Estado de Hidalgo, Sindicato Nacional de Trabajadores de la Educación, Sección 15 del SNTE</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, Alfonso Cepeda Salas</t>
-  </si>
-  <si>
-    <t>Desarrollan estudiantes hidalguenses prototipos de go-karts eléctricos</t>
-  </si>
-  <si>
-    <t>Alumnos de octavo semestre de Ingeniería en Sistemas Automotrices del ITESA diseñaron y construyeron dos prototipos funcionales de go-karts 100% eléctricos como parte de su especialidad de electromovilidad. El coordinador del proyecto, Joshio Guadalupe García Acosta, destacó que este desarrollo está alineado con las metas del Plan México y de la estrategia federal Olinia para impulsar vehículos eléctricos de manufactura nacional.</t>
-  </si>
-  <si>
-    <t>Apan</t>
-  </si>
-  <si>
-    <t>Plan México</t>
-  </si>
-  <si>
-    <t>Estudiantes de Ingeniería de Sistemas Automotrices de ITESA ensamblaron dos prototipos de go-karts eléctricos alineados con los objetivos del Plan México.</t>
-  </si>
-  <si>
-    <t>Instituto Tecnológico Superior del Oriente del Estado de Hidalgo, Secretaría de Educación Pública de Hidalgo</t>
-  </si>
-  <si>
-    <t>Joshio Guadalupe García Acosta</t>
-  </si>
-  <si>
-    <t>Espejeando: Presentación de la orquesta sinfónica del Estado de Hidalgo en la catedral de Huejutla / Retorno de vacacionistas / Xantolo</t>
-  </si>
-  <si>
-    <t>Columna de opinión que aborda diversos temas locales de la Huasteca: 1) El éxito de la presentación de la Orquesta Sinfónica en la catedral de Huejutla y la descentralización de la cultura promovida por Neyda Naranjo. 2) La expectativa del ayuntamiento para el último Xantolo de la actual administración. 3) El retorno de vacacionistas por el regreso a clases que reactivará el comercio de calzado y útiles.</t>
-  </si>
-  <si>
     <t>Temas varios</t>
   </si>
   <si>
-    <t>Trascendidos que destacan la presentación de la orquesta sinfónica en la catedral de Huejutla, las expectativas por el Xantolo y la reactivación comercial por el regreso a clases.</t>
-  </si>
-  <si>
-    <t>Perseo</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura de Hidalgo, Ayuntamiento de Huejutla</t>
-  </si>
-  <si>
-    <t>Neyda Naranjo Baltazar, Genaro Zuviri González</t>
-  </si>
-  <si>
-    <t>Desde Jacala Julio Menchaca concluye Rutas para la Reconstrucción</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca concluyó la etapa de las Rutas de la Transformación para la Reconstrucción en Jacala de Ledezma, reportando obras por más de 225 mdp para atender daños pluviales. Destacó el respaldo del gobierno federal de Claudia Sheinbaum con 115.7 mdp para reconstruir 8 caminos y puentes. Alejandro Sánchez (Sipdus) anunció puentes sobre el río Amajac; CEAA y Conagua informaron sobre rehabilitación de agua.</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (Sipdus), Comisión Estatal del Agua y Alcantarillado (CEAA), Centro SICT en Hidalgo, Comisión Nacional del Agua (Conagua), Ayuntamiento de Jacala</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Claudia Sheinbaum Pardo, Pablo Octavio Olvera Sánchez, Alejandro Sánchez García, Juan Carlos Chávez González, Kendra Martínez Sánchez</t>
-  </si>
-  <si>
-    <t>Sebiso hace entrega de tarjetas a domicilio a personas cuidadoras</t>
-  </si>
-  <si>
-    <t>La Secretaría de Bienestar e Inclusión Social (Sebiso) inició la entrega de tarjetas de apoyo económico de 10 mil pesos para personas cuidadoras de personas con discapacidad severa. Debido a las limitaciones de movilidad, se programaron 89 visitas domiciliarias en municipios como San Felipe Orizatlán, Huejutla, Jacala y La Misión.</t>
-  </si>
-  <si>
-    <t>La Sebiso hidalguense formalizó la dispersión de apoyos de los programas del Bienestar enfocados a respaldar económicamente la labor de personas cuidadoras.</t>
-  </si>
-  <si>
-    <t>Secretaría de Bienestar e Inclusión Social, Dirección General de Inclusión para las Personas con Discapacidad, Servidores del Pueblo</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Ricardo Gómez Moreno, Alfonso Hayyim Flores Barrera, Jorge Miguel García Vázquez</t>
-  </si>
-  <si>
-    <t>Realizan en Mineral de la Reforma Feria Nacional de Empleo para las Juventudes</t>
-  </si>
-  <si>
-    <t>Con la participación de 25 empresas y 700 plazas ofertadas, se llevó a cabo la Feria Nacional de Empleo para las Juventudes 2026 en el municipio de Mineral de la Reforma. El titular de la STPSH, Oscar Javier González Hernández, informó que al segundo trimestre de 2026, la tasa de desocupación se ubicó en 2.2 por ciento, 0.5 puntos porcentuales por debajo de la media nacional. Se firmó un convenio de colaboración con la UNID para elevar la empleabilidad.</t>
-  </si>
-  <si>
-    <t>La Secretaría del Trabajo de Hidalgo inauguró una feria de empleo juvenil en Mineral de la Reforma con una oferta de 700 vacantes y 25 firmas participantes.</t>
-  </si>
-  <si>
-    <t>Secretaría del Trabajo y Previsión Social de Hidalgo, Ayuntamiento de Mineral de la Reforma, Instituto de Capacitación para el Trabajo del Estado de Hidalgo (Icathi)</t>
-  </si>
-  <si>
-    <t>Oscar Javier González Hernández, Eduardo Medécigo Rubio, Sergio Arturo Hernández Echagaray, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Atendemos cada rincón de Hidalgo; hay obra en los 84 municipios: Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar encabezó una gira de trabajo en el municipio de La Misión, donde dio cuenta de las obras y acciones realizadas para atender las afectaciones pluviales y recuperar la movilidad de la zona. Se destacó que la SICT federal destinará más de 178 mdp para reconstruir 24 caminos y un puente peatonal. Desde 2023 se han invertido más de 80 mdp estatales en obras locales.</t>
-  </si>
-  <si>
-    <t>El mandatario estatal reportó obras estatales por más de 80 mdp y una inversión de la SICT federal de 178 mdp para reconstruir 24 caminos dañados en La Misión.</t>
-  </si>
-  <si>
-    <t>Gobierno de Hidalgo, Secretaría de Infraestructura, Comunicaciones y Transportes (SICT), Comisión Estatal del Agua y Alcantarillado (CEAA), Ayuntamiento de La Misión</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Pablo Octavio Olvera Sánchez, Ibsan Israel Villeda Villeda</t>
-  </si>
-  <si>
-    <t>Obra La Celestina llega a Pachuca con el 2º Festival Internacional</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura de Hidalgo, en colaboración con el Centro Cultural Helénico y El Claustro de Sor Juana, presentará en Pachuca dos actividades del 2º Festival Internacional Sor Juana Inés de la Cruz: Escena Barroca. El viernes 28 de agosto a las 18:00 horas se escenificará 'La Celestina. De mujeres y brujas' en el Teatro Romo de Vivar, y el sábado 29 se impartirá el taller 'El bululú contemporáneo' en el Ferrocarril.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura del Estado de Hidalgo, Centro Cultural Helénico, El Claustro de Sor Juana</t>
-  </si>
-  <si>
-    <t>Jesús Torres, Carol Delgado</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura y CIESAS firman convenio para mapear expresiones rituales de Hidalgo</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura de Hidalgo y el CIESAS firmaron un convenio general de colaboración académica y científica para instrumentar el proyecto 'Cartografía Ritual del Estado de Hidalgo', que combinará la investigación documental y de campo con tecnologías de Sistemas de Información Geográfica geoespaciales para documentar las tradiciones de las diez regiones geoculturales.</t>
-  </si>
-  <si>
-    <t>Conservación del Patrimonio Cultural</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura y el Ciesas firmaron un convenio académico y de georreferenciación para mapear digitalmente las expresiones rituales hidalguenses.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura del Estado de Hidalgo, Centro de Investigaciones y Estudios Superiores en Antropología Social (CIESAS), Centro INAH Hidalgo, ProSIG-CSH</t>
-  </si>
-  <si>
-    <t>Neyda Naranjo Baltazar, Francisco Fernández de Castro Santos, Manuel Villarruel Vázquez, Deborah Monroy Magaldi, Luis Francisco Sánchez Fonseca, Antonio Escobar Ohmstede, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Llega Muestra PECDA a su última semana con teatro, fotografía y artes visuales</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura de Hidalgo invitó a la última semana de actividades de la Muestra del Programa de Estímulos a la Creación y Desarrollo Artístico (PECDA) Hidalgo 2025. Los eventos se desarrollarán hasta el 31 de agosto, incluyendo representaciones de teatro en el Teatro Romo de Vivar, exposiciones fotográficas en el Ferrocarril y artes visuales en el Centro de Cultura Digital.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura anunció el cierre de la muestra del estímulo PECDA con funciones teatrales, de fotografía y artes visuales en diversos recintos de Pachuca.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura del Estado de Hidalgo, Teatro Guillermo Romo de Vivar, Centro Cultural del Ferrocarril, Centro de Cultura Digital, PECDA</t>
-  </si>
-  <si>
-    <t>Fátima Carrillo Marrodán, Jéssica Miriam Mejía Domínguez, Mariana Castillo Monterrubio, Andrea Natalia Arriaga Pájaro, Fabrizio Otamendi Servín</t>
-  </si>
-  <si>
-    <t>Avanzan proyectos de infraestructura vial y de conectividad en aeropuerto AIFA</t>
-  </si>
-  <si>
-    <t>En el marco de la Mesa de Trabajo en Materia de Movilidad y Conectividad 2026 del AIFA, se presentaron propuestas de infraestructura clave como la conexión vial Zumpango-AIFA, el ramal Arco Norte-Paseo del Bicentenario, y los avances de la planeación para la extensión del Tren Suburbano hacia la ciudad de Pachuca, buscando fortalecer la conectividad metropolitana.</t>
-  </si>
-  <si>
-    <t>Edomex</t>
-  </si>
-  <si>
-    <t>Se presentaron proyectos metropolitanos de infraestructura vial y ferroviaria de conectividad con el AIFA, incluyendo el ramal a Pachuca.</t>
-  </si>
-  <si>
-    <t>Secretaría de Turismo de Hidalgo (Secturh), Secretaría de Movilidad y Transporte (Semot), Secretaría de Desarrollo Agrario, Territorial y Urbano (Sedatu), Comisión Consultiva del AIFA</t>
-  </si>
-  <si>
-    <t>Isidoro Pastor Román, Elizabeth Quintanar Gómez, Lyzbeth Robles Gutiérrez</t>
-  </si>
-  <si>
-    <t>SEPH y SNTE reconocen trayectoria de mil 912 trabajadores de la educación</t>
-  </si>
-  <si>
-    <t>En representación del gobernador, el titular de la SEPH, Natividad Castrejón Valdez, junto con el dirigente nacional del SNTE, Alfonso Cepeda Salas, y el secretario general de la Sección 15, Said Vargas Sáenz, entregaron estímulos y medallas por 20, 25, 30, 40 y 50 años de servicio a mil 912 trabajadores de la educación hidalguenses, refrendando el compromiso con el magisterio.</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, Alfonso Zepeda Salas, Said Vargas Sáenz, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Más de 130 hidalguenses participarán en el pabellón artesanal y gastronómico de la Feria de San Francisco Pachuca 2026</t>
-  </si>
-  <si>
-    <t>La Secretaría de Bienestar e Inclusión Social de Hidalgo (Sebiso) dio a conocer los resultados de la segunda asignación de espacios para el Pabellón Artesanal y Gastronómico de la Feria San Francisco Pachuca 2026, beneficiando a más de 130 artesanos regionales con stands gratuitos y hospedaje coordinado con el DIF estatal.</t>
-  </si>
-  <si>
-    <t>Ricardo Gómez Moreno, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>En Zapotlán se impulsará industria médica y farmacéutica</t>
-  </si>
-  <si>
-    <t>El titular de la Unidad de Planeación y Prospectiva (Uplaph), Miguel Ángel Tello Vargas, develo que el Polo de Desarrollo Económico para el Bienestar (Podeco) en Zapotlán de Juárez impulsará la industria médica y farmacéutica hacia 2040, aprovechando el potencial de conectividad regional y la millonaria inversión de 10 mil 106 mdp de la firma DEWA.</t>
-  </si>
-  <si>
-    <t>La Uplaph prevé un alto auge industrial químico y farmacéutico en el estado a partir de la detonación de la infraestructura del Polo de Desarrollo Podeco en Zapotlán.</t>
-  </si>
-  <si>
-    <t>Unidad de Planeación y Prospectiva de Hidalgo (Uplaph), Gobierno del Estado de Hidalgo, Gobierno de México</t>
-  </si>
-  <si>
-    <t>Miguel Ángel Tello Vargas, Claudia Sheinbaum Pardo, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Banda Sinfónica de Hidalgo Estará en Tlanchinol</t>
-  </si>
-  <si>
-    <t>El alcalde de Tlanchinol, Gabino Hernández Vite, extendió la invitación a disfrutar del concierto gratuito que ofrecerá la Banda Sinfónica del Estado de Hidalgo este viernes a las 15:00 horas en la parroquia de San Agustín, un evento coordinado de la mano de la Secretaría de Cultura para acercar las expresiones culturales a las regiones.</t>
-  </si>
-  <si>
-    <t>Tlanchinol</t>
-  </si>
-  <si>
-    <t>El municipio de Tlanchinol será sede del concierto de la Banda Sinfónica del Estado de Hidalgo en la Parroquia de San Agustín para descentralizar los eventos artísticos.</t>
-  </si>
-  <si>
-    <t>Ángel Osiris Castillo García</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura de Gobierno del Estado de Hidalgo, Ayuntamiento de Tlanchinol</t>
-  </si>
-  <si>
-    <t>Gabino Hernández Vite, Neyda Naranjo Baltazar</t>
-  </si>
-  <si>
-    <t>SSPH aseguró dos personas con hidrocarburo de procedencia ilícita en Ixmiquilpan</t>
-  </si>
-  <si>
-    <t>Elementos de la SSPH junto con el Mando Coordinado de Ixmiquilpan aseguraron en el barrio de Santa Ana a dos personas que transportaban un cargamento ilícito de aproximadamente 1,200 litros de hidrocarburo de Pemex, distribuidos en 19 garrafones en el área de carga de una camioneta pick-up. Quedaron a disposición de la FGR en Tula de Allende.</t>
-  </si>
-  <si>
-    <t>Ixmiquilpan</t>
-  </si>
-  <si>
-    <t>Fuerzas de seguridad y el Mando Coordinado incautaron 1,200 litros de combustible ilícito en Ixmiquilpan y arrestaron a dos personas involucradas.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Mando Coordinado de Ixmiquilpan, Fiscalía General de la República (FGR)</t>
-  </si>
-  <si>
-    <t>Dese por enterado: Israel Félix va con todo / Condolencias a Guadarrama / Aplazan elecciones Sección XV / Regularán bacheo en Pachuca</t>
-  </si>
-  <si>
-    <t>Trascendidos locales que analizan: 1) La campaña política contra el alcalde de Mineral de la Reforma, Eduardo Medécigo, y las intenciones de Israel Félix de posicionar a Shaida Lozada para 2027. 2) Condolencias para José Guadarrama por el deceso de su hermana Aseneth. 3) El posible aplazamiento de las elecciones en la Sección XV del SNTE en Hidalgo para evitar interferencias con los comicios de 2027, lo cual daría un respiro a Said Vargas. 4) El anuncio del secretario de Obras Públicas de Pachuca, Francisco Lugo Espinosa, sobre la regulación del bacheo por parte de particulares.</t>
-  </si>
-  <si>
-    <t>Trascendidos políticos sobre campañas contra Eduardo Medécigo, el virtual aplazamiento electoral en el SNTE de Said Vargas y la nueva regulación del bacheo particular en Pachuca.</t>
-  </si>
-  <si>
-    <t>Dese por enterado</t>
-  </si>
-  <si>
-    <t>Sindicato Nacional de Trabajadores de la Educación, Ayuntamiento de Pachuca, Ayuntamiento de Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>Eduardo Medécigo Rubio, Israel Félix Soto, Shaida Lozada Martínez, José Guadarrama Márquez, Aseneth Guadarrama Márquez, Alfonso Cepeda Salas, Said Vargas Sáenz, Francisco Lugo Espinosa</t>
-  </si>
-  <si>
-    <t>Más de 130 hidalguenses participarán en pabellón artesanal</t>
-  </si>
-  <si>
-    <t>La Secretaría de Bienestar e Inclusión Social (Sebiso) publicó los resultados de la segunda etapa de asignación de espacios gratuitos para el Pabellón Artesanal y Gastronómico de la Feria San Francisco Pachuca 2026 (del 24 de septiembre al 18 de octubre). El titular Ricardo Gómez Moreno destacó que el objetivo es promover la venta directa sin intermediarios. Se coordinará hospedaje gratuito para expositores distantes mediante el DIF estatal.</t>
-  </si>
-  <si>
-    <t>La Sebiso otorgará stands comerciales gratuitos en el pabellón de la Feria de Pachuca a más de 130 artesanos, facilitando hospedaje sin costo a través del DIFH.</t>
-  </si>
-  <si>
-    <t>Vidas dedicadas a la docencia</t>
-  </si>
-  <si>
-    <t>En un evento protocolario con cena y música celebrado en el salón Veravia de Pachuca, se entregaron estímulos y medallas oficiales de la Casa de Moneda de México a mil 212 docentes de Hidalgo por cumplir trayectorias de 20 a 50 años de servicio en el magisterio básico, en un acto encabezado por el titular de la SEPH, Natividad Castrejón Valdez, en representación del gobernador Julio Menchaca.</t>
-  </si>
-  <si>
-    <t>La SEPH coordinó la entrega de estímulos monetarios y medallas conmemorativas por años de antigüedad laboral a mil 212 profesores de educación básica.</t>
-  </si>
-  <si>
-    <t>Catalina Hermosillo Durán</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Sindicato Nacional de Trabajadores de la Educación</t>
-  </si>
-  <si>
     <t>Natividad Castrejón Valdez, Julio Menchaca Salazar</t>
   </si>
   <si>
-    <t>Con operativos permanentes mejoran la seguridad en regiones del Estado</t>
-  </si>
-  <si>
-    <t>La SSPH emitió un comunicado para ratificar que mantiene desplegados operativos policiales de manera permanente durante los 365 días del año en las distintas regiones de Hidalgo. Las brigadas realizan patrullajes de proximidad social, vigilancia activa y presencia preventiva, exhortando a reportar anomalías al 911 o 089.</t>
-  </si>
-  <si>
-    <t>Operativo de Seguridad</t>
-  </si>
-  <si>
-    <t>La SSPH reafirmó el despliegue permanente de patrullas y tareas de proximidad social en las regiones de Hidalgo para preservar la tranquilidad.</t>
-  </si>
-  <si>
     <t>Secretaría de Seguridad Pública de Hidalgo</t>
   </si>
   <si>
-    <t>Impartieron una conferencia para evitar casos de extorsión</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Ciudadana de Tizayuca organizó un curso de adiestramiento técnico para sus oficiales en materia de identificación, prevención y combate al delito de extorsión. El taller fue impartido de manera conjunta por Michael Emmanuel Ángeles y el agente Raúl Pimentel, especialistas de la Unidad Especializada en el Combate al Secuestro de la procuraduría estatal.</t>
-  </si>
-  <si>
-    <t>Prevención de Extorsión</t>
-  </si>
-  <si>
-    <t>La policía municipal de Tizayuca recibió capacitación por parte de la UECS de la procuraduría para contener delitos de extorsión telefónica.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Ciudadana de Tizayuca, Procuraduría General de Justicia del Estado de Hidalgo, Unidad Especializada en el Combate al Secuestro (UECS)</t>
-  </si>
-  <si>
-    <t>Michael Emmanuel Ángeles, Raúl Pimentel</t>
-  </si>
-  <si>
-    <t>Policía Estatal aseguró a 2 personas con combustible ilícito</t>
-  </si>
-  <si>
-    <t>Elementos de la SSPH y el Mando Coordinado de Ixmiquilpan interceptaron en el barrio de Santa Ana una camioneta pick-up cargada con 19 garrafones con capacidad de 50 y 60 litros. En total, se aseguraron mil 200 litros de hidrocarburo de procedencia ilícita y se detuvo a dos personas por no acreditar la documentación legal del combustible, quedando a disposición de la FGR en Tula.</t>
-  </si>
-  <si>
-    <t>La SSPH y policías locales decomisaron mil 200 litros de huachicol y detuvieron a dos hombres a bordo de una camioneta de carga en Ixmiquilpan.</t>
-  </si>
-  <si>
-    <t>A balazos perpetran violento crimen</t>
-  </si>
-  <si>
-    <t>En Huejutla de Reyes se registró una violenta ejecución armada en contra de un hombre de 25 años de edad, identificado de forma extraoficial como Jesús Gustavo L., originario de la región. La víctima viajaba a bordo de su vehículo cuando fue atacada con armas de fuego. Tras corroborarse que no contaba con signos vitales, la policía municipal acordonó la escena y la PGJEH inició las investigaciones periciales correspondientes.</t>
-  </si>
-  <si>
-    <t>Homicidios</t>
-  </si>
-  <si>
-    <t>Sujetos armados ejecutaron a un joven de 25 años al interior de su automóvil en Huejutla de Reyes, activándose las diligencias periciales de la procuraduría.</t>
-  </si>
-  <si>
-    <t>Procuraduría General de Justicia del Estado de Hidalgo, Policía Municipal de Huejutla de Reyes</t>
-  </si>
-  <si>
-    <t>Jesús Gustavo L</t>
-  </si>
-  <si>
-    <t>Buscan proteger a los docentes ante denuncias</t>
-  </si>
-  <si>
-    <t>La SEPH respaldó la reforma legal aprobada por el Congreso del Estado de Hidalgo que adiciona el artículo 117 Bis a la Ley de Educación estatal para garantizar la presunción de inocencia de maestros y personal administrativo. El secretario Natividad Castrejón Valdez explicó que trabajarán conjuntamente con los legisladores para definir la aplicación del protocolo, ya que actualmente la normativa obliga a la separación inmediata del cargo ante quejas, afectando injustamente a cientos de docentes cuyas denuncias resultan no corresponder con la realidad.</t>
-  </si>
-  <si>
-    <t>La SEPH respalda la reforma del Congreso para salvaguardar la presunción de inocencia de docentes hidalguenses y estructurar protocolos de mediación ante quejas infundadas.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Congreso del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Analizan reubicar escuela por litigio</t>
-  </si>
-  <si>
-    <t>La SEPH busca mediar un acuerdo armonioso con el legítimo propietario de un terreno en Tezontepec de Aldama donde se edificó, hace 40 años, un plantel de educación media superior tras una donación de buena fe. El secretario Natividad Castrejón Valdez informó que resolver el conflicto legal del predio costaría unos 10 millones de pesos, por lo que paralelamente se evalúa reubicar el plantel aprovechando la infraestructura disponible de educación básica en el municipio para resguardar la inversión física del edificio, la cual asciende a 40 millones de pesos.</t>
-  </si>
-  <si>
-    <t>El titular de la SEPH analiza alternativas de reubicación y negociaciones de indemnización por 10 mdp para solucionar la disputa de tierras de una preparatoria en Tezontepec.</t>
-  </si>
-  <si>
-    <t>Menchaca concluye con Rutas de Reconstrucción</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar formalizó el cierre de la actual fase de las Rutas de la Transformación para la Reconstrucción en Jacala de Ledezma, reportando inversiones por más de 225 millones de pesos asignadas a resarcir los daños por inundaciones de 2025. Destacó que el gobierno de Claudia Sheinbaum aportará 115.7 mdp federales para reconstruir ocho caminos que comunican poblados como Quetzalapa, La Palma y El Aguaje, mientras que la SICT ejecutará los puentes de La Palma (91.28 metros) y Quetzalapa (110 metros) sobre el río Amajac.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar concluyó en Jacala las Rutas de la Reconstrucción con un informe de obras carreteras por 225 mdp respaldado por la federación.</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible, Comisión Estatal del Agua y Alcantarillado, Centro SICT en Hidalgo, Comisión Nacional del Agua, Ayuntamiento de Jacala</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Claudia Sheinbaum Pardo, Pablo Octavio Olvera Sánchez, Kendra Martínez Sánchez, Juan Carlos Chávez González</t>
-  </si>
-  <si>
-    <t>Feria San Francisco abre espacios para artesanos</t>
-  </si>
-  <si>
-    <t>La Secretaría de Bienestar e Inclusión Social de Hidalgo (Sebiso) dio a conocer los resultados de la segunda fase de asignación de espacios del Pabellón Artesanal y Gastronómico de la Feria San Francisco Pachuca 2026, beneficiando a más de 130 artesanos de las regiones del Mezquital, la Huasteca, Sierra y Otomí-Tepehua. El titular Ricardo Gómez Moreno puntualizó que los locales serán completamente gratuitos para promover la comercialización directa, coordinándose con el DIF estatal hospedaje sin costo en sus albergues.</t>
-  </si>
-  <si>
-    <t>La Sebiso asignó espacios gratuitos en el pabellón comercial de la Feria de Pachuca a más de 130 artesanos, facilitando hospedaje sin costo mediante albergues del DIF.</t>
+    <t>Planea Menchaca tres obras clave para cierre de sexenio</t>
+  </si>
+  <si>
+    <t>Al detallar los temas prioritarios que marcarán el cierre de su administración, el gobernador Julio Menchaca Salazar adelantó los proyectos que definirán los pendientes de su gestión, destacando tres obras de infraestructura fundamentales para la comunicación y la vialidad. Dos se ubicarán en Pachuca y una más fuera del estado que tendrá un impacto directo en toda la entidad. Asimismo, Menchaca Salazar destacó que Hidalgo mantiene cifras históricas en materia de inversión y generación de empleos, una tendencia que se mantendrá durante los próximos dos años.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca anunció que cerrará su sexenio con tres obras de infraestructura clave para mejorar la comunicación y movilidad en Pachuca y el estado.</t>
+  </si>
+  <si>
+    <t>Nathali González</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Secretaría de Desarrollo Económico</t>
+  </si>
+  <si>
+    <t>Trasladan a 174 internos del Cereso de Mixquiahuala a Tula</t>
+  </si>
+  <si>
+    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH) llevó a cabo la madrugada de este viernes un operativo para trasladar a 174 personas privadas de la libertad desde el Cereso de Mixquiahuala de Juárez hacia el nuevo módulo de dormitorios del Cereso de Tula de Allende. La medida de reubicación responde principalmente a la severa sobrepoblación que registraba el penal de Mixquiahuala, que opera a más del doble de su capacidad, además de filtraciones pluviales en los dormitorios.</t>
+  </si>
+  <si>
+    <t>Mixquiahuala</t>
+  </si>
+  <si>
+    <t>Deficiencias Ceresos</t>
+  </si>
+  <si>
+    <t>La SSPH trasladó a 174 personas recluidas de Mixquiahuala a Tula para mitigar el hacinamiento y solventar daños pluviales en la infraestructura.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Gobierno del Estado de Hidalgo, Dirección de Protección Civil</t>
+  </si>
+  <si>
+    <t>Cierra la Muestra PECDA con actividades gratuitas en Pachuca</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura del Estado de Hidalgo invita a la última semana de actividades de la Muestra del Programa de Estímulos a la Creación y Desarrollo Artístico (PECDA) Hidalgo 2025, que se llevarán a cabo hasta el 31 de agosto. Los eventos se desarrollarán en tres recintos culturales de Pachuca: el Centro Cultural del Ferrocarril, el Teatro Guillermo Romo de Vivar y el Centro de Cultura Digital, incluyendo teatro, fotografía y artes visuales.</t>
+  </si>
+  <si>
+    <t>PECDA</t>
+  </si>
+  <si>
+    <t>La muestra artística PECDA cierra sus actividades de estímulos de artes escénicas y visuales en Pachuca con funciones y talleres interactivos gratuitos.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura de Hidalgo, Centro Cultural del Ferrocarril, Centro de Cultura Digital, Teatro Guillermo Romo de Vivar</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo Baltazar, Jéssica Miriam Mejía, Mariana Castillo Monterrubio, Andrea Natalia Arriaga Pájaro, Fabrizio Otamendi Servín, Carol Delgado</t>
+  </si>
+  <si>
+    <t>Adelanta Menchaca anuncio de tres obras “importantes” de vialidad</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar informó que su cuarto informe de gobierno, programado para el próximo viernes 4 de septiembre, se realizará en las instalaciones de la Feria de Pachuca, cambiando de sede respecto a Plaza Juárez. Dentro de los próximos anuncios que incluirá su rendición de cuentas, adelantó que serán tres obras de infraestructura 'importantes' para comunicación y vialidad, mismas que también ayudarán a reducir el tráfico. Dos de ellas se ubicarán en la Zona Metropolitana de Pachuca y una más fuera de la entidad, pero 'que impactará directamente en el estado'. En otro tema, el titular del Ejecutivo estatal confirmó que Carlos Rivera será el artista que amenizará el festejo del 15 de septiembre, la noche del Grito de Independencia, en Plaza Juárez, junto a un grupo musical cuyo nombre se reservó.</t>
+  </si>
+  <si>
+    <t>Marco Cerón</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Carlos Rivera</t>
+  </si>
+  <si>
+    <t>Envían a 174 reos del Cereso de Mixquiahuala a Tula</t>
+  </si>
+  <si>
+    <t>Por motivos de sobrepoblación, un total de 174 hombres que se encontraban recluidos en el Centro de Reinserción Social del municipio de Mixquiahuala fueron trasladados al penal de Tula. Además, se informó que otra de las causas por las que se realizó dicha acción fue porque los dormitorios presentaban filtraciones de agua y Protección Civil ordenó realizar un reforzamiento de los espacios y remodelación de los techos. La dependencia destacó que la capacidad del Cereso donde se encontraban es para 70 personas y albergaba a 191 internos. De acuerdo con la Secretaría de Seguridad Pública del estado (SSPH), los reos fueron removidos durante la madrugada de este 28 de agosto.</t>
+  </si>
+  <si>
+    <t>Reinserción social</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Dirección de Protección Civil</t>
+  </si>
+  <si>
+    <t>Evaluación de aprendizajes fortalece la práctica educativa: IHE</t>
+  </si>
+  <si>
+    <t>El Instituto Hidalguense de Educación (IHE) fortalece la capacitación y actualización del personal docente mediante los Ejercicios Integradores del Aprendizaje (EIA), procesos formativos alineados con los retos que enfrentan las escuelas y orientados a mejorar la práctica educativa en el aula. Los EIA permiten identificar conocimientos, habilidades y actitudes que las y los estudiantes ponen en práctica para resolver situaciones concretas, vinculadas con su contexto escolar y con los principios de la Nueva Escuela Mexicana. Durante el ciclo escolar 2025–2026, Hidalgo realizó este diagnóstico en todos los niveles de educación básica, con la participación de 3 mil 220 escuelas y 379 mil estudiantes. El titular del IHE y secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, destacó que tienen una visión humanista y su propósito es contar con información que permita tomar decisiones para mejorar aprendizajes.</t>
+  </si>
+  <si>
+    <t>El IHE implementó evaluaciones diagnósticas a 379 mil estudiantes en 3,220 planteles básicos para orientar la planeación docente y mejorar aprendizajes.</t>
+  </si>
+  <si>
+    <t>Instituto Hidalguense de Educación, Secretaría de Educación Pública de Hidalgo</t>
+  </si>
+  <si>
+    <t>ITESHU fortalece su oferta de posgrados</t>
+  </si>
+  <si>
+    <t>El Instituto Tecnológico Superior de Huichapan (ITESHU) inició formalmente el ciclo escolar con una matrícula presencial superior a 2 mil 200 alumnos. La institución presentó su nueva Maestría en Desarrollo Regional e Innovación Tecnológica, sumando dos programas de maestría. El nuevo programa busca ofrecer mayores opciones de especialización y formación alineadas con las necesidades del entorno productivo de la región. La oferta académica del ITESHU incluye carreras en Arquitectura y Gastronomía, así como las ingenierías en Energías Renovables, Gestión Empresarial, Innovación Agrícola Sustentable, Sistemas y Mecatrónica. En el nivel de posgrado, además de la nueva Maestría en Desarrollo Regional e Innovación Tecnológica, ofrece también la Maestría en Ingeniería Mecatrónica.</t>
+  </si>
+  <si>
+    <t>Huichapan</t>
+  </si>
+  <si>
+    <t>Oferta educativa</t>
+  </si>
+  <si>
+    <t>El ITESHU dio inicio al nuevo ciclo escolar para más de 2,200 alumnos presenciales, presentando su nueva Maestría en Desarrollo Regional e Innovación Tecnológica.</t>
+  </si>
+  <si>
+    <t>Instituto Tecnológico Superior de Huichapan</t>
+  </si>
+  <si>
+    <t>Despresurizan penal de Mixquiahuala</t>
+  </si>
+  <si>
+    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH) trasladó a 174 personas privadas de la libertad del Cereso de Mixquiahuala al penal de Tula de Allende, debido a la sobrepoblación que registra el centro penitenciario y a recomendaciones de Protección Civil por filtraciones de agua en el área de dormitorios. De acuerdo con una tarjeta informativa emitida por la dependencia, el operativo se realizó durante la madrugada del viernes en las instalaciones del Centro de Reinserción Social de Mixquiahuala de Juárez. El traslado se efectuó hacia el nuevo módulo de dormitorios del Cereso de Tula de Allende. La SSPH informó que el penal ubicado en Mixquiahuala tiene una capacidad para 70 personas, pero antes del operativo albergaba a 191 internos, por lo que presentaba una ocupación considerablemente superior a su capacidad. Ante esta situación, se trasladó a 174 integrantes de la población varonil a las nuevas instalaciones de Tula.</t>
+  </si>
+  <si>
+    <t>La SSPH trasladó a 174 internos del Cereso de Mixquiahuala a las nuevas instalaciones de Tula de Allende para abatir el hacinamiento y prevenir riesgos pluviales en dormitorios.</t>
+  </si>
+  <si>
+    <t>IAAMEH celebra a personas mayores</t>
+  </si>
+  <si>
+    <t>En el marco del Día Nacional de las Personas Mayores, que se conmemora cada 28 de agosto, el Instituto para la Atención de las y los Adultos Mayores del Estado de Hidalgo (IAAMEH) realizó festejos en distintos municipios de la entidad para quienes acuden a los Centros Gerontológicos Integrales (CGI) y Casas de Día. Las actividades tuvieron como propósito promover la convivencia, el esparcimiento y el bienestar integral de las personas mayores.</t>
+  </si>
+  <si>
+    <t>Atención a adultos mayores</t>
+  </si>
+  <si>
+    <t>El IAAMEH organizó diversas jornadas de festejo y convivencia en la entidad para conmemorar el Día Nacional de las Personas Mayores en sus centros gerontológicos.</t>
+  </si>
+  <si>
+    <t>Instituto para la Atención de las y los Adultos Mayores del Estado de Hidalgo (IAAMEH)</t>
+  </si>
+  <si>
+    <t>Documentan los saberes de las cocineras tradicionales</t>
+  </si>
+  <si>
+    <t>En las instalaciones del Centro Cultural del Ferrocarril se llevó a cabo la presentación de “Memoria Culinaria: vestigios ancestrales de la cocina hidalguense”, una exposición fotográfica de la creadora visual Jessica Mejía que tiene por objetivo reconocer las historias, saberes de preparación y tradiciones ancestrales de las cocineras del municipio de Santiago de Anaya. El proyecto reúne diversos retratos y testimonios orales de mujeres locales para enaltecer la gastronomía como parte viva de nuestra identidad cultural y patrimonio hidalguense.</t>
+  </si>
+  <si>
+    <t>Santiago de Anaya</t>
+  </si>
+  <si>
+    <t>Cocineras Tradicionales</t>
+  </si>
+  <si>
+    <t>Se inauguró en Pachuca la muestra fotográfica de Jessica Mejía titulada 'Memoria Culinaria', dedicada a recopilar el legado y saberes tradicionales de las cocineras de Santiago de Anaya.</t>
+  </si>
+  <si>
+    <t>Portada</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura de Hidalgo, Centro Cultural del Ferrocarril</t>
+  </si>
+  <si>
+    <t>Jessica Mejía</t>
+  </si>
+  <si>
+    <t>Suicidio se concreta más en hombres, indica especialista</t>
+  </si>
+  <si>
+    <t>Durante el desarrollo del Panel Internacional de Salud Mental y Prevención del Suicidio, José Joaquín Ceballos, presidente de la Coalición Nacional de Prevención del Suicidio (Conapresu), informó que de cada 10 hombres que atentan contra su vida, ocho consuman el hecho, mientras que en las mujeres el índice alcanza siete de cada 10, lo que devela una mayor letalidad en el género masculino. El especialista aclaró que la conducta suicida es un proceso de ideación cognitivo que abarca varias etapas y no un acto repentino. En su mensaje de apertura, el titular de la PIBEH, Francisco Martínez Gómez, destacó que la salud mental es un eje prioritario de atención preventiva.</t>
+  </si>
+  <si>
+    <t>Prevención del suicidio</t>
+  </si>
+  <si>
+    <t>Durante el Panel de Salud Mental se reveló que el 80% de los hombres que atentan contra su vida logran consumar el suicidio, superando la tasa de letalidad femenina.</t>
+  </si>
+  <si>
+    <t>Socorro Ávila</t>
+  </si>
+  <si>
+    <t>Policía Industrial Bancaria del Estado de Hidalgo (PIBEH), Sistema DIF Hidalgo, Comisión de Derechos Humanos del Estado de Hidalgo (CDHEH), Coalición Nacional de Prevención del Suicidio (Conapresu)</t>
+  </si>
+  <si>
+    <t>José Joaquín Ceballos, Francisco Martínez Gómez, Edda Vite Ramos, Ana Karen Parra Bonilla, Arturo Gómez Canales</t>
+  </si>
+  <si>
+    <t>El Chico impulsará oferta turística con el nuevo centro Los Lavaderos</t>
+  </si>
+  <si>
+    <t>Con el propósito de detonar la infraestructura turística y el comercio artesanal de uno de los Pueblos Mágicos más representativos del estado, la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (SIPDUS) emitió la licitación pública EO-SIPDUS-N113-2026 para construir el Centro Turístico Multifuncional Los Lavaderos. La obra se realizará en el centro histórico de Mineral del Chico, contemplando fachadas de acceso, techumbres, vestidores, muro de contención, instalación eléctrica, gradas y nivelación de terraplenes. El fallo será emitido el 11 de septiembre, programándose el inicio para el 2 de octubre de 2026.</t>
+  </si>
+  <si>
+    <t>Mineral del Chico</t>
+  </si>
+  <si>
+    <t>Infraestructura Turística</t>
+  </si>
+  <si>
+    <t>La SIPDUS emitió convocatoria pública para la edificación del nuevo Centro Turístico Los Lavaderos en el centro de Mineral del Chico, proyectando iniciar obras el 2 de octubre.</t>
+  </si>
+  <si>
+    <t>Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (SIPDUS)</t>
+  </si>
+  <si>
+    <t>Con infraestructura, Hidalgo refuerza seguridad y atención de emergencias</t>
+  </si>
+  <si>
+    <t>En menos de un mes, el estado de Hidalgo puso en marcha dos nuevas instalaciones tácticas para el auxilio de emergencias y la seguridad civil en Pachuca. La primera corresponde a la nueva Estación de Bomberos “José María Morelos y Pavón” y oficinas de Protección Civil estatal, cuya inversión representó 91 millones de pesos con dormitorios, sala de juntas, cabina de despacho electrónico y equipo tecnológico. Además, se incorporaron 19 elementos al cuerpo de bomberos. La segunda corresponde al nuevo Cuartel de la Policía Estatal en Cubitos, edificado en un terreno de 1,550 metros cuadrados con inversión de 22 mdp, evento donde además 116 nuevos cadetes rindieron protesta.</t>
+  </si>
+  <si>
+    <t>Fortalecimiento Policiaco</t>
+  </si>
+  <si>
+    <t>El gobierno estatal inauguró la nueva estación metropolitana de Bomberos (91 mdp) y el Cuartel de Policía en la colonia Cubitos (22 mdp), sumando 116 policías graduados.</t>
+  </si>
+  <si>
+    <t>Benjamín H. V.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública del Estado de Hidalgo, Subsecretaría de Protección Civil del Estado, Cuerpo de Bomberos de Hidalgo, Instituto de Formación Profesional</t>
+  </si>
+  <si>
+    <t>Gusano barrenador suma 83 casos activos en 32 municipios</t>
+  </si>
+  <si>
+    <t>El Servicio Nacional de Sanidad, Inocuidad y Calidad Agroalimentaria (Senasica) confirmó que el estado de Hidalgo registra 83 casos activos del parásito del gusano barrenador (larva que infesta heridas abiertas en animales) distribuidos en 32 municipios. La propagación coloca a la entidad en el noveno lugar nacional de contagios. Del total de brotes vigentes, el municipio de Eloxochitlán encabeza el volumen de contagios con 11 casos, seguido por Huehuetla con ocho. Asimismo, por especie, el ganado bovino encabeza el daño con 33 casos activos, mientras que el sector de mascotas caninas reporta un total de 27 casos activos.</t>
+  </si>
+  <si>
+    <t>Gusano barrenador</t>
+  </si>
+  <si>
+    <t>La Senasica confirmó que Hidalgo sumó 83 casos activos de gusano barrenador en 32 municipios, siendo Eloxochitlán la demarcación con la mayor incidencia.</t>
+  </si>
+  <si>
+    <t>Saderh</t>
+  </si>
+  <si>
+    <t>Servicio Nacional de Sanidad, Inocuidad y Calidad Agroalimentaria (Senasica)</t>
+  </si>
+  <si>
+    <t>Formalizan comodato de predio para nuevo CEMSaD en Progreso</t>
+  </si>
+  <si>
+    <t>El Colegio de Bachilleres del Estado de Hidalgo (Cobaeh) y la Dirección General de Patrimonio Inmobiliario del Gobierno del Estado de Hidalgo formalizaron el comodato de un predio destinado al CEMSaD Progreso de Obregón. El espacio cuenta con una extensión de 4 mil 400 metros cuadrados y contempla la construcción de aulas, oficinas administrativas, talleres, sanitarios y áreas deportivas. En coordinación con el Instituto Hidalguense de la Infraestructura Física Educativa (INHIFE), se realizó una valoración técnica del predio, en la que se determinó que cumple con las condiciones requeridas para el desarrollo del proyecto, y se prevé iniciar en septiembre la elaboración del proyecto de construcción. Este nuevo espacio busca beneficiar a aproximadamente 200 estudiantes del CEMSaD Progreso de Obregón, asimismo, busca ampliar la capacidad de atención y favorecer el ingreso de jóvenes egresados de secundaria de la región. El acto protocolario se realizó en las instalaciones de la Subsecretaría de Educación Media Superior y Superior de la SEPH y estuvo encabezado por el subsecretario Daniel Fragoso Torres, en compañía del titular del Cobaeh, Rubén López Valdez, y la diputada por el Distrito VII de Mixquiahuala, Diana Rangel Zúñiga, quienes signaron el documento correspondiente, en presencia de autoridades educativas y representantes del Comité de Madres y Padres de Familia.</t>
+  </si>
+  <si>
+    <t>Progreso</t>
+  </si>
+  <si>
+    <t>Comodato</t>
+  </si>
+  <si>
+    <t>El Cobaeh y el Gobierno de Hidalgo formalizaron la cesión en comodato de un predio de 4,400 metros cuadrados para edificar las nuevas instalaciones del CEMSaD Progreso de Obregón, beneficiando a 200 alumnos.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Colegio de Bachilleres del Estado de Hidalgo, Instituto Hidalguense de la Infraestructura Física Educativa, Dirección General de Patrimonio Inmobiliario</t>
+  </si>
+  <si>
+    <t>Daniel Fragoso Torres, Rubén López Valdez, Diana Rangel Zúñiga</t>
+  </si>
+  <si>
+    <t>Hidalgo registró 409 defunciones fetales en 2025: INEGI</t>
+  </si>
+  <si>
+    <t>Durante 2025, Hidalgo registró 409 casos de Estadísticas de Defunciones Fetales (EDF), de acuerdo con datos publicados por el Instituto Nacional de Estadística y Geografía (INEGI). Del total estatal, 283 casos fueron captados mediante el procedimiento tradicional, mientras que 126 corresponden a casos complementarios captados por la Secretaría de Salud e incorporados en formato digital. A nivel nacional se contabilizaron 20 mil 74 defunciones fetales, por lo que Hidalgo se ubicó en el lugar 14 entre las entidades con mayor número de registros, exactamente en la media nacional. Las entidades con más defunciones fetales fueron el Estado de México con 3 mil 823 casos; Ciudad de México con 2 mil 68; Guanajuato con mil 391; Jalisco con mil 229 y Puebla con mil 108 casos. Las defunciones fetales se registraron principalmente en unidades de la Secretaría de Salud, el IMSS e IMSS-Bienestar, seguidas de las unidades médicas privadas. Un caso de muerte materna está en investigación.</t>
+  </si>
+  <si>
+    <t>Salud materna</t>
+  </si>
+  <si>
+    <t>El INEGI reportó que Hidalgo registró 409 defunciones fetales en 2025, ubicándose en la media nacional, ocurriendo la mayoría de los decesos en la Secretaría de Salud, IMSS e IMSS-Bienestar.</t>
+  </si>
+  <si>
+    <t>Secretaría de Salud de Hidalgo, Instituto Mexicano del Seguro Social, IMSS-Bienestar</t>
+  </si>
+  <si>
+    <t>En servicio de hospedaje se concentran las principales quejas turísticas en Mineral del Chico</t>
+  </si>
+  <si>
+    <t>En servicio de hospedaje se concentran las principales quejas turísticas en Mineral del Chico y registran un incremento, de acuerdo con información de la Secretaría de Turismo municipal, ante la presencia de establecimientos que operan sin licencia o sin inscripción en el Registro Nacional de Turismo (RNT). Francisco Javier Olmos García, secretario de Turismo de Mineral del Chico, explicó que esta situación se presenta principalmente con espacios que se promocionan mediante plataformas como Airbnb, así como con personas que adaptan habitaciones o áreas de sus viviendas para rentarlas a visitantes sin realizar los trámites correspondientes. Ante este escenario, la autoridad municipal mantiene una campaña dirigida a los prestadores de servicios para que regularicen sus establecimientos, tramiten la licencia y el RNT, además de acceder a capacitación para mejorar la atención a los turistas. La presencia de estos sitios también dificulta determinar con exactitud cuántos espacios de alojamiento funcionan actualmente en el municipio. Hasta el año pasado, las autoridades tenían registradas 285 cabañas y 290 cuartos de hotel; no obstante, Olmos García señaló que esta cifra puede modificarse debido a los inmuebles que ofrecen el servicio de manera informal. El funcionario añadió que la dependencia también participa en el ordenamiento territorial turístico, en coordinación con autoridades estatales, para la vigilancia y regulación.</t>
+  </si>
+  <si>
+    <t>Airbnb</t>
+  </si>
+  <si>
+    <t>La Secretaría de Turismo de Mineral del Chico reportó un repunte de quejas turísticas dirigidas a servicios informales de alojamiento tipo Airbnb que operan sin licencias ni RNT, por lo que promueve su regularización.</t>
+  </si>
+  <si>
+    <t>Berenice Gamboa</t>
+  </si>
+  <si>
+    <t>Secretaría de Turismo de Mineral del Chico, Secretaría de Turismo del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Francisco Javier Olmos García</t>
+  </si>
+  <si>
+    <t>Alrededor de 650 mil estudiantes iniciarán ciclo escolar 2026-2027</t>
+  </si>
+  <si>
+    <t>Este lunes 31 de agosto, alrededor de 650 mil estudiantes de nivel básico regresan a las aulas en más de 7 mil planteles de Hidalgo, como parte del inicio del ciclo escolar 2026-2027, indicó el secretario de Educación en la entidad, Natividad Castrejón Valdez. El arranque protocolario de clases se realizará en la Escuela Secundaria General 2 de Pachuca, donde se llevará a cabo la entrega simbólica de útiles y uniformes escolares. El titular de la SEPH adelantó que realizará giras regionales de inauguración simbólica e informó que el 100 por ciento del nivel básico tiene cobertura, buscando alternativas de absorción de capacidad en planteles de alta demanda poblacional como Tizayuca y Atotonilco de Tula.</t>
+  </si>
+  <si>
+    <t>Regreso A Clases</t>
+  </si>
+  <si>
+    <t>Alrededor de 650 mil alumnos de nivel básico en Hidalgo inician clases de la mano de la SEPH, realizándose el protocolo escolar en Pachuca.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Instituto Hidalguense de Educación</t>
+  </si>
+  <si>
+    <t>Incumplimiento de acuerdos en obra afecta a locatarios en Plaza Perisur</t>
+  </si>
+  <si>
+    <t>Locatarios de la plaza Perisur, en Pachuca, padecen un mes complicado en ventas, pérdida de clientes y caos vehicular, derivado del incumplimiento de acuerdos por parte de la Secretaría de Infraestructura Pública y Desarrollo Urbano (Sipdus), relacionados con los trabajos de rehabilitación del bulevar Felipe Ángeles a la altura de ese espacio comercial. Denunciaron que desde el inicio de las labores el pasado 10 de agosto han registrado caídas de hasta el 70% y 90% en sus ventas por la inhabilitación de accesos sin previo aviso, afectando a restaurantes, papelerías, zapaterías, gimnasios, mueblerías y laboratorios, vulnerando la subsistencia de los comercios por la falta de señalética vial de la dependencia.</t>
+  </si>
+  <si>
+    <t>Inconformidad por obra</t>
+  </si>
+  <si>
+    <t>Locatarios de Plaza Perisur acusan caídas de hasta el 90% en ventas por el cierre de accesos de la obra de rehabilitación vial de la Sipdus.</t>
+  </si>
+  <si>
+    <t>Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible, Ayuntamiento de Pachuca</t>
+  </si>
+  <si>
+    <t>Miguel Islas, Lili N.</t>
+  </si>
+  <si>
+    <t>Un viacrucis, el tráfico de norte a sur</t>
+  </si>
+  <si>
+    <t>Cientos de automovilistas de Pachuca se enfrentan diariamente a un severo viacrucis vial al intentar regresar a sus hogares por la tarde, principalmente en el bulevar Felipe Ángeles con dirección a la salida sur. El trayecto, que anteriormente demoraba 20 minutos, ahora requiere casi dos horas debido al congestionamiento generado por las obras de rehabilitación de la Sipdus a la altura de Las Torres y Plaza de Toros. Al transitar a menos de 10 kilómetros por hora, la desesperación aumenta entre conductores que además ya no cuentan con la opción de invadir el carril exclusivo del Tuzobús debido a que las sanciones de cultura vial entraron en vigor con multas de hasta 3 mil 519 pesos.</t>
+  </si>
+  <si>
+    <t>Crónica</t>
+  </si>
+  <si>
+    <t>Vialidad En Mal Estado</t>
+  </si>
+  <si>
+    <t>Las obras de rehabilitación vial de la Sipdus en la salida sur de Pachuca provocan filas vehiculares kilométricas de hasta dos horas.</t>
+  </si>
+  <si>
+    <t>Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible, Secretaría de Educación Pública de Hidalgo, Sistema Integrado de Transporte Masivo de Hidalgo</t>
+  </si>
+  <si>
+    <t>“Ni uno más”, el clamor de familiares de desaparecidos</t>
+  </si>
+  <si>
+    <t>Con pancartas, mantas, fotografías y consignas, colectivos y familiares de personas desaparecidas marcharon en Pachuca en conmemoración del Día Internacional de las Víctimas de Desapariciones Forzadas. La movilización partió del Reloj Monumental hacia las calles aledañas del centro de la ciudad para visibilizar sus casos y reclamar a las autoridades la falta de avances en las investigaciones penales. Los manifestantes exigieron que la comisión de búsqueda y la procuraduría agilicen las carpetas que, en casos históricos de larga data, acumulan hasta 20 años de rezago.</t>
+  </si>
+  <si>
+    <t>Desapariciones</t>
+  </si>
+  <si>
+    <t>Familias de desaparecidos marcharon del Reloj de Pachuca a fin de exigir que la fiscalía y la comisión de búsqueda desahoguen indagatorias.</t>
+  </si>
+  <si>
+    <t>Procuraduría General de Justicia de Hidalgo, Comisión de Búsqueda de Personas de Hidalgo</t>
+  </si>
+  <si>
+    <t>José Francisco García Reyes</t>
+  </si>
+  <si>
+    <t>A 31 años del caso, buscan el paradero de Enriqueta</t>
+  </si>
+  <si>
+    <t>La familia Dimas Serrano mantiene intacta la búsqueda y esperanza de localizar a Enriqueta Dimas Serrano, quien desapareció a los 31 años de edad el 8 de junio de 1995 tras salir de su domicilio en la colonia Morelos, de Pachuca, para encontrarse con su expareja. Celia Dimas, hermana de la víctima, reprochó de forma severa que la procuraduría estatal se niegue a establecer líneas activas de investigación argumentando el paso del tiempo, provocando que la familia afronte la parálisis del caso por su propia cuenta sin apoyo gubernamental.</t>
+  </si>
+  <si>
+    <t>Búsqueda de personas</t>
+  </si>
+  <si>
+    <t>Familiares de Enriqueta Dimas reprochan abandono institucional en la búsqueda de la mujer desaparecida en Pachuca hace 31 años.</t>
+  </si>
+  <si>
+    <t>Procuraduría General de Justicia del Estado de Hidalgo, Comisión de Búsqueda de Personas del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Enriqueta Dimas Serrano, Celia Dimas Serrano</t>
+  </si>
+  <si>
+    <t>Anega lluvia aulas de primaria en Huehuetla</t>
+  </si>
+  <si>
+    <t>Una lluvia torrencial anegó la escuela primaria Benito Juárez del municipio de Huehuetla, afectando gravemente un módulo de cuatro aulas que ya se encontraba deteriorado tras los efectos de la vaguada monzónica de octubre de 2025. Padres de familia, directivos y el comité de la escuela expresaron su molestia debido a que el Inhife se ha negado a demoler y elevar el terreno del módulo dañado alegando falta de presupuesto, forzando a reprogramar el ciclo escolar para que los alumnos de estos grupos inicien clases de manera remota/a distancia.</t>
+  </si>
+  <si>
+    <t>Huehuetla</t>
+  </si>
+  <si>
+    <t>Afectaciones Por Lluvias</t>
+  </si>
+  <si>
+    <t>Fuertes precipitaciones inundaron cuatro salones en la primaria de Huehuetla, obligando a los alumnos a tomar clases a distancia.</t>
+  </si>
+  <si>
+    <t>María Antonieta Islas</t>
+  </si>
+  <si>
+    <t>Instituto Hidalguense de la Infraestructura Física Educativa, Dirección del plantel</t>
+  </si>
+  <si>
+    <t>Complicado, el inicio de clases en Tianguistengo</t>
+  </si>
+  <si>
+    <t>El ciclo escolar 2026-2027 iniciará bajo condiciones complejas para los estudiantes de la comunidad de Tlacolula, en Tianguistengo, debido a que las cuatro instituciones de educación que resultaron siniestradas por la vaguada monzónica del año anterior continúan en fase de reconstrucción y rehabilitación. Alrededor de 40 alumnos de nivel primaria tomarán cursos en una casa particular adaptada y prestada por vecinos de la zona, mientras que el nivel preescolar ocupará de forma provisional una estructura escolar antigua que resistió las lluvias, esperándose que el INHIFE culmine las obras en los próximos tres meses.</t>
+  </si>
+  <si>
+    <t>Tianguistengo</t>
+  </si>
+  <si>
+    <t>Reconstrucción de escuela</t>
+  </si>
+  <si>
+    <t>Alumnos de cuatro escuelas dañadas por lluvias en Tianguistengo inician clases en viviendas adaptadas por la parálisis de obras.</t>
+  </si>
+  <si>
+    <t>Martha Sáenz</t>
+  </si>
+  <si>
+    <t>Instituto Hidalguense de la Infraestructura Física Educativa, Secretaría de Educación Pública de Hidalgo</t>
+  </si>
+  <si>
+    <t>Bonifacio Ramos Villegas</t>
+  </si>
+  <si>
+    <t>Iniciará Aquiles Serdán su ciclo escolar en línea</t>
+  </si>
+  <si>
+    <t>La dirección de la escuela primaria Aquiles Serdán en Tulancingo, una de las instituciones educativas básicas con mayor antigüedad del municipio, informó que las clases del nuevo ciclo escolar 2026-2027 serán impartidas de forma virtual para sus 410 alumnos. El plantel tomó esta determinación tras un dictamen de planeación de la SEPH derivado del inicio de los trabajos de demolición y edificación de una nueva estructura física, debido a que seis de sus 14 aulas presentaban un severo desgaste de cimentación agudizado por lluvias previas. La decisión generó molestia entre los padres de familia.</t>
+  </si>
+  <si>
+    <t>Educación en línea</t>
+  </si>
+  <si>
+    <t>La primaria Aquiles Serdán en Tulancingo iniciará su ciclo en formato virtual debido a las obras de demolición de aulas dañadas.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública del Estado de Hidalgo, Dirección de la escuela primaria Aquiles Serdán</t>
+  </si>
+  <si>
+    <t>María de la Luz Vargas</t>
+  </si>
+  <si>
+    <t>Aquí los Políticos: Regreso a clases, carrera FUL, y robo de agua</t>
+  </si>
+  <si>
+    <t>Columna de trascendidos políticos de El Sol de Hidalgo que aborda: 1) El inicio del ciclo escolar 2026-2027 que moviliza a más de medio millón de estudiantes de nivel básico y provoca severas congestiones viales en Pachuca. 2) Las expectativas de la 21a edición de la Carrera Atlética de la UAEH que se celebrará el domingo 6 de septiembre en el marco de la FUL. 3) El incremento del robo de agua o tomas clandestinas en Mineral de la Reforma detectado por el personal de la Caasim.</t>
+  </si>
+  <si>
+    <t>Trascendidos que analizan el caos vial del regreso a clases en Pachuca, la carrera de la FUL de la UAEH y el robo de agua en Mineral de la Reforma.</t>
+  </si>
+  <si>
+    <t>Aquí los políticos</t>
+  </si>
+  <si>
+    <t>Sipdus, UAEH, Caasim, Ayuntamiento de Pachuca, Ayuntamiento de Mineral de la Reforma</t>
+  </si>
+  <si>
+    <t>Andrés Velázquez, Julio Menchaca</t>
+  </si>
+  <si>
+    <t>Exigen localizar a sus familiares</t>
+  </si>
+  <si>
+    <t>Integrantes de colectivos y familiares de personas no localizadas realizaron una manifestación pacífica en Pachuca para exigir la localización y avances reales en las carpetas de investigación por desapariciones forzadas en la entidad. Colectivos denunciaron la falta de apoyo de agentes ministeriales y lentitud burocrática, citando casos como el del joven Regino Cano Bautista, desaparecido en 2025 en Tepetitlán. Exhortaron a la Comisión de Búsqueda del Estado de Hidalgo a agilizar las diligencias de rastreo.</t>
+  </si>
+  <si>
+    <t>Familiares de desaparecidos marcharon en Pachuca para denunciar impunidad y exigir a la Comisión de Búsqueda estatal y fiscalías acelerar rastreos.</t>
+  </si>
+  <si>
+    <t>Segobh</t>
+  </si>
+  <si>
+    <t>Segobh, CBPEH, PGJEH</t>
+  </si>
+  <si>
+    <t>Regino Cano Bautista, José Francisco García</t>
+  </si>
+  <si>
+    <t>Regresarán a clases 569 mil estudiantes</t>
+  </si>
+  <si>
+    <t>Un total de 569 mil estudiantes de educación básica en Hidalgo inician clases este lunes para el ciclo escolar 2026-2027. El secretario de Educación, Natividad Castrejón, detalló que se distribuyeron de forma oportuna casi 4 millones de libros de texto gratuitos de la Nueva Escuela Mexicana y 489 mil paquetes de útiles escolares. El regreso escolar contará con un estricto operativo de vialidad de la policía para evitar el congestionamiento en las zonas escolares.</t>
+  </si>
+  <si>
+    <t>La SEPH reportó el regreso a clases de 569 mil alumnos de educación básica en Hidalgo, distribuyéndose útiles escolares y libros de texto.</t>
+  </si>
+  <si>
+    <t>Blanca Soriano</t>
+  </si>
+  <si>
+    <t>Bajo Reserva: Sin debut y con despedida / Labor que habla por sí misma / Extrema promoción personal</t>
+  </si>
+  <si>
+    <t>Trascendidos locales que analizan tres temas de la política hidalguense: 1) El IEEH decidirá el retiro del registro al Partido Espacio Hidalgo de Esperanza Flores Rojo por falta de afiliados antes de debutar en 2027. 2) El exitoso e impecable segundo informe de actividades del diputado local Andrés Velázquez Vázquez. 3) El proselitismo anticipado del director de la Comisión de Agua de Tulancingo, Enzo Balderas Castro, ante el dirigente Marco Antonio Rico.</t>
+  </si>
+  <si>
+    <t>Trascendidos que exponen la inminente pérdida de registro de Espacio Hidalgo, el buen balance del informe de Andrés Velázquez y el proselitismo anticipado del director de agua de Tulancingo.</t>
+  </si>
+  <si>
+    <t>Bajo Reserva</t>
+  </si>
+  <si>
+    <t>Instituto Estatal Electoral de Hidalgo, Congreso del Estado de Hidalgo, Comisión de Agua y Alcantarillado de Tulancingo, Morena</t>
+  </si>
+  <si>
+    <t>Esperanza Flores Rojo, Andrés Velázquez Vázquez, Enzo Balderas Castro, Marco Antonio Rico Mercado</t>
+  </si>
+  <si>
+    <t>En riesgo por rocas, 26 barrios y colonias de Pachuca, alertan</t>
+  </si>
+  <si>
+    <t>Al menos 26 barrios y colonias de Pachuca enfrentan problemas de desprendimiento de bloques de rocas o hundimientos por antiguas minas y la extracción de agua. El Atlas de Riesgo estatal identificó 34 casas en riesgo alto en El Porvenir, Nueva Estrella, Barrio San Nicolás, La Alcantarilla y El Tezontle. Asimismo, se reportan 13 zonas de peligro alto de hundimientos como El Arbolito, Camelia, Xotol, San Rafael, El Cristo, El Lobo, Buenos Aires, Cubitos y El Túnel.</t>
+  </si>
+  <si>
+    <t>Atlas de Riesgos</t>
+  </si>
+  <si>
+    <t>El Atlas de Riesgo de Hidalgo identificó graves peligros geológicos de hundimiento e inestabilidad de laderas que amenazan a 26 barrios históricos y viviendas de Pachuca.</t>
+  </si>
+  <si>
+    <t>Ricardo Calleja</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Ayuntamiento de Pachuca</t>
+  </si>
+  <si>
+    <t>Suman más de 13 mil tomas clandestinas de agua clausuradas</t>
+  </si>
+  <si>
+    <t>El titular de la Caasim, Juan Evel Chávez Trovamala, informó que el organismo ha clausurado un total de 13 mil 794 tomas clandestinas de agua potable en lo que va del año, principalmente en Pachuca, Mineral de la Reforma y Zempoala. Asimismo, detalló que iniciaron 176 procesos legales contra usuarios reincidentes, que abarcan domicilios particulares y empresas, incluyendo algunos clubes deportivos.</t>
+  </si>
+  <si>
+    <t>Tomas clandestinas</t>
+  </si>
+  <si>
+    <t>La Caasim reportó la inmovilización de 13,794 conexiones irregulares de agua de la red pública e impulsó demandas contra 176 infractores por reincidencia.</t>
+  </si>
+  <si>
+    <t>Comisión de Agua y Alcantarillado de Sistemas Intermunicipales</t>
+  </si>
+  <si>
+    <t>Juan Evel Chávez Trovamala</t>
+  </si>
+  <si>
+    <t>A 10 meses, de la vaguada, cinco desaparecidos por la vaguada</t>
+  </si>
+  <si>
+    <t>A casi un año del impacto de la vaguada monzónica en el estado de Hidalgo en octubre de 2025, cinco personas originarias del municipio de Tianguistengo continúan desaparecidas, informó el titular de la Comisión de Búsqueda de Personas del Estado de Hidalgo (CBPEH), José Francisco García Reyes. El funcionario detalló que permanecen activos cuatro reportes de Chapula y uno de Tlacolula.</t>
+  </si>
+  <si>
+    <t>La Comisión de Búsqueda estatal reportó que a 10 meses de las contingencias pluviales de 2025, cinco personas siguen desaparecidas en comunidades de Tianguistengo.</t>
+  </si>
+  <si>
+    <t>Comisión de Búsqueda de Personas del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Saderh entrega 5.3 mdp en apoyos para 600 familias</t>
+  </si>
+  <si>
+    <t>La Saderh de Hidalgo destinó un apoyo económico y en especie de 5 millones 347 mil 252 pesos para favorecer la productividad de 618 personas y productores locales del campo. El titular Napoleón González Pérez encabezó la entrega en Tolcayuca, distribuyendo semillas de avena, cebada, maíz, vientres ovinos, porcinos, aves de doble propósito y equipamiento a productores de Tolcayuca, Villa de Tezontepec, Zapotlán de Juárez y Tizayuca, con la presencia del alcalde Armando Zúñiga.</t>
+  </si>
+  <si>
+    <t>Tolcayuca</t>
+  </si>
+  <si>
+    <t>Apoyo Al Agro</t>
+  </si>
+  <si>
+    <t>La Saderh estatal entregó 5.3 mdp en paquetes agrícolas, semillas de temporal e insumos pecuarios para reactivar la soberanía productiva en el sur de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Secretaría de Agricultura y Desarrollo Rural de Hidalgo, Ayuntamientos de Tolcayuca, Villa de Tezontepec, Zapotlán de Juárez, Tizayuca</t>
+  </si>
+  <si>
+    <t>Napoleón González Pérez, Armando Zúñiga Gutiérrez</t>
+  </si>
+  <si>
+    <t>Regresan a clases 569 mil alumnos de nivel básico</t>
+  </si>
+  <si>
+    <t>Este lunes inician el ciclo escolar 2026-2027 un total de 569 mil 987 estudiantes de educación básica de Hidalgo en 7 mil 866 planteles de la entidad. La SEPH informó que desde el primer día se distribuyen de forma gratuita 3 millones 958 mil 230 libros de texto y 488 mil 977 paquetes de útiles escolares, mientras que los uniformes y calzado (475 mil 14 de cada uno) se entregarán gradualmente.</t>
+  </si>
+  <si>
+    <t>La SEPH reportó el reinicio escolar para 569 mil alumnos de nivel básico, coordinando la dispersión inicial de libros de texto, útiles, uniformes y calzado escolar.</t>
+  </si>
+  <si>
+    <t>Canalizan a menores por falta de lugar en escuelas, acusan padres</t>
+  </si>
+  <si>
+    <t>Padres de familia de los fraccionamientos Héroes de Tizayuca y Fuentes de Tizayuca acusaron que la falta de cobertura de espacios en escuelas de la zona ha provocado que decenas de niños sean canalizados a escuelas en otras zonas lejanas del municipio. Las familias reclamaron que el cupo opera al límite de su capacidad debido al aumento demográfico, estimando que unos 300 menores se quedaron sin cupo local.</t>
+  </si>
+  <si>
+    <t>Quejas padres de familia</t>
+  </si>
+  <si>
+    <t>Padres de familia protestaron en Tizayuca ante la saturación de los centros escolares locales y el traslado forzoso de alumnos hacia escuelas distantes.</t>
+  </si>
+  <si>
+    <t>Javier Quezada</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Dirección escolar de Tizayuca</t>
+  </si>
+  <si>
+    <t>Nohemí N</t>
+  </si>
+  <si>
+    <t>Balean auto y dejan paquete sospechoso, en Huejutla</t>
+  </si>
+  <si>
+    <t>Un ataque armado contra un vehículo Ford Fiesta blanco sin placas de circulación se registró en la calle Ricardo Flores Magón de la colonia Rojo Lugo, en Huejutla de Reyes. Los delincuentes realizaron nueve disparos contra la unidad y colocaron un paquete misterioso envuelto arriba del cofre. La agresión provocó la movilización de corporaciones policiales, el Ejército Mexicano y agentes periciales de la PGJEH para acordonar el área e integrar la carpeta de investigación.</t>
+  </si>
+  <si>
+    <t>Fuerzas militares y periciales resguardaron la colonia Rojo Lugo en Huejutla tras detonarse múltiples impactos contra un coche particular, dejando los agresores un paquete sospechoso.</t>
+  </si>
+  <si>
+    <t>Francisco Bautista</t>
+  </si>
+  <si>
+    <t>Procuraduría General de Justicia del Estado de Hidalgo, Secretaría de Seguridad Pública Municipal de Huejutla, Ejército Mexicano</t>
+  </si>
+  <si>
+    <t>Marchan familias buscadoras; exigen justicia, empatía y menor burocracia</t>
+  </si>
+  <si>
+    <t>En el marco del Día Internacional de las Víctimas de Desapariciones Forzadas, un grupo de aproximadamente 25 familias provenientes de municipios como Tula, Tlaxcoapan, Tetepango, Pachuca y Ajacuba marchó para exigir investigaciones más oportunas, mayor sensibilidad institucional y avances reales en la localización de sus seres queridos. Los familiares señalaron que los obstáculos burocráticos y los retrasos iniciales en las indagatorias —que en algunos casos alcanzan hasta cuatro o cinco días— vulneran el derecho de acceso a la justicia. El titular de la Comisión de Búsqueda de Personas del Estado de Hidalgo (CBPEH), José Francisco García Reyes, informó que al corte más reciente de 2026 la institución registra 315 reportes, de los cuales 310 personas han sido localizadas, aclarando que esta cifra incluye casos tanto actuales como de larga data.</t>
+  </si>
+  <si>
+    <t>Un grupo de 25 familias de personas desaparecidas marchó en Pachuca en el Día de las Víctimas de Desaparición Forzada para demandar celeridad procesal.</t>
+  </si>
+  <si>
+    <t>Comisión de Búsqueda de Personas del Estado de Hidalgo, Procuraduría General de Justicia del Estado de Hidalgo, Procuraduría de Protección de Niñas, Niños y Adolescentes</t>
+  </si>
+  <si>
+    <t>José Francisco García Reyes, Regino Cano Bautista</t>
+  </si>
+  <si>
+    <t>Cinco personas siguen sin aparecer tras la vaguada</t>
+  </si>
+  <si>
+    <t>A casi un año de las afectaciones provocadas por la vaguada monzónica de octubre de 2025, cinco personas continúan sin ser localizadas en Hidalgo, informó José Francisco García Reyes, titular de la Comisión de Búsqueda de Personas del Estado de Hidalgo (CBPEH). El funcionario detalló que las personas pendientes de localizar corresponden al municipio de Tianguistengo: cuatro son originarias de la comunidad de Chapula y una más de Tlacolula. Explicó que inicialmente se recibió un número importante de reportes debido a las condiciones de incomunicación de las lluvias, quedando en activo nueve de los cuales cuatro ya fueron ubicados.</t>
+  </si>
+  <si>
+    <t>A casi un año de la vaguada monzónica de 2025, cinco personas originarias de Tianguistengo continúan sin aparecer, manteniéndose los operativos fluviales.</t>
+  </si>
+  <si>
+    <t>Comisión de Búsqueda de Personas del Estado de Hidalgo, Protección Civil, Comisión Ejecutiva de Atención a Víctimas</t>
+  </si>
+  <si>
+    <t>Aumento de violencia escolar, por mayor cultura de denuncia: Castrejón</t>
+  </si>
+  <si>
+    <t>Durante el ciclo escolar 2025-2026 se registraron mil 381 reportes de violencia y situaciones de riesgo en escuelas de educación básica de Hidalgo, con corte al 21 de agosto de 2026, de acuerdo con información de la Secretaría de Educación Pública de Hidalgo (SEPH). El secretario de Educación Pública estatal, Natividad Castrejón Valdez, atribuyó el incremento a una mayor cultura de la denuncia y no necesariamente a un aumento de la violencia en las escuelas, destacando que Hidalgo cuenta con protocolos actualizados de prevención y atención de acoso, violencia física, psicológica y sexual.</t>
+  </si>
+  <si>
+    <t>La SEPH reportó mil 381 incidentes de violencia escolar en el ciclo 2025-2026, destacando que el alza responde al fomento de la cultura de denuncia.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Procuraduría de Protección de Niñas, Niños y Adolescentes, Procuraduría General de Justicia del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Regresan a clases 967 mil; casi la mitad recibe apoyo</t>
+  </si>
+  <si>
+    <t>Más de 967 mil estudiantes regresaron este lunes a las aulas en Hidalgo para iniciar el ciclo escolar 2026-2027, mientras que cerca de la mitad de los alumnos de primaria y secundaria reciben algún tipo de apoyo económico, además de útiles, uniformes, calzado y libros de texto gratuitos. El secretario de Educación Pública estatal, Natividad Castrejón Valdez, informó que en total 967 mil 397 estudiantes iniciaron actividades académicas en 8 mil 717 escuelas de los diferentes niveles y modalidades educativas.</t>
+  </si>
+  <si>
+    <t>Un total de 967 mil alumnos iniciaron clases en Hidalgo, reportando la SEPH la entrega masiva de libros, calzado, paquetes de útiles y uniformes gratuitos.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Gobierno del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Avanzan 42 proyectos para integrar el catálogo nacional de turismo comunitario</t>
+  </si>
+  <si>
+    <t>De un total inicial de casi 300 propuestas, un filtro riguroso de evaluación redujo a 42 los proyectos de turismo comunitario en Hidalgo que continúan en la ruta para integrarse al catálogo nacional impulsado por autoridades federales y la Unesco. Así lo informó la secretaria de Turismo estatal, Elizabeth Quintanar Gómez, quien destacó el creciente interés de las comunidades por organizarse en torno a sus tradiciones y recursos naturales, promoviéndose grupos reducidos de entre dos y 12 personas.</t>
+  </si>
+  <si>
+    <t>Turismo Comunitario</t>
+  </si>
+  <si>
+    <t>La Secretaría de Turismo reportó que 42 propuestas locales de turismo comunitario continúan vigentes en las evaluaciones para formar parte de la colección de la Unesco.</t>
+  </si>
+  <si>
+    <t>Secretaría de Turismo del Estado de Hidalgo, Gobierno Federal, UNESCO</t>
+  </si>
+  <si>
+    <t>Elizabeth Quintanar Gómez</t>
+  </si>
+  <si>
+    <t>Entregan 5.3 mdp en apoyos para productores de Hidalgo</t>
+  </si>
+  <si>
+    <t>Como parte del compromiso del gobernador Julio Menchaca Salazar de acercar a la población y fortalecer el bienestar de las familias del campo, la Secretaría de Agricultura (Saderh) encabezada por Napoleón González Pérez, entregó apoyos por un monto de 5 millones 347 mil 252 pesos. Beneficiará a 618 personas de Tolcayuca, Villa de Tezontepec, Zapotlán de Juárez y Tizayuca, en insumos y herramientas. En Tolcayuca se distribuyeron semillas de avena, cebada, jitomate, maíz, equipamiento acuícola, ovinos, porcinos, aves de doble propósito y plantas de maguey.</t>
+  </si>
+  <si>
+    <t>La Saderh entregó apoyos por 5.3 mdp a 618 productores del campo de Tolcayuca, Villa de Tezontepec, Zapotlán y Tizayuca en semillas, vientres ovinos, porcinos y aves de doble propósito.</t>
+  </si>
+  <si>
+    <t>Secretaría de Agricultura y Desarrollo Rural de Hidalgo, Gobierno del Estado de Hidalgo, Ayuntamiento de Tolcayuca</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Napoleón González Pérez, Armando Zúñiga Gutiérrez</t>
+  </si>
+  <si>
+    <t>Advierten riesgos urbanos por Tren México-Pachuca</t>
+  </si>
+  <si>
+    <t>La Zona Metropolitana de Pachuca de Soto enfrenta riesgos por el crecimiento urbano acelerado y la expansión desordenada sobre zonas rurales, de conservación y de recarga hídrica, situación que podría agravarse con la puesta en marcha del Tren México-Pachuca, advierte el Programa Parcial de Desarrollo Urbano de Pachuca y Mineral de la Reforma. El tren representará una transformación en la configuración territorial de la región, al fortalecer la conexión de Pachuca con el Valle de México y modificar las condiciones de movilidad, accesibilidad e inversión. Sin embargo, sin planeación, el crecimiento habitacional podría incrementar la especulación del suelo.</t>
+  </si>
+  <si>
+    <t>El Programa Parcial de Desarrollo Urbano advierte que la puesta en marcha del Tren México-Pachuca podría agravar los riesgos de expansión urbana desordenada y especulación del suelo en la zona conurbada.</t>
+  </si>
+  <si>
+    <t>Unidad de Planeación y Prospectiva, Ayuntamiento de Pachuca, Ayuntamiento de Mineral de la Reforma</t>
+  </si>
+  <si>
+    <t>Un recorrido por la historia</t>
+  </si>
+  <si>
+    <t>La Galería Leo Acosta presenta "Huella de la historia. La comunidad China en México", exposición fotográfica que recorre la presencia y aportaciones de la comunidad china en el país, desde el siglo XIX, destacando su impacto cultural y de desarrollo.</t>
+  </si>
+  <si>
+    <t>Exposición Fotográfica</t>
+  </si>
+  <si>
+    <t>La Galería Leo Acosta de Pachuca inauguró la exposición fotográfica 'Huella de la historia. La comunidad China en México' para difundir las aportaciones de este sector social desde el siglo XIX.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura de Hidalgo, Galería Leo Acosta</t>
+  </si>
+  <si>
+    <t>Madres buscadoras piden respuestas en Pachuca</t>
+  </si>
+  <si>
+    <t>En el marco del Día Internacional de las Víctimas de Desaparición Forzada, integrantes del colectivo Madres Buscadoras de Hidalgo marcharon por las calles del Centro Histórico de Pachuca para visibilizar los casos de sus familiares desaparecidos y exigir a las autoridades que continúen las investigaciones. La agrupación reúne a familiares de personas desaparecidas en municipios como Tula, Tlaxcoapan, Tetepango, Mixquiahuala, Progreso, Ixmiquilpan, Pachuca, Zempoala, San Agustín Tlaxiaca, Ajacuba, Tepeapulco y Mineral de la Reforma. Entre los casos se encuentra el de Enriqueta Dimas Serrano, desaparecida el 8 de junio de 1995 en Pachuca; Gustavo Alberto de la Cruz (2007); José Antonio Jiménez Jiménez (21 de marzo de 2007); y Édgar Vázquez Gutiérrez (28 de noviembre de 2015).</t>
+  </si>
+  <si>
+    <t>El colectivo Madres Buscadoras de Hidalgo marchó en Pachuca en el Día Internacional de las Víctimas de Desaparición Forzada para visibilizar expedientes y exigir avances.</t>
+  </si>
+  <si>
+    <t>Comisión de Búsqueda de Personas del Estado de Hidalgo, Procuraduría General de Justicia del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Enriqueta Dimas Serrano, Gustavo Alberto de la Cruz, José Antonio Jiménez Jiménez, Édgar Vázquez Gutiérrez</t>
+  </si>
+  <si>
+    <t>Buscan a cinco tras vaguada 2025</t>
+  </si>
+  <si>
+    <t>A casi un año de las afectaciones provocadas por la vaguada monzónica en Hidalgo, cinco personas originarias de Tianguistengo permanecen sin localizar, informó el titular de la Comisión de Búsqueda de Personas del Estado, José Francisco García Reyes. De las cinco personas desaparecidas, cuatro son de la localidad de Chapula y una de Tlacolula. García Reyes explicó que se trató de restos óseos localizados en la zona afectada, a los que se les practican pruebas genéticas para establecer su identidad. Señaló que el número de reportes de personas desaparecidas en Tianguistengo, Yahualica, San Bartolo Tutotepec, Huehuetla, Tenango de Doria y Zacualtipán llegó en su momento a 22 personas fallecidas y 20 desaparecidas, además de más de 217 viviendas afectadas y 155 comunidades incomunicadas.</t>
+  </si>
+  <si>
+    <t>La Comisión de Búsqueda de Personas de Hidalgo efectúa peritajes de ADN a restos óseos para identificar a cinco desaparecidos de Tianguistengo tras el temporal de 2025.</t>
+  </si>
+  <si>
+    <t>Comisión de Búsqueda de Personas del Estado de Hidalgo, Dirección de Servicios Periciales</t>
+  </si>
+  <si>
+    <t>Muertes maternas llegan a seis en Hidalgo</t>
+  </si>
+  <si>
+    <t>Tras dos defunciones registradas de manera consecutiva, Hidalgo acumula seis muertes maternas hasta la semana epidemiológica 33 de 2026, con lo que igualó el número de casos registrados durante todo 2025, de acuerdo con el Informe Semanal de Notificación Inmediata de Muerte Materna de la Secretaría de Salud federal. De las seis muertes maternas, una ocurrió en el IMSS, dos en el IMSS-Bienestar, una en atención particular y dos fueron clasificadas en el apartado de sin atención. La Secretaría de Salud de Hidalgo (SSH) informó que cuatro de las seis defunciones ocurrieron en Zempoala, Tula de Allende, Tasquillo y Pacula. Al corte de la semana 32 se habían registrado cinco decesos, y en la semana 33 se contabilizaron 285 muertes maternas a nivel nacional.</t>
+  </si>
+  <si>
+    <t>Muerte Materna</t>
+  </si>
+  <si>
+    <t>Hidalgo suma seis muertes maternas al corte de la semana epidemiológica 33 de 2026, igualando los registros de 2025; la SSH reportó decesos en Zempoala, Tula, Tasquillo y Pacula.</t>
+  </si>
+  <si>
+    <t>Secretaría de Salud de Hidalgo, Instituto Mexicano del Seguro Social, IMSS-Bienestar, Secretaría de Salud Federal</t>
+  </si>
+  <si>
+    <t>Realizan marcha, ofrenda y misa a favor de personas desaparecidas</t>
+  </si>
+  <si>
+    <t>En el marco del Día Internacional de las Víctimas de Desapariciones Forzadas, en Pachuca se realizaron diversas actividades para exigir la aparición de las personas desaparecidas, entre ellas una marcha pacífica, la colocación de un tendedero con fichas de búsqueda y una misa en la Basílica Menor de Guadalupe oficiada por el arzobispo de Tulancingo. Las actividades fueron encabezadas por el Colectivo de Madres Buscadoras, cuyos integrantes, desde las 11:00 horas, recorrieron calles céntricas de Pachuca y llegaron a la explanada de la Plaza Independencia, donde pasaron lista de las personas desaparecidas y exigieron a las autoridades la localización y aparición de sus familiares. El señor Regino Cano Bautista, integrante de la organización y padre buscador, señaló que el colectivo se formó a raíz de la necesidad de recibir atención por parte de las autoridades, al señalar que han enfrentado falta de atención y empatía de algunos funcionarios. Pidió a las autoridades que las investigaciones se lleven a cabo con prontitud, ya que algunas indagatorias comienzan hasta cinco días después de que se reporta una desaparición. Durante la misa oficiada este domingo en la Basílica Menor de Guadalupe de Pachuca, el arzobispo de Tulancingo, monseñor Óscar Roberto Domínguez, llamó a la población a no guardar silencio ante el dolor de las familias.</t>
+  </si>
+  <si>
+    <t>El Colectivo de Madres Buscadoras marchó en Pachuca y colocó tendedero de fichas de búsqueda en Plaza Independencia para exigir empatía y celeridad en investigaciones, mientras que el arzobispo Óscar Roberto Domínguez ofició una misa dominical en su honor.</t>
+  </si>
+  <si>
+    <t>Regino Cano Bautista, Óscar Roberto Domínguez</t>
+  </si>
+  <si>
+    <t>Regresarán a clases 569 mil estudiantes de educación básica</t>
+  </si>
+  <si>
+    <t>El secretario de Educación Pública del estado y titular del Instituto Hidalguense de Educación (IHE), Natividad Castrejón Valdez, informó que 569 mil estudiantes de educación básica retornarán a clases el próximo 31 de agosto, en apego al calendario escolar 2026-2027. Como parte de la preparación para el inicio del ciclo y con base en la política educativa estatal, la SEPH realizó acciones coordinadas para que las comunidades escolares contaran con los materiales necesarios desde el primer día. Con ese propósito se distribuirán 3 millones 958 mil 230 libros de texto gratuitos y 488 mil 977 paquetes de útiles escolares, mediante un trabajo conjunto con las subsecretarías de Educación Básica, Administración y Finanzas, así como Planeación y Evaluación; además de las direcciones generales de Servicios Regionales y Educación Básica, a través de la dirección de Materiales Educativos. Castrejón Valdéz especificó que se prevé la entrega de 475 mil 14 uniformes y 475 mil 14 pares de calzado escolar, que serán distribuidos durante las primeras semanas del ciclo directamente en los centros escolares, incluidas las comunidades apartadas. Los vales para útiles escolares comenzaron a imprimirse el 24 de agosto mediante el Sistema de Padres de Familia (SIP) y podrán canjearse desde el primer día de clases.</t>
+  </si>
+  <si>
+    <t>El titular de la SEPH, Natividad Castrejón Valdez, anunció el regreso a clases de 569 mil alumnos de educación básica para el ciclo escolar 2026-2027, confirmando la distribución coordinada de libros de texto, útiles, uniformes y calzado escolar.</t>
+  </si>
+  <si>
+    <t>COBAEH fortalece infraestructura educativa en Progreso de Obregón</t>
+  </si>
+  <si>
+    <t>El Colegio de Bachilleres del Estado de Hidalgo (COBAEH) y la Dirección General de Patrimonio Inmobiliario del Gobierno del Estado de Hidalgo formalizaron el comodato de un predio destinado al CEMSaD Progreso de Obregón, como parte de las acciones para fortalecer su infraestructura educativa. El espacio cuenta con una extensión de 4 mil 400 metros cuadrados y contempla la construcción de aulas, oficinas administrativas, talleres, sanitarios y áreas deportivas. El acto protocolario se realizó en las instalaciones de la Subsecretaría de Educación Media Superior y Superior de la SEPH y estuvo encabezado por el subsecretario Daniel Fragoso Torres, en compañía del titular del COBAEH, Rubén López Valdez, y la diputada Diana Rangel Zúñiga.</t>
+  </si>
+  <si>
+    <t>El COBAEH y el Gobierno de Hidalgo formalizaron el comodato de un terreno de 4,400 metros cuadrados para la construcción del CEMSaD Progreso de Obregón, proyectando beneficiar a 200 estudiantes.</t>
+  </si>
+  <si>
+    <t>Colegio de Bachilleres del Estado de Hidalgo, Dirección General de Patrimonio Inmobiliario, Instituto Hidalguense de la Infraestructura Física Educativa, Secretaría de Educación Pública de Hidalgo</t>
+  </si>
+  <si>
+    <t>UTEC fortalece oferta académica con la creación de nuevas maestrías</t>
+  </si>
+  <si>
+    <t>La Universidad Tecnológica de Tulancingo (UTEC) amplió su oferta académica con la apertura de dos programas de posgrado: la Maestría en Ingeniería y la Maestría en Gestión del Emprendimiento e Innovación, con el propósito de responder a las necesidades de especialización regional. El rector de la UTEC, Tito Dorantes Castillo, destacó que, a 31 años de su creación, la incorporación de estos programas representa un paso en la consolidación de la institución con los sectores productivo y social. Ambos programas tienen una duración de dos años bajo la modalidad híbrida.</t>
+  </si>
+  <si>
+    <t>Oferta académica</t>
+  </si>
+  <si>
+    <t>La UTEC amplió su oferta de posgrados con la creación de las maestrías en Ingeniería y en Gestión del Emprendimiento e Innovación, orientadas a la especialización regional.</t>
+  </si>
+  <si>
+    <t>Universidad Tecnológica de Tulancingo, Secretaría de Educación Pública de Hidalgo</t>
+  </si>
+  <si>
+    <t>Tito Dorantes Castillo</t>
+  </si>
+  <si>
+    <t>Regresarán a clases 569 mil estudiantes de educación básica en estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, informó que 569 mil estudiantes de educación básica regresarán a clases el próximo 31 de agosto, en apego al calendario escolar 2026-2027. Castrejón informó que se distribuirán 3 millones 958 mil 230 libros de texto gratuitos y 488 mil 977 paquetes de útiles escolares. Asimismo, se contempla la entrega de 475 mil 14 uniformes y 475 mil 14 pares de calzado escolar, que serán distribuidos durante las primeras semanas del ciclo directamente en los planteles escolares.</t>
+  </si>
+  <si>
+    <t>La SEPH reportó el regreso escolar de 569 mil alumnos en Hidalgo, garantizando la entrega de libros de texto, paquetes de útiles, uniformes y calzado escolar.</t>
+  </si>
+  <si>
+    <t>Las Rutas de la Transformación consolidan un gobierno cercano y presente en Hidalgo</t>
+  </si>
+  <si>
+    <t>En el marco del Cuarto Informe de Gobierno, el mandatario Julio Menchaca Salazar destacó el fortalecimiento de las Rutas de la Transformación “Gobierno en Movimiento” como la columna vertebral de una administración cercana, con presencia permanente en municipios de Hidalgo. A lo largo de cuatro años, las rutas han recorrido el estado en ocasiones a través de 224 eventos y 161 supervisiones de obra. Se complementa con ferias de Servicios para el Pueblo, que mediante 103 jornadas, han otorgado más de 200 mil atenciones directas.</t>
+  </si>
+  <si>
+    <t>Ruta de la Transformación</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar destacó que las Rutas de la Transformación han recorrido Hidalgo acercando programas, obras y ferias de servicios directos con 200 mil atenciones.</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura lleva al Congreso del Estado la campaña #HidalgoNoRegatea</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura convocó a la jornada #HidalgoNoRegatea y a la expo-venta artesanal “Manos que Crean” en las instalaciones del Congreso del Estado de Hidalgo. Lanzada en el marco del Día Mundial del Bordado, la campaña promueve el pago justo por las piezas. “El talento y el tiempo de las artesanas y los artesanos no se negocian. Cada pieza guarda identidad, memoria y años de oficio, por lo que merece un pago justo”, señaló la secretaria de Cultura, Neyda Naranjo Baltazar.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura convocó a la jornada de comercio justo #HidalgoNoRegatea y la expo-venta 'Manos que Crean' en las instalaciones del Congreso del Estado.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura de Hidalgo, Congreso del Estado de Hidalgo, Gobierno del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo Baltazar, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Destinan 5.3 mdp en agro para más de 600 familias</t>
+  </si>
+  <si>
+    <t>En cumplimiento al compromiso de dar prioridad al bienestar de las familias del campo, la Saderh, encabezada por Napoleón González Pérez, hizo entrega de apoyos por un monto de 5 millones 347 mil 252 pesos. A través de estas acciones se beneficiará a un total de 618 personas de Tolcayuca, Villa de Tezontepec, Zapotlán de Juárez y Tizayuca. La entrega se llevó a cabo en Tolcayuca, distribuyendo semillas de avena, cebada, jitomate, maíz, equipamiento acuícola, ovinos, porcinos e hijuelos de maguey.</t>
+  </si>
+  <si>
+    <t>La Saderh entregó apoyos por 5.3 mdp a 618 productores del campo en Tolcayuca, Villa de Tezontepec, Zapotlán de Juárez y Tizayuca en semillas, vientres ovinos, porcinos y aves de doble propósito.</t>
+  </si>
+  <si>
+    <t>Napoleón González Pérez, Julio Menchaca Salazar, Armando Zúñiga Gutiérrez</t>
+  </si>
+  <si>
+    <t>Realizan el rally “Caminando en tus zapatos”</t>
+  </si>
+  <si>
+    <t>Junto a estudiantes, docentes del plantel y personal administrativo del COBAEH Plantel Tula, la Dirección de la Juventud realizó el rally “Caminando en tus zapatos”, con dinámicas para aprender que cada quien trae su propia historia y experiencias. Asimismo, la actividad buscó fortalecer el vínculo afectivo y la comunicación asertiva entre padres y adolescentes mediante un recorrido de estaciones que fomente la empatía, el perdón y el reconocimiento mutuo. Finalmente, la institución agradeció a los padres de familia que asistieron “lo cual nos fortalece como institución comprometida con el bienestar emocional”.</t>
+  </si>
+  <si>
+    <t>Convivencia Escolar</t>
+  </si>
+  <si>
+    <t>La Dirección de la Juventud de Tula realizó el rally recreativo-emocional "Caminando en tus zapatos" con estudiantes y tutores del COBAEH Plantel Tula para incentivar la empatía y armonía familiar.</t>
+  </si>
+  <si>
+    <t>Colegio de Bachilleres del Estado de Hidalgo Plantel Tula, Dirección de la Juventud de Tula</t>
+  </si>
+  <si>
+    <t>La SSPH, mantiene el fortalecimiento de la seguridad en el Estado</t>
+  </si>
+  <si>
+    <t>La tarde de este domingo la Secretaría de Seguridad Pública de Hidalgo (SSPH), que dirige el comisario general Salvador Cruz Neri, emitió un comunicado oficial, donde se resalta que bajo el lema de “Primero el Pueblo”, se da a conocer que se mantiene el fortalecimiento de la seguridad. Así mismo, se refrendó que la seguridad es una prioridad desde el primer minuto del día. La información relata que, en el territorio hidalguense se despliegan operativos de vigilancia y prevención en puntos estratégicos, calles y espacios públicos para garantizar un entorno de paz para todas las familias. La SSPH advirtió a la ciudadanía en general que es necesario que con responsabilidad se haga uso de las líneas de Emergencias 911 y 089 de Denuncia Anónima.</t>
+  </si>
+  <si>
+    <t>Estrategia de seguridad</t>
+  </si>
+  <si>
+    <t>La SSPH emitió un boletín confirmando el despliegue permanente de retenes, patrullajes y cercos preventivos de seguridad en los 84 municipios de Hidalgo, solicitando el uso responsable del 911.</t>
+  </si>
+  <si>
+    <t>Evaluaron y certificaron al 99.69% de las fuerzas de seguridad</t>
+  </si>
+  <si>
+    <t>Gracias al apoyo del Gobierno del Estado que encabeza Julio Menchaca Salazar, así como as acciones emprendidas por la Secretaría de Seguridad Pública de Hidalgo, se ha logrado una excelente profesionalización de los cuerpos de seguridad en la entidad. Se destacó que para el mandatario hidalguense la seguridad es prioridad estratégica, por lo que se da atención a evaluaciones de control de confianza, lo que garantiza tener elementos de las corporaciones policiacas preparados, eficientes y leales a la ciudadanía. Actualmente, se ha evaluado y certificado al 99.69% de las fuerzas de seguridad, renovando el 25% de la plantilla operativa con 475 cadetes graduados en 7 generaciones. El fortalecimiento institucional es impulsado para, brindar mayor certidumbre y profesionalismo.</t>
+  </si>
+  <si>
+    <t>Certificación policial</t>
+  </si>
+  <si>
+    <t>La SSPH de Hidalgo logró la evaluación y certificación de control de confianza del 99.69% de los elementos policiales, incorporando además a 475 nuevos policías graduados.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Gobierno del Estado de Hidalgo, Instituto de Formación Profesional</t>
+  </si>
+  <si>
+    <t>Remueven a 174 internos del CeReSo de Mixquiahuala al de Tula</t>
+  </si>
+  <si>
+    <t>Luego de causar expectación y temor de los habitantes del Municipio de Mixquiahuala, por un impressive operativo policial se descubrió que se habría tratado del traslado conjunto de internos del penal de esa demarcación hidalguense... la Secretaría de Seguridad Pública de Hidalgo (SSPH) informa lo siguiente: La información revela que la institución que encabeza el comisario general Salvador Cruz Neri, que se trató de movilización para realizar el traslado de los varones internos del CeReSo de Mixquiahuala, al nuevo módulo de dormitorios en el CeReSo de Tula de Allende. Así mismo se dejó en claro que el despliegue policial y traslado de los reos obedeció principalmente a la sobrepoblación que existía en ese penal, ya que la capacidad es para 70 personas privadas de la libertad y este albergaba a 191 internos, por lo que se procedió al traslado de 174 personas de la población varonil. Otra de las causas es porque los dormitorios presentan filtraciones de agua y protección civil recomendó hacer un reforzamiento y remodelación de los techos. Finalmente, el Gobierno del estado de Hidalgo advirtió que, el objetivo que se persigue es el de buscar mejoras en las condiciones de reclusión y de vida de las personas privadas de la libertad, siempre actuando bajo el marco de la Ley de la Ejecución Penal.</t>
+  </si>
+  <si>
+    <t>Un operativo coordinado de la SSPH trasladó a 174 reos del penal de Mixquiahuala (que superaba el doble de su capacidad real de 70 personas) hacia los dormitorios nuevos de Tula, solucionando además filtraciones pluviales en techumbres.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Dirección de Protección Civil, Gobierno del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Rescatan cuerpo de hombre en presa</t>
+  </si>
+  <si>
+    <t>Luego de reportarse la desaparición de una persona en una presa del territorio hidalguense, se tuvo la pronta intervención de elementos del H. Cuerpo de Bomberos de Hidalgo, quienes procedieron a las complicadas labores de localización y recuperaron el cuerpo de un joven de 24 años de edad, en una presa ubicada en la comunidad de Carpinteros Norte, perteneciente al municipio de San Agustín Metzquititlán. Se sabe, que fueron vecinos del lugar los que el jueves anterior alertaron a las autoridades policiales, sobre el extravió del infortunado... De acuerdo con los reportes oficiales de la Secretaría de Seguridad Pública de Hidalgo (SSPH), el individuo se encontraba desaparecido desde el pasado 27 de agosto. Las labores de inmersión y búsqueda especializada comenzaron a las 09:35 horas, logrando el hallazgo y rescate de los restos a las 11:06 horas. Finalmente, se informó que durante el operativo coordinado participaron elementos de la SSPH, además de agentes de la policía municipal, personal de la Secretaría de Gobernación y pobladores de la localidad, quienes colaboraron en las tareas de rastreo en la zona.</t>
+  </si>
+  <si>
+    <t>San Agustín Metzquititlán</t>
+  </si>
+  <si>
+    <t>Rescate de cuerpo</t>
+  </si>
+  <si>
+    <t>Buzos del H. Cuerpo de Bomberos de Hidalgo adscritos a la SSPH recuperaron de una presa en Carpinteros Norte, San Agustín Metzquititlán, el cuerpo sin vida de un joven de 24 años ahogado tras caer al agua el pasado jueves.</t>
+  </si>
+  <si>
+    <t>Cuerpo de Bomberos de Hidalgo, Secretaría de Seguridad Pública de Hidalgo, Secretaría de Gobernación, Policía Municipal de San Agustín Metzquititlán</t>
+  </si>
+  <si>
+    <t>Familias buscadoras marchan en Pachuca</t>
+  </si>
+  <si>
+    <t>Las familias buscadoras salieron a las calles para exigirle a las autoridades que actúen, denunciando que las carpetas no avanzan y las respuestas no llegan. Alrededor de 25 familias de distintos municipios marcharon en Pachuca por el Día Internacional de las Víctimas de Desapariciones Forzadas, con fichas de búsqueda y demandas firmes de celeridad judicial.</t>
+  </si>
+  <si>
+    <t>Un grupo de 25 familias de víctimas de desaparición marcharon en Pachuca en su día conmemorativo para protestar contra el nulo avance de las investigaciones penales.</t>
+  </si>
+  <si>
+    <t>Regresan a las aulas 569 mil estudiantes de básica en Hidalgo</t>
+  </si>
+  <si>
+    <t>Un total de 569 mil estudiantes de educación básica regresarán a clases este lunes 31 de agosto en Hidalgo, conforme al calendario escolar 2026-2027. El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, informó que se distribuirán 3 millones 958 mil 230 libros de texto gratuitos y 488 mil 977 paquetes de útiles escolares para garantizar que las comunidades escolares cuenten con los materiales desde el primer día de clases. Además, durante las primeras semanas se distribuirán 475 mil 14 uniformes y el mismo número de pares de calzado escolar directamente en los planteles.</t>
+  </si>
+  <si>
+    <t>La SEPH coordinó el inicio del ciclo lectivo para 569 mil alumnos, entregando libros de texto, útiles, calzado y uniformes gratuitos.</t>
+  </si>
+  <si>
+    <t>Matrícula de prepa al 50% de lo esperado</t>
+  </si>
+  <si>
+    <t>El titular de la SEPH, Natividad Castrejón Valdez, informó que el Bachillerato Nacional Margarita Maza registra una matrícula inicial de alrededor de 600 estudiantes inscritos, cifra que representa la mitad de la meta planteada por la secretaría. El funcionario detalló que ocho sedes ya están totalmente listas para iniciar actividades el próximo 8 de septiembre en modalidad mixta semipresencial, durando dos años divididos en 16 módulos de seis semanas. Asimismo, precisó que se proyectan dos planteles definitivos en Mineral de la Reforma una vez concluidas las licitaciones físicas.</t>
+  </si>
+  <si>
+    <t>Bachillerato Nacional</t>
+  </si>
+  <si>
+    <t>El Bachillerato Nacional Margarita Maza de la SEPH captó un 50% del aforo estimado, preparándose para arrancar el 8 de septiembre con 600 inscritos.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Bachillerato Nacional Margarita Maza</t>
   </si>
 </sst>
 </file>
@@ -1565,8 +1445,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}" name="Tabla1" displayName="Tabla1" ref="A1:AJ70" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ70" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}" name="Tabla1" displayName="Tabla1" ref="A1:AJ64" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ64" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{D3CF0D4E-B6F9-44AC-AB4F-0535BBEB6872}" uniqueName="Canal" name="Canal">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
@@ -1998,7 +1878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DBE5F67-B229-448F-97D5-0E5E46CD1702}">
-  <dimension ref="A1:AJ70"/>
+  <dimension ref="A1:AJ64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -2150,28 +2030,28 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F2" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="I2" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -2180,75 +2060,75 @@
         <v>13262</v>
       </c>
       <c r="T2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V2" t="s">
         <v>38</v>
       </c>
       <c r="W2" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="X2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="Y2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z2" t="s">
         <v>47</v>
       </c>
       <c r="AA2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD2" t="s">
         <v>48</v>
       </c>
       <c r="AF2" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="AG2" t="s">
         <v>41</v>
       </c>
       <c r="AH2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="AI2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AJ2" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F3" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="I3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -2257,28 +2137,28 @@
         <v>13262</v>
       </c>
       <c r="T3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V3" t="s">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="W3" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="X3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z3" t="s">
         <v>47</v>
       </c>
       <c r="AA3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AB3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC3" t="s">
         <v>39</v>
@@ -2287,45 +2167,45 @@
         <v>48</v>
       </c>
       <c r="AF3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AG3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH3" t="s">
         <v>49</v>
       </c>
       <c r="AI3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F4" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="I4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -2334,19 +2214,19 @@
         <v>13262</v>
       </c>
       <c r="T4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V4" t="s">
         <v>38</v>
       </c>
       <c r="W4" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="X4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="Y4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z4" t="s">
         <v>47</v>
@@ -2355,51 +2235,54 @@
         <v>20</v>
       </c>
       <c r="AB4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC4" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD4" t="s">
         <v>48</v>
       </c>
       <c r="AF4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AG4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH4" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AI4" t="s">
-        <v>118</v>
+        <v>115</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F5" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="I5" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -2408,75 +2291,75 @@
         <v>13262</v>
       </c>
       <c r="T5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V5" t="s">
         <v>38</v>
       </c>
       <c r="W5" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="X5" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="Y5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z5" t="s">
         <v>47</v>
       </c>
       <c r="AA5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC5" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD5" t="s">
         <v>48</v>
       </c>
       <c r="AF5" t="s">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="AG5" t="s">
         <v>41</v>
       </c>
       <c r="AH5" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="AI5" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="AJ5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F6" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="I6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -2485,19 +2368,19 @@
         <v>13262</v>
       </c>
       <c r="T6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V6" t="s">
         <v>38</v>
       </c>
       <c r="W6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="X6" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="Y6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z6" t="s">
         <v>47</v>
@@ -2506,7 +2389,7 @@
         <v>20</v>
       </c>
       <c r="AB6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC6" t="s">
         <v>39</v>
@@ -2515,42 +2398,42 @@
         <v>48</v>
       </c>
       <c r="AF6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AG6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH6" t="s">
-        <v>129</v>
+        <v>49</v>
       </c>
       <c r="AI6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F7" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="G7">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="I7" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -2559,19 +2442,19 @@
         <v>13262</v>
       </c>
       <c r="T7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V7" t="s">
         <v>38</v>
       </c>
       <c r="W7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="X7" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="Y7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z7" t="s">
         <v>47</v>
@@ -2580,7 +2463,7 @@
         <v>20</v>
       </c>
       <c r="AB7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC7" t="s">
         <v>39</v>
@@ -2595,39 +2478,39 @@
         <v>43</v>
       </c>
       <c r="AH7" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="AI7" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="AJ7" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E8" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F8" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="G8">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="I8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -2636,28 +2519,28 @@
         <v>13262</v>
       </c>
       <c r="T8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V8" t="s">
         <v>38</v>
       </c>
       <c r="W8" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="X8" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="Y8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Z8" t="s">
         <v>47</v>
       </c>
       <c r="AA8">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC8" t="s">
         <v>48</v>
@@ -2672,39 +2555,36 @@
         <v>43</v>
       </c>
       <c r="AH8" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="AI8" t="s">
-        <v>140</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E9" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F9" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="I9" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -2713,28 +2593,28 @@
         <v>13262</v>
       </c>
       <c r="T9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V9" t="s">
         <v>38</v>
       </c>
       <c r="W9" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="X9" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="Y9" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z9" t="s">
         <v>47</v>
       </c>
       <c r="AA9">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC9" t="s">
         <v>39</v>
@@ -2743,45 +2623,42 @@
         <v>48</v>
       </c>
       <c r="AF9" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="AG9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AI9" t="s">
-        <v>146</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E10" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="F10" s="1">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -2790,37 +2667,34 @@
         <v>13262</v>
       </c>
       <c r="T10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V10" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="W10" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="X10" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="Y10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="Z10" t="s">
         <v>47</v>
       </c>
       <c r="AA10">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB10" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC10" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD10" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE10" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="AF10" t="s">
         <v>43</v>
@@ -2829,39 +2703,36 @@
         <v>43</v>
       </c>
       <c r="AH10" t="s">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="AI10" t="s">
-        <v>153</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>45</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="F11" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="G11">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -2870,28 +2741,28 @@
         <v>13262</v>
       </c>
       <c r="T11" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V11" t="s">
         <v>38</v>
       </c>
       <c r="W11" t="s">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="X11" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="Y11" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z11" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AB11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC11" t="s">
         <v>39</v>
@@ -2900,42 +2771,42 @@
         <v>48</v>
       </c>
       <c r="AF11" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="AG11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AI11" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="AJ11" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E12" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="F12" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="G12">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I12" t="s">
         <v>55</v>
@@ -2947,19 +2818,19 @@
         <v>13262</v>
       </c>
       <c r="T12" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V12" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="W12" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="X12" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="Y12" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z12" t="s">
         <v>47</v>
@@ -2968,57 +2839,54 @@
         <v>20</v>
       </c>
       <c r="AB12" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC12" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD12" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE12" t="s">
-        <v>164</v>
+        <v>48</v>
       </c>
       <c r="AF12" t="s">
-        <v>43</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH12" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="AI12" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="AJ12" t="s">
-        <v>45</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E13" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F13" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="I13" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -3027,78 +2895,72 @@
         <v>13262</v>
       </c>
       <c r="T13" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V13" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="W13" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="X13" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="Y13" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z13" t="s">
         <v>47</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB13" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC13" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD13" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="AF13" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="AG13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH13" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s">
-        <v>170</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>45</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
         <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E14" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F14" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="I14" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -3107,28 +2969,28 @@
         <v>13262</v>
       </c>
       <c r="T14" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V14" t="s">
         <v>38</v>
       </c>
       <c r="W14" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="X14" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Y14" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z14" t="s">
         <v>47</v>
       </c>
       <c r="AA14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AB14" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC14" t="s">
         <v>39</v>
@@ -3137,42 +2999,42 @@
         <v>48</v>
       </c>
       <c r="AF14" t="s">
-        <v>72</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s">
         <v>41</v>
       </c>
       <c r="AH14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AI14" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
         <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E15" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F15" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="I15" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -3181,19 +3043,19 @@
         <v>13262</v>
       </c>
       <c r="T15" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V15" t="s">
         <v>38</v>
       </c>
       <c r="W15" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="X15" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="Y15" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z15" t="s">
         <v>47</v>
@@ -3202,54 +3064,51 @@
         <v>20</v>
       </c>
       <c r="AB15" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC15" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD15" t="s">
         <v>48</v>
       </c>
       <c r="AF15" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="AG15" t="s">
         <v>41</v>
       </c>
       <c r="AH15" t="s">
-        <v>63</v>
+        <v>174</v>
       </c>
       <c r="AI15" t="s">
-        <v>180</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D16" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E16" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F16" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>99</v>
+        <v>178</v>
       </c>
       <c r="I16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -3258,75 +3117,75 @@
         <v>13262</v>
       </c>
       <c r="T16" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V16" t="s">
-        <v>184</v>
+        <v>38</v>
       </c>
       <c r="W16" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="X16" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="Y16" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z16" t="s">
         <v>47</v>
       </c>
       <c r="AA16">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB16" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC16" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD16" t="s">
         <v>48</v>
       </c>
       <c r="AF16" t="s">
-        <v>187</v>
+        <v>61</v>
       </c>
       <c r="AG16" t="s">
-        <v>188</v>
+        <v>41</v>
       </c>
       <c r="AH16" t="s">
-        <v>189</v>
+        <v>51</v>
       </c>
       <c r="AI16" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="AJ16" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="E17" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F17" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="G17">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -3335,28 +3194,28 @@
         <v>13262</v>
       </c>
       <c r="T17" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V17" t="s">
         <v>38</v>
       </c>
       <c r="W17" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="X17" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="Y17" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z17" t="s">
         <v>47</v>
       </c>
       <c r="AA17">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AB17" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC17" t="s">
         <v>39</v>
@@ -3365,45 +3224,42 @@
         <v>48</v>
       </c>
       <c r="AF17" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AG17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH17" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="AI17" t="s">
-        <v>197</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E18" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="F18" s="1">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="I18" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -3412,19 +3268,19 @@
         <v>13262</v>
       </c>
       <c r="T18" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V18" t="s">
         <v>38</v>
       </c>
       <c r="W18" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="X18" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="Y18" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z18" t="s">
         <v>47</v>
@@ -3433,7 +3289,7 @@
         <v>15</v>
       </c>
       <c r="AB18" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC18" t="s">
         <v>39</v>
@@ -3442,42 +3298,42 @@
         <v>48</v>
       </c>
       <c r="AF18" t="s">
-        <v>43</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH18" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="AI18" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="AJ18" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="E19" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="F19" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H19" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="I19" t="s">
         <v>55</v>
@@ -3489,28 +3345,28 @@
         <v>13262</v>
       </c>
       <c r="T19" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V19" t="s">
         <v>38</v>
       </c>
       <c r="W19" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="X19" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="Y19" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z19" t="s">
         <v>47</v>
       </c>
       <c r="AA19">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB19" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC19" t="s">
         <v>39</v>
@@ -3519,45 +3375,45 @@
         <v>48</v>
       </c>
       <c r="AF19" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="AG19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH19" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="AI19" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="AJ19" t="s">
-        <v>210</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="E20" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="F20" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G20">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H20" t="s">
         <v>50</v>
       </c>
       <c r="I20" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -3566,19 +3422,19 @@
         <v>13262</v>
       </c>
       <c r="T20" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V20" t="s">
         <v>38</v>
       </c>
       <c r="W20" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="X20" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="Y20" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z20" t="s">
         <v>47</v>
@@ -3587,7 +3443,7 @@
         <v>20</v>
       </c>
       <c r="AB20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC20" t="s">
         <v>39</v>
@@ -3596,45 +3452,45 @@
         <v>48</v>
       </c>
       <c r="AF20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AG20" t="s">
         <v>41</v>
       </c>
       <c r="AH20" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="AI20" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="AJ20" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E21" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F21" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G21">
         <v>7</v>
       </c>
       <c r="H21" t="s">
-        <v>219</v>
+        <v>50</v>
       </c>
       <c r="I21" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -3643,28 +3499,28 @@
         <v>13262</v>
       </c>
       <c r="T21" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V21" t="s">
-        <v>38</v>
+        <v>208</v>
       </c>
       <c r="W21" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="X21" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="Y21" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z21" t="s">
         <v>47</v>
       </c>
       <c r="AA21">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB21" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC21" t="s">
         <v>39</v>
@@ -3673,42 +3529,42 @@
         <v>48</v>
       </c>
       <c r="AF21" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="AG21" t="s">
         <v>41</v>
       </c>
       <c r="AH21" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AJ21" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="E22" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="F22" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G22">
         <v>9</v>
       </c>
       <c r="H22" t="s">
-        <v>224</v>
+        <v>50</v>
       </c>
       <c r="I22" t="s">
         <v>46</v>
@@ -3720,19 +3576,19 @@
         <v>13262</v>
       </c>
       <c r="T22" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V22" t="s">
         <v>38</v>
       </c>
       <c r="W22" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="X22" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="Y22" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z22" t="s">
         <v>47</v>
@@ -3741,7 +3597,7 @@
         <v>20</v>
       </c>
       <c r="AB22" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC22" t="s">
         <v>39</v>
@@ -3750,42 +3606,45 @@
         <v>48</v>
       </c>
       <c r="AF22" t="s">
-        <v>227</v>
+        <v>40</v>
       </c>
       <c r="AG22" t="s">
         <v>41</v>
       </c>
       <c r="AH22" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="AI22" t="s">
-        <v>228</v>
+        <v>216</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E23" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="F23" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G23">
         <v>9</v>
       </c>
       <c r="H23" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I23" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R23">
         <v>1</v>
@@ -3794,19 +3653,19 @@
         <v>13262</v>
       </c>
       <c r="T23" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V23" t="s">
         <v>38</v>
       </c>
       <c r="W23" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="X23" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="Y23" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Z23" t="s">
         <v>47</v>
@@ -3815,7 +3674,7 @@
         <v>15</v>
       </c>
       <c r="AB23" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC23" t="s">
         <v>48</v>
@@ -3824,45 +3683,45 @@
         <v>48</v>
       </c>
       <c r="AF23" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="AG23" t="s">
         <v>41</v>
       </c>
       <c r="AH23" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="AI23" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="AJ23" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="E24" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="F24" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G24">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H24" t="s">
-        <v>50</v>
+        <v>226</v>
       </c>
       <c r="I24" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -3871,19 +3730,19 @@
         <v>13262</v>
       </c>
       <c r="T24" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V24" t="s">
         <v>38</v>
       </c>
       <c r="W24" t="s">
-        <v>93</v>
+        <v>227</v>
       </c>
       <c r="X24" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="Y24" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z24" t="s">
         <v>47</v>
@@ -3892,7 +3751,7 @@
         <v>20</v>
       </c>
       <c r="AB24" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC24" t="s">
         <v>39</v>
@@ -3901,45 +3760,45 @@
         <v>48</v>
       </c>
       <c r="AF24" t="s">
-        <v>100</v>
+        <v>229</v>
       </c>
       <c r="AG24" t="s">
         <v>41</v>
       </c>
       <c r="AH24" t="s">
-        <v>129</v>
+        <v>51</v>
       </c>
       <c r="AI24" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="AJ24" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E25" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="F25" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H25" t="s">
-        <v>85</v>
+        <v>233</v>
       </c>
       <c r="I25" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R25">
         <v>1</v>
@@ -3948,19 +3807,19 @@
         <v>13262</v>
       </c>
       <c r="T25" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V25" t="s">
         <v>38</v>
       </c>
       <c r="W25" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="X25" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="Y25" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z25" t="s">
         <v>47</v>
@@ -3969,7 +3828,7 @@
         <v>20</v>
       </c>
       <c r="AB25" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC25" t="s">
         <v>39</v>
@@ -3978,7 +3837,7 @@
         <v>48</v>
       </c>
       <c r="AF25" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s">
         <v>41</v>
@@ -3987,33 +3846,33 @@
         <v>51</v>
       </c>
       <c r="AI25" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="AJ25" t="s">
-        <v>147</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E26" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F26" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G26">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H26" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="I26" t="s">
         <v>46</v>
@@ -4025,72 +3884,72 @@
         <v>13262</v>
       </c>
       <c r="T26" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V26" t="s">
-        <v>184</v>
+        <v>38</v>
       </c>
       <c r="W26" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="X26" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="Y26" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z26" t="s">
         <v>47</v>
       </c>
       <c r="AA26">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB26" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC26" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD26" t="s">
         <v>48</v>
       </c>
       <c r="AF26" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="AG26" t="s">
-        <v>188</v>
+        <v>41</v>
       </c>
       <c r="AH26" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="AI26" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="AJ26" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D27" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="E27" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="F27" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G27">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="I27" t="s">
         <v>55</v>
@@ -4102,72 +3961,72 @@
         <v>13262</v>
       </c>
       <c r="T27" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V27" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="W27" t="s">
-        <v>254</v>
+        <v>97</v>
       </c>
       <c r="X27" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="Y27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Z27" t="s">
         <v>47</v>
       </c>
       <c r="AA27">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB27" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC27" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD27" t="s">
         <v>48</v>
       </c>
       <c r="AF27" t="s">
-        <v>43</v>
+        <v>248</v>
       </c>
       <c r="AG27" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="AH27" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="AI27" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AJ27" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D28" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E28" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="F28" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" t="s">
-        <v>259</v>
+        <v>77</v>
       </c>
       <c r="I28" t="s">
         <v>46</v>
@@ -4179,28 +4038,28 @@
         <v>13262</v>
       </c>
       <c r="T28" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V28" t="s">
         <v>38</v>
       </c>
       <c r="W28" t="s">
-        <v>260</v>
+        <v>220</v>
       </c>
       <c r="X28" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="Y28" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z28" t="s">
         <v>47</v>
       </c>
       <c r="AA28">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB28" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC28" t="s">
         <v>39</v>
@@ -4209,45 +4068,45 @@
         <v>48</v>
       </c>
       <c r="AF28" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="AG28" t="s">
         <v>41</v>
       </c>
       <c r="AH28" t="s">
-        <v>49</v>
+        <v>254</v>
       </c>
       <c r="AI28" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="AJ28" t="s">
-        <v>45</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D29" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E29" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="F29" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G29">
         <v>4</v>
       </c>
       <c r="H29" t="s">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="I29" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -4256,19 +4115,19 @@
         <v>13262</v>
       </c>
       <c r="T29" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V29" t="s">
         <v>38</v>
       </c>
       <c r="W29" t="s">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="X29" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="Y29" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z29" t="s">
         <v>47</v>
@@ -4277,7 +4136,7 @@
         <v>24</v>
       </c>
       <c r="AB29" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC29" t="s">
         <v>39</v>
@@ -4286,45 +4145,45 @@
         <v>48</v>
       </c>
       <c r="AF29" t="s">
-        <v>43</v>
+        <v>260</v>
       </c>
       <c r="AG29" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH29" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="AI29" t="s">
-        <v>267</v>
+        <v>96</v>
       </c>
       <c r="AJ29" t="s">
-        <v>198</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" t="s">
         <v>57</v>
       </c>
-      <c r="B30" t="s">
-        <v>65</v>
-      </c>
       <c r="D30" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="E30" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="F30" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="I30" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R30">
         <v>1</v>
@@ -4333,66 +4192,66 @@
         <v>13262</v>
       </c>
       <c r="T30" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V30" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="W30" t="s">
-        <v>270</v>
+        <v>97</v>
       </c>
       <c r="X30" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="Y30" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Z30" t="s">
         <v>47</v>
       </c>
       <c r="AA30">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB30" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC30" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD30" t="s">
         <v>48</v>
       </c>
       <c r="AF30" t="s">
-        <v>43</v>
+        <v>264</v>
       </c>
       <c r="AG30" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="AH30" t="s">
         <v>42</v>
       </c>
       <c r="AI30" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AJ30" t="s">
-        <v>198</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" t="s">
         <v>57</v>
       </c>
-      <c r="B31" t="s">
-        <v>65</v>
-      </c>
       <c r="D31" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E31" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F31" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -4401,7 +4260,7 @@
         <v>50</v>
       </c>
       <c r="I31" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -4410,72 +4269,69 @@
         <v>13262</v>
       </c>
       <c r="T31" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V31" t="s">
         <v>38</v>
       </c>
       <c r="W31" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="X31" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="Y31" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z31" t="s">
         <v>47</v>
       </c>
       <c r="AA31">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB31" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC31" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD31" t="s">
         <v>48</v>
       </c>
       <c r="AF31" t="s">
-        <v>43</v>
+        <v>271</v>
       </c>
       <c r="AG31" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH31" t="s">
-        <v>62</v>
+        <v>254</v>
       </c>
       <c r="AI31" t="s">
-        <v>256</v>
-      </c>
-      <c r="AJ31" t="s">
-        <v>210</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" t="s">
         <v>57</v>
       </c>
-      <c r="B32" t="s">
-        <v>65</v>
-      </c>
       <c r="D32" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E32" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F32" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H32" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I32" t="s">
         <v>55</v>
@@ -4487,19 +4343,19 @@
         <v>13262</v>
       </c>
       <c r="T32" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V32" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="W32" t="s">
-        <v>162</v>
+        <v>275</v>
       </c>
       <c r="X32" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y32" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z32" t="s">
         <v>47</v>
@@ -4508,57 +4364,54 @@
         <v>20</v>
       </c>
       <c r="AB32" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC32" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD32" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE32" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="AF32" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="AG32" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH32" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s">
-        <v>165</v>
+        <v>277</v>
       </c>
       <c r="AJ32" t="s">
-        <v>45</v>
+        <v>278</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" t="s">
         <v>57</v>
       </c>
-      <c r="B33" t="s">
-        <v>65</v>
-      </c>
       <c r="D33" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E33" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F33" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H33" t="s">
-        <v>99</v>
+        <v>233</v>
       </c>
       <c r="I33" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -4567,72 +4420,72 @@
         <v>13262</v>
       </c>
       <c r="T33" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V33" t="s">
         <v>38</v>
       </c>
       <c r="W33" t="s">
-        <v>93</v>
+        <v>220</v>
       </c>
       <c r="X33" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Y33" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z33" t="s">
         <v>47</v>
       </c>
       <c r="AA33">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB33" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC33" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD33" t="s">
         <v>48</v>
       </c>
       <c r="AF33" t="s">
-        <v>281</v>
+        <v>67</v>
       </c>
       <c r="AG33" t="s">
         <v>41</v>
       </c>
       <c r="AH33" t="s">
-        <v>129</v>
+        <v>254</v>
       </c>
       <c r="AI33" t="s">
         <v>282</v>
       </c>
       <c r="AJ33" t="s">
-        <v>283</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" t="s">
         <v>57</v>
       </c>
-      <c r="B34" t="s">
-        <v>65</v>
-      </c>
       <c r="D34" t="s">
+        <v>283</v>
+      </c>
+      <c r="E34" t="s">
         <v>284</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" s="1">
+        <v>46265</v>
+      </c>
+      <c r="G34">
+        <v>6</v>
+      </c>
+      <c r="H34" t="s">
         <v>285</v>
-      </c>
-      <c r="F34" s="1">
-        <v>46262</v>
-      </c>
-      <c r="G34">
-        <v>10</v>
-      </c>
-      <c r="H34" t="s">
-        <v>286</v>
       </c>
       <c r="I34" t="s">
         <v>37</v>
@@ -4644,28 +4497,28 @@
         <v>13262</v>
       </c>
       <c r="T34" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V34" t="s">
         <v>38</v>
       </c>
       <c r="W34" t="s">
+        <v>286</v>
+      </c>
+      <c r="X34" t="s">
         <v>287</v>
       </c>
-      <c r="X34" t="s">
-        <v>288</v>
-      </c>
       <c r="Y34" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z34" t="s">
         <v>47</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB34" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC34" t="s">
         <v>48</v>
@@ -4680,21 +4533,21 @@
         <v>43</v>
       </c>
       <c r="AH34" t="s">
-        <v>68</v>
+        <v>174</v>
       </c>
       <c r="AI34" t="s">
+        <v>288</v>
+      </c>
+      <c r="AJ34" t="s">
         <v>289</v>
-      </c>
-      <c r="AJ34" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" t="s">
         <v>57</v>
-      </c>
-      <c r="B35" t="s">
-        <v>65</v>
       </c>
       <c r="D35" t="s">
         <v>290</v>
@@ -4703,16 +4556,16 @@
         <v>291</v>
       </c>
       <c r="F35" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H35" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="I35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R35">
         <v>1</v>
@@ -4721,75 +4574,75 @@
         <v>13262</v>
       </c>
       <c r="T35" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V35" t="s">
         <v>38</v>
       </c>
       <c r="W35" t="s">
+        <v>197</v>
+      </c>
+      <c r="X35" t="s">
         <v>292</v>
       </c>
-      <c r="X35" t="s">
-        <v>293</v>
-      </c>
       <c r="Y35" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z35" t="s">
         <v>47</v>
       </c>
       <c r="AA35">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AB35" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC35" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD35" t="s">
         <v>48</v>
       </c>
       <c r="AF35" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="AG35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH35" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="AI35" t="s">
-        <v>294</v>
+        <v>96</v>
       </c>
       <c r="AJ35" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" t="s">
         <v>57</v>
       </c>
-      <c r="B36" t="s">
-        <v>65</v>
-      </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E36" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F36" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G36">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H36" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -4798,75 +4651,75 @@
         <v>13262</v>
       </c>
       <c r="T36" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V36" t="s">
         <v>38</v>
       </c>
       <c r="W36" t="s">
-        <v>241</v>
+        <v>295</v>
       </c>
       <c r="X36" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Y36" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z36" t="s">
         <v>47</v>
       </c>
       <c r="AA36">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB36" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC36" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD36" t="s">
         <v>48</v>
       </c>
       <c r="AF36" t="s">
-        <v>43</v>
+        <v>297</v>
       </c>
       <c r="AG36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH36" t="s">
         <v>51</v>
       </c>
       <c r="AI36" t="s">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="AJ36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" t="s">
         <v>57</v>
       </c>
-      <c r="B37" t="s">
-        <v>65</v>
-      </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F37" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="I37" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -4875,28 +4728,28 @@
         <v>13262</v>
       </c>
       <c r="T37" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V37" t="s">
         <v>38</v>
       </c>
       <c r="W37" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="X37" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Y37" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z37" t="s">
         <v>47</v>
       </c>
       <c r="AA37">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB37" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC37" t="s">
         <v>48</v>
@@ -4905,45 +4758,42 @@
         <v>48</v>
       </c>
       <c r="AF37" t="s">
-        <v>43</v>
+        <v>303</v>
       </c>
       <c r="AG37" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH37" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="AI37" t="s">
-        <v>215</v>
-      </c>
-      <c r="AJ37" t="s">
-        <v>45</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D38" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E38" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F38" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G38">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H38" t="s">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="I38" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R38">
         <v>1</v>
@@ -4952,75 +4802,75 @@
         <v>13262</v>
       </c>
       <c r="T38" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V38" t="s">
         <v>38</v>
       </c>
       <c r="W38" t="s">
-        <v>305</v>
+        <v>220</v>
       </c>
       <c r="X38" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Y38" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z38" t="s">
         <v>47</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB38" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC38" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD38" t="s">
         <v>48</v>
       </c>
       <c r="AF38" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="AG38" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH38" t="s">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="AI38" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AJ38" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D39" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E39" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F39" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G39">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H39" t="s">
-        <v>85</v>
+        <v>233</v>
       </c>
       <c r="I39" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R39">
         <v>1</v>
@@ -5029,57 +4879,57 @@
         <v>13262</v>
       </c>
       <c r="T39" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V39" t="s">
         <v>38</v>
       </c>
       <c r="W39" t="s">
-        <v>311</v>
+        <v>220</v>
       </c>
       <c r="X39" t="s">
         <v>312</v>
       </c>
       <c r="Y39" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z39" t="s">
         <v>47</v>
       </c>
       <c r="AA39">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AB39" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC39" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD39" t="s">
         <v>48</v>
       </c>
       <c r="AF39" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="AG39" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH39" t="s">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="AI39" t="s">
         <v>313</v>
       </c>
       <c r="AJ39" t="s">
-        <v>308</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D40" t="s">
         <v>314</v>
@@ -5088,13 +4938,13 @@
         <v>315</v>
       </c>
       <c r="F40" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G40">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H40" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="I40" t="s">
         <v>55</v>
@@ -5106,28 +4956,28 @@
         <v>13262</v>
       </c>
       <c r="T40" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V40" t="s">
         <v>38</v>
       </c>
       <c r="W40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="X40" t="s">
         <v>316</v>
       </c>
       <c r="Y40" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z40" t="s">
         <v>47</v>
       </c>
       <c r="AA40">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB40" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC40" t="s">
         <v>39</v>
@@ -5136,27 +4986,27 @@
         <v>48</v>
       </c>
       <c r="AF40" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="AG40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH40" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="AI40" t="s">
         <v>317</v>
       </c>
       <c r="AJ40" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B41" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D41" t="s">
         <v>318</v>
@@ -5165,16 +5015,16 @@
         <v>319</v>
       </c>
       <c r="F41" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G41">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H41" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="I41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -5183,28 +5033,28 @@
         <v>13262</v>
       </c>
       <c r="T41" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V41" t="s">
         <v>38</v>
       </c>
       <c r="W41" t="s">
-        <v>88</v>
+        <v>197</v>
       </c>
       <c r="X41" t="s">
         <v>320</v>
       </c>
       <c r="Y41" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z41" t="s">
         <v>47</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AB41" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC41" t="s">
         <v>39</v>
@@ -5213,27 +5063,27 @@
         <v>48</v>
       </c>
       <c r="AF41" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="AG41" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH41" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="AI41" t="s">
         <v>321</v>
       </c>
       <c r="AJ41" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D42" t="s">
         <v>322</v>
@@ -5242,16 +5092,16 @@
         <v>323</v>
       </c>
       <c r="F42" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H42" t="s">
-        <v>324</v>
+        <v>77</v>
       </c>
       <c r="I42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="R42">
         <v>1</v>
@@ -5260,28 +5110,28 @@
         <v>13262</v>
       </c>
       <c r="T42" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V42" t="s">
         <v>38</v>
       </c>
       <c r="W42" t="s">
+        <v>324</v>
+      </c>
+      <c r="X42" t="s">
         <v>325</v>
       </c>
-      <c r="X42" t="s">
-        <v>326</v>
-      </c>
       <c r="Y42" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z42" t="s">
         <v>47</v>
       </c>
       <c r="AA42">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB42" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC42" t="s">
         <v>39</v>
@@ -5290,27 +5140,27 @@
         <v>48</v>
       </c>
       <c r="AF42" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="AG42" t="s">
         <v>41</v>
       </c>
       <c r="AH42" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AI42" t="s">
+        <v>326</v>
+      </c>
+      <c r="AJ42" t="s">
         <v>327</v>
-      </c>
-      <c r="AJ42" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D43" t="s">
         <v>328</v>
@@ -5319,13 +5169,13 @@
         <v>329</v>
       </c>
       <c r="F43" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" t="s">
-        <v>194</v>
+        <v>285</v>
       </c>
       <c r="I43" t="s">
         <v>37</v>
@@ -5337,19 +5187,19 @@
         <v>13262</v>
       </c>
       <c r="T43" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V43" t="s">
         <v>38</v>
       </c>
       <c r="W43" t="s">
+        <v>286</v>
+      </c>
+      <c r="X43" t="s">
         <v>330</v>
       </c>
-      <c r="X43" t="s">
-        <v>331</v>
-      </c>
       <c r="Y43" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z43" t="s">
         <v>47</v>
@@ -5358,7 +5208,7 @@
         <v>24</v>
       </c>
       <c r="AB43" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC43" t="s">
         <v>39</v>
@@ -5367,27 +5217,27 @@
         <v>48</v>
       </c>
       <c r="AF43" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="AG43" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH43" t="s">
-        <v>42</v>
+        <v>174</v>
       </c>
       <c r="AI43" t="s">
+        <v>331</v>
+      </c>
+      <c r="AJ43" t="s">
         <v>332</v>
-      </c>
-      <c r="AJ43" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D44" t="s">
         <v>333</v>
@@ -5396,13 +5246,13 @@
         <v>334</v>
       </c>
       <c r="F44" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="I44" t="s">
         <v>55</v>
@@ -5414,19 +5264,19 @@
         <v>13262</v>
       </c>
       <c r="T44" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V44" t="s">
         <v>38</v>
       </c>
       <c r="W44" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="X44" t="s">
         <v>335</v>
       </c>
       <c r="Y44" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z44" t="s">
         <v>47</v>
@@ -5435,7 +5285,7 @@
         <v>20</v>
       </c>
       <c r="AB44" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC44" t="s">
         <v>48</v>
@@ -5444,45 +5294,45 @@
         <v>48</v>
       </c>
       <c r="AF44" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="AG44" t="s">
         <v>41</v>
       </c>
       <c r="AH44" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="AI44" t="s">
         <v>336</v>
       </c>
       <c r="AJ44" t="s">
-        <v>337</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="D45" t="s">
+        <v>337</v>
+      </c>
+      <c r="E45" t="s">
         <v>338</v>
       </c>
-      <c r="E45" t="s">
-        <v>339</v>
-      </c>
       <c r="F45" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G45">
         <v>3</v>
       </c>
       <c r="H45" t="s">
-        <v>340</v>
+        <v>50</v>
       </c>
       <c r="I45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -5491,28 +5341,28 @@
         <v>13262</v>
       </c>
       <c r="T45" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V45" t="s">
         <v>38</v>
       </c>
       <c r="W45" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="X45" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="Y45" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Z45" t="s">
         <v>47</v>
       </c>
       <c r="AA45">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB45" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC45" t="s">
         <v>39</v>
@@ -5521,45 +5371,45 @@
         <v>48</v>
       </c>
       <c r="AF45" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="AG45" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH45" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="AI45" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AJ45" t="s">
-        <v>344</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D46" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E46" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F46" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H46" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="I46" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R46">
         <v>1</v>
@@ -5568,75 +5418,75 @@
         <v>13262</v>
       </c>
       <c r="T46" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V46" t="s">
-        <v>184</v>
+        <v>38</v>
       </c>
       <c r="W46" t="s">
-        <v>347</v>
+        <v>220</v>
       </c>
       <c r="X46" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="Y46" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z46" t="s">
         <v>47</v>
       </c>
       <c r="AA46">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB46" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC46" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD46" t="s">
         <v>48</v>
       </c>
       <c r="AF46" t="s">
-        <v>349</v>
+        <v>83</v>
       </c>
       <c r="AG46" t="s">
-        <v>188</v>
+        <v>41</v>
       </c>
       <c r="AH46" t="s">
-        <v>70</v>
+        <v>254</v>
       </c>
       <c r="AI46" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="AJ46" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D47" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="E47" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="F47" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G47">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H47" t="s">
-        <v>194</v>
+        <v>233</v>
       </c>
       <c r="I47" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R47">
         <v>1</v>
@@ -5645,28 +5495,28 @@
         <v>13262</v>
       </c>
       <c r="T47" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V47" t="s">
         <v>38</v>
       </c>
       <c r="W47" t="s">
-        <v>330</v>
+        <v>220</v>
       </c>
       <c r="X47" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="Y47" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z47" t="s">
         <v>47</v>
       </c>
       <c r="AA47">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB47" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC47" t="s">
         <v>39</v>
@@ -5675,45 +5525,45 @@
         <v>48</v>
       </c>
       <c r="AF47" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="AG47" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH47" t="s">
-        <v>42</v>
+        <v>254</v>
       </c>
       <c r="AI47" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="AJ47" t="s">
-        <v>355</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D48" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="E48" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="F48" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G48">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H48" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I48" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R48">
         <v>1</v>
@@ -5722,19 +5572,19 @@
         <v>13262</v>
       </c>
       <c r="T48" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V48" t="s">
         <v>38</v>
       </c>
       <c r="W48" t="s">
-        <v>292</v>
+        <v>353</v>
       </c>
       <c r="X48" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="Y48" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z48" t="s">
         <v>47</v>
@@ -5743,54 +5593,54 @@
         <v>20</v>
       </c>
       <c r="AB48" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC48" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD48" t="s">
         <v>48</v>
       </c>
       <c r="AF48" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="AG48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH48" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="AI48" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AJ48" t="s">
-        <v>360</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="D49" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E49" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="F49" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G49">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H49" t="s">
-        <v>304</v>
+        <v>50</v>
       </c>
       <c r="I49" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R49">
         <v>1</v>
@@ -5799,19 +5649,19 @@
         <v>13262</v>
       </c>
       <c r="T49" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V49" t="s">
         <v>38</v>
       </c>
       <c r="W49" t="s">
-        <v>305</v>
+        <v>220</v>
       </c>
       <c r="X49" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="Y49" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z49" t="s">
         <v>47</v>
@@ -5820,7 +5670,7 @@
         <v>20</v>
       </c>
       <c r="AB49" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC49" t="s">
         <v>39</v>
@@ -5829,45 +5679,45 @@
         <v>48</v>
       </c>
       <c r="AF49" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="AG49" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH49" t="s">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="AI49" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="AJ49" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="D50" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E50" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F50" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G50">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H50" t="s">
-        <v>265</v>
+        <v>77</v>
       </c>
       <c r="I50" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="R50">
         <v>1</v>
@@ -5876,19 +5726,19 @@
         <v>13262</v>
       </c>
       <c r="T50" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V50" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="W50" t="s">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="X50" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="Y50" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z50" t="s">
         <v>47</v>
@@ -5897,7 +5747,7 @@
         <v>24</v>
       </c>
       <c r="AB50" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC50" t="s">
         <v>39</v>
@@ -5906,45 +5756,45 @@
         <v>48</v>
       </c>
       <c r="AF50" t="s">
-        <v>43</v>
+        <v>119</v>
       </c>
       <c r="AG50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH50" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="AI50" t="s">
-        <v>369</v>
+        <v>199</v>
       </c>
       <c r="AJ50" t="s">
-        <v>370</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D51" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="E51" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="F51" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G51">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H51" t="s">
-        <v>50</v>
+        <v>178</v>
       </c>
       <c r="I51" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R51">
         <v>1</v>
@@ -5953,28 +5803,28 @@
         <v>13262</v>
       </c>
       <c r="T51" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V51" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="W51" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="X51" t="s">
-        <v>316</v>
+        <v>365</v>
       </c>
       <c r="Y51" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z51" t="s">
         <v>47</v>
       </c>
       <c r="AA51">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AB51" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC51" t="s">
         <v>39</v>
@@ -5989,39 +5839,39 @@
         <v>43</v>
       </c>
       <c r="AH51" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="AI51" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="AJ51" t="s">
-        <v>374</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D52" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="E52" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="F52" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G52">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H52" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I52" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R52">
         <v>1</v>
@@ -6030,19 +5880,19 @@
         <v>13262</v>
       </c>
       <c r="T52" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V52" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="W52" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="X52" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="Y52" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z52" t="s">
         <v>47</v>
@@ -6051,10 +5901,10 @@
         <v>20</v>
       </c>
       <c r="AB52" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC52" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD52" t="s">
         <v>48</v>
@@ -6066,39 +5916,39 @@
         <v>43</v>
       </c>
       <c r="AH52" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="AI52" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="AJ52" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D53" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="E53" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="F53" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G53">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H53" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="I53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R53">
         <v>1</v>
@@ -6107,28 +5957,28 @@
         <v>13262</v>
       </c>
       <c r="T53" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V53" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="W53" t="s">
-        <v>88</v>
+        <v>197</v>
       </c>
       <c r="X53" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="Y53" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z53" t="s">
         <v>47</v>
       </c>
       <c r="AA53">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AB53" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC53" t="s">
         <v>39</v>
@@ -6143,39 +5993,39 @@
         <v>43</v>
       </c>
       <c r="AH53" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="AI53" t="s">
-        <v>384</v>
+        <v>321</v>
       </c>
       <c r="AJ53" t="s">
-        <v>385</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D54" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="E54" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="F54" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G54">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H54" t="s">
-        <v>388</v>
+        <v>77</v>
       </c>
       <c r="I54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R54">
         <v>1</v>
@@ -6184,31 +6034,31 @@
         <v>13262</v>
       </c>
       <c r="T54" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V54" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="W54" t="s">
-        <v>93</v>
+        <v>378</v>
       </c>
       <c r="X54" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="Y54" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z54" t="s">
         <v>47</v>
       </c>
       <c r="AA54">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB54" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC54" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD54" t="s">
         <v>48</v>
@@ -6220,39 +6070,39 @@
         <v>43</v>
       </c>
       <c r="AH54" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="AI54" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AJ54" t="s">
-        <v>391</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D55" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="E55" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="F55" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G55">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H55" t="s">
         <v>50</v>
       </c>
       <c r="I55" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="R55">
         <v>1</v>
@@ -6261,19 +6111,19 @@
         <v>13262</v>
       </c>
       <c r="T55" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V55" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="W55" t="s">
-        <v>241</v>
+        <v>94</v>
       </c>
       <c r="X55" t="s">
-        <v>297</v>
+        <v>383</v>
       </c>
       <c r="Y55" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z55" t="s">
         <v>47</v>
@@ -6282,7 +6132,7 @@
         <v>20</v>
       </c>
       <c r="AB55" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC55" t="s">
         <v>39</v>
@@ -6297,39 +6147,39 @@
         <v>43</v>
       </c>
       <c r="AH55" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="AI55" t="s">
-        <v>244</v>
+        <v>384</v>
       </c>
       <c r="AJ55" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D56" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="E56" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="F56" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G56">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H56" t="s">
-        <v>50</v>
+        <v>285</v>
       </c>
       <c r="I56" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -6338,19 +6188,19 @@
         <v>13262</v>
       </c>
       <c r="T56" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V56" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="W56" t="s">
-        <v>254</v>
+        <v>286</v>
       </c>
       <c r="X56" t="s">
-        <v>255</v>
+        <v>388</v>
       </c>
       <c r="Y56" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z56" t="s">
         <v>47</v>
@@ -6359,7 +6209,7 @@
         <v>20</v>
       </c>
       <c r="AB56" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC56" t="s">
         <v>39</v>
@@ -6374,39 +6224,39 @@
         <v>43</v>
       </c>
       <c r="AH56" t="s">
-        <v>62</v>
+        <v>174</v>
       </c>
       <c r="AI56" t="s">
-        <v>256</v>
+        <v>331</v>
       </c>
       <c r="AJ56" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D57" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="E57" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="F57" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G57">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H57" t="s">
-        <v>286</v>
+        <v>84</v>
       </c>
       <c r="I57" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="R57">
         <v>1</v>
@@ -6415,28 +6265,28 @@
         <v>13262</v>
       </c>
       <c r="T57" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V57" t="s">
         <v>38</v>
       </c>
       <c r="W57" t="s">
-        <v>287</v>
+        <v>392</v>
       </c>
       <c r="X57" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="Y57" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Z57" t="s">
         <v>47</v>
       </c>
       <c r="AA57">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB57" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC57" t="s">
         <v>48</v>
@@ -6451,39 +6301,36 @@
         <v>43</v>
       </c>
       <c r="AH57" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="AI57" t="s">
-        <v>401</v>
-      </c>
-      <c r="AJ57" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
     </row>
     <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D58" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="E58" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="F58" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G58">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H58" t="s">
-        <v>405</v>
+        <v>77</v>
       </c>
       <c r="I58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R58">
         <v>1</v>
@@ -6492,19 +6339,19 @@
         <v>13262</v>
       </c>
       <c r="T58" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V58" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="W58" t="s">
-        <v>88</v>
+        <v>397</v>
       </c>
       <c r="X58" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="Y58" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z58" t="s">
         <v>47</v>
@@ -6513,54 +6360,54 @@
         <v>20</v>
       </c>
       <c r="AB58" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC58" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD58" t="s">
         <v>48</v>
       </c>
       <c r="AF58" t="s">
-        <v>407</v>
+        <v>43</v>
       </c>
       <c r="AG58" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH58" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="AI58" t="s">
-        <v>408</v>
+        <v>99</v>
       </c>
       <c r="AJ58" t="s">
-        <v>409</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D59" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="E59" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="F59" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G59">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H59" t="s">
-        <v>412</v>
+        <v>77</v>
       </c>
       <c r="I59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R59">
         <v>1</v>
@@ -6569,28 +6416,28 @@
         <v>13262</v>
       </c>
       <c r="T59" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V59" t="s">
         <v>38</v>
       </c>
       <c r="W59" t="s">
-        <v>95</v>
+        <v>401</v>
       </c>
       <c r="X59" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="Y59" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Z59" t="s">
         <v>47</v>
       </c>
       <c r="AA59">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB59" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC59" t="s">
         <v>39</v>
@@ -6608,33 +6455,36 @@
         <v>49</v>
       </c>
       <c r="AI59" t="s">
-        <v>414</v>
+        <v>403</v>
+      </c>
+      <c r="AJ59" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D60" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="E60" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="F60" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H60" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="I60" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="R60">
         <v>1</v>
@@ -6643,75 +6493,75 @@
         <v>13262</v>
       </c>
       <c r="T60" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V60" t="s">
-        <v>184</v>
+        <v>38</v>
       </c>
       <c r="W60" t="s">
-        <v>347</v>
+        <v>123</v>
       </c>
       <c r="X60" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="Y60" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z60" t="s">
         <v>47</v>
       </c>
       <c r="AA60">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AB60" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC60" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD60" t="s">
         <v>48</v>
       </c>
       <c r="AF60" t="s">
-        <v>418</v>
+        <v>43</v>
       </c>
       <c r="AG60" t="s">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="AH60" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="AI60" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="AJ60" t="s">
-        <v>420</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D61" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="E61" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="F61" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H61" t="s">
-        <v>50</v>
+        <v>410</v>
       </c>
       <c r="I61" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R61">
         <v>1</v>
@@ -6720,19 +6570,19 @@
         <v>13262</v>
       </c>
       <c r="T61" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V61" t="s">
         <v>38</v>
       </c>
       <c r="W61" t="s">
-        <v>254</v>
+        <v>411</v>
       </c>
       <c r="X61" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="Y61" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z61" t="s">
         <v>47</v>
@@ -6741,7 +6591,7 @@
         <v>20</v>
       </c>
       <c r="AB61" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC61" t="s">
         <v>39</v>
@@ -6756,39 +6606,36 @@
         <v>43</v>
       </c>
       <c r="AH61" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="AI61" t="s">
-        <v>256</v>
-      </c>
-      <c r="AJ61" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
     </row>
     <row r="62" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B62" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D62" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="E62" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="F62" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G62">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H62" t="s">
         <v>50</v>
       </c>
       <c r="I62" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R62">
         <v>1</v>
@@ -6797,28 +6644,28 @@
         <v>13262</v>
       </c>
       <c r="T62" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V62" t="s">
         <v>38</v>
       </c>
       <c r="W62" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="X62" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="Y62" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Z62" t="s">
         <v>47</v>
       </c>
       <c r="AA62">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB62" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC62" t="s">
         <v>39</v>
@@ -6827,45 +6674,42 @@
         <v>48</v>
       </c>
       <c r="AF62" t="s">
-        <v>427</v>
+        <v>43</v>
       </c>
       <c r="AG62" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH62" t="s">
-        <v>51</v>
+        <v>254</v>
       </c>
       <c r="AI62" t="s">
-        <v>428</v>
-      </c>
-      <c r="AJ62" t="s">
-        <v>429</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B63" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D63" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="E63" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="F63" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G63">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H63" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R63">
         <v>1</v>
@@ -6874,28 +6718,28 @@
         <v>13262</v>
       </c>
       <c r="T63" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V63" t="s">
         <v>38</v>
       </c>
       <c r="W63" t="s">
-        <v>432</v>
+        <v>197</v>
       </c>
       <c r="X63" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="Y63" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z63" t="s">
         <v>47</v>
       </c>
       <c r="AA63">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AB63" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC63" t="s">
         <v>39</v>
@@ -6910,36 +6754,36 @@
         <v>43</v>
       </c>
       <c r="AH63" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AI63" t="s">
-        <v>434</v>
+        <v>96</v>
       </c>
       <c r="AJ63" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B64" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D64" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="E64" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="F64" s="1">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="G64">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H64" t="s">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="I64" t="s">
         <v>55</v>
@@ -6951,28 +6795,28 @@
         <v>13262</v>
       </c>
       <c r="T64" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="V64" t="s">
         <v>38</v>
       </c>
       <c r="W64" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="X64" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="Y64" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="Z64" t="s">
         <v>47</v>
       </c>
       <c r="AA64">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB64" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AC64" t="s">
         <v>39</v>
@@ -6981,481 +6825,19 @@
         <v>48</v>
       </c>
       <c r="AF64" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="AG64" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH64" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AI64" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="AJ64" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>57</v>
-      </c>
-      <c r="B65" t="s">
-        <v>69</v>
-      </c>
-      <c r="D65" t="s">
-        <v>441</v>
-      </c>
-      <c r="E65" t="s">
-        <v>442</v>
-      </c>
-      <c r="F65" s="1">
-        <v>46262</v>
-      </c>
-      <c r="G65">
-        <v>8</v>
-      </c>
-      <c r="H65" t="s">
-        <v>412</v>
-      </c>
-      <c r="I65" t="s">
-        <v>55</v>
-      </c>
-      <c r="R65">
-        <v>1</v>
-      </c>
-      <c r="S65">
-        <v>13262</v>
-      </c>
-      <c r="T65" t="s">
-        <v>77</v>
-      </c>
-      <c r="V65" t="s">
-        <v>38</v>
-      </c>
-      <c r="W65" t="s">
-        <v>95</v>
-      </c>
-      <c r="X65" t="s">
-        <v>443</v>
-      </c>
-      <c r="Y65" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z65" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA65">
-        <v>20</v>
-      </c>
-      <c r="AB65" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC65" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD65" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF65" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG65" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH65" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI65" t="s">
-        <v>414</v>
-      </c>
-      <c r="AJ65" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>57</v>
-      </c>
-      <c r="B66" t="s">
-        <v>69</v>
-      </c>
-      <c r="D66" t="s">
-        <v>444</v>
-      </c>
-      <c r="E66" t="s">
-        <v>445</v>
-      </c>
-      <c r="F66" s="1">
-        <v>46262</v>
-      </c>
-      <c r="G66">
-        <v>9</v>
-      </c>
-      <c r="H66" t="s">
-        <v>90</v>
-      </c>
-      <c r="I66" t="s">
-        <v>46</v>
-      </c>
-      <c r="R66">
-        <v>1</v>
-      </c>
-      <c r="S66">
-        <v>13262</v>
-      </c>
-      <c r="T66" t="s">
-        <v>77</v>
-      </c>
-      <c r="V66" t="s">
-        <v>38</v>
-      </c>
-      <c r="W66" t="s">
-        <v>446</v>
-      </c>
-      <c r="X66" t="s">
-        <v>447</v>
-      </c>
-      <c r="Y66" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z66" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA66">
-        <v>20</v>
-      </c>
-      <c r="AB66" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC66" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD66" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF66" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG66" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH66" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI66" t="s">
-        <v>448</v>
-      </c>
-      <c r="AJ66" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>57</v>
-      </c>
-      <c r="B67" t="s">
-        <v>71</v>
-      </c>
-      <c r="D67" t="s">
-        <v>450</v>
-      </c>
-      <c r="E67" t="s">
-        <v>451</v>
-      </c>
-      <c r="F67" s="1">
-        <v>46262</v>
-      </c>
-      <c r="G67">
-        <v>3</v>
-      </c>
-      <c r="H67" t="s">
-        <v>85</v>
-      </c>
-      <c r="I67" t="s">
-        <v>55</v>
-      </c>
-      <c r="R67">
-        <v>1</v>
-      </c>
-      <c r="S67">
-        <v>13262</v>
-      </c>
-      <c r="T67" t="s">
-        <v>77</v>
-      </c>
-      <c r="V67" t="s">
-        <v>38</v>
-      </c>
-      <c r="W67" t="s">
-        <v>104</v>
-      </c>
-      <c r="X67" t="s">
-        <v>452</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z67" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA67">
-        <v>20</v>
-      </c>
-      <c r="AB67" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC67" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD67" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF67" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG67" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH67" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI67" t="s">
-        <v>453</v>
-      </c>
-      <c r="AJ67" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>57</v>
-      </c>
-      <c r="B68" t="s">
-        <v>71</v>
-      </c>
-      <c r="D68" t="s">
-        <v>454</v>
-      </c>
-      <c r="E68" t="s">
-        <v>455</v>
-      </c>
-      <c r="F68" s="1">
-        <v>46262</v>
-      </c>
-      <c r="G68">
-        <v>3</v>
-      </c>
-      <c r="H68" t="s">
-        <v>324</v>
-      </c>
-      <c r="I68" t="s">
-        <v>56</v>
-      </c>
-      <c r="R68">
-        <v>1</v>
-      </c>
-      <c r="S68">
-        <v>13262</v>
-      </c>
-      <c r="T68" t="s">
-        <v>77</v>
-      </c>
-      <c r="V68" t="s">
-        <v>38</v>
-      </c>
-      <c r="W68" t="s">
-        <v>325</v>
-      </c>
-      <c r="X68" t="s">
-        <v>456</v>
-      </c>
-      <c r="Y68" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z68" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA68">
-        <v>20</v>
-      </c>
-      <c r="AB68" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC68" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD68" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF68" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG68" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH68" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI68" t="s">
-        <v>327</v>
-      </c>
-      <c r="AJ68" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>57</v>
-      </c>
-      <c r="B69" t="s">
-        <v>71</v>
-      </c>
-      <c r="D69" t="s">
-        <v>457</v>
-      </c>
-      <c r="E69" t="s">
-        <v>458</v>
-      </c>
-      <c r="F69" s="1">
-        <v>46262</v>
-      </c>
-      <c r="G69">
-        <v>4</v>
-      </c>
-      <c r="H69" t="s">
-        <v>194</v>
-      </c>
-      <c r="I69" t="s">
-        <v>37</v>
-      </c>
-      <c r="R69">
-        <v>1</v>
-      </c>
-      <c r="S69">
-        <v>13262</v>
-      </c>
-      <c r="T69" t="s">
-        <v>77</v>
-      </c>
-      <c r="V69" t="s">
-        <v>38</v>
-      </c>
-      <c r="W69" t="s">
-        <v>330</v>
-      </c>
-      <c r="X69" t="s">
-        <v>459</v>
-      </c>
-      <c r="Y69" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z69" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA69">
-        <v>24</v>
-      </c>
-      <c r="AB69" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC69" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD69" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF69" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG69" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH69" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI69" t="s">
-        <v>460</v>
-      </c>
-      <c r="AJ69" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="70" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>57</v>
-      </c>
-      <c r="B70" t="s">
-        <v>71</v>
-      </c>
-      <c r="D70" t="s">
-        <v>462</v>
-      </c>
-      <c r="E70" t="s">
-        <v>463</v>
-      </c>
-      <c r="F70" s="1">
-        <v>46262</v>
-      </c>
-      <c r="G70">
-        <v>5</v>
-      </c>
-      <c r="H70" t="s">
-        <v>50</v>
-      </c>
-      <c r="I70" t="s">
-        <v>37</v>
-      </c>
-      <c r="R70">
-        <v>1</v>
-      </c>
-      <c r="S70">
-        <v>13262</v>
-      </c>
-      <c r="T70" t="s">
-        <v>77</v>
-      </c>
-      <c r="V70" t="s">
-        <v>38</v>
-      </c>
-      <c r="W70" t="s">
-        <v>254</v>
-      </c>
-      <c r="X70" t="s">
-        <v>464</v>
-      </c>
-      <c r="Y70" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z70" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA70">
-        <v>20</v>
-      </c>
-      <c r="AB70" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC70" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD70" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF70" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG70" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH70" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI70" t="s">
-        <v>256</v>
-      </c>
-      <c r="AJ70" t="s">
-        <v>397</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93289598-7255-46AE-8868-96116496E313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D651E5-608D-4337-B570-5DF6B9C79481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="424">
   <si>
     <t>Canal</t>
   </si>
@@ -235,18 +235,12 @@
     <t>Veida Martínez Miranda</t>
   </si>
   <si>
-    <t>Zunoticia</t>
-  </si>
-  <si>
     <t>Planeación</t>
   </si>
   <si>
     <t>Plaza Juárez</t>
   </si>
   <si>
-    <t>Cultura</t>
-  </si>
-  <si>
     <t>Al Día Noticias</t>
   </si>
   <si>
@@ -274,9 +268,6 @@
     <t>Carmen Hernández</t>
   </si>
   <si>
-    <t>Obras De Infraestructura</t>
-  </si>
-  <si>
     <t>Turismo</t>
   </si>
   <si>
@@ -286,18 +277,9 @@
     <t>Boletín</t>
   </si>
   <si>
-    <t>Salvador Cruz Neri</t>
-  </si>
-  <si>
     <t>Huejutla</t>
   </si>
   <si>
-    <t>Capacitación docente</t>
-  </si>
-  <si>
-    <t>Desarrollo Urbano</t>
-  </si>
-  <si>
     <t>Alejandro Reyes</t>
   </si>
   <si>
@@ -316,9 +298,6 @@
     <t>Sipdus</t>
   </si>
   <si>
-    <t>Alma Leticia Sánchez</t>
-  </si>
-  <si>
     <t>Opinión</t>
   </si>
   <si>
@@ -331,997 +310,1015 @@
     <t>Dulce Castillo</t>
   </si>
   <si>
-    <t>Apoyo a artesanos</t>
-  </si>
-  <si>
-    <t>Ataque Armado</t>
-  </si>
-  <si>
     <t>Secretaría de Educación Pública de Hidalgo</t>
   </si>
   <si>
     <t>Temas varios</t>
   </si>
   <si>
-    <t>Natividad Castrejón Valdez, Julio Menchaca Salazar</t>
-  </si>
-  <si>
     <t>Secretaría de Seguridad Pública de Hidalgo</t>
   </si>
   <si>
-    <t>Planea Menchaca tres obras clave para cierre de sexenio</t>
-  </si>
-  <si>
-    <t>Al detallar los temas prioritarios que marcarán el cierre de su administración, el gobernador Julio Menchaca Salazar adelantó los proyectos que definirán los pendientes de su gestión, destacando tres obras de infraestructura fundamentales para la comunicación y la vialidad. Dos se ubicarán en Pachuca y una más fuera del estado que tendrá un impacto directo en toda la entidad. Asimismo, Menchaca Salazar destacó que Hidalgo mantiene cifras históricas en materia de inversión y generación de empleos, una tendencia que se mantendrá durante los próximos dos años.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca anunció que cerrará su sexenio con tres obras de infraestructura clave para mejorar la comunicación y movilidad en Pachuca y el estado.</t>
-  </si>
-  <si>
-    <t>Nathali González</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Secretaría de Desarrollo Económico</t>
-  </si>
-  <si>
-    <t>Trasladan a 174 internos del Cereso de Mixquiahuala a Tula</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH) llevó a cabo la madrugada de este viernes un operativo para trasladar a 174 personas privadas de la libertad desde el Cereso de Mixquiahuala de Juárez hacia el nuevo módulo de dormitorios del Cereso de Tula de Allende. La medida de reubicación responde principalmente a la severa sobrepoblación que registraba el penal de Mixquiahuala, que opera a más del doble de su capacidad, además de filtraciones pluviales en los dormitorios.</t>
-  </si>
-  <si>
-    <t>Mixquiahuala</t>
-  </si>
-  <si>
-    <t>Deficiencias Ceresos</t>
-  </si>
-  <si>
-    <t>La SSPH trasladó a 174 personas recluidas de Mixquiahuala a Tula para mitigar el hacinamiento y solventar daños pluviales en la infraestructura.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Gobierno del Estado de Hidalgo, Dirección de Protección Civil</t>
-  </si>
-  <si>
-    <t>Cierra la Muestra PECDA con actividades gratuitas en Pachuca</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura del Estado de Hidalgo invita a la última semana de actividades de la Muestra del Programa de Estímulos a la Creación y Desarrollo Artístico (PECDA) Hidalgo 2025, que se llevarán a cabo hasta el 31 de agosto. Los eventos se desarrollarán en tres recintos culturales de Pachuca: el Centro Cultural del Ferrocarril, el Teatro Guillermo Romo de Vivar y el Centro de Cultura Digital, incluyendo teatro, fotografía y artes visuales.</t>
-  </si>
-  <si>
-    <t>PECDA</t>
-  </si>
-  <si>
-    <t>La muestra artística PECDA cierra sus actividades de estímulos de artes escénicas y visuales en Pachuca con funciones y talleres interactivos gratuitos.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura de Hidalgo, Centro Cultural del Ferrocarril, Centro de Cultura Digital, Teatro Guillermo Romo de Vivar</t>
-  </si>
-  <si>
-    <t>Neyda Naranjo Baltazar, Jéssica Miriam Mejía, Mariana Castillo Monterrubio, Andrea Natalia Arriaga Pájaro, Fabrizio Otamendi Servín, Carol Delgado</t>
-  </si>
-  <si>
-    <t>Adelanta Menchaca anuncio de tres obras “importantes” de vialidad</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar informó que su cuarto informe de gobierno, programado para el próximo viernes 4 de septiembre, se realizará en las instalaciones de la Feria de Pachuca, cambiando de sede respecto a Plaza Juárez. Dentro de los próximos anuncios que incluirá su rendición de cuentas, adelantó que serán tres obras de infraestructura 'importantes' para comunicación y vialidad, mismas que también ayudarán a reducir el tráfico. Dos de ellas se ubicarán en la Zona Metropolitana de Pachuca y una más fuera de la entidad, pero 'que impactará directamente en el estado'. En otro tema, el titular del Ejecutivo estatal confirmó que Carlos Rivera será el artista que amenizará el festejo del 15 de septiembre, la noche del Grito de Independencia, en Plaza Juárez, junto a un grupo musical cuyo nombre se reservó.</t>
-  </si>
-  <si>
     <t>Marco Cerón</t>
   </si>
   <si>
-    <t>Julio Menchaca Salazar, Carlos Rivera</t>
-  </si>
-  <si>
-    <t>Envían a 174 reos del Cereso de Mixquiahuala a Tula</t>
-  </si>
-  <si>
-    <t>Por motivos de sobrepoblación, un total de 174 hombres que se encontraban recluidos en el Centro de Reinserción Social del municipio de Mixquiahuala fueron trasladados al penal de Tula. Además, se informó que otra de las causas por las que se realizó dicha acción fue porque los dormitorios presentaban filtraciones de agua y Protección Civil ordenó realizar un reforzamiento de los espacios y remodelación de los techos. La dependencia destacó que la capacidad del Cereso donde se encontraban es para 70 personas y albergaba a 191 internos. De acuerdo con la Secretaría de Seguridad Pública del estado (SSPH), los reos fueron removidos durante la madrugada de este 28 de agosto.</t>
-  </si>
-  <si>
-    <t>Reinserción social</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Dirección de Protección Civil</t>
-  </si>
-  <si>
-    <t>Evaluación de aprendizajes fortalece la práctica educativa: IHE</t>
-  </si>
-  <si>
-    <t>El Instituto Hidalguense de Educación (IHE) fortalece la capacitación y actualización del personal docente mediante los Ejercicios Integradores del Aprendizaje (EIA), procesos formativos alineados con los retos que enfrentan las escuelas y orientados a mejorar la práctica educativa en el aula. Los EIA permiten identificar conocimientos, habilidades y actitudes que las y los estudiantes ponen en práctica para resolver situaciones concretas, vinculadas con su contexto escolar y con los principios de la Nueva Escuela Mexicana. Durante el ciclo escolar 2025–2026, Hidalgo realizó este diagnóstico en todos los niveles de educación básica, con la participación de 3 mil 220 escuelas y 379 mil estudiantes. El titular del IHE y secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, destacó que tienen una visión humanista y su propósito es contar con información que permita tomar decisiones para mejorar aprendizajes.</t>
-  </si>
-  <si>
-    <t>El IHE implementó evaluaciones diagnósticas a 379 mil estudiantes en 3,220 planteles básicos para orientar la planeación docente y mejorar aprendizajes.</t>
-  </si>
-  <si>
-    <t>Instituto Hidalguense de Educación, Secretaría de Educación Pública de Hidalgo</t>
-  </si>
-  <si>
-    <t>ITESHU fortalece su oferta de posgrados</t>
-  </si>
-  <si>
-    <t>El Instituto Tecnológico Superior de Huichapan (ITESHU) inició formalmente el ciclo escolar con una matrícula presencial superior a 2 mil 200 alumnos. La institución presentó su nueva Maestría en Desarrollo Regional e Innovación Tecnológica, sumando dos programas de maestría. El nuevo programa busca ofrecer mayores opciones de especialización y formación alineadas con las necesidades del entorno productivo de la región. La oferta académica del ITESHU incluye carreras en Arquitectura y Gastronomía, así como las ingenierías en Energías Renovables, Gestión Empresarial, Innovación Agrícola Sustentable, Sistemas y Mecatrónica. En el nivel de posgrado, además de la nueva Maestría en Desarrollo Regional e Innovación Tecnológica, ofrece también la Maestría en Ingeniería Mecatrónica.</t>
-  </si>
-  <si>
-    <t>Huichapan</t>
-  </si>
-  <si>
-    <t>Oferta educativa</t>
-  </si>
-  <si>
-    <t>El ITESHU dio inicio al nuevo ciclo escolar para más de 2,200 alumnos presenciales, presentando su nueva Maestría en Desarrollo Regional e Innovación Tecnológica.</t>
-  </si>
-  <si>
-    <t>Instituto Tecnológico Superior de Huichapan</t>
-  </si>
-  <si>
-    <t>Despresurizan penal de Mixquiahuala</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH) trasladó a 174 personas privadas de la libertad del Cereso de Mixquiahuala al penal de Tula de Allende, debido a la sobrepoblación que registra el centro penitenciario y a recomendaciones de Protección Civil por filtraciones de agua en el área de dormitorios. De acuerdo con una tarjeta informativa emitida por la dependencia, el operativo se realizó durante la madrugada del viernes en las instalaciones del Centro de Reinserción Social de Mixquiahuala de Juárez. El traslado se efectuó hacia el nuevo módulo de dormitorios del Cereso de Tula de Allende. La SSPH informó que el penal ubicado en Mixquiahuala tiene una capacidad para 70 personas, pero antes del operativo albergaba a 191 internos, por lo que presentaba una ocupación considerablemente superior a su capacidad. Ante esta situación, se trasladó a 174 integrantes de la población varonil a las nuevas instalaciones de Tula.</t>
-  </si>
-  <si>
-    <t>La SSPH trasladó a 174 internos del Cereso de Mixquiahuala a las nuevas instalaciones de Tula de Allende para abatir el hacinamiento y prevenir riesgos pluviales en dormitorios.</t>
-  </si>
-  <si>
-    <t>IAAMEH celebra a personas mayores</t>
-  </si>
-  <si>
-    <t>En el marco del Día Nacional de las Personas Mayores, que se conmemora cada 28 de agosto, el Instituto para la Atención de las y los Adultos Mayores del Estado de Hidalgo (IAAMEH) realizó festejos en distintos municipios de la entidad para quienes acuden a los Centros Gerontológicos Integrales (CGI) y Casas de Día. Las actividades tuvieron como propósito promover la convivencia, el esparcimiento y el bienestar integral de las personas mayores.</t>
-  </si>
-  <si>
-    <t>Atención a adultos mayores</t>
-  </si>
-  <si>
-    <t>El IAAMEH organizó diversas jornadas de festejo y convivencia en la entidad para conmemorar el Día Nacional de las Personas Mayores en sus centros gerontológicos.</t>
-  </si>
-  <si>
-    <t>Instituto para la Atención de las y los Adultos Mayores del Estado de Hidalgo (IAAMEH)</t>
-  </si>
-  <si>
-    <t>Documentan los saberes de las cocineras tradicionales</t>
-  </si>
-  <si>
-    <t>En las instalaciones del Centro Cultural del Ferrocarril se llevó a cabo la presentación de “Memoria Culinaria: vestigios ancestrales de la cocina hidalguense”, una exposición fotográfica de la creadora visual Jessica Mejía que tiene por objetivo reconocer las historias, saberes de preparación y tradiciones ancestrales de las cocineras del municipio de Santiago de Anaya. El proyecto reúne diversos retratos y testimonios orales de mujeres locales para enaltecer la gastronomía como parte viva de nuestra identidad cultural y patrimonio hidalguense.</t>
-  </si>
-  <si>
-    <t>Santiago de Anaya</t>
-  </si>
-  <si>
-    <t>Cocineras Tradicionales</t>
-  </si>
-  <si>
-    <t>Se inauguró en Pachuca la muestra fotográfica de Jessica Mejía titulada 'Memoria Culinaria', dedicada a recopilar el legado y saberes tradicionales de las cocineras de Santiago de Anaya.</t>
-  </si>
-  <si>
-    <t>Portada</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura de Hidalgo, Centro Cultural del Ferrocarril</t>
-  </si>
-  <si>
-    <t>Jessica Mejía</t>
-  </si>
-  <si>
-    <t>Suicidio se concreta más en hombres, indica especialista</t>
-  </si>
-  <si>
-    <t>Durante el desarrollo del Panel Internacional de Salud Mental y Prevención del Suicidio, José Joaquín Ceballos, presidente de la Coalición Nacional de Prevención del Suicidio (Conapresu), informó que de cada 10 hombres que atentan contra su vida, ocho consuman el hecho, mientras que en las mujeres el índice alcanza siete de cada 10, lo que devela una mayor letalidad en el género masculino. El especialista aclaró que la conducta suicida es un proceso de ideación cognitivo que abarca varias etapas y no un acto repentino. En su mensaje de apertura, el titular de la PIBEH, Francisco Martínez Gómez, destacó que la salud mental es un eje prioritario de atención preventiva.</t>
-  </si>
-  <si>
-    <t>Prevención del suicidio</t>
-  </si>
-  <si>
-    <t>Durante el Panel de Salud Mental se reveló que el 80% de los hombres que atentan contra su vida logran consumar el suicidio, superando la tasa de letalidad femenina.</t>
-  </si>
-  <si>
-    <t>Socorro Ávila</t>
-  </si>
-  <si>
-    <t>Policía Industrial Bancaria del Estado de Hidalgo (PIBEH), Sistema DIF Hidalgo, Comisión de Derechos Humanos del Estado de Hidalgo (CDHEH), Coalición Nacional de Prevención del Suicidio (Conapresu)</t>
-  </si>
-  <si>
-    <t>José Joaquín Ceballos, Francisco Martínez Gómez, Edda Vite Ramos, Ana Karen Parra Bonilla, Arturo Gómez Canales</t>
-  </si>
-  <si>
-    <t>El Chico impulsará oferta turística con el nuevo centro Los Lavaderos</t>
-  </si>
-  <si>
-    <t>Con el propósito de detonar la infraestructura turística y el comercio artesanal de uno de los Pueblos Mágicos más representativos del estado, la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (SIPDUS) emitió la licitación pública EO-SIPDUS-N113-2026 para construir el Centro Turístico Multifuncional Los Lavaderos. La obra se realizará en el centro histórico de Mineral del Chico, contemplando fachadas de acceso, techumbres, vestidores, muro de contención, instalación eléctrica, gradas y nivelación de terraplenes. El fallo será emitido el 11 de septiembre, programándose el inicio para el 2 de octubre de 2026.</t>
-  </si>
-  <si>
-    <t>Mineral del Chico</t>
-  </si>
-  <si>
-    <t>Infraestructura Turística</t>
-  </si>
-  <si>
-    <t>La SIPDUS emitió convocatoria pública para la edificación del nuevo Centro Turístico Los Lavaderos en el centro de Mineral del Chico, proyectando iniciar obras el 2 de octubre.</t>
-  </si>
-  <si>
-    <t>Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (SIPDUS)</t>
-  </si>
-  <si>
-    <t>Con infraestructura, Hidalgo refuerza seguridad y atención de emergencias</t>
-  </si>
-  <si>
-    <t>En menos de un mes, el estado de Hidalgo puso en marcha dos nuevas instalaciones tácticas para el auxilio de emergencias y la seguridad civil en Pachuca. La primera corresponde a la nueva Estación de Bomberos “José María Morelos y Pavón” y oficinas de Protección Civil estatal, cuya inversión representó 91 millones de pesos con dormitorios, sala de juntas, cabina de despacho electrónico y equipo tecnológico. Además, se incorporaron 19 elementos al cuerpo de bomberos. La segunda corresponde al nuevo Cuartel de la Policía Estatal en Cubitos, edificado en un terreno de 1,550 metros cuadrados con inversión de 22 mdp, evento donde además 116 nuevos cadetes rindieron protesta.</t>
-  </si>
-  <si>
-    <t>Fortalecimiento Policiaco</t>
-  </si>
-  <si>
-    <t>El gobierno estatal inauguró la nueva estación metropolitana de Bomberos (91 mdp) y el Cuartel de Policía en la colonia Cubitos (22 mdp), sumando 116 policías graduados.</t>
-  </si>
-  <si>
-    <t>Benjamín H. V.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública del Estado de Hidalgo, Subsecretaría de Protección Civil del Estado, Cuerpo de Bomberos de Hidalgo, Instituto de Formación Profesional</t>
-  </si>
-  <si>
-    <t>Gusano barrenador suma 83 casos activos en 32 municipios</t>
-  </si>
-  <si>
-    <t>El Servicio Nacional de Sanidad, Inocuidad y Calidad Agroalimentaria (Senasica) confirmó que el estado de Hidalgo registra 83 casos activos del parásito del gusano barrenador (larva que infesta heridas abiertas en animales) distribuidos en 32 municipios. La propagación coloca a la entidad en el noveno lugar nacional de contagios. Del total de brotes vigentes, el municipio de Eloxochitlán encabeza el volumen de contagios con 11 casos, seguido por Huehuetla con ocho. Asimismo, por especie, el ganado bovino encabeza el daño con 33 casos activos, mientras que el sector de mascotas caninas reporta un total de 27 casos activos.</t>
-  </si>
-  <si>
-    <t>Gusano barrenador</t>
-  </si>
-  <si>
-    <t>La Senasica confirmó que Hidalgo sumó 83 casos activos de gusano barrenador en 32 municipios, siendo Eloxochitlán la demarcación con la mayor incidencia.</t>
-  </si>
-  <si>
-    <t>Saderh</t>
-  </si>
-  <si>
-    <t>Servicio Nacional de Sanidad, Inocuidad y Calidad Agroalimentaria (Senasica)</t>
-  </si>
-  <si>
-    <t>Formalizan comodato de predio para nuevo CEMSaD en Progreso</t>
-  </si>
-  <si>
-    <t>El Colegio de Bachilleres del Estado de Hidalgo (Cobaeh) y la Dirección General de Patrimonio Inmobiliario del Gobierno del Estado de Hidalgo formalizaron el comodato de un predio destinado al CEMSaD Progreso de Obregón. El espacio cuenta con una extensión de 4 mil 400 metros cuadrados y contempla la construcción de aulas, oficinas administrativas, talleres, sanitarios y áreas deportivas. En coordinación con el Instituto Hidalguense de la Infraestructura Física Educativa (INHIFE), se realizó una valoración técnica del predio, en la que se determinó que cumple con las condiciones requeridas para el desarrollo del proyecto, y se prevé iniciar en septiembre la elaboración del proyecto de construcción. Este nuevo espacio busca beneficiar a aproximadamente 200 estudiantes del CEMSaD Progreso de Obregón, asimismo, busca ampliar la capacidad de atención y favorecer el ingreso de jóvenes egresados de secundaria de la región. El acto protocolario se realizó en las instalaciones de la Subsecretaría de Educación Media Superior y Superior de la SEPH y estuvo encabezado por el subsecretario Daniel Fragoso Torres, en compañía del titular del Cobaeh, Rubén López Valdez, y la diputada por el Distrito VII de Mixquiahuala, Diana Rangel Zúñiga, quienes signaron el documento correspondiente, en presencia de autoridades educativas y representantes del Comité de Madres y Padres de Familia.</t>
-  </si>
-  <si>
-    <t>Progreso</t>
-  </si>
-  <si>
-    <t>Comodato</t>
-  </si>
-  <si>
-    <t>El Cobaeh y el Gobierno de Hidalgo formalizaron la cesión en comodato de un predio de 4,400 metros cuadrados para edificar las nuevas instalaciones del CEMSaD Progreso de Obregón, beneficiando a 200 alumnos.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Colegio de Bachilleres del Estado de Hidalgo, Instituto Hidalguense de la Infraestructura Física Educativa, Dirección General de Patrimonio Inmobiliario</t>
-  </si>
-  <si>
-    <t>Daniel Fragoso Torres, Rubén López Valdez, Diana Rangel Zúñiga</t>
-  </si>
-  <si>
-    <t>Hidalgo registró 409 defunciones fetales en 2025: INEGI</t>
-  </si>
-  <si>
-    <t>Durante 2025, Hidalgo registró 409 casos de Estadísticas de Defunciones Fetales (EDF), de acuerdo con datos publicados por el Instituto Nacional de Estadística y Geografía (INEGI). Del total estatal, 283 casos fueron captados mediante el procedimiento tradicional, mientras que 126 corresponden a casos complementarios captados por la Secretaría de Salud e incorporados en formato digital. A nivel nacional se contabilizaron 20 mil 74 defunciones fetales, por lo que Hidalgo se ubicó en el lugar 14 entre las entidades con mayor número de registros, exactamente en la media nacional. Las entidades con más defunciones fetales fueron el Estado de México con 3 mil 823 casos; Ciudad de México con 2 mil 68; Guanajuato con mil 391; Jalisco con mil 229 y Puebla con mil 108 casos. Las defunciones fetales se registraron principalmente en unidades de la Secretaría de Salud, el IMSS e IMSS-Bienestar, seguidas de las unidades médicas privadas. Un caso de muerte materna está en investigación.</t>
-  </si>
-  <si>
-    <t>Salud materna</t>
-  </si>
-  <si>
-    <t>El INEGI reportó que Hidalgo registró 409 defunciones fetales en 2025, ubicándose en la media nacional, ocurriendo la mayoría de los decesos en la Secretaría de Salud, IMSS e IMSS-Bienestar.</t>
-  </si>
-  <si>
-    <t>Secretaría de Salud de Hidalgo, Instituto Mexicano del Seguro Social, IMSS-Bienestar</t>
-  </si>
-  <si>
-    <t>En servicio de hospedaje se concentran las principales quejas turísticas en Mineral del Chico</t>
-  </si>
-  <si>
-    <t>En servicio de hospedaje se concentran las principales quejas turísticas en Mineral del Chico y registran un incremento, de acuerdo con información de la Secretaría de Turismo municipal, ante la presencia de establecimientos que operan sin licencia o sin inscripción en el Registro Nacional de Turismo (RNT). Francisco Javier Olmos García, secretario de Turismo de Mineral del Chico, explicó que esta situación se presenta principalmente con espacios que se promocionan mediante plataformas como Airbnb, así como con personas que adaptan habitaciones o áreas de sus viviendas para rentarlas a visitantes sin realizar los trámites correspondientes. Ante este escenario, la autoridad municipal mantiene una campaña dirigida a los prestadores de servicios para que regularicen sus establecimientos, tramiten la licencia y el RNT, además de acceder a capacitación para mejorar la atención a los turistas. La presencia de estos sitios también dificulta determinar con exactitud cuántos espacios de alojamiento funcionan actualmente en el municipio. Hasta el año pasado, las autoridades tenían registradas 285 cabañas y 290 cuartos de hotel; no obstante, Olmos García señaló que esta cifra puede modificarse debido a los inmuebles que ofrecen el servicio de manera informal. El funcionario añadió que la dependencia también participa en el ordenamiento territorial turístico, en coordinación con autoridades estatales, para la vigilancia y regulación.</t>
-  </si>
-  <si>
-    <t>Airbnb</t>
-  </si>
-  <si>
-    <t>La Secretaría de Turismo de Mineral del Chico reportó un repunte de quejas turísticas dirigidas a servicios informales de alojamiento tipo Airbnb que operan sin licencias ni RNT, por lo que promueve su regularización.</t>
-  </si>
-  <si>
     <t>Berenice Gamboa</t>
   </si>
   <si>
-    <t>Secretaría de Turismo de Mineral del Chico, Secretaría de Turismo del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Francisco Javier Olmos García</t>
-  </si>
-  <si>
-    <t>Alrededor de 650 mil estudiantes iniciarán ciclo escolar 2026-2027</t>
-  </si>
-  <si>
-    <t>Este lunes 31 de agosto, alrededor de 650 mil estudiantes de nivel básico regresan a las aulas en más de 7 mil planteles de Hidalgo, como parte del inicio del ciclo escolar 2026-2027, indicó el secretario de Educación en la entidad, Natividad Castrejón Valdez. El arranque protocolario de clases se realizará en la Escuela Secundaria General 2 de Pachuca, donde se llevará a cabo la entrega simbólica de útiles y uniformes escolares. El titular de la SEPH adelantó que realizará giras regionales de inauguración simbólica e informó que el 100 por ciento del nivel básico tiene cobertura, buscando alternativas de absorción de capacidad en planteles de alta demanda poblacional como Tizayuca y Atotonilco de Tula.</t>
-  </si>
-  <si>
     <t>Regreso A Clases</t>
   </si>
   <si>
-    <t>Alrededor de 650 mil alumnos de nivel básico en Hidalgo inician clases de la mano de la SEPH, realizándose el protocolo escolar en Pachuca.</t>
-  </si>
-  <si>
     <t>Secretaría de Educación Pública de Hidalgo, Instituto Hidalguense de Educación</t>
   </si>
   <si>
-    <t>Incumplimiento de acuerdos en obra afecta a locatarios en Plaza Perisur</t>
-  </si>
-  <si>
-    <t>Locatarios de la plaza Perisur, en Pachuca, padecen un mes complicado en ventas, pérdida de clientes y caos vehicular, derivado del incumplimiento de acuerdos por parte de la Secretaría de Infraestructura Pública y Desarrollo Urbano (Sipdus), relacionados con los trabajos de rehabilitación del bulevar Felipe Ángeles a la altura de ese espacio comercial. Denunciaron que desde el inicio de las labores el pasado 10 de agosto han registrado caídas de hasta el 70% y 90% en sus ventas por la inhabilitación de accesos sin previo aviso, afectando a restaurantes, papelerías, zapaterías, gimnasios, mueblerías y laboratorios, vulnerando la subsistencia de los comercios por la falta de señalética vial de la dependencia.</t>
-  </si>
-  <si>
-    <t>Inconformidad por obra</t>
-  </si>
-  <si>
-    <t>Locatarios de Plaza Perisur acusan caídas de hasta el 90% en ventas por el cierre de accesos de la obra de rehabilitación vial de la Sipdus.</t>
-  </si>
-  <si>
-    <t>Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible, Ayuntamiento de Pachuca</t>
-  </si>
-  <si>
-    <t>Miguel Islas, Lili N.</t>
-  </si>
-  <si>
-    <t>Un viacrucis, el tráfico de norte a sur</t>
-  </si>
-  <si>
-    <t>Cientos de automovilistas de Pachuca se enfrentan diariamente a un severo viacrucis vial al intentar regresar a sus hogares por la tarde, principalmente en el bulevar Felipe Ángeles con dirección a la salida sur. El trayecto, que anteriormente demoraba 20 minutos, ahora requiere casi dos horas debido al congestionamiento generado por las obras de rehabilitación de la Sipdus a la altura de Las Torres y Plaza de Toros. Al transitar a menos de 10 kilómetros por hora, la desesperación aumenta entre conductores que además ya no cuentan con la opción de invadir el carril exclusivo del Tuzobús debido a que las sanciones de cultura vial entraron en vigor con multas de hasta 3 mil 519 pesos.</t>
-  </si>
-  <si>
-    <t>Crónica</t>
-  </si>
-  <si>
-    <t>Vialidad En Mal Estado</t>
-  </si>
-  <si>
-    <t>Las obras de rehabilitación vial de la Sipdus en la salida sur de Pachuca provocan filas vehiculares kilométricas de hasta dos horas.</t>
-  </si>
-  <si>
-    <t>Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible, Secretaría de Educación Pública de Hidalgo, Sistema Integrado de Transporte Masivo de Hidalgo</t>
-  </si>
-  <si>
-    <t>“Ni uno más”, el clamor de familiares de desaparecidos</t>
-  </si>
-  <si>
-    <t>Con pancartas, mantas, fotografías y consignas, colectivos y familiares de personas desaparecidas marcharon en Pachuca en conmemoración del Día Internacional de las Víctimas de Desapariciones Forzadas. La movilización partió del Reloj Monumental hacia las calles aledañas del centro de la ciudad para visibilizar sus casos y reclamar a las autoridades la falta de avances en las investigaciones penales. Los manifestantes exigieron que la comisión de búsqueda y la procuraduría agilicen las carpetas que, en casos históricos de larga data, acumulan hasta 20 años de rezago.</t>
-  </si>
-  <si>
     <t>Desapariciones</t>
   </si>
   <si>
-    <t>Familias de desaparecidos marcharon del Reloj de Pachuca a fin de exigir que la fiscalía y la comisión de búsqueda desahoguen indagatorias.</t>
-  </si>
-  <si>
-    <t>Procuraduría General de Justicia de Hidalgo, Comisión de Búsqueda de Personas de Hidalgo</t>
-  </si>
-  <si>
     <t>José Francisco García Reyes</t>
   </si>
   <si>
-    <t>A 31 años del caso, buscan el paradero de Enriqueta</t>
-  </si>
-  <si>
-    <t>La familia Dimas Serrano mantiene intacta la búsqueda y esperanza de localizar a Enriqueta Dimas Serrano, quien desapareció a los 31 años de edad el 8 de junio de 1995 tras salir de su domicilio en la colonia Morelos, de Pachuca, para encontrarse con su expareja. Celia Dimas, hermana de la víctima, reprochó de forma severa que la procuraduría estatal se niegue a establecer líneas activas de investigación argumentando el paso del tiempo, provocando que la familia afronte la parálisis del caso por su propia cuenta sin apoyo gubernamental.</t>
-  </si>
-  <si>
     <t>Búsqueda de personas</t>
   </si>
   <si>
-    <t>Familiares de Enriqueta Dimas reprochan abandono institucional en la búsqueda de la mujer desaparecida en Pachuca hace 31 años.</t>
-  </si>
-  <si>
-    <t>Procuraduría General de Justicia del Estado de Hidalgo, Comisión de Búsqueda de Personas del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Enriqueta Dimas Serrano, Celia Dimas Serrano</t>
-  </si>
-  <si>
-    <t>Anega lluvia aulas de primaria en Huehuetla</t>
-  </si>
-  <si>
-    <t>Una lluvia torrencial anegó la escuela primaria Benito Juárez del municipio de Huehuetla, afectando gravemente un módulo de cuatro aulas que ya se encontraba deteriorado tras los efectos de la vaguada monzónica de octubre de 2025. Padres de familia, directivos y el comité de la escuela expresaron su molestia debido a que el Inhife se ha negado a demoler y elevar el terreno del módulo dañado alegando falta de presupuesto, forzando a reprogramar el ciclo escolar para que los alumnos de estos grupos inicien clases de manera remota/a distancia.</t>
-  </si>
-  <si>
     <t>Huehuetla</t>
   </si>
   <si>
     <t>Afectaciones Por Lluvias</t>
   </si>
   <si>
-    <t>Fuertes precipitaciones inundaron cuatro salones en la primaria de Huehuetla, obligando a los alumnos a tomar clases a distancia.</t>
-  </si>
-  <si>
     <t>María Antonieta Islas</t>
   </si>
   <si>
-    <t>Instituto Hidalguense de la Infraestructura Física Educativa, Dirección del plantel</t>
-  </si>
-  <si>
-    <t>Complicado, el inicio de clases en Tianguistengo</t>
-  </si>
-  <si>
-    <t>El ciclo escolar 2026-2027 iniciará bajo condiciones complejas para los estudiantes de la comunidad de Tlacolula, en Tianguistengo, debido a que las cuatro instituciones de educación que resultaron siniestradas por la vaguada monzónica del año anterior continúan en fase de reconstrucción y rehabilitación. Alrededor de 40 alumnos de nivel primaria tomarán cursos en una casa particular adaptada y prestada por vecinos de la zona, mientras que el nivel preescolar ocupará de forma provisional una estructura escolar antigua que resistió las lluvias, esperándose que el INHIFE culmine las obras en los próximos tres meses.</t>
-  </si>
-  <si>
     <t>Tianguistengo</t>
   </si>
   <si>
     <t>Reconstrucción de escuela</t>
   </si>
   <si>
-    <t>Alumnos de cuatro escuelas dañadas por lluvias en Tianguistengo inician clases en viviendas adaptadas por la parálisis de obras.</t>
-  </si>
-  <si>
     <t>Martha Sáenz</t>
   </si>
   <si>
-    <t>Instituto Hidalguense de la Infraestructura Física Educativa, Secretaría de Educación Pública de Hidalgo</t>
-  </si>
-  <si>
-    <t>Bonifacio Ramos Villegas</t>
-  </si>
-  <si>
-    <t>Iniciará Aquiles Serdán su ciclo escolar en línea</t>
-  </si>
-  <si>
-    <t>La dirección de la escuela primaria Aquiles Serdán en Tulancingo, una de las instituciones educativas básicas con mayor antigüedad del municipio, informó que las clases del nuevo ciclo escolar 2026-2027 serán impartidas de forma virtual para sus 410 alumnos. El plantel tomó esta determinación tras un dictamen de planeación de la SEPH derivado del inicio de los trabajos de demolición y edificación de una nueva estructura física, debido a que seis de sus 14 aulas presentaban un severo desgaste de cimentación agudizado por lluvias previas. La decisión generó molestia entre los padres de familia.</t>
-  </si>
-  <si>
-    <t>Educación en línea</t>
-  </si>
-  <si>
-    <t>La primaria Aquiles Serdán en Tulancingo iniciará su ciclo en formato virtual debido a las obras de demolición de aulas dañadas.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública del Estado de Hidalgo, Dirección de la escuela primaria Aquiles Serdán</t>
-  </si>
-  <si>
-    <t>María de la Luz Vargas</t>
-  </si>
-  <si>
-    <t>Aquí los Políticos: Regreso a clases, carrera FUL, y robo de agua</t>
-  </si>
-  <si>
-    <t>Columna de trascendidos políticos de El Sol de Hidalgo que aborda: 1) El inicio del ciclo escolar 2026-2027 que moviliza a más de medio millón de estudiantes de nivel básico y provoca severas congestiones viales en Pachuca. 2) Las expectativas de la 21a edición de la Carrera Atlética de la UAEH que se celebrará el domingo 6 de septiembre en el marco de la FUL. 3) El incremento del robo de agua o tomas clandestinas en Mineral de la Reforma detectado por el personal de la Caasim.</t>
-  </si>
-  <si>
-    <t>Trascendidos que analizan el caos vial del regreso a clases en Pachuca, la carrera de la FUL de la UAEH y el robo de agua en Mineral de la Reforma.</t>
-  </si>
-  <si>
-    <t>Aquí los políticos</t>
-  </si>
-  <si>
-    <t>Sipdus, UAEH, Caasim, Ayuntamiento de Pachuca, Ayuntamiento de Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>Andrés Velázquez, Julio Menchaca</t>
-  </si>
-  <si>
-    <t>Exigen localizar a sus familiares</t>
-  </si>
-  <si>
-    <t>Integrantes de colectivos y familiares de personas no localizadas realizaron una manifestación pacífica en Pachuca para exigir la localización y avances reales en las carpetas de investigación por desapariciones forzadas en la entidad. Colectivos denunciaron la falta de apoyo de agentes ministeriales y lentitud burocrática, citando casos como el del joven Regino Cano Bautista, desaparecido en 2025 en Tepetitlán. Exhortaron a la Comisión de Búsqueda del Estado de Hidalgo a agilizar las diligencias de rastreo.</t>
-  </si>
-  <si>
-    <t>Familiares de desaparecidos marcharon en Pachuca para denunciar impunidad y exigir a la Comisión de Búsqueda estatal y fiscalías acelerar rastreos.</t>
-  </si>
-  <si>
     <t>Segobh</t>
   </si>
   <si>
-    <t>Segobh, CBPEH, PGJEH</t>
-  </si>
-  <si>
-    <t>Regino Cano Bautista, José Francisco García</t>
-  </si>
-  <si>
-    <t>Regresarán a clases 569 mil estudiantes</t>
-  </si>
-  <si>
-    <t>Un total de 569 mil estudiantes de educación básica en Hidalgo inician clases este lunes para el ciclo escolar 2026-2027. El secretario de Educación, Natividad Castrejón, detalló que se distribuyeron de forma oportuna casi 4 millones de libros de texto gratuitos de la Nueva Escuela Mexicana y 489 mil paquetes de útiles escolares. El regreso escolar contará con un estricto operativo de vialidad de la policía para evitar el congestionamiento en las zonas escolares.</t>
-  </si>
-  <si>
-    <t>La SEPH reportó el regreso a clases de 569 mil alumnos de educación básica en Hidalgo, distribuyéndose útiles escolares y libros de texto.</t>
-  </si>
-  <si>
     <t>Blanca Soriano</t>
   </si>
   <si>
-    <t>Bajo Reserva: Sin debut y con despedida / Labor que habla por sí misma / Extrema promoción personal</t>
-  </si>
-  <si>
-    <t>Trascendidos locales que analizan tres temas de la política hidalguense: 1) El IEEH decidirá el retiro del registro al Partido Espacio Hidalgo de Esperanza Flores Rojo por falta de afiliados antes de debutar en 2027. 2) El exitoso e impecable segundo informe de actividades del diputado local Andrés Velázquez Vázquez. 3) El proselitismo anticipado del director de la Comisión de Agua de Tulancingo, Enzo Balderas Castro, ante el dirigente Marco Antonio Rico.</t>
-  </si>
-  <si>
-    <t>Trascendidos que exponen la inminente pérdida de registro de Espacio Hidalgo, el buen balance del informe de Andrés Velázquez y el proselitismo anticipado del director de agua de Tulancingo.</t>
-  </si>
-  <si>
-    <t>Bajo Reserva</t>
-  </si>
-  <si>
-    <t>Instituto Estatal Electoral de Hidalgo, Congreso del Estado de Hidalgo, Comisión de Agua y Alcantarillado de Tulancingo, Morena</t>
-  </si>
-  <si>
-    <t>Esperanza Flores Rojo, Andrés Velázquez Vázquez, Enzo Balderas Castro, Marco Antonio Rico Mercado</t>
-  </si>
-  <si>
-    <t>En riesgo por rocas, 26 barrios y colonias de Pachuca, alertan</t>
-  </si>
-  <si>
-    <t>Al menos 26 barrios y colonias de Pachuca enfrentan problemas de desprendimiento de bloques de rocas o hundimientos por antiguas minas y la extracción de agua. El Atlas de Riesgo estatal identificó 34 casas en riesgo alto en El Porvenir, Nueva Estrella, Barrio San Nicolás, La Alcantarilla y El Tezontle. Asimismo, se reportan 13 zonas de peligro alto de hundimientos como El Arbolito, Camelia, Xotol, San Rafael, El Cristo, El Lobo, Buenos Aires, Cubitos y El Túnel.</t>
-  </si>
-  <si>
-    <t>Atlas de Riesgos</t>
-  </si>
-  <si>
-    <t>El Atlas de Riesgo de Hidalgo identificó graves peligros geológicos de hundimiento e inestabilidad de laderas que amenazan a 26 barrios históricos y viviendas de Pachuca.</t>
-  </si>
-  <si>
-    <t>Ricardo Calleja</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Ayuntamiento de Pachuca</t>
-  </si>
-  <si>
-    <t>Suman más de 13 mil tomas clandestinas de agua clausuradas</t>
-  </si>
-  <si>
-    <t>El titular de la Caasim, Juan Evel Chávez Trovamala, informó que el organismo ha clausurado un total de 13 mil 794 tomas clandestinas de agua potable en lo que va del año, principalmente en Pachuca, Mineral de la Reforma y Zempoala. Asimismo, detalló que iniciaron 176 procesos legales contra usuarios reincidentes, que abarcan domicilios particulares y empresas, incluyendo algunos clubes deportivos.</t>
-  </si>
-  <si>
-    <t>Tomas clandestinas</t>
-  </si>
-  <si>
-    <t>La Caasim reportó la inmovilización de 13,794 conexiones irregulares de agua de la red pública e impulsó demandas contra 176 infractores por reincidencia.</t>
-  </si>
-  <si>
-    <t>Comisión de Agua y Alcantarillado de Sistemas Intermunicipales</t>
-  </si>
-  <si>
-    <t>Juan Evel Chávez Trovamala</t>
-  </si>
-  <si>
-    <t>A 10 meses, de la vaguada, cinco desaparecidos por la vaguada</t>
-  </si>
-  <si>
-    <t>A casi un año del impacto de la vaguada monzónica en el estado de Hidalgo en octubre de 2025, cinco personas originarias del municipio de Tianguistengo continúan desaparecidas, informó el titular de la Comisión de Búsqueda de Personas del Estado de Hidalgo (CBPEH), José Francisco García Reyes. El funcionario detalló que permanecen activos cuatro reportes de Chapula y uno de Tlacolula.</t>
-  </si>
-  <si>
-    <t>La Comisión de Búsqueda estatal reportó que a 10 meses de las contingencias pluviales de 2025, cinco personas siguen desaparecidas en comunidades de Tianguistengo.</t>
-  </si>
-  <si>
     <t>Comisión de Búsqueda de Personas del Estado de Hidalgo</t>
   </si>
   <si>
-    <t>Saderh entrega 5.3 mdp en apoyos para 600 familias</t>
-  </si>
-  <si>
-    <t>La Saderh de Hidalgo destinó un apoyo económico y en especie de 5 millones 347 mil 252 pesos para favorecer la productividad de 618 personas y productores locales del campo. El titular Napoleón González Pérez encabezó la entrega en Tolcayuca, distribuyendo semillas de avena, cebada, maíz, vientres ovinos, porcinos, aves de doble propósito y equipamiento a productores de Tolcayuca, Villa de Tezontepec, Zapotlán de Juárez y Tizayuca, con la presencia del alcalde Armando Zúñiga.</t>
-  </si>
-  <si>
-    <t>Tolcayuca</t>
-  </si>
-  <si>
-    <t>Apoyo Al Agro</t>
-  </si>
-  <si>
-    <t>La Saderh estatal entregó 5.3 mdp en paquetes agrícolas, semillas de temporal e insumos pecuarios para reactivar la soberanía productiva en el sur de Hidalgo.</t>
-  </si>
-  <si>
-    <t>Secretaría de Agricultura y Desarrollo Rural de Hidalgo, Ayuntamientos de Tolcayuca, Villa de Tezontepec, Zapotlán de Juárez, Tizayuca</t>
-  </si>
-  <si>
-    <t>Napoleón González Pérez, Armando Zúñiga Gutiérrez</t>
-  </si>
-  <si>
-    <t>Regresan a clases 569 mil alumnos de nivel básico</t>
-  </si>
-  <si>
-    <t>Este lunes inician el ciclo escolar 2026-2027 un total de 569 mil 987 estudiantes de educación básica de Hidalgo en 7 mil 866 planteles de la entidad. La SEPH informó que desde el primer día se distribuyen de forma gratuita 3 millones 958 mil 230 libros de texto y 488 mil 977 paquetes de útiles escolares, mientras que los uniformes y calzado (475 mil 14 de cada uno) se entregarán gradualmente.</t>
-  </si>
-  <si>
-    <t>La SEPH reportó el reinicio escolar para 569 mil alumnos de nivel básico, coordinando la dispersión inicial de libros de texto, útiles, uniformes y calzado escolar.</t>
-  </si>
-  <si>
-    <t>Canalizan a menores por falta de lugar en escuelas, acusan padres</t>
-  </si>
-  <si>
-    <t>Padres de familia de los fraccionamientos Héroes de Tizayuca y Fuentes de Tizayuca acusaron que la falta de cobertura de espacios en escuelas de la zona ha provocado que decenas de niños sean canalizados a escuelas en otras zonas lejanas del municipio. Las familias reclamaron que el cupo opera al límite de su capacidad debido al aumento demográfico, estimando que unos 300 menores se quedaron sin cupo local.</t>
-  </si>
-  <si>
     <t>Quejas padres de familia</t>
   </si>
   <si>
-    <t>Padres de familia protestaron en Tizayuca ante la saturación de los centros escolares locales y el traslado forzoso de alumnos hacia escuelas distantes.</t>
-  </si>
-  <si>
     <t>Javier Quezada</t>
   </si>
   <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Dirección escolar de Tizayuca</t>
-  </si>
-  <si>
-    <t>Nohemí N</t>
-  </si>
-  <si>
-    <t>Balean auto y dejan paquete sospechoso, en Huejutla</t>
-  </si>
-  <si>
-    <t>Un ataque armado contra un vehículo Ford Fiesta blanco sin placas de circulación se registró en la calle Ricardo Flores Magón de la colonia Rojo Lugo, en Huejutla de Reyes. Los delincuentes realizaron nueve disparos contra la unidad y colocaron un paquete misterioso envuelto arriba del cofre. La agresión provocó la movilización de corporaciones policiales, el Ejército Mexicano y agentes periciales de la PGJEH para acordonar el área e integrar la carpeta de investigación.</t>
-  </si>
-  <si>
-    <t>Fuerzas militares y periciales resguardaron la colonia Rojo Lugo en Huejutla tras detonarse múltiples impactos contra un coche particular, dejando los agresores un paquete sospechoso.</t>
-  </si>
-  <si>
-    <t>Francisco Bautista</t>
-  </si>
-  <si>
-    <t>Procuraduría General de Justicia del Estado de Hidalgo, Secretaría de Seguridad Pública Municipal de Huejutla, Ejército Mexicano</t>
-  </si>
-  <si>
-    <t>Marchan familias buscadoras; exigen justicia, empatía y menor burocracia</t>
-  </si>
-  <si>
-    <t>En el marco del Día Internacional de las Víctimas de Desapariciones Forzadas, un grupo de aproximadamente 25 familias provenientes de municipios como Tula, Tlaxcoapan, Tetepango, Pachuca y Ajacuba marchó para exigir investigaciones más oportunas, mayor sensibilidad institucional y avances reales en la localización de sus seres queridos. Los familiares señalaron que los obstáculos burocráticos y los retrasos iniciales en las indagatorias —que en algunos casos alcanzan hasta cuatro o cinco días— vulneran el derecho de acceso a la justicia. El titular de la Comisión de Búsqueda de Personas del Estado de Hidalgo (CBPEH), José Francisco García Reyes, informó que al corte más reciente de 2026 la institución registra 315 reportes, de los cuales 310 personas han sido localizadas, aclarando que esta cifra incluye casos tanto actuales como de larga data.</t>
-  </si>
-  <si>
-    <t>Un grupo de 25 familias de personas desaparecidas marchó en Pachuca en el Día de las Víctimas de Desaparición Forzada para demandar celeridad procesal.</t>
-  </si>
-  <si>
-    <t>Comisión de Búsqueda de Personas del Estado de Hidalgo, Procuraduría General de Justicia del Estado de Hidalgo, Procuraduría de Protección de Niñas, Niños y Adolescentes</t>
-  </si>
-  <si>
-    <t>José Francisco García Reyes, Regino Cano Bautista</t>
-  </si>
-  <si>
-    <t>Cinco personas siguen sin aparecer tras la vaguada</t>
-  </si>
-  <si>
-    <t>A casi un año de las afectaciones provocadas por la vaguada monzónica de octubre de 2025, cinco personas continúan sin ser localizadas en Hidalgo, informó José Francisco García Reyes, titular de la Comisión de Búsqueda de Personas del Estado de Hidalgo (CBPEH). El funcionario detalló que las personas pendientes de localizar corresponden al municipio de Tianguistengo: cuatro son originarias de la comunidad de Chapula y una más de Tlacolula. Explicó que inicialmente se recibió un número importante de reportes debido a las condiciones de incomunicación de las lluvias, quedando en activo nueve de los cuales cuatro ya fueron ubicados.</t>
-  </si>
-  <si>
-    <t>A casi un año de la vaguada monzónica de 2025, cinco personas originarias de Tianguistengo continúan sin aparecer, manteniéndose los operativos fluviales.</t>
-  </si>
-  <si>
-    <t>Comisión de Búsqueda de Personas del Estado de Hidalgo, Protección Civil, Comisión Ejecutiva de Atención a Víctimas</t>
-  </si>
-  <si>
-    <t>Aumento de violencia escolar, por mayor cultura de denuncia: Castrejón</t>
-  </si>
-  <si>
-    <t>Durante el ciclo escolar 2025-2026 se registraron mil 381 reportes de violencia y situaciones de riesgo en escuelas de educación básica de Hidalgo, con corte al 21 de agosto de 2026, de acuerdo con información de la Secretaría de Educación Pública de Hidalgo (SEPH). El secretario de Educación Pública estatal, Natividad Castrejón Valdez, atribuyó el incremento a una mayor cultura de la denuncia y no necesariamente a un aumento de la violencia en las escuelas, destacando que Hidalgo cuenta con protocolos actualizados de prevención y atención de acoso, violencia física, psicológica y sexual.</t>
-  </si>
-  <si>
-    <t>La SEPH reportó mil 381 incidentes de violencia escolar en el ciclo 2025-2026, destacando que el alza responde al fomento de la cultura de denuncia.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Procuraduría de Protección de Niñas, Niños y Adolescentes, Procuraduría General de Justicia del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Regresan a clases 967 mil; casi la mitad recibe apoyo</t>
-  </si>
-  <si>
-    <t>Más de 967 mil estudiantes regresaron este lunes a las aulas en Hidalgo para iniciar el ciclo escolar 2026-2027, mientras que cerca de la mitad de los alumnos de primaria y secundaria reciben algún tipo de apoyo económico, además de útiles, uniformes, calzado y libros de texto gratuitos. El secretario de Educación Pública estatal, Natividad Castrejón Valdez, informó que en total 967 mil 397 estudiantes iniciaron actividades académicas en 8 mil 717 escuelas de los diferentes niveles y modalidades educativas.</t>
-  </si>
-  <si>
-    <t>Un total de 967 mil alumnos iniciaron clases en Hidalgo, reportando la SEPH la entrega masiva de libros, calzado, paquetes de útiles y uniformes gratuitos.</t>
-  </si>
-  <si>
     <t>Secretaría de Educación Pública de Hidalgo, Gobierno del Estado de Hidalgo</t>
   </si>
   <si>
-    <t>Avanzan 42 proyectos para integrar el catálogo nacional de turismo comunitario</t>
-  </si>
-  <si>
-    <t>De un total inicial de casi 300 propuestas, un filtro riguroso de evaluación redujo a 42 los proyectos de turismo comunitario en Hidalgo que continúan en la ruta para integrarse al catálogo nacional impulsado por autoridades federales y la Unesco. Así lo informó la secretaria de Turismo estatal, Elizabeth Quintanar Gómez, quien destacó el creciente interés de las comunidades por organizarse en torno a sus tradiciones y recursos naturales, promoviéndose grupos reducidos de entre dos y 12 personas.</t>
-  </si>
-  <si>
-    <t>Turismo Comunitario</t>
-  </si>
-  <si>
-    <t>La Secretaría de Turismo reportó que 42 propuestas locales de turismo comunitario continúan vigentes en las evaluaciones para formar parte de la colección de la Unesco.</t>
-  </si>
-  <si>
-    <t>Secretaría de Turismo del Estado de Hidalgo, Gobierno Federal, UNESCO</t>
-  </si>
-  <si>
-    <t>Elizabeth Quintanar Gómez</t>
-  </si>
-  <si>
-    <t>Entregan 5.3 mdp en apoyos para productores de Hidalgo</t>
-  </si>
-  <si>
-    <t>Como parte del compromiso del gobernador Julio Menchaca Salazar de acercar a la población y fortalecer el bienestar de las familias del campo, la Secretaría de Agricultura (Saderh) encabezada por Napoleón González Pérez, entregó apoyos por un monto de 5 millones 347 mil 252 pesos. Beneficiará a 618 personas de Tolcayuca, Villa de Tezontepec, Zapotlán de Juárez y Tizayuca, en insumos y herramientas. En Tolcayuca se distribuyeron semillas de avena, cebada, jitomate, maíz, equipamiento acuícola, ovinos, porcinos, aves de doble propósito y plantas de maguey.</t>
-  </si>
-  <si>
-    <t>La Saderh entregó apoyos por 5.3 mdp a 618 productores del campo de Tolcayuca, Villa de Tezontepec, Zapotlán y Tizayuca en semillas, vientres ovinos, porcinos y aves de doble propósito.</t>
-  </si>
-  <si>
-    <t>Secretaría de Agricultura y Desarrollo Rural de Hidalgo, Gobierno del Estado de Hidalgo, Ayuntamiento de Tolcayuca</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Napoleón González Pérez, Armando Zúñiga Gutiérrez</t>
-  </si>
-  <si>
-    <t>Advierten riesgos urbanos por Tren México-Pachuca</t>
-  </si>
-  <si>
-    <t>La Zona Metropolitana de Pachuca de Soto enfrenta riesgos por el crecimiento urbano acelerado y la expansión desordenada sobre zonas rurales, de conservación y de recarga hídrica, situación que podría agravarse con la puesta en marcha del Tren México-Pachuca, advierte el Programa Parcial de Desarrollo Urbano de Pachuca y Mineral de la Reforma. El tren representará una transformación en la configuración territorial de la región, al fortalecer la conexión de Pachuca con el Valle de México y modificar las condiciones de movilidad, accesibilidad e inversión. Sin embargo, sin planeación, el crecimiento habitacional podría incrementar la especulación del suelo.</t>
-  </si>
-  <si>
-    <t>El Programa Parcial de Desarrollo Urbano advierte que la puesta en marcha del Tren México-Pachuca podría agravar los riesgos de expansión urbana desordenada y especulación del suelo en la zona conurbada.</t>
-  </si>
-  <si>
-    <t>Unidad de Planeación y Prospectiva, Ayuntamiento de Pachuca, Ayuntamiento de Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>Un recorrido por la historia</t>
-  </si>
-  <si>
-    <t>La Galería Leo Acosta presenta "Huella de la historia. La comunidad China en México", exposición fotográfica que recorre la presencia y aportaciones de la comunidad china en el país, desde el siglo XIX, destacando su impacto cultural y de desarrollo.</t>
-  </si>
-  <si>
-    <t>Exposición Fotográfica</t>
-  </si>
-  <si>
-    <t>La Galería Leo Acosta de Pachuca inauguró la exposición fotográfica 'Huella de la historia. La comunidad China en México' para difundir las aportaciones de este sector social desde el siglo XIX.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura de Hidalgo, Galería Leo Acosta</t>
-  </si>
-  <si>
-    <t>Madres buscadoras piden respuestas en Pachuca</t>
-  </si>
-  <si>
-    <t>En el marco del Día Internacional de las Víctimas de Desaparición Forzada, integrantes del colectivo Madres Buscadoras de Hidalgo marcharon por las calles del Centro Histórico de Pachuca para visibilizar los casos de sus familiares desaparecidos y exigir a las autoridades que continúen las investigaciones. La agrupación reúne a familiares de personas desaparecidas en municipios como Tula, Tlaxcoapan, Tetepango, Mixquiahuala, Progreso, Ixmiquilpan, Pachuca, Zempoala, San Agustín Tlaxiaca, Ajacuba, Tepeapulco y Mineral de la Reforma. Entre los casos se encuentra el de Enriqueta Dimas Serrano, desaparecida el 8 de junio de 1995 en Pachuca; Gustavo Alberto de la Cruz (2007); José Antonio Jiménez Jiménez (21 de marzo de 2007); y Édgar Vázquez Gutiérrez (28 de noviembre de 2015).</t>
-  </si>
-  <si>
-    <t>El colectivo Madres Buscadoras de Hidalgo marchó en Pachuca en el Día Internacional de las Víctimas de Desaparición Forzada para visibilizar expedientes y exigir avances.</t>
-  </si>
-  <si>
-    <t>Comisión de Búsqueda de Personas del Estado de Hidalgo, Procuraduría General de Justicia del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Enriqueta Dimas Serrano, Gustavo Alberto de la Cruz, José Antonio Jiménez Jiménez, Édgar Vázquez Gutiérrez</t>
-  </si>
-  <si>
-    <t>Buscan a cinco tras vaguada 2025</t>
-  </si>
-  <si>
-    <t>A casi un año de las afectaciones provocadas por la vaguada monzónica en Hidalgo, cinco personas originarias de Tianguistengo permanecen sin localizar, informó el titular de la Comisión de Búsqueda de Personas del Estado, José Francisco García Reyes. De las cinco personas desaparecidas, cuatro son de la localidad de Chapula y una de Tlacolula. García Reyes explicó que se trató de restos óseos localizados en la zona afectada, a los que se les practican pruebas genéticas para establecer su identidad. Señaló que el número de reportes de personas desaparecidas en Tianguistengo, Yahualica, San Bartolo Tutotepec, Huehuetla, Tenango de Doria y Zacualtipán llegó en su momento a 22 personas fallecidas y 20 desaparecidas, además de más de 217 viviendas afectadas y 155 comunidades incomunicadas.</t>
-  </si>
-  <si>
-    <t>La Comisión de Búsqueda de Personas de Hidalgo efectúa peritajes de ADN a restos óseos para identificar a cinco desaparecidos de Tianguistengo tras el temporal de 2025.</t>
-  </si>
-  <si>
-    <t>Comisión de Búsqueda de Personas del Estado de Hidalgo, Dirección de Servicios Periciales</t>
-  </si>
-  <si>
-    <t>Muertes maternas llegan a seis en Hidalgo</t>
-  </si>
-  <si>
-    <t>Tras dos defunciones registradas de manera consecutiva, Hidalgo acumula seis muertes maternas hasta la semana epidemiológica 33 de 2026, con lo que igualó el número de casos registrados durante todo 2025, de acuerdo con el Informe Semanal de Notificación Inmediata de Muerte Materna de la Secretaría de Salud federal. De las seis muertes maternas, una ocurrió en el IMSS, dos en el IMSS-Bienestar, una en atención particular y dos fueron clasificadas en el apartado de sin atención. La Secretaría de Salud de Hidalgo (SSH) informó que cuatro de las seis defunciones ocurrieron en Zempoala, Tula de Allende, Tasquillo y Pacula. Al corte de la semana 32 se habían registrado cinco decesos, y en la semana 33 se contabilizaron 285 muertes maternas a nivel nacional.</t>
-  </si>
-  <si>
-    <t>Muerte Materna</t>
-  </si>
-  <si>
-    <t>Hidalgo suma seis muertes maternas al corte de la semana epidemiológica 33 de 2026, igualando los registros de 2025; la SSH reportó decesos en Zempoala, Tula, Tasquillo y Pacula.</t>
-  </si>
-  <si>
-    <t>Secretaría de Salud de Hidalgo, Instituto Mexicano del Seguro Social, IMSS-Bienestar, Secretaría de Salud Federal</t>
-  </si>
-  <si>
-    <t>Realizan marcha, ofrenda y misa a favor de personas desaparecidas</t>
-  </si>
-  <si>
-    <t>En el marco del Día Internacional de las Víctimas de Desapariciones Forzadas, en Pachuca se realizaron diversas actividades para exigir la aparición de las personas desaparecidas, entre ellas una marcha pacífica, la colocación de un tendedero con fichas de búsqueda y una misa en la Basílica Menor de Guadalupe oficiada por el arzobispo de Tulancingo. Las actividades fueron encabezadas por el Colectivo de Madres Buscadoras, cuyos integrantes, desde las 11:00 horas, recorrieron calles céntricas de Pachuca y llegaron a la explanada de la Plaza Independencia, donde pasaron lista de las personas desaparecidas y exigieron a las autoridades la localización y aparición de sus familiares. El señor Regino Cano Bautista, integrante de la organización y padre buscador, señaló que el colectivo se formó a raíz de la necesidad de recibir atención por parte de las autoridades, al señalar que han enfrentado falta de atención y empatía de algunos funcionarios. Pidió a las autoridades que las investigaciones se lleven a cabo con prontitud, ya que algunas indagatorias comienzan hasta cinco días después de que se reporta una desaparición. Durante la misa oficiada este domingo en la Basílica Menor de Guadalupe de Pachuca, el arzobispo de Tulancingo, monseñor Óscar Roberto Domínguez, llamó a la población a no guardar silencio ante el dolor de las familias.</t>
-  </si>
-  <si>
-    <t>El Colectivo de Madres Buscadoras marchó en Pachuca y colocó tendedero de fichas de búsqueda en Plaza Independencia para exigir empatía y celeridad en investigaciones, mientras que el arzobispo Óscar Roberto Domínguez ofició una misa dominical en su honor.</t>
-  </si>
-  <si>
-    <t>Regino Cano Bautista, Óscar Roberto Domínguez</t>
-  </si>
-  <si>
-    <t>Regresarán a clases 569 mil estudiantes de educación básica</t>
-  </si>
-  <si>
-    <t>El secretario de Educación Pública del estado y titular del Instituto Hidalguense de Educación (IHE), Natividad Castrejón Valdez, informó que 569 mil estudiantes de educación básica retornarán a clases el próximo 31 de agosto, en apego al calendario escolar 2026-2027. Como parte de la preparación para el inicio del ciclo y con base en la política educativa estatal, la SEPH realizó acciones coordinadas para que las comunidades escolares contaran con los materiales necesarios desde el primer día. Con ese propósito se distribuirán 3 millones 958 mil 230 libros de texto gratuitos y 488 mil 977 paquetes de útiles escolares, mediante un trabajo conjunto con las subsecretarías de Educación Básica, Administración y Finanzas, así como Planeación y Evaluación; además de las direcciones generales de Servicios Regionales y Educación Básica, a través de la dirección de Materiales Educativos. Castrejón Valdéz especificó que se prevé la entrega de 475 mil 14 uniformes y 475 mil 14 pares de calzado escolar, que serán distribuidos durante las primeras semanas del ciclo directamente en los centros escolares, incluidas las comunidades apartadas. Los vales para útiles escolares comenzaron a imprimirse el 24 de agosto mediante el Sistema de Padres de Familia (SIP) y podrán canjearse desde el primer día de clases.</t>
-  </si>
-  <si>
-    <t>El titular de la SEPH, Natividad Castrejón Valdez, anunció el regreso a clases de 569 mil alumnos de educación básica para el ciclo escolar 2026-2027, confirmando la distribución coordinada de libros de texto, útiles, uniformes y calzado escolar.</t>
-  </si>
-  <si>
-    <t>COBAEH fortalece infraestructura educativa en Progreso de Obregón</t>
-  </si>
-  <si>
-    <t>El Colegio de Bachilleres del Estado de Hidalgo (COBAEH) y la Dirección General de Patrimonio Inmobiliario del Gobierno del Estado de Hidalgo formalizaron el comodato de un predio destinado al CEMSaD Progreso de Obregón, como parte de las acciones para fortalecer su infraestructura educativa. El espacio cuenta con una extensión de 4 mil 400 metros cuadrados y contempla la construcción de aulas, oficinas administrativas, talleres, sanitarios y áreas deportivas. El acto protocolario se realizó en las instalaciones de la Subsecretaría de Educación Media Superior y Superior de la SEPH y estuvo encabezado por el subsecretario Daniel Fragoso Torres, en compañía del titular del COBAEH, Rubén López Valdez, y la diputada Diana Rangel Zúñiga.</t>
-  </si>
-  <si>
-    <t>El COBAEH y el Gobierno de Hidalgo formalizaron el comodato de un terreno de 4,400 metros cuadrados para la construcción del CEMSaD Progreso de Obregón, proyectando beneficiar a 200 estudiantes.</t>
-  </si>
-  <si>
-    <t>Colegio de Bachilleres del Estado de Hidalgo, Dirección General de Patrimonio Inmobiliario, Instituto Hidalguense de la Infraestructura Física Educativa, Secretaría de Educación Pública de Hidalgo</t>
-  </si>
-  <si>
-    <t>UTEC fortalece oferta académica con la creación de nuevas maestrías</t>
-  </si>
-  <si>
-    <t>La Universidad Tecnológica de Tulancingo (UTEC) amplió su oferta académica con la apertura de dos programas de posgrado: la Maestría en Ingeniería y la Maestría en Gestión del Emprendimiento e Innovación, con el propósito de responder a las necesidades de especialización regional. El rector de la UTEC, Tito Dorantes Castillo, destacó que, a 31 años de su creación, la incorporación de estos programas representa un paso en la consolidación de la institución con los sectores productivo y social. Ambos programas tienen una duración de dos años bajo la modalidad híbrida.</t>
-  </si>
-  <si>
-    <t>Oferta académica</t>
-  </si>
-  <si>
-    <t>La UTEC amplió su oferta de posgrados con la creación de las maestrías en Ingeniería y en Gestión del Emprendimiento e Innovación, orientadas a la especialización regional.</t>
-  </si>
-  <si>
-    <t>Universidad Tecnológica de Tulancingo, Secretaría de Educación Pública de Hidalgo</t>
-  </si>
-  <si>
-    <t>Tito Dorantes Castillo</t>
-  </si>
-  <si>
-    <t>Regresarán a clases 569 mil estudiantes de educación básica en estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, informó que 569 mil estudiantes de educación básica regresarán a clases el próximo 31 de agosto, en apego al calendario escolar 2026-2027. Castrejón informó que se distribuirán 3 millones 958 mil 230 libros de texto gratuitos y 488 mil 977 paquetes de útiles escolares. Asimismo, se contempla la entrega de 475 mil 14 uniformes y 475 mil 14 pares de calzado escolar, que serán distribuidos durante las primeras semanas del ciclo directamente en los planteles escolares.</t>
-  </si>
-  <si>
-    <t>La SEPH reportó el regreso escolar de 569 mil alumnos en Hidalgo, garantizando la entrega de libros de texto, paquetes de útiles, uniformes y calzado escolar.</t>
-  </si>
-  <si>
-    <t>Las Rutas de la Transformación consolidan un gobierno cercano y presente en Hidalgo</t>
-  </si>
-  <si>
-    <t>En el marco del Cuarto Informe de Gobierno, el mandatario Julio Menchaca Salazar destacó el fortalecimiento de las Rutas de la Transformación “Gobierno en Movimiento” como la columna vertebral de una administración cercana, con presencia permanente en municipios de Hidalgo. A lo largo de cuatro años, las rutas han recorrido el estado en ocasiones a través de 224 eventos y 161 supervisiones de obra. Se complementa con ferias de Servicios para el Pueblo, que mediante 103 jornadas, han otorgado más de 200 mil atenciones directas.</t>
-  </si>
-  <si>
-    <t>Ruta de la Transformación</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar destacó que las Rutas de la Transformación han recorrido Hidalgo acercando programas, obras y ferias de servicios directos con 200 mil atenciones.</t>
-  </si>
-  <si>
     <t>Gobierno del Estado de Hidalgo</t>
   </si>
   <si>
-    <t>Secretaría de Cultura lleva al Congreso del Estado la campaña #HidalgoNoRegatea</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura convocó a la jornada #HidalgoNoRegatea y a la expo-venta artesanal “Manos que Crean” en las instalaciones del Congreso del Estado de Hidalgo. Lanzada en el marco del Día Mundial del Bordado, la campaña promueve el pago justo por las piezas. “El talento y el tiempo de las artesanas y los artesanos no se negocian. Cada pieza guarda identidad, memoria y años de oficio, por lo que merece un pago justo”, señaló la secretaria de Cultura, Neyda Naranjo Baltazar.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Cultura convocó a la jornada de comercio justo #HidalgoNoRegatea y la expo-venta 'Manos que Crean' en las instalaciones del Congreso del Estado.</t>
-  </si>
-  <si>
-    <t>Secretaría de Cultura de Hidalgo, Congreso del Estado de Hidalgo, Gobierno del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Neyda Naranjo Baltazar, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Destinan 5.3 mdp en agro para más de 600 familias</t>
-  </si>
-  <si>
-    <t>En cumplimiento al compromiso de dar prioridad al bienestar de las familias del campo, la Saderh, encabezada por Napoleón González Pérez, hizo entrega de apoyos por un monto de 5 millones 347 mil 252 pesos. A través de estas acciones se beneficiará a un total de 618 personas de Tolcayuca, Villa de Tezontepec, Zapotlán de Juárez y Tizayuca. La entrega se llevó a cabo en Tolcayuca, distribuyendo semillas de avena, cebada, jitomate, maíz, equipamiento acuícola, ovinos, porcinos e hijuelos de maguey.</t>
-  </si>
-  <si>
-    <t>La Saderh entregó apoyos por 5.3 mdp a 618 productores del campo en Tolcayuca, Villa de Tezontepec, Zapotlán de Juárez y Tizayuca en semillas, vientres ovinos, porcinos y aves de doble propósito.</t>
-  </si>
-  <si>
-    <t>Napoleón González Pérez, Julio Menchaca Salazar, Armando Zúñiga Gutiérrez</t>
-  </si>
-  <si>
-    <t>Realizan el rally “Caminando en tus zapatos”</t>
-  </si>
-  <si>
-    <t>Junto a estudiantes, docentes del plantel y personal administrativo del COBAEH Plantel Tula, la Dirección de la Juventud realizó el rally “Caminando en tus zapatos”, con dinámicas para aprender que cada quien trae su propia historia y experiencias. Asimismo, la actividad buscó fortalecer el vínculo afectivo y la comunicación asertiva entre padres y adolescentes mediante un recorrido de estaciones que fomente la empatía, el perdón y el reconocimiento mutuo. Finalmente, la institución agradeció a los padres de familia que asistieron “lo cual nos fortalece como institución comprometida con el bienestar emocional”.</t>
-  </si>
-  <si>
     <t>Convivencia Escolar</t>
   </si>
   <si>
-    <t>La Dirección de la Juventud de Tula realizó el rally recreativo-emocional "Caminando en tus zapatos" con estudiantes y tutores del COBAEH Plantel Tula para incentivar la empatía y armonía familiar.</t>
-  </si>
-  <si>
-    <t>Colegio de Bachilleres del Estado de Hidalgo Plantel Tula, Dirección de la Juventud de Tula</t>
-  </si>
-  <si>
-    <t>La SSPH, mantiene el fortalecimiento de la seguridad en el Estado</t>
-  </si>
-  <si>
-    <t>La tarde de este domingo la Secretaría de Seguridad Pública de Hidalgo (SSPH), que dirige el comisario general Salvador Cruz Neri, emitió un comunicado oficial, donde se resalta que bajo el lema de “Primero el Pueblo”, se da a conocer que se mantiene el fortalecimiento de la seguridad. Así mismo, se refrendó que la seguridad es una prioridad desde el primer minuto del día. La información relata que, en el territorio hidalguense se despliegan operativos de vigilancia y prevención en puntos estratégicos, calles y espacios públicos para garantizar un entorno de paz para todas las familias. La SSPH advirtió a la ciudadanía en general que es necesario que con responsabilidad se haga uso de las líneas de Emergencias 911 y 089 de Denuncia Anónima.</t>
-  </si>
-  <si>
-    <t>Estrategia de seguridad</t>
-  </si>
-  <si>
-    <t>La SSPH emitió un boletín confirmando el despliegue permanente de retenes, patrullajes y cercos preventivos de seguridad en los 84 municipios de Hidalgo, solicitando el uso responsable del 911.</t>
-  </si>
-  <si>
-    <t>Evaluaron y certificaron al 99.69% de las fuerzas de seguridad</t>
-  </si>
-  <si>
-    <t>Gracias al apoyo del Gobierno del Estado que encabeza Julio Menchaca Salazar, así como as acciones emprendidas por la Secretaría de Seguridad Pública de Hidalgo, se ha logrado una excelente profesionalización de los cuerpos de seguridad en la entidad. Se destacó que para el mandatario hidalguense la seguridad es prioridad estratégica, por lo que se da atención a evaluaciones de control de confianza, lo que garantiza tener elementos de las corporaciones policiacas preparados, eficientes y leales a la ciudadanía. Actualmente, se ha evaluado y certificado al 99.69% de las fuerzas de seguridad, renovando el 25% de la plantilla operativa con 475 cadetes graduados en 7 generaciones. El fortalecimiento institucional es impulsado para, brindar mayor certidumbre y profesionalismo.</t>
-  </si>
-  <si>
-    <t>Certificación policial</t>
-  </si>
-  <si>
-    <t>La SSPH de Hidalgo logró la evaluación y certificación de control de confianza del 99.69% de los elementos policiales, incorporando además a 475 nuevos policías graduados.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Gobierno del Estado de Hidalgo, Instituto de Formación Profesional</t>
-  </si>
-  <si>
-    <t>Remueven a 174 internos del CeReSo de Mixquiahuala al de Tula</t>
-  </si>
-  <si>
-    <t>Luego de causar expectación y temor de los habitantes del Municipio de Mixquiahuala, por un impressive operativo policial se descubrió que se habría tratado del traslado conjunto de internos del penal de esa demarcación hidalguense... la Secretaría de Seguridad Pública de Hidalgo (SSPH) informa lo siguiente: La información revela que la institución que encabeza el comisario general Salvador Cruz Neri, que se trató de movilización para realizar el traslado de los varones internos del CeReSo de Mixquiahuala, al nuevo módulo de dormitorios en el CeReSo de Tula de Allende. Así mismo se dejó en claro que el despliegue policial y traslado de los reos obedeció principalmente a la sobrepoblación que existía en ese penal, ya que la capacidad es para 70 personas privadas de la libertad y este albergaba a 191 internos, por lo que se procedió al traslado de 174 personas de la población varonil. Otra de las causas es porque los dormitorios presentan filtraciones de agua y protección civil recomendó hacer un reforzamiento y remodelación de los techos. Finalmente, el Gobierno del estado de Hidalgo advirtió que, el objetivo que se persigue es el de buscar mejoras en las condiciones de reclusión y de vida de las personas privadas de la libertad, siempre actuando bajo el marco de la Ley de la Ejecución Penal.</t>
-  </si>
-  <si>
-    <t>Un operativo coordinado de la SSPH trasladó a 174 reos del penal de Mixquiahuala (que superaba el doble de su capacidad real de 70 personas) hacia los dormitorios nuevos de Tula, solucionando además filtraciones pluviales en techumbres.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Dirección de Protección Civil, Gobierno del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Rescatan cuerpo de hombre en presa</t>
-  </si>
-  <si>
-    <t>Luego de reportarse la desaparición de una persona en una presa del territorio hidalguense, se tuvo la pronta intervención de elementos del H. Cuerpo de Bomberos de Hidalgo, quienes procedieron a las complicadas labores de localización y recuperaron el cuerpo de un joven de 24 años de edad, en una presa ubicada en la comunidad de Carpinteros Norte, perteneciente al municipio de San Agustín Metzquititlán. Se sabe, que fueron vecinos del lugar los que el jueves anterior alertaron a las autoridades policiales, sobre el extravió del infortunado... De acuerdo con los reportes oficiales de la Secretaría de Seguridad Pública de Hidalgo (SSPH), el individuo se encontraba desaparecido desde el pasado 27 de agosto. Las labores de inmersión y búsqueda especializada comenzaron a las 09:35 horas, logrando el hallazgo y rescate de los restos a las 11:06 horas. Finalmente, se informó que durante el operativo coordinado participaron elementos de la SSPH, además de agentes de la policía municipal, personal de la Secretaría de Gobernación y pobladores de la localidad, quienes colaboraron en las tareas de rastreo en la zona.</t>
-  </si>
-  <si>
-    <t>San Agustín Metzquititlán</t>
-  </si>
-  <si>
-    <t>Rescate de cuerpo</t>
-  </si>
-  <si>
-    <t>Buzos del H. Cuerpo de Bomberos de Hidalgo adscritos a la SSPH recuperaron de una presa en Carpinteros Norte, San Agustín Metzquititlán, el cuerpo sin vida de un joven de 24 años ahogado tras caer al agua el pasado jueves.</t>
-  </si>
-  <si>
-    <t>Cuerpo de Bomberos de Hidalgo, Secretaría de Seguridad Pública de Hidalgo, Secretaría de Gobernación, Policía Municipal de San Agustín Metzquititlán</t>
-  </si>
-  <si>
-    <t>Familias buscadoras marchan en Pachuca</t>
-  </si>
-  <si>
-    <t>Las familias buscadoras salieron a las calles para exigirle a las autoridades que actúen, denunciando que las carpetas no avanzan y las respuestas no llegan. Alrededor de 25 familias de distintos municipios marcharon en Pachuca por el Día Internacional de las Víctimas de Desapariciones Forzadas, con fichas de búsqueda y demandas firmes de celeridad judicial.</t>
-  </si>
-  <si>
-    <t>Un grupo de 25 familias de víctimas de desaparición marcharon en Pachuca en su día conmemorativo para protestar contra el nulo avance de las investigaciones penales.</t>
-  </si>
-  <si>
-    <t>Regresan a las aulas 569 mil estudiantes de básica en Hidalgo</t>
-  </si>
-  <si>
-    <t>Un total de 569 mil estudiantes de educación básica regresarán a clases este lunes 31 de agosto en Hidalgo, conforme al calendario escolar 2026-2027. El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, informó que se distribuirán 3 millones 958 mil 230 libros de texto gratuitos y 488 mil 977 paquetes de útiles escolares para garantizar que las comunidades escolares cuenten con los materiales desde el primer día de clases. Además, durante las primeras semanas se distribuirán 475 mil 14 uniformes y el mismo número de pares de calzado escolar directamente en los planteles.</t>
-  </si>
-  <si>
-    <t>La SEPH coordinó el inicio del ciclo lectivo para 569 mil alumnos, entregando libros de texto, útiles, calzado y uniformes gratuitos.</t>
-  </si>
-  <si>
-    <t>Matrícula de prepa al 50% de lo esperado</t>
-  </si>
-  <si>
-    <t>El titular de la SEPH, Natividad Castrejón Valdez, informó que el Bachillerato Nacional Margarita Maza registra una matrícula inicial de alrededor de 600 estudiantes inscritos, cifra que representa la mitad de la meta planteada por la secretaría. El funcionario detalló que ocho sedes ya están totalmente listas para iniciar actividades el próximo 8 de septiembre en modalidad mixta semipresencial, durando dos años divididos en 16 módulos de seis semanas. Asimismo, precisó que se proyectan dos planteles definitivos en Mineral de la Reforma una vez concluidas las licitaciones físicas.</t>
-  </si>
-  <si>
-    <t>Bachillerato Nacional</t>
-  </si>
-  <si>
-    <t>El Bachillerato Nacional Margarita Maza de la SEPH captó un 50% del aforo estimado, preparándose para arrancar el 8 de septiembre con 600 inscritos.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Bachillerato Nacional Margarita Maza</t>
+    <t>Inician ciclo escolar 569 mil 987 alumnos</t>
+  </si>
+  <si>
+    <t>Entre prisas, tráfico, ambulantaje, aplausos y dinámicas para un ameno regreso a las aulas, inició el ciclo escolar 2026-2027, que este año recibió a 569 mil 987 estudiantes del nivel básico. Desde las primeras horas del día, calles y avenidas con escuelas de nivel básico volvieron a llenarse de niñas, niños y adolescentes con uniformes y mochilas al hombro. Este año, el arranque oficial se realizó en la Escuela Secundaria General 2, en Pachuca, donde cientos de alumnos se dieron cita en el auditorio para presenciar la inauguración del ciclo por parte de autoridades estatales. Durante el evento, la alumna María Fernanda González consideró el regreso como una oportunidad de reencuentro y metas nuevas.</t>
+  </si>
+  <si>
+    <t>Un total de 569 mil 987 estudiantes de nivel básico iniciaron el ciclo escolar 2026-2027 en Hidalgo, con protocolo oficial en Pachuca.</t>
+  </si>
+  <si>
+    <t>Portadas</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, María Fernanda González Ramírez</t>
+  </si>
+  <si>
+    <t>“Equilibrado”, deberá ser el protocolo que defienda a docentes</t>
+  </si>
+  <si>
+    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, afirmó que se sigue trabajando en un protocolo “equilibrado” entre la protección al derecho de las infancias y de los docentes, luego de las quejas o demandas por presunta violencia escolar en contra de los maestros. El mandatario estatal afirmó que, en algunas ocasiones, los maestros han sido sujetos de acusaciones sin sustento, por lo que el Congreso local ya trabaja en ese tema de forma responsable. Reiteró que los protocolos son para definir los pasos a seguir ante hechos que se pudieran suscitar y que no dependen estrictamente de la opinión de una persona.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar precisó que el Congreso local diseña un protocolo de protección equilibrada para el sector docente.</t>
+  </si>
+  <si>
+    <t>Congreso del Estado de Hidalgo, Secretaría de Educación Pública de Hidalgo</t>
+  </si>
+  <si>
+    <t>Se dispara 76% violencia escolar en Hidalgo: SEPH</t>
+  </si>
+  <si>
+    <t>El ciclo escolar 2025-2026 registró un aumento del 76 por ciento en los reportes de presunta violencia escolar, en comparación con el curso previo, que registró 787 incidentes. En el periodo recién concluido se contabilizaron mil 385 reportes en todos los niveles educativos, según dio a conocer el secretario de educación estatal, Natividad Castrejón Valdez. Las tres principales causas reportadas ante el REPAEVE fueron violencia física (380 casos), violencia psicológica (316 casos) y violencia sexual (163 reportes). Los casos que involucran a docentes representan el 29.1 por ciento del total (alrededor de 400 hechos), concentrándose la mayoría de las quejas en primarias generales con 614 reportes.</t>
+  </si>
+  <si>
+    <t>La SEPH reportó un incremento del 76% de reportes de violencia escolar en el ciclo 2025-2026, con un total de 1,385 incidencias registradas.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Registro Estatal de Prevención, Atención y Erradicación de la Violencia Escolar (REPAEVE), Procuraduría General de Justicia de Hidalgo</t>
+  </si>
+  <si>
+    <t>Frena proyectos la falta de socialización en región Tula: Tello</t>
+  </si>
+  <si>
+    <t>El secretario de Planeación y Prospectiva de Hidalgo, Miguel Ángel Tello Vargas, reconoció que la falta de socialización y la politización de los proyectos han sido algunos de los principales obstáculos para concretar obras en la región Tula-Tepeji. Al referirse a proyectos viales de Nopala, viviendas en Atotonilco de Tula y el control del lirio acuático, destacó que se requiere mayor diálogo. Subrayó que los pobladores tienen razón en muchas cosas y hay que escucharlos, anunciando que preparan nuevas inversiones para diversificar la vocación de Tula de una ciudad industrial hacia un destino turístico.</t>
+  </si>
+  <si>
+    <t>Socialización de obra</t>
+  </si>
+  <si>
+    <t>El secretario Miguel Ángel Tello admitió rezagos en obras por fallas de socialización en la región Tula, promoviendo mayor apertura vecinal.</t>
+  </si>
+  <si>
+    <t>Lizania Zavala</t>
+  </si>
+  <si>
+    <t>Unidad de Planeación y Prospectiva, Comisión Nacional del Agua (Conagua)</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Tello Vargas</t>
+  </si>
+  <si>
+    <t>Hidalgo recibió remesas por 863 mdd en 6 meses</t>
+  </si>
+  <si>
+    <t>Hidalgo recibió 863.65 millones de dólares por concepto de remesas durante el primer semestre de 2026, un incremento de 20.20 millones de dólares frente a los 843.45 millones registrados en el mismo periodo de 2025. El secretario de Bienestar e Inclusión Social, Ricardo Gómez Moreno, informó que el recurso es una fuente vital para miles de familias en municipios de origen migratorio como Tulancingo, Ixmiquilpan, Pachuca, Actopan y Zacualtipán. Detalló que 466 mil 199 hidalguenses radican en Estados Unidos, concentrados principalmente en California, Texas y Florida.</t>
+  </si>
+  <si>
+    <t>Remesas</t>
+  </si>
+  <si>
+    <t>La Sebiso estatal informó la captación de 863.65 mdd por concepto de remesas familiares en el primer semestre de 2026.</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Instituto Nacional de Migración (Unidad de Política Migratoria)</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno</t>
+  </si>
+  <si>
+    <t>Zanja frente al panteón: una trampa bajo el agua</t>
+  </si>
+  <si>
+    <t>La temporada de lluvias convirtió un punto del bulevar del Minero, a la altura del Panteón Municipal de Pachuca, en una trampa para automovilistas, donde tres vehículos han caído en una canaleta encharcada en los últimos días. El 27 de agosto, una camioneta y una Urvan de transporte público quedaron varadas frente al Cereso, repitiéndose la incidencia el 29 de agosto con otro automóvil particular. Ante ello, la Policía Estatal y el H. Cuerpo de Bomberos de la SSPH implementaron recorridos de auxilio por lluvias torrenciales en el bulevar Felipe Ángeles, Explanada, Real Toledo y Bulevar El Minero.</t>
+  </si>
+  <si>
+    <t>Lluvias torrenciales provocaron que tres unidades cayeran en una zanja cubierta por encharcamientos en Pachuca, desplegándose auxilio de la SSPH.</t>
+  </si>
+  <si>
+    <t>Luis Godínez</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Policía Estatal, Cuerpo de Bomberos de Hidalgo</t>
+  </si>
+  <si>
+    <t>Aumentan denuncias por violencia familiar y robo en Molango</t>
+  </si>
+  <si>
+    <t>El registro de denuncias por el delito de violencia familiar en Molango de Escamilla creció 140 por ciento de enero a julio de 2026, en comparación con el mismo periodo de la anualidad pasada; además, también presentaron un incremento de 142 por ciento las denuncias por robo, y las de narcomenudeo, 133 por ciento. De acuerdo con el Índice Delictivo del SESNSP, los primeros siete meses de 2025 sumaron cinco casos de violencia familiar, mientras que en el mismo periodo de este año van 12 denuncias formales ante la autoridad jurisdiccional.</t>
+  </si>
+  <si>
+    <t>Molango</t>
+  </si>
+  <si>
+    <t>Incidencia Delictiva</t>
+  </si>
+  <si>
+    <t>La incidencia delictiva del SESNSP reportó alzas de 140% en violencia intrafamiliar y del 142% en robos en el municipio de Molango.</t>
+  </si>
+  <si>
+    <t>Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública (SESNSP), Procuraduría General de Justicia del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Buscan diseñar plan de movilidad para Huejutla</t>
+  </si>
+  <si>
+    <t>El gobierno de Hidalgo emitió una licitación para la elaboración del Plan Integral de Movilidad Urbana Sustentable (PIMUS) del municipio de Huejutla de Reyes, a solicitud de la Secretaría de Movilidad y Transporte (Semot). De acuerdo con las bases del procedimiento EA-913003989-N0518-2026, se busca un proveedor para desarrollar el estudio que delimitará el territorio y abarcará aspectos demográficos, topografía, hidrología y análisis socioeconómicos de Huejutla e Ixmiquilpan.</t>
+  </si>
+  <si>
+    <t>Movilidad sustentable</t>
+  </si>
+  <si>
+    <t>La Semot licitó la elaboración del Plan Integral de Movilidad Urbana (PIMUS) para planear el desarrollo de transporte en Huejutla e Ixmiquilpan.</t>
+  </si>
+  <si>
+    <t>Semot</t>
+  </si>
+  <si>
+    <t>Secretaría de Movilidad y Transporte de Hidalgo, Instituto Nacional de Estadística y Geografía (Inegi)</t>
+  </si>
+  <si>
+    <t>Desapariciones aumentan durante agosto en Hidalgo</t>
+  </si>
+  <si>
+    <t>Un hombre sin vida, quien contaba con ficha de búsqueda, y 13 reportes de personas desaparecidas fueron el saldo que dejó el mes de agosto en Hidalgo, de acuerdo con la plataforma administrada por la Secretaría de Gobierno y la Comisión Nacional de Búsqueda (CNB). En cuanto a las personas no localizadas, ocho corresponden a hombres y cinco a mujeres, concentrándose en Tizayuca, Pachuca y Atitalaquia. En contraste, 29 personas fueron ubicadas con vida (18 mujeres, 11 hombres) principalmente en Mineral de la Reforma y Pachuca.</t>
+  </si>
+  <si>
+    <t>La CNB y la Segobh reportaron un acumulado de 13 personas desaparecidas en agosto, localizándose además a 29 ciudadanos con vida.</t>
+  </si>
+  <si>
+    <t>Secretaría de Gobierno de Hidalgo, Comisión Nacional de Búsqueda (CNB), Comisión de Búsqueda de Personas del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Ser foráneo en la UTHH, un sacrificio económico</t>
+  </si>
+  <si>
+    <t>Para los estudiantes foráneos universitarios, acudir diariamente a clases representa un esfuerzo económico adicional para sus familias, debido al costo del transporte, alimentación y, en algunos casos, el pago de una renta en Huejutla. Alumnos de Chalma gastan 50 pesos diarios en pasaje, Patricio de Tempoal requiere 94 pesos, Alfredo de Calnali gasta 75 pesos por viaje y Yami de Chicontepec gasta hasta 180 pesos de pasaje de ida y vuelta. A esto se suma el gasto de comida de 90 pesos y rentas de hasta 2,500 pesos.</t>
+  </si>
+  <si>
+    <t>Estudiantes foráneos de la UTHH de Huejutla afrontan un alto desgaste de hasta 180 pesos de pasaje diario para cursar sus estudios presenciales.</t>
+  </si>
+  <si>
+    <t>Salomón Hernández</t>
+  </si>
+  <si>
+    <t>Universidad Tecnológica de la Huasteca Hidalguense (UTHH)</t>
+  </si>
+  <si>
+    <t>Amaury N, Patricio N, Alfredo N, Yami N</t>
+  </si>
+  <si>
+    <t>Advierten paterfamilias que no aceptarán clases en línea</t>
+  </si>
+  <si>
+    <t>Madres y padres de alumnos de la escuela primaria Aquiles Serdán en Tulancingo informaron que sus hijos recibirán clases presenciales en el plantel durante un mes y medio aproximadamente, lapso en el que las autoridades educativas buscarán una sede alterna para continuar bajo la misma modalidad, ya que no permitirán la enseñanza en línea. Los paterfamilias se opusieron al formato virtual anunciado por la dirección tras emitirse el dictamen de demolición física de la escuela y reconstrucción de aulas.</t>
+  </si>
+  <si>
+    <t>Padres de familia de Tulancingo rechazaron clases virtuales, logrando clases presenciales provisionales antes de la demolición del plantel.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Servicios Regionales</t>
+  </si>
+  <si>
+    <t>Inaugura Menchaca el inicio de clases</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar presidió en Pachuca el inicio escolar del ciclo 2026-2027 en la Secundaria General No. 2, destacando una inversión educativa de 121 mil millones de pesos acumulada en cuatro años. El titular de la SEPH, Natividad Castrejón Valdez, reportó el retorno de 967 mil alumnos en 8 mil 717 planteles, destacando la asignación de apoyos Rita Cetina de 2 mil 500 pesos y la futura regulación del uso excesivo de celulares y dispositivos digitales en las escuelas por problemas de ansiedad y de salud visual.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca presidió el inicio escolar 2026-2027 en Pachuca, destacando una inversión educativa de 121 mil mdp en cuatro años, mientras la SEPH analiza regular el uso de celulares.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Instituto Hidalguense de Educación, Sindicato Nacional de Trabajadores de la Educación</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Natividad Castrejón Valdez, Said Vargas Sáenz, Alberto García Palacios</t>
+  </si>
+  <si>
+    <t>Cítnova financia 220 becas de investigación</t>
+  </si>
+  <si>
+    <t>El Consejo de Ciencia, Tecnología e Innovación de Hidalgo (Citnova) publicó el padrón de 220 becarios beneficiados por el programa Fondo Hidalgo para estudios de posgrado e investigaciones de base tecnológica. La convocatoria asignará montos de 250 mil y 20 mil pesos para el desarrollo de proyectos en la UAEH, UPP, ITESA e institutos tecnológicos, favoreciendo además a investigadores del Congreso del Estado de Hidalgo, Saderh, la Secretaría de Bienestar e Inclusión Social y diversos ayuntamientos.</t>
+  </si>
+  <si>
+    <t>Becas De Posgrado</t>
+  </si>
+  <si>
+    <t>El Citnova publicó los beneficiarios de 220 becas de posgrado y proyectos tecnológicos del programa Fondo Hidalgo, apoyando a investigadores, ayuntamientos, Saderh y Congreso local.</t>
+  </si>
+  <si>
+    <t>Sonia Nochebuena</t>
+  </si>
+  <si>
+    <t>Consejo de Ciencia, Tecnología e Innovación de Hidalgo, Secretaría de Agricultura y Desarrollo Rural de Hidalgo, Congreso del Estado de Hidalgo, Instituto Hidalguense de Educación</t>
+  </si>
+  <si>
+    <t>Zianya Gómez Soto, Gabriela Salas Cabrera, Leyza Aída Fernández Vega, Carlos Arturo Castro del Ángel, Juan de Dios Robles Pérez, Víctor Díaz Hernández, José Trinidad Ramírez Vargas, Gerardo Falcón Lucario, Sergio Aguilar Carrera</t>
+  </si>
+  <si>
+    <t>Hidalgo supera 50 por ciento de meta de esterilización</t>
+  </si>
+  <si>
+    <t>Durante el primer semestre en Hidalgo se realizaron 22 mil 929 esterilizaciones, que representan el 57.7 por ciento de la meta para todo 2026; además, 16 municipios superaron la programación de todo el año. En contraste, Lolotla, Progreso y Eloxochitlán no hicieron ninguna cirugía, reveló la Secretaría de Salud estatal (SSH). Erick José Canales Vargas, coordinador estatal del programa de zoonosis de la SSH, informó que la meta de este año es realizar 42 mil 669 esterilizaciones en perros y gatos, y de enero a junio superaron la mitad, con 22 mil 929 cirugías. Con esta actividad buscamos que disminuya el abandono de los perros y gatos en vía pública, porque la presencia de esos animales causa impactos en la salud. Tepeji de Río es el municipio con más cirugías con mil 955 (155.1% de su meta de 1,260). Apan 919 (meta 676), Zacualtipán 745 (meta 540), Huichapan 738 (meta 705), Alfajayucan 544 (meta 320). Lolotla, Progreso y Eloxochitlán cero. Calnali 15, Almoloya 25, Mixquiahuala 27, Tlaxcoapan 32, Huazalingo 34, Ajacuba 37. Pachuca 869 (26.2% de 3,316). Meta de vacunación antirrábica es 1,066,737, logrando 396,692 (37.2%). Alba Luisa Jiménez de Jauría de Balú destacó que es viable para el control animal.</t>
+  </si>
+  <si>
+    <t>Campaña de esterilización</t>
+  </si>
+  <si>
+    <t>Hidalgo alcanzó el 57.7% de su meta de esterilización de mascotas en el primer semestre de 2026, con Tepeji del Río a la cabeza y Lolotla, Progreso y Eloxochitlán con cero cirugías.</t>
+  </si>
+  <si>
+    <t>Secretaría de Salud de Hidalgo, Ayuntamientos locales</t>
+  </si>
+  <si>
+    <t>Erick José Canales Vargas, Alba Luisa Jiménez</t>
+  </si>
+  <si>
+    <t>REMESAS AUMENTARON EN 20 MDD EN UN AÑO</t>
+  </si>
+  <si>
+    <t>Pachuca.- Los hidalguenses que radican en el extranjero enviaron a sus familias 20.2 millones de dólares más en remesas durante el primer semestre de 2026, en comparación con el mismo periodo del año anterior, informó Ricardo Gómez Moreno, titular de la Secretaría de Bienestar e Inclusión Social (Sebiso) de Hidalgo. De acuerdo con el funcionario, entre enero y junio de este año, la entidad captó 863.65 millones de dólares, mientras que en el mismo periodo de 2025 ingresó 843.45 millones de dólares. Dicha diferencia representa un incremento en las remesas de 2.39 por ciento en un periodo de un año. Los municipios que concentraron la mayor captación durante el periodo de referencia fueron Tulancingo, Ixmiquilpan, Pachuca, Actopan y Zacualtipán. El flujo de recursos ocurre en un contexto de presencia de hidalguenses en Estados Unidos, ya que, de acuerdo con los datos de Gómez Moreno, 466 mil 199 migrantes originarios del estado habitan en ese país, cifra que coloca a Hidalgo en el décimo lugar nacional en intensidad migratoria. La población migrante se concentra principalmente en cinco estados de la Unión Americana: California, con 17.4 por ciento; Texas, 13.6 por ciento; Florida, 13.5 por ciento, y Carolina del Norte y Georgia, ambos con 7.8 por ciento. Mientras tanto, los municipios hidalguenses identificados como principales lugares de origen de la población migrante son Pisaflores, La Misión, Chapulhuacán, Tecozautla y Tasquillo, detalló el funcionario. Jacala, Pacula, Atotonilco el Grande, Santiago de Anaya, Acatlán, Tlahuiltepa, Zimapán, Nicolás Flores, Huasca, Huichapan, Alfajayucan, Chilcuautla, Ixmiquilpan y Cardonal. Repatriaciones: de enero a junio de 2026 se contabilizaron 2 mil 848 repatriaciones de hidalguenses, de acuerdo con registros del Instituto Nacional de Migración (INM).</t>
+  </si>
+  <si>
+    <t>La Sebiso de Hidalgo reportó un crecimiento de 2.39% anual en la captación de remesas en el primer semestre de 2026, alcanzando los 863.65 mdd, beneficiando a municipios clave como Tulancingo e Ixmiquilpan.</t>
+  </si>
+  <si>
+    <t>Lorena Rosas</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Instituto Nacional de Migración</t>
+  </si>
+  <si>
+    <t>Capacitan a personas con discapacidad para el trabajo</t>
+  </si>
+  <si>
+    <t>Pachuca.- La Secretaría de Bienestar e Inclusión Social (Sebiso) lleva a cabo un taller de habilidades laborales, diseñado para promover la autonomía económica de las personas con discapacidad en Hidalgo. Esta iniciativa ofrece a los participantes la oportunidad de adentrarse en el sector productivo, mediante un programa de formación enfocado en la costura, centrado principalmente en la elaboración artesanal de piezas para peluches, detalló la dependencia. Las jornadas de formación se realizan de manera presencial en las instalaciones de la Dirección de Inclusión, donde el personal capacita a los asistentes en las técnicas de costura y confección. Conforme los participantes avanzan y perfeccionan su producción, la fábrica receptora de estas piezas puede adquirirlas y brindar un apoyo económico directo durante su capacitación. Este beneficio monetario sirve como un incentivo constante que inspira, recompensa y reconoce su valioso esfuerzo e impulso productivo. El programa cuenta con una comunidad activa de 30 personas: 10 productoras y 20 practicantes.</t>
+  </si>
+  <si>
+    <t>Apoyo a personas con discapacidad</t>
+  </si>
+  <si>
+    <t>La Sebiso estatal implementó un taller presencial de costura en Pachuca enfocado en capacitar en la confección de piezas para peluches a una comunidad de 30 personas con discapacidad, fomentando su autonomía laboral.</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Dirección de Inclusión de la Sebiso</t>
+  </si>
+  <si>
+    <t>Prevén sumar 6 municipios a Viviendas del Bienestar</t>
+  </si>
+  <si>
+    <t>Pachuca.- Actualmente se construyen casas del programa Viviendas del Bienestar en siete municipios de Hidalgo, mientras que en otros 13 está prevista la edificación y seis más podrían incorporarse antes de concluir el año, informó la Unidad de Planeación y Prospectiva de Hidalgo. Los lugares donde ya se construyen son El Arenal, Mineral de la Reforma, San Agustín Tlaxiaca, Tepeapulco, Tepeji del Río, Tulancingo y Zempoala. Mientras que se iniciará la construcción en Actopan, Apan, Atotonilco de Tula, Cuautepec, Huautla, Huejutla, Huichapan, Ixmiquilpan, Mixquiahuala, Progreso de Obregón, Tizayuca, Tula y Zapotlán. La meta estatal contempla 60 mil viviendas durante el actual sexenio, de las cuales 31 mil 500 están en proceso de edificación, con un costo promedio de 600 mil pesos por casa. Los proyectos están a cargo del Instituto del Fondo Nacional de la Vivienda para los Trabajadores (Infonavit) y la Comisión Nacional de Vivienda (Conavi); además, se prevé la incorporación del Fondo de la Vivienda del Instituto de Seguridad y Servicios Sociales de los Trabajadores del Estado (Fovissste). De acuerdo con la Unidad de Planeación, el estado y los municipios tendrán la responsabilidad de garantizar servicios básicos y transporte para los nuevos desarrollos.</t>
+  </si>
+  <si>
+    <t>Plan Nacional De Vivienda</t>
+  </si>
+  <si>
+    <t>La Unidad de Planeación y Prospectiva de Hidalgo informó que el programa Viviendas del Bienestar (Infonavit y Conavi) edifica 31,500 casas en la entidad de una meta sexenal de 60,000, proyectando expandirse a 19 demarcaciones.</t>
+  </si>
+  <si>
+    <t>Unidad de Planeación y Prospectiva, Instituto del Fondo Nacional de la Vivienda para los Trabajadores, Comisión Nacional de Vivienda, Fondo de la Vivienda del ISSSTE</t>
+  </si>
+  <si>
+    <t>EN BUSCA DEL CIUDADANO: Cuatro años de la administración Menchaca</t>
+  </si>
+  <si>
+    <t>El viernes de esta semana se cumple la segunda mitad del actual gobierno en el estado de Hidalgo. Lo alcanzado hasta este momento obedece a las decisiones que se han tomado en el corto plazo. El presupuesto para programas sociales aumentó en un 360%, pasando de mil 61 millones de pesos a más de 4 mil 900 millones este año. Se redujo la pobreza del 41% al 35%, lo que hizo posible que más de 154 mil personas salieran de esta condición. En el rubro de la educación se ha destinado en los últimos cuatro años un monto de 121 mil millones de pesos, lo que representa el 44% del presupuesto total del estado. Llegaron al estado más de 147 mil millones de pesos en inversiones, lo que supera el monto obtenido en las 4 administraciones anteriores, generando más de 191 mil empleos. Se redujo la deuda pública en un 42%, con un crecimiento histórico del 96% en la recaudación de ingresos propios.</t>
+  </si>
+  <si>
+    <t>Columna de opinión que hace un balance favorable de los primeros cuatro años de la administración estatal, destacando el incremento presupuestal del 360% en programas sociales, la reducción de pobreza y deuda, y la atracción de 147 mil mdp en inversiones.</t>
+  </si>
+  <si>
+    <t>Enrique López</t>
+  </si>
+  <si>
+    <t>La SSH capacitó a personal médico sobre el cáncer de cuello uterino</t>
+  </si>
+  <si>
+    <t>Pachuca.- La Secretaría de Salud de Hidalgo (SSH) capacitó a 163 profesionales de la salud y estudiantes de instituciones públicas y privadas para fortalecer las competencias técnicas en la prevención, detección oportuna y atención del cáncer de cuello uterino, una de las principales causas de enfermedad y muerte entre las mujeres cuando no se identifica y trata a tiempo. La jornada académica reunió a personal del Centro Médico Nacional Siglo XXI, IMSS Ordinario, Issste, IMSS Bienestar, así como al Instituto de Estudios Superiores Elise Freinet, Intermédica, Hospital del Niño DIF Hidalgo, Universidad Autónoma del Estado de Hidalgo (UAEH) y Universidad La Salle Pachuca. La secretaria de Salud de Hidalgo, Vanesa Escalante Arroyo, destacó que la actualización permanente del personal sanitario es una herramienta fundamental para fortalecer las acciones preventivas, ampliar la detección oportuna y garantizar servicios de calidad. Destacó que, bajo esta perspectiva, se impulsan estrategias como las Brigadas de la Salud.</t>
+  </si>
+  <si>
+    <t>Cáncer de la mujer</t>
+  </si>
+  <si>
+    <t>La titular de la SSH, Vanesa Escalante, encabezó la capacitación técnica de 163 médicos, enfermeros y estudiantes de salud sobre detección oportuna y prevención de cáncer de cuello uterino en el estado.</t>
+  </si>
+  <si>
+    <t>Secretaría de Salud de Hidalgo, Instituto Mexicano del Seguro Social, ISSSTE, IMSS-Bienestar, Hospital del Niño DIF Hidalgo, Universidad Autónoma del Estado de Hidalgo, Universidad La Salle Pachuca</t>
+  </si>
+  <si>
+    <t>Vanesa Escalante Arroyo</t>
+  </si>
+  <si>
+    <t>DIFH adquiere tecnología robótica para rehabilitación</t>
+  </si>
+  <si>
+    <t>Pachuca.- El Sistema DIF Hidalgo presentó el Lokomat, dispositivo cuya inversión asciende a 18 millones 498 mil 956 pesos, y que el organismo incorporó al Centro de Rehabilitación Integral de Hidalgo (CRIH), con el objetivo de ampliar las alternativas de atención para niños, adolescentes, personas adultas y adultas mayores a un costo accesible. Edda Vite Ramos, presidenta del Patronato del Sistema DIFH, destacó que esta tecnología no sustituye a los profesionales de la rehabilitación, sino que fortalece su trabajo y permite complementar los tratamientos, de acuerdo con las condiciones y necesidades específicas de cada paciente. Actualmente, el CRIH cuenta con 415 pacientes registrados, de los cuales 215 son candidatos para utilizar dicha tecnología, previa valoración del personal especializado. En este sentido, destacó el trabajo coordinado con el Sistema Nacional DIF. Por su parte, Ricardo Alvizo Contreras, titular del Sistema DIF Hidalgo, puntualizó que en México únicamente existen 33 equipos Lokomat al servicio de la población en general, con sesiones a costos accesibles.</t>
+  </si>
+  <si>
+    <t>Rehabilitación CRIRH</t>
+  </si>
+  <si>
+    <t>Con una inversión de 18.4 mdp, el DIF Hidalgo integró al CRIH un dispositivo robótico Lokomat de alta tecnología para complementar los tratamientos de rehabilitación motora a costos accesibles para la población.</t>
+  </si>
+  <si>
+    <t>DIFH</t>
+  </si>
+  <si>
+    <t>Sistema DIF Hidalgo, Centro de Rehabilitación Integral de Hidalgo, Sistema Nacional DIF</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos, Ricardo Alvizo Contreras</t>
+  </si>
+  <si>
+    <t>Han invertido 121 mil mdp en educación</t>
+  </si>
+  <si>
+    <t>En cuatro años, el gobierno de Hidalgo invirtió 121 mil millones de pesos en educación, derivado de un mejor uso de los recursos públicos, destacó el gobernador Julio Menchaca Salazar durante el inicio de clases del ciclo escolar 2026-2027. Ante estudiantes, padres y madres de familia y personal docente de la Secundaria General 2, de Pachuca, el mandatario estatal indicó que el presupuesto invertido busca respaldar el esfuerzo de las familias. Además, el gobernador encabezó el inicio de entrega de libros de texto y útiles escolares para el nivel básico, con un acto simbólico. De acuerdo con datos de la Secretaría de Educación Pública de Hidalgo (SEPH), en todo el estado entregarán 3 millones 958 mil 230 libros de texto gratuitos y 488 mil 977 paquetes de útiles escolares. Mientras tanto, la entrega de 475 mil 14 uniformes y 475 mil 14 pares de calzado escolar se realizará durante las primeras semanas. El titular de la SEPH, Natividad Castrejón Valdez, informó que volvieron a las aulas 569 mil 987 estudiantes de educación básica en toda la entidad.</t>
+  </si>
+  <si>
+    <t>Impulso A La Educación</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca inauguró el ciclo escolar 2026-2027 en Pachuca, resaltando una inversión de 121 mil mdp acumulada en materia educativa y poniendo en marcha la repartición de 3.9 millones de libros de texto y útiles escolares.</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Natividad Castrejón Valdez</t>
+  </si>
+  <si>
+    <t>Vuelven a las aulas estudiantes de nivel básico en Pachuca</t>
+  </si>
+  <si>
+    <t>Pachuca.- Prisas al caminar, mochilas y loncheras con olor a nuevo, niñas y niños con caras lavadas, algunas con bostezos por la desmañanada y otras con expresión de extrañeza al entrar a una nueva escuela fue parte de la dinámica del regreso a clases en la Secundaria General 2, ubicada en Pachuca. El inicio del ciclo escolar 2026-2027 reactivó la movilidad vehicular y económica en la mayor parte de la entidad hidalguense por el regreso a las escuelas de 569 mil 987 alumnos de nivel básico, con mayor carga de tráfico en las llamadas horas pico, cuando inician las clases y en la salida. Al exterior de las escuelas, principalmente en primarias, padres y madres de familia veían alejarse a sus hijos, les deseaban buena suerte en su nuevo curso, algunos les daban la bendición. Los estudiantes expresaban su felicidad al reencontarse con sus compañeros, a quienes saludaban con una sonrisa. Así se vivió el primero de varios días que comprende el ciclo, cuya próxima suspensión de clases será el 16 de septiembre.</t>
+  </si>
+  <si>
+    <t>Con el regreso oficial de 569 mil alumnos en Hidalgo se restableció la habitual saturación vial en Pachuca, marcando escenas cotidianas de desvelo, prisas y reencuentros de estudiantes en la Secundaria General 2.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Primarias locales</t>
+  </si>
+  <si>
+    <t>Sumaron mil 385 casos de violencia el ciclo pasado</t>
+  </si>
+  <si>
+    <t>Durante el ciclo escolar pasado, la Secretaría de Educación Pública de Hidalgo (SEPH) registró mil 385 casos de violencia escolar en todos los niveles educativos del estado, principalmente física, psicológica y sexual, informó el titular de la dependencia, Natividad Castrejón Valdez, quien destacó que más de la mitad de los hechos están resueltos. El funcionario detalló que, del total de casos de violencia escolar del ciclo 2025-2026, los tipos más recurrentes son física, con 380 reportes; psicológica, con 316; sexual, con 163, además de 83 por uso de sustancias ilícitas, 56 de violencia sexual dentro del entorno familiar, 56 por exclusión social, y 53 por llevar artículos prohibidos. Por otra parte, el diputado local José María Alejandro Pérez Ramírez dio a conocer que los protocols de actuación para los maestros del estado en caso de ser señalados por supuestos actos de violencia presentan 80 por ciento de avance. Además, el gobernador Julio Menchaca Salazar se pronunció a favor de establecer un protocolo que permita proteger la integridad de trabajadores del sector educativo ante posibles acusaciones infundadas.</t>
+  </si>
+  <si>
+    <t>El titular de la SEPH reportó que el ciclo escolar 2025-2026 cerró con un total de 1,385 quejas por violencia escolar en Hidalgo, principalmente por agresión física (380) y psicológica (316), avanzando a la par el diseño de un protocolo de defensa docente.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Congreso del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, José María Alejandro Pérez Ramírez, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>DEMOLICIÓN DE PRIMARIA COMENZARÁ EN OCTUBRE</t>
+  </si>
+  <si>
+    <t>En octubre iniciarán los trabajos de demolición y reconstrucción de las primarias Aquiles Serdán y Rafael Ramírez, confirmó el secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, quien señaló que el plantel deberá ser intervenido en su totalidad y que las obras se prolongarán durante todo el ciclo escolar; en tanto, padres de familia solicitaron la reubicación de 693 alumnos y rechazaron las clases virtuales. El funcionario explicó que durante septiembre se deberán definir alternativas para garantizar la continuidad de las actividades académicas mientras se realizan los trabajos, al priorizar que los estudiantes permanezcan en clases presenciales. Castrejón Valdez precisó que la situación de la primaria de Tulancingo es similar a la de la escuela Ignacio Zaragoza, ubicada en Pachuca, que también determinaron demolerla y reconstruirla. Padres y madres de familia de ambos turnos tuvieron una reunión con docentes y directivos, en la que se informó que las actividades escolares se desarrollarán de manera virtual debido a los trabajos. Padres exigieron una alternativa presencial y propusieron que los alumnos sean distribuidos temporalmente en otros planteles.</t>
+  </si>
+  <si>
+    <t>La SEPH confirmó la demolición de las primarias Aquiles Serdán y Rafael Ramírez en Tulancingo a partir de octubre, enfrentando reclamos de padres que rechazan la educación en línea y exigen sedes presenciales alternas para 693 alumnos.</t>
+  </si>
+  <si>
+    <t>Mirely Santos</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Primarias Aquiles Serdán, Rafael Ramírez e Ignacio Zaragoza</t>
+  </si>
+  <si>
+    <t>Incrementa 10 por ciento la eficiencia terminal en el Cobaeh</t>
+  </si>
+  <si>
+    <t>Tizayuca.- Reducir la deserción escolar y lograr que un mayor número de jóvenes concluya su educación media superior se ha convertido en una de las prioridades del Colegio de Bachilleres de Hidalgo (Cobaeh), afirmó su director general, Rubén López Valdez. El funcionario destacó que el subsistema ha registrado 'avances importantes' en materia de eficiencia terminal, al señalar que este indicador ha aumentado cerca de 10 puntos porcentuales, como resultado de las acciones implementadas para evitar que los estudiantes abandonen sus estudios. López Valdez sostuvo que el objetivo de su administración es disminuir la deserción y los índices reprobatorios. De acuerdo con el director general, la reducción del abandono escolar no depende únicamente del trabajo académico, sino también de generar mejores condiciones para que los estudiantes permanezcan en las aulas. Entre estas medidas se encuentra la inversión en laboratorios STEM, la entrega de tabletas y la distribución de libros de texto gratuitos, herramientas que buscan fortalecer el aprendizaje y ofrecer a los jóvenes mayores oportunidades. Actualmente, el Cobaeh cuenta con 133 centros educativos y cerca de 3 mil empleados.</t>
+  </si>
+  <si>
+    <t>Deserción escolar</t>
+  </si>
+  <si>
+    <t>El director general del Cobaeh, Rubén López, reportó que la eficiencia terminal de la institución aumentó cerca de 10 puntos porcentuales gracias a medidas de retención escolar como laboratorios STEM, libros y tabletas.</t>
+  </si>
+  <si>
+    <t>Colegio de Bachilleres del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Rubén López Valdez</t>
+  </si>
+  <si>
+    <t>Cierran calle para pedir que no acepten a hijos de padres problemáticos</t>
+  </si>
+  <si>
+    <t>Ixmiquilpan.- Padres de familia de la primaria Niños Héroes, ubicada en San Nicolás, Ixmiquilpan, cerraron la carretera que comunica a Cardonal y comunidades de la zona norte, la tarde del lunes. El motivo del bloqueo, señalaron, es que no quieren recibir a alumnos cuyos padres son calificados de conflictivos, pero, agregaron, las autoridades escolares quieren imponer que sean aceptados en esa institución educativa. Los inconformes expusieron que ya existen antecedentes de que son problemáticos dichos padres de familia. La semana pasada, de manera formal, mediante un oficio, las autoridades escolares ordenaron a los directivos de la primaria recibir a los estudiantes. Al respecto, los manifestantes mantienen su postura de rechazo y hasta el cierre de esta edición esperaban a las autoridades escolares de la zona. Los tutores colocaron cartulinas afuera de la institución educativa con leyendas como 'No queremos a la señora Brenda Luz Evelino Vázquez'.</t>
+  </si>
+  <si>
+    <t>Ixmiquilpan</t>
+  </si>
+  <si>
+    <t>Padres de familia de la primaria Niños Héroes en San Nicolás, Ixmiquilpan, bloquearon la carretera para protestar contra la imposición oficial de recibir a hijos de tutores considerados conflictivos, nombrando en cartelones a Brenda Luz Evelino.</t>
+  </si>
+  <si>
+    <t>Erika Gutiérrez</t>
+  </si>
+  <si>
+    <t>Escuela Primaria Niños Héroes de Ixmiquilpan, Dirección Escolar de la zona</t>
+  </si>
+  <si>
+    <t>Brenda Luz Evelino Vázquez</t>
+  </si>
+  <si>
+    <t>Prevén 60 mil nuevas viviendas durante el actual gobierno federal</t>
+  </si>
+  <si>
+    <t>El programa federal de vivienda en Hidalgo tiene como meta construir 60 mil viviendas durante el sexenio. El titular de la Unidad de Planeación y Prospectiva de Hidalgo, Miguel Ángel Tello Vargas, destacó que 31 mil 500 casas ya están en proceso de construcción, con una inversión de 18 mil 900 millones de pesos y un costo promedio de 600 mil pesos por vivienda. El proyecto está enfocado en atender a familias que no cotizan ante instituciones de seguridad social y contempla esquemas sin intereses, con pagos ajustados a sus ingresos. Las obras ya marchan en San Agustín Tlaxiaca, Tulancingo, El Arenal, Zempoala, Tepeapulco, Tepeji del Río y Mineral de la Reforma.</t>
+  </si>
+  <si>
+    <t>La Unidad de Planeación y Prospectiva de Hidalgo reportó que la meta de vivienda federal de este sexenio es de 60 mil casas, con 31 mil 500 ya en construcción.</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Tello Vargas, Claudia Sheinbaum Pardo</t>
+  </si>
+  <si>
+    <t>Hidalgo reporta avances en saneamiento y tecnificación como parte del Plan Hídrico</t>
+  </si>
+  <si>
+    <t>El gobierno de Hidalgo reportó avances en las acciones del Plan Hídrico Nacional, calificado por la Comisión Estatal del Agua y Alcantarillado (CEAA) como el proyecto de largo plazo más ambicioso de la entidad en 50 años. El titular de la CEAA, Juan Carlos Chávez González, informó que durante 2025 se destinaron 200 millones de pesos para la primera etapa del saneamiento en Tula, mediante colectores. Para 2026, se tiene prevista una segunda etapa de saneamiento con 320 millones de pesos, además de la nivelación de 5 mil hectáreas agrícolas y el revestimiento de canales en los distritos 03 de Tula, 100 de Alfajayucan y 112 de Ajacuba.</t>
+  </si>
+  <si>
+    <t>Plan Hídrico</t>
+  </si>
+  <si>
+    <t>La CEAA reportó avances de saneamiento de aguas residuales en el río Tula y en la tecnificación de distritos de riego en Tula, Alfajayucan y Ajacuba.</t>
+  </si>
+  <si>
+    <t>Comisión Estatal del Agua y Alcantarillado, Comisión Federal de Electricidad</t>
+  </si>
+  <si>
+    <t>Juan Carlos Chávez González</t>
+  </si>
+  <si>
+    <t>Hidalgo alista regulación para el uso de celulares en educación básica</t>
+  </si>
+  <si>
+    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, informó que el estado avanza en una propuesta para regular el uso de teléfonos celulares y medios digitales entre estudiantes de educación básica, con el objetivo de evitar efectos negativos derivados del uso excesivo de pantallas. Explicó que la medida no busca prohibir los dispositivos, sino establecer reglas sobre edades, momentos y condiciones para su utilización. Advirtió que, a través de Ver Bien para Aprender Mejor, se ha identificado un crecimiento exponencial de problemas visuales en primero y segundo de primaria, relacionados con el tiempo frente a pantallas.</t>
+  </si>
+  <si>
+    <t>Regulación de dispositivos digitales</t>
+  </si>
+  <si>
+    <t>La SEPH diseña una propuesta para regular y normar el uso de celulares en primarias hidalguenses ante el alza desmedida de problemas de visión infantil.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Fideicomiso Ver Bien para Aprender Mejor</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, Claudia Sheinbaum Pardo</t>
+  </si>
+  <si>
+    <t>Gobernador respalda protocolos para resolver conflictos escolares</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar señaló que se debe establecer un equilibrio entre la protección de niñas, niños y adolescentes ante cualquier forma de violencia y la defensa de las maestras y maestros frente a posibles acusaciones infundadas, por lo que respaldó la creación de protocolos claros para atender estos casos. El titular de la SEPH, Natividad Castrejón Valdez, confirmó que el estado trabaja de forma coordinada con el SNTE y el Congreso local en la elaboración de dicho documento.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca respaldó el diseño de protocolos escolares equilibrados que prevengan la violencia infantil y defiendan la reputación de docentes.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Sindicato Nacional de Trabajadores de la Educación, Congreso del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Por condiciones críticas, demolerán la primaria Aquiles Serdán en Tulancingo</t>
+  </si>
+  <si>
+    <t>Ante las condiciones críticas de su infraestructura, la escuela primaria Aquiles Serdán, en Tulancingo, será demolida y reconstruida en su totalidad, un proceso que tomará todo el ciclo escolar. El titular de la SEPH, Natividad Castrejón Valdez, reconoció que se evalúan alternativas urgentes para reubicar a los estudiantes de los turnos matutino y vespertino en espacios presenciales, descartando las clases virtuales tras el rechazo inmediato manifestado por las madres y padres de familia.</t>
+  </si>
+  <si>
+    <t>La SEPH autorizó la demolición total y reconstrucción del plantel Aquiles Serdán en Tulancingo, programando la distribución física de grupos en otras escuelas.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Consejo Nacional de Fomento Educativo</t>
+  </si>
+  <si>
+    <t>Lluvias impiden regreso a primaria de Huehuetla</t>
+  </si>
+  <si>
+    <t>Derivado de las recientes lluvias registradas en Hidalgo, la Escuela Primaria Benito Juárez, ubicada en el municipio de Huehuetla, no abrió sus puertas ayer para el inicio del ciclo escolar 2026-2027, debido a los encharcamientos que se registraron nuevamente en el plantel. El gobernador Julio Menchaca Salazar reconoció que las lluvias del fin de semana provocaron nuevamente la acumulación de agua en el plantel, pese a que previamente se habían realizado labores de limpieza.</t>
+  </si>
+  <si>
+    <t>Graves inundaciones por temporales del fin de semana impidieron el inicio de clases físicas en la primaria Benito Juárez de Huehuetla.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Protección Civil</t>
+  </si>
+  <si>
+    <t>Repatrian desde EU a 2 mil 800 durante el primer semestre</t>
+  </si>
+  <si>
+    <t>Entre enero y junio de 2026, 2 mil 848 hidalguenses fueron repatriados desde Estados Unidos, informó el titular de la Secretaría de Bienestar e Inclusión Social (Sebiso), Ricardo Gómez Moreno, durante la conferencia de prensa del Gobierno de Hidalgo. De acuerdo con datos de la Unidad de Política Migratoria del INM, la entidad ocupa el décimo lugar nacional en intensidad migratoria, con 466 mil 199 hidalguenses radicando principalmente en California, Texas y Florida. En el primer semestre, el estado recibió 863.65 millones de dólares en remesas.</t>
+  </si>
+  <si>
+    <t>Repatriación</t>
+  </si>
+  <si>
+    <t>La Sebiso estatal informó de la repatriación de 2,848 hidalguenses desde Estados Unidos y de un alza de 20 mdd anuales en remesas captadas.</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Instituto Nacional de Migración, Unidad de Política Migratoria</t>
+  </si>
+  <si>
+    <t>Último año registró mil 380 denuncias contra docentes</t>
+  </si>
+  <si>
+    <t>En el pasado ciclo escolar se recibieron mil 383 quejas en contra de docentes; aunque todas se investigaron, se detectaron casos en que se trataba de una calumnia o una mentira tras las indagaciones realizadas por la Procuraduría General de Justicia del Estado de Hidalgo (PGJEH). Luego de que se instrumenten protocolos de actuación ante denuncias emitidas por padres de familia, estudiantes e incluso los propios docentes por temas diversos como violencia, acoso o abuso, Natividad Castrejón Valdez, titular de la Secretaría de Educación Pública en la entidad (SEPH), llamó a que en redes sociales no se linche mediáticamente, pues no se tiene la certeza sobre un hecho. El funcionario explicó que se debe generar conciencia en los jóvenes y la población, que 'no es una broma cuando se recurre a una acción de esa naturaleza, pues hay consecuencias'.</t>
+  </si>
+  <si>
+    <t>La SEPH reportó que durante el pasado ciclo escolar se recibieron mil 383 quejas contra docentes, llamando a evitar linchamientos mediáticos hasta que concluyan las indagaciones penales.</t>
+  </si>
+  <si>
+    <t>Miriam Avilés</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Procuraduría General de Justicia del Estado de Hidalgo, Subprocuraduría de Niños, Niñas y Adolescentes</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, Jorge Sánchez</t>
+  </si>
+  <si>
+    <t>Evitarán riesgos en escuelas ante lluvias</t>
+  </si>
+  <si>
+    <t>Derivado de las recientes lluvias en el estado, un plantel escolar en el municipio de Huehuetla no contó con las condiciones idóneas para iniciar el ciclo escolar, reconoció el gobernador Julio Menchaca Salazar. Pese a esto, apuntó el mandatario estatal que la Secretaría de Educación Pública de Hidalgo (SEPH) lleva a cabo labores de limpieza para habilitar el inmueble y con ello no afectar las actividades del alumnado. De igual manera, garantizó los trabajos para supervisar y vigilar todos los planteles escolares en los 28 municipios más afectados por la vaguada monzónica de octubre del año pasado, ya que las precipitaciones continúan y por ello se tomarán las previsiones adecuadas para evitar riesgos.</t>
+  </si>
+  <si>
+    <t>Atención Afectaciones Por Lluvias</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca informó que una primaria en Huehuetla no pudo iniciar clases por inundaciones causadas por lluvias recientes, por lo que la SEPH realiza labores de desazolve.</t>
+  </si>
+  <si>
+    <t>Teodoro Santos</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Gobierno del Estado de Hidalgo, Protección Civil</t>
+  </si>
+  <si>
+    <t>Tello destaca ofensiva federal al huachicol</t>
+  </si>
+  <si>
+    <t>Las acciones emprendidas por el gobierno federal para combatir el robo de hidrocarburo y el llamado 'huachicol fiscal' representan una ofensiva sin precedentes contra ambos delitos y permitirán generar mejores condiciones de seguridad para Hidalgo, afirmó Miguel Ángel Tello Vargas, titular de la Unidad de Planeación y Prospectiva del estado. Durante una conferencia de prensa, el funcionario sostuvo que el gobierno de la presidenta Claudia Sheinbaum mantiene una estrategia frontal para abatir estas actividades ilícitas, las cuales, dijo, han afectado durante años al país y particularmente a regiones como Tula-Tepeji.</t>
+  </si>
+  <si>
+    <t>Combate Al Huachicol</t>
+  </si>
+  <si>
+    <t>El secretario Miguel Ángel Tello destacó la estrategia federal de Claudia Sheinbaum contra el robo de hidrocarburo y el huachicol fiscal para el resguardo de la región Tula-Tepeji.</t>
+  </si>
+  <si>
+    <t>Unidad de Planeación y Prospectiva, Gobierno Federal, Petróleos Mexicanos, Cruz Azul</t>
+  </si>
+  <si>
+    <t>Meses de espera para buscar desaparecidos</t>
+  </si>
+  <si>
+    <t>Integrantes de Madres Buscadoras de Hidalgo denunciaron retrasos en las investigaciones y búsquedas de personas desaparecidas, al señalar que la Fiscalía Especializada de Delitos de Desaparición de Personas y la Comisión de Búsqueda de Personas del Estado de Hidalgo no atienden los casos de manera oportuna. Las familias afirmaron que en la Fiscalía las investigaciones pueden comenzar hasta cuatro o cinco días después de que se reporta una desaparición, mientras que en la Comisión algunas diligencias de campo tardan meses en ser asignadas.</t>
+  </si>
+  <si>
+    <t>El colectivo Madres Buscadoras denunció retrasos procesales por parte de la PGJEH y dilación de meses en operativos de campo de la Comisión de Búsqueda de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Comisión de Búsqueda de Personas del Estado de Hidalgo, Procuraduría General de Justicia del Estado de Hidalgo, Fiscalía Especializada de Delitos de Desaparición de Personas</t>
+  </si>
+  <si>
+    <t>Francisco García Reyes</t>
+  </si>
+  <si>
+    <t>Fortalece cercanía con 818 menores</t>
+  </si>
+  <si>
+    <t>Durante el período vacacional, la Secretaría de Seguridad Pública de Hidalgo (SSPH) acercó a 818 niños y niñas a la policía estatal mediante actividades recreativas, formativas y de convivencia, como parte de los programas Ciudad Policía y Polivioleta. Entre el 21 de julio y el 14 de agosto, estudiantes de nueve municipios participaron en estas acciones de prevención del delito y proximidad social, con el acompañamiento de personal de la corporación. De este grupo, 783 estudiantes fueron trasladados al parque de conservación de vida silvestre Tuzoofari, ubicado en Epazoyucan.</t>
+  </si>
+  <si>
+    <t>La SSPH implementó los programas Ciudad Policía y Polivioleta con la participación de 818 infantes, culminando con visitas al parque de conservación Tuzoofari.</t>
+  </si>
+  <si>
+    <t>Sebiso impulsa inclusión laboral</t>
+  </si>
+  <si>
+    <t>Con el compromiso de construir un estado más equitativo, accesible y humano, la Secretaría de Bienestar e Inclusión Social (Sebiso), a través de la Dirección de Inclusión, lleva a cabo un taller de habilidades laborales diseñado para promover la autonomía económica de las personas con discapacidad en Hidalgo. Esta iniciativa ofrece a las y los participantes la oportunidad de adentrarse en el sector productivo mediante un programa de formación enfocado en la costura, centrado principalmente en la elaboración artesanal de peluches.</t>
+  </si>
+  <si>
+    <t>La Sebiso realiza talleres presenciales de costura de peluches para brindar habilidades laborales y autonomía financiera a personas hidalguenses con discapacidad.</t>
+  </si>
+  <si>
+    <t>Evalúan los nueve Pueblos Mágicos</t>
+  </si>
+  <si>
+    <t>Como parte de las acciones del gobierno de Julio Menchaca Salazar para consolidar a los Pueblos Mágicos de Hidalgo como destinos competitivos, la Secretaría de Turismo de Hidalgo (Secturh), encabezada por Elizabeth Quintanar Gómez, realizará visitas técnicas a los nueve Pueblos Mágicos de la entidad, a través de la Dirección General de Productos Turísticos y Pueblos Mágicos. Quinta Gómez señaló que las visitas tienen como propósito dar seguimiento al Plan de Fortalecimiento de Pueblos Mágicos y atender las observaciones emitidas por la Secretaría de Turismo del Gobierno de México (Sectur), además de impulsar acciones coordinadas.</t>
+  </si>
+  <si>
+    <t>Pueblos Mágicos</t>
+  </si>
+  <si>
+    <t>La Secturh evaluará mediante inspecciones de campo a los nueve Pueblos Mágicos de Hidalgo, asegurando su competitividad y solventando observaciones de la Sectur federal.</t>
+  </si>
+  <si>
+    <t>Secretaría de Turismo del Estado de Hidalgo, Secretaría de Turismo Federal</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Elizabeth Quintanar Gómez</t>
+  </si>
+  <si>
+    <t>Hidalgo atrae 147 mil mdp en inversiones</t>
+  </si>
+  <si>
+    <t>El estado de Hidalgo es una potencia en marcha que mantendrá una vinculación estratégica entre el gobierno estatal y el sector privado para generar nuevas oportunidades e impulsar el bienestar de las familias hidalguenses, afirmó el gobernador de la entidad, Julio Menchaca Salazar, en el marco del foro 'Es tiempo de Hidalgo, Potencia en Marcha'. Durante su mensaje, el mandatario reconoció la iniciativa del Banco Multiva para generar espacios de diálogo y establecer una comunicación directa entre el sector productivo y el gobierno de Hidalgo, el cual tiene claro que se debe facilitar la llegada de nuevas inversiones, respetando los lineamientos que permitan tener empresas socialmente responsables en la entidad. 'Con el noveno anuncio de inversiones, son 147 mil millones de pesos comprometidos para generar aproximadamente 191 mil empleos.</t>
+  </si>
+  <si>
+    <t>Atracción De Inversiones</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar anunció que en cuatro años de administración se ha alcanzado la cifra histórica de 147 mil mdp en inversiones privadas en la entidad.</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Banco Multiva</t>
+  </si>
+  <si>
+    <t>Implementan patrullajes preventivos ante tormentas</t>
+  </si>
+  <si>
+    <t>Ante las condiciones de lluvia registradas esta tarde en distintos puntos de la entidad, elementos de la policía estatal implementaron recorridos de vigilancia y presencia preventiva.</t>
+  </si>
+  <si>
+    <t>Elementos de la SSPH desplegaron patrullajes de prevención y asistencia vial en diversos puntos vulnerables por las persistentes tormentas de la temporada.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Policía Estatal</t>
+  </si>
+  <si>
+    <t>Destacan sector público y privado oportunidades de inversión en “Es tiempo de Hidalgo”</t>
+  </si>
+  <si>
+    <t>En el marco del foro “Es tiempo de Hidalgo, Potencia en Marcha”, el gobernador Julio Menchaca Salazar, destacó que el estado mantendrá una vinculación estratégica entre el gobierno estatal y el sector privado para generar nuevas oportunidades e impulsar el bienestar a las familias hidalguenses. El mandatario reconoció la iniciativa del Banco Multiva para generar el intercambio de opiniones y establecer una comunicación directa entre el sector productivo y gubernamental, sobre la llegada de nuevas inversiones respetando los lineamientos para contar con empresas responsables en la entidad. Con el noveno anuncio de inversiones, son 147 mil millones de pesos comprometidos para generar aproximadamente 191 mil empleos.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar destacó en el foro 'Es tiempo de Hidalgo' el compromiso de 147 mil mdp en inversiones privadas generadoras de 191 mil empleos.</t>
+  </si>
+  <si>
+    <t>Registran mil 385 casos de violencia escolar; más de la mitad resueltos: Castrejón Valdez</t>
+  </si>
+  <si>
+    <t>Con corte al 27 de agosto de 2026, la SEPH reportó mil 385 casos de violencia escolar durante el ciclo escolar 2025-2026, de los cuales los de mayor incidencia son los relacionados con violencia física (330 casos), psicológica (316), y sexual (163). El titular de la dependencia, Natividad Castrejón Valdez, mencionó que más de la mitad de los casos están resueltos, mientras que los más graves, relacionados con abuso sexual, se dirigen a la PGJEH y a la Procuraduría de Protección de Niñas, Niños, Adolescentes y la Familia para su investigación.</t>
+  </si>
+  <si>
+    <t>El titular de la SEPH, Natividad Castrejón Valdez, reportó mil 385 incidencias de violencia escolar en el ciclo 2025-2026, con más de la mitad de casos resueltos.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Procuraduría General de Justicia del Estado de Hidalgo, Procuraduría de Protección de Niñas, Niños, Adolescentes y la Familia</t>
+  </si>
+  <si>
+    <t>Lokomat: tecnología robótica para terapias de rehabilitación</t>
+  </si>
+  <si>
+    <t>Con una inversión de 18 millones 498 mil 956 pesos, el Sistema DIF Hidalgo incorporó al Centro de Rehabilitación Integral Hidalgo (CRIH) un Lokomat, una tecnología robótica que funcionará para terapias dirigidas a personas con discapacidad a costo accesible. Edda Vite Ramos destacó que esta tecnología permite complementar los tratamientos de acuerdo con las condiciones y necesidades de cada paciente. Actualmente, el CRIH cuenta con 415 pacientes registrados, de los cuales 215 son candidatos. Se gestionaron además tres camionetas de traslado.</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo adquirió un robot de terapia Lokomat de 18.4 mdp para el CRIH de Pachuca, siendo la primera institución pública estatal de la zona centro de México en incorporarlo.</t>
+  </si>
+  <si>
+    <t>Margarita esperó 24 años para volver a abrazar a su hijo</t>
+  </si>
+  <si>
+    <t>“Los sueños sí se cumplen”, declaró Margarita Hernández Galarza con la ilusión de reencontrarse con su hijo, Ricardo Hernández, después de 24 años de estar separados. Ella y su esposo lograron obtener la Visa con el acompañamiento de la Dirección General de Atención al Migrante, como parte del programa “Raíces de Hidalgo”. El señor Margarito García Mayor, originario de Cañada Chica, Ixmiquilpan, también obtuvo su documentación para viajar a Estados Unidos y reencontrarse con su hija tras 23 años. El trámite otorga 10 años de vigencia.</t>
+  </si>
+  <si>
+    <t>Reunificación familiar</t>
+  </si>
+  <si>
+    <t>Mediante el programa Raíces de Hidalgo de la Sebiso, Margarita Hernández y Margarito García obtuvieron visas de diez años de vigencia para reencontrarse en EUA con sus hijos tras más de dos décadas.</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Dirección General de Atención al Migrante</t>
+  </si>
+  <si>
+    <t>Margarita Hernández Galarza, Ricardo Hernández, Margarito García Mayor</t>
+  </si>
+  <si>
+    <t>Vivienda para el Bienestar alcanza 52.5% de su meta en Hidalgo</t>
+  </si>
+  <si>
+    <t>El programa Vivienda para el Bienestar en Hidalgo alcanzó un avance de 52.5 por ciento de su meta actual, con 31 mil 500 viviendas que ya se construyen, de las 60 mil contempladas para el estado. El titular de la Unidad de Planeación y Prospectiva de Hidalgo, Miguel Tello Vargas, informó que cada vivienda tiene un costo de 600 mil pesos, lo que representa una inversión estimada de 18 mil 900 millones de pesos. El programa busca atender necesidades de calidad y servicios habitacionales en la entidad.</t>
+  </si>
+  <si>
+    <t>El titular de Planeación, Miguel Tello Vargas, reportó que el programa Vivienda para el Bienestar registra la edificación de 31 mil 500 casas de un total de 60 mil, representando una inversión de 18 mil 900 mdp.</t>
+  </si>
+  <si>
+    <t>Unidad de Planeación y Prospectiva de Hidalgo, Instituto del Fondo Nacional de la Vivienda para los Trabajadores, Comisión Nacional de Vivienda, Fondo de la Vivienda del ISSSTE</t>
+  </si>
+  <si>
+    <t>Miguel Tello Vargas</t>
+  </si>
+  <si>
+    <t>Siguen desaparecidas en Tianguistengo cinco personas tras lluvias atípicas de 2025</t>
+  </si>
+  <si>
+    <t>José Francisco García Reyes, titular de la CBPHEH, dio a conocer que el organismo continúa la búsqueda de cinco personas que resultaron ilocalizables tras las inundaciones derivadas de la vaguada monzónica en octubre del 2025. Se trata de personas que vivían en el municipio de Tianguistengo, cuatro en la localidad de Chapula y una en Tlacolula. Detalló que de las nueve personas inicialmente reportadas, cuatro ya fueron localizadas (una de ellas identificada sin vida mediante perfiles genéticos).</t>
+  </si>
+  <si>
+    <t>El comisionado de Búsqueda de Hidalgo, José Francisco García Reyes, informó que cinco pobladores de Tianguistengo continúan desaparecidos tras las inundaciones de octubre de 2025.</t>
+  </si>
+  <si>
+    <t>Contemplan 320 mdp para continuar saneamiento del río Tula en Hidalgo</t>
+  </si>
+  <si>
+    <t>Una partida de 320 millones de pesos permitirá continuar este año con el saneamiento del río Tula en Hidalgo, mediante la segunda fase de los trabajos previstos dentro del Plan Nacional Hídrico, informó Juan Carlos Chávez, director general de la CEAA. Los recursos se utilizarán para colectores marginales de aguas residuales, que conducirán el líquido para su tratamiento por parte de la CFE. A esto se sumarán 40 millones para nivelación de parcelas (5 mil hectáreas) y la tecnificación de canales de riego por parte de Conagua.</t>
+  </si>
+  <si>
+    <t>Saneamiento río Tula</t>
+  </si>
+  <si>
+    <t>La CEAA anunció una partida de 320 mdp para la segunda etapa del saneamiento del río Tula mediante colectores de aguas residuales, complementada con obras de Conagua y CFE.</t>
+  </si>
+  <si>
+    <t>Comisión Estatal de Agua y Escantarillado, Comisión Federal de Electricidad, Comisión Nacional del Agua</t>
+  </si>
+  <si>
+    <t>Juan Carlos Chávez</t>
+  </si>
+  <si>
+    <t>Caasim corta servicio de agua potable a gimnasios deudores en Pachuca</t>
+  </si>
+  <si>
+    <t>La Comisión de Agua y Alcantarillado de Sistemas Intermunicipales (Caasim) procedió al corte del suministro de agua potable a diversos gimnasios y centros deportivos exclusivos de la zona metropolitana de Pachuca debido al impago acumulado del servicio por parte de sus propietarios.</t>
+  </si>
+  <si>
+    <t>Adeudos Caasim</t>
+  </si>
+  <si>
+    <t>La Caasim suspendió el servicio de agua a gimnasios de lujo en Pachuca que presentaban adeudos históricos e incumplimiento de pago.</t>
+  </si>
+  <si>
+    <t>Dese por enterado</t>
+  </si>
+  <si>
+    <t>Comisión de Agua y Alcantarillado de Sistemas Intermunicipales (Caasim)</t>
+  </si>
+  <si>
+    <t>En marcha más de 253 mil MDP de inversión federal en Hidalgo</t>
+  </si>
+  <si>
+    <t>El titular de la Unidad de Planeación y Prospectiva, Miguel Ángel Tello Vargas, detalló que hay más de 253 mil millones de pesos federales en marcha en la entidad. Entre los rubros destacan 128 mil mdp para proyectos carreteros y los trenes México-Pachuca y México-Querétaro, 84 mil mdp para modernizar la termoeléctrica Tula II, la coquizadora de Pemex y el saneamiento del río Tula, así como 10 mil mdp para el Podecobi de Zapotlán.</t>
+  </si>
+  <si>
+    <t>Planeación detalló inversiones federales por 253 mil mdp en Hidalgo, abarcando trenes interurbanos, obras energéticas en Tula y polos industriales.</t>
+  </si>
+  <si>
+    <t>Unidad de Planeación y Prospectiva de Hidalgo, Comisión Federal de Electricidad, Petróleos Mexicanos</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Tello Vargas, Claudia Sheinbaum Pardo, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Capacita SSH a profesionales de la salud y estudiantes</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo (SSH) capacitó a 163 profesionales y estudiantes de medicina en prevención, detección temprana y manejo de cáncer cervicouterino. La titular Vanesa Escalante Arroyo resaltó que las Brigadas de la Salud son instrumentos fundamentales para llevar consultas preventivas directas a regiones con barreras geográficas.</t>
+  </si>
+  <si>
+    <t>La SSH instruyó a 163 médicos y alumnos sobre cáncer cervicouterino, impulsando la detección móvil por medio de las Brigadas de la Salud.</t>
+  </si>
+  <si>
+    <t>Secretaría de Salud de Hidalgo</t>
+  </si>
+  <si>
+    <t>En el sexenio de AMLO 170 mil hidalguenses salieron de la pobreza</t>
+  </si>
+  <si>
+    <t>El secretario de Bienestar e Inclusión Social de Hidalgo, Ricardo Gómez Moreno, dio a conocer que conforme a mediciones del Inegi, 170 mil hidalguenses superaron la condición de pobreza extrema y moderada entre 2018 y 2024. Explicó que durante 2025 se canalizaron 22 mil 651 mdp federales para programas de bienestar en Hidalgo, y para 2026 se estima erogar más de 4 mil mdp de presupuesto social estatal, de los cuales la Sebiso coordinará 602 mdp.</t>
+  </si>
+  <si>
+    <t>Índice De Pobreza</t>
+  </si>
+  <si>
+    <t>La Sebiso reportó que 170 mil hidalguenses superaron la pobreza durante el pasado sexenio de López Obrador, previendo 4 mil mdp en apoyos locales en 2026.</t>
+  </si>
+  <si>
+    <t>Oscar Raúl Pérez</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Instituto Nacional de Estadística y Geografía (Inegi)</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno, Andrés Manuel López Obrador, Julio Menchaca Salazar, Claudia Sheinbaum Pardo</t>
+  </si>
+  <si>
+    <t>Hidalgo ha destinado 121 mil MDP a la educación</t>
+  </si>
+  <si>
+    <t>En un acto de inicio de ciclo escolar 2026-2027 en la Secundaria General No. 2 de Pachuca, el gobernador Julio Menchaca Salazar resaltó que se han invertido 121 mil millones de pesos en materia educativa durante su administración, fruto de un eficiente manejo de los recursos del erario, entregando paquetes escolares, calzado, uniformes y útiles gratuitos.</t>
+  </si>
+  <si>
+    <t>Julio Menchaca inauguró el ciclo lectivo en Pachuca, destacando una inversión magisterial acumulada de 121 mil mdp y distribuyendo apoyos escolares.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Gobierno del Estado de Hidalgo, Secundaria General No. 2 de Pachuca</t>
+  </si>
+  <si>
+    <t>Advierten con bloquear la Pachuca-Tulancingo</t>
+  </si>
+  <si>
+    <t>Padres de familia de la escuela primaria Gregorio Torres Quintero, de La Lagunilla, Tulancingo, impidieron el ingreso a clases en el primer día del ciclo escolar debido a que las autoridades de la SEPH incumplieron la sustitución del intendente, plaza vacante desde mayo. Ana Karen Vargas Alvarado, tesorera del comité, advirtió que bloquearán la carretera Pachuca-Tulancingo si no hay solución, reclamando además la falta de renovación contractual de dos docentes que afecta a 132 alumnos.</t>
+  </si>
+  <si>
+    <t>Queja padres de familia</t>
+  </si>
+  <si>
+    <t>Tutores de primaria en Tulancingo tomaron las instalaciones escolares por falta de conserje y profesores suplentes, amenazando con bloquear la carretera federal.</t>
+  </si>
+  <si>
+    <t>Jesús Riveros</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Primaria Gregorio Torres Quintero, Comité de Padres de Familia</t>
+  </si>
+  <si>
+    <t>Ana Karen Vargas Alvarado</t>
+  </si>
+  <si>
+    <t>Policías, apoyan a pachuqueños por torrencial lluvia de ayer</t>
+  </si>
+  <si>
+    <t>Elementos de la policía estatal de la SSPH desplegaron un operativo de patrullaje, auxilio y remolque para conductores y familias cuyos automóviles quedaron varados en charcos e inundaciones pluviales en diversos puntos críticos de Pachuca. Los cuerpos de seguridad instaron al uso responsable de la línea 911 ante emergencias meteorológicas.</t>
+  </si>
+  <si>
+    <t>Agentes de la Policía Estatal de Hidalgo proporcionaron auxilio vial y remorcaron vehículos descompuestos por las severas inundaciones en Pachuca.</t>
+  </si>
+  <si>
+    <t>Regreso a clases fue normal: Gabinete de Seguridad de Hidalgo</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar informó que el operativo del regreso a clases concluyó con saldo blanco. Durante la reunión del Gabinete de Seguridad, se reportó además el desmantelamiento de tres narcotienditas en Atitalaquia y Tolcayuca (deteniendo a cinco hombres con 1,306 dosis de droga), la aprehensión de 16 personas con 984 dosis de estupefacientes en 8 municipios (entre ellos Tizayuca y Pachuca), el decomiso de 7,531 litros de huachicol en Ixmiquilpan y Tlaxcoapan, y la captura de 6 generadores de violencia con armas largas y cortas en la vía Huichapan-Tecozautla. Asimismo, PC atendió la caída de siete árboles y dos barda por el temporal, y se logró la localización de nueve personas con fichas de búsqueda activas.</t>
+  </si>
+  <si>
+    <t>Informe de seguridad</t>
+  </si>
+  <si>
+    <t>El Gabinete de Seguridad de Hidalgo reportó saldo blanco en el regreso escolar y detalló el decomiso de 7,500 litros de huachicol y captura de narcomenudistas.</t>
+  </si>
+  <si>
+    <t>Gabinete de Seguridad de Hidalgo, Secretaría de Seguridad Pública de Hidalgo, Secretaría de la Defensa Nacional, Comisión Federal de Electricidad, Protección Civil, C5i</t>
+  </si>
+  <si>
+    <t>En la Mira: Restricciones sin soluciones en el bulevar Felipe Ángeles</t>
+  </si>
+  <si>
+    <t>Menos de 48 horas de movimiento vehicular habitual bastaron para colapsar nuevamente el bulevar Felipe Ángeles. Todo apunta a que la exclusividad del carril confinado sí ahorca el desahogo de autos en esta vía que es de vital importancia para quienes viajan todos los días a la Ciudad de México o estudian en escuelas del sur de la capital hidalguense. Algo tendrán que hacer para revertir este efecto porque es cuestión de que la ciudadanía llegue al hartazgo con las multas para que nuevamente arda el descontento social. Lo peor es que solo hay restricciones, pero no hay soluciones.</t>
+  </si>
+  <si>
+    <t>Carril confinado</t>
+  </si>
+  <si>
+    <t>Columna que critica las restricciones viales y la aplicación de multas en el bulevar Felipe Ángeles debido a la exclusividad del carril confinado del Tuzobús.</t>
+  </si>
+  <si>
+    <t>En la Mira</t>
+  </si>
+  <si>
+    <t>Secretaría de Movilidad y Transporte</t>
+  </si>
+  <si>
+    <t>En la Mira: Necesidad de regular pantallas y dispositivos en las aulas</t>
+  </si>
+  <si>
+    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón, habló sobre la necesidad de regular el uso de dispositivos electrónicos en las aulas. Aclaró que no se trata de prohibir por prohibir, pero advirtió que han detectado menores cuyo sistema visual aún está en desarrollo y que pasan demasiado tiempo frente a las pantallas, con posibles afectaciones a su salud visual.</t>
+  </si>
+  <si>
+    <t>Columna de opinión que aborda el planteamiento de Natividad Castrejón de normar las pantallas digitales escolares para proteger la salud visual infantil.</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón</t>
+  </si>
+  <si>
+    <t>Gobernador da inicio formal a ciclo escolar</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar encabezó el inicio del ciclo escolar 2026-2027 en la Secundaria General No. 2 de Pachuca, donde destacó que durante cuatro años se han destinado 121 mil millones de pesos a la educación. El mandatario señaló que estos recursos permiten mejorar y garantizar el acceso y la permanencia escolar, además de respaldar a las familias mediante la entrega de becas, uniformes, calzado y útiles. Durante el acto, se entregaron paquetes de uniformes, calzado, útiles escolares y libros de texto. En total, el gobierno estatal distribuirá 500 mil paquetes para estudiantes de educación básica. Natividad Castrejón Valdez informó que regresaron a las aulas 569 mil 987 alumnas y alumnos de educación básica, junto con más de 53 mil docentes, directivos y trabajadores en la entidad.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca inauguró formalmente el ciclo lectivo 2026-2027 en Pachuca, resaltando una inversión de 121 mil mdp y la entrega gratuita de 500 mil paquetes de útiles, uniformes y calzado.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Secundaria General No. 2 de Pachuca</t>
+  </si>
+  <si>
+    <t>Ciclo pasado registró mil 385 casos de violencia escolar</t>
+  </si>
+  <si>
+    <t>La violencia física y psicológica concentró la mayor cantidad de reportes registrados por la Secretaría de Educación Pública de Hidalgo (SEPH) durante el ciclo escolar 2025-2026, con 380 y 316 casos, respectivamente, informó el titular de la dependencia, Natividad Castrejón Valdez. Al corte del 27 de agosto de 2026, la dependencia acumuló mil 385 reportes de distintas formas de violencia, de los cuales más de la mitad ya fueron atendidos y resueltos. Después de los casos de violencia física y psicológica, se contabilizaron 163 reportes de violencia sexual, 83 relacionados con sustancias ilícitas, 56 de violencia sexual dentro de la familia y 56 por exclusión social. La lista también incluye 53 casos por artículos prohibidos, 43 por tendencia suicida, 43 por omisión del personal educativo, 38 relacionados con actividades de riesgo difundidas en entornos digitales y sociales, 35 de violencia cibernética, 32 de violencia familiar y 32 de violencia verbal. Además, hubo reportes por omisión de madres, padres o tutores, autolesiones, violencia económica y moral. El secretario de la SEPH explicó que la SEPH no limita sus registros a hechos ocurridos dentro de los planteles, pues también recibe casos de abandono parental y violencia sexual dentro del hogar. Cuando se trata de agresiones sexuales, los reportes son canalizados de inmediato a la Procuraduría General de Justicia del Estado de Hidalgo (PGJEH).</t>
+  </si>
+  <si>
+    <t>La SEPH reportó mil 385 quejas por violencia escolar en el ciclo 2025-2026 en Hidalgo, lideradas por agresiones físicas (380) y psicológicas (316), con un 50% ya resuelto.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Procuraduría General de Justicia del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Dejan la pobreza 170 mil hidalguenses en 7 años</t>
+  </si>
+  <si>
+    <t>Los programas sociales federales y estatales contribuyeron a reducir la pobreza y las brechas de desigualdad en Hidalgo, donde 170 mil personas salieron de esa condición entre 2018 y 2024, de acuerdo con datos del Instituto Nacional de Estadística y Geografía (Inegi). Durante la conferencia de prensa semanal del gobierno estatal, Ricardo Gómez Moreno, secretario de Bienestar e Inclusión Social, destacó que la coordinación con la administración de la presidenta Claudia Sheinbaum Pardo permitió ampliar la atención a sectores vulnerables. Explicó que desde el inicio del gobierno de Julio Menchaca se diseñaron acciones para llegar a familias que antes no recibían apoyos. Para 2026, Hidalgo destinará más de 4 mil millones de pesos a programas sociales, mientras que la dependencia ejercerá más de 602 millones en apoyos para madres trabajadoras, personas cuidadoras, migrantes, juventudes, adultos mayores y otros grupos. La inversión federal en programas sociales alcanzó 22 mil 651 millones de pesos durante 2025 y anticipó que este año superará esa cantidad. Añadió que los recursos también generan actividad económica en las distintas regiones.</t>
+  </si>
+  <si>
+    <t>La Sebiso hidalguense reportó que 170 mil ciudadanos superaron la condición de pobreza entre 2018 y 2024 gracias a programas sociales, anunciando un presupuesto de 4 mil mdp estatales para 2026.</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Instituto Nacional de Estadística y Geografía</t>
+  </si>
+  <si>
+    <t>Ricardo Gómez Moreno, Julio Menchaca Salazar, Claudia Sheinbaum Pardo</t>
+  </si>
+  <si>
+    <t>Van a demoler primaria en Tulancingo; edificarán otra</t>
+  </si>
+  <si>
+    <t>La escuela primaria Aquiles Serdán, de Tulancingo, deberá ser demolida y reconstruida, proceso que podría extenderse durante todo el ciclo escolar 2026-2027, informó el titular de la Secretaría de Educación Pública de Hidalgo (SEPH), Natividad Castrejón. Castrejón indicó que los alumnos iniciarán clases con normalidad mientras se define una sede de clases presenciales de manera temporal. La postura de la SEPH contrasta con la información recibida por padres de familia de los turnos matutino y vespertino, a quienes se les había planteado la modalidad en línea mientras se efectuaban las obras en el plantel que presenta daños estructurales. Padres rechazaron distribuir a sus hijos en otras escuelas y pidieron que, si resulta indispensable abandonar temporalmente la escuela, se habilite un solo espacio presencial temporal.</t>
+  </si>
+  <si>
+    <t>La SEPH de Hidalgo decretó la demolición completa y reconstrucción de la primaria Aquiles Serdán en Tulancingo por fallas estructurales, buscando habilitar una sede presencial provisional ante la queja de padres por clases virtuales.</t>
+  </si>
+  <si>
+    <t>Octavio Jaimes</t>
   </si>
 </sst>
 </file>
@@ -2030,28 +2027,28 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="F2" s="1">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -2060,28 +2057,28 @@
         <v>13262</v>
       </c>
       <c r="T2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V2" t="s">
         <v>38</v>
       </c>
       <c r="W2" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="X2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="Y2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z2" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="AA2">
         <v>24</v>
       </c>
       <c r="AB2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC2" t="s">
         <v>39</v>
@@ -2090,45 +2087,45 @@
         <v>48</v>
       </c>
       <c r="AF2" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="AG2" t="s">
         <v>41</v>
       </c>
       <c r="AH2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="AI2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="AJ2" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="F3" s="1">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="I3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -2137,75 +2134,75 @@
         <v>13262</v>
       </c>
       <c r="T3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V3" t="s">
         <v>38</v>
       </c>
       <c r="W3" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="X3" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="Y3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z3" t="s">
         <v>47</v>
       </c>
       <c r="AA3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD3" t="s">
         <v>48</v>
       </c>
       <c r="AF3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AG3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="AI3" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="AJ3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="F4" s="1">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="G4">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="I4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -2214,28 +2211,28 @@
         <v>13262</v>
       </c>
       <c r="T4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V4" t="s">
         <v>38</v>
       </c>
       <c r="W4" t="s">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="X4" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z4" t="s">
         <v>114</v>
       </c>
-      <c r="Y4" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>47</v>
-      </c>
       <c r="AA4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC4" t="s">
         <v>39</v>
@@ -2244,45 +2241,45 @@
         <v>48</v>
       </c>
       <c r="AF4" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="AG4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH4" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="AI4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="AJ4" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F5" s="1">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -2291,28 +2288,28 @@
         <v>13262</v>
       </c>
       <c r="T5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V5" t="s">
         <v>38</v>
       </c>
       <c r="W5" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="X5" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="Y5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z5" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="AA5">
         <v>24</v>
       </c>
       <c r="AB5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC5" t="s">
         <v>39</v>
@@ -2321,42 +2318,42 @@
         <v>48</v>
       </c>
       <c r="AF5" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="AG5" t="s">
         <v>41</v>
       </c>
       <c r="AH5" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="AI5" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="AJ5" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F6" s="1">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="I6" t="s">
         <v>54</v>
@@ -2368,16 +2365,16 @@
         <v>13262</v>
       </c>
       <c r="T6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V6" t="s">
         <v>38</v>
       </c>
       <c r="W6" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="X6" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="Y6" t="s">
         <v>69</v>
@@ -2386,54 +2383,57 @@
         <v>47</v>
       </c>
       <c r="AA6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC6" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD6" t="s">
         <v>48</v>
       </c>
       <c r="AF6" t="s">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="AG6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH6" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="AI6" t="s">
-        <v>124</v>
+        <v>135</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="F7" s="1">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -2442,16 +2442,16 @@
         <v>13262</v>
       </c>
       <c r="T7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V7" t="s">
         <v>38</v>
       </c>
       <c r="W7" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="X7" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="Y7" t="s">
         <v>69</v>
@@ -2460,10 +2460,10 @@
         <v>47</v>
       </c>
       <c r="AA7">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC7" t="s">
         <v>39</v>
@@ -2472,45 +2472,45 @@
         <v>48</v>
       </c>
       <c r="AF7" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="AG7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AI7" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="AJ7" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="F8" s="1">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="I8" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -2519,28 +2519,28 @@
         <v>13262</v>
       </c>
       <c r="T8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V8" t="s">
         <v>38</v>
       </c>
       <c r="W8" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="X8" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="Y8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="Z8" t="s">
         <v>47</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC8" t="s">
         <v>48</v>
@@ -2549,39 +2549,42 @@
         <v>48</v>
       </c>
       <c r="AF8" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="AG8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH8" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="AI8" t="s">
-        <v>134</v>
+        <v>147</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="F9" s="1">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H9" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="I9" t="s">
         <v>54</v>
@@ -2593,72 +2596,75 @@
         <v>13262</v>
       </c>
       <c r="T9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V9" t="s">
         <v>38</v>
       </c>
       <c r="W9" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="X9" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="Y9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z9" t="s">
         <v>47</v>
       </c>
       <c r="AA9">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC9" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD9" t="s">
         <v>48</v>
       </c>
       <c r="AF9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AG9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH9" t="s">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="AI9" t="s">
-        <v>124</v>
+        <v>153</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="E10" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="F10" s="1">
-        <v>46263</v>
+        <v>46266</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I10" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -2667,72 +2673,75 @@
         <v>13262</v>
       </c>
       <c r="T10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V10" t="s">
         <v>38</v>
       </c>
       <c r="W10" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="X10" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="Y10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="Z10" t="s">
         <v>47</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC10" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD10" t="s">
         <v>48</v>
       </c>
       <c r="AF10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AG10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH10" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="AI10" t="s">
-        <v>142</v>
+        <v>157</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="E11" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="F11" s="1">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H11" t="s">
-        <v>145</v>
+        <v>76</v>
       </c>
       <c r="I11" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -2741,28 +2750,28 @@
         <v>13262</v>
       </c>
       <c r="T11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V11" t="s">
         <v>38</v>
       </c>
       <c r="W11" t="s">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="X11" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="Y11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z11" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="AA11">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC11" t="s">
         <v>39</v>
@@ -2771,45 +2780,45 @@
         <v>48</v>
       </c>
       <c r="AF11" t="s">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="AG11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH11" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="AI11" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="AJ11" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="E12" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="F12" s="1">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I12" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2818,19 +2827,19 @@
         <v>13262</v>
       </c>
       <c r="T12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V12" t="s">
         <v>38</v>
       </c>
       <c r="W12" t="s">
-        <v>153</v>
+        <v>92</v>
       </c>
       <c r="X12" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="Y12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z12" t="s">
         <v>47</v>
@@ -2839,7 +2848,7 @@
         <v>20</v>
       </c>
       <c r="AB12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC12" t="s">
         <v>48</v>
@@ -2848,45 +2857,45 @@
         <v>48</v>
       </c>
       <c r="AF12" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="AG12" t="s">
         <v>41</v>
       </c>
       <c r="AH12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AI12" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="AJ12" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="E13" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="F13" s="1">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="G13">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="I13" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -2895,28 +2904,28 @@
         <v>13262</v>
       </c>
       <c r="T13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V13" t="s">
         <v>38</v>
       </c>
       <c r="W13" t="s">
-        <v>161</v>
+        <v>92</v>
       </c>
       <c r="X13" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="Y13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z13" t="s">
         <v>47</v>
       </c>
       <c r="AA13">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC13" t="s">
         <v>39</v>
@@ -2925,42 +2934,45 @@
         <v>48</v>
       </c>
       <c r="AF13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG13" t="s">
         <v>41</v>
       </c>
       <c r="AH13" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="AI13" t="s">
-        <v>163</v>
+        <v>171</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E14" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F14" s="1">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="G14">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H14" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="I14" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -2969,28 +2981,28 @@
         <v>13262</v>
       </c>
       <c r="T14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V14" t="s">
         <v>38</v>
       </c>
       <c r="W14" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="X14" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="Y14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z14" t="s">
         <v>47</v>
       </c>
       <c r="AA14">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AB14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC14" t="s">
         <v>39</v>
@@ -2999,42 +3011,45 @@
         <v>48</v>
       </c>
       <c r="AF14" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s">
         <v>41</v>
       </c>
       <c r="AH14" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="AI14" t="s">
-        <v>169</v>
+        <v>178</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="F15" s="1">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="G15">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I15" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -3043,19 +3058,19 @@
         <v>13262</v>
       </c>
       <c r="T15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V15" t="s">
         <v>38</v>
       </c>
       <c r="W15" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="X15" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="Y15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z15" t="s">
         <v>47</v>
@@ -3064,7 +3079,7 @@
         <v>20</v>
       </c>
       <c r="AB15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC15" t="s">
         <v>39</v>
@@ -3073,39 +3088,42 @@
         <v>48</v>
       </c>
       <c r="AF15" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="AG15" t="s">
         <v>41</v>
       </c>
       <c r="AH15" t="s">
-        <v>174</v>
+        <v>52</v>
       </c>
       <c r="AI15" t="s">
-        <v>175</v>
+        <v>184</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="E16" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="F16" s="1">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" t="s">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="I16" t="s">
         <v>54</v>
@@ -3117,28 +3135,28 @@
         <v>13262</v>
       </c>
       <c r="T16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V16" t="s">
         <v>38</v>
       </c>
       <c r="W16" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="X16" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="Y16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z16" t="s">
         <v>47</v>
       </c>
       <c r="AA16">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC16" t="s">
         <v>39</v>
@@ -3147,45 +3165,45 @@
         <v>48</v>
       </c>
       <c r="AF16" t="s">
-        <v>61</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s">
         <v>41</v>
       </c>
       <c r="AH16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="AI16" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="AJ16" t="s">
-        <v>182</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E17" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F17" s="1">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I17" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -3194,16 +3212,16 @@
         <v>13262</v>
       </c>
       <c r="T17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V17" t="s">
         <v>38</v>
       </c>
       <c r="W17" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="X17" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="Y17" t="s">
         <v>69</v>
@@ -3215,7 +3233,7 @@
         <v>12</v>
       </c>
       <c r="AB17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC17" t="s">
         <v>39</v>
@@ -3224,42 +3242,45 @@
         <v>48</v>
       </c>
       <c r="AF17" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AG17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH17" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AI17" t="s">
-        <v>187</v>
+        <v>195</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="E18" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="F18" s="1">
-        <v>46264</v>
+        <v>46266</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H18" t="s">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I18" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -3268,28 +3289,28 @@
         <v>13262</v>
       </c>
       <c r="T18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V18" t="s">
         <v>38</v>
       </c>
       <c r="W18" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="X18" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="Y18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z18" t="s">
         <v>47</v>
       </c>
       <c r="AA18">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC18" t="s">
         <v>39</v>
@@ -3298,45 +3319,45 @@
         <v>48</v>
       </c>
       <c r="AF18" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s">
         <v>41</v>
       </c>
       <c r="AH18" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="AI18" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="AJ18" t="s">
-        <v>194</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E19" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F19" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I19" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -3345,16 +3366,16 @@
         <v>13262</v>
       </c>
       <c r="T19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V19" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="W19" t="s">
-        <v>197</v>
+        <v>88</v>
       </c>
       <c r="X19" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="Y19" t="s">
         <v>69</v>
@@ -3363,57 +3384,57 @@
         <v>47</v>
       </c>
       <c r="AA19">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AB19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC19" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD19" t="s">
         <v>48</v>
       </c>
       <c r="AF19" t="s">
-        <v>74</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="AH19" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="AI19" t="s">
-        <v>199</v>
+        <v>109</v>
       </c>
       <c r="AJ19" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E20" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F20" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" t="s">
         <v>50</v>
       </c>
       <c r="I20" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -3422,19 +3443,19 @@
         <v>13262</v>
       </c>
       <c r="T20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V20" t="s">
         <v>38</v>
       </c>
       <c r="W20" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="X20" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="Y20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z20" t="s">
         <v>47</v>
@@ -3443,7 +3464,7 @@
         <v>20</v>
       </c>
       <c r="AB20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC20" t="s">
         <v>39</v>
@@ -3452,45 +3473,45 @@
         <v>48</v>
       </c>
       <c r="AF20" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="AG20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH20" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="AI20" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AJ20" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E21" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F21" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H21" t="s">
         <v>50</v>
       </c>
       <c r="I21" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -3499,19 +3520,19 @@
         <v>13262</v>
       </c>
       <c r="T21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V21" t="s">
-        <v>208</v>
+        <v>38</v>
       </c>
       <c r="W21" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="X21" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Y21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z21" t="s">
         <v>47</v>
@@ -3520,7 +3541,7 @@
         <v>20</v>
       </c>
       <c r="AB21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC21" t="s">
         <v>39</v>
@@ -3529,45 +3550,45 @@
         <v>48</v>
       </c>
       <c r="AF21" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AG21" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH21" t="s">
-        <v>88</v>
+        <v>215</v>
       </c>
       <c r="AI21" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AJ21" t="s">
-        <v>45</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E22" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F22" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H22" t="s">
         <v>50</v>
       </c>
       <c r="I22" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -3576,28 +3597,28 @@
         <v>13262</v>
       </c>
       <c r="T22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V22" t="s">
         <v>38</v>
       </c>
       <c r="W22" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="X22" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="Y22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z22" t="s">
         <v>47</v>
       </c>
       <c r="AA22">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC22" t="s">
         <v>39</v>
@@ -3606,45 +3627,45 @@
         <v>48</v>
       </c>
       <c r="AF22" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AG22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH22" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AI22" t="s">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="AJ22" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E23" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F23" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H23" t="s">
         <v>50</v>
       </c>
       <c r="I23" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="R23">
         <v>1</v>
@@ -3653,72 +3674,72 @@
         <v>13262</v>
       </c>
       <c r="T23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V23" t="s">
         <v>38</v>
       </c>
       <c r="W23" t="s">
-        <v>220</v>
+        <v>92</v>
       </c>
       <c r="X23" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Y23" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="Z23" t="s">
         <v>47</v>
       </c>
       <c r="AA23">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC23" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD23" t="s">
         <v>48</v>
       </c>
       <c r="AF23" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AG23" t="s">
         <v>41</v>
       </c>
       <c r="AH23" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AI23" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AJ23" t="s">
-        <v>223</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E24" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F24" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H24" t="s">
-        <v>226</v>
+        <v>74</v>
       </c>
       <c r="I24" t="s">
         <v>46</v>
@@ -3730,19 +3751,19 @@
         <v>13262</v>
       </c>
       <c r="T24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V24" t="s">
         <v>38</v>
       </c>
       <c r="W24" t="s">
-        <v>227</v>
+        <v>80</v>
       </c>
       <c r="X24" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Y24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z24" t="s">
         <v>47</v>
@@ -3751,16 +3772,16 @@
         <v>20</v>
       </c>
       <c r="AB24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC24" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD24" t="s">
         <v>48</v>
       </c>
       <c r="AF24" t="s">
-        <v>229</v>
+        <v>65</v>
       </c>
       <c r="AG24" t="s">
         <v>41</v>
@@ -3772,30 +3793,30 @@
         <v>230</v>
       </c>
       <c r="AJ24" t="s">
-        <v>68</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E25" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F25" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H25" t="s">
-        <v>233</v>
+        <v>53</v>
       </c>
       <c r="I25" t="s">
         <v>46</v>
@@ -3807,19 +3828,19 @@
         <v>13262</v>
       </c>
       <c r="T25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V25" t="s">
         <v>38</v>
       </c>
       <c r="W25" t="s">
+        <v>101</v>
+      </c>
+      <c r="X25" t="s">
         <v>234</v>
       </c>
-      <c r="X25" t="s">
-        <v>235</v>
-      </c>
       <c r="Y25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z25" t="s">
         <v>47</v>
@@ -3828,7 +3849,7 @@
         <v>20</v>
       </c>
       <c r="AB25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC25" t="s">
         <v>39</v>
@@ -3837,7 +3858,7 @@
         <v>48</v>
       </c>
       <c r="AF25" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s">
         <v>41</v>
@@ -3846,36 +3867,36 @@
         <v>51</v>
       </c>
       <c r="AI25" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AJ25" t="s">
-        <v>238</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E26" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F26" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H26" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="I26" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R26">
         <v>1</v>
@@ -3884,19 +3905,19 @@
         <v>13262</v>
       </c>
       <c r="T26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V26" t="s">
         <v>38</v>
       </c>
       <c r="W26" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="X26" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Y26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z26" t="s">
         <v>47</v>
@@ -3905,7 +3926,7 @@
         <v>20</v>
       </c>
       <c r="AB26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC26" t="s">
         <v>39</v>
@@ -3914,7 +3935,7 @@
         <v>48</v>
       </c>
       <c r="AF26" t="s">
-        <v>229</v>
+        <v>107</v>
       </c>
       <c r="AG26" t="s">
         <v>41</v>
@@ -3923,36 +3944,36 @@
         <v>51</v>
       </c>
       <c r="AI26" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AJ26" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s">
+        <v>243</v>
+      </c>
+      <c r="E27" t="s">
+        <v>244</v>
+      </c>
+      <c r="F27" s="1">
+        <v>46266</v>
+      </c>
+      <c r="G27">
+        <v>9</v>
+      </c>
+      <c r="H27" t="s">
         <v>245</v>
       </c>
-      <c r="E27" t="s">
-        <v>246</v>
-      </c>
-      <c r="F27" s="1">
-        <v>46265</v>
-      </c>
-      <c r="G27">
-        <v>2</v>
-      </c>
-      <c r="H27" t="s">
-        <v>77</v>
-      </c>
       <c r="I27" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R27">
         <v>1</v>
@@ -3961,75 +3982,75 @@
         <v>13262</v>
       </c>
       <c r="T27" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V27" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="W27" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="X27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Y27" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="Z27" t="s">
         <v>47</v>
       </c>
       <c r="AA27">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC27" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD27" t="s">
         <v>48</v>
       </c>
       <c r="AF27" t="s">
+        <v>247</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI27" t="s">
         <v>248</v>
       </c>
-      <c r="AG27" t="s">
-        <v>91</v>
-      </c>
-      <c r="AH27" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI27" t="s">
+      <c r="AJ27" t="s">
         <v>249</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D28" t="s">
+        <v>250</v>
+      </c>
+      <c r="E28" t="s">
         <v>251</v>
       </c>
-      <c r="E28" t="s">
-        <v>252</v>
-      </c>
       <c r="F28" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I28" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R28">
         <v>1</v>
@@ -4038,19 +4059,19 @@
         <v>13262</v>
       </c>
       <c r="T28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V28" t="s">
         <v>38</v>
       </c>
       <c r="W28" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="X28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Y28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z28" t="s">
         <v>47</v>
@@ -4059,7 +4080,7 @@
         <v>20</v>
       </c>
       <c r="AB28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC28" t="s">
         <v>39</v>
@@ -4068,42 +4089,42 @@
         <v>48</v>
       </c>
       <c r="AF28" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AG28" t="s">
         <v>41</v>
       </c>
       <c r="AH28" t="s">
-        <v>254</v>
+        <v>62</v>
       </c>
       <c r="AI28" t="s">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="AJ28" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D29" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E29" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F29" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I29" t="s">
         <v>54</v>
@@ -4115,19 +4136,19 @@
         <v>13262</v>
       </c>
       <c r="T29" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V29" t="s">
         <v>38</v>
       </c>
       <c r="W29" t="s">
-        <v>197</v>
+        <v>256</v>
       </c>
       <c r="X29" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="Y29" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z29" t="s">
         <v>47</v>
@@ -4136,7 +4157,7 @@
         <v>24</v>
       </c>
       <c r="AB29" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC29" t="s">
         <v>39</v>
@@ -4145,42 +4166,42 @@
         <v>48</v>
       </c>
       <c r="AF29" t="s">
-        <v>260</v>
+        <v>86</v>
       </c>
       <c r="AG29" t="s">
         <v>41</v>
       </c>
       <c r="AH29" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI29" t="s">
-        <v>96</v>
+        <v>258</v>
       </c>
       <c r="AJ29" t="s">
-        <v>87</v>
+        <v>259</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D30" t="s">
+        <v>260</v>
+      </c>
+      <c r="E30" t="s">
         <v>261</v>
       </c>
-      <c r="E30" t="s">
-        <v>262</v>
-      </c>
       <c r="F30" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I30" t="s">
         <v>55</v>
@@ -4192,75 +4213,75 @@
         <v>13262</v>
       </c>
       <c r="T30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V30" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="W30" t="s">
-        <v>97</v>
+        <v>262</v>
       </c>
       <c r="X30" t="s">
         <v>263</v>
       </c>
       <c r="Y30" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="Z30" t="s">
         <v>47</v>
       </c>
       <c r="AA30">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AB30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC30" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD30" t="s">
         <v>48</v>
       </c>
       <c r="AF30" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>41</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI30" t="s">
         <v>264</v>
       </c>
-      <c r="AG30" t="s">
-        <v>91</v>
-      </c>
-      <c r="AH30" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI30" t="s">
+      <c r="AJ30" t="s">
         <v>265</v>
-      </c>
-      <c r="AJ30" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D31" t="s">
+        <v>266</v>
+      </c>
+      <c r="E31" t="s">
         <v>267</v>
       </c>
-      <c r="E31" t="s">
-        <v>268</v>
-      </c>
       <c r="F31" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G31">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H31" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="I31" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -4269,19 +4290,19 @@
         <v>13262</v>
       </c>
       <c r="T31" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V31" t="s">
         <v>38</v>
       </c>
       <c r="W31" t="s">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="X31" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="Y31" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z31" t="s">
         <v>47</v>
@@ -4290,51 +4311,54 @@
         <v>20</v>
       </c>
       <c r="AB31" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC31" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD31" t="s">
         <v>48</v>
       </c>
       <c r="AF31" t="s">
-        <v>271</v>
+        <v>86</v>
       </c>
       <c r="AG31" t="s">
         <v>41</v>
       </c>
       <c r="AH31" t="s">
-        <v>254</v>
+        <v>42</v>
       </c>
       <c r="AI31" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D32" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E32" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F32" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G32">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H32" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I32" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R32">
         <v>1</v>
@@ -4343,72 +4367,72 @@
         <v>13262</v>
       </c>
       <c r="T32" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V32" t="s">
         <v>38</v>
       </c>
       <c r="W32" t="s">
-        <v>275</v>
+        <v>101</v>
       </c>
       <c r="X32" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="Y32" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z32" t="s">
         <v>47</v>
       </c>
       <c r="AA32">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB32" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC32" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD32" t="s">
         <v>48</v>
       </c>
       <c r="AF32" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="AG32" t="s">
         <v>41</v>
       </c>
       <c r="AH32" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="AI32" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="AJ32" t="s">
-        <v>278</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D33" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="E33" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F33" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G33">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H33" t="s">
-        <v>233</v>
+        <v>97</v>
       </c>
       <c r="I33" t="s">
         <v>46</v>
@@ -4420,16 +4444,16 @@
         <v>13262</v>
       </c>
       <c r="T33" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V33" t="s">
         <v>38</v>
       </c>
       <c r="W33" t="s">
-        <v>220</v>
+        <v>98</v>
       </c>
       <c r="X33" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="Y33" t="s">
         <v>69</v>
@@ -4438,57 +4462,57 @@
         <v>47</v>
       </c>
       <c r="AA33">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC33" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD33" t="s">
         <v>48</v>
       </c>
       <c r="AF33" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="AG33" t="s">
         <v>41</v>
       </c>
       <c r="AH33" t="s">
-        <v>254</v>
+        <v>51</v>
       </c>
       <c r="AI33" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AJ33" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D34" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E34" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F34" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="H34" t="s">
-        <v>285</v>
+        <v>74</v>
       </c>
       <c r="I34" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -4497,19 +4521,19 @@
         <v>13262</v>
       </c>
       <c r="T34" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V34" t="s">
         <v>38</v>
       </c>
       <c r="W34" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="X34" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="Y34" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z34" t="s">
         <v>47</v>
@@ -4518,54 +4542,54 @@
         <v>20</v>
       </c>
       <c r="AB34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC34" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD34" t="s">
         <v>48</v>
       </c>
       <c r="AF34" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="AG34" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH34" t="s">
-        <v>174</v>
+        <v>58</v>
       </c>
       <c r="AI34" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="AJ34" t="s">
-        <v>289</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D35" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="E35" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="F35" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G35">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H35" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I35" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="R35">
         <v>1</v>
@@ -4574,19 +4598,19 @@
         <v>13262</v>
       </c>
       <c r="T35" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V35" t="s">
         <v>38</v>
       </c>
       <c r="W35" t="s">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="X35" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="Y35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z35" t="s">
         <v>47</v>
@@ -4595,7 +4619,7 @@
         <v>24</v>
       </c>
       <c r="AB35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC35" t="s">
         <v>39</v>
@@ -4604,7 +4628,7 @@
         <v>48</v>
       </c>
       <c r="AF35" t="s">
-        <v>67</v>
+        <v>286</v>
       </c>
       <c r="AG35" t="s">
         <v>41</v>
@@ -4613,33 +4637,33 @@
         <v>51</v>
       </c>
       <c r="AI35" t="s">
-        <v>96</v>
+        <v>287</v>
       </c>
       <c r="AJ35" t="s">
-        <v>87</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D36" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E36" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F36" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G36">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H36" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="I36" t="s">
         <v>46</v>
@@ -4651,19 +4675,19 @@
         <v>13262</v>
       </c>
       <c r="T36" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V36" t="s">
         <v>38</v>
       </c>
       <c r="W36" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="X36" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="Y36" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z36" t="s">
         <v>47</v>
@@ -4672,54 +4696,54 @@
         <v>20</v>
       </c>
       <c r="AB36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC36" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD36" t="s">
         <v>48</v>
       </c>
       <c r="AF36" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG36" t="s">
         <v>41</v>
       </c>
       <c r="AH36" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="AI36" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AJ36" t="s">
-        <v>299</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E37" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="F37" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G37">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H37" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I37" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -4728,69 +4752,72 @@
         <v>13262</v>
       </c>
       <c r="T37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V37" t="s">
         <v>38</v>
       </c>
       <c r="W37" t="s">
-        <v>95</v>
+        <v>297</v>
       </c>
       <c r="X37" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="Y37" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z37" t="s">
         <v>47</v>
       </c>
       <c r="AA37">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC37" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD37" t="s">
         <v>48</v>
       </c>
       <c r="AF37" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="AG37" t="s">
         <v>41</v>
       </c>
       <c r="AH37" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="AI37" t="s">
-        <v>304</v>
+        <v>299</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D38" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="E38" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="F38" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I38" t="s">
         <v>46</v>
@@ -4802,19 +4829,19 @@
         <v>13262</v>
       </c>
       <c r="T38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V38" t="s">
         <v>38</v>
       </c>
       <c r="W38" t="s">
-        <v>220</v>
+        <v>96</v>
       </c>
       <c r="X38" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="Y38" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z38" t="s">
         <v>47</v>
@@ -4823,54 +4850,54 @@
         <v>20</v>
       </c>
       <c r="AB38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC38" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD38" t="s">
         <v>48</v>
       </c>
       <c r="AF38" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AG38" t="s">
         <v>41</v>
       </c>
       <c r="AH38" t="s">
-        <v>254</v>
+        <v>103</v>
       </c>
       <c r="AI38" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="AJ38" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D39" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="E39" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="F39" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H39" t="s">
-        <v>233</v>
+        <v>74</v>
       </c>
       <c r="I39" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R39">
         <v>1</v>
@@ -4879,16 +4906,16 @@
         <v>13262</v>
       </c>
       <c r="T39" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V39" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="W39" t="s">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="X39" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="Y39" t="s">
         <v>69</v>
@@ -4897,10 +4924,10 @@
         <v>47</v>
       </c>
       <c r="AA39">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB39" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC39" t="s">
         <v>39</v>
@@ -4909,45 +4936,42 @@
         <v>48</v>
       </c>
       <c r="AF39" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="AG39" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH39" t="s">
-        <v>254</v>
+        <v>49</v>
       </c>
       <c r="AI39" t="s">
-        <v>313</v>
-      </c>
-      <c r="AJ39" t="s">
-        <v>217</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="E40" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="F40" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H40" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R40">
         <v>1</v>
@@ -4956,16 +4980,16 @@
         <v>13262</v>
       </c>
       <c r="T40" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V40" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="W40" t="s">
-        <v>86</v>
+        <v>193</v>
       </c>
       <c r="X40" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="Y40" t="s">
         <v>69</v>
@@ -4974,54 +4998,51 @@
         <v>47</v>
       </c>
       <c r="AA40">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC40" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD40" t="s">
         <v>48</v>
       </c>
       <c r="AF40" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="AG40" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH40" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="AI40" t="s">
-        <v>317</v>
-      </c>
-      <c r="AJ40" t="s">
-        <v>87</v>
+        <v>195</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D41" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="E41" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="F41" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H41" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I41" t="s">
         <v>54</v>
@@ -5033,16 +5054,16 @@
         <v>13262</v>
       </c>
       <c r="T41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V41" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="W41" t="s">
-        <v>197</v>
+        <v>313</v>
       </c>
       <c r="X41" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="Y41" t="s">
         <v>69</v>
@@ -5051,57 +5072,57 @@
         <v>47</v>
       </c>
       <c r="AA41">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB41" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC41" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD41" t="s">
         <v>48</v>
       </c>
       <c r="AF41" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="AG41" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH41" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="AI41" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AJ41" t="s">
-        <v>98</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D42" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F42" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G42">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H42" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I42" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="R42">
         <v>1</v>
@@ -5110,19 +5131,19 @@
         <v>13262</v>
       </c>
       <c r="T42" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V42" t="s">
         <v>38</v>
       </c>
       <c r="W42" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="X42" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="Y42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z42" t="s">
         <v>47</v>
@@ -5131,7 +5152,7 @@
         <v>20</v>
       </c>
       <c r="AB42" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC42" t="s">
         <v>39</v>
@@ -5140,45 +5161,45 @@
         <v>48</v>
       </c>
       <c r="AF42" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="AG42" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AH42" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="AI42" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="AJ42" t="s">
-        <v>327</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B43" t="s">
         <v>60</v>
       </c>
       <c r="D43" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="E43" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F43" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H43" t="s">
-        <v>285</v>
+        <v>74</v>
       </c>
       <c r="I43" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="R43">
         <v>1</v>
@@ -5187,16 +5208,16 @@
         <v>13262</v>
       </c>
       <c r="T43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V43" t="s">
         <v>38</v>
       </c>
       <c r="W43" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="X43" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="Y43" t="s">
         <v>69</v>
@@ -5205,10 +5226,10 @@
         <v>47</v>
       </c>
       <c r="AA43">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB43" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC43" t="s">
         <v>39</v>
@@ -5223,39 +5244,36 @@
         <v>43</v>
       </c>
       <c r="AH43" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="AI43" t="s">
-        <v>331</v>
-      </c>
-      <c r="AJ43" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E44" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="F44" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="I44" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R44">
         <v>1</v>
@@ -5264,19 +5282,19 @@
         <v>13262</v>
       </c>
       <c r="T44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V44" t="s">
         <v>38</v>
       </c>
       <c r="W44" t="s">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="X44" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="Y44" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z44" t="s">
         <v>47</v>
@@ -5285,54 +5303,54 @@
         <v>20</v>
       </c>
       <c r="AB44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC44" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD44" t="s">
         <v>48</v>
       </c>
       <c r="AF44" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="AG44" t="s">
         <v>41</v>
       </c>
       <c r="AH44" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="AI44" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="AJ44" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="E45" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F45" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="I45" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -5341,28 +5359,28 @@
         <v>13262</v>
       </c>
       <c r="T45" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V45" t="s">
         <v>38</v>
       </c>
       <c r="W45" t="s">
-        <v>339</v>
+        <v>80</v>
       </c>
       <c r="X45" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="Y45" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="Z45" t="s">
         <v>47</v>
       </c>
       <c r="AA45">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AB45" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC45" t="s">
         <v>39</v>
@@ -5371,45 +5389,45 @@
         <v>48</v>
       </c>
       <c r="AF45" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="AG45" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH45" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="AI45" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="AJ45" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="D46" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="E46" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="F46" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G46">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H46" t="s">
         <v>50</v>
       </c>
       <c r="I46" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R46">
         <v>1</v>
@@ -5418,16 +5436,16 @@
         <v>13262</v>
       </c>
       <c r="T46" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V46" t="s">
         <v>38</v>
       </c>
       <c r="W46" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="X46" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="Y46" t="s">
         <v>69</v>
@@ -5436,10 +5454,10 @@
         <v>47</v>
       </c>
       <c r="AA46">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB46" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC46" t="s">
         <v>39</v>
@@ -5448,45 +5466,45 @@
         <v>48</v>
       </c>
       <c r="AF46" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="AG46" t="s">
         <v>41</v>
       </c>
       <c r="AH46" t="s">
-        <v>254</v>
+        <v>215</v>
       </c>
       <c r="AI46" t="s">
-        <v>345</v>
+        <v>216</v>
       </c>
       <c r="AJ46" t="s">
-        <v>346</v>
+        <v>217</v>
       </c>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="E47" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="F47" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G47">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H47" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="I47" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R47">
         <v>1</v>
@@ -5495,28 +5513,28 @@
         <v>13262</v>
       </c>
       <c r="T47" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V47" t="s">
         <v>38</v>
       </c>
       <c r="W47" t="s">
-        <v>220</v>
+        <v>338</v>
       </c>
       <c r="X47" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="Y47" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z47" t="s">
         <v>47</v>
       </c>
       <c r="AA47">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB47" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC47" t="s">
         <v>39</v>
@@ -5525,45 +5543,45 @@
         <v>48</v>
       </c>
       <c r="AF47" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AG47" t="s">
         <v>41</v>
       </c>
       <c r="AH47" t="s">
-        <v>254</v>
+        <v>58</v>
       </c>
       <c r="AI47" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AJ47" t="s">
-        <v>217</v>
+        <v>341</v>
       </c>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B48" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="D48" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="E48" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="F48" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G48">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H48" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I48" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R48">
         <v>1</v>
@@ -5572,19 +5590,19 @@
         <v>13262</v>
       </c>
       <c r="T48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V48" t="s">
         <v>38</v>
       </c>
       <c r="W48" t="s">
-        <v>353</v>
+        <v>198</v>
       </c>
       <c r="X48" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="Y48" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z48" t="s">
         <v>47</v>
@@ -5593,51 +5611,51 @@
         <v>20</v>
       </c>
       <c r="AB48" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC48" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD48" t="s">
         <v>48</v>
       </c>
       <c r="AF48" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="AG48" t="s">
         <v>41</v>
       </c>
       <c r="AH48" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="AI48" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="AJ48" t="s">
-        <v>45</v>
+        <v>346</v>
       </c>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B49" t="s">
         <v>23</v>
       </c>
       <c r="D49" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="E49" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="F49" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H49" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I49" t="s">
         <v>46</v>
@@ -5649,19 +5667,19 @@
         <v>13262</v>
       </c>
       <c r="T49" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V49" t="s">
         <v>38</v>
       </c>
       <c r="W49" t="s">
-        <v>220</v>
+        <v>96</v>
       </c>
       <c r="X49" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="Y49" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z49" t="s">
         <v>47</v>
@@ -5670,7 +5688,7 @@
         <v>20</v>
       </c>
       <c r="AB49" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC49" t="s">
         <v>39</v>
@@ -5679,42 +5697,42 @@
         <v>48</v>
       </c>
       <c r="AF49" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="AG49" t="s">
         <v>41</v>
       </c>
       <c r="AH49" t="s">
-        <v>254</v>
+        <v>103</v>
       </c>
       <c r="AI49" t="s">
-        <v>345</v>
+        <v>105</v>
       </c>
       <c r="AJ49" t="s">
-        <v>359</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B50" t="s">
         <v>23</v>
       </c>
       <c r="D50" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="E50" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="F50" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I50" t="s">
         <v>54</v>
@@ -5726,28 +5744,28 @@
         <v>13262</v>
       </c>
       <c r="T50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V50" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="W50" t="s">
-        <v>197</v>
+        <v>352</v>
       </c>
       <c r="X50" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="Y50" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z50" t="s">
         <v>47</v>
       </c>
       <c r="AA50">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB50" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC50" t="s">
         <v>39</v>
@@ -5756,45 +5774,45 @@
         <v>48</v>
       </c>
       <c r="AF50" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="AG50" t="s">
         <v>41</v>
       </c>
       <c r="AH50" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s">
-        <v>199</v>
+        <v>354</v>
       </c>
       <c r="AJ50" t="s">
-        <v>87</v>
+        <v>355</v>
       </c>
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D51" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="E51" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="F51" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G51">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H51" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="I51" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="R51">
         <v>1</v>
@@ -5803,16 +5821,16 @@
         <v>13262</v>
       </c>
       <c r="T51" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V51" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="W51" t="s">
-        <v>179</v>
+        <v>358</v>
       </c>
       <c r="X51" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="Y51" t="s">
         <v>69</v>
@@ -5821,54 +5839,51 @@
         <v>47</v>
       </c>
       <c r="AA51">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB51" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC51" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD51" t="s">
         <v>48</v>
       </c>
       <c r="AF51" t="s">
-        <v>43</v>
+        <v>360</v>
       </c>
       <c r="AG51" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="AH51" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s">
-        <v>366</v>
-      </c>
-      <c r="AJ51" t="s">
-        <v>182</v>
+        <v>361</v>
       </c>
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D52" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E52" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="F52" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G52">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H52" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="I52" t="s">
         <v>54</v>
@@ -5880,31 +5895,31 @@
         <v>13262</v>
       </c>
       <c r="T52" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V52" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="W52" t="s">
-        <v>369</v>
+        <v>319</v>
       </c>
       <c r="X52" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="Y52" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z52" t="s">
         <v>47</v>
       </c>
       <c r="AA52">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB52" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC52" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD52" t="s">
         <v>48</v>
@@ -5916,36 +5931,36 @@
         <v>43</v>
       </c>
       <c r="AH52" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="AI52" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="AJ52" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D53" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="E53" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="F53" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G53">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H53" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="I53" t="s">
         <v>54</v>
@@ -5957,28 +5972,28 @@
         <v>13262</v>
       </c>
       <c r="T53" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V53" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="W53" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="X53" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="Y53" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z53" t="s">
         <v>47</v>
       </c>
       <c r="AA53">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB53" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC53" t="s">
         <v>39</v>
@@ -5993,36 +6008,36 @@
         <v>43</v>
       </c>
       <c r="AH53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AI53" t="s">
-        <v>321</v>
+        <v>370</v>
       </c>
       <c r="AJ53" t="s">
-        <v>98</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D54" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="E54" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="F54" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G54">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H54" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I54" t="s">
         <v>54</v>
@@ -6034,28 +6049,28 @@
         <v>13262</v>
       </c>
       <c r="T54" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V54" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="W54" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="X54" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="Y54" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z54" t="s">
         <v>47</v>
       </c>
       <c r="AA54">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB54" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC54" t="s">
         <v>39</v>
@@ -6064,39 +6079,39 @@
         <v>48</v>
       </c>
       <c r="AF54" t="s">
-        <v>43</v>
+        <v>375</v>
       </c>
       <c r="AG54" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH54" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="AI54" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AJ54" t="s">
-        <v>68</v>
+        <v>377</v>
       </c>
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D55" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E55" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F55" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G55">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H55" t="s">
         <v>50</v>
@@ -6111,19 +6126,19 @@
         <v>13262</v>
       </c>
       <c r="T55" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V55" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="W55" t="s">
-        <v>94</v>
+        <v>220</v>
       </c>
       <c r="X55" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="Y55" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z55" t="s">
         <v>47</v>
@@ -6132,7 +6147,7 @@
         <v>20</v>
       </c>
       <c r="AB55" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC55" t="s">
         <v>39</v>
@@ -6147,39 +6162,39 @@
         <v>43</v>
       </c>
       <c r="AH55" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="AI55" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AJ55" t="s">
-        <v>385</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D56" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E56" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F56" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G56">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H56" t="s">
-        <v>285</v>
+        <v>53</v>
       </c>
       <c r="I56" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -6188,19 +6203,19 @@
         <v>13262</v>
       </c>
       <c r="T56" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V56" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="W56" t="s">
-        <v>286</v>
+        <v>384</v>
       </c>
       <c r="X56" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="Y56" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z56" t="s">
         <v>47</v>
@@ -6209,7 +6224,7 @@
         <v>20</v>
       </c>
       <c r="AB56" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC56" t="s">
         <v>39</v>
@@ -6218,42 +6233,42 @@
         <v>48</v>
       </c>
       <c r="AF56" t="s">
-        <v>43</v>
+        <v>386</v>
       </c>
       <c r="AG56" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH56" t="s">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="AI56" t="s">
-        <v>331</v>
+        <v>387</v>
       </c>
       <c r="AJ56" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D57" t="s">
+        <v>389</v>
+      </c>
+      <c r="E57" t="s">
         <v>390</v>
       </c>
-      <c r="E57" t="s">
-        <v>391</v>
-      </c>
       <c r="F57" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G57">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H57" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="I57" t="s">
         <v>54</v>
@@ -6265,31 +6280,31 @@
         <v>13262</v>
       </c>
       <c r="T57" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V57" t="s">
         <v>38</v>
       </c>
       <c r="W57" t="s">
-        <v>392</v>
+        <v>291</v>
       </c>
       <c r="X57" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Y57" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="Z57" t="s">
         <v>47</v>
       </c>
       <c r="AA57">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB57" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC57" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD57" t="s">
         <v>48</v>
@@ -6301,33 +6316,33 @@
         <v>43</v>
       </c>
       <c r="AH57" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AI57" t="s">
-        <v>394</v>
+        <v>325</v>
       </c>
     </row>
     <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D58" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E58" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F58" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G58">
         <v>8</v>
       </c>
       <c r="H58" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I58" t="s">
         <v>54</v>
@@ -6339,31 +6354,31 @@
         <v>13262</v>
       </c>
       <c r="T58" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V58" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="W58" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="X58" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="Y58" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z58" t="s">
         <v>47</v>
       </c>
       <c r="AA58">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB58" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC58" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="AD58" t="s">
         <v>48</v>
@@ -6375,39 +6390,39 @@
         <v>43</v>
       </c>
       <c r="AH58" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="AI58" t="s">
-        <v>99</v>
+        <v>396</v>
       </c>
       <c r="AJ58" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B59" t="s">
         <v>64</v>
       </c>
       <c r="D59" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E59" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F59" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G59">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H59" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="I59" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="R59">
         <v>1</v>
@@ -6416,19 +6431,19 @@
         <v>13262</v>
       </c>
       <c r="T59" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V59" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="W59" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="X59" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="Y59" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Z59" t="s">
         <v>47</v>
@@ -6437,51 +6452,48 @@
         <v>10</v>
       </c>
       <c r="AB59" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC59" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD59" t="s">
         <v>48</v>
       </c>
       <c r="AF59" t="s">
-        <v>43</v>
+        <v>401</v>
       </c>
       <c r="AG59" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="AH59" t="s">
-        <v>49</v>
+        <v>152</v>
       </c>
       <c r="AI59" t="s">
-        <v>403</v>
-      </c>
-      <c r="AJ59" t="s">
-        <v>68</v>
+        <v>402</v>
       </c>
     </row>
     <row r="60" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B60" t="s">
         <v>64</v>
       </c>
       <c r="D60" t="s">
+        <v>403</v>
+      </c>
+      <c r="E60" t="s">
         <v>404</v>
       </c>
-      <c r="E60" t="s">
-        <v>405</v>
-      </c>
       <c r="F60" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G60">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H60" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="I60" t="s">
         <v>55</v>
@@ -6493,16 +6505,16 @@
         <v>13262</v>
       </c>
       <c r="T60" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V60" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="W60" t="s">
-        <v>123</v>
+        <v>262</v>
       </c>
       <c r="X60" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Y60" t="s">
         <v>69</v>
@@ -6511,57 +6523,57 @@
         <v>47</v>
       </c>
       <c r="AA60">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB60" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC60" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="AD60" t="s">
         <v>48</v>
       </c>
       <c r="AF60" t="s">
-        <v>43</v>
+        <v>401</v>
       </c>
       <c r="AG60" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="AH60" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AI60" t="s">
-        <v>407</v>
+        <v>87</v>
       </c>
       <c r="AJ60" t="s">
-        <v>79</v>
+        <v>406</v>
       </c>
     </row>
     <row r="61" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B61" t="s">
         <v>64</v>
       </c>
       <c r="D61" t="s">
+        <v>407</v>
+      </c>
+      <c r="E61" t="s">
         <v>408</v>
       </c>
-      <c r="E61" t="s">
-        <v>409</v>
-      </c>
       <c r="F61" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G61">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H61" t="s">
-        <v>410</v>
+        <v>50</v>
       </c>
       <c r="I61" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R61">
         <v>1</v>
@@ -6570,19 +6582,19 @@
         <v>13262</v>
       </c>
       <c r="T61" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V61" t="s">
         <v>38</v>
       </c>
       <c r="W61" t="s">
-        <v>411</v>
+        <v>92</v>
       </c>
       <c r="X61" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="Y61" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z61" t="s">
         <v>47</v>
@@ -6591,7 +6603,7 @@
         <v>20</v>
       </c>
       <c r="AB61" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC61" t="s">
         <v>39</v>
@@ -6606,33 +6618,36 @@
         <v>43</v>
       </c>
       <c r="AH61" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="AI61" t="s">
-        <v>413</v>
+        <v>410</v>
+      </c>
+      <c r="AJ61" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="62" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B62" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D62" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E62" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F62" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H62" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="I62" t="s">
         <v>46</v>
@@ -6644,28 +6659,28 @@
         <v>13262</v>
       </c>
       <c r="T62" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V62" t="s">
         <v>38</v>
       </c>
       <c r="W62" t="s">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="X62" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="Y62" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z62" t="s">
         <v>47</v>
       </c>
       <c r="AA62">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AB62" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC62" t="s">
         <v>39</v>
@@ -6674,39 +6689,42 @@
         <v>48</v>
       </c>
       <c r="AF62" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="AG62" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AH62" t="s">
-        <v>254</v>
+        <v>51</v>
       </c>
       <c r="AI62" t="s">
-        <v>345</v>
+        <v>414</v>
+      </c>
+      <c r="AJ62" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="63" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B63" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D63" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E63" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F63" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H63" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I63" t="s">
         <v>54</v>
@@ -6718,28 +6736,28 @@
         <v>13262</v>
       </c>
       <c r="T63" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V63" t="s">
         <v>38</v>
       </c>
       <c r="W63" t="s">
-        <v>197</v>
+        <v>373</v>
       </c>
       <c r="X63" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Y63" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z63" t="s">
         <v>47</v>
       </c>
       <c r="AA63">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB63" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC63" t="s">
         <v>39</v>
@@ -6754,21 +6772,21 @@
         <v>43</v>
       </c>
       <c r="AH63" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="AI63" t="s">
-        <v>96</v>
+        <v>418</v>
       </c>
       <c r="AJ63" t="s">
-        <v>87</v>
+        <v>419</v>
       </c>
     </row>
     <row r="64" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D64" t="s">
         <v>420</v>
@@ -6777,16 +6795,16 @@
         <v>421</v>
       </c>
       <c r="F64" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="G64">
         <v>5</v>
       </c>
       <c r="H64" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I64" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="R64">
         <v>1</v>
@@ -6795,28 +6813,28 @@
         <v>13262</v>
       </c>
       <c r="T64" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="V64" t="s">
         <v>38</v>
       </c>
       <c r="W64" t="s">
+        <v>101</v>
+      </c>
+      <c r="X64" t="s">
         <v>422</v>
       </c>
-      <c r="X64" t="s">
-        <v>423</v>
-      </c>
       <c r="Y64" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z64" t="s">
         <v>47</v>
       </c>
       <c r="AA64">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB64" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC64" t="s">
         <v>39</v>
@@ -6825,7 +6843,7 @@
         <v>48</v>
       </c>
       <c r="AF64" t="s">
-        <v>85</v>
+        <v>423</v>
       </c>
       <c r="AG64" t="s">
         <v>41</v>
@@ -6834,10 +6852,10 @@
         <v>51</v>
       </c>
       <c r="AI64" t="s">
-        <v>424</v>
+        <v>87</v>
       </c>
       <c r="AJ64" t="s">
-        <v>87</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D651E5-608D-4337-B570-5DF6B9C79481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D2D738-17E0-476C-8873-A550C85D09EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="455">
   <si>
     <t>Canal</t>
   </si>
@@ -160,9 +160,6 @@
     <t>Criterio</t>
   </si>
   <si>
-    <t>Muy positivo</t>
-  </si>
-  <si>
     <t>Noticia</t>
   </si>
   <si>
@@ -184,9 +181,6 @@
     <t>PGJEH</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Negativo</t>
   </si>
   <si>
@@ -268,15 +262,9 @@
     <t>Carmen Hernández</t>
   </si>
   <si>
-    <t>Turismo</t>
-  </si>
-  <si>
     <t>Hidalgo</t>
   </si>
   <si>
-    <t>Boletín</t>
-  </si>
-  <si>
     <t>Huejutla</t>
   </si>
   <si>
@@ -289,9 +277,6 @@
     <t>Erick Perales</t>
   </si>
   <si>
-    <t>Violencia Escolar</t>
-  </si>
-  <si>
     <t>Natividad Castrejón Valdez</t>
   </si>
   <si>
@@ -304,1021 +289,1129 @@
     <t>Columnista</t>
   </si>
   <si>
-    <t>Tizayuca</t>
-  </si>
-  <si>
-    <t>Dulce Castillo</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo</t>
-  </si>
-  <si>
-    <t>Temas varios</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo</t>
-  </si>
-  <si>
     <t>Marco Cerón</t>
   </si>
   <si>
     <t>Berenice Gamboa</t>
   </si>
   <si>
-    <t>Regreso A Clases</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Instituto Hidalguense de Educación</t>
-  </si>
-  <si>
-    <t>Desapariciones</t>
-  </si>
-  <si>
-    <t>José Francisco García Reyes</t>
-  </si>
-  <si>
-    <t>Búsqueda de personas</t>
-  </si>
-  <si>
-    <t>Huehuetla</t>
-  </si>
-  <si>
-    <t>Afectaciones Por Lluvias</t>
-  </si>
-  <si>
-    <t>María Antonieta Islas</t>
-  </si>
-  <si>
-    <t>Tianguistengo</t>
-  </si>
-  <si>
     <t>Reconstrucción de escuela</t>
   </si>
   <si>
-    <t>Martha Sáenz</t>
-  </si>
-  <si>
-    <t>Segobh</t>
-  </si>
-  <si>
     <t>Blanca Soriano</t>
   </si>
   <si>
-    <t>Comisión de Búsqueda de Personas del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Quejas padres de familia</t>
-  </si>
-  <si>
-    <t>Javier Quezada</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Gobierno del Estado de Hidalgo</t>
-  </si>
-  <si>
     <t>Gobierno del Estado de Hidalgo</t>
   </si>
   <si>
-    <t>Convivencia Escolar</t>
-  </si>
-  <si>
-    <t>Inician ciclo escolar 569 mil 987 alumnos</t>
-  </si>
-  <si>
-    <t>Entre prisas, tráfico, ambulantaje, aplausos y dinámicas para un ameno regreso a las aulas, inició el ciclo escolar 2026-2027, que este año recibió a 569 mil 987 estudiantes del nivel básico. Desde las primeras horas del día, calles y avenidas con escuelas de nivel básico volvieron a llenarse de niñas, niños y adolescentes con uniformes y mochilas al hombro. Este año, el arranque oficial se realizó en la Escuela Secundaria General 2, en Pachuca, donde cientos de alumnos se dieron cita en el auditorio para presenciar la inauguración del ciclo por parte de autoridades estatales. Durante el evento, la alumna María Fernanda González consideró el regreso como una oportunidad de reencuentro y metas nuevas.</t>
-  </si>
-  <si>
-    <t>Un total de 569 mil 987 estudiantes de nivel básico iniciaron el ciclo escolar 2026-2027 en Hidalgo, con protocolo oficial en Pachuca.</t>
-  </si>
-  <si>
-    <t>Portadas</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, María Fernanda González Ramírez</t>
-  </si>
-  <si>
-    <t>“Equilibrado”, deberá ser el protocolo que defienda a docentes</t>
-  </si>
-  <si>
-    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, afirmó que se sigue trabajando en un protocolo “equilibrado” entre la protección al derecho de las infancias y de los docentes, luego de las quejas o demandas por presunta violencia escolar en contra de los maestros. El mandatario estatal afirmó que, en algunas ocasiones, los maestros han sido sujetos de acusaciones sin sustento, por lo que el Congreso local ya trabaja en ese tema de forma responsable. Reiteró que los protocolos son para definir los pasos a seguir ante hechos que se pudieran suscitar y que no dependen estrictamente de la opinión de una persona.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar precisó que el Congreso local diseña un protocolo de protección equilibrada para el sector docente.</t>
-  </si>
-  <si>
-    <t>Congreso del Estado de Hidalgo, Secretaría de Educación Pública de Hidalgo</t>
-  </si>
-  <si>
-    <t>Se dispara 76% violencia escolar en Hidalgo: SEPH</t>
-  </si>
-  <si>
-    <t>El ciclo escolar 2025-2026 registró un aumento del 76 por ciento en los reportes de presunta violencia escolar, en comparación con el curso previo, que registró 787 incidentes. En el periodo recién concluido se contabilizaron mil 385 reportes en todos los niveles educativos, según dio a conocer el secretario de educación estatal, Natividad Castrejón Valdez. Las tres principales causas reportadas ante el REPAEVE fueron violencia física (380 casos), violencia psicológica (316 casos) y violencia sexual (163 reportes). Los casos que involucran a docentes representan el 29.1 por ciento del total (alrededor de 400 hechos), concentrándose la mayoría de las quejas en primarias generales con 614 reportes.</t>
-  </si>
-  <si>
-    <t>La SEPH reportó un incremento del 76% de reportes de violencia escolar en el ciclo 2025-2026, con un total de 1,385 incidencias registradas.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Registro Estatal de Prevención, Atención y Erradicación de la Violencia Escolar (REPAEVE), Procuraduría General de Justicia de Hidalgo</t>
-  </si>
-  <si>
-    <t>Frena proyectos la falta de socialización en región Tula: Tello</t>
-  </si>
-  <si>
-    <t>El secretario de Planeación y Prospectiva de Hidalgo, Miguel Ángel Tello Vargas, reconoció que la falta de socialización y la politización de los proyectos han sido algunos de los principales obstáculos para concretar obras en la región Tula-Tepeji. Al referirse a proyectos viales de Nopala, viviendas en Atotonilco de Tula y el control del lirio acuático, destacó que se requiere mayor diálogo. Subrayó que los pobladores tienen razón en muchas cosas y hay que escucharlos, anunciando que preparan nuevas inversiones para diversificar la vocación de Tula de una ciudad industrial hacia un destino turístico.</t>
-  </si>
-  <si>
-    <t>Socialización de obra</t>
-  </si>
-  <si>
-    <t>El secretario Miguel Ángel Tello admitió rezagos en obras por fallas de socialización en la región Tula, promoviendo mayor apertura vecinal.</t>
-  </si>
-  <si>
-    <t>Lizania Zavala</t>
-  </si>
-  <si>
-    <t>Unidad de Planeación y Prospectiva, Comisión Nacional del Agua (Conagua)</t>
-  </si>
-  <si>
     <t>Miguel Ángel Tello Vargas</t>
   </si>
   <si>
-    <t>Hidalgo recibió remesas por 863 mdd en 6 meses</t>
-  </si>
-  <si>
-    <t>Hidalgo recibió 863.65 millones de dólares por concepto de remesas durante el primer semestre de 2026, un incremento de 20.20 millones de dólares frente a los 843.45 millones registrados en el mismo periodo de 2025. El secretario de Bienestar e Inclusión Social, Ricardo Gómez Moreno, informó que el recurso es una fuente vital para miles de familias en municipios de origen migratorio como Tulancingo, Ixmiquilpan, Pachuca, Actopan y Zacualtipán. Detalló que 466 mil 199 hidalguenses radican en Estados Unidos, concentrados principalmente en California, Texas y Florida.</t>
-  </si>
-  <si>
-    <t>Remesas</t>
-  </si>
-  <si>
-    <t>La Sebiso estatal informó la captación de 863.65 mdd por concepto de remesas familiares en el primer semestre de 2026.</t>
-  </si>
-  <si>
-    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Instituto Nacional de Migración (Unidad de Política Migratoria)</t>
-  </si>
-  <si>
-    <t>Ricardo Gómez Moreno</t>
-  </si>
-  <si>
-    <t>Zanja frente al panteón: una trampa bajo el agua</t>
-  </si>
-  <si>
-    <t>La temporada de lluvias convirtió un punto del bulevar del Minero, a la altura del Panteón Municipal de Pachuca, en una trampa para automovilistas, donde tres vehículos han caído en una canaleta encharcada en los últimos días. El 27 de agosto, una camioneta y una Urvan de transporte público quedaron varadas frente al Cereso, repitiéndose la incidencia el 29 de agosto con otro automóvil particular. Ante ello, la Policía Estatal y el H. Cuerpo de Bomberos de la SSPH implementaron recorridos de auxilio por lluvias torrenciales en el bulevar Felipe Ángeles, Explanada, Real Toledo y Bulevar El Minero.</t>
-  </si>
-  <si>
-    <t>Lluvias torrenciales provocaron que tres unidades cayeran en una zanja cubierta por encharcamientos en Pachuca, desplegándose auxilio de la SSPH.</t>
-  </si>
-  <si>
     <t>Luis Godínez</t>
   </si>
   <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Policía Estatal, Cuerpo de Bomberos de Hidalgo</t>
-  </si>
-  <si>
-    <t>Aumentan denuncias por violencia familiar y robo en Molango</t>
-  </si>
-  <si>
-    <t>El registro de denuncias por el delito de violencia familiar en Molango de Escamilla creció 140 por ciento de enero a julio de 2026, en comparación con el mismo periodo de la anualidad pasada; además, también presentaron un incremento de 142 por ciento las denuncias por robo, y las de narcomenudeo, 133 por ciento. De acuerdo con el Índice Delictivo del SESNSP, los primeros siete meses de 2025 sumaron cinco casos de violencia familiar, mientras que en el mismo periodo de este año van 12 denuncias formales ante la autoridad jurisdiccional.</t>
-  </si>
-  <si>
-    <t>Molango</t>
-  </si>
-  <si>
-    <t>Incidencia Delictiva</t>
-  </si>
-  <si>
-    <t>La incidencia delictiva del SESNSP reportó alzas de 140% en violencia intrafamiliar y del 142% en robos en el municipio de Molango.</t>
-  </si>
-  <si>
-    <t>Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública (SESNSP), Procuraduría General de Justicia del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Buscan diseñar plan de movilidad para Huejutla</t>
-  </si>
-  <si>
-    <t>El gobierno de Hidalgo emitió una licitación para la elaboración del Plan Integral de Movilidad Urbana Sustentable (PIMUS) del municipio de Huejutla de Reyes, a solicitud de la Secretaría de Movilidad y Transporte (Semot). De acuerdo con las bases del procedimiento EA-913003989-N0518-2026, se busca un proveedor para desarrollar el estudio que delimitará el territorio y abarcará aspectos demográficos, topografía, hidrología y análisis socioeconómicos de Huejutla e Ixmiquilpan.</t>
-  </si>
-  <si>
-    <t>Movilidad sustentable</t>
-  </si>
-  <si>
-    <t>La Semot licitó la elaboración del Plan Integral de Movilidad Urbana (PIMUS) para planear el desarrollo de transporte en Huejutla e Ixmiquilpan.</t>
-  </si>
-  <si>
-    <t>Semot</t>
-  </si>
-  <si>
-    <t>Secretaría de Movilidad y Transporte de Hidalgo, Instituto Nacional de Estadística y Geografía (Inegi)</t>
-  </si>
-  <si>
-    <t>Desapariciones aumentan durante agosto en Hidalgo</t>
-  </si>
-  <si>
-    <t>Un hombre sin vida, quien contaba con ficha de búsqueda, y 13 reportes de personas desaparecidas fueron el saldo que dejó el mes de agosto en Hidalgo, de acuerdo con la plataforma administrada por la Secretaría de Gobierno y la Comisión Nacional de Búsqueda (CNB). En cuanto a las personas no localizadas, ocho corresponden a hombres y cinco a mujeres, concentrándose en Tizayuca, Pachuca y Atitalaquia. En contraste, 29 personas fueron ubicadas con vida (18 mujeres, 11 hombres) principalmente en Mineral de la Reforma y Pachuca.</t>
-  </si>
-  <si>
-    <t>La CNB y la Segobh reportaron un acumulado de 13 personas desaparecidas en agosto, localizándose además a 29 ciudadanos con vida.</t>
-  </si>
-  <si>
-    <t>Secretaría de Gobierno de Hidalgo, Comisión Nacional de Búsqueda (CNB), Comisión de Búsqueda de Personas del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Ser foráneo en la UTHH, un sacrificio económico</t>
-  </si>
-  <si>
-    <t>Para los estudiantes foráneos universitarios, acudir diariamente a clases representa un esfuerzo económico adicional para sus familias, debido al costo del transporte, alimentación y, en algunos casos, el pago de una renta en Huejutla. Alumnos de Chalma gastan 50 pesos diarios en pasaje, Patricio de Tempoal requiere 94 pesos, Alfredo de Calnali gasta 75 pesos por viaje y Yami de Chicontepec gasta hasta 180 pesos de pasaje de ida y vuelta. A esto se suma el gasto de comida de 90 pesos y rentas de hasta 2,500 pesos.</t>
-  </si>
-  <si>
-    <t>Estudiantes foráneos de la UTHH de Huejutla afrontan un alto desgaste de hasta 180 pesos de pasaje diario para cursar sus estudios presenciales.</t>
-  </si>
-  <si>
     <t>Salomón Hernández</t>
   </si>
   <si>
-    <t>Universidad Tecnológica de la Huasteca Hidalguense (UTHH)</t>
-  </si>
-  <si>
-    <t>Amaury N, Patricio N, Alfredo N, Yami N</t>
-  </si>
-  <si>
-    <t>Advierten paterfamilias que no aceptarán clases en línea</t>
-  </si>
-  <si>
-    <t>Madres y padres de alumnos de la escuela primaria Aquiles Serdán en Tulancingo informaron que sus hijos recibirán clases presenciales en el plantel durante un mes y medio aproximadamente, lapso en el que las autoridades educativas buscarán una sede alterna para continuar bajo la misma modalidad, ya que no permitirán la enseñanza en línea. Los paterfamilias se opusieron al formato virtual anunciado por la dirección tras emitirse el dictamen de demolición física de la escuela y reconstrucción de aulas.</t>
-  </si>
-  <si>
-    <t>Padres de familia de Tulancingo rechazaron clases virtuales, logrando clases presenciales provisionales antes de la demolición del plantel.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Servicios Regionales</t>
-  </si>
-  <si>
-    <t>Inaugura Menchaca el inicio de clases</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar presidió en Pachuca el inicio escolar del ciclo 2026-2027 en la Secundaria General No. 2, destacando una inversión educativa de 121 mil millones de pesos acumulada en cuatro años. El titular de la SEPH, Natividad Castrejón Valdez, reportó el retorno de 967 mil alumnos en 8 mil 717 planteles, destacando la asignación de apoyos Rita Cetina de 2 mil 500 pesos y la futura regulación del uso excesivo de celulares y dispositivos digitales en las escuelas por problemas de ansiedad y de salud visual.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca presidió el inicio escolar 2026-2027 en Pachuca, destacando una inversión educativa de 121 mil mdp en cuatro años, mientras la SEPH analiza regular el uso de celulares.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Instituto Hidalguense de Educación, Sindicato Nacional de Trabajadores de la Educación</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Natividad Castrejón Valdez, Said Vargas Sáenz, Alberto García Palacios</t>
-  </si>
-  <si>
-    <t>Cítnova financia 220 becas de investigación</t>
-  </si>
-  <si>
-    <t>El Consejo de Ciencia, Tecnología e Innovación de Hidalgo (Citnova) publicó el padrón de 220 becarios beneficiados por el programa Fondo Hidalgo para estudios de posgrado e investigaciones de base tecnológica. La convocatoria asignará montos de 250 mil y 20 mil pesos para el desarrollo de proyectos en la UAEH, UPP, ITESA e institutos tecnológicos, favoreciendo además a investigadores del Congreso del Estado de Hidalgo, Saderh, la Secretaría de Bienestar e Inclusión Social y diversos ayuntamientos.</t>
-  </si>
-  <si>
-    <t>Becas De Posgrado</t>
-  </si>
-  <si>
-    <t>El Citnova publicó los beneficiarios de 220 becas de posgrado y proyectos tecnológicos del programa Fondo Hidalgo, apoyando a investigadores, ayuntamientos, Saderh y Congreso local.</t>
-  </si>
-  <si>
     <t>Sonia Nochebuena</t>
   </si>
   <si>
-    <t>Consejo de Ciencia, Tecnología e Innovación de Hidalgo, Secretaría de Agricultura y Desarrollo Rural de Hidalgo, Congreso del Estado de Hidalgo, Instituto Hidalguense de Educación</t>
-  </si>
-  <si>
-    <t>Zianya Gómez Soto, Gabriela Salas Cabrera, Leyza Aída Fernández Vega, Carlos Arturo Castro del Ángel, Juan de Dios Robles Pérez, Víctor Díaz Hernández, José Trinidad Ramírez Vargas, Gerardo Falcón Lucario, Sergio Aguilar Carrera</t>
-  </si>
-  <si>
-    <t>Hidalgo supera 50 por ciento de meta de esterilización</t>
-  </si>
-  <si>
-    <t>Durante el primer semestre en Hidalgo se realizaron 22 mil 929 esterilizaciones, que representan el 57.7 por ciento de la meta para todo 2026; además, 16 municipios superaron la programación de todo el año. En contraste, Lolotla, Progreso y Eloxochitlán no hicieron ninguna cirugía, reveló la Secretaría de Salud estatal (SSH). Erick José Canales Vargas, coordinador estatal del programa de zoonosis de la SSH, informó que la meta de este año es realizar 42 mil 669 esterilizaciones en perros y gatos, y de enero a junio superaron la mitad, con 22 mil 929 cirugías. Con esta actividad buscamos que disminuya el abandono de los perros y gatos en vía pública, porque la presencia de esos animales causa impactos en la salud. Tepeji de Río es el municipio con más cirugías con mil 955 (155.1% de su meta de 1,260). Apan 919 (meta 676), Zacualtipán 745 (meta 540), Huichapan 738 (meta 705), Alfajayucan 544 (meta 320). Lolotla, Progreso y Eloxochitlán cero. Calnali 15, Almoloya 25, Mixquiahuala 27, Tlaxcoapan 32, Huazalingo 34, Ajacuba 37. Pachuca 869 (26.2% de 3,316). Meta de vacunación antirrábica es 1,066,737, logrando 396,692 (37.2%). Alba Luisa Jiménez de Jauría de Balú destacó que es viable para el control animal.</t>
-  </si>
-  <si>
-    <t>Campaña de esterilización</t>
-  </si>
-  <si>
-    <t>Hidalgo alcanzó el 57.7% de su meta de esterilización de mascotas en el primer semestre de 2026, con Tepeji del Río a la cabeza y Lolotla, Progreso y Eloxochitlán con cero cirugías.</t>
-  </si>
-  <si>
-    <t>Secretaría de Salud de Hidalgo, Ayuntamientos locales</t>
-  </si>
-  <si>
-    <t>Erick José Canales Vargas, Alba Luisa Jiménez</t>
-  </si>
-  <si>
-    <t>REMESAS AUMENTARON EN 20 MDD EN UN AÑO</t>
-  </si>
-  <si>
-    <t>Pachuca.- Los hidalguenses que radican en el extranjero enviaron a sus familias 20.2 millones de dólares más en remesas durante el primer semestre de 2026, en comparación con el mismo periodo del año anterior, informó Ricardo Gómez Moreno, titular de la Secretaría de Bienestar e Inclusión Social (Sebiso) de Hidalgo. De acuerdo con el funcionario, entre enero y junio de este año, la entidad captó 863.65 millones de dólares, mientras que en el mismo periodo de 2025 ingresó 843.45 millones de dólares. Dicha diferencia representa un incremento en las remesas de 2.39 por ciento en un periodo de un año. Los municipios que concentraron la mayor captación durante el periodo de referencia fueron Tulancingo, Ixmiquilpan, Pachuca, Actopan y Zacualtipán. El flujo de recursos ocurre en un contexto de presencia de hidalguenses en Estados Unidos, ya que, de acuerdo con los datos de Gómez Moreno, 466 mil 199 migrantes originarios del estado habitan en ese país, cifra que coloca a Hidalgo en el décimo lugar nacional en intensidad migratoria. La población migrante se concentra principalmente en cinco estados de la Unión Americana: California, con 17.4 por ciento; Texas, 13.6 por ciento; Florida, 13.5 por ciento, y Carolina del Norte y Georgia, ambos con 7.8 por ciento. Mientras tanto, los municipios hidalguenses identificados como principales lugares de origen de la población migrante son Pisaflores, La Misión, Chapulhuacán, Tecozautla y Tasquillo, detalló el funcionario. Jacala, Pacula, Atotonilco el Grande, Santiago de Anaya, Acatlán, Tlahuiltepa, Zimapán, Nicolás Flores, Huasca, Huichapan, Alfajayucan, Chilcuautla, Ixmiquilpan y Cardonal. Repatriaciones: de enero a junio de 2026 se contabilizaron 2 mil 848 repatriaciones de hidalguenses, de acuerdo con registros del Instituto Nacional de Migración (INM).</t>
-  </si>
-  <si>
-    <t>La Sebiso de Hidalgo reportó un crecimiento de 2.39% anual en la captación de remesas en el primer semestre de 2026, alcanzando los 863.65 mdd, beneficiando a municipios clave como Tulancingo e Ixmiquilpan.</t>
-  </si>
-  <si>
-    <t>Lorena Rosas</t>
-  </si>
-  <si>
-    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Instituto Nacional de Migración</t>
-  </si>
-  <si>
-    <t>Capacitan a personas con discapacidad para el trabajo</t>
-  </si>
-  <si>
-    <t>Pachuca.- La Secretaría de Bienestar e Inclusión Social (Sebiso) lleva a cabo un taller de habilidades laborales, diseñado para promover la autonomía económica de las personas con discapacidad en Hidalgo. Esta iniciativa ofrece a los participantes la oportunidad de adentrarse en el sector productivo, mediante un programa de formación enfocado en la costura, centrado principalmente en la elaboración artesanal de piezas para peluches, detalló la dependencia. Las jornadas de formación se realizan de manera presencial en las instalaciones de la Dirección de Inclusión, donde el personal capacita a los asistentes en las técnicas de costura y confección. Conforme los participantes avanzan y perfeccionan su producción, la fábrica receptora de estas piezas puede adquirirlas y brindar un apoyo económico directo durante su capacitación. Este beneficio monetario sirve como un incentivo constante que inspira, recompensa y reconoce su valioso esfuerzo e impulso productivo. El programa cuenta con una comunidad activa de 30 personas: 10 productoras y 20 practicantes.</t>
-  </si>
-  <si>
     <t>Apoyo a personas con discapacidad</t>
   </si>
   <si>
-    <t>La Sebiso estatal implementó un taller presencial de costura en Pachuca enfocado en capacitar en la confección de piezas para peluches a una comunidad de 30 personas con discapacidad, fomentando su autonomía laboral.</t>
-  </si>
-  <si>
-    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Dirección de Inclusión de la Sebiso</t>
-  </si>
-  <si>
-    <t>Prevén sumar 6 municipios a Viviendas del Bienestar</t>
-  </si>
-  <si>
-    <t>Pachuca.- Actualmente se construyen casas del programa Viviendas del Bienestar en siete municipios de Hidalgo, mientras que en otros 13 está prevista la edificación y seis más podrían incorporarse antes de concluir el año, informó la Unidad de Planeación y Prospectiva de Hidalgo. Los lugares donde ya se construyen son El Arenal, Mineral de la Reforma, San Agustín Tlaxiaca, Tepeapulco, Tepeji del Río, Tulancingo y Zempoala. Mientras que se iniciará la construcción en Actopan, Apan, Atotonilco de Tula, Cuautepec, Huautla, Huejutla, Huichapan, Ixmiquilpan, Mixquiahuala, Progreso de Obregón, Tizayuca, Tula y Zapotlán. La meta estatal contempla 60 mil viviendas durante el actual sexenio, de las cuales 31 mil 500 están en proceso de edificación, con un costo promedio de 600 mil pesos por casa. Los proyectos están a cargo del Instituto del Fondo Nacional de la Vivienda para los Trabajadores (Infonavit) y la Comisión Nacional de Vivienda (Conavi); además, se prevé la incorporación del Fondo de la Vivienda del Instituto de Seguridad y Servicios Sociales de los Trabajadores del Estado (Fovissste). De acuerdo con la Unidad de Planeación, el estado y los municipios tendrán la responsabilidad de garantizar servicios básicos y transporte para los nuevos desarrollos.</t>
-  </si>
-  <si>
-    <t>Plan Nacional De Vivienda</t>
-  </si>
-  <si>
-    <t>La Unidad de Planeación y Prospectiva de Hidalgo informó que el programa Viviendas del Bienestar (Infonavit y Conavi) edifica 31,500 casas en la entidad de una meta sexenal de 60,000, proyectando expandirse a 19 demarcaciones.</t>
-  </si>
-  <si>
-    <t>Unidad de Planeación y Prospectiva, Instituto del Fondo Nacional de la Vivienda para los Trabajadores, Comisión Nacional de Vivienda, Fondo de la Vivienda del ISSSTE</t>
-  </si>
-  <si>
-    <t>EN BUSCA DEL CIUDADANO: Cuatro años de la administración Menchaca</t>
-  </si>
-  <si>
-    <t>El viernes de esta semana se cumple la segunda mitad del actual gobierno en el estado de Hidalgo. Lo alcanzado hasta este momento obedece a las decisiones que se han tomado en el corto plazo. El presupuesto para programas sociales aumentó en un 360%, pasando de mil 61 millones de pesos a más de 4 mil 900 millones este año. Se redujo la pobreza del 41% al 35%, lo que hizo posible que más de 154 mil personas salieran de esta condición. En el rubro de la educación se ha destinado en los últimos cuatro años un monto de 121 mil millones de pesos, lo que representa el 44% del presupuesto total del estado. Llegaron al estado más de 147 mil millones de pesos en inversiones, lo que supera el monto obtenido en las 4 administraciones anteriores, generando más de 191 mil empleos. Se redujo la deuda pública en un 42%, con un crecimiento histórico del 96% en la recaudación de ingresos propios.</t>
-  </si>
-  <si>
-    <t>Columna de opinión que hace un balance favorable de los primeros cuatro años de la administración estatal, destacando el incremento presupuestal del 360% en programas sociales, la reducción de pobreza y deuda, y la atracción de 147 mil mdp en inversiones.</t>
-  </si>
-  <si>
-    <t>Enrique López</t>
-  </si>
-  <si>
-    <t>La SSH capacitó a personal médico sobre el cáncer de cuello uterino</t>
-  </si>
-  <si>
-    <t>Pachuca.- La Secretaría de Salud de Hidalgo (SSH) capacitó a 163 profesionales de la salud y estudiantes de instituciones públicas y privadas para fortalecer las competencias técnicas en la prevención, detección oportuna y atención del cáncer de cuello uterino, una de las principales causas de enfermedad y muerte entre las mujeres cuando no se identifica y trata a tiempo. La jornada académica reunió a personal del Centro Médico Nacional Siglo XXI, IMSS Ordinario, Issste, IMSS Bienestar, así como al Instituto de Estudios Superiores Elise Freinet, Intermédica, Hospital del Niño DIF Hidalgo, Universidad Autónoma del Estado de Hidalgo (UAEH) y Universidad La Salle Pachuca. La secretaria de Salud de Hidalgo, Vanesa Escalante Arroyo, destacó que la actualización permanente del personal sanitario es una herramienta fundamental para fortalecer las acciones preventivas, ampliar la detección oportuna y garantizar servicios de calidad. Destacó que, bajo esta perspectiva, se impulsan estrategias como las Brigadas de la Salud.</t>
-  </si>
-  <si>
-    <t>Cáncer de la mujer</t>
-  </si>
-  <si>
-    <t>La titular de la SSH, Vanesa Escalante, encabezó la capacitación técnica de 163 médicos, enfermeros y estudiantes de salud sobre detección oportuna y prevención de cáncer de cuello uterino en el estado.</t>
-  </si>
-  <si>
-    <t>Secretaría de Salud de Hidalgo, Instituto Mexicano del Seguro Social, ISSSTE, IMSS-Bienestar, Hospital del Niño DIF Hidalgo, Universidad Autónoma del Estado de Hidalgo, Universidad La Salle Pachuca</t>
-  </si>
-  <si>
     <t>Vanesa Escalante Arroyo</t>
   </si>
   <si>
-    <t>DIFH adquiere tecnología robótica para rehabilitación</t>
-  </si>
-  <si>
-    <t>Pachuca.- El Sistema DIF Hidalgo presentó el Lokomat, dispositivo cuya inversión asciende a 18 millones 498 mil 956 pesos, y que el organismo incorporó al Centro de Rehabilitación Integral de Hidalgo (CRIH), con el objetivo de ampliar las alternativas de atención para niños, adolescentes, personas adultas y adultas mayores a un costo accesible. Edda Vite Ramos, presidenta del Patronato del Sistema DIFH, destacó que esta tecnología no sustituye a los profesionales de la rehabilitación, sino que fortalece su trabajo y permite complementar los tratamientos, de acuerdo con las condiciones y necesidades específicas de cada paciente. Actualmente, el CRIH cuenta con 415 pacientes registrados, de los cuales 215 son candidatos para utilizar dicha tecnología, previa valoración del personal especializado. En este sentido, destacó el trabajo coordinado con el Sistema Nacional DIF. Por su parte, Ricardo Alvizo Contreras, titular del Sistema DIF Hidalgo, puntualizó que en México únicamente existen 33 equipos Lokomat al servicio de la población en general, con sesiones a costos accesibles.</t>
-  </si>
-  <si>
     <t>Rehabilitación CRIRH</t>
   </si>
   <si>
-    <t>Con una inversión de 18.4 mdp, el DIF Hidalgo integró al CRIH un dispositivo robótico Lokomat de alta tecnología para complementar los tratamientos de rehabilitación motora a costos accesibles para la población.</t>
-  </si>
-  <si>
     <t>DIFH</t>
   </si>
   <si>
-    <t>Sistema DIF Hidalgo, Centro de Rehabilitación Integral de Hidalgo, Sistema Nacional DIF</t>
-  </si>
-  <si>
     <t>Edda Vite Ramos, Ricardo Alvizo Contreras</t>
   </si>
   <si>
-    <t>Han invertido 121 mil mdp en educación</t>
-  </si>
-  <si>
-    <t>En cuatro años, el gobierno de Hidalgo invirtió 121 mil millones de pesos en educación, derivado de un mejor uso de los recursos públicos, destacó el gobernador Julio Menchaca Salazar durante el inicio de clases del ciclo escolar 2026-2027. Ante estudiantes, padres y madres de familia y personal docente de la Secundaria General 2, de Pachuca, el mandatario estatal indicó que el presupuesto invertido busca respaldar el esfuerzo de las familias. Además, el gobernador encabezó el inicio de entrega de libros de texto y útiles escolares para el nivel básico, con un acto simbólico. De acuerdo con datos de la Secretaría de Educación Pública de Hidalgo (SEPH), en todo el estado entregarán 3 millones 958 mil 230 libros de texto gratuitos y 488 mil 977 paquetes de útiles escolares. Mientras tanto, la entrega de 475 mil 14 uniformes y 475 mil 14 pares de calzado escolar se realizará durante las primeras semanas. El titular de la SEPH, Natividad Castrejón Valdez, informó que volvieron a las aulas 569 mil 987 estudiantes de educación básica en toda la entidad.</t>
-  </si>
-  <si>
-    <t>Impulso A La Educación</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca inauguró el ciclo escolar 2026-2027 en Pachuca, resaltando una inversión de 121 mil mdp acumulada en materia educativa y poniendo en marcha la repartición de 3.9 millones de libros de texto y útiles escolares.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Natividad Castrejón Valdez</t>
-  </si>
-  <si>
-    <t>Vuelven a las aulas estudiantes de nivel básico en Pachuca</t>
-  </si>
-  <si>
-    <t>Pachuca.- Prisas al caminar, mochilas y loncheras con olor a nuevo, niñas y niños con caras lavadas, algunas con bostezos por la desmañanada y otras con expresión de extrañeza al entrar a una nueva escuela fue parte de la dinámica del regreso a clases en la Secundaria General 2, ubicada en Pachuca. El inicio del ciclo escolar 2026-2027 reactivó la movilidad vehicular y económica en la mayor parte de la entidad hidalguense por el regreso a las escuelas de 569 mil 987 alumnos de nivel básico, con mayor carga de tráfico en las llamadas horas pico, cuando inician las clases y en la salida. Al exterior de las escuelas, principalmente en primarias, padres y madres de familia veían alejarse a sus hijos, les deseaban buena suerte en su nuevo curso, algunos les daban la bendición. Los estudiantes expresaban su felicidad al reencontarse con sus compañeros, a quienes saludaban con una sonrisa. Así se vivió el primero de varios días que comprende el ciclo, cuya próxima suspensión de clases será el 16 de septiembre.</t>
-  </si>
-  <si>
-    <t>Con el regreso oficial de 569 mil alumnos en Hidalgo se restableció la habitual saturación vial en Pachuca, marcando escenas cotidianas de desvelo, prisas y reencuentros de estudiantes en la Secundaria General 2.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Primarias locales</t>
-  </si>
-  <si>
-    <t>Sumaron mil 385 casos de violencia el ciclo pasado</t>
-  </si>
-  <si>
-    <t>Durante el ciclo escolar pasado, la Secretaría de Educación Pública de Hidalgo (SEPH) registró mil 385 casos de violencia escolar en todos los niveles educativos del estado, principalmente física, psicológica y sexual, informó el titular de la dependencia, Natividad Castrejón Valdez, quien destacó que más de la mitad de los hechos están resueltos. El funcionario detalló que, del total de casos de violencia escolar del ciclo 2025-2026, los tipos más recurrentes son física, con 380 reportes; psicológica, con 316; sexual, con 163, además de 83 por uso de sustancias ilícitas, 56 de violencia sexual dentro del entorno familiar, 56 por exclusión social, y 53 por llevar artículos prohibidos. Por otra parte, el diputado local José María Alejandro Pérez Ramírez dio a conocer que los protocols de actuación para los maestros del estado en caso de ser señalados por supuestos actos de violencia presentan 80 por ciento de avance. Además, el gobernador Julio Menchaca Salazar se pronunció a favor de establecer un protocolo que permita proteger la integridad de trabajadores del sector educativo ante posibles acusaciones infundadas.</t>
-  </si>
-  <si>
-    <t>El titular de la SEPH reportó que el ciclo escolar 2025-2026 cerró con un total de 1,385 quejas por violencia escolar en Hidalgo, principalmente por agresión física (380) y psicológica (316), avanzando a la par el diseño de un protocolo de defensa docente.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Congreso del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, José María Alejandro Pérez Ramírez, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>DEMOLICIÓN DE PRIMARIA COMENZARÁ EN OCTUBRE</t>
-  </si>
-  <si>
-    <t>En octubre iniciarán los trabajos de demolición y reconstrucción de las primarias Aquiles Serdán y Rafael Ramírez, confirmó el secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, quien señaló que el plantel deberá ser intervenido en su totalidad y que las obras se prolongarán durante todo el ciclo escolar; en tanto, padres de familia solicitaron la reubicación de 693 alumnos y rechazaron las clases virtuales. El funcionario explicó que durante septiembre se deberán definir alternativas para garantizar la continuidad de las actividades académicas mientras se realizan los trabajos, al priorizar que los estudiantes permanezcan en clases presenciales. Castrejón Valdez precisó que la situación de la primaria de Tulancingo es similar a la de la escuela Ignacio Zaragoza, ubicada en Pachuca, que también determinaron demolerla y reconstruirla. Padres y madres de familia de ambos turnos tuvieron una reunión con docentes y directivos, en la que se informó que las actividades escolares se desarrollarán de manera virtual debido a los trabajos. Padres exigieron una alternativa presencial y propusieron que los alumnos sean distribuidos temporalmente en otros planteles.</t>
-  </si>
-  <si>
-    <t>La SEPH confirmó la demolición de las primarias Aquiles Serdán y Rafael Ramírez en Tulancingo a partir de octubre, enfrentando reclamos de padres que rechazan la educación en línea y exigen sedes presenciales alternas para 693 alumnos.</t>
-  </si>
-  <si>
     <t>Mirely Santos</t>
   </si>
   <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Primarias Aquiles Serdán, Rafael Ramírez e Ignacio Zaragoza</t>
-  </si>
-  <si>
-    <t>Incrementa 10 por ciento la eficiencia terminal en el Cobaeh</t>
-  </si>
-  <si>
-    <t>Tizayuca.- Reducir la deserción escolar y lograr que un mayor número de jóvenes concluya su educación media superior se ha convertido en una de las prioridades del Colegio de Bachilleres de Hidalgo (Cobaeh), afirmó su director general, Rubén López Valdez. El funcionario destacó que el subsistema ha registrado 'avances importantes' en materia de eficiencia terminal, al señalar que este indicador ha aumentado cerca de 10 puntos porcentuales, como resultado de las acciones implementadas para evitar que los estudiantes abandonen sus estudios. López Valdez sostuvo que el objetivo de su administración es disminuir la deserción y los índices reprobatorios. De acuerdo con el director general, la reducción del abandono escolar no depende únicamente del trabajo académico, sino también de generar mejores condiciones para que los estudiantes permanezcan en las aulas. Entre estas medidas se encuentra la inversión en laboratorios STEM, la entrega de tabletas y la distribución de libros de texto gratuitos, herramientas que buscan fortalecer el aprendizaje y ofrecer a los jóvenes mayores oportunidades. Actualmente, el Cobaeh cuenta con 133 centros educativos y cerca de 3 mil empleados.</t>
-  </si>
-  <si>
-    <t>Deserción escolar</t>
-  </si>
-  <si>
-    <t>El director general del Cobaeh, Rubén López, reportó que la eficiencia terminal de la institución aumentó cerca de 10 puntos porcentuales gracias a medidas de retención escolar como laboratorios STEM, libros y tabletas.</t>
-  </si>
-  <si>
-    <t>Colegio de Bachilleres del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Rubén López Valdez</t>
-  </si>
-  <si>
-    <t>Cierran calle para pedir que no acepten a hijos de padres problemáticos</t>
-  </si>
-  <si>
-    <t>Ixmiquilpan.- Padres de familia de la primaria Niños Héroes, ubicada en San Nicolás, Ixmiquilpan, cerraron la carretera que comunica a Cardonal y comunidades de la zona norte, la tarde del lunes. El motivo del bloqueo, señalaron, es que no quieren recibir a alumnos cuyos padres son calificados de conflictivos, pero, agregaron, las autoridades escolares quieren imponer que sean aceptados en esa institución educativa. Los inconformes expusieron que ya existen antecedentes de que son problemáticos dichos padres de familia. La semana pasada, de manera formal, mediante un oficio, las autoridades escolares ordenaron a los directivos de la primaria recibir a los estudiantes. Al respecto, los manifestantes mantienen su postura de rechazo y hasta el cierre de esta edición esperaban a las autoridades escolares de la zona. Los tutores colocaron cartulinas afuera de la institución educativa con leyendas como 'No queremos a la señora Brenda Luz Evelino Vázquez'.</t>
-  </si>
-  <si>
-    <t>Ixmiquilpan</t>
-  </si>
-  <si>
-    <t>Padres de familia de la primaria Niños Héroes en San Nicolás, Ixmiquilpan, bloquearon la carretera para protestar contra la imposición oficial de recibir a hijos de tutores considerados conflictivos, nombrando en cartelones a Brenda Luz Evelino.</t>
-  </si>
-  <si>
-    <t>Erika Gutiérrez</t>
-  </si>
-  <si>
-    <t>Escuela Primaria Niños Héroes de Ixmiquilpan, Dirección Escolar de la zona</t>
-  </si>
-  <si>
-    <t>Brenda Luz Evelino Vázquez</t>
-  </si>
-  <si>
-    <t>Prevén 60 mil nuevas viviendas durante el actual gobierno federal</t>
-  </si>
-  <si>
-    <t>El programa federal de vivienda en Hidalgo tiene como meta construir 60 mil viviendas durante el sexenio. El titular de la Unidad de Planeación y Prospectiva de Hidalgo, Miguel Ángel Tello Vargas, destacó que 31 mil 500 casas ya están en proceso de construcción, con una inversión de 18 mil 900 millones de pesos y un costo promedio de 600 mil pesos por vivienda. El proyecto está enfocado en atender a familias que no cotizan ante instituciones de seguridad social y contempla esquemas sin intereses, con pagos ajustados a sus ingresos. Las obras ya marchan en San Agustín Tlaxiaca, Tulancingo, El Arenal, Zempoala, Tepeapulco, Tepeji del Río y Mineral de la Reforma.</t>
-  </si>
-  <si>
-    <t>La Unidad de Planeación y Prospectiva de Hidalgo reportó que la meta de vivienda federal de este sexenio es de 60 mil casas, con 31 mil 500 ya en construcción.</t>
-  </si>
-  <si>
-    <t>Miguel Ángel Tello Vargas, Claudia Sheinbaum Pardo</t>
-  </si>
-  <si>
-    <t>Hidalgo reporta avances en saneamiento y tecnificación como parte del Plan Hídrico</t>
-  </si>
-  <si>
-    <t>El gobierno de Hidalgo reportó avances en las acciones del Plan Hídrico Nacional, calificado por la Comisión Estatal del Agua y Alcantarillado (CEAA) como el proyecto de largo plazo más ambicioso de la entidad en 50 años. El titular de la CEAA, Juan Carlos Chávez González, informó que durante 2025 se destinaron 200 millones de pesos para la primera etapa del saneamiento en Tula, mediante colectores. Para 2026, se tiene prevista una segunda etapa de saneamiento con 320 millones de pesos, además de la nivelación de 5 mil hectáreas agrícolas y el revestimiento de canales en los distritos 03 de Tula, 100 de Alfajayucan y 112 de Ajacuba.</t>
-  </si>
-  <si>
     <t>Plan Hídrico</t>
   </si>
   <si>
-    <t>La CEAA reportó avances de saneamiento de aguas residuales en el río Tula y en la tecnificación de distritos de riego en Tula, Alfajayucan y Ajacuba.</t>
-  </si>
-  <si>
-    <t>Comisión Estatal del Agua y Alcantarillado, Comisión Federal de Electricidad</t>
-  </si>
-  <si>
     <t>Juan Carlos Chávez González</t>
   </si>
   <si>
-    <t>Hidalgo alista regulación para el uso de celulares en educación básica</t>
-  </si>
-  <si>
-    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, informó que el estado avanza en una propuesta para regular el uso de teléfonos celulares y medios digitales entre estudiantes de educación básica, con el objetivo de evitar efectos negativos derivados del uso excesivo de pantallas. Explicó que la medida no busca prohibir los dispositivos, sino establecer reglas sobre edades, momentos y condiciones para su utilización. Advirtió que, a través de Ver Bien para Aprender Mejor, se ha identificado un crecimiento exponencial de problemas visuales en primero y segundo de primaria, relacionados con el tiempo frente a pantallas.</t>
-  </si>
-  <si>
     <t>Regulación de dispositivos digitales</t>
   </si>
   <si>
-    <t>La SEPH diseña una propuesta para regular y normar el uso de celulares en primarias hidalguenses ante el alza desmedida de problemas de visión infantil.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Fideicomiso Ver Bien para Aprender Mejor</t>
-  </si>
-  <si>
     <t>Natividad Castrejón Valdez, Claudia Sheinbaum Pardo</t>
   </si>
   <si>
-    <t>Gobernador respalda protocolos para resolver conflictos escolares</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar señaló que se debe establecer un equilibrio entre la protección de niñas, niños y adolescentes ante cualquier forma de violencia y la defensa de las maestras y maestros frente a posibles acusaciones infundadas, por lo que respaldó la creación de protocolos claros para atender estos casos. El titular de la SEPH, Natividad Castrejón Valdez, confirmó que el estado trabaja de forma coordinada con el SNTE y el Congreso local en la elaboración de dicho documento.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca respaldó el diseño de protocolos escolares equilibrados que prevengan la violencia infantil y defiendan la reputación de docentes.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Sindicato Nacional de Trabajadores de la Educación, Congreso del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Por condiciones críticas, demolerán la primaria Aquiles Serdán en Tulancingo</t>
-  </si>
-  <si>
-    <t>Ante las condiciones críticas de su infraestructura, la escuela primaria Aquiles Serdán, en Tulancingo, será demolida y reconstruida en su totalidad, un proceso que tomará todo el ciclo escolar. El titular de la SEPH, Natividad Castrejón Valdez, reconoció que se evalúan alternativas urgentes para reubicar a los estudiantes de los turnos matutino y vespertino en espacios presenciales, descartando las clases virtuales tras el rechazo inmediato manifestado por las madres y padres de familia.</t>
-  </si>
-  <si>
-    <t>La SEPH autorizó la demolición total y reconstrucción del plantel Aquiles Serdán en Tulancingo, programando la distribución física de grupos en otras escuelas.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Consejo Nacional de Fomento Educativo</t>
-  </si>
-  <si>
-    <t>Lluvias impiden regreso a primaria de Huehuetla</t>
-  </si>
-  <si>
-    <t>Derivado de las recientes lluvias registradas en Hidalgo, la Escuela Primaria Benito Juárez, ubicada en el municipio de Huehuetla, no abrió sus puertas ayer para el inicio del ciclo escolar 2026-2027, debido a los encharcamientos que se registraron nuevamente en el plantel. El gobernador Julio Menchaca Salazar reconoció que las lluvias del fin de semana provocaron nuevamente la acumulación de agua en el plantel, pese a que previamente se habían realizado labores de limpieza.</t>
-  </si>
-  <si>
-    <t>Graves inundaciones por temporales del fin de semana impidieron el inicio de clases físicas en la primaria Benito Juárez de Huehuetla.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Protección Civil</t>
-  </si>
-  <si>
-    <t>Repatrian desde EU a 2 mil 800 durante el primer semestre</t>
-  </si>
-  <si>
-    <t>Entre enero y junio de 2026, 2 mil 848 hidalguenses fueron repatriados desde Estados Unidos, informó el titular de la Secretaría de Bienestar e Inclusión Social (Sebiso), Ricardo Gómez Moreno, durante la conferencia de prensa del Gobierno de Hidalgo. De acuerdo con datos de la Unidad de Política Migratoria del INM, la entidad ocupa el décimo lugar nacional en intensidad migratoria, con 466 mil 199 hidalguenses radicando principalmente en California, Texas y Florida. En el primer semestre, el estado recibió 863.65 millones de dólares en remesas.</t>
-  </si>
-  <si>
-    <t>Repatriación</t>
-  </si>
-  <si>
-    <t>La Sebiso estatal informó de la repatriación de 2,848 hidalguenses desde Estados Unidos y de un alza de 20 mdd anuales en remesas captadas.</t>
-  </si>
-  <si>
-    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Instituto Nacional de Migración, Unidad de Política Migratoria</t>
-  </si>
-  <si>
-    <t>Último año registró mil 380 denuncias contra docentes</t>
-  </si>
-  <si>
-    <t>En el pasado ciclo escolar se recibieron mil 383 quejas en contra de docentes; aunque todas se investigaron, se detectaron casos en que se trataba de una calumnia o una mentira tras las indagaciones realizadas por la Procuraduría General de Justicia del Estado de Hidalgo (PGJEH). Luego de que se instrumenten protocolos de actuación ante denuncias emitidas por padres de familia, estudiantes e incluso los propios docentes por temas diversos como violencia, acoso o abuso, Natividad Castrejón Valdez, titular de la Secretaría de Educación Pública en la entidad (SEPH), llamó a que en redes sociales no se linche mediáticamente, pues no se tiene la certeza sobre un hecho. El funcionario explicó que se debe generar conciencia en los jóvenes y la población, que 'no es una broma cuando se recurre a una acción de esa naturaleza, pues hay consecuencias'.</t>
-  </si>
-  <si>
-    <t>La SEPH reportó que durante el pasado ciclo escolar se recibieron mil 383 quejas contra docentes, llamando a evitar linchamientos mediáticos hasta que concluyan las indagaciones penales.</t>
-  </si>
-  <si>
-    <t>Miriam Avilés</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Procuraduría General de Justicia del Estado de Hidalgo, Subprocuraduría de Niños, Niñas y Adolescentes</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, Jorge Sánchez</t>
-  </si>
-  <si>
-    <t>Evitarán riesgos en escuelas ante lluvias</t>
-  </si>
-  <si>
-    <t>Derivado de las recientes lluvias en el estado, un plantel escolar en el municipio de Huehuetla no contó con las condiciones idóneas para iniciar el ciclo escolar, reconoció el gobernador Julio Menchaca Salazar. Pese a esto, apuntó el mandatario estatal que la Secretaría de Educación Pública de Hidalgo (SEPH) lleva a cabo labores de limpieza para habilitar el inmueble y con ello no afectar las actividades del alumnado. De igual manera, garantizó los trabajos para supervisar y vigilar todos los planteles escolares en los 28 municipios más afectados por la vaguada monzónica de octubre del año pasado, ya que las precipitaciones continúan y por ello se tomarán las previsiones adecuadas para evitar riesgos.</t>
-  </si>
-  <si>
     <t>Atención Afectaciones Por Lluvias</t>
   </si>
   <si>
-    <t>El gobernador Julio Menchaca informó que una primaria en Huehuetla no pudo iniciar clases por inundaciones causadas por lluvias recientes, por lo que la SEPH realiza labores de desazolve.</t>
-  </si>
-  <si>
     <t>Teodoro Santos</t>
   </si>
   <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Gobierno del Estado de Hidalgo, Protección Civil</t>
-  </si>
-  <si>
-    <t>Tello destaca ofensiva federal al huachicol</t>
-  </si>
-  <si>
-    <t>Las acciones emprendidas por el gobierno federal para combatir el robo de hidrocarburo y el llamado 'huachicol fiscal' representan una ofensiva sin precedentes contra ambos delitos y permitirán generar mejores condiciones de seguridad para Hidalgo, afirmó Miguel Ángel Tello Vargas, titular de la Unidad de Planeación y Prospectiva del estado. Durante una conferencia de prensa, el funcionario sostuvo que el gobierno de la presidenta Claudia Sheinbaum mantiene una estrategia frontal para abatir estas actividades ilícitas, las cuales, dijo, han afectado durante años al país y particularmente a regiones como Tula-Tepeji.</t>
-  </si>
-  <si>
     <t>Combate Al Huachicol</t>
   </si>
   <si>
-    <t>El secretario Miguel Ángel Tello destacó la estrategia federal de Claudia Sheinbaum contra el robo de hidrocarburo y el huachicol fiscal para el resguardo de la región Tula-Tepeji.</t>
-  </si>
-  <si>
-    <t>Unidad de Planeación y Prospectiva, Gobierno Federal, Petróleos Mexicanos, Cruz Azul</t>
-  </si>
-  <si>
-    <t>Meses de espera para buscar desaparecidos</t>
-  </si>
-  <si>
-    <t>Integrantes de Madres Buscadoras de Hidalgo denunciaron retrasos en las investigaciones y búsquedas de personas desaparecidas, al señalar que la Fiscalía Especializada de Delitos de Desaparición de Personas y la Comisión de Búsqueda de Personas del Estado de Hidalgo no atienden los casos de manera oportuna. Las familias afirmaron que en la Fiscalía las investigaciones pueden comenzar hasta cuatro o cinco días después de que se reporta una desaparición, mientras que en la Comisión algunas diligencias de campo tardan meses en ser asignadas.</t>
-  </si>
-  <si>
-    <t>El colectivo Madres Buscadoras denunció retrasos procesales por parte de la PGJEH y dilación de meses en operativos de campo de la Comisión de Búsqueda de Hidalgo.</t>
-  </si>
-  <si>
-    <t>Comisión de Búsqueda de Personas del Estado de Hidalgo, Procuraduría General de Justicia del Estado de Hidalgo, Fiscalía Especializada de Delitos de Desaparición de Personas</t>
-  </si>
-  <si>
-    <t>Francisco García Reyes</t>
-  </si>
-  <si>
-    <t>Fortalece cercanía con 818 menores</t>
-  </si>
-  <si>
-    <t>Durante el período vacacional, la Secretaría de Seguridad Pública de Hidalgo (SSPH) acercó a 818 niños y niñas a la policía estatal mediante actividades recreativas, formativas y de convivencia, como parte de los programas Ciudad Policía y Polivioleta. Entre el 21 de julio y el 14 de agosto, estudiantes de nueve municipios participaron en estas acciones de prevención del delito y proximidad social, con el acompañamiento de personal de la corporación. De este grupo, 783 estudiantes fueron trasladados al parque de conservación de vida silvestre Tuzoofari, ubicado en Epazoyucan.</t>
-  </si>
-  <si>
-    <t>La SSPH implementó los programas Ciudad Policía y Polivioleta con la participación de 818 infantes, culminando con visitas al parque de conservación Tuzoofari.</t>
-  </si>
-  <si>
-    <t>Sebiso impulsa inclusión laboral</t>
-  </si>
-  <si>
-    <t>Con el compromiso de construir un estado más equitativo, accesible y humano, la Secretaría de Bienestar e Inclusión Social (Sebiso), a través de la Dirección de Inclusión, lleva a cabo un taller de habilidades laborales diseñado para promover la autonomía económica de las personas con discapacidad en Hidalgo. Esta iniciativa ofrece a las y los participantes la oportunidad de adentrarse en el sector productivo mediante un programa de formación enfocado en la costura, centrado principalmente en la elaboración artesanal de peluches.</t>
-  </si>
-  <si>
-    <t>La Sebiso realiza talleres presenciales de costura de peluches para brindar habilidades laborales y autonomía financiera a personas hidalguenses con discapacidad.</t>
-  </si>
-  <si>
-    <t>Evalúan los nueve Pueblos Mágicos</t>
-  </si>
-  <si>
-    <t>Como parte de las acciones del gobierno de Julio Menchaca Salazar para consolidar a los Pueblos Mágicos de Hidalgo como destinos competitivos, la Secretaría de Turismo de Hidalgo (Secturh), encabezada por Elizabeth Quintanar Gómez, realizará visitas técnicas a los nueve Pueblos Mágicos de la entidad, a través de la Dirección General de Productos Turísticos y Pueblos Mágicos. Quinta Gómez señaló que las visitas tienen como propósito dar seguimiento al Plan de Fortalecimiento de Pueblos Mágicos y atender las observaciones emitidas por la Secretaría de Turismo del Gobierno de México (Sectur), además de impulsar acciones coordinadas.</t>
-  </si>
-  <si>
-    <t>Pueblos Mágicos</t>
-  </si>
-  <si>
-    <t>La Secturh evaluará mediante inspecciones de campo a los nueve Pueblos Mágicos de Hidalgo, asegurando su competitividad y solventando observaciones de la Sectur federal.</t>
-  </si>
-  <si>
-    <t>Secretaría de Turismo del Estado de Hidalgo, Secretaría de Turismo Federal</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Elizabeth Quintanar Gómez</t>
-  </si>
-  <si>
-    <t>Hidalgo atrae 147 mil mdp en inversiones</t>
-  </si>
-  <si>
-    <t>El estado de Hidalgo es una potencia en marcha que mantendrá una vinculación estratégica entre el gobierno estatal y el sector privado para generar nuevas oportunidades e impulsar el bienestar de las familias hidalguenses, afirmó el gobernador de la entidad, Julio Menchaca Salazar, en el marco del foro 'Es tiempo de Hidalgo, Potencia en Marcha'. Durante su mensaje, el mandatario reconoció la iniciativa del Banco Multiva para generar espacios de diálogo y establecer una comunicación directa entre el sector productivo y el gobierno de Hidalgo, el cual tiene claro que se debe facilitar la llegada de nuevas inversiones, respetando los lineamientos que permitan tener empresas socialmente responsables en la entidad. 'Con el noveno anuncio de inversiones, son 147 mil millones de pesos comprometidos para generar aproximadamente 191 mil empleos.</t>
-  </si>
-  <si>
-    <t>Atracción De Inversiones</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar anunció que en cuatro años de administración se ha alcanzado la cifra histórica de 147 mil mdp en inversiones privadas en la entidad.</t>
-  </si>
-  <si>
-    <t>Gobierno del Estado de Hidalgo, Banco Multiva</t>
-  </si>
-  <si>
-    <t>Implementan patrullajes preventivos ante tormentas</t>
-  </si>
-  <si>
-    <t>Ante las condiciones de lluvia registradas esta tarde en distintos puntos de la entidad, elementos de la policía estatal implementaron recorridos de vigilancia y presencia preventiva.</t>
-  </si>
-  <si>
-    <t>Elementos de la SSPH desplegaron patrullajes de prevención y asistencia vial en diversos puntos vulnerables por las persistentes tormentas de la temporada.</t>
-  </si>
-  <si>
-    <t>Secretaría de Seguridad Pública de Hidalgo, Policía Estatal</t>
-  </si>
-  <si>
-    <t>Destacan sector público y privado oportunidades de inversión en “Es tiempo de Hidalgo”</t>
-  </si>
-  <si>
-    <t>En el marco del foro “Es tiempo de Hidalgo, Potencia en Marcha”, el gobernador Julio Menchaca Salazar, destacó que el estado mantendrá una vinculación estratégica entre el gobierno estatal y el sector privado para generar nuevas oportunidades e impulsar el bienestar a las familias hidalguenses. El mandatario reconoció la iniciativa del Banco Multiva para generar el intercambio de opiniones y establecer una comunicación directa entre el sector productivo y gubernamental, sobre la llegada de nuevas inversiones respetando los lineamientos para contar con empresas responsables en la entidad. Con el noveno anuncio de inversiones, son 147 mil millones de pesos comprometidos para generar aproximadamente 191 mil empleos.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar destacó en el foro 'Es tiempo de Hidalgo' el compromiso de 147 mil mdp en inversiones privadas generadoras de 191 mil empleos.</t>
-  </si>
-  <si>
-    <t>Registran mil 385 casos de violencia escolar; más de la mitad resueltos: Castrejón Valdez</t>
-  </si>
-  <si>
-    <t>Con corte al 27 de agosto de 2026, la SEPH reportó mil 385 casos de violencia escolar durante el ciclo escolar 2025-2026, de los cuales los de mayor incidencia son los relacionados con violencia física (330 casos), psicológica (316), y sexual (163). El titular de la dependencia, Natividad Castrejón Valdez, mencionó que más de la mitad de los casos están resueltos, mientras que los más graves, relacionados con abuso sexual, se dirigen a la PGJEH y a la Procuraduría de Protección de Niñas, Niños, Adolescentes y la Familia para su investigación.</t>
-  </si>
-  <si>
-    <t>El titular de la SEPH, Natividad Castrejón Valdez, reportó mil 385 incidencias de violencia escolar en el ciclo 2025-2026, con más de la mitad de casos resueltos.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Procuraduría General de Justicia del Estado de Hidalgo, Procuraduría de Protección de Niñas, Niños, Adolescentes y la Familia</t>
-  </si>
-  <si>
-    <t>Lokomat: tecnología robótica para terapias de rehabilitación</t>
-  </si>
-  <si>
-    <t>Con una inversión de 18 millones 498 mil 956 pesos, el Sistema DIF Hidalgo incorporó al Centro de Rehabilitación Integral Hidalgo (CRIH) un Lokomat, una tecnología robótica que funcionará para terapias dirigidas a personas con discapacidad a costo accesible. Edda Vite Ramos destacó que esta tecnología permite complementar los tratamientos de acuerdo con las condiciones y necesidades de cada paciente. Actualmente, el CRIH cuenta con 415 pacientes registrados, de los cuales 215 son candidatos. Se gestionaron además tres camionetas de traslado.</t>
-  </si>
-  <si>
-    <t>El Sistema DIF Hidalgo adquirió un robot de terapia Lokomat de 18.4 mdp para el CRIH de Pachuca, siendo la primera institución pública estatal de la zona centro de México en incorporarlo.</t>
-  </si>
-  <si>
-    <t>Margarita esperó 24 años para volver a abrazar a su hijo</t>
-  </si>
-  <si>
-    <t>“Los sueños sí se cumplen”, declaró Margarita Hernández Galarza con la ilusión de reencontrarse con su hijo, Ricardo Hernández, después de 24 años de estar separados. Ella y su esposo lograron obtener la Visa con el acompañamiento de la Dirección General de Atención al Migrante, como parte del programa “Raíces de Hidalgo”. El señor Margarito García Mayor, originario de Cañada Chica, Ixmiquilpan, también obtuvo su documentación para viajar a Estados Unidos y reencontrarse con su hija tras 23 años. El trámite otorga 10 años de vigencia.</t>
-  </si>
-  <si>
-    <t>Reunificación familiar</t>
-  </si>
-  <si>
-    <t>Mediante el programa Raíces de Hidalgo de la Sebiso, Margarita Hernández y Margarito García obtuvieron visas de diez años de vigencia para reencontrarse en EUA con sus hijos tras más de dos décadas.</t>
-  </si>
-  <si>
-    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Dirección General de Atención al Migrante</t>
-  </si>
-  <si>
-    <t>Margarita Hernández Galarza, Ricardo Hernández, Margarito García Mayor</t>
-  </si>
-  <si>
-    <t>Vivienda para el Bienestar alcanza 52.5% de su meta en Hidalgo</t>
-  </si>
-  <si>
-    <t>El programa Vivienda para el Bienestar en Hidalgo alcanzó un avance de 52.5 por ciento de su meta actual, con 31 mil 500 viviendas que ya se construyen, de las 60 mil contempladas para el estado. El titular de la Unidad de Planeación y Prospectiva de Hidalgo, Miguel Tello Vargas, informó que cada vivienda tiene un costo de 600 mil pesos, lo que representa una inversión estimada de 18 mil 900 millones de pesos. El programa busca atender necesidades de calidad y servicios habitacionales en la entidad.</t>
-  </si>
-  <si>
-    <t>El titular de Planeación, Miguel Tello Vargas, reportó que el programa Vivienda para el Bienestar registra la edificación de 31 mil 500 casas de un total de 60 mil, representando una inversión de 18 mil 900 mdp.</t>
-  </si>
-  <si>
-    <t>Unidad de Planeación y Prospectiva de Hidalgo, Instituto del Fondo Nacional de la Vivienda para los Trabajadores, Comisión Nacional de Vivienda, Fondo de la Vivienda del ISSSTE</t>
-  </si>
-  <si>
-    <t>Miguel Tello Vargas</t>
-  </si>
-  <si>
-    <t>Siguen desaparecidas en Tianguistengo cinco personas tras lluvias atípicas de 2025</t>
-  </si>
-  <si>
-    <t>José Francisco García Reyes, titular de la CBPHEH, dio a conocer que el organismo continúa la búsqueda de cinco personas que resultaron ilocalizables tras las inundaciones derivadas de la vaguada monzónica en octubre del 2025. Se trata de personas que vivían en el municipio de Tianguistengo, cuatro en la localidad de Chapula y una en Tlacolula. Detalló que de las nueve personas inicialmente reportadas, cuatro ya fueron localizadas (una de ellas identificada sin vida mediante perfiles genéticos).</t>
-  </si>
-  <si>
-    <t>El comisionado de Búsqueda de Hidalgo, José Francisco García Reyes, informó que cinco pobladores de Tianguistengo continúan desaparecidos tras las inundaciones de octubre de 2025.</t>
-  </si>
-  <si>
-    <t>Contemplan 320 mdp para continuar saneamiento del río Tula en Hidalgo</t>
-  </si>
-  <si>
-    <t>Una partida de 320 millones de pesos permitirá continuar este año con el saneamiento del río Tula en Hidalgo, mediante la segunda fase de los trabajos previstos dentro del Plan Nacional Hídrico, informó Juan Carlos Chávez, director general de la CEAA. Los recursos se utilizarán para colectores marginales de aguas residuales, que conducirán el líquido para su tratamiento por parte de la CFE. A esto se sumarán 40 millones para nivelación de parcelas (5 mil hectáreas) y la tecnificación de canales de riego por parte de Conagua.</t>
-  </si>
-  <si>
-    <t>Saneamiento río Tula</t>
-  </si>
-  <si>
-    <t>La CEAA anunció una partida de 320 mdp para la segunda etapa del saneamiento del río Tula mediante colectores de aguas residuales, complementada con obras de Conagua y CFE.</t>
-  </si>
-  <si>
-    <t>Comisión Estatal de Agua y Escantarillado, Comisión Federal de Electricidad, Comisión Nacional del Agua</t>
-  </si>
-  <si>
-    <t>Juan Carlos Chávez</t>
-  </si>
-  <si>
-    <t>Caasim corta servicio de agua potable a gimnasios deudores en Pachuca</t>
-  </si>
-  <si>
-    <t>La Comisión de Agua y Alcantarillado de Sistemas Intermunicipales (Caasim) procedió al corte del suministro de agua potable a diversos gimnasios y centros deportivos exclusivos de la zona metropolitana de Pachuca debido al impago acumulado del servicio por parte de sus propietarios.</t>
-  </si>
-  <si>
-    <t>Adeudos Caasim</t>
-  </si>
-  <si>
-    <t>La Caasim suspendió el servicio de agua a gimnasios de lujo en Pachuca que presentaban adeudos históricos e incumplimiento de pago.</t>
-  </si>
-  <si>
     <t>Dese por enterado</t>
   </si>
   <si>
     <t>Comisión de Agua y Alcantarillado de Sistemas Intermunicipales (Caasim)</t>
   </si>
   <si>
-    <t>En marcha más de 253 mil MDP de inversión federal en Hidalgo</t>
-  </si>
-  <si>
-    <t>El titular de la Unidad de Planeación y Prospectiva, Miguel Ángel Tello Vargas, detalló que hay más de 253 mil millones de pesos federales en marcha en la entidad. Entre los rubros destacan 128 mil mdp para proyectos carreteros y los trenes México-Pachuca y México-Querétaro, 84 mil mdp para modernizar la termoeléctrica Tula II, la coquizadora de Pemex y el saneamiento del río Tula, así como 10 mil mdp para el Podecobi de Zapotlán.</t>
-  </si>
-  <si>
-    <t>Planeación detalló inversiones federales por 253 mil mdp en Hidalgo, abarcando trenes interurbanos, obras energéticas en Tula y polos industriales.</t>
-  </si>
-  <si>
-    <t>Unidad de Planeación y Prospectiva de Hidalgo, Comisión Federal de Electricidad, Petróleos Mexicanos</t>
-  </si>
-  <si>
-    <t>Miguel Ángel Tello Vargas, Claudia Sheinbaum Pardo, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Capacita SSH a profesionales de la salud y estudiantes</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo (SSH) capacitó a 163 profesionales y estudiantes de medicina en prevención, detección temprana y manejo de cáncer cervicouterino. La titular Vanesa Escalante Arroyo resaltó que las Brigadas de la Salud son instrumentos fundamentales para llevar consultas preventivas directas a regiones con barreras geográficas.</t>
-  </si>
-  <si>
-    <t>La SSH instruyó a 163 médicos y alumnos sobre cáncer cervicouterino, impulsando la detección móvil por medio de las Brigadas de la Salud.</t>
-  </si>
-  <si>
-    <t>Secretaría de Salud de Hidalgo</t>
-  </si>
-  <si>
-    <t>En el sexenio de AMLO 170 mil hidalguenses salieron de la pobreza</t>
-  </si>
-  <si>
-    <t>El secretario de Bienestar e Inclusión Social de Hidalgo, Ricardo Gómez Moreno, dio a conocer que conforme a mediciones del Inegi, 170 mil hidalguenses superaron la condición de pobreza extrema y moderada entre 2018 y 2024. Explicó que durante 2025 se canalizaron 22 mil 651 mdp federales para programas de bienestar en Hidalgo, y para 2026 se estima erogar más de 4 mil mdp de presupuesto social estatal, de los cuales la Sebiso coordinará 602 mdp.</t>
-  </si>
-  <si>
     <t>Índice De Pobreza</t>
   </si>
   <si>
-    <t>La Sebiso reportó que 170 mil hidalguenses superaron la pobreza durante el pasado sexenio de López Obrador, previendo 4 mil mdp en apoyos locales en 2026.</t>
-  </si>
-  <si>
     <t>Oscar Raúl Pérez</t>
   </si>
   <si>
-    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Instituto Nacional de Estadística y Geografía (Inegi)</t>
-  </si>
-  <si>
-    <t>Ricardo Gómez Moreno, Andrés Manuel López Obrador, Julio Menchaca Salazar, Claudia Sheinbaum Pardo</t>
-  </si>
-  <si>
-    <t>Hidalgo ha destinado 121 mil MDP a la educación</t>
-  </si>
-  <si>
-    <t>En un acto de inicio de ciclo escolar 2026-2027 en la Secundaria General No. 2 de Pachuca, el gobernador Julio Menchaca Salazar resaltó que se han invertido 121 mil millones de pesos en materia educativa durante su administración, fruto de un eficiente manejo de los recursos del erario, entregando paquetes escolares, calzado, uniformes y útiles gratuitos.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca inauguró el ciclo lectivo en Pachuca, destacando una inversión magisterial acumulada de 121 mil mdp y distribuyendo apoyos escolares.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Gobierno del Estado de Hidalgo, Secundaria General No. 2 de Pachuca</t>
-  </si>
-  <si>
-    <t>Advierten con bloquear la Pachuca-Tulancingo</t>
-  </si>
-  <si>
-    <t>Padres de familia de la escuela primaria Gregorio Torres Quintero, de La Lagunilla, Tulancingo, impidieron el ingreso a clases en el primer día del ciclo escolar debido a que las autoridades de la SEPH incumplieron la sustitución del intendente, plaza vacante desde mayo. Ana Karen Vargas Alvarado, tesorera del comité, advirtió que bloquearán la carretera Pachuca-Tulancingo si no hay solución, reclamando además la falta de renovación contractual de dos docentes que afecta a 132 alumnos.</t>
-  </si>
-  <si>
     <t>Queja padres de familia</t>
   </si>
   <si>
-    <t>Tutores de primaria en Tulancingo tomaron las instalaciones escolares por falta de conserje y profesores suplentes, amenazando con bloquear la carretera federal.</t>
-  </si>
-  <si>
     <t>Jesús Riveros</t>
   </si>
   <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Primaria Gregorio Torres Quintero, Comité de Padres de Familia</t>
-  </si>
-  <si>
-    <t>Ana Karen Vargas Alvarado</t>
-  </si>
-  <si>
-    <t>Policías, apoyan a pachuqueños por torrencial lluvia de ayer</t>
-  </si>
-  <si>
-    <t>Elementos de la policía estatal de la SSPH desplegaron un operativo de patrullaje, auxilio y remolque para conductores y familias cuyos automóviles quedaron varados en charcos e inundaciones pluviales en diversos puntos críticos de Pachuca. Los cuerpos de seguridad instaron al uso responsable de la línea 911 ante emergencias meteorológicas.</t>
-  </si>
-  <si>
-    <t>Agentes de la Policía Estatal de Hidalgo proporcionaron auxilio vial y remorcaron vehículos descompuestos por las severas inundaciones en Pachuca.</t>
-  </si>
-  <si>
-    <t>Regreso a clases fue normal: Gabinete de Seguridad de Hidalgo</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar informó que el operativo del regreso a clases concluyó con saldo blanco. Durante la reunión del Gabinete de Seguridad, se reportó además el desmantelamiento de tres narcotienditas en Atitalaquia y Tolcayuca (deteniendo a cinco hombres con 1,306 dosis de droga), la aprehensión de 16 personas con 984 dosis de estupefacientes en 8 municipios (entre ellos Tizayuca y Pachuca), el decomiso de 7,531 litros de huachicol en Ixmiquilpan y Tlaxcoapan, y la captura de 6 generadores de violencia con armas largas y cortas en la vía Huichapan-Tecozautla. Asimismo, PC atendió la caída de siete árboles y dos barda por el temporal, y se logró la localización de nueve personas con fichas de búsqueda activas.</t>
-  </si>
-  <si>
-    <t>Informe de seguridad</t>
-  </si>
-  <si>
-    <t>El Gabinete de Seguridad de Hidalgo reportó saldo blanco en el regreso escolar y detalló el decomiso de 7,500 litros de huachicol y captura de narcomenudistas.</t>
-  </si>
-  <si>
-    <t>Gabinete de Seguridad de Hidalgo, Secretaría de Seguridad Pública de Hidalgo, Secretaría de la Defensa Nacional, Comisión Federal de Electricidad, Protección Civil, C5i</t>
-  </si>
-  <si>
-    <t>En la Mira: Restricciones sin soluciones en el bulevar Felipe Ángeles</t>
-  </si>
-  <si>
-    <t>Menos de 48 horas de movimiento vehicular habitual bastaron para colapsar nuevamente el bulevar Felipe Ángeles. Todo apunta a que la exclusividad del carril confinado sí ahorca el desahogo de autos en esta vía que es de vital importancia para quienes viajan todos los días a la Ciudad de México o estudian en escuelas del sur de la capital hidalguense. Algo tendrán que hacer para revertir este efecto porque es cuestión de que la ciudadanía llegue al hartazgo con las multas para que nuevamente arda el descontento social. Lo peor es que solo hay restricciones, pero no hay soluciones.</t>
-  </si>
-  <si>
-    <t>Carril confinado</t>
-  </si>
-  <si>
-    <t>Columna que critica las restricciones viales y la aplicación de multas en el bulevar Felipe Ángeles debido a la exclusividad del carril confinado del Tuzobús.</t>
-  </si>
-  <si>
-    <t>En la Mira</t>
-  </si>
-  <si>
-    <t>Secretaría de Movilidad y Transporte</t>
-  </si>
-  <si>
-    <t>En la Mira: Necesidad de regular pantallas y dispositivos en las aulas</t>
-  </si>
-  <si>
-    <t>El secretario de Educación Pública de Hidalgo, Natividad Castrejón, habló sobre la necesidad de regular el uso de dispositivos electrónicos en las aulas. Aclaró que no se trata de prohibir por prohibir, pero advirtió que han detectado menores cuyo sistema visual aún está en desarrollo y que pasan demasiado tiempo frente a las pantallas, con posibles afectaciones a su salud visual.</t>
-  </si>
-  <si>
-    <t>Columna de opinión que aborda el planteamiento de Natividad Castrejón de normar las pantallas digitales escolares para proteger la salud visual infantil.</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón</t>
-  </si>
-  <si>
-    <t>Gobernador da inicio formal a ciclo escolar</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar encabezó el inicio del ciclo escolar 2026-2027 en la Secundaria General No. 2 de Pachuca, donde destacó que durante cuatro años se han destinado 121 mil millones de pesos a la educación. El mandatario señaló que estos recursos permiten mejorar y garantizar el acceso y la permanencia escolar, además de respaldar a las familias mediante la entrega de becas, uniformes, calzado y útiles. Durante el acto, se entregaron paquetes de uniformes, calzado, útiles escolares y libros de texto. En total, el gobierno estatal distribuirá 500 mil paquetes para estudiantes de educación básica. Natividad Castrejón Valdez informó que regresaron a las aulas 569 mil 987 alumnas y alumnos de educación básica, junto con más de 53 mil docentes, directivos y trabajadores en la entidad.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca inauguró formalmente el ciclo lectivo 2026-2027 en Pachuca, resaltando una inversión de 121 mil mdp y la entrega gratuita de 500 mil paquetes de útiles, uniformes y calzado.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Secundaria General No. 2 de Pachuca</t>
-  </si>
-  <si>
-    <t>Ciclo pasado registró mil 385 casos de violencia escolar</t>
-  </si>
-  <si>
-    <t>La violencia física y psicológica concentró la mayor cantidad de reportes registrados por la Secretaría de Educación Pública de Hidalgo (SEPH) durante el ciclo escolar 2025-2026, con 380 y 316 casos, respectivamente, informó el titular de la dependencia, Natividad Castrejón Valdez. Al corte del 27 de agosto de 2026, la dependencia acumuló mil 385 reportes de distintas formas de violencia, de los cuales más de la mitad ya fueron atendidos y resueltos. Después de los casos de violencia física y psicológica, se contabilizaron 163 reportes de violencia sexual, 83 relacionados con sustancias ilícitas, 56 de violencia sexual dentro de la familia y 56 por exclusión social. La lista también incluye 53 casos por artículos prohibidos, 43 por tendencia suicida, 43 por omisión del personal educativo, 38 relacionados con actividades de riesgo difundidas en entornos digitales y sociales, 35 de violencia cibernética, 32 de violencia familiar y 32 de violencia verbal. Además, hubo reportes por omisión de madres, padres o tutores, autolesiones, violencia económica y moral. El secretario de la SEPH explicó que la SEPH no limita sus registros a hechos ocurridos dentro de los planteles, pues también recibe casos de abandono parental y violencia sexual dentro del hogar. Cuando se trata de agresiones sexuales, los reportes son canalizados de inmediato a la Procuraduría General de Justicia del Estado de Hidalgo (PGJEH).</t>
-  </si>
-  <si>
-    <t>La SEPH reportó mil 385 quejas por violencia escolar en el ciclo 2025-2026 en Hidalgo, lideradas por agresiones físicas (380) y psicológicas (316), con un 50% ya resuelto.</t>
-  </si>
-  <si>
-    <t>Secretaría de Educación Pública de Hidalgo, Procuraduría General de Justicia del Estado de Hidalgo</t>
-  </si>
-  <si>
-    <t>Dejan la pobreza 170 mil hidalguenses en 7 años</t>
-  </si>
-  <si>
-    <t>Los programas sociales federales y estatales contribuyeron a reducir la pobreza y las brechas de desigualdad en Hidalgo, donde 170 mil personas salieron de esa condición entre 2018 y 2024, de acuerdo con datos del Instituto Nacional de Estadística y Geografía (Inegi). Durante la conferencia de prensa semanal del gobierno estatal, Ricardo Gómez Moreno, secretario de Bienestar e Inclusión Social, destacó que la coordinación con la administración de la presidenta Claudia Sheinbaum Pardo permitió ampliar la atención a sectores vulnerables. Explicó que desde el inicio del gobierno de Julio Menchaca se diseñaron acciones para llegar a familias que antes no recibían apoyos. Para 2026, Hidalgo destinará más de 4 mil millones de pesos a programas sociales, mientras que la dependencia ejercerá más de 602 millones en apoyos para madres trabajadoras, personas cuidadoras, migrantes, juventudes, adultos mayores y otros grupos. La inversión federal en programas sociales alcanzó 22 mil 651 millones de pesos durante 2025 y anticipó que este año superará esa cantidad. Añadió que los recursos también generan actividad económica en las distintas regiones.</t>
-  </si>
-  <si>
-    <t>La Sebiso hidalguense reportó que 170 mil ciudadanos superaron la condición de pobreza entre 2018 y 2024 gracias a programas sociales, anunciando un presupuesto de 4 mil mdp estatales para 2026.</t>
-  </si>
-  <si>
-    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Instituto Nacional de Estadística y Geografía</t>
-  </si>
-  <si>
     <t>Ricardo Gómez Moreno, Julio Menchaca Salazar, Claudia Sheinbaum Pardo</t>
   </si>
   <si>
     <t>Van a demoler primaria en Tulancingo; edificarán otra</t>
   </si>
   <si>
-    <t>La escuela primaria Aquiles Serdán, de Tulancingo, deberá ser demolida y reconstruida, proceso que podría extenderse durante todo el ciclo escolar 2026-2027, informó el titular de la Secretaría de Educación Pública de Hidalgo (SEPH), Natividad Castrejón. Castrejón indicó que los alumnos iniciarán clases con normalidad mientras se define una sede de clases presenciales de manera temporal. La postura de la SEPH contrasta con la información recibida por padres de familia de los turnos matutino y vespertino, a quienes se les había planteado la modalidad en línea mientras se efectuaban las obras en el plantel que presenta daños estructurales. Padres rechazaron distribuir a sus hijos en otras escuelas y pidieron que, si resulta indispensable abandonar temporalmente la escuela, se habilite un solo espacio presencial temporal.</t>
-  </si>
-  <si>
-    <t>La SEPH de Hidalgo decretó la demolición completa y reconstrucción de la primaria Aquiles Serdán en Tulancingo por fallas estructurales, buscando habilitar una sede presencial provisional ante la queja de padres por clases virtuales.</t>
-  </si>
-  <si>
     <t>Octavio Jaimes</t>
+  </si>
+  <si>
+    <t>Celulares o aprendizaje</t>
+  </si>
+  <si>
+    <t>Columna de opinión de la diputada federal Nuvia Mayorga Delgado, quien analiza el impacto del regreso a clases del ciclo escolar 2026-2027 en Hidalgo. La columnista aborda con rigor los datos de la OCDE, los cuales alertan que la reducción de inversión educativa por estudiante ha derivado en un rezago educativo de 4.9% en la entidad. Asimismo, defiende la urgencia de regular de forma estricta el uso de teléfonos celulares y dispositivos digitales en los planteles de nivel básico y media superior, argumentando que funcionan como un severo distractor en las aulas y afectan la salud visual e intelectual de los menores, promoviendo en su lugar la alfabetización digital con supervisión pedagógica.</t>
+  </si>
+  <si>
+    <t>Columna de Nuvia Mayorga que analiza las implicaciones del uso descontrolado de celulares en las aulas hidalguenses, respaldando la necesidad de establecer regulaciones para optimizar el aprendizaje.</t>
+  </si>
+  <si>
+    <t>Organización para la Cooperación y el Desarrollo Económicos, Secretaría de Educación Pública</t>
+  </si>
+  <si>
+    <t>Nuvia Mayorga Delgado</t>
+  </si>
+  <si>
+    <t>El curado de piñón es el más costoso</t>
+  </si>
+  <si>
+    <t>Hidalgo produjo 106 millones 155 mil 660 litros de pulque durante el año 2023, consolidando a la entidad como el principal productor de esta tradicional bebida ancestral en el país, por delante de Tlaxcala y el Estado de México. De acuerdo con el Servicio de Información Agroalimentaria y Pesquera (SIAP), adscrito a la Secretaría de Agricultura y Desarrollo Rural (Sader), el curado de piñón se cotiza como el sabor más costoso del mercado (con un costo promedio de 40 pesos por litro la base natural, incrementándose sustancialmente con frutos, semillas o piñones). Se destaca la riqueza cultural de los tradicionales curados de nuez, almendra, guayaba y fresa en el Altiplano Pulquero, particularmente en la comarca de los Llanos de Apan.</t>
+  </si>
+  <si>
+    <t>Apan</t>
+  </si>
+  <si>
+    <t>A qué sabe la patria</t>
+  </si>
+  <si>
+    <t>El curado de piñón lidera los costos en el mercado de curados del Altiplano de Apan, en un contexto donde Hidalgo destaca a nivel nacional con una producción de 106 millones de litros de pulque.</t>
+  </si>
+  <si>
+    <t>Alma Leticia Sánchez</t>
+  </si>
+  <si>
+    <t>Saderh</t>
+  </si>
+  <si>
+    <t>Secretaría de Agricultura y Desarrollo Rural, Servicio de Información Agroalimentaria y Pesquera</t>
+  </si>
+  <si>
+    <t>Opera Centro de Verificación Móvil</t>
+  </si>
+  <si>
+    <t>La Secretaría de Medio Ambiente y Recursos Naturales de Hidalgo (Semarnath) puso en funcionamiento un módulo móvil de verificación vehicular con el objetivo de facilitar el trámite ambiental a los automovilistas locales. La unidad opera de forma regular en los municipios de Apan (instalada dentro de la Delegación) e Ixmiquilpan (en el Mirador, colonia San Miguel), ofreciendo servicios de lunes a sábado de 9:00 a 18:00 horas. Con este sistema se busca desahogar la afluencia en los verificentros tradicionales fijos del estado y garantizar emisiones limpias.</t>
+  </si>
+  <si>
+    <t>Verificación vehicular</t>
+  </si>
+  <si>
+    <t>La Semarnath implementó una unidad móvil de verificación en Apan e Ixmiquilpan para acercar y agilizar el trámite de control de emisiones vehiculares.</t>
+  </si>
+  <si>
+    <t>Semarnath</t>
+  </si>
+  <si>
+    <t>Secretaría de Medio Ambiente y Recursos Naturales de Hidalgo</t>
+  </si>
+  <si>
+    <t>Destaca Menchaca las obras federales</t>
+  </si>
+  <si>
+    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, expresó su total respaldo a los logros y avances expuestos por la presidenta de la República, Claudia Sheinbaum Pardo, en el marco de la entrega de su Segundo Informe de Gobierno. El mandatario estatal reconoció el impacto directo de megaproyectos federales en Hidalgo, como la construcción del tren de alta velocidad México-Pachuca, la modernización de distritos agrícolas de riego, programas sociales del Bienestar y la entrega de más de 31 mil viviendas que ya se edifican en la entidad con recursos conjuntos del Infonavit, Conavi y dependencias estatales.</t>
+  </si>
+  <si>
+    <t>Informe Sheinbaum</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar respaldó las obras federales en Hidalgo presentadas en el Segundo Informe de Gobierno de la presidenta Claudia Sheinbaum.</t>
+  </si>
+  <si>
+    <t>Gobierno de la República, Instituto del Fondo Nacional de la Vivienda para los Trabajadores, Comisión Nacional de Vivienda</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Claudia Sheinbaum Pardo</t>
+  </si>
+  <si>
+    <t>Amenaza el descortezador hasta 30% de oyameles</t>
+  </si>
+  <si>
+    <t>La proliferación del escarabajo descortezador amenaza la biodiversidad del Parque Nacional El Chico, poniendo en riesgo latente de infestación hasta un 30 por ciento del bosque de oyamel de esta importante área natural protegida. Investigadores y estudiantes de biología de la Universidad Autónoma del Estado de Hidalgo (UAEH), encabezados por Edith Maldonado Cruz y los académicos Maritza López Herrera y Raúl Velasco Azorsa, llevan a cabo muestreos de suelo y de insectos para evaluar la afectación y proponer medidas de control biológico e introducción de especies vegetales que sirvan como barrera de protección natural contra la plaga.</t>
+  </si>
+  <si>
+    <t>Mineral del Chico</t>
+  </si>
+  <si>
+    <t>Gusano Descortezador</t>
+  </si>
+  <si>
+    <t>Investigadores de la UAEH alertaron sobre una severa infestación de escarabajo descortezador que pone en riesgo hasta el 30% del oyamel en el Parque Nacional El Chico.</t>
+  </si>
+  <si>
+    <t>Universidad Autónoma del Estado de Hidalgo, Parque Nacional El Chico</t>
+  </si>
+  <si>
+    <t>Edith Maldonado Cruz, Maritza López Herrera, Raúl Velasco Azorsa</t>
+  </si>
+  <si>
+    <t>Cecatis te capacita para emprender</t>
+  </si>
+  <si>
+    <t>La Secretaría de Educación Pública (SEP) federal mantiene abiertos los procesos de capacitación para el trabajo en 24 especialidades industriales, comerciales y técnicas de los Centros de Capacitación para el Trabajo Industrial (Cecati) en Hidalgo. Los planteles, ubicados en municipios clave como Tizayuca (Cecati 47), Tepeji del Río, Pachuca (Cecati 114), Tulancingo (Cecati 123) y Atotonilco de Tula (Cecati 201), ofrecen talleres de mecánica automotriz, confección de ropa, carpintería, electricidad y computación con certificación oficial de la SEP, favoreciendo la inserción laboral y el autoempleo de jóvenes y adultos mayores.</t>
+  </si>
+  <si>
+    <t>Capacitación Para El Trabajo</t>
+  </si>
+  <si>
+    <t>Los planteles del Cecati en Hidalgo ofrecen cursos certificados por la SEP en 24 especialidades para fomentar el emprendimiento y la profesionalización técnica.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública</t>
+  </si>
+  <si>
+    <t>Nelly Campos</t>
+  </si>
+  <si>
+    <t>Punk-To Creativo festeja aniversario</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura municipal de Pachuca, en coordinación con el colectivo artístico Dedos, anunció el programa de actividades de Punk-To Creativo, encuentro juvenil que festejará su aniversario los días 5 y 6 de septiembre en el Parque de Maestranza. El evento tiene como propósito la recuperación del tejido social e impulso del talento de los jóvenes, reuniendo a creadores gráficos, músicos urbanos, artistas de grafiti y promotores culturales del estado para un intercambio lúdico y formativo de libre acceso para las familias de la capital.</t>
+  </si>
+  <si>
+    <t>Impulso a la cultura</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura municipal de Pachuca y el colectivo Dedos realizarán el encuentro cultural juvenil 'Punk-To Creativo' el 5 y 6 de septiembre en Parque de Maestranza.</t>
+  </si>
+  <si>
+    <t>Fernanda Huerta</t>
+  </si>
+  <si>
+    <t>Cultura</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura municipal</t>
+  </si>
+  <si>
+    <t>Celebran El Grito en barrios de Pachuca</t>
+  </si>
+  <si>
+    <t>Para conmemorar las festividades septembrinas, en Pachuca de Soto se realizarán de forma paralela los tradicionales 'Gritos de Independencia' en diversas colonias y barrios emblemáticos de la capital hidalguense, destacando las celebraciones populares comunitarias organizadas de forma autónoma en El Cubitos, Santa Catarina, San Miguel Cerezo, Santiago Tlapacoya, San Antonio El Desmonte, Huixmí y Tlapacoya. El gobernador Julio Menchaca Salazar presidirá la ceremonia cívica oficial de El Grito en la Plaza Juárez el próximo 15 de septiembre de 2026 en el Edificio de Gobierno, coordinándose operativos preventivos de Protección Civil.</t>
+  </si>
+  <si>
+    <t>Grito De Independencia</t>
+  </si>
+  <si>
+    <t>Pachuca se alista para las Fiestas Patrias con festejos comunitarios y vecinales de El Grito en los barrios y la ceremonia oficial en Plaza Juárez a cargo de Julio Menchaca.</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Protección Civil</t>
+  </si>
+  <si>
+    <t>Proponen sitios para reubicar el basurero</t>
+  </si>
+  <si>
+    <t>Vecinos e integrantes del Movimiento en Defensa del Manantial Cerro Colorado presentaron ante la titular de la Secretaría de Medio Ambiente y Recursos Naturales de Hidalgo (Semarnath), Mónica Patricia Mixtega Trejo, tres opciones técnicas para reubicar el relleno sanitario regional del municipio de Tula. Las propuestas se centran en tres antiguas canteras abandonadas y sin uso ubicadas en la comarca del ejido Xhiteje de Zapata, abarcando una superficie total de 12.5 hectáreas. Por su parte, colonos de Siete Mezquites rechazaron la opción del ejido, advirtiendo sobre posibles filtraciones ambientales al manantial de agua de la comarca del cual dependen más de 300 mil habitantes.</t>
+  </si>
+  <si>
+    <t>Rello Sanitario</t>
+  </si>
+  <si>
+    <t>Vecinos de Tula propusieron a la Semarnath tres canteras del ejido Xhiteje de Zapata para reubicar el basurero regional, con la oposición de colonos de Siete Mezquites.</t>
+  </si>
+  <si>
+    <t>Rosalía Maldonado</t>
+  </si>
+  <si>
+    <t>Secretaría de Medio Ambiente y Recursos Naturales de Hidalgo, Movimiento en Defensa del Manantial Cerro Colorado, Comisión Federal de Electricidad</t>
+  </si>
+  <si>
+    <t>Mónica Patricia Mixtega Trejo, Fernando Quijano</t>
+  </si>
+  <si>
+    <t>Gobernador reconoce proyectos federales de gran impacto en Hidalgo</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar respaldó a la presidenta Claudia Sheinbaum Pardo tras asistir a la entrega de su segundo Informe de Gobierno. Menchaca destacó la coordinación de proyectos federales de gran impacto en Hidalgo: el Tren México-Pachuca, la estación en Tula del Tren México-Querétaro, el Polo de Desarrollo Económico para el Bienestar en Zapotlán, la tecnificación de distritos de riego, la construcción de Viviendas para el Bienestar, la carretera Huejutla-Tamazunchale y el saneamiento de Tula. Asimismo, agradeció a la mandataria por el apoyo brindado tras la vaguada monzónica de octubre de 2025 para atender a 28 municipios hidalguenses.</t>
+  </si>
+  <si>
+    <t>Respaldo a Sheinbaum</t>
+  </si>
+  <si>
+    <t>Julio Menchaca reconoció y agradeció el impacto de las obras federales en Hidalgo, como los trenes México-Pachuca y México-Querétaro, impulsados por la presidenta Claudia Sheinbaum.</t>
+  </si>
+  <si>
+    <t>Gobierno del Estado de Hidalgo, Gobierno de la República, Infonavit, Conavi</t>
+  </si>
+  <si>
+    <t>El 5 de septiembre el Congreso recibirá oficialmente el informe</t>
+  </si>
+  <si>
+    <t>El Congreso de Hidalgo recibirá formalmente el informe de actividades del gobernador Julio Menchaca Salazar el próximo sábado 5 de septiembre, informó el diputado Andrés Velázquez Vázquez, presidente de la Junta de Gobierno. El secretario de Gobierno, Guillermo Olivares Reyna, será quien acude al recinto legislativo en representación del mandatario estatal para realizar la entrega protocolaria durante una sesión solemne. Por su parte, el gobernador Menchaca llevará a cabo una ceremonia para la entrega de su informe el viernes 4 de septiembre en las instalaciones de la Feria de Pachuca.</t>
+  </si>
+  <si>
+    <t>Informe De Gobierno</t>
+  </si>
+  <si>
+    <t>El secretario de Gobierno, Guillermo Olivares, entregará el informe oficial del gobernador Julio Menchaca al Congreso del Estado el próximo 5 de septiembre en una sesión solemne.</t>
+  </si>
+  <si>
+    <t>Socorro Ávila</t>
+  </si>
+  <si>
+    <t>Congreso del Estado de Hidalgo, Secretaría de Gobierno, Secretaría de Cultura del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares Reyna, Andrés Velázquez Vázquez, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Ranking de Gobernadores (Demoscopia)</t>
+  </si>
+  <si>
+    <t>La encuestadora Demoscopia publicó su ranking nacional de aprobación de gobernadores correspondiente al mes de agosto de 2026. El gobernador del estado de Hidalgo, Julio Menchaca Salazar, se posicionó en el primer lugar nacional con una calificación de 68.4% de aprobación ciudadana, seguido por los mandatarios de Puebla, Querétaro, CDMX y el Estado de México en las primeras posiciones del estudio de opinión.</t>
+  </si>
+  <si>
+    <t>Aprobación Gobernador</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar se ubicó como el mandatario estatal mejor calificado del país en agosto de 2026, alcanzando el 68.4% de la aprobación en la encuesta de Demoscopia.</t>
+  </si>
+  <si>
+    <t>Suman 2 muertes por gusano barrenador en humanos: SSa</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud (SSa) federal reportó en su último informe epidemiológico que el estado de Hidalgo documenta un acumulado de 21 contagios humanos por miasis provocada por cochliomyia hominivorax (gusano barrenador), lo que representa el 4.1% de la incidencia nacional de la enfermedad. El estado acumula también dos fallecimientos asociados a este padecimiento, habiéndose detectado dos nuevos contagios en los últimos siete días. Las autoridades estatales y federales han urgido a la población a extremar la higiene y la curación oportuna de heridas.</t>
+  </si>
+  <si>
+    <t>Gusano barrenador</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud federal reportó que Hidalgo acumula 21 contagios y dos decesos humanos debido a infestaciones por el gusano barrenador, reforzando campañas de prevención.</t>
+  </si>
+  <si>
+    <t>Nathali González</t>
+  </si>
+  <si>
+    <t>Secretaría de Salud Federal, Secretaría de Salud de Hidalgo, Dirección General de Epidemiología</t>
+  </si>
+  <si>
+    <t>Titular de Cultura descarta lucro y plagio de bordados de Jaltocán</t>
+  </si>
+  <si>
+    <t>La secretaria de Cultura de Hidalgo, Neyda Naranjo Baltazar, descartó que se haya registrado plagio o lucro en la venta de prendas con sublimado de bordados típicos de Jaltocán en el estado. Explicó que tras analizar el caso en el Consejo Técnico Artesanal, se determinó que se trató de un maestro de danza que imprimió faldas de ensayo para sus alumnas de bajos recursos que no podían costear un traje bordado a mano. No obstante, alertó sobre intermediarios que compran artesanías locales a bajo costo y defendió la campaña 'Hidalgo no regatea' para fomentar la compra directa.</t>
+  </si>
+  <si>
+    <t>Jaltocán</t>
+  </si>
+  <si>
+    <t>Apropiación cultural</t>
+  </si>
+  <si>
+    <t>La titular de Cultura de Hidalgo, Neyda Naranjo, aclaró que la impresión de faldas sublimadas de Jaltocán fue un apoyo escolar sin fines de lucro, descartando plagio de artesanías.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura de Hidalgo, Consejo Técnico Artesanal, Congreso del Estado de Hidalgo, Secretaría de Bienestar, Secretaría de Turismo</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo Baltazar</t>
+  </si>
+  <si>
+    <t>Trabajos del Plan Hídrico acumulan más de 650 mdp</t>
+  </si>
+  <si>
+    <t>Como parte de la inversión del proyecto federal denominado "Plan Hídrico" en la región de Tula, el gobierno de Hidalgo destinó un monto de 657 millones en diferentes acciones en 2025 y lo que va de 2026, informó el director general de la Comisión Estatal de Agua y Alcantarillado, Juan Carlos Chávez González. El funcionario detalló que como parte de la primera etapa de estos trabajos, el gobierno del estado destinó el año pasado 200 millones de pesos para la primera fase de la rehabilitación y saneamiento de colectores de agua residual en Tula, infraestructura que traslada estos residuos a la Planta de Tratamiento de Aguas Residuales propiedad de CFE. De igual manera, el gobierno de Hidalgo erogó 27 millones de pesos más para nivelación de 2 mil 600 hectáreas de parcelas; finalmente, el gasto de 110 millones de pesos en adquisición de maquinaria para continuar con las labores. En tanto, para este año se prevé la segunda etapa de atención de los colectores en Tula, con un monto de 320 millones de pesos para el saneamiento y 40 millones de pesos adicionales en nivelación de parcelas, buscando atender 5 mil hectáreas.</t>
+  </si>
+  <si>
+    <t>La CEAA estatal reportó que el gobierno de Hidalgo ha destinado 657 mdp entre 2025 y 2026 para obras de saneamiento de colectores de agua residual, tecnificación agrícola y adquisición de maquinaria en la región de Tula como parte de la primera etapa del Plan Hídrico.</t>
+  </si>
+  <si>
+    <t>Sipdus, Presidencia, Gobernador</t>
+  </si>
+  <si>
+    <t>Buscan ahorrar 650 millones de metros cúbicos de agua</t>
+  </si>
+  <si>
+    <t>Un ahorro estimado de 650 millones de metros cúbicos de agua al año es la meta central del proyecto hídrico que se plantea para territorio hidalguense, una estrategia con una inversión federal superior a 11 mil 500 millones de pesos y una proyección de 30 años que pretende atacar al mismo tiempo los problemas de inundaciones, contaminación y desperdicio de agua en el campo. El plan contempla intervenciones en cuatro municipios para reducir el riesgo de inundaciones mediante la construcción y reforzamiento de taludes y bordos en puntos críticos de Tula, Tepeji, Mixquiahuala e Ixmiquilpan. La intención es disminuir la exposición de zonas urbanas vulnerables ante fenómenos que en los últimos años han dejado daños importantes en la región. "No podemos hablar de agua sin hablar de seguridad", sostuvo Juan Carlos Chávez González, director general de la Comisión Estatal del Agua y Alcantarillado, al explicar que la infraestructura hidráulica también tiene una función preventiva, toda vez que con ella se protegerá a miles de familias que están asentadas en zonas consideradas como susceptibles de inundación.</t>
+  </si>
+  <si>
+    <t>La Comisión Estatal del Agua y Alcantarillado (CEAA) informó que el proyecto hídrico estatal tiene como meta ahorrar 650 millones de metros cúbicos de agua al año y ejecutar defensas en Tula, Tepeji, Mixquiahuala e Ixmiquilpan para reducir riesgos de inundación.</t>
+  </si>
+  <si>
+    <t>Sipdus, Presidencia</t>
+  </si>
+  <si>
+    <t>Menchaca entregará su segundo informe el 5 de septiembre</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar entregará oficialmente su segundo informe de actividades gubernamentales el sábado 5 de septiembre ante el Congreso del Estado de Hidalgo, mediante la representación solemne de Guillermo Olivares Reyna, secretario de Gobierno. La presidencia de la Junta de Gobierno legislativa, encabezada por Andrés Velázquez Vázquez, confirmó la recepción en el Salón de Plenos de la Cámara, mientras que el gobernador encabezará una ceremonia pública masiva el viernes 4 de septiembre en las instalaciones de la Feria de Pachuca.</t>
+  </si>
+  <si>
+    <t>La Junta de Gobierno del Congreso confirmó que el secretario de Gobierno Guillermo Olivares entregará formalmente el segundo informe de Julio Menchaca el 5 de septiembre, previo al evento público del 4 de septiembre en la Feria.</t>
+  </si>
+  <si>
+    <t>Gobernador, Congreso del Estado de Hidalgo, Secretaría de Gobierno, Junta de Gobierno</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Guillermo Olivares Reyna, Andrés Velázquez Vázquez</t>
+  </si>
+  <si>
+    <t>Suman 2 decesos humanos por miasis de gusano barrenador</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud federal y estatal emitieron un reporte epidemiológico conjunto en el que informaron que en Hidalgo se acumulan 21 casos acumulados de miasis cutánea en humanos provocados por la larva del gusano barrenador (Cochliomyia hominivorax), que representan el 4.1% del total nacional. Se confirmaron dos nuevos contagios en la última semana, así como dos lamentables defunciones en la entidad vinculadas directamente a la gravedad de las infecciones y demoras en atención. Se exhorta a curar heridas de inmediato.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud federal y del estado reportaron un acumulado de 21 contagios de miasis cutánea por gusano barrenador en humanos en Hidalgo, sumando dos defunciones asociadas.</t>
+  </si>
+  <si>
+    <t>Guadalupe Trejo</t>
+  </si>
+  <si>
+    <t>SSH, Secretaría de Salud Federal, Dirección General de Epidemiología</t>
+  </si>
+  <si>
+    <t>Exigen intendente en primaria de Tulancingo</t>
+  </si>
+  <si>
+    <t>Padres de familia de la Escuela Primaria Gregorio Torres Quintero, de la localidad de La Lagunilla en Tulancingo, clausuraron y tomaron las instalaciones del plantel escolar durante el primer día del ciclo escolar 2026-2027. Los tutores e integrantes del comité denuncian que la SEPH ha incumplido con la asignación y sustitución de la plaza de intendente escolar que se mantiene vacante desde mayo, afectando las condiciones sanitarias de 132 alumnos. Advierten que de no haber respuesta, bloquearán de forma indefinida la carretera federal Pachuca-Tulancingo.</t>
+  </si>
+  <si>
+    <t>Tutores de la primaria Gregorio Torres Quintero en Tulancingo tomaron el plantel escolar en protesta por la falta de conserje y advirtieron con bloquear la carretera federal si la SEPH no resuelve.</t>
+  </si>
+  <si>
+    <t>SEPH, Escuela Primaria Gregorio Torres Quintero, Comité de Padres de Familia</t>
+  </si>
+  <si>
+    <t>DIFH incorpora tecnología robótica Lokomat para terapias</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo, presidido por Edda Vite Ramos, presentó oficialmente la adquisición del robot Lokomat, una innovadora tecnología de vanguardia robótica médica diseñada para terapias de marcha y neuro-rehabilitación de pacientes con discapacidad motora. El equipo implicó una inversión de 18 millones 498 mil 956 pesos en el Centro de Rehabilitación Integral de Hidalgo (CRIH) en Pachuca. Edda Vite destacó que el CRIH cuenta con 415 pacientes registrados, de los cuales 215 son candidatos. El titular del DIFH, Ricardo Alvizo Contreras, resaltó que es el primer DIF estatal de la zona centro en implementarlo.</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo adquirió e instaló un robot Lokomat de 18.4 mdp en el CRIH en Pachuca para brindar terapias de neuro-rehabilitación motriz accesibles a 215 pacientes.</t>
+  </si>
+  <si>
+    <t>DIFH, Centro de Rehabilitación Integral de Hidalgo, Sistema Nacional DIF</t>
+  </si>
+  <si>
+    <t>Salen de la pobreza 170 mil hidalguenses en seis años</t>
+  </si>
+  <si>
+    <t>Durante el periodo 2018-2024, un total de 170 mil hidalguenses superaron las condiciones de pobreza extrema y moderada en la entidad, gracias a la inyección coordinada de programas sociales estatales y de la Federación, informó el titular de la Sebiso, Ricardo Gómez Moreno, en conferencia semanal. Señaló que en 2025 se dispersaron 22 mil 651 mdp en programas de Bienestar en Hidalgo. Para 2026, la inversión social estatal sumará 4 mil mdp, de los cuales la Sebiso ejercerá 602 mdp en diversos apoyos, consolidando las acciones conjuntas instruidas por Julio Menchaca y Claudia Sheinbaum.</t>
+  </si>
+  <si>
+    <t>La Sebiso estatal reportó que 170 mil personas superaron la pobreza en Hidalgo en el periodo 2018-2024, destacando un presupuesto de 4 mil mdp de origen estatal para apoyos sociales en 2026.</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar e Inclusión Social de Hidalgo, Instituto Nacional de Estadística y Geografía, Gobierno del Estado de Hidalgo</t>
+  </si>
+  <si>
+    <t>Impresos locales</t>
+  </si>
+  <si>
+    <t>Zunoticia</t>
+  </si>
+  <si>
+    <t>Espejeando: Ajustes presupuestales municipales para obras de Bienestar</t>
+  </si>
+  <si>
+    <t>Se han aplicado ajustes a los presupuestos de los gobiernos municipales para poder destinar parte de sus fondos a la realización de obra a través de la Secretaría del Bienestar, y hasta la fecha se sigue señalando que no se manejan las reglas claras sobre la asignación de las obras y el recurso con las comunidades. Lo cierto es que es un programa que se ha ido puliendo sobre la marcha, a prueba y error, aunque finalmente las obras han ido ejecutándose y hoy se puede ya observar en las comunidades calles pavimentadas, galeras, obras de abastecimiento de agua, entre otras.</t>
+  </si>
+  <si>
+    <t>Ejecución de obras</t>
+  </si>
+  <si>
+    <t>Columna que evalúa el esquema de redirección presupuestal de los ayuntamientos hacia obras federales a través de la Secretaría del Bienestar.</t>
+  </si>
+  <si>
+    <t>Perseo</t>
+  </si>
+  <si>
+    <t>Secretaría de Bienestar Federal, Gobiernos Municipales</t>
+  </si>
+  <si>
+    <t>Reconoce Menchaca liderazgo de Claudia Sheinbaum Pardo en transformación de Hidalgo</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar respaldó a la presidenta Claudia Sheinbaum Pardo en la transformación que lleva a cabo en el país a través de proyectos de gran impacto, la entrega de programas sociales y diversas acciones para garantizar el bienestar de las familias mexicanas. Durante la presentación de su Segundo Informe de Gobierno, Sheinbaum Pardo aseguró que el Estado mexicano es rector en la planeación del desarrollo del país, convirtiendo las políticas públicas en derechos que le pertenecen al pueblo; como ejemplo, más de 42.8 millones de personas serán beneficiadas con los programas sociales para el cierre del 2026. Menchaca Salazar enlistó las acciones emprendidas por el Gobierno de México en coordinación con la administración estatal, entre las que destacan el Tren México-Pachuca, la estación en Tula del Tren México-Querétaro y el Polo de Desarrollo Económico para el Bienestar de Zapotlán. Asimismo, la tecnificación de distritos de riego, la construcción de Viviendas para el Bienestar, la carretera Huejutla-Tamazunchale y el saneamiento de Tula. Además, el titular del gobierno de Hidalgo agradeció a la mandataria nacional el apoyo brindado tras la vaguada monzónica registrada en octubre del 2025, para atender los daños en 28 municipios hidalguenses.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca Salazar reconoció y respaldó la gestión y el impacto de los proyectos federales de la presidenta Claudia Sheinbaum en Hidalgo.</t>
+  </si>
+  <si>
+    <t>Caasim fortalece la infraestructura de tipo sanitaria en San Antonio</t>
+  </si>
+  <si>
+    <t>Con el objetivo de mejorar la operación del sistema de alcantarillado sanitario, la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales (Caasim), llevó a cabo trabajos de modernización en la calle 2, del fraccionamiento Rinconadas de San Francisco, en San Antonio el Desmonte. Personal especializado realizó la sustitución de más de 200 metros de tubería de 12 pulgadas de diámetro, de la línea de alcantarillado sanitario, así como la construcción de siete pozos de visita y el reemplazo de 26 descargas domiciliarias. Estas acciones permitieron atender la presencia de obstrucciones recurrentes en la línea existente, asociada a las características del material con el que fue fabricada en su momento, y contribuirán a mejorar su funcionamiento y eficiencia, en beneficio de más de mil habitantes del sector.</t>
+  </si>
+  <si>
+    <t>Alcantarillado</t>
+  </si>
+  <si>
+    <t>Caasim ejecutó obras de modernización y sustitución de más de 200 metros de tubería de drenaje en el fraccionamiento Rinconadas de San Francisco, San Antonio el Desmonte.</t>
+  </si>
+  <si>
+    <t>Casi 2 mil hidalguenses recuperan posibilidad de escuchar y comunicarse mejor con la sociedad</t>
+  </si>
+  <si>
+    <t>Con una inversión superior a 18 mdp, concluyó la estrategia estatal que acercó 3 mil 564 auxiliares auditivos a personas de 57 municipios. El esfuerzo conjunto entre la Administración del Patrimonio de la Beneficencia Pública Nacional, los Servicios de Salud de Hidalgo, la Administración del Patrimonio Social y los Sistemas DIF municipales permitió actuar para acercar este beneficio a habitantes de 57 municipios, mediante la entrega de 3 mil 564 auxiliares auditivos, mediante una inversión de 18 millones 422 mil 494 pesos. Durante la ceremonia de clausura de la Primera Jornada de Entrega de Auxiliares Auditivos 2026, realizada en el auditorio del Hospital del Niño DIF Hidalgo, autoridades destacaron la importancia de fortalecer acciones que promuevan la inclusión y la de oportunidades para las personas con discapacidad auditiva.</t>
+  </si>
+  <si>
+    <t>Concluyó la Primera Jornada de Auxiliares Auditivos con la entrega de 3,564 aparatos en beneficio de 1,782 hidalguenses en 57 municipios y una inversión de 18.4 mdp.</t>
+  </si>
+  <si>
+    <t>Sistema DIF Hidalgo, Servicios de Salud de Hidalgo, Hospital del Niño DIF Hidalgo, Beneficencia Pública Nacional</t>
+  </si>
+  <si>
+    <t>Vanesa Escalante Arroyo, Ricardo Alvizo Contreras, Leivy Lizeth López Calderón, José Alfredo Cordero Esquivel</t>
+  </si>
+  <si>
+    <t>CEDSPI fortalece jornada de capacitación sobre derechos de los pueblos indígenas</t>
+  </si>
+  <si>
+    <t>Con el objetivo de fortalecer la atención institucional con enfoque intercultural, personal de la Comisión Estatal para el Desarrollo Sostenible de los Pueblos Indígenas (CEDSPI), encabezada por Prisco Manuel Gutiérrez, impartió una jornada de capacitación a 150 personas servidoras públicas de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (SIPDUS). La actividad se llevó a cabo de manera presencial en el Auditorio del Ex Centro Minero “Andrés Manuel del Río” y estuvo dirigida a personal directivo, administrativo, de vinculación y supervisión de obra que mantiene contacto con las comunidades durante los procesos de planeación, ejecución y seguimiento de proyectos de infraestructura. Durante la jornada se brindaron conocimientos y herramientas para fortalecer la actuación institucional desde una perspectiva de derechos.</t>
+  </si>
+  <si>
+    <t>Derechos humanos</t>
+  </si>
+  <si>
+    <t>La CEDSPI impartió una jornada de capacitación sobre enfoque intercultural y derechos de pueblos indígenas a 150 servidores públicos de la SIPDUS.</t>
+  </si>
+  <si>
+    <t>Comisión Estatal para el Desarrollo Sostenible de los Pueblos Indígenas (CEDSPI), Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (SIPDUS)</t>
+  </si>
+  <si>
+    <t>Prisco Manuel Gutiérrez, Miguel Ángel Tello Vargas, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Productores de Chapantongo y de Progreso de Obregón recibieron insumos por 9.7 mdp</t>
+  </si>
+  <si>
+    <t>En un esfuerzo coordinado por fortalecer la soberanía alimentaria y reactivar la economía rural, los municipios de Chapantongo y Progreso de Obregón se convirtieron en las sedes principales para la entrega regional de apoyos al agro hidalguense. La jornada benefició de manera directa a 984 productoras y productores de la región, sumando una inversión que supera los 9.7 mdp. La entrega de apoyos estuvo encabezada por el titular de la Secretaría de Agricultura y Desarrollo Rural, Napoleón González Pérez. Las familias beneficiadas recibieron un paquete de insumos estratégicos diseñados para impulsar las diversas vocaciones productivas de la zona: semilla para avena, cebada y maguey, vientres ovinos y porcinos, aves de doble propósito y maquinaria ligera.</t>
+  </si>
+  <si>
+    <t>Progreso</t>
+  </si>
+  <si>
+    <t>Apoyo Al Agro</t>
+  </si>
+  <si>
+    <t>Saderh entregó semillas, aves, ovinos, porcinos y herramientas por 9.7 mdp a 984 productores rurales de Chapantongo y Progreso de Obregón.</t>
+  </si>
+  <si>
+    <t>Secretaría de Agricultura y Desarrollo Rural</t>
+  </si>
+  <si>
+    <t>Napoleón González Pérez, Julio Menchaca Salazar, Eligio Figueroa Chávez, Lorena Estrada Flores, Julio Agustín Cruz Tovar, Miguel Ángel Peña Flores, Diana Rangel Zúñiga</t>
+  </si>
+  <si>
+    <t>Brinda Procuraduría Estatal de la Defensa del Trabajo mil 800 asesorías gratuitas</t>
+  </si>
+  <si>
+    <t>La Procuraduría Estatal de la Defensa del Trabajo, adscrita a la Secretaría del Trabajo y Previsión Social de Hidalgo (STPSH), mantiene como prioridad brindar orientación y acompañamiento a las personas trabajadoras que enfrentan alguna situación que pueda vulnerar sus derechos laborales. Como parte de esta labor, al mes de julio, la Procuraduría registra un acumulado en 2026, de mil 832 asesorías laborales gratuitas, mediante las cuales, se proporcionó información y orientación jurídica a las y los trabajadores sobre sus derechos y alternativas legales. Entre los principales motivos de atención destacan los casos relacionados con despidos injustificados, prestaciones, declaración de beneficiarios, renuncia y accidentes de trabajo. Las autoridades revelaron que se han alcanzado 296 convenios fuera de juicio.</t>
+  </si>
+  <si>
+    <t>Mineral de la Reforma</t>
+  </si>
+  <si>
+    <t>Defensa del trabajador</t>
+  </si>
+  <si>
+    <t>La Procuraduría de la Defensa del Trabajo del estado de Hidalgo brindó 1,832 asesorías gratuitas y logró 296 convenios de conciliación en el primer semestre.</t>
+  </si>
+  <si>
+    <t>STPSH</t>
+  </si>
+  <si>
+    <t>Procuraduría Estatal de la Defensa del Trabajo, Secretaría del Trabajo y Previsión Social de Hidalgo</t>
+  </si>
+  <si>
+    <t>Oscar Javier González Hernández</t>
+  </si>
+  <si>
+    <t>SEPH convoca a inscribirse al Bachillerato Nacional “Margarita Maza”</t>
+  </si>
+  <si>
+    <t>La Secretaría de Educación Pública de Hidalgo (SEPH), que encabeza Natividad Castrejón Valdez, convoca a las y los jóvenes de entre 15 y 19 años cumplidos que deseen continuar sus estudios de Educación Media Superior a inscribirse al Bachillerato Nacional Margarita Maza, nueva opción educativa que iniciará actividades el 28 de septiembre. El secretario destacó que el nuevo esquema, impulsado por el Gobierno de México, está diseñado para ampliar las oportunidades educativas y favorecer la reincorporación al Sistema Educativo Nacional de jóvenes que actualmente se encuentran fuera de la escuela, mediante un modelo que combina formación académica con actividades de cultura, deporte, integración social y acompañamiento tutorial. Operarán en municipios como Tula de Allende, Mineral de la Reforma, Pachuca de Soto, Atotonilco de Tula, Apan y Tezontepec de Aldama.</t>
+  </si>
+  <si>
+    <t>Bachillerato Nacional</t>
+  </si>
+  <si>
+    <t>La SEPH convocó a jóvenes de 15 a 19 años a inscribirse en el Bachillerato Nacional 'Margarita Maza', que arrancará en septiembre en seis municipios de la entidad.</t>
+  </si>
+  <si>
+    <t>Secretaría de Educación Pública de Hidalgo, Gobierno de México</t>
+  </si>
+  <si>
+    <t>Inhjuve ofrece gratis atención psicológica y de tipo nutricional, presencial y a distancia</t>
+  </si>
+  <si>
+    <t>Las y los jóvenes de Hidalgo pueden solicitar atención y acompañamiento psicológico y de nutrición de manera gratuita a través del Instituto Hidalguense de la Juventud (Inhjuve), en sesiones presenciales o a distancia para personas de municipios apartados. Así lo dio a conocer su titular, Ricardo Olvera Molina, quien señaló, que el objetivo es contribuir al bienestar general de las juventudes del estado, ofreciendo servicios de atención profesional, accesible y confidencial que les permitan desarrollar un estilo de vida saludable. Se invita a personas jóvenes de entre 12 y 29 años a aprovechar estas herramientas de manera presencial en la planta baja del Centro Administrativo del Bienestar y Desarrollo Rural en Pachuca o en modalidad virtual.</t>
+  </si>
+  <si>
+    <t>Salud Mental</t>
+  </si>
+  <si>
+    <t>El Inhjuve ofrece servicios profesionales y gratuitos de terapia psicológica y asesoría nutricional para jóvenes de 12 a 29 años en Pachuca o vía virtual.</t>
+  </si>
+  <si>
+    <t>Instituto Hidalguense de la Juventud (Inhjuve), Centro Administrativo del Bienestar y Desarrollo Rural</t>
+  </si>
+  <si>
+    <t>Ricardo Olvera Molina</t>
+  </si>
+  <si>
+    <t>SSPH mantiene recorridos de apoyo ante lluvias registradas en Pachuca</t>
+  </si>
+  <si>
+    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH), a través de la Policía Estatal y el H. Cuerpo de Bomberos, mantiene recorridos de prevención, vigilancia y apoyo a la ciudadanía ante las precipitaciones pluviales registradas esta tarde en Pachuca de Soto, Mineral de la Reforma y Zempoala. Derivado de las lluvias, se han recibido reportes de inundaciones en diferentes colonias de Pachuca, por lo que personal operativo mantiene presencia en zonas susceptibles y brinda apoyo a la población ante posibles afectaciones. En coordinación con instancias de los gobiernos estatal y municipal, la SSPH mantiene monitoreo permanente y atiende los reportes recibidos a través del C5i Hidalgo y el 911 de Emergencias.</t>
+  </si>
+  <si>
+    <t>Policía Estatal y Cuerpo de Bomberos de la SSPH desplegaron patrullajes preventivos y de auxilio vial ante las inundaciones pluviales en Pachuca.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Policía Estatal, Cuerpo de Bomberos de Hidalgo, C5i</t>
+  </si>
+  <si>
+    <t>Por delito de narcomenudeo, PGJEH detiene 2 personas, en Mineral de la Reforma</t>
+  </si>
+  <si>
+    <t>Elementos de la Agencia de Investigación Criminal de la Procuraduría General de Justicia del Estado de Hidalgo detuvieron a dos personas por encontrarse en posesión de diversas dosis de estupefacientes y dos armas de fuego. Las acciones ministeriales se llevaron a cabo en la colonia Parque de los Encinos, en Mineral de la Reforma, donde las personas fueron intervenidas cuando presuntamente realizaban actividades relacionadas con la comercialización de narcóticos. A una de las personas detenidas, de iniciales R. G. T., le fueron asegurados casi un centenar de envoltorios de cristal y mariguana, un arma y una báscula. A quien se le identificó como A. A. C. O., se le localizaron diversos envoltorios de cristal, metanfetaminas y otra arma de fuego.</t>
+  </si>
+  <si>
+    <t>Combate Al Narcomenudeo</t>
+  </si>
+  <si>
+    <t>La Agencia de Investigación Criminal de la PGJEH detuvo a dos personas con dosis de cristal, metanfetamina, mariguana y armas de fuego en Mineral de la Reforma.</t>
+  </si>
+  <si>
+    <t>Procuraduría General de Justicia del Estado de Hidalgo, Agencia de Investigación Criminal</t>
+  </si>
+  <si>
+    <t>En operativo coordinado, SSPH aseguró 7 vehículos Y 6 mil lts de hidrocarburo en municipio del Tlaxcoapan</t>
+  </si>
+  <si>
+    <t>Como resultado de los recorridos permanentes de seguridad, vigilancia y presencia que se mantienen en el estado, elementos de la Secretaría de Seguridad Pública de Hidalgo (SSPH), en coordinación con la Guardia Nacional (GN) y el Mando Coordinado de Tlaxcoapan, realizaron un importante aseguramiento en la localidad de La Vega. Durante el despliegue operativo sobre un camino de terracería, los efectivos detectaron un conjunto de unidades presuntamente vinculadas con actividades de extracción y traslado ilegal de hidrocarburo. Se aseguraron siete vehículos en total: cinco camionetas y dos tipo sedán (tres con reporte de robo vigente), así como 6 mil 331 litros de hidrocarburo de procedencia ilegal almacenados en 77 contenedores de distintas capacidades.</t>
+  </si>
+  <si>
+    <t>Tlaxcoapan</t>
+  </si>
+  <si>
+    <t>En operativo conjunto de la SSPH, Guardia Nacional y policía local, se incautaron siete vehículos y más de 6,300 litros de huachicol en Tlaxcoapan.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Guardia Nacional, Mando Coordinado de Tlaxcoapan</t>
+  </si>
+  <si>
+    <t>Bajo Reserva: Destaca Hidalgo en informe de Sheinbaum</t>
+  </si>
+  <si>
+    <t>Buen sabor de boca dejó el discurso de la presidenta Claudia Sheinbaum a los hidalguenses, al tener en cuenta a la entidad en varios proyectos federales, como la planta coquizadora de Tula, de la cual adelantó que estará funcionando este mismo año, así como el tren AIFA-Pachuca que conectará con la Ciudad de México, además del saneamiento y rehabilitación del río Tula, infraestructura hidroagrícola y la reconstrucción tras la vaguada de octubre de 2025. Nos dicen que estos proyectos se suman a los que, además, están en marcha por parte del gobierno del estado, que encabeza el mandatario Julio Menchaca.</t>
+  </si>
+  <si>
+    <t>Columna Bajo Reserva que destaca el impacto positivo de las obras federales en Hidalgo, como la coquizadora de Tula y el tren AIFA-Pachuca, mencionadas por Claudia Sheinbaum.</t>
+  </si>
+  <si>
+    <t>Bajo Reserva</t>
+  </si>
+  <si>
+    <t>Gobernador, Presidencia, Sipdus</t>
+  </si>
+  <si>
+    <t>Claudia Sheinbaum Pardo, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares entregará informe del gobernador al Congreso</t>
+  </si>
+  <si>
+    <t>La sesión solemne de entrega del cuarto informe del gobernador Julio Menchaca Salazar será el próximo sábado 5 de septiembre, en el Congreso de Hidalgo, y sólo acudirá el secretario de Gobierno, adelantó el diputado local Andrés Velázquez Vázquez. Esto, porque un día antes el titular del Ejecutivo hará el acto político en las instalaciones de la feria de Pachuca. Olivares Reyna acudirá en representación del gobernador a entregar la glosa de cuatro años ante la LXVI Legislatura.</t>
+  </si>
+  <si>
+    <t>El secretario de Gobierno, Guillermo Olivares Reyna, entregará formalmente el cuarto informe de Julio Menchaca ante el Congreso del Estado el próximo 5 de septiembre.</t>
+  </si>
+  <si>
+    <t>Gobernador, Congreso, Secretaría de Gobierno</t>
+  </si>
+  <si>
+    <t>El secretario estatal de Agricultura rechaza bloqueo a obras de CFE</t>
+  </si>
+  <si>
+    <t>Tras los señalamientos en su contra por habitantes de comunidades de Tlanchinol, Napoleón González Pérez, titular de la Saderh, negó oponerse a la instalación de líneas de la CFE que pasan por terrenos propiedad de su familia; por el contrario, dijo, brinda las facilidades para el desarrollo de la región. Comentó que mantiene diálogo y apoya también con la edificación de un camino artesanal en el rancho de su padre.</t>
+  </si>
+  <si>
+    <t>Tlanchinol</t>
+  </si>
+  <si>
+    <t>Suministro eléctrico</t>
+  </si>
+  <si>
+    <t>El titular de Saderh, Napoleón González Pérez, rechazó oponerse a la instalación de líneas eléctricas de la CFE que atraviesan predios familiares en Tlanchinol, avalando las obras.</t>
+  </si>
+  <si>
+    <t>Saderh, Presidencia</t>
+  </si>
+  <si>
+    <t>Napoleón González Pérez</t>
+  </si>
+  <si>
+    <t>Menores, las principales víctimas de quemaduras</t>
+  </si>
+  <si>
+    <t>La población que sufre más quemaduras son los menores de edad, informó Lidia Monroy Pérez, presidenta de la Asociación Mexicana para la Prevención y Tratamiento de Quemaduras, San Martín de Porres. Las principales causas son líquidos calientes, electricidad o químicos. Tenango de Doria, San Bartolo Tutotepec, Santiago de Anaya, Pachuca y Mineral de la Reforma son los municipios de Hidalgo con más incidencia. Se invitó a participar en el primer Congreso Nacional de Atención Integral de Quemaduras en La Maestranza, Pachuca.</t>
+  </si>
+  <si>
+    <t>Prevención de accidentes</t>
+  </si>
+  <si>
+    <t>La Asociación Mexicana para la Prevención de Quemaduras alertó que menores son los más vulnerables a quemaduras en el hogar, siendo Pachuca y el Mezquital zonas de alta incidencia.</t>
+  </si>
+  <si>
+    <t>Lidia Monroy Pérez</t>
+  </si>
+  <si>
+    <t>Entregaron auxiliares auditivos a mil 782 pacientes hidalguenses</t>
+  </si>
+  <si>
+    <t>Mil 782 hidalguenses recibieron auxiliares auditivos como parte de una estrategia impulsada en todo el estado, informó la Secretaría de Salud de Hidalgo (SSH). Se beneficiaron habitantes de 57 municipios mediante la entrega de 3 mil 564 auxiliares auditivos, mediante una inversión de 18 millones 422 mil 494 pesos. Los dispositivos fueron entregados en el Hospital del Niño DIF Hidalgo. La secretaria de Salud estatal, Vanesa Escalante Arroyo, señaló que el trabajo coordinado acerca soluciones positivas y duraderas.</t>
+  </si>
+  <si>
+    <t>La SSH entregó 3 mil 564 auxiliares auditivos en beneficio de 1,782 pacientes en 57 municipios, lograda con un presupuesto de 18.4 mdp en colaboración con el DIF Hidalgo.</t>
+  </si>
+  <si>
+    <t>DIFH, SSH</t>
+  </si>
+  <si>
+    <t>Aseguran 7 vehículos y 6 mil litros de combustible</t>
+  </si>
+  <si>
+    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH) informó que siete vehículos y 6 mil 331 litros de combustible fueron decomisados en un operativo realizado en Tlaxcoapan. El aseguramiento ocurrió en la comunidad La Vega, en Tlaxcoapan, como resultado de los recorridos permanentes de seguridad, vigilancia y presencia que se mantienen en el estado por elementos de la SSPH, en coordinación con la Guardia Nacional (GN) y el Mando Coordinado de Tlaxcoapan. Cinco camionetas y dos tipo sedán fueron asegurados; tres contaban con reporte de robo.</t>
+  </si>
+  <si>
+    <t>La SSPH incautó siete unidades y más de 6,300 litros de huachicol almacenados en contenedores en terracerías de la comunidad de La Vega en Tlaxcoapan.</t>
+  </si>
+  <si>
+    <t>SSPH, Presidencia</t>
+  </si>
+  <si>
+    <t>Detienen a dos individuos por narcomenudeo en La Reforma</t>
+  </si>
+  <si>
+    <t>Elementos de la Agencia de Investigación Criminal de la Procuraduría General de Justicia del Estado de Hidalgo detuvieron a dos personas en posesión de diversas dosis de estupefacientes y dos armas de fuego. Las acciones ministeriales se llevaron a cabo en la colonia Parque de los Encinos, en Mineral de la Reforma, donde las personas fueron intervenidas cuando presuntamente realizaban actividades relacionadas con la comercialización de narcóticos, informó la Procuraduría General de Justicia del Estado de Hidalgo (PGJEH). R. G. T. portaba un centenar de dosis de cristal, mientras que A. A. C. O. portaba cristal y aparente metanfetamina.</t>
+  </si>
+  <si>
+    <t>La AIC de la PGJEH arrestó a dos presuntos narcomenudistas en la colonia Parque de los Encinos de Mineral de la Reforma, asegurando cristal, marihuana y dos armas.</t>
+  </si>
+  <si>
+    <t>Procuraduría ha dado asesoría a más de mil 800 trabajadores en el actual año</t>
+  </si>
+  <si>
+    <t>La Procuraduría Estatal de la Defensa del Trabajo acumula mil 832 asesorías laborales gratuitas en 2026, mediante las cuales proporcionó información y orientación jurídica a trabajadores sobre sus derechos y alternativas legales. Entre los principales motivos de atención destacan los casos relacionados con despidos injustificados, prestaciones, renuncia y accidentes de trabajo. Las autoridades revelaron que han alcanzado 296 convenios fuera de juicio. El titular de la STPSH, Oscar Javier González Hernández, destacó el acompañamiento gratuito.</t>
+  </si>
+  <si>
+    <t>La Procuraduría de la Defensa del Trabajo de Hidalgo ha brindado mil 832 asesorías legales en 2026 y concretado 296 convenios de conciliación en favor de los empleados.</t>
+  </si>
+  <si>
+    <t>PERSONAL UNIVERSITARIO PIDE MEJORAS LABORALES</t>
+  </si>
+  <si>
+    <t>La comunidad académica y administrativa de la Universidad Tecnológica de la Huasteca Hidalguense (UTHH) inició una serie de movilizaciones para exigir la firma de las condiciones generales de trabajo, a fin de dar sustento jurídico a las prestaciones e ingresos del personal, certeza en los nombramientos docentes y transparencia en escalafones. El líder del Sututeh, Efrén Juárez Castillo, aseveró que las demandas acumulan más de tres años de gestiones sin respuesta ante la rectoría de la universidad y las autoridades de la SEPH.</t>
+  </si>
+  <si>
+    <t>Protesta sindical</t>
+  </si>
+  <si>
+    <t>Personal académico y administrativo de la UTHH se manifestó en Huejutla exigiendo su contrato colectivo de trabajo y certeza en nombramientos docentes tras tres años de parálisis.</t>
+  </si>
+  <si>
+    <t>Francisco Bautista</t>
+  </si>
+  <si>
+    <t>Efrén Juárez Castillo</t>
+  </si>
+  <si>
+    <t>Padres de familia toman por segundo día primaria en La Lagunilla</t>
+  </si>
+  <si>
+    <t>Padres de familia de la primaria Gregorio Torres Quintero, ubicada en la comunidad La Lagunilla, mantienen tomada la institución por segundo día consecutivo exigiendo que la SEPH asigne un intendente (vacante desde mayo) y dos maestros para el plantel. Ana Karen Vargas Alvarado, tesorera del plantel, explicó que recibieron promesas incumplidas en mayo pasado. Este martes los padres de familia fueron atendidos por René Reyes, quien les informó que a partir del jueves recibirán el recurso para cubrir la plaza de intendente.</t>
+  </si>
+  <si>
+    <t>Tutores mantuvieron cerrada la primaria Gregorio Torres Quintero en Tulancingo exigiendo que la SEPH autorice un conserje y dos profesores vacantes, con el compromiso estatal de solución para el jueves.</t>
+  </si>
+  <si>
+    <t>Ana Karen Vargas Alvarado, René Reyes</t>
+  </si>
+  <si>
+    <t>Hidalgo descarta plagio y lucro en bordados de Jaltocán</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura de Hidalgo descartó, hasta el momento, que exista lucro o plagio relacionado con los bordados tradicionales de Jaltocán, luego de una denuncia difundida por creadores de contenido en redes sociales. Neyda Naranjo, titular de la dependencia, explicó que el caso llegó al Consejo Técnico Artesanal, donde se revisó la situación y se conoció la versión de la persona señalada, quien aparentemente es un maestro de baile. El docente buscó una alternativa para que sus alumnas pudieran ensayar con faldas similares a las tradicionales, debido a que algunas familias no cuentan con los recursos económicos para adquirir un vestido bordado. Por ello, realizó una sublimación del diseño para utilizarla durante los ensayos. 'No hubo hasta donde sabemos un lucro para eso. No fue con el tema de un plagio, sino de darles la oportunidad a sus alumnos', señaló la funcionaria. Asimismo, explicó que aparentemente al maestro le sobró un pedazo de tela y, con la intención de recuperar parte de lo que había gastado, publicó el material en redes sociales para venderlo. Naranjo precisó que la Secretaría de Cultura recibió un documento de un particular en el que se hizo de conocimiento la situación, por lo que el tema llegó a una sesión del Consejo Técnico Artesanal.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura, Neyda Naranjo, aclaró que la impresión de faldas con bordados sublimados de Jaltocán fue para un ensayo escolar sin fines de lucro, descartando plagio.</t>
+  </si>
+  <si>
+    <t>Secretaría de Cultura de Hidalgo, Consejo Técnico Artesanal</t>
+  </si>
+  <si>
+    <t>Provocan lluvias anegamientos en Zona Metropolitana de Pachuca</t>
+  </si>
+  <si>
+    <t>Derivado de las lluvias que se registraron la tarde de este martes en Pachuca, la Secretaría de Seguridad Pública del Estado (SSPH), en coordinación con personal del Cuerpo de Bomberos de Hidalgo, realizó recorridos preventivos en la Zona Metropolitana de Pachuca para apoyar a la ciudadanía tras los encharcamientos registrados. En coordinación con los gobiernos estatal y municipales de Pachuca, Mineral de la Reforma y Zempoala, se atendieron diferentes reportes de anegamientos y se brindó apoyo a la población afectada. Mediante redes sociales se publicaron videos en los que se pudo observar que varios automóviles quedaron inundados sobre el bulevar Colosio, a la altura de la deportiva Piracantos, debido a la acumulación de agua de lluvia. Asimismo, algunos transeúntes fueron auxiliados por elementos de Bomberos para atravesar las zonas con encharcamientos. Algunos estudiantes de escuelas cercanas al cruce de los bulevares Ramón G. Bonfil y Colosio, frente a la colonia El Palmar, fueron auxiliados por policías municipales para evitar algún accidente debido a la acumulación de agua. Cerca de esa zona, en la colonia San Cayetano, un automóvil quedó atrapado cerca de un canal, por lo que fue necesaria la intervención de elementos de Bomberos. Asimismo, se identifican escurrimientos provenientes del bulevar del Minero hacia las zonas de Punta Azul, Piracantos, Parque de Poblamiento, Plutarco Elías Calles y Rojo Gómez. Las y los automovilistas que transitaban por el bulevar Minero también se vieron afectados por las fuertes lluvias, al igual que quienes circulaban por el bulevar Felipe Ángeles, al sur de la ciudad.</t>
+  </si>
+  <si>
+    <t>Fuertes lluvias causaron inundaciones y encharcamientos severos en los bulevares Colosio, Bonfil, Minero y Felipe Ángeles en Pachuca, por lo que elementos de la SSPH y Bomberos realizaron labores de auxilio vial.</t>
+  </si>
+  <si>
+    <t>Secretaría de Seguridad Pública de Hidalgo, Cuerpo de Bomberos de Hidalgo, C5i</t>
+  </si>
+  <si>
+    <t>Regular, no prohibir: Castrejón sobre uso de celulares en escuelas</t>
+  </si>
+  <si>
+    <t>El secretario de Educación Pública del Estado de Hidalgo (SEPH), Natividad Castrejón Valdez, informó que en Hidalgo se avanza en la regulación sobre el uso de teléfonos celulares en las escuelas y señaló que incluso “ya está en un planteamiento de ley”, no obstante, negó que se planteara prohibirlos y aclaró que solamente se busca regular su uso para fines pedagógicos. Esto en alusión a la declaración de la presidenta de México, Claudia Sheinbaum Pardo, quien señaló que se trabaja en una regulación para el uso de teléfonos móviles en las aulas. “No se trata de prohibir por prohibir, se trata de buscar los momentos, las edades adecuadas para el uso ya autónomo de los medios digitales”, declaró el funcionario. Indicó que lo que se busca con la regulación planteada es que, en el caso del nivel primaria, si las y los alumnos llevan celulares a las escuelas, sean utilizados solamente en caso de emergencias para comunicarse con sus padres, o para realizar algún trabajo ocasional que se requiera con orden pedagógico del docente, incluyendo la regulación desde casa por parte de padres y madres de familia. A través del programa “Ver bien para aprender mejor”, se investiga la posible relación de los problemas de la vista con el uso de dispositivos móviles.</t>
+  </si>
+  <si>
+    <t>El titular de la SEPH, Natividad Castrejón Valdez, planteó normar el uso de celulares en las aulas para fines exclusivamente pedagógicos y de salud visual, descartando una prohibición total.</t>
+  </si>
+  <si>
+    <t>Divide gobernador informe en dos días</t>
+  </si>
+  <si>
+    <t>El Cuarto Informe de Gobierno del mandatario estatal, Julio Menchaca Salazar, tendrá actividades durante dos días. El viernes 4 de septiembre, el gobernador encabezará el acto público de rendición de cuentas en las instalaciones de la Feria de Pachuca, mientras que el sábado 5 el documento será entregado formalmente al Congreso de Hidalgo por parte de la Secretaría de Gobierno. Andrés Velázquez Vázquez, presidente de la Junta de Gobierno del Poder Legislativo, confirmó que para el segundo acto será el secretario de Gobierno, Guillermo Olivares Reyna, quien acuda en representation del gobernador a la sede del Legislativo hidalguense, por lo que Menchaca Salazar no será quien entregue el documento este año.</t>
+  </si>
+  <si>
+    <t>El cuarto informe de actividades del gobernador Julio Menchaca Salazar se dividirá en dos jornadas, realizándose un mensaje público el viernes 4 de septiembre en la Feria de Pachuca y la entrega formal ante el Congreso local por parte de la Secretaría de Gobierno el sábado 5 de septiembre.</t>
+  </si>
+  <si>
+    <t>Saúl Hernández</t>
+  </si>
+  <si>
+    <t>En siete meses, 28 denuncias por delitos electorales en Hidalgo</t>
+  </si>
+  <si>
+    <t>Previo al inicio formal del periodo electoral 2026-2027, durante los primeros siete meses del año, en Hidalgo se iniciaron 28 carpetas de investigación por presuntos delitos electorales, según datos de la incidencia delictiva municipal del Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública (SESNSP). El municipio que concentra el mayor número de denuncias es Pachuca, con 12; seguido de Ajacuba con tres denuncias, Tulancingo con dos y Tula con dos. El proceso para la renovación de los 84 ayuntamientos comenzará formalmente el 15 de septiembre.</t>
+  </si>
+  <si>
+    <t>Delitos Electorales</t>
+  </si>
+  <si>
+    <t>Durante los primeros siete meses de 2026, la incidencia delictiva del Secretariado Ejecutivo reportó la apertura de 28 carpetas de investigación por presuntos delitos electorales en Hidalgo, concentrando Pachuca el mayor número de querellas iniciadas con 12 de ellas.</t>
+  </si>
+  <si>
+    <t>Suma Hidalgo tres muertes por Covid al cierre de mes</t>
+  </si>
+  <si>
+    <t>Por más de tres meses consecutivos, Hidalgo se ha posicionado como la entidad con mayor número de defunciones por Covid-19 a nivel nacional, con un alza de tres muertes durante la semana del 17 al 24 de agosto, según información de la Secretaría de Salud federal (Ssa). Actualmente, el estado acumula un total de 12 defunciones y 162 casos positivos de Covid-19, lo que representa que el 7.5 por ciento de los contagios confirmados a la fecha han culminado con el deceso de los pacientes. Asimismo, se reporta que el estado no cuenta con dosis de vacunación contra Covid-19 y la reanudación del fármaco está destinada para octubre.</t>
+  </si>
+  <si>
+    <t>Covid 19</t>
+  </si>
+  <si>
+    <t>Hidalgo acumuló un total de 12 defunciones y 162 casos positivos de Covid-19 en el último reporte de la Secretaría de Salud federal, posicionándose como el estado líder en mortalidad por esta enfermedad a nivel nacional, en un escenario donde la entidad carece de vacunas disponibles hasta octubre.</t>
+  </si>
+  <si>
+    <t>SSH, Presidencia</t>
+  </si>
+  <si>
+    <t>Buscan reducir el congestionamiento en puente Colonias por tráfico vehicular</t>
+  </si>
+  <si>
+    <t>La Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (Sipdus) inició los trabajos de ampliación entre el bulevar Felipe Ángeles y el retorno del puente Colonias, a la altura de una gasera, en la capital hidalguense. Lo anterior tiene como objetivo disminuir el cuello de botella que se genera en esa zona y reducir el congestionamiento vial en el sur de la capital, en dirección hacia la salida a Tizayuca. Las labores se concentran de momento en la sustitución del acueducto, a cargo de la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales (Caasim). En junio pasado, el titular de la Sipdus, Alejandro Sánchez García, detalló la importancia de esta intervención acotada.</t>
+  </si>
+  <si>
+    <t>La Sipdus inició trabajos de ampliación y reubicación hidráulica a cargo de la Caasim debajo del puente Colonias en el bulevar Felipe Ángeles de Pachuca, con el propósito de resolver un histórico cuello de botella que afecta la movilidad y conexión con la carretera federal hacia la Ciudad de México.</t>
+  </si>
+  <si>
+    <t>Sipdus, Caasim</t>
+  </si>
+  <si>
+    <t>Alejandro Sánchez García</t>
+  </si>
+  <si>
+    <t>Artesanías no se venden en su valor real</t>
+  </si>
+  <si>
+    <t>Piezas textiles elaboradas por maestros artesanos de Jaltocán son adquiridas a precios por debajo de su valor real, detectó la Secretaría de Cultura de Hidalgo durante recorridos realizados en talleres de la región. La titular de la dependencia, Neyda Naranjo Baltazar, explicó que esta situación salió a la luz luego de que el Consejo Técnico Artesanal revisara un caso difundido en redes sociales como supuesto plagio de bordados huastecos. Sin embargo, descartó que exista dicha situación, pues explicó que, según la versión recabada, un maestro de baile mandó elaborar prendas sublimadas para que niños las utilizaran durante ensayos, debido a que algunas familias no contaban con recursos para adquirir vestimenta bordada. Las visitas permitieron detectar que varios creadores venden sus piezas a intermediarios por cantidades menores a su valor cultural real.</t>
+  </si>
+  <si>
+    <t>Apoyo a artesanos</t>
+  </si>
+  <si>
+    <t>La secretaria de Cultura, Neyda Naranjo, alertó sobre intermediarios que compran artesanías textiles de Jaltocán por debajo de su valor real, por lo que impulsará la estrategia 'Hidalgo No Regatea' para promover la comercialización directa y sin abusos comerciales.</t>
+  </si>
+  <si>
+    <t>Sipdus emite la licitación para obra de adecuación</t>
+  </si>
+  <si>
+    <t>A más de dos años de que se inició el proceso de transición de la Escuela de Música de la dependencia de Cultura a la de Educación Pública de Hidalgo (SEPH), la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (Sipdus) emitió una licitación para realizar adecuaciones en la sede de la institución educativa. De acuerdo con el procedimiento EO-SIP-DUS-N129-2026, se busca proveedor para realizar los trabajos en el inmueble, identificado como el antiguo Palacio de Gobierno, cerca de la calle Patoni, en Pachuca. En 2024, el titular de la SEPH, Natividad Castrejón Valdez, confirmó un presupuesto de 8 millones de pesos para equipamiento.</t>
+  </si>
+  <si>
+    <t>Licitaciones</t>
+  </si>
+  <si>
+    <t>La Sipdus emitió la convocatoria de licitación para la adecuación del antiguo Palacio de Gobierno de Pachuca, el cual albergará de manera definitiva las instalaciones de la Escuela de Música tras su transición administrativa a la SEPH.</t>
+  </si>
+  <si>
+    <t>Sipdus, SEPH, Cultura</t>
+  </si>
+  <si>
+    <t>Solución a movilidad: dos troncales más del Tuzobús</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Tello Vargas, titular de la Unidad de Planeación y Prospectiva Hidalgo, afirmó que el proyecto que permitirá mejorar la movilidad en la zona metropolitana de Pachuca es contar, al menos, con dos troncales más del Sistema de Transporte Metropolitano, antes Tuzobús, una en Mineral de la Reforma y otra transversal, de esta ciudad hacia San Agustín Tlaxiaca. El funcionario destacó que con lo anterior se tendría la posibilidad de brindar movilidad a las 200 mil o 300 mil personas que saturan el tráfico vial. El proyecto cuenta ya con solicitud ante Banobras para financiamiento.</t>
+  </si>
+  <si>
+    <t>Modernización Tuzobús</t>
+  </si>
+  <si>
+    <t>El titular de la Unidad de Planeación y Prospectiva, Miguel Ángel Tello, planteó que la solución de fondo al tráfico en la zona metropolitana de Pachuca consiste en construir dos nuevas troncales del Tuzobús (una en Mineral de la Reforma y otra hacia San Agustín Tlaxiaca) mediante financiamiento de Banobras.</t>
+  </si>
+  <si>
+    <t>Planeación, Semot</t>
+  </si>
+  <si>
+    <t>UTHH estalla en protesta; piden mejoras en su trabajo</t>
+  </si>
+  <si>
+    <t>Personal académico y administrativo de la Universidad Tecnológica de la Huasteca Hidalguense (UTHH) realizó un paro de labores y una manifestación al interior de la institución para exigir la firma de las Condiciones Generales de Trabajo, proceso que, de acuerdo con el sindicato, lleva más de tres años sin concretarse. Efrén Juárez Castillo, secretario general del Sindicato de Trabajadores de la UTHH, explicó que el documento contempla aspectos relacionados con contratación, ascensos, preparación de exámenes, asignación de horas y pago de prestaciones como aguinaldos.</t>
+  </si>
+  <si>
+    <t>Trabajadores académicos y administrativos de la Universidad Tecnológica de la Huasteca Hidalguense iniciaron un paro laboral exigiendo la firma de las Condiciones Generales de Trabajo que garantice sus prestaciones, escalafones, y horas docentes tras tres años de gestiones sin formalización.</t>
+  </si>
+  <si>
+    <t>Acusan presuntos abusos de agentes de investigación</t>
+  </si>
+  <si>
+    <t>El abogado postulante Joel Medina Hernández señaló que ha tenido conocimiento de presuntos actos de abuso de autoridad y cobros irregulares atribuidos a elementos de la Agencia de Investigación del grupo Huejutla, quienes, afirmó, han sido señalados por ciudadanos que prefieren no denunciar por temor a sufrir represalias. El litigante explicó que, en algunos casos, los elementos se limitarían a reproducir los hechos de la querella y posteriormente solicitarían dinero para gasolina u otros gastos.</t>
+  </si>
+  <si>
+    <t>Abuso De Autoridad</t>
+  </si>
+  <si>
+    <t>El abogado Joel Medina de Huejutla denunció abusos y cobros ilegales atribuidos a agentes ministeriales del grupo Huejutla, advirtiendo que la Procuraduría se limita a reubicar al personal denunciado.</t>
+  </si>
+  <si>
+    <t>Joel Medina Hernández</t>
+  </si>
+  <si>
+    <t>Destinarán 85 mdp para obras carreteras en la Tehuetlán-Huazalingo</t>
+  </si>
+  <si>
+    <t>Tras los reclamos de transportistas y usuarios por las malas condiciones de la carretera, iniciaron los trabajos de reconstrucción del tramo Tehuetlán-Huazalingo, vialidad que resultó con graves afectaciones por las lluvias asociadas a la vaguada monzónica. La intervención forma parte de las acciones de reconstrucción impulsadas por el Gobierno de Hidalgo para atender la infraestructura dañada por fenómenos meteorológicos, con una inversión de alrededor de 85 millones de pesos destinada a mejorar el tramo de 20 kilómetros.</t>
+  </si>
+  <si>
+    <t>Huazalingo</t>
+  </si>
+  <si>
+    <t>Rehabilitación carretera</t>
+  </si>
+  <si>
+    <t>El gobierno de Hidalgo inició los trabajos de reconstrucción carretera en el tramo Tehuetlán-Huazalingo, con una inversión estimada de 85 mdp para restaurar 20 kilómetros de carpeta asfáltica dañada por deslaves y baches tras el impacto de la vaguada monzónica.</t>
+  </si>
+  <si>
+    <t>Abren nuevo bachillerato para jóvenes que buscan concluir sus estudios</t>
+  </si>
+  <si>
+    <t>La Secretaría de Educación Pública de Hidalgo (SEPH) anunció la apertura del Bachillerato Nacional Margarita Maza, una nueva alternativa educativa dirigida a jóvenes de entre 15 y 19 años que desean iniciar, retomar o concluir sus estudios de nivel medio superior. El modelo comenzará actividades el próximo 28 de septiembre y permitirá que las y los estudiantes concluyan el bachillerato en un periodo de dos años, además de acceder a la Beca Benito Juárez. El secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, destacó que esta opción busca ampliar las oportunidades educativas y facilitar la reincorporación de los jóvenes.</t>
+  </si>
+  <si>
+    <t>La SEPH anunció la apertura del nuevo Bachillerato Nacional Margarita Maza, una modalidad modular de dos años de duración orientada a jóvenes de 15 a 19 años fuera del sistema educativo, con sede en seis municipios del estado y vinculada a las Becas Benito Juárez.</t>
+  </si>
+  <si>
+    <t>Productores son beneficiados con 9.7 mdp en insumos en Chapantongo y Progreso</t>
+  </si>
+  <si>
+    <t>Los municipios de Chapantongo y Progreso de Obregón se convirtieron en las sedes principales para la entrega regional de apoyos al agro hidalguense. La jornada benefició de manera directa a 984 productoras y productores de la región, sumando una inversión que supera los 9.7 millones de pesos. La entrega de apoyos estuvo encabezada por el titular de la Secretaría de Agricultura y Desarrollo Rural, Napoleón González Pérez, otorgando semilla para siembra de avena, cebada, maíz y maguey, así como vientres ovinos, porcinos y herramientas de trabajo.</t>
+  </si>
+  <si>
+    <t>La Saderh, que encabeza Napoleón González Pérez, dispersó insumos, semillas de avena y cebada, maquinaria ligera, vientres de ovinos y porcinos con valor de 9.7 millones de pesos en beneficio de 984 productores rurales de Progreso de Obregón y Chapantongo.</t>
+  </si>
+  <si>
+    <t>Dese por enterado: DOS AÑOS DE LA PRESIDENTA SHEINBAUM. A HIDALGO LE HA IDO BIEN</t>
+  </si>
+  <si>
+    <t>Siempre debe mirarse el asunto político desde la óptica más cercana, y la pregunta evidente es, ¿le ha ido bien al estado de Hidalgo? La respuesta es que sí, por el número de obras que ya están en marcha, por las acciones reales para terminar, de una vez por todas, con una injusticia de tipo histórico cometida en contra del Estado hidalguense, directamente desde la Federación. Con lo anterior, la terminación de ese trato de patio trasero, a una entidad que siempre dio mucho a cambio de nada, o peor, a cambio de enfermos, inundaciones y saqueo. Le ha ido bien a Hidalgo, porque hay futuro por vez primera y en términos reales.</t>
+  </si>
+  <si>
+    <t>Columna Dese por enterado que resalta los beneficios y proyectos federales que están llegando a Hidalgo en la administración de Claudia Sheinbaum.</t>
+  </si>
+  <si>
+    <t>Gobernador, Presidencia</t>
+  </si>
+  <si>
+    <t>Mil 700 hidalguenses recuperan la posibilidad de escuchar</t>
+  </si>
+  <si>
+    <t>Volver a escuchar una conversación familiar, participar activamente en la comunidad y desarrollar las actividades cotidianas con mayor independencia es hoy una realidad para mil 782 personas hidalguenses que recibieron auxiliares auditivos. El esfuerzo conjunto entre la Administración del Patrimonio de la Beneficencia Pública Nacional, los Servicios de Salud de Hidalgo, la Administración del Patrimonio Social y los Sistemas DIF municipales permitió acercar este beneficio a 57 municipios, mediante la entrega de 3 mil 564 auxiliares auditivos, mediante una inversión de 18 millones 422 mil 494 pesos.</t>
+  </si>
+  <si>
+    <t>Se clausuró la entrega de 3,564 auxiliares auditivos en beneficio de 1,782 personas de 57 municipios con una inversión coordinada de 18.4 mdp.</t>
+  </si>
+  <si>
+    <t>Más de mil casos de infecciones intestinales</t>
+  </si>
+  <si>
+    <t>De acuerdo con el Boletín Epidemiológico que emite la Secretaría de Salud Federal, en lo que va del 2026 se han registrado un total de 47 mil 175 casos de enfermedades infecciosas intestinales. Con base en el reporte que registra la semana epidemiológica número 33, que comprende del 16 al 22 de agosto, en el apartado de enfermedades infecciosas y parasitarias del aparato digestivo, la entidad reportó mil 14 atenciones de enfermedades infecciosas intestinales. Cabe destacar que el sector femenino es el que más atenciones recibe, y en ocho meses se han acumulado 47 mil 175, de los cuales 26 mil 260 corresponden a mujeres y 20 mil 915 a hombres. En tanto, el segundo padecimiento con más reportes en una semana son las infecciones intestinales por otros organismos y las mal definidas, con 968 atenciones, lo que arroja un total de 45 mil 478 en lo que va del año. La tercera enfermedad del aparato digestivo que más fue atendida es la amebiasis, con 37 casos, le sigue la intoxicación alimentaria por bacterias con tres y la salmonelosis con dos.</t>
+  </si>
+  <si>
+    <t>Prevención De Enfermedades</t>
+  </si>
+  <si>
+    <t>Hidalgo acumula 47,175 casos de infecciones intestinales en lo que va de 2026, de los cuales las mujeres representan la mayoría de las atenciones de salud digestiva.</t>
+  </si>
+  <si>
+    <t>Ana Luisa Vega</t>
+  </si>
+  <si>
+    <t>SSH, Secretaría de Salud Federal</t>
+  </si>
+  <si>
+    <t>Reconoce Hidalgo el liderazgo de Claudia Sheinbaum</t>
+  </si>
+  <si>
+    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, respaldó a la presidenta Claudia Sheinbaum Pardo en la transformación que lleva a cabo en el país a través de proyectos de gran impacto, la entrega de programas sociales y diversas acciones para garantizar el bienestar de las familias mexicanas. Durante la presentación de su Segundo Informe de Gobierno, Sheinbaum Pardo aseguró que el Estado mexicano es rector en la planeación del desarrollo del país, convirtiendo las políticas públicas en derechos que le pertenecen al pueblo; como ejemplo, más de 42.8 millones de personas serán beneficiadas con los programas sociales para el cierre del 2026. “El Segundo Informe de la presidenta Claudia Sheinbaum es un ejercicio muy resumido, pero de grandes logros en todas las materias, en todos los aspectos que le corresponden al Poder Ejecutivo federal y, particularmente, hizo referencia a proyectos en Hidalgo que van a ayudar sin duda a la transformación del estado”, puntualizó el mandatario estatal. En ese sentido, Menchaca Salazar enlistó las acciones emprendidas por el Gobierno de México en coordinación con la administración estatal, entre las que destacan el Tren México-Pachuca, la estación en Tula del Tren México-Querétaro y el Polo de Desarrollo Económico para el Bienestar de Zapotlán. Asimismo, la tecnificación de distritos de riego, la construcción de Viviendas para el Bienestar, la carretera Huejutla-Tamazunchale y el saneamiento de Tula. Además, el titular del gobierno de Hidalgo agradeció a la mandataria nacional el apoyo brindado tras la vaguada monzónica registrada en octubre del 2025, para atender los daños en 28 municipios hidalguenses.</t>
+  </si>
+  <si>
+    <t>El gobernador Julio Menchaca expresó su total respaldo a los logros expuestos por la presidenta Claudia Sheinbaum en su Segundo Informe, destacando proyectos ferroviarios, de vivienda y de saneamiento ambiental.</t>
+  </si>
+  <si>
+    <t>Gobernador, Presidencia, Infonavit, Conavi, SCT</t>
+  </si>
+  <si>
+    <t>Exigen firma de Condiciones Generales de Trabajo</t>
+  </si>
+  <si>
+    <t>Trabajadores de la Universidad Tecnológica de la Huasteca Hidalguense (UTHH), agremiados al Sindicato Único de Trabajadores de las Universidades Tecnológicas del Estado de Hidalgo (SUTUTEH), se manifestaron el martes frente a las instalaciones de la institución para exigir el cumplimiento de los acuerdos relacionados con la firma de las Condiciones Generales de Trabajo. Con pancartas, los trabajadores señalaron que llevan más de tres años a la espera de una solución y reclamaron a las autoridades cumplir con los acuerdos establecidos. Efrén Juárez Castillo, secretario general del SUTUTEH, explicó que el sindicato entregó el proyecto de Condiciones Generales de Trabajo el 8 de marzo de 2023, documento mediante el cual buscan establecer y garantizar los derechos laborales de los trabajadores de la universidad. El dirigente sindical recordó que, ante la falta de avances, el sindicato incluso solicitó ejercer su derecho a huelga, estableciéndose como fecha límite el 31 de diciembre de 2025 para concretar la firma.</t>
+  </si>
+  <si>
+    <t>Trabajadores de la UTHH agremiados al SUTUTEH protestaron en Huejutla para exigir la firma formal de sus Condiciones Generales de Trabajo pendientes desde hace tres años.</t>
+  </si>
+  <si>
+    <t>SEPH, Sindicato Único de Trabajadores de las Universidades Tecnológicas</t>
+  </si>
+  <si>
+    <t>Padres de familia extienden protesta hasta la Jefatura de Sector</t>
+  </si>
+  <si>
+    <t>Padres de familia de la Escuela Primaria Gregorio Torres Quintero, de la comunidad de La Lagunilla en Tulancingo, se manifestaron la mañana del pasado martes 1 de septiembre en las oficinas de Sector, ubicadas en el centro de Tulancingo, en demanda de la sustitución del conserje que desde mayo fue removido de su cargo por diversas irregularidades. Los padres de familia fueron atendidos por el profesor René Vargas, quien les informó que el recurso llegaría el próximo jueves o viernes; no obstante, los inconformes se mantienen en su postura de no abrir la escuela hasta que no llegue el nuevo conserje y exigir solución inmediata. Además, solicitan la reincorporación de dos maestros más, a quienes no se les renovó su contrato temporal y no se presentaron a trabajar el pasado lunes 31 de agosto. Pese al diálogo con el profesor René, los padres de familia no quisieron reabrir la escuela que se encuentra en la comunidad de La Lagunilla, ya que aseguraron que lo mismo les prometieron en mayo pasado, y hasta el momento, no se han cumplido los acuerdos. Cabe mencionar que este miércoles 2 de septiembre cumplirán tres días sin clases, un total de 132 alumnos de dicha comunidad, que estudian en esta escuela.</t>
+  </si>
+  <si>
+    <t>Padres de familia mantuvieron cerrada la primaria Gregorio Torres Quintero de Tulancingo y protestaron ante la SEPH exigiendo intendente y dos maestros, dejando a 132 niños sin clases.</t>
+  </si>
+  <si>
+    <t>SEPH, Escuela Primaria Gregorio Torres Quintero</t>
+  </si>
+  <si>
+    <t>René Vargas</t>
+  </si>
+  <si>
+    <t>Mantienen apoyo por lluvias en Pachuca, Mineral de la Reforma y Zempoala</t>
+  </si>
+  <si>
+    <t>La Secretaría de Seguridad Pública de Hidalgo (SSPH), informó que a través de la Policía Estatal y el Cuerpo de Bomberos, mantuvieron la tarde de ayer recorridos de prevención, vigilancia y apoyo a la ciudadanía ante las precipitaciones pluviales registradas durante las últimas horas en los municipios de Pachuca, Mineral de la Reforma y Zempoala. Derivado de las lluvias, se han recibido reportes de inundaciones en diferentes colonias de Pachuca, por lo que personal operativo mantiene presencia en zonas susceptibles y brinda apoyo a la población ante posibles afectaciones. En coordinación con instancias de los gobiernos estatal y municipal, la SSPH mantiene monitoreo permanente y atiende los reportes recibidos a través del C5i Hidalgo y el 911 de Emergencias.</t>
+  </si>
+  <si>
+    <t>Elementos de la SSPH y Bomberos de Hidalgo desplegaron operativos preventivos y auxilio vial ante encharcamientos pluviales registrados en Pachuca, Mineral de la Reforma y Zempoala.</t>
+  </si>
+  <si>
+    <t>SSPH, Policía Estatal, Cuerpo de Bomberos de Hidalgo, C5i</t>
+  </si>
+  <si>
+    <t>Hidalgo se encuentra entre las más seguras del país</t>
+  </si>
+  <si>
+    <t>En la actualidad, Hidalgo se encuentra entre los 10 estados más seguros del país, la extorsión disminuyó 71%, los homicidios bajaron 24% y la percepción del desempeño y la efectividad de la policía aumentó del 51 al 56%. Ahora contamos con más equipo, más movilidad y más preparación para Hidalgo. Durante esta administración se fortaleció la capacidad operativa con 416 vehículos, 416 armas, 191 mil cartuchos y más de 149 mil piezas de uniformes y equipo balístico. Una estrategia que busca contar con instituciones mejor preparadas y equipadas para brindar mayor protección a las familias hidalguenses. Actualmente se cuenta con más capacidad, más fuerza institucional y Más seguridad. Por lo cual, el Gobernador Julio Menchaca Salazar advierte “Hidalgo es una potencia en marcha”.</t>
+  </si>
+  <si>
+    <t>Seguridad</t>
+  </si>
+  <si>
+    <t>Hidalgo se ubicó en el top 10 de estados más seguros del país, registrando una baja del 71% en extorsión y del 24% en homicidios, apuntalado con inversión en equipamiento y armamento policiaco.</t>
+  </si>
+  <si>
+    <t>Gobernador, SSPH, Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública</t>
+  </si>
+  <si>
+    <t>Agentes de la PGJH atoraron a dos con drogas y armas de fuego</t>
+  </si>
+  <si>
+    <t>Elementos de la Agencia de Investigación Criminal de la Procuraduría General de Justicia de Hidalgo detuvieron a dos en posesión de diversas dosis de estupefacientes y dos armas de fuego. Las acciones ministeriales ocurrieron en la colonia Parque los Encinos, en Mineral de la Reforma, donde las personas fueron intervenidas cuando realizaban actividades relacionadas con comercialización de narcóticos. A, R. G. T., le fueron asegurados casi un centenar de envoltorios de cristal, mariguana, un arma de fuego, una libreta, dinero y báscula gramera. A quien se le identificó como A. A. C. O., le localizaron diversos envoltorios de cristal, metanfetaminas y al interior de una mochila verde fue localizada otra arma de fuego.</t>
+  </si>
+  <si>
+    <t>Elementos de la AIC detuvieron en la colonia Parque los Encinos de Mineral de la Reforma a dos personas en posesión de dosis de cristal, mariguana, metanfetaminas y armas de fuego.</t>
+  </si>
+  <si>
+    <t>PGJEH, Agencia de Investigación Criminal</t>
+  </si>
+  <si>
+    <t>Aguaceros colapsan bulevares en Pachuca</t>
+  </si>
+  <si>
+    <t>La lluvia intensa volvió a poner a prueba las calles de la ciudad de Pachuca, provocando escurrimientos e inundaciones en distintos puntos e inhabilitando temporalmente seis estaciones del Tuzobús. Personal de Protección Civil y de la Secretaría de Seguridad Pública, Tránsito y Vialidad de Pachuca mantuvieron presencia en áreas críticas como los bulevares del Minero, Felipe Ángeles, Ramón G. Bonfil y Colosio. Los escurrimientos descendieron con fuerza desde el bulevar del Minero hacia Punta Azul, Piracantos, Parque de Poblamiento, Plutarco Elías Calles y Rojo Gómez. Ante la contingencia, la Policía Estatal y el H. Cuerpo de Bomberos de la SSPH desplegaron patrullajes preventivos, auxiliando a transeúntes y trasladando a civiles en patrullas. Las autoridades instaron a evitar transitar por zonas anegadas y reportar incidencias al 911.</t>
+  </si>
+  <si>
+    <t>Fuertes lluvias provocaron severas inundaciones en bulevares de Pachuca y el cierre de seis estaciones del Tuzobús, motivando el despliegue de auxilio vial por parte de Protección Civil, Policía Estatal y Bomberos.</t>
+  </si>
+  <si>
+    <t>SSPH, Policía Estatal, Bomberos, Protección Civil</t>
+  </si>
+  <si>
+    <t>Cuarto Informe: viernes el evento, sábado la glosa</t>
+  </si>
+  <si>
+    <t>El cuarto informe de actividades del gobernador Julio Menchaca Salazar se dividirá en dos jornadas este año, según informó el diputado Andrés Velázquez Vázquez. El mensaje político masivo se realizará el viernes 4 de septiembre a las 11:00 horas en el recinto ferial de Pachuca. En tanto, la entrega formal y protocolaria del documento de rendición de cuentas se llevará a cabo ante el Pleno del Congreso de Hidalgo el sábado 5 de septiembre a las 12:00 horas durante una sesión solemne. El diputado explicó que el ajuste de formato responde a que el 5 de septiembre caerá en sábado, por lo que el secretario de Gobierno, Guillermo Olivares Reyna, acudirá en representación de Menchaca a entregar formalmente la glosa legislativa.</t>
+  </si>
+  <si>
+    <t>El informe anual del gobernador Julio Menchaca se presentará en dos eventos: un acto masivo el viernes 4 de septiembre en la Feria, y la entrega formal en el Congreso el sábado 5 de septiembre a través de la Segobh.</t>
+  </si>
+  <si>
+    <t>Julio Menchaca Salazar, Andrés Velázquez Vázquez, Guillermo Olivares Reyna</t>
+  </si>
+  <si>
+    <t>Descartan plagio en bordados de Jaltocán</t>
+  </si>
+  <si>
+    <t>El Consejo Técnico Artesanal de Hidalgo descartó la existencia de plagio o aprovechamiento lucrativo indebido relacionado con los bordados tradicionales huastecos de Jaltocán. El caso surgió a raíz de la denuncia de un particular, tras lo cual personal técnico inspeccionó la zona. La secretaria de Cultura, Neyda Naranjo Baltazar, detalló que el análisis confirmó que se trató de un maestro de danza de bajos recursos que, al no poder costear trajes bordados a mano para sus alumnas, recurrió a la técnica de sublimación del diseño en tela con fines exclusivamente didácticos para los ensayos coreográficos, descartándose intenciones de comercialización masiva.</t>
+  </si>
+  <si>
+    <t>El Consejo Técnico Artesanal de Hidalgo dictaminó que no se configuró plagio comercial en bordados de Jaltocán por parte de un maestro que empleó estampados sublimados para ensayos escolares de danza.</t>
+  </si>
+  <si>
+    <t>Cultura, Consejo Técnico Artesanal</t>
+  </si>
+  <si>
+    <t>El titular de la Secretaría de Educación Pública de Hidalgo (SEPH), Natividad Castrejón Valdez, informó que la histórica escuela primaria Aquiles Serdán, ubicada en Tulancingo, presenta severas fallas y agrietamientos estructurales que obligan a su demolición total y reconstrucción desde los cimientos. El proyecto contempla levantar una infraestructura completamente nueva con de cinco aulas didácticas y dos direcciones. Las obras de demolición arrancarán formalmente en octubre de 2026 y se prevé que duren la totalidad del ciclo escolar 2026-2027. Castrejón precisó que en septiembre se definirán sedes alternas para reubicar presencialmente a los alumnos, contemplándose formatos virtuales o híbridos en caso de no hallar un plantel cercano con capacidad suficiente de 14 aulas, lo que genera reticencia entre padres de familia.</t>
+  </si>
+  <si>
+    <t>La SEPH demolerá y reconstruirá la primaria Aquiles Serdán en Tulancingo por daños estructurales, previéndose reubicar a alumnos presencial o virtualmente durante el ciclo 2026-2027.</t>
+  </si>
+  <si>
+    <t>SEPH, Dirección de Servicios Escolares</t>
   </si>
 </sst>
 </file>
@@ -1442,8 +1535,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}" name="Tabla1" displayName="Tabla1" ref="A1:AJ64" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ64" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}" name="Tabla1" displayName="Tabla1" ref="A1:AJ72" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ72" xr:uid="{73367CC7-8808-4B98-88CC-067832E75CF0}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{D3CF0D4E-B6F9-44AC-AB4F-0535BBEB6872}" uniqueName="Canal" name="Canal">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
@@ -1875,7 +1968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DBE5F67-B229-448F-97D5-0E5E46CD1702}">
-  <dimension ref="A1:AJ64"/>
+  <dimension ref="A1:AJ72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -2027,10 +2120,10 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
         <v>111</v>
@@ -2039,16 +2132,16 @@
         <v>112</v>
       </c>
       <c r="F2" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G2">
         <v>4</v>
       </c>
       <c r="H2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -2057,13 +2150,13 @@
         <v>13262</v>
       </c>
       <c r="T2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V2" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="W2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="X2" t="s">
         <v>113</v>
@@ -2072,31 +2165,31 @@
         <v>67</v>
       </c>
       <c r="Z2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA2">
+        <v>15</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI2" t="s">
         <v>114</v>
-      </c>
-      <c r="AA2">
-        <v>24</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>72</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>93</v>
       </c>
       <c r="AJ2" t="s">
         <v>115</v>
@@ -2104,10 +2197,10 @@
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
         <v>116</v>
@@ -2116,16 +2209,16 @@
         <v>117</v>
       </c>
       <c r="F3" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="I3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -2134,75 +2227,72 @@
         <v>13262</v>
       </c>
       <c r="T3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W3" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="X3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Y3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA3">
         <v>20</v>
       </c>
       <c r="AB3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AD3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG3" t="s">
         <v>40</v>
       </c>
-      <c r="AG3" t="s">
-        <v>41</v>
-      </c>
       <c r="AH3" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="AI3" t="s">
-        <v>119</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F4" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G4">
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="I4" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -2211,75 +2301,72 @@
         <v>13262</v>
       </c>
       <c r="T4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V4" t="s">
+        <v>37</v>
+      </c>
+      <c r="W4" t="s">
+        <v>126</v>
+      </c>
+      <c r="X4" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA4">
+        <v>15</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC4" t="s">
         <v>38</v>
       </c>
-      <c r="W4" t="s">
-        <v>80</v>
-      </c>
-      <c r="X4" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA4">
-        <v>24</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>39</v>
-      </c>
       <c r="AD4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF4" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="AG4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH4" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="AI4" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F5" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5" t="s">
         <v>71</v>
       </c>
-      <c r="B5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F5" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
-      <c r="H5" t="s">
-        <v>78</v>
-      </c>
       <c r="I5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R5">
         <v>1</v>
@@ -2288,75 +2375,75 @@
         <v>13262</v>
       </c>
       <c r="T5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W5" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="X5" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="Y5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z5" t="s">
-        <v>114</v>
+        <v>45</v>
       </c>
       <c r="AA5">
         <v>24</v>
       </c>
       <c r="AB5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF5" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="AG5" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH5" t="s">
         <v>41</v>
       </c>
-      <c r="AH5" t="s">
-        <v>62</v>
-      </c>
       <c r="AI5" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="AJ5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F6" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H6" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="I6" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -2365,75 +2452,75 @@
         <v>13262</v>
       </c>
       <c r="T6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W6" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="X6" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="Y6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="Z6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA6">
         <v>15</v>
       </c>
       <c r="AB6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AD6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF6" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH6" t="s">
         <v>128</v>
       </c>
-      <c r="AG6" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>58</v>
-      </c>
       <c r="AI6" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="AJ6" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F7" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
         <v>71</v>
       </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" t="s">
-        <v>138</v>
-      </c>
-      <c r="F7" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G7">
-        <v>7</v>
-      </c>
-      <c r="H7" t="s">
-        <v>50</v>
-      </c>
       <c r="I7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -2442,75 +2529,75 @@
         <v>13262</v>
       </c>
       <c r="T7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V7" t="s">
+        <v>37</v>
+      </c>
+      <c r="W7" t="s">
+        <v>145</v>
+      </c>
+      <c r="X7" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA7">
+        <v>20</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC7" t="s">
         <v>38</v>
       </c>
-      <c r="W7" t="s">
-        <v>98</v>
-      </c>
-      <c r="X7" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA7">
-        <v>15</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>39</v>
-      </c>
       <c r="AD7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF7" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="AG7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH7" t="s">
         <v>49</v>
       </c>
       <c r="AI7" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="AJ7" t="s">
-        <v>45</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F8" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -2519,75 +2606,72 @@
         <v>13262</v>
       </c>
       <c r="T8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V8" t="s">
+        <v>37</v>
+      </c>
+      <c r="W8" t="s">
+        <v>151</v>
+      </c>
+      <c r="X8" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA8">
+        <v>12</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC8" t="s">
         <v>38</v>
       </c>
-      <c r="W8" t="s">
-        <v>145</v>
-      </c>
-      <c r="X8" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA8">
-        <v>20</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>48</v>
-      </c>
       <c r="AD8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF8" t="s">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="AG8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH8" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="AI8" t="s">
-        <v>147</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E9" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F9" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H9" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="I9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R9">
         <v>1</v>
@@ -2596,75 +2680,75 @@
         <v>13262</v>
       </c>
       <c r="T9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W9" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="X9" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="Y9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA9">
         <v>20</v>
       </c>
       <c r="AB9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC9" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AD9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG9" t="s">
         <v>40</v>
       </c>
-      <c r="AG9" t="s">
+      <c r="AH9" t="s">
         <v>41</v>
       </c>
-      <c r="AH9" t="s">
-        <v>152</v>
-      </c>
       <c r="AI9" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AJ9" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F10" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H10" t="s">
         <v>74</v>
       </c>
       <c r="I10" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="R10">
         <v>1</v>
@@ -2673,75 +2757,75 @@
         <v>13262</v>
       </c>
       <c r="T10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V10" t="s">
+        <v>37</v>
+      </c>
+      <c r="W10" t="s">
+        <v>163</v>
+      </c>
+      <c r="X10" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA10">
+        <v>24</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC10" t="s">
         <v>38</v>
       </c>
-      <c r="W10" t="s">
-        <v>94</v>
-      </c>
-      <c r="X10" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA10">
-        <v>20</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC10" t="s">
-        <v>39</v>
-      </c>
       <c r="AD10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF10" t="s">
+        <v>165</v>
+      </c>
+      <c r="AG10" t="s">
         <v>40</v>
       </c>
-      <c r="AG10" t="s">
-        <v>41</v>
-      </c>
       <c r="AH10" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="AI10" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="AJ10" t="s">
-        <v>45</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F11" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11" t="s">
         <v>71</v>
       </c>
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>158</v>
-      </c>
-      <c r="E11" t="s">
-        <v>159</v>
-      </c>
-      <c r="F11" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-      <c r="H11" t="s">
-        <v>76</v>
-      </c>
       <c r="I11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -2750,75 +2834,75 @@
         <v>13262</v>
       </c>
       <c r="T11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V11" t="s">
+        <v>37</v>
+      </c>
+      <c r="W11" t="s">
+        <v>170</v>
+      </c>
+      <c r="X11" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA11">
+        <v>24</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC11" t="s">
         <v>38</v>
       </c>
-      <c r="W11" t="s">
-        <v>88</v>
-      </c>
-      <c r="X11" t="s">
-        <v>160</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA11">
-        <v>20</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>39</v>
-      </c>
       <c r="AD11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF11" t="s">
-        <v>161</v>
+        <v>42</v>
       </c>
       <c r="AG11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH11" t="s">
         <v>41</v>
       </c>
-      <c r="AH11" t="s">
-        <v>51</v>
-      </c>
       <c r="AI11" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="AJ11" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E12" t="s">
+        <v>174</v>
+      </c>
+      <c r="F12" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="H12" t="s">
         <v>71</v>
       </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="s">
-        <v>164</v>
-      </c>
-      <c r="E12" t="s">
-        <v>165</v>
-      </c>
-      <c r="F12" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>53</v>
-      </c>
-      <c r="I12" t="s">
-        <v>46</v>
       </c>
       <c r="R12">
         <v>1</v>
@@ -2827,75 +2911,75 @@
         <v>13262</v>
       </c>
       <c r="T12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W12" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
       <c r="X12" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="Y12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA12">
         <v>20</v>
       </c>
       <c r="AB12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC12" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AD12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF12" t="s">
-        <v>99</v>
+        <v>177</v>
       </c>
       <c r="AG12" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH12" t="s">
         <v>41</v>
       </c>
-      <c r="AH12" t="s">
-        <v>51</v>
-      </c>
       <c r="AI12" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="AJ12" t="s">
-        <v>45</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="F13" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G13">
         <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="I13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R13">
         <v>1</v>
@@ -2904,75 +2988,75 @@
         <v>13262</v>
       </c>
       <c r="T13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V13" t="s">
+        <v>37</v>
+      </c>
+      <c r="W13" t="s">
+        <v>182</v>
+      </c>
+      <c r="X13" t="s">
+        <v>183</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA13">
+        <v>20</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC13" t="s">
         <v>38</v>
       </c>
-      <c r="W13" t="s">
-        <v>92</v>
-      </c>
-      <c r="X13" t="s">
-        <v>170</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA13">
-        <v>24</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>39</v>
-      </c>
       <c r="AD13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF13" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="AG13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH13" t="s">
         <v>41</v>
       </c>
-      <c r="AH13" t="s">
-        <v>42</v>
-      </c>
       <c r="AI13" t="s">
-        <v>171</v>
+        <v>84</v>
       </c>
       <c r="AJ13" t="s">
-        <v>172</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E14" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G14">
+        <v>17</v>
+      </c>
+      <c r="H14" t="s">
         <v>71</v>
       </c>
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" t="s">
-        <v>173</v>
-      </c>
-      <c r="E14" t="s">
-        <v>174</v>
-      </c>
-      <c r="F14" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G14">
-        <v>8</v>
-      </c>
-      <c r="H14" t="s">
-        <v>74</v>
-      </c>
       <c r="I14" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="R14">
         <v>1</v>
@@ -2981,75 +3065,75 @@
         <v>13262</v>
       </c>
       <c r="T14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W14" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="X14" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="Y14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA14">
         <v>20</v>
       </c>
       <c r="AB14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF14" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="AG14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH14" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="AI14" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="AJ14" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
         <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="E15" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="F15" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="I15" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -3058,75 +3142,75 @@
         <v>13262</v>
       </c>
       <c r="T15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W15" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="X15" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="Y15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA15">
         <v>20</v>
       </c>
       <c r="AB15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC15" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AD15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF15" t="s">
-        <v>65</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH15" t="s">
-        <v>52</v>
+        <v>154</v>
       </c>
       <c r="AI15" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="AJ15" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" t="s">
+        <v>197</v>
+      </c>
+      <c r="E16" t="s">
+        <v>198</v>
+      </c>
+      <c r="F16" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16" t="s">
         <v>71</v>
       </c>
-      <c r="B16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" t="s">
-        <v>186</v>
-      </c>
-      <c r="E16" t="s">
-        <v>187</v>
-      </c>
-      <c r="F16" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G16">
-        <v>4</v>
-      </c>
-      <c r="H16" t="s">
-        <v>74</v>
-      </c>
       <c r="I16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R16">
         <v>1</v>
@@ -3135,75 +3219,75 @@
         <v>13262</v>
       </c>
       <c r="T16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W16" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="X16" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="Y16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA16">
         <v>24</v>
       </c>
       <c r="AB16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF16" t="s">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="AG16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH16" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="AI16" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AJ16" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" t="s">
+        <v>202</v>
+      </c>
+      <c r="F17" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17" t="s">
         <v>71</v>
       </c>
-      <c r="B17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" t="s">
-        <v>191</v>
-      </c>
-      <c r="E17" t="s">
-        <v>192</v>
-      </c>
-      <c r="F17" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G17">
-        <v>4</v>
-      </c>
-      <c r="H17" t="s">
-        <v>74</v>
-      </c>
       <c r="I17" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R17">
         <v>1</v>
@@ -3212,75 +3296,75 @@
         <v>13262</v>
       </c>
       <c r="T17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W17" t="s">
-        <v>193</v>
+        <v>95</v>
       </c>
       <c r="X17" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="Y17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA17">
         <v>12</v>
       </c>
       <c r="AB17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AG17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH17" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="AI17" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="AJ17" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" t="s">
+        <v>205</v>
+      </c>
+      <c r="E18" t="s">
+        <v>206</v>
+      </c>
+      <c r="F18" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+      <c r="H18" t="s">
         <v>71</v>
       </c>
-      <c r="B18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" t="s">
-        <v>196</v>
-      </c>
-      <c r="E18" t="s">
-        <v>197</v>
-      </c>
-      <c r="F18" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G18">
-        <v>4</v>
-      </c>
-      <c r="H18" t="s">
-        <v>74</v>
-      </c>
       <c r="I18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -3289,75 +3373,75 @@
         <v>13262</v>
       </c>
       <c r="T18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V18" t="s">
+        <v>37</v>
+      </c>
+      <c r="W18" t="s">
+        <v>175</v>
+      </c>
+      <c r="X18" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA18">
+        <v>24</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC18" t="s">
         <v>38</v>
       </c>
-      <c r="W18" t="s">
-        <v>198</v>
-      </c>
-      <c r="X18" t="s">
-        <v>199</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA18">
-        <v>20</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>39</v>
-      </c>
       <c r="AD18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF18" t="s">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="AG18" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH18" t="s">
         <v>41</v>
       </c>
-      <c r="AH18" t="s">
-        <v>62</v>
-      </c>
       <c r="AI18" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="AJ18" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="E19" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="F19" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G19">
         <v>4</v>
       </c>
       <c r="H19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I19" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -3366,75 +3450,72 @@
         <v>13262</v>
       </c>
       <c r="T19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V19" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="W19" t="s">
-        <v>88</v>
+        <v>186</v>
       </c>
       <c r="X19" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="Y19" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="Z19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA19">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AB19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC19" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AD19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF19" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AG19" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="AH19" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AI19" t="s">
-        <v>109</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>66</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E20" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="F20" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="R20">
         <v>1</v>
@@ -3443,75 +3524,72 @@
         <v>13262</v>
       </c>
       <c r="T20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V20" t="s">
+        <v>37</v>
+      </c>
+      <c r="W20" t="s">
+        <v>106</v>
+      </c>
+      <c r="X20" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA20">
+        <v>15</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC20" t="s">
         <v>38</v>
       </c>
-      <c r="W20" t="s">
-        <v>207</v>
-      </c>
-      <c r="X20" t="s">
-        <v>208</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA20">
-        <v>20</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>39</v>
-      </c>
       <c r="AD20" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF20" t="s">
-        <v>43</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AH20" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AI20" t="s">
-        <v>209</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E21" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="F21" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G21">
         <v>5</v>
       </c>
       <c r="H21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -3520,75 +3598,75 @@
         <v>13262</v>
       </c>
       <c r="T21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V21" t="s">
+        <v>37</v>
+      </c>
+      <c r="W21" t="s">
+        <v>91</v>
+      </c>
+      <c r="X21" t="s">
+        <v>221</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA21">
+        <v>24</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC21" t="s">
         <v>38</v>
       </c>
-      <c r="W21" t="s">
-        <v>213</v>
-      </c>
-      <c r="X21" t="s">
-        <v>214</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA21">
-        <v>20</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>39</v>
-      </c>
       <c r="AD21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AG21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH21" t="s">
-        <v>215</v>
+        <v>92</v>
       </c>
       <c r="AI21" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="AJ21" t="s">
-        <v>217</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>223</v>
+      </c>
+      <c r="E22" t="s">
+        <v>224</v>
+      </c>
+      <c r="F22" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="H22" t="s">
         <v>71</v>
       </c>
-      <c r="B22" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" t="s">
-        <v>218</v>
-      </c>
-      <c r="E22" t="s">
-        <v>219</v>
-      </c>
-      <c r="F22" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G22">
-        <v>7</v>
-      </c>
-      <c r="H22" t="s">
-        <v>50</v>
-      </c>
       <c r="I22" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R22">
         <v>1</v>
@@ -3597,75 +3675,75 @@
         <v>13262</v>
       </c>
       <c r="T22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V22" t="s">
+        <v>37</v>
+      </c>
+      <c r="W22" t="s">
+        <v>104</v>
+      </c>
+      <c r="X22" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA22">
+        <v>20</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC22" t="s">
         <v>38</v>
       </c>
-      <c r="W22" t="s">
-        <v>220</v>
-      </c>
-      <c r="X22" t="s">
-        <v>221</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA22">
-        <v>24</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC22" t="s">
-        <v>39</v>
-      </c>
       <c r="AD22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF22" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="AG22" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AH22" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AI22" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ22" t="s">
         <v>108</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>227</v>
+      </c>
+      <c r="B23" t="s">
+        <v>228</v>
+      </c>
+      <c r="D23" t="s">
+        <v>229</v>
+      </c>
+      <c r="E23" t="s">
+        <v>230</v>
+      </c>
+      <c r="F23" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+      <c r="H23" t="s">
         <v>71</v>
       </c>
-      <c r="B23" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" t="s">
-        <v>223</v>
-      </c>
-      <c r="E23" t="s">
-        <v>224</v>
-      </c>
-      <c r="F23" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G23">
-        <v>7</v>
-      </c>
-      <c r="H23" t="s">
-        <v>50</v>
-      </c>
       <c r="I23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="R23">
         <v>1</v>
@@ -3674,75 +3752,72 @@
         <v>13262</v>
       </c>
       <c r="T23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V23" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="W23" t="s">
-        <v>92</v>
+        <v>231</v>
       </c>
       <c r="X23" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="Y23" t="s">
         <v>67</v>
       </c>
       <c r="Z23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA23">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB23" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC23" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AD23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF23" t="s">
-        <v>65</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AI23" t="s">
-        <v>226</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>45</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>228</v>
       </c>
       <c r="D24" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E24" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F24" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G24">
         <v>7</v>
       </c>
       <c r="H24" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I24" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -3751,75 +3826,75 @@
         <v>13262</v>
       </c>
       <c r="T24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V24" t="s">
+        <v>37</v>
+      </c>
+      <c r="W24" t="s">
+        <v>170</v>
+      </c>
+      <c r="X24" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA24">
+        <v>24</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC24" t="s">
         <v>38</v>
       </c>
-      <c r="W24" t="s">
-        <v>80</v>
-      </c>
-      <c r="X24" t="s">
-        <v>229</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA24">
-        <v>20</v>
-      </c>
-      <c r="AB24" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>48</v>
-      </c>
       <c r="AD24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF24" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AG24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH24" t="s">
         <v>41</v>
       </c>
-      <c r="AH24" t="s">
-        <v>51</v>
-      </c>
       <c r="AI24" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="AJ24" t="s">
-        <v>231</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>228</v>
       </c>
       <c r="D25" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E25" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="F25" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H25" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I25" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R25">
         <v>1</v>
@@ -3828,75 +3903,72 @@
         <v>13262</v>
       </c>
       <c r="T25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W25" t="s">
-        <v>101</v>
+        <v>240</v>
       </c>
       <c r="X25" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="Y25" t="s">
         <v>67</v>
       </c>
       <c r="Z25" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA25">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AB25" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD25" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF25" t="s">
-        <v>235</v>
+        <v>42</v>
       </c>
       <c r="AG25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AH25" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s">
-        <v>236</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>227</v>
+      </c>
+      <c r="B26" t="s">
+        <v>228</v>
+      </c>
+      <c r="D26" t="s">
+        <v>242</v>
+      </c>
+      <c r="E26" t="s">
+        <v>243</v>
+      </c>
+      <c r="F26" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G26">
+        <v>8</v>
+      </c>
+      <c r="H26" t="s">
         <v>71</v>
       </c>
-      <c r="B26" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" t="s">
-        <v>237</v>
-      </c>
-      <c r="E26" t="s">
-        <v>238</v>
-      </c>
-      <c r="F26" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G26">
-        <v>9</v>
-      </c>
-      <c r="H26" t="s">
-        <v>85</v>
-      </c>
       <c r="I26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R26">
         <v>1</v>
@@ -3905,75 +3977,75 @@
         <v>13262</v>
       </c>
       <c r="T26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V26" t="s">
+        <v>37</v>
+      </c>
+      <c r="W26" t="s">
+        <v>89</v>
+      </c>
+      <c r="X26" t="s">
+        <v>244</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA26">
+        <v>24</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC26" t="s">
         <v>38</v>
       </c>
-      <c r="W26" t="s">
-        <v>239</v>
-      </c>
-      <c r="X26" t="s">
-        <v>240</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA26">
-        <v>20</v>
-      </c>
-      <c r="AB26" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC26" t="s">
-        <v>39</v>
-      </c>
       <c r="AD26" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF26" t="s">
-        <v>107</v>
+        <v>42</v>
       </c>
       <c r="AG26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AH26" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="AI26" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AJ26" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>228</v>
       </c>
       <c r="D27" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E27" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F27" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G27">
         <v>9</v>
       </c>
       <c r="H27" t="s">
-        <v>245</v>
+        <v>48</v>
       </c>
       <c r="I27" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R27">
         <v>1</v>
@@ -3982,75 +4054,75 @@
         <v>13262</v>
       </c>
       <c r="T27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V27" t="s">
+        <v>37</v>
+      </c>
+      <c r="W27" t="s">
+        <v>249</v>
+      </c>
+      <c r="X27" t="s">
+        <v>250</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA27">
+        <v>24</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC27" t="s">
         <v>38</v>
       </c>
-      <c r="W27" t="s">
-        <v>106</v>
-      </c>
-      <c r="X27" t="s">
-        <v>246</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA27">
-        <v>20</v>
-      </c>
-      <c r="AB27" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC27" t="s">
-        <v>39</v>
-      </c>
       <c r="AD27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF27" t="s">
-        <v>247</v>
+        <v>42</v>
       </c>
       <c r="AG27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AH27" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="AI27" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AJ27" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>228</v>
       </c>
       <c r="D28" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E28" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F28" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H28" t="s">
-        <v>74</v>
+        <v>255</v>
       </c>
       <c r="I28" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R28">
         <v>1</v>
@@ -4059,75 +4131,75 @@
         <v>13262</v>
       </c>
       <c r="T28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W28" t="s">
-        <v>198</v>
+        <v>256</v>
       </c>
       <c r="X28" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="Y28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA28">
         <v>20</v>
       </c>
       <c r="AB28" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD28" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF28" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="AG28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AH28" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="AI28" t="s">
-        <v>200</v>
+        <v>258</v>
       </c>
       <c r="AJ28" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>228</v>
       </c>
       <c r="D29" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E29" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="F29" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H29" t="s">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="I29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R29">
         <v>1</v>
@@ -4136,75 +4208,75 @@
         <v>13262</v>
       </c>
       <c r="T29" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W29" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="X29" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="Y29" t="s">
         <v>67</v>
       </c>
       <c r="Z29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA29">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC29" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AD29" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF29" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="AG29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AH29" t="s">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="AI29" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AJ29" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>227</v>
+      </c>
+      <c r="B30" t="s">
+        <v>228</v>
+      </c>
+      <c r="D30" t="s">
+        <v>268</v>
+      </c>
+      <c r="E30" t="s">
+        <v>269</v>
+      </c>
+      <c r="F30" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G30">
+        <v>11</v>
+      </c>
+      <c r="H30" t="s">
         <v>71</v>
       </c>
-      <c r="B30" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" t="s">
-        <v>260</v>
-      </c>
-      <c r="E30" t="s">
-        <v>261</v>
-      </c>
-      <c r="F30" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G30">
-        <v>4</v>
-      </c>
-      <c r="H30" t="s">
-        <v>74</v>
-      </c>
       <c r="I30" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R30">
         <v>1</v>
@@ -4213,75 +4285,75 @@
         <v>13262</v>
       </c>
       <c r="T30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W30" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="X30" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="Y30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA30">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB30" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC30" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AD30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF30" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="AG30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AH30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AI30" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="AJ30" t="s">
-        <v>265</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>228</v>
       </c>
       <c r="D31" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E31" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="F31" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G31">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H31" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="I31" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -4290,75 +4362,75 @@
         <v>13262</v>
       </c>
       <c r="T31" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W31" t="s">
-        <v>80</v>
+        <v>275</v>
       </c>
       <c r="X31" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="Y31" t="s">
         <v>67</v>
       </c>
       <c r="Z31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA31">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB31" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AD31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF31" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="AG31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AH31" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="AI31" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AJ31" t="s">
-        <v>222</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B32" t="s">
-        <v>59</v>
+        <v>228</v>
       </c>
       <c r="D32" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E32" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="F32" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G32">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H32" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I32" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R32">
         <v>1</v>
@@ -4367,75 +4439,72 @@
         <v>13262</v>
       </c>
       <c r="T32" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V32" t="s">
+        <v>37</v>
+      </c>
+      <c r="W32" t="s">
+        <v>99</v>
+      </c>
+      <c r="X32" t="s">
+        <v>281</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA32">
+        <v>20</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC32" t="s">
         <v>38</v>
       </c>
-      <c r="W32" t="s">
-        <v>101</v>
-      </c>
-      <c r="X32" t="s">
-        <v>272</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z32" t="s">
+      <c r="AD32" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH32" t="s">
         <v>47</v>
       </c>
-      <c r="AA32">
-        <v>24</v>
-      </c>
-      <c r="AB32" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG32" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH32" t="s">
-        <v>51</v>
-      </c>
       <c r="AI32" t="s">
-        <v>273</v>
-      </c>
-      <c r="AJ32" t="s">
-        <v>81</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>228</v>
       </c>
       <c r="D33" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="E33" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="F33" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G33">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>97</v>
+        <v>262</v>
       </c>
       <c r="I33" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -4444,75 +4513,72 @@
         <v>13262</v>
       </c>
       <c r="T33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V33" t="s">
+        <v>37</v>
+      </c>
+      <c r="W33" t="s">
+        <v>285</v>
+      </c>
+      <c r="X33" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA33">
+        <v>24</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC33" t="s">
         <v>38</v>
       </c>
-      <c r="W33" t="s">
-        <v>98</v>
-      </c>
-      <c r="X33" t="s">
-        <v>276</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z33" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA33">
-        <v>15</v>
-      </c>
-      <c r="AB33" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC33" t="s">
-        <v>39</v>
-      </c>
       <c r="AD33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF33" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="AG33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AH33" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AI33" t="s">
-        <v>277</v>
-      </c>
-      <c r="AJ33" t="s">
-        <v>222</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>228</v>
       </c>
       <c r="D34" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="E34" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="F34" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G34">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>74</v>
+        <v>290</v>
       </c>
       <c r="I34" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R34">
         <v>1</v>
@@ -4521,75 +4587,72 @@
         <v>13262</v>
       </c>
       <c r="T34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V34" t="s">
+        <v>37</v>
+      </c>
+      <c r="W34" t="s">
+        <v>101</v>
+      </c>
+      <c r="X34" t="s">
+        <v>291</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA34">
+        <v>24</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC34" t="s">
         <v>38</v>
       </c>
-      <c r="W34" t="s">
-        <v>280</v>
-      </c>
-      <c r="X34" t="s">
-        <v>281</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z34" t="s">
+      <c r="AD34" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH34" t="s">
         <v>47</v>
       </c>
-      <c r="AA34">
-        <v>20</v>
-      </c>
-      <c r="AB34" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC34" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>86</v>
-      </c>
-      <c r="AG34" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH34" t="s">
-        <v>58</v>
-      </c>
       <c r="AI34" t="s">
-        <v>282</v>
-      </c>
-      <c r="AJ34" t="s">
-        <v>136</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>227</v>
+      </c>
+      <c r="B35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" t="s">
+        <v>293</v>
+      </c>
+      <c r="E35" t="s">
+        <v>294</v>
+      </c>
+      <c r="F35" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35" t="s">
         <v>71</v>
       </c>
-      <c r="B35" t="s">
-        <v>60</v>
-      </c>
-      <c r="D35" t="s">
-        <v>283</v>
-      </c>
-      <c r="E35" t="s">
-        <v>284</v>
-      </c>
-      <c r="F35" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G35">
-        <v>3</v>
-      </c>
-      <c r="H35" t="s">
-        <v>74</v>
-      </c>
       <c r="I35" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R35">
         <v>1</v>
@@ -4598,75 +4661,75 @@
         <v>13262</v>
       </c>
       <c r="T35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V35" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="W35" t="s">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="X35" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="Y35" t="s">
         <v>67</v>
       </c>
       <c r="Z35" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA35">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB35" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC35" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AD35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF35" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH35" t="s">
         <v>41</v>
       </c>
-      <c r="AH35" t="s">
-        <v>51</v>
-      </c>
       <c r="AI35" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="AJ35" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D36" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="E36" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="F36" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G36">
         <v>3</v>
       </c>
       <c r="H36" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="I36" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -4675,75 +4738,75 @@
         <v>13262</v>
       </c>
       <c r="T36" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W36" t="s">
-        <v>291</v>
+        <v>175</v>
       </c>
       <c r="X36" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="Y36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA36">
         <v>20</v>
       </c>
       <c r="AB36" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF36" t="s">
-        <v>293</v>
+        <v>63</v>
       </c>
       <c r="AG36" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH36" t="s">
         <v>41</v>
       </c>
-      <c r="AH36" t="s">
-        <v>42</v>
-      </c>
       <c r="AI36" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="AJ36" t="s">
-        <v>66</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B37" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D37" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="E37" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F37" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G37">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="I37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R37">
         <v>1</v>
@@ -4752,75 +4815,75 @@
         <v>13262</v>
       </c>
       <c r="T37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W37" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="X37" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="Y37" t="s">
         <v>67</v>
       </c>
       <c r="Z37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA37">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AB37" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC37" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AD37" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF37" t="s">
-        <v>293</v>
+        <v>63</v>
       </c>
       <c r="AG37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH37" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="AI37" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="AJ37" t="s">
-        <v>253</v>
+        <v>309</v>
       </c>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>227</v>
+      </c>
+      <c r="B38" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" t="s">
+        <v>310</v>
+      </c>
+      <c r="E38" t="s">
+        <v>311</v>
+      </c>
+      <c r="F38" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G38">
+        <v>4</v>
+      </c>
+      <c r="H38" t="s">
         <v>71</v>
       </c>
-      <c r="B38" t="s">
-        <v>60</v>
-      </c>
-      <c r="D38" t="s">
-        <v>300</v>
-      </c>
-      <c r="E38" t="s">
-        <v>301</v>
-      </c>
-      <c r="F38" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G38">
-        <v>6</v>
-      </c>
-      <c r="H38" t="s">
-        <v>74</v>
-      </c>
       <c r="I38" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R38">
         <v>1</v>
@@ -4829,75 +4892,75 @@
         <v>13262</v>
       </c>
       <c r="T38" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W38" t="s">
-        <v>96</v>
+        <v>312</v>
       </c>
       <c r="X38" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="Y38" t="s">
         <v>67</v>
       </c>
       <c r="Z38" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA38">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB38" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC38" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AD38" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF38" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="AG38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH38" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="AI38" t="s">
-        <v>303</v>
+        <v>50</v>
       </c>
       <c r="AJ38" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>227</v>
+      </c>
+      <c r="B39" t="s">
+        <v>55</v>
+      </c>
+      <c r="D39" t="s">
+        <v>315</v>
+      </c>
+      <c r="E39" t="s">
+        <v>316</v>
+      </c>
+      <c r="F39" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G39">
+        <v>4</v>
+      </c>
+      <c r="H39" t="s">
         <v>71</v>
       </c>
-      <c r="B39" t="s">
-        <v>60</v>
-      </c>
-      <c r="D39" t="s">
-        <v>305</v>
-      </c>
-      <c r="E39" t="s">
-        <v>306</v>
-      </c>
-      <c r="F39" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G39">
-        <v>8</v>
-      </c>
-      <c r="H39" t="s">
-        <v>74</v>
-      </c>
       <c r="I39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R39">
         <v>1</v>
@@ -4906,72 +4969,75 @@
         <v>13262</v>
       </c>
       <c r="T39" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V39" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="W39" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="X39" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="Y39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z39" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AB39" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC39" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AD39" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AG39" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH39" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="AI39" t="s">
-        <v>89</v>
+        <v>318</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="E40" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="F40" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G40">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H40" t="s">
-        <v>74</v>
+        <v>290</v>
       </c>
       <c r="I40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R40">
         <v>1</v>
@@ -4980,72 +5046,72 @@
         <v>13262</v>
       </c>
       <c r="T40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V40" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="W40" t="s">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="X40" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="Y40" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z40" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA40">
+        <v>15</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF40" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG40" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH40" t="s">
         <v>47</v>
       </c>
-      <c r="AA40">
-        <v>10</v>
-      </c>
-      <c r="AB40" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC40" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD40" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF40" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG40" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH40" t="s">
-        <v>58</v>
-      </c>
       <c r="AI40" t="s">
-        <v>195</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D41" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="E41" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="F41" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G41">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H41" t="s">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="I41" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -5054,75 +5120,72 @@
         <v>13262</v>
       </c>
       <c r="T41" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V41" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="W41" t="s">
-        <v>313</v>
+        <v>285</v>
       </c>
       <c r="X41" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="Y41" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z41" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AB41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC41" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AD41" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF41" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG41" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH41" t="s">
         <v>43</v>
       </c>
-      <c r="AG41" t="s">
+      <c r="AI41" t="s">
         <v>43</v>
-      </c>
-      <c r="AH41" t="s">
-        <v>73</v>
-      </c>
-      <c r="AI41" t="s">
-        <v>315</v>
-      </c>
-      <c r="AJ41" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D42" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="E42" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="F42" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G42">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H42" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="I42" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="R42">
         <v>1</v>
@@ -5131,75 +5194,75 @@
         <v>13262</v>
       </c>
       <c r="T42" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W42" t="s">
-        <v>319</v>
+        <v>263</v>
       </c>
       <c r="X42" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="Y42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z42" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA42">
         <v>20</v>
       </c>
       <c r="AB42" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD42" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AG42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AH42" t="s">
-        <v>42</v>
+        <v>265</v>
       </c>
       <c r="AI42" t="s">
-        <v>321</v>
+        <v>265</v>
       </c>
       <c r="AJ42" t="s">
-        <v>66</v>
+        <v>267</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B43" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D43" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="E43" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="F43" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H43" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I43" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="R43">
         <v>1</v>
@@ -5208,72 +5271,75 @@
         <v>13262</v>
       </c>
       <c r="T43" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V43" t="s">
+        <v>37</v>
+      </c>
+      <c r="W43" t="s">
+        <v>331</v>
+      </c>
+      <c r="X43" t="s">
+        <v>332</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA43">
+        <v>20</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC43" t="s">
         <v>38</v>
       </c>
-      <c r="W43" t="s">
-        <v>291</v>
-      </c>
-      <c r="X43" t="s">
-        <v>324</v>
-      </c>
-      <c r="Y43" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z43" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA43">
-        <v>10</v>
-      </c>
-      <c r="AB43" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC43" t="s">
-        <v>39</v>
-      </c>
       <c r="AD43" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF43" t="s">
-        <v>43</v>
+        <v>333</v>
       </c>
       <c r="AG43" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AH43" t="s">
         <v>49</v>
       </c>
       <c r="AI43" t="s">
-        <v>325</v>
+        <v>49</v>
+      </c>
+      <c r="AJ43" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="D44" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="E44" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="F44" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H44" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="I44" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="R44">
         <v>1</v>
@@ -5282,75 +5348,75 @@
         <v>13262</v>
       </c>
       <c r="T44" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W44" t="s">
-        <v>319</v>
+        <v>106</v>
       </c>
       <c r="X44" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="Y44" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z44" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA44">
         <v>20</v>
       </c>
       <c r="AB44" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD44" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF44" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="AG44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH44" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="AI44" t="s">
-        <v>321</v>
+        <v>49</v>
       </c>
       <c r="AJ44" t="s">
-        <v>66</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B45" t="s">
         <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="E45" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="F45" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G45">
         <v>2</v>
       </c>
       <c r="H45" t="s">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="I45" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -5359,75 +5425,75 @@
         <v>13262</v>
       </c>
       <c r="T45" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W45" t="s">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="X45" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="Y45" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z45" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA45">
         <v>24</v>
       </c>
       <c r="AB45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD45" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF45" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="AG45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH45" t="s">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="AI45" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="AJ45" t="s">
-        <v>81</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B46" t="s">
         <v>23</v>
       </c>
       <c r="D46" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="E46" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="F46" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I46" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="R46">
         <v>1</v>
@@ -5436,75 +5502,72 @@
         <v>13262</v>
       </c>
       <c r="T46" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V46" t="s">
+        <v>37</v>
+      </c>
+      <c r="W46" t="s">
+        <v>99</v>
+      </c>
+      <c r="X46" t="s">
+        <v>345</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA46">
+        <v>24</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC46" t="s">
         <v>38</v>
       </c>
-      <c r="W46" t="s">
-        <v>213</v>
-      </c>
-      <c r="X46" t="s">
-        <v>335</v>
-      </c>
-      <c r="Y46" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z46" t="s">
+      <c r="AD46" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF46" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG46" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH46" t="s">
         <v>47</v>
       </c>
-      <c r="AA46">
-        <v>15</v>
-      </c>
-      <c r="AB46" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC46" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD46" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF46" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG46" t="s">
-        <v>41</v>
-      </c>
-      <c r="AH46" t="s">
-        <v>215</v>
-      </c>
       <c r="AI46" t="s">
-        <v>216</v>
-      </c>
-      <c r="AJ46" t="s">
-        <v>217</v>
+        <v>346</v>
       </c>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B47" t="s">
         <v>23</v>
       </c>
       <c r="D47" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="E47" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="F47" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G47">
         <v>3</v>
       </c>
       <c r="H47" t="s">
-        <v>245</v>
+        <v>71</v>
       </c>
       <c r="I47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R47">
         <v>1</v>
@@ -5513,75 +5576,75 @@
         <v>13262</v>
       </c>
       <c r="T47" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V47" t="s">
+        <v>37</v>
+      </c>
+      <c r="W47" t="s">
+        <v>97</v>
+      </c>
+      <c r="X47" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA47">
+        <v>20</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC47" t="s">
         <v>38</v>
       </c>
-      <c r="W47" t="s">
-        <v>338</v>
-      </c>
-      <c r="X47" t="s">
-        <v>339</v>
-      </c>
-      <c r="Y47" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z47" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA47">
-        <v>24</v>
-      </c>
-      <c r="AB47" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC47" t="s">
-        <v>39</v>
-      </c>
       <c r="AD47" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF47" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="AG47" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH47" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="AI47" t="s">
-        <v>340</v>
+        <v>272</v>
       </c>
       <c r="AJ47" t="s">
-        <v>341</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>227</v>
+      </c>
+      <c r="B48" t="s">
+        <v>36</v>
+      </c>
+      <c r="D48" t="s">
+        <v>350</v>
+      </c>
+      <c r="E48" t="s">
+        <v>351</v>
+      </c>
+      <c r="F48" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G48">
+        <v>4</v>
+      </c>
+      <c r="H48" t="s">
         <v>71</v>
       </c>
-      <c r="B48" t="s">
-        <v>23</v>
-      </c>
-      <c r="D48" t="s">
-        <v>342</v>
-      </c>
-      <c r="E48" t="s">
-        <v>343</v>
-      </c>
-      <c r="F48" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G48">
-        <v>3</v>
-      </c>
-      <c r="H48" t="s">
-        <v>74</v>
-      </c>
       <c r="I48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R48">
         <v>1</v>
@@ -5590,75 +5653,75 @@
         <v>13262</v>
       </c>
       <c r="T48" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V48" t="s">
+        <v>37</v>
+      </c>
+      <c r="W48" t="s">
+        <v>175</v>
+      </c>
+      <c r="X48" t="s">
+        <v>352</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA48">
+        <v>24</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC48" t="s">
         <v>38</v>
       </c>
-      <c r="W48" t="s">
-        <v>198</v>
-      </c>
-      <c r="X48" t="s">
-        <v>344</v>
-      </c>
-      <c r="Y48" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z48" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA48">
-        <v>20</v>
-      </c>
-      <c r="AB48" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC48" t="s">
-        <v>39</v>
-      </c>
       <c r="AD48" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF48" t="s">
-        <v>91</v>
+        <v>353</v>
       </c>
       <c r="AG48" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH48" t="s">
         <v>41</v>
       </c>
-      <c r="AH48" t="s">
-        <v>62</v>
-      </c>
       <c r="AI48" t="s">
-        <v>345</v>
+        <v>302</v>
       </c>
       <c r="AJ48" t="s">
-        <v>346</v>
+        <v>209</v>
       </c>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>227</v>
+      </c>
+      <c r="B49" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" t="s">
+        <v>354</v>
+      </c>
+      <c r="E49" t="s">
+        <v>355</v>
+      </c>
+      <c r="F49" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G49">
+        <v>5</v>
+      </c>
+      <c r="H49" t="s">
         <v>71</v>
       </c>
-      <c r="B49" t="s">
-        <v>23</v>
-      </c>
-      <c r="D49" t="s">
-        <v>347</v>
-      </c>
-      <c r="E49" t="s">
-        <v>348</v>
-      </c>
-      <c r="F49" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G49">
-        <v>4</v>
-      </c>
-      <c r="H49" t="s">
-        <v>100</v>
-      </c>
       <c r="I49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R49">
         <v>1</v>
@@ -5667,75 +5730,72 @@
         <v>13262</v>
       </c>
       <c r="T49" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W49" t="s">
-        <v>96</v>
+        <v>356</v>
       </c>
       <c r="X49" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="Y49" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z49" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA49">
         <v>20</v>
       </c>
       <c r="AB49" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD49" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF49" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AG49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH49" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="AI49" t="s">
-        <v>105</v>
-      </c>
-      <c r="AJ49" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>227</v>
+      </c>
+      <c r="B50" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" t="s">
+        <v>358</v>
+      </c>
+      <c r="E50" t="s">
+        <v>359</v>
+      </c>
+      <c r="F50" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G50">
+        <v>6</v>
+      </c>
+      <c r="H50" t="s">
         <v>71</v>
       </c>
-      <c r="B50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D50" t="s">
-        <v>350</v>
-      </c>
-      <c r="E50" t="s">
-        <v>351</v>
-      </c>
-      <c r="F50" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G50">
-        <v>4</v>
-      </c>
-      <c r="H50" t="s">
-        <v>78</v>
-      </c>
       <c r="I50" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="R50">
         <v>1</v>
@@ -5744,75 +5804,72 @@
         <v>13262</v>
       </c>
       <c r="T50" t="s">
+        <v>68</v>
+      </c>
+      <c r="V50" t="s">
+        <v>37</v>
+      </c>
+      <c r="W50" t="s">
+        <v>360</v>
+      </c>
+      <c r="X50" t="s">
+        <v>361</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA50">
+        <v>24</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF50" t="s">
         <v>70</v>
       </c>
-      <c r="V50" t="s">
-        <v>38</v>
-      </c>
-      <c r="W50" t="s">
-        <v>352</v>
-      </c>
-      <c r="X50" t="s">
-        <v>353</v>
-      </c>
-      <c r="Y50" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z50" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA50">
-        <v>20</v>
-      </c>
-      <c r="AB50" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC50" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD50" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF50" t="s">
-        <v>91</v>
-      </c>
       <c r="AG50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH50" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="AI50" t="s">
-        <v>354</v>
-      </c>
-      <c r="AJ50" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D51" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E51" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F51" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H51" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I51" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R51">
         <v>1</v>
@@ -5821,72 +5878,75 @@
         <v>13262</v>
       </c>
       <c r="T51" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V51" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="W51" t="s">
-        <v>358</v>
+        <v>231</v>
       </c>
       <c r="X51" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="Y51" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="Z51" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA51">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AB51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC51" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AD51" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF51" t="s">
-        <v>360</v>
+        <v>39</v>
       </c>
       <c r="AG51" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="AH51" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AI51" t="s">
-        <v>361</v>
+        <v>366</v>
+      </c>
+      <c r="AJ51" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D52" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E52" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="F52" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H52" t="s">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="I52" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="R52">
         <v>1</v>
@@ -5895,75 +5955,75 @@
         <v>13262</v>
       </c>
       <c r="T52" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V52" t="s">
+        <v>37</v>
+      </c>
+      <c r="W52" t="s">
+        <v>370</v>
+      </c>
+      <c r="X52" t="s">
+        <v>371</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA52">
+        <v>20</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC52" t="s">
         <v>38</v>
       </c>
-      <c r="W52" t="s">
-        <v>319</v>
-      </c>
-      <c r="X52" t="s">
-        <v>364</v>
-      </c>
-      <c r="Y52" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z52" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA52">
-        <v>24</v>
-      </c>
-      <c r="AB52" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC52" t="s">
-        <v>39</v>
-      </c>
       <c r="AD52" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF52" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="AG52" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AH52" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="AI52" t="s">
-        <v>365</v>
+        <v>154</v>
       </c>
       <c r="AJ52" t="s">
-        <v>366</v>
+        <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D53" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E53" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F53" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H53" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R53">
         <v>1</v>
@@ -5972,75 +6032,75 @@
         <v>13262</v>
       </c>
       <c r="T53" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W53" t="s">
-        <v>207</v>
+        <v>374</v>
       </c>
       <c r="X53" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="Y53" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z53" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA53">
         <v>20</v>
       </c>
       <c r="AB53" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC53" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF53" t="s">
         <v>39</v>
       </c>
-      <c r="AD53" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF53" t="s">
-        <v>43</v>
-      </c>
       <c r="AG53" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AH53" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="AI53" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="AJ53" t="s">
-        <v>210</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D54" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="E54" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="F54" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G54">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H54" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="I54" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R54">
         <v>1</v>
@@ -6049,75 +6109,75 @@
         <v>13262</v>
       </c>
       <c r="T54" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V54" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W54" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="X54" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="Y54" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z54" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA54">
         <v>24</v>
       </c>
       <c r="AB54" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD54" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF54" t="s">
-        <v>375</v>
+        <v>42</v>
       </c>
       <c r="AG54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH54" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AI54" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="AJ54" t="s">
-        <v>377</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D55" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E55" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="F55" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H55" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="I55" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="R55">
         <v>1</v>
@@ -6126,75 +6186,75 @@
         <v>13262</v>
       </c>
       <c r="T55" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W55" t="s">
-        <v>220</v>
+        <v>331</v>
       </c>
       <c r="X55" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="Y55" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z55" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA55">
         <v>20</v>
       </c>
       <c r="AB55" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC55" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD55" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF55" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="AG55" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AH55" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AI55" t="s">
-        <v>381</v>
+        <v>49</v>
       </c>
       <c r="AJ55" t="s">
-        <v>66</v>
+        <v>334</v>
       </c>
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D56" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E56" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F56" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G56">
         <v>6</v>
       </c>
       <c r="H56" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="I56" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -6203,75 +6263,75 @@
         <v>13262</v>
       </c>
       <c r="T56" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V56" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W56" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="X56" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="Y56" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z56" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA56">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB56" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC56" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AD56" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF56" t="s">
-        <v>386</v>
+        <v>87</v>
       </c>
       <c r="AG56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH56" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AI56" t="s">
-        <v>387</v>
+        <v>43</v>
       </c>
       <c r="AJ56" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D57" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E57" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F57" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G57">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H57" t="s">
-        <v>50</v>
+        <v>392</v>
       </c>
       <c r="I57" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R57">
         <v>1</v>
@@ -6280,72 +6340,72 @@
         <v>13262</v>
       </c>
       <c r="T57" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W57" t="s">
-        <v>291</v>
+        <v>393</v>
       </c>
       <c r="X57" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="Y57" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z57" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA57">
         <v>20</v>
       </c>
       <c r="AB57" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD57" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF57" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="AG57" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AH57" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="AI57" t="s">
-        <v>325</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="D58" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E58" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F58" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G58">
         <v>8</v>
       </c>
       <c r="H58" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I58" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R58">
         <v>1</v>
@@ -6354,75 +6414,75 @@
         <v>13262</v>
       </c>
       <c r="T58" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V58" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W58" t="s">
-        <v>394</v>
+        <v>270</v>
       </c>
       <c r="X58" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Y58" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z58" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA58">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB58" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC58" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AD58" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF58" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AG58" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="AH58" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="AI58" t="s">
-        <v>396</v>
+        <v>49</v>
       </c>
       <c r="AJ58" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B59" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="D59" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E59" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F59" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H59" t="s">
-        <v>50</v>
+        <v>255</v>
       </c>
       <c r="I59" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R59">
         <v>1</v>
@@ -6431,72 +6491,75 @@
         <v>13262</v>
       </c>
       <c r="T59" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V59" t="s">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="W59" t="s">
-        <v>399</v>
+        <v>256</v>
       </c>
       <c r="X59" t="s">
         <v>400</v>
       </c>
       <c r="Y59" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="Z59" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA59">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB59" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC59" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AD59" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF59" t="s">
-        <v>401</v>
+        <v>42</v>
       </c>
       <c r="AG59" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="AH59" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="AI59" t="s">
-        <v>402</v>
+        <v>122</v>
+      </c>
+      <c r="AJ59" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="60" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B60" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D60" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E60" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F60" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G60">
         <v>2</v>
       </c>
       <c r="H60" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I60" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R60">
         <v>1</v>
@@ -6505,75 +6568,75 @@
         <v>13262</v>
       </c>
       <c r="T60" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V60" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="W60" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="X60" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="Y60" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z60" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA60">
         <v>10</v>
       </c>
       <c r="AB60" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC60" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AD60" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF60" t="s">
-        <v>401</v>
+        <v>102</v>
       </c>
       <c r="AG60" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AH60" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="AI60" t="s">
-        <v>87</v>
+        <v>404</v>
       </c>
       <c r="AJ60" t="s">
-        <v>406</v>
+        <v>298</v>
       </c>
     </row>
     <row r="61" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B61" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D61" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E61" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F61" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G61">
         <v>3</v>
       </c>
       <c r="H61" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="I61" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R61">
         <v>1</v>
@@ -6582,75 +6645,72 @@
         <v>13262</v>
       </c>
       <c r="T61" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V61" t="s">
+        <v>37</v>
+      </c>
+      <c r="W61" t="s">
+        <v>89</v>
+      </c>
+      <c r="X61" t="s">
+        <v>407</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA61">
+        <v>24</v>
+      </c>
+      <c r="AB61" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC61" t="s">
         <v>38</v>
       </c>
-      <c r="W61" t="s">
+      <c r="AD61" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF61" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG61" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH61" t="s">
         <v>92</v>
       </c>
-      <c r="X61" t="s">
-        <v>409</v>
-      </c>
-      <c r="Y61" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z61" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA61">
-        <v>20</v>
-      </c>
-      <c r="AB61" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC61" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD61" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF61" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG61" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH61" t="s">
-        <v>42</v>
-      </c>
       <c r="AI61" t="s">
-        <v>410</v>
-      </c>
-      <c r="AJ61" t="s">
-        <v>222</v>
+        <v>318</v>
       </c>
     </row>
     <row r="62" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>227</v>
+      </c>
+      <c r="B62" t="s">
+        <v>61</v>
+      </c>
+      <c r="D62" t="s">
+        <v>408</v>
+      </c>
+      <c r="E62" t="s">
+        <v>409</v>
+      </c>
+      <c r="F62" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G62">
+        <v>4</v>
+      </c>
+      <c r="H62" t="s">
         <v>71</v>
       </c>
-      <c r="B62" t="s">
-        <v>64</v>
-      </c>
-      <c r="D62" t="s">
-        <v>411</v>
-      </c>
-      <c r="E62" t="s">
-        <v>412</v>
-      </c>
-      <c r="F62" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G62">
-        <v>3</v>
-      </c>
-      <c r="H62" t="s">
-        <v>74</v>
-      </c>
       <c r="I62" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R62">
         <v>1</v>
@@ -6659,75 +6719,72 @@
         <v>13262</v>
       </c>
       <c r="T62" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W62" t="s">
-        <v>80</v>
+        <v>410</v>
       </c>
       <c r="X62" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Y62" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z62" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AA62">
         <v>24</v>
       </c>
       <c r="AB62" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AC62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AD62" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF62" t="s">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="AG62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH62" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AI62" t="s">
-        <v>414</v>
-      </c>
-      <c r="AJ62" t="s">
-        <v>81</v>
+        <v>413</v>
       </c>
     </row>
     <row r="63" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>227</v>
+      </c>
+      <c r="B63" t="s">
+        <v>61</v>
+      </c>
+      <c r="D63" t="s">
+        <v>414</v>
+      </c>
+      <c r="E63" t="s">
+        <v>415</v>
+      </c>
+      <c r="F63" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G63">
+        <v>5</v>
+      </c>
+      <c r="H63" t="s">
         <v>71</v>
       </c>
-      <c r="B63" t="s">
-        <v>64</v>
-      </c>
-      <c r="D63" t="s">
-        <v>415</v>
-      </c>
-      <c r="E63" t="s">
-        <v>416</v>
-      </c>
-      <c r="F63" s="1">
-        <v>46266</v>
-      </c>
-      <c r="G63">
-        <v>4</v>
-      </c>
-      <c r="H63" t="s">
-        <v>74</v>
-      </c>
       <c r="I63" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="R63">
         <v>1</v>
@@ -6736,75 +6793,75 @@
         <v>13262</v>
       </c>
       <c r="T63" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V63" t="s">
+        <v>37</v>
+      </c>
+      <c r="W63" t="s">
+        <v>170</v>
+      </c>
+      <c r="X63" t="s">
+        <v>416</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA63">
+        <v>24</v>
+      </c>
+      <c r="AB63" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC63" t="s">
         <v>38</v>
       </c>
-      <c r="W63" t="s">
-        <v>373</v>
-      </c>
-      <c r="X63" t="s">
+      <c r="AD63" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF63" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG63" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH63" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI63" t="s">
         <v>417</v>
       </c>
-      <c r="Y63" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z63" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA63">
-        <v>20</v>
-      </c>
-      <c r="AB63" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC63" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD63" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF63" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG63" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH63" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI63" t="s">
-        <v>418</v>
-      </c>
       <c r="AJ63" t="s">
-        <v>419</v>
+        <v>135</v>
       </c>
     </row>
     <row r="64" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D64" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E64" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F64" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="G64">
         <v>5</v>
       </c>
       <c r="H64" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="I64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R64">
         <v>1</v>
@@ -6813,49 +6870,656 @@
         <v>13262</v>
       </c>
       <c r="T64" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="V64" t="s">
+        <v>37</v>
+      </c>
+      <c r="W64" t="s">
+        <v>331</v>
+      </c>
+      <c r="X64" t="s">
+        <v>420</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA64">
+        <v>20</v>
+      </c>
+      <c r="AB64" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC64" t="s">
         <v>38</v>
       </c>
-      <c r="W64" t="s">
-        <v>101</v>
-      </c>
-      <c r="X64" t="s">
+      <c r="AD64" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF64" t="s">
+        <v>105</v>
+      </c>
+      <c r="AG64" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH64" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI64" t="s">
+        <v>421</v>
+      </c>
+      <c r="AJ64" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>227</v>
+      </c>
+      <c r="B65" t="s">
+        <v>61</v>
+      </c>
+      <c r="D65" t="s">
         <v>422</v>
       </c>
-      <c r="Y64" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z64" t="s">
+      <c r="E65" t="s">
+        <v>423</v>
+      </c>
+      <c r="F65" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G65">
+        <v>7</v>
+      </c>
+      <c r="H65" t="s">
+        <v>51</v>
+      </c>
+      <c r="I65" t="s">
+        <v>44</v>
+      </c>
+      <c r="R65">
+        <v>1</v>
+      </c>
+      <c r="S65">
+        <v>13262</v>
+      </c>
+      <c r="T65" t="s">
+        <v>68</v>
+      </c>
+      <c r="V65" t="s">
+        <v>37</v>
+      </c>
+      <c r="W65" t="s">
+        <v>106</v>
+      </c>
+      <c r="X65" t="s">
+        <v>424</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA65">
+        <v>20</v>
+      </c>
+      <c r="AB65" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC65" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD65" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF65" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG65" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH65" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI65" t="s">
+        <v>425</v>
+      </c>
+      <c r="AJ65" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>227</v>
+      </c>
+      <c r="B66" t="s">
+        <v>61</v>
+      </c>
+      <c r="D66" t="s">
+        <v>427</v>
+      </c>
+      <c r="E66" t="s">
+        <v>428</v>
+      </c>
+      <c r="F66" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G66">
+        <v>8</v>
+      </c>
+      <c r="H66" t="s">
+        <v>48</v>
+      </c>
+      <c r="I66" t="s">
+        <v>52</v>
+      </c>
+      <c r="R66">
+        <v>1</v>
+      </c>
+      <c r="S66">
+        <v>13262</v>
+      </c>
+      <c r="T66" t="s">
+        <v>68</v>
+      </c>
+      <c r="V66" t="s">
+        <v>37</v>
+      </c>
+      <c r="W66" t="s">
+        <v>99</v>
+      </c>
+      <c r="X66" t="s">
+        <v>429</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA66">
+        <v>20</v>
+      </c>
+      <c r="AB66" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC66" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF66" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG66" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH66" t="s">
         <v>47</v>
       </c>
-      <c r="AA64">
+      <c r="AI66" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>227</v>
+      </c>
+      <c r="B67" t="s">
+        <v>61</v>
+      </c>
+      <c r="D67" t="s">
+        <v>431</v>
+      </c>
+      <c r="E67" t="s">
+        <v>432</v>
+      </c>
+      <c r="F67" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G67">
+        <v>8</v>
+      </c>
+      <c r="H67" t="s">
+        <v>71</v>
+      </c>
+      <c r="I67" t="s">
+        <v>52</v>
+      </c>
+      <c r="R67">
+        <v>1</v>
+      </c>
+      <c r="S67">
+        <v>13262</v>
+      </c>
+      <c r="T67" t="s">
+        <v>68</v>
+      </c>
+      <c r="V67" t="s">
+        <v>37</v>
+      </c>
+      <c r="W67" t="s">
+        <v>433</v>
+      </c>
+      <c r="X67" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA67">
         <v>24</v>
       </c>
-      <c r="AB64" t="s">
+      <c r="AB67" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC67" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD67" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF67" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG67" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH67" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI67" t="s">
+        <v>435</v>
+      </c>
+      <c r="AJ67" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>227</v>
+      </c>
+      <c r="B68" t="s">
+        <v>61</v>
+      </c>
+      <c r="D68" t="s">
+        <v>436</v>
+      </c>
+      <c r="E68" t="s">
+        <v>437</v>
+      </c>
+      <c r="F68" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G68">
+        <v>8</v>
+      </c>
+      <c r="H68" t="s">
+        <v>262</v>
+      </c>
+      <c r="I68" t="s">
+        <v>52</v>
+      </c>
+      <c r="R68">
+        <v>1</v>
+      </c>
+      <c r="S68">
+        <v>13262</v>
+      </c>
+      <c r="T68" t="s">
         <v>68</v>
       </c>
-      <c r="AC64" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD64" t="s">
+      <c r="V68" t="s">
+        <v>37</v>
+      </c>
+      <c r="W68" t="s">
+        <v>285</v>
+      </c>
+      <c r="X68" t="s">
+        <v>438</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA68">
+        <v>24</v>
+      </c>
+      <c r="AB68" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC68" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD68" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF68" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG68" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH68" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI68" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>227</v>
+      </c>
+      <c r="B69" t="s">
+        <v>62</v>
+      </c>
+      <c r="D69" t="s">
+        <v>440</v>
+      </c>
+      <c r="E69" t="s">
+        <v>441</v>
+      </c>
+      <c r="F69" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G69">
+        <v>2</v>
+      </c>
+      <c r="H69" t="s">
         <v>48</v>
       </c>
-      <c r="AF64" t="s">
-        <v>423</v>
-      </c>
-      <c r="AG64" t="s">
+      <c r="I69" t="s">
+        <v>44</v>
+      </c>
+      <c r="R69">
+        <v>1</v>
+      </c>
+      <c r="S69">
+        <v>13262</v>
+      </c>
+      <c r="T69" t="s">
+        <v>68</v>
+      </c>
+      <c r="V69" t="s">
+        <v>37</v>
+      </c>
+      <c r="W69" t="s">
+        <v>99</v>
+      </c>
+      <c r="X69" t="s">
+        <v>442</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA69">
+        <v>24</v>
+      </c>
+      <c r="AB69" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC69" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD69" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF69" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG69" t="s">
+        <v>42</v>
+      </c>
+      <c r="AH69" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI69" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="70" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>227</v>
+      </c>
+      <c r="B70" t="s">
+        <v>62</v>
+      </c>
+      <c r="D70" t="s">
+        <v>444</v>
+      </c>
+      <c r="E70" t="s">
+        <v>445</v>
+      </c>
+      <c r="F70" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G70">
+        <v>3</v>
+      </c>
+      <c r="H70" t="s">
+        <v>71</v>
+      </c>
+      <c r="I70" t="s">
+        <v>53</v>
+      </c>
+      <c r="R70">
+        <v>1</v>
+      </c>
+      <c r="S70">
+        <v>13262</v>
+      </c>
+      <c r="T70" t="s">
+        <v>68</v>
+      </c>
+      <c r="V70" t="s">
+        <v>37</v>
+      </c>
+      <c r="W70" t="s">
+        <v>175</v>
+      </c>
+      <c r="X70" t="s">
+        <v>446</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA70">
+        <v>24</v>
+      </c>
+      <c r="AB70" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC70" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF70" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG70" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH70" t="s">
         <v>41</v>
       </c>
-      <c r="AH64" t="s">
+      <c r="AI70" t="s">
+        <v>302</v>
+      </c>
+      <c r="AJ70" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="71" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>227</v>
+      </c>
+      <c r="B71" t="s">
+        <v>62</v>
+      </c>
+      <c r="D71" t="s">
+        <v>448</v>
+      </c>
+      <c r="E71" t="s">
+        <v>449</v>
+      </c>
+      <c r="F71" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G71">
+        <v>3</v>
+      </c>
+      <c r="H71" t="s">
+        <v>192</v>
+      </c>
+      <c r="I71" t="s">
+        <v>52</v>
+      </c>
+      <c r="R71">
+        <v>1</v>
+      </c>
+      <c r="S71">
+        <v>13262</v>
+      </c>
+      <c r="T71" t="s">
+        <v>68</v>
+      </c>
+      <c r="V71" t="s">
+        <v>37</v>
+      </c>
+      <c r="W71" t="s">
+        <v>193</v>
+      </c>
+      <c r="X71" t="s">
+        <v>450</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA71">
+        <v>20</v>
+      </c>
+      <c r="AB71" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC71" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD71" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF71" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG71" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH71" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI71" t="s">
+        <v>451</v>
+      </c>
+      <c r="AJ71" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="72" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>227</v>
+      </c>
+      <c r="B72" t="s">
+        <v>62</v>
+      </c>
+      <c r="D72" t="s">
+        <v>109</v>
+      </c>
+      <c r="E72" t="s">
+        <v>452</v>
+      </c>
+      <c r="F72" s="1">
+        <v>46267</v>
+      </c>
+      <c r="G72">
+        <v>3</v>
+      </c>
+      <c r="H72" t="s">
         <v>51</v>
       </c>
-      <c r="AI64" t="s">
-        <v>87</v>
-      </c>
-      <c r="AJ64" t="s">
-        <v>406</v>
+      <c r="I72" t="s">
+        <v>44</v>
+      </c>
+      <c r="R72">
+        <v>1</v>
+      </c>
+      <c r="S72">
+        <v>13262</v>
+      </c>
+      <c r="T72" t="s">
+        <v>68</v>
+      </c>
+      <c r="V72" t="s">
+        <v>37</v>
+      </c>
+      <c r="W72" t="s">
+        <v>82</v>
+      </c>
+      <c r="X72" t="s">
+        <v>453</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA72">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC72" t="s">
+        <v>46</v>
+      </c>
+      <c r="AD72" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF72" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG72" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH72" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI72" t="s">
+        <v>454</v>
+      </c>
+      <c r="AJ72" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/tABLA PARA XML.xlsx
+++ b/tABLA PARA XML.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vivie\Repositorios de capturas y reportes\capturanotas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8E4A8E-45AC-475F-B82D-BE0EA9B04125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA37217E-7277-49A9-B0AA-532069C8BDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EC6A074E-FCBB-47BE-8A38-21B2F7C2A33F}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="387">
   <si>
     <t>Canal</t>
   </si>
@@ -262,24 +262,15 @@
     <t>Blanca Soriano</t>
   </si>
   <si>
-    <t>Salomón Hernández</t>
-  </si>
-  <si>
     <t>Octavio Jaimes</t>
   </si>
   <si>
-    <t>Alma Leticia Sánchez</t>
-  </si>
-  <si>
     <t>Cultura</t>
   </si>
   <si>
     <t>Impresos locales</t>
   </si>
   <si>
-    <t>Ejecución de obras</t>
-  </si>
-  <si>
     <t>STPSH</t>
   </si>
   <si>
@@ -289,9 +280,6 @@
     <t>Portadas</t>
   </si>
   <si>
-    <t>Dulce Castillo</t>
-  </si>
-  <si>
     <t>Lorena Rosas</t>
   </si>
   <si>
@@ -304,24 +292,12 @@
     <t>Contraloría</t>
   </si>
   <si>
-    <t>Gobernador</t>
-  </si>
-  <si>
     <t>Gusano barrenador</t>
   </si>
   <si>
-    <t>Generación de empleos</t>
-  </si>
-  <si>
-    <t>Sedeco</t>
-  </si>
-  <si>
     <t>Saderh</t>
   </si>
   <si>
-    <t>Alejandro Reyes</t>
-  </si>
-  <si>
     <t>Sipdus, Gobernador</t>
   </si>
   <si>
@@ -331,832 +307,907 @@
     <t>Impresiones locales</t>
   </si>
   <si>
-    <t>Gobernador, Sipdus</t>
-  </si>
-  <si>
     <t>Segobh</t>
   </si>
   <si>
-    <t>Mineral de la Reforma</t>
-  </si>
-  <si>
-    <t>Alerta Meteorológica</t>
-  </si>
-  <si>
-    <t>Román Bernal Díaz</t>
-  </si>
-  <si>
-    <t>Donación De Órganos</t>
-  </si>
-  <si>
     <t>Maximiliano Pérez</t>
   </si>
   <si>
     <t>Adela Garmez</t>
   </si>
   <si>
-    <t>Robo de hidrocarburo</t>
-  </si>
-  <si>
     <t>Tizayuca</t>
   </si>
   <si>
-    <t>Julio Menchaca</t>
-  </si>
-  <si>
-    <t>Sipdus, Gobernador, Presidencia</t>
-  </si>
-  <si>
-    <t>Víctor Valera</t>
-  </si>
-  <si>
     <t>Personas desaparecidas</t>
   </si>
   <si>
-    <t>Segobh, Ayuntamientos</t>
-  </si>
-  <si>
-    <t>SSPH, PGJEH</t>
-  </si>
-  <si>
     <t>Erick Perales</t>
   </si>
   <si>
-    <t>Natividad Castrejón</t>
-  </si>
-  <si>
-    <t>Bienestar</t>
-  </si>
-  <si>
     <t>Martha Sáenz</t>
   </si>
   <si>
-    <t>SE ANALIZA SEGUNDA RUTA DEL TRANSPORTE METROPOLITANO: JMS</t>
-  </si>
-  <si>
-    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, aseguró que se analizará ejecutar el proyecto de la segunda ruta troncal del Sistema de Transporte Metropolitano, antes llamado Tuzobús, en la que se incluya ofrecer el servicio en Mineral de la Reforma. Sin embargo, explicó que, por lo pronto, se buscará rehabilitar todas las estaciones de la actual línea troncal y, posteriormente, definir si se amplía el servicio. Por lo pronto, es consolidar, con una inversión aproximada de los 100 millones, el estar rehabilitando las estaciones.</t>
-  </si>
-  <si>
-    <t>Ampliación Tuzobús</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar anunció que se analizará una segunda ruta troncal del Tuzobús para Mineral de la Reforma, priorizando la rehabilitación de las estaciones actuales con una inversión de 100 mdp.</t>
-  </si>
-  <si>
-    <t>Semot, Gobernador, Planeación</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Miguel Ángel Tello Vargas</t>
-  </si>
-  <si>
-    <t>INVERTIRÁN MÁS DE SEIS MIL MDP EN TRES OBRAS</t>
-  </si>
-  <si>
-    <t>El titular de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (Sipdus), Alejandro Sánchez García, dio a conocer los detalles de tres nuevas obras que ejecutará el gobierno estatal, con una inversión superior a los seis mil millones de pesos, mismas que comenzarán antes de concluir el presente año. Los proyectos incluyen la ampliación a ocho carriles de la autopista Pachuca-México, el encauzamiento del Río de las Avenidas y el eje transversal Actopan-Atotonilco.</t>
-  </si>
-  <si>
-    <t>El titular de Sipdus, Alejandro Sánchez García, detalló un paquete de infraestructura estatal por más de 6 mil mdp para la ampliación vial de Pachuca-México, Río de las Avenidas y Actopan-Atotonilco.</t>
-  </si>
-  <si>
-    <t>Carmen Hernández</t>
-  </si>
-  <si>
-    <t>Alejandro Sánchez García</t>
-  </si>
-  <si>
-    <t>SE HAN EROGADO 20 MDP PARA FESTEJOS DEL 15 DE SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>La inversión para las actividades patrias, así como para la contratación de Carlos Rivera y Los Cardenales de Nuevo León, quienes se presentarán la noche del 15 de septiembre en Plaza Juárez, en Pachuca, tuvo un costo aproximado de 20 millones de pesos, reveló el titular de la Oficialía Mayor, Edgar Orlando Ángeles Pérez. De acuerdo con la licitación EA-913003989-N0454-2026, la Oficialía Mayor contrató el servicio para el espectáculo, que incluye audio, iluminación y montaje.</t>
-  </si>
-  <si>
     <t>Fiestas Patrias</t>
   </si>
   <si>
-    <t>El oficial mayor, Edgar Orlando Ángeles, informó que la erogación para los festejos patrios y la cartelera musical del 15 de septiembre en Plaza Juárez asciende a unos 20 mdp.</t>
-  </si>
-  <si>
     <t>Oficialía Mayor</t>
   </si>
   <si>
     <t>Oficialía Mayor, Gobernador</t>
   </si>
   <si>
-    <t>Edgar Orlando Ángeles Pérez, Carlos Rivera, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>ATRIBUYEN INFORMALIDAD A LAS INVERSIONES Y OBRAS</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar atribuyó que la tasa del 72 por ciento de informalidad en el empleo en Hidalgo —difundida en la última Encuesta Nacional de Ocupación y Empleo (ENOE) del Instituto Nacional de Inegi— se debe al incremento de inversiones y obras de tipo federal y estatal, que también aumentan la generación de empleos formales y, en consecuencia, derivan en servicios informales como el comercio. Puso de ejemplo el tren AIFA-Pachuca, que generó 5 mil empleos formales, disparando indirectamente el comercio informal de comida y servicios en sus alrededores.</t>
-  </si>
-  <si>
-    <t>Informalidad laboral</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar atribuyó el índice de 72% de empleo informal al repunte de grandes proyectos de infraestructura (como el tren AIFA) que dinamizan el comercio indirecto.</t>
-  </si>
-  <si>
-    <t>Gobernador, Otros</t>
-  </si>
-  <si>
-    <t>FAUNA SILVESTRE SIN CASOS DE GUSANO BARRENADOR: SADERH</t>
-  </si>
-  <si>
-    <t>El titular de la Secretaría de Agricultura y Desarrollo Rural de Hidalgo (Saderh), Napoleón González Pérez, negó que, a la fecha, exista algún reporte sobre fauna silvestre infectada por gusano barrenador en el estado. Sin embargo, el funcionario no descartó que pudiera existir algún caso aislado, debido a la naturaleza de la plaga, 'pues anda en los lugares abiertos'. El secretario reiteró que el tema del gusano barrenador es atendido a través del Comité de Sanidad, coordinado por Senasica.</t>
-  </si>
-  <si>
-    <t>El secretario de Agricultura estatal, Napoleón González, descartó que existan casos confirmados de gusano barrenador en la fauna silvestre, coordinando acciones preventivas con Senasica.</t>
-  </si>
-  <si>
-    <t>Saderh, Semarnath, Presidencia</t>
-  </si>
-  <si>
-    <t>Napoleón González Pérez, Mónica Mixtega</t>
-  </si>
-  <si>
-    <t>TERMINA EL PARO DE LA UTHH; HOY RETOMAN CLASES</t>
-  </si>
-  <si>
-    <t>Luego de siete días de huelga y suspensión de actividades académicas, la Universidad Tecnológica de la Huasteca Hidalguense (UTHH) y el Sindicato Único de Trabajadores de las Universidades Tecnológicas del Estado de Hidalgo (SUTUTEH) alcanzaron acuerdos mediante el diálogo y las negociaciones, con lo que se concretó la firma de las Condiciones Generales de Trabajo. Con ello, alrededor de 3 mil 300 estudiantes reanudarán actividades.</t>
-  </si>
-  <si>
-    <t>La rectoría de la UTHH de Huejutla y el sindicato SUTUTEH acordaron la firma contractual, concluyendo el paro de labores de una semana para reactivar clases para 3,300 alumnos.</t>
-  </si>
-  <si>
-    <t>USUARIOS DENUNCIARON ABUSOS Y MANIOBRAS PELIGROSAS DE TAXISTAS EN HUEJUTLA DE REYES</t>
-  </si>
-  <si>
-    <t>Usuarios del servicio de transporte público en modal de taxi en Huejutla denunciaron irregularidades y conductas de riesgo por parte de algunos trabajadores del volante, entre ellas la falta de exhibición de tarifas y la circulación en sentido contrario, situación que, además de infringir las disposiciones de tránsito, puede poner en peligro a pasajeros y automovilistas.</t>
-  </si>
-  <si>
-    <t>Abusos taxistas</t>
-  </si>
-  <si>
-    <t>Pasajeros de Huejutla externaron quejas por cobros abusivos, falta de tarifas exhibidas en las unidades y maniobras viales temerarias en sentido contrario de los taxistas.</t>
-  </si>
-  <si>
     <t>Semot, Ayuntamiento</t>
   </si>
   <si>
-    <t>Roberto Ramírez Hernández, Rosario Hernández Hernández</t>
-  </si>
-  <si>
-    <t>AUMENTAN DELITOS CONTRA LA LIBERTAD Y LA SEGURIDAD SEXUAL EN JUÁREZ HIDALGO</t>
-  </si>
-  <si>
-    <t>Durante los primeros siete meses de 2026, disminuyeron un 60 por ciento las denuncias por la suma de todos los tipos penales en Juárez Hidalgo, en comparación con el mismo periodo del año pasado; sin embargo, los delitos contra la libertad y seguridad sexual presentaron un aumento en el plazo mencionado. La incidencia de los ilícitos de abuso sexual y violación a la intimidad sexual pasó de cero en 2025 a dos hechos.</t>
-  </si>
-  <si>
-    <t>Juárez Hidalgo</t>
-  </si>
-  <si>
-    <t>Incidencia Delictiva</t>
-  </si>
-  <si>
-    <t>El SESNSP reportó que las denuncias generales cayeron 60% en Juárez Hidalgo con solo 9 carpetas de investigación, aunque los delitos de agresión sexual subieron de cero a dos casos.</t>
-  </si>
-  <si>
     <t>PGJEH</t>
   </si>
   <si>
-    <t>PGJEH, Otros</t>
-  </si>
-  <si>
-    <t>Prevén concluir en 2028 las obras de movilidad</t>
-  </si>
-  <si>
-    <t>Alejandro Sánchez García, titular de la Secretaría de Infraestructura Pública y Desarrollo Udano Sostenible (Sipdus), detalló tres obras anunciadas por el gobernador Julio Menchaca para mejorar la movilidad en la zona metropolitana de Pachuca. Los proyectos que atenderán vialidades, encauzamientos y accesos ante el crecimiento previsto en la zona sur, iniciarán en octubre de 2026 y se prevé que concluyan en junio de 2028. Refirió que durante la primera etapa de la construcción del eje transversal Actopan-Atotonilco El Grande, se dará mantenimiento y bacheo de la carretera en los tramos: La Estancia-La Magdalena, en Actopan; Sanctorum-Santa María Amajac, en Atotonilco, y se trabajará en la liberación de derecho de vía de 28 propietarios en el primer municipio y 24 en el segundo. Estas acciones iniciarán en octubre de 2026 y durarán seis meses.</t>
-  </si>
-  <si>
-    <t>El titular de la Sipdus, Alejandro Sánchez García, detalló el cronograma de ejecución de los tres megaproyectos viales anunciados por el gobernador Julio Menchaca para Pachuca y su zona metropolitana, proyectando concluir en junio de 2028.</t>
-  </si>
-  <si>
     <t>Alejandro Sánchez García, Julio Menchaca Salazar</t>
   </si>
   <si>
-    <t>Vigilan pirotecnia de cara a fiestas patrias</t>
-  </si>
-  <si>
-    <t>A pocos días de la celebración del 15 de septiembre, autoridades de seguridad y protección civil mantienen acciones de vigilancia para prevenir el traslado, almacenamiento y venta ilegal de material pirotécnico en Hidalgo; sin embargo, hasta el momento no se ha dado a conocer oficialmente el operativo específico que implementarán la Secretaría de Seguridad Pública de Hidalgo (SSPH), la Procuraduría General de Justicia del Estado de Hidalgo (PGJEH), Guardia Nacional y Ejército Mexicano para estas fechas. Durante los festejos patrios de 2025, la SSPH desplegó un operativo especial en los 84 municipios, con más de de cinco mil elementos.</t>
-  </si>
-  <si>
-    <t>Pirotecnia</t>
-  </si>
-  <si>
-    <t>Las autoridades locales coordinan tareas de prevención contra la venta y acopio clandestino de pirotecnia para las fiestas patrias, basándose en la rigurosa Ley Federal de Armas de Fuego y Explosivos.</t>
-  </si>
-  <si>
-    <t>SSPH, PGJEH, Presidencia</t>
-  </si>
-  <si>
-    <t>Monumento a Niños Héroes, abandonado</t>
-  </si>
-  <si>
-    <t>El Monumento a los Niños Héroes, ubicado en el jardín de los Niños Héroes, en la colonia Centro de Pachuca, luce vandalizado con pintas de grafiti a tan solo unos días del 13 de septiembre, fecha en que se conmemora la Batalla del Castillo de Chapultepec y la gesta de los cadetes del Colegio Militar. La base de cantera y las placas alusivas a Juan Escutia, Agustín Melgar, Fernando Montes de Oca, Vicente Suárez, Francisco Márquez y Juan de la Barrera tienen meses con pintas, al parecer, con aerosol color negro y rojo, con leyendas ilegibles que cubren parte de los nombres y del pedestal.</t>
-  </si>
-  <si>
-    <t>Vandalismo</t>
-  </si>
-  <si>
-    <t>Vecinos de la col. Centro de Pachuca criticaron el abandono y vandalismo que muestra el Monumento a los Niños Héroes en vísperas de su conmemoración nacional, pidiendo acciones prontas de rescate urbano.</t>
-  </si>
-  <si>
-    <t>Cultura, Ayuntamientos, Presidencia</t>
-  </si>
-  <si>
-    <t>Juan Manuel Llaguno, George Santayana</t>
-  </si>
-  <si>
-    <t>Refuerzan los operativos contra la delincuencia</t>
-  </si>
-  <si>
-    <t>El gobernador de Hidalgo, Julio Menchaca Salazar, indicó que se siguen fortaleciendo las acciones para inhibir el robo de combustible, el narcomenudeo y el robo a transporte de carga. Las denuncias ciudadanas y los operativos coordinados del Gabinete de Seguridad de Hidalgo derivaron en la detención de 31 personas señaladas por la comisión de diversos delitos, informó el mandatario en su reunión semanal. En ella detalló que en la última semana fueron arrestados 15 hombres y tres mujeres en nueve municipios, quienes presuntamente tenían en su posesión tres mil 952 dosis de distintos estupefacientes.</t>
-  </si>
-  <si>
-    <t>Combate a la delincuencia</t>
-  </si>
-  <si>
-    <t>Operativos del Gabinete de Seguridad en Hidalgo permitieron detener a 31 generadores de violencia, decomisar dosis de droga y recuperar vehículos de carga robados con acero en la entidad.</t>
-  </si>
-  <si>
-    <t>SSPH, Gobernador, Presidencia</t>
-  </si>
-  <si>
-    <t>Tres proyectos viales para cerrar el sexenio requerirán 7 mil mdp</t>
-  </si>
-  <si>
-    <t>En los dos últimos años del actual gobierno estatal se trabajarán tres proyectos carreteros que implicarán una inversión superior a los 7 mil millones de pesos y cuyos trabajos iniciarán en los últimos meses del año en curso. El secretario de Infraestructura Pública y Desarrollo Urbano Sostenible (SIPDUS), Alejandro Sánchez García, informó que el primero será el Eje transversal Actopan-Atotonilco el Grande, cuyos trabajos empezaron desde hace 10 años por la Secretaría de Infraestructura, Comunicaciones y Transportes (SICT), pero no se le ha invertido nada desde entonces. El gobierno del estado destinará 992 millones de pesos para intervenir el tramo que conecta la autopista México-Laredo y México-Tampico. El segundo proyecto corresponderá a la construcción de vía y encauzamiento Río de las Avenidas, con una inversión superior a los 2 mil 200 millones de pesos. Por último, la tercera obra corresponderá a la modernización de la carretera Pachuca-México, con una inversión superior de 3 mil 259 millones de pesos.</t>
-  </si>
-  <si>
-    <t>El secretario de Sipdus, Alejandro Sánchez García, detalló un paquete de tres obras de infraestructura vial por más de 7 mil mdp, las cuales iniciarán a finales de 2026 y contemplan la ampliación de la México-Pachuca, el encauzamiento del Río de las Avenidas y el eje Actopan-Atotonilco.</t>
-  </si>
-  <si>
-    <t>Superan el billón de pesos los programas de Bienestar</t>
-  </si>
-  <si>
-    <t>Los programas de Bienestar llegan este año a más de 42 millones de mexicanos, con una inversión social anual superior al billón de pesos, informó la secretaria de Bienestar, Leticia Ramírez. Detalló que hay 18 programas de Bienestar y destacó que más de 13 millones de adultos mayores reciben 6 mil 400 pesos bimestrales, mientras casi 3 millones de mujeres de 60 a 64 años cuentan con la Pensión Mujeres Bienestar. La presidenta Claudia Sheinbaum destacó que hay 29 mil servidores de la nación que participan en tareas de registro, atención y organización.</t>
-  </si>
-  <si>
-    <t>CDMX</t>
-  </si>
-  <si>
-    <t>Programas Del Bienestar</t>
-  </si>
-  <si>
-    <t>La secretaria de Bienestar, Leticia Ramírez, informó que los 18 programas sociales federales benefician a 42 millones de mexicanos con una inversión superior al billón de pesos anuales.</t>
-  </si>
-  <si>
-    <t>Mauricio Bautista</t>
-  </si>
-  <si>
-    <t>Bienestar, Presidencia</t>
-  </si>
-  <si>
-    <t>Leticia Ramírez, Claudia Sheinbaum Pardo</t>
-  </si>
-  <si>
-    <t>Sheinbaum dará su informe en Pachuca el domingo: gobernador</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar informó que la presidenta de México, Claudia Sheinbaum Pardo, visitará Pachuca el próximo 13 de septiembre, como parte de su gira de trabajo por las 32 entidades del país para dar a conocer su segundo informe de gobierno. Precisó que, hasta el momento, el gobierno federal les notificó que la mandataria se presentará a las 13:45 horas en las instalaciones de la feria. Respecto a la entrega de apoyos a familias que perdieron sus viviendas derivado de las lluvias por la vaguada monzónica, adelantó que se otorgará un apoyo económico a mil 185 familias, lo que ascendería a un total de 874 millones de pesos.</t>
-  </si>
-  <si>
-    <t>Visita Sheinbaum</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca anunció la visita de la presidenta Claudia Sheinbaum a Pachuca este domingo en el recinto ferial, detallando la erogación de 874 mdp para apoyar a 1,185 familias damnificadas por tormentas.</t>
-  </si>
-  <si>
-    <t>Gobernador, Presidencia, Bienestar</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Claudia Sheinbaum Pardo, Adán Augusto López, Cuauhtémoc Ochoa, Simey Olvera Bautista</t>
-  </si>
-  <si>
-    <t>Presupuesto estatal podría sumar 76 mil mdp para 2027: Ramírez</t>
-  </si>
-  <si>
-    <t>El gobierno de Hidalgo proyecta un presupuesto estatal cercano a los 76 mil millones de pesos para el ejercicio fiscal 2027, sujeto a las proyecciones macroeconómicas y de ingresos que establezca la Federación, informó la secretaria de Hacienda, María Esther Ramírez Vargas. De los primeros cuatro años de la administración, Ramírez Vargas destacó que el Presupuesto de Egresos creció un 37% en comparación con 2021, al pasar de 54 mil 892 millones de pesos a más de 75 mil 343 millones para el cierre de 2026. Uno de los rubros con mayor dinamismo fue la recaudación local: los ingresos propios repuntaron 96% —de 4 mil 916 millones a más de 9 mil 636 millones de pesos—, elevando su participación dentro del presupuesto total del 9 al 13%. En materia de pasivos, la Secretaría de Hacienda reportó una reducción de 42% en la deuda pública heredada, cuyo saldo bajó de 3 mil 906 millones de pesos en septiembre de 2022 a 2 mil 274 millones en agosto de 2026.</t>
-  </si>
-  <si>
-    <t>Presupuesto De Egresos</t>
-  </si>
-  <si>
-    <t>La secretaria de Hacienda, María Esther Ramírez, proyectó un paquete de egresos de 76 mil mdp para 2027, destacando la reducción del 42% de la deuda pública estatal heredada y un aumento de 96% en recaudación propia.</t>
-  </si>
-  <si>
     <t>Hacienda</t>
   </si>
   <si>
-    <t>Hacienda, Congreso, Gobernador</t>
-  </si>
-  <si>
-    <t>María Esther Ramírez Vargas, Julio Menchaca</t>
-  </si>
-  <si>
-    <t>Casi 40 mil empleos formales en 4 años de Julio Menchaca</t>
-  </si>
-  <si>
-    <t>En los primeros cuatro años de la actual administración, Hidalgo ha registrado la creación de más de 39 mil 545 empleos formales, impulsados por un incremento en la actividad económica y la atracción de inversiones, informaron autoridades estatales. El secretario del Trabajo, Oscar Javier González Hernández, detalló que cerca de 20 mil de estas plazas se han colocado mediante el Servicio Nacional de Empleo (SNE). Destacó el alcance de los programas de movilidad laboral, los cuales han permitido que unos 4 mil 500 hidalguenses accedan a puestos legales en el extranjero —en países como Alemania, Estados Unidos, España y Canadá—. Asimismo, a través del esquema Primero el Pueblo, han destinado 50 millones de pesos para 7 mil 100 incentivos orientados al autoempleo.</t>
-  </si>
-  <si>
-    <t>La STPSH reportó que Hidalgo acumula 39,545 empleos formales creados en 4 años, destacando la colocación de 4,500 hidalguenses en el extranjero y apoyos al autoempleo por 50 mdp.</t>
-  </si>
-  <si>
-    <t>STPSH, SNE, Gobernador</t>
-  </si>
-  <si>
-    <t>Oscar Javier González Hernández, Julio Menchaca</t>
-  </si>
-  <si>
-    <t>Hidalgo: 101 casos de gusano barrenador en 30 municipios</t>
-  </si>
-  <si>
-    <t>Hidalgo acumula 101 casos activos de gusano barrenador distribuidos en más de 30 demarcaciones, de acuerdo con el reporte oficial del Servicio Nacional de Sanidad, Inocuidad y Calidad Agroalimentaria (Senasica), con corte al 4 de septiembre de 2026. La incidencia se concentra principalmente en la región de Nopala de Villagrán, que encabeza la lista con 16 casos; Tecozautla, con siete; Huejutla de Reyes y San Bartolo Tutotepec, con seis cada uno; e Ixmiquilpan, con cinco. El titular de la SADERH, Napoleón González Pérez, aclaró que no se cuenta con registros oficiales de este tipo en fauna silvestre en la entidad.</t>
-  </si>
-  <si>
-    <t>El Senasica y la Saderh confirmaron un acumulado de 101 casos de gusano barrenador en ganado de la entidad, descartando que el parásito esté presente en especies silvestres locales.</t>
-  </si>
-  <si>
-    <t>Saderh, Presidencia, Semarnath, SSH, Bienestar</t>
-  </si>
-  <si>
-    <t>Napoleón González Pérez</t>
-  </si>
-  <si>
-    <t>Intensifican operativo de búsqueda de familia en Tizayuca; van 11 días</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Ciudadana de Tizayuca informó que mantiene un despliegue operativo para dar seguimiento a las cuatro fichas de búsqueda emitidas por la Comisión de Búsqueda de Personas del Estado de Hidalgo, correspondientes a los integrantes de una familia reportada como desaparecida desde el pasado 27 de agosto en esta demarcación. De acuerdo con la dependencia, a partir del fin de semana pasado se intensificaron las labores para ubicar a la madre y tres hijos que permanecen extraviados. Desde el pasado 1 de septiembre se han realizado recorridos continuos en el sector El Pedregal, entrevistas con vecinos y la revisión de videograbaciones.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad local y la Comisión de Búsqueda intensificaron la búsqueda terrestre y el análisis de videovigilancia de Massiel Mendoza y sus tres hijos en el sector El Pedregal tras 11 días desaparecidos.</t>
-  </si>
-  <si>
-    <t>Massiel Mendoza</t>
-  </si>
-  <si>
-    <t>Gobierno destinará 20 mdp para los festejos del Grito</t>
-  </si>
-  <si>
-    <t>El gobierno estatal destinará más de 20 millones de pesos para los festejos patrios de este año, los cuales cubrirán el escenario y estructura que se utilizará para el evento protocolario del 15 de septiembre, así como la contratación del artista que se presentará después del Grito de Independencia (Carlos Rivera y Los Cardenales de Nuevo León). Así lo informó el titular de la Oficialía Mayor del estado, Orlando Ángeles Pérez. Se contempla un rider que incluye audio, iluminación, 200 metros cuadrados de pantalla LED y 23 arcos detectores de seguridad.</t>
-  </si>
-  <si>
-    <t>El oficial mayor, Orlando Ángeles, detalló que se destinarán 20 mdp para el montaje del escenario y cartelera artística del 15 de septiembre en Plaza Juárez, contratándose a la empresa Macrovisión Creaciones.</t>
-  </si>
-  <si>
-    <t>Orlando Ángeles Pérez, Carlos Rivera, Julio Menchaca</t>
-  </si>
-  <si>
-    <t>Destruyen un túnel de casi 9 metros en Santa Catarina</t>
-  </si>
-  <si>
-    <t>Un túnel de 8.90 metros de longitud que se dirigía desde una zona de locales comerciales hacia el área de ductos de Pemex fue destruido en Santa Catarina, municipio de Pachuca, informó el Gabinete de Seguridad de Hidalgo. La excavación tenía una altura aproximada de 2.40 metros y contaba con un acceso de apenas 80 por 80 centímetros. De acuerdo con las autoridades, el túnel fue localizado antes de que consiguiera alcanzar el ducto.</t>
-  </si>
-  <si>
-    <t>Huachitúnel</t>
-  </si>
-  <si>
-    <t>Fuerzas de seguridad inhabilitaron un túnel de extracción ilegal de 9 metros de largo ubicado en Santa Catarina, Pachuca, el cual amenazaba las líneas operativas de Pemex en la zona urbana.</t>
-  </si>
-  <si>
-    <t>SSPH, Presidencia, Segobh</t>
-  </si>
-  <si>
-    <t>Implementa el C5i 4 mil cámaras en cuatro años</t>
-  </si>
-  <si>
-    <t>En los últimos cuatro años el Centro de Control, Comando, Comunicaciones, Cómputo, Coordinación e Inteligencia (C5i), de la Secretaría de Seguridad Pública, implementó 4 mil 500 nuevas cámaras. De acuerdo con el estado, en septiembre de 2022 se recibió al C5i con 8 mil 500 cámaras de videovigilancia; para septiembre de 2026, informó la administración estatal, se ampliaron a más de 13 mil. Mencionó que en un inicio las 8 mil 500 cámaras de seguridad tenían una cobertura de 10 municipios, y actualmente la red de seguridad se extendió a las 84 demarcaciones. El Centro de Control, Comando, Comunicaciones, Cómputo, Coordinación e Inteligencia tiene un incremento de recursos para este año de 118 millones 917 mil 792 pesos en comparación con el presupuesto que le fue destinado en 2025. Emergencias y denuncias: De acuerdo con el Presupuesto de Egresos del estado para el ejercicio fiscal 2026, al C5i se le etiquetaron 702 millones 718 mil 478 pesos; el documento señala el fortalecimiento al sistema de videovigilancia estatal.</t>
-  </si>
-  <si>
-    <t>Videovigilancia</t>
-  </si>
-  <si>
-    <t>La Secretaría de Seguridad Pública de Hidalgo amplió la red de videovigilancia del C5i a más de 13 mil cámaras con cobertura en los 84 municipios, operando con un presupuesto de 702 millones de pesos en 2026.</t>
-  </si>
-  <si>
-    <t>Plataforma Hidalgo permite identificar 11 cuerpos en 3 años</t>
-  </si>
-  <si>
-    <t>A tres años y dos meses de su implementación, a través de la plataforma Identificación y Búsqueda Hidalgo de la Procuraduría General de Justicia, se han identificado 11 cuerpos resguardados en el Servicio Médico Forense (Semefo). Tan solo en agosto se identificaron tres cuerpos, uno de ellos era un hombre originario del Estado de México; el second es un cuerpo localizado en Villa de Tezontepec; y el tercero es un cuerpo del cual sus familiares se trasladaron desde Chiapas para su identificación. El 9 de julio de 2023 el gobierno de Hidalgo, a través de la Procuraduría General de Justicia del estado, puso en marcha la plataforma tecnológica con la finalidad de brindar accesibilidad a la consulta sobre información general de los restos humanos desconocidos y sin reclamar que se encuentran resguardados en el Servicio Médico Forense, ubicado en Pachuca. El objetivo primordial de la plataforma es que los restos humanos puedan ser localizados, identificados y entregados a sus familiares dignamente. La plataforma puede consultarse en el sitio web https://identificacionybusqueda.hidalgo.gob.mx/. Las personas que identifiquen a un familiar deben comunicarse y acudir al Servicio Médico Forense. La Plataforma Hidalgo ofrece un servicio de investigación pericial forense, enfocado en la identificación y búsqueda de personas desaparecidas de cuerpos no identificados.</t>
-  </si>
-  <si>
-    <t>La Procuraduría General de Justicia de Hidalgo reportó la identificación de 11 cuerpos resguardados en el Semefo gracias a la Plataforma Hidalgo de Identificación y Búsqueda, la cual facilita la localización y entrega digna de restos humanos.</t>
-  </si>
-  <si>
-    <t>Destruyen túnel con fines de ordeña en Pachuca</t>
-  </si>
-  <si>
-    <t>Personal de Petróleos Mexicanos (Pemex), la delegación de la Fiscalía General de la República (FGR) en Hidalgo y la Subsecretaría de Protección Civil y Gestión de Riesgos inhabilitaron y destruyeron este lunes un túnel que pretendía utilizarse para el robo de combustible en Pachuca. Este es el segundo túnel inhabilitado en la capital del estado. De acuerdo con el subsecretario de Protección Civil y Gestión de Riesgos, Román Bernal Díaz, de los 18 túneles identificados en territorio estatal para la extracción ilegal de hidrocarburos 13 ya han sido destruidos. Este segundo túnel se encontraba en una propiedad privada, en la colonia Santa Catarina; en dicho predio la Fiscalía General de Justicia colocó sellos con la leyenda 'Asegurado'. De igual manera, el subsecretario de Protección Civil y Gestión de Riesgos mencionó que el túnel fue detectado a principios de años, el cual no llegó hasta el ducto de Petróleos Mexicanos, puesto que se quedó a un metro y medio; sin embargo, puntualizó que sí representaba un riesgo para la ciudadanía, 'ya que estaba localizado a dos metros de profundidad por casi nueve metros de largo, un túnel de 80 por 80 centímetros en la abertura, entonces procedimos a su inhabilitación y destrucción con maquinaria a fin de mitigar el riesgo'. Mencionó que hasta el momento se han inhabilitado 13 túneles en coordinación con Petróleos Mexicanos y la delegación en el estado de la Fiscalía General de la República en los municipios de Atotonilco de Tula, Pachuca, Mineral de la Reforma, Cuautepec de Hinojosa, Tepeapulco y Nopala de Villagrán. Agregó que restan cinco túneles por inhabilitar en los municipios de Atitalaquia, Tepeji del Río, Tepeapulco y Tlaxcoapan, 'hay algunos que todavía tienen carpeta de investigación, estamos esperando el tema legal'.</t>
-  </si>
-  <si>
-    <t>La FGR, Pemex y Protección Civil de Hidalgo inhabilitaron un túnel clandestino de 9 metros de longitud en la colonia Santa Catarina de Pachuca, sumando 13 de los 18 túneles destruidos en la entidad.</t>
-  </si>
-  <si>
-    <t>DESTRUYEN 16 TÚNELES UTILIZADOS EN TRASIEGO DE HUACHICOL</t>
-  </si>
-  <si>
-    <t>De junio a agosto, el gobierno de Hidalgo, junto con la FGR, han desactivado perforaciones en 9 municipios. El último, en Pachuca, se dirigía de locales comerciales a la zona de ductos. El más reciente fue desactivado en Santa Catarina, Pachuca, donde la excavación se dirigía desde unos locales comerciales hacia la zona de ductos. Tenía una longitud de 8.90 metros, una altura aproximada de 2.40 metros y un acceso de 80 por 80 centímetros.</t>
-  </si>
-  <si>
-    <t>El gobierno de Hidalgo y la FGR destruyeron 16 túneles clandestinos de huachicol de junio a agosto, localizándose el más reciente en la colonia Santa Catarina de Pachuca.</t>
-  </si>
-  <si>
-    <t>Perfila Menchaca 2 últimos años con más obras</t>
-  </si>
-  <si>
-    <t>Pachuca.- El gobernador Julio Menchaca afirmó que su administración trabajará durante el resto del sexenio para seguir posicionando a Hidalgo en el contexto nacional, con obra pública y programas sociales.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca Salazar reafirmó que enfocará los dos últimos años de su gestión en consolidar obras públicas de infraestructura y programas de desarrollo social.</t>
-  </si>
-  <si>
-    <t>Descartan impacto a cebaderos por posible aumento a cerveza</t>
-  </si>
-  <si>
-    <t>Ante la posibilidad de un incremento al impuesto de la cerveza para el próximo año, el titular de la Secretaría de Agricultura y Desarrollo Rural de Hidalgo (Saderh), Napoleón González Pérez, descartó que los productores de cebada sufran afectaciones, ya que el aumento se plantea al producto final. Lo anterior, luego que la semana pasada, diputados del Congreso de la Unión plantearon incrementar el Impuesto Especial sobre Producción y Servicios (IEPS) aplicado a la cerveza, lo cual se traduce en un ajuste de entre 60 centavos y un peso por unidad.</t>
-  </si>
-  <si>
-    <t>Cebaderos</t>
-  </si>
-  <si>
-    <t>El titular de la Saderh, Napoleón González, aclaró que un incremento al IEPS de la cerveza no perjudicará a los cebaderos locales de Hidalgo, ya que el precio de la materia prima ya está pactado.</t>
-  </si>
-  <si>
-    <t>Saderh, Congreso</t>
-  </si>
-  <si>
-    <t>EN 3 MESES, 16 TÚNELES FUERON DESTRUIDOS</t>
-  </si>
-  <si>
-    <t>Eran usados para el trasiego de huachicol; el más reciente fue desactivado en Santa Catarina, Pachuca. De junio a agosto, el gobierno de Hidalgo destruyó 16 túneles en nueve municipios: Pachuca, Cuautepec, Tula, Mineral de la Reforma, Tepeapulco, Atitalaquia, Nopala, Tepeji del Río y Tlanalapa. El más reciente fue desactivado en Santa Catarina, Pachuca, donde la excavación se dirigía desde unos locales comerciales hacia la zona de ductos.</t>
-  </si>
-  <si>
-    <t>El Gobierno de Hidalgo y la FGR reportaron la inhabilitación de 16 túneles clandestinos de robo de hidrocarburo de junio a agosto en 9 municipios del estado.</t>
-  </si>
-  <si>
-    <t>Caen 31 presuntos generadores de violencia</t>
-  </si>
-  <si>
-    <t>Pachuca.- Las denuncias ciudadanas y los operativos coordinados del Gabinete de Seguridad de Hidalgo derivaron en la detención de 31 personas señaladas por la comisión de diversos delitos, informó el gobernador Julio Menchaca Salazar. En reunión semanal, se detalló que en la última semana fueron arrestados 15 hombres y tres mujeres en nueve municipios, quienes presuntamente tenían en su posesión 3 mil 952 dosis de distintos estupefacientes y tres básculas grameras.</t>
-  </si>
-  <si>
-    <t>El Gabinete de Seguridad de Hidalgo reportó la aprehensión de 31 presuntos delincuentes implicados en narcomenudeo, robo de carga y robo a transeúntes.</t>
-  </si>
-  <si>
-    <t>SSPH, Gobernador, C5i, Presidencia</t>
-  </si>
-  <si>
-    <t>Llama Cristina Rivera a combatir indolencia ante los feminicidios</t>
-  </si>
-  <si>
-    <t>Pachuca.- Pese a que existen avances en la atención de feminicidios en México, aún hay mucho por hacer, por una parte el Estado tiene una responsabilidad de proteger a todos y combatir la impunidad, y por otro, la sociedad civil no debe ser indolente ante casos de violencia, indicó la escritora mexicana Cristina Rivera Garza. Durante su visita a Hidalgo, la Premio Pulitzer 2024 comentó que la escritura es un espacio y una práctica de pensamiento crítico.</t>
-  </si>
-  <si>
-    <t>Feminicidio</t>
-  </si>
-  <si>
-    <t>De visita en Pachuca, la escritora Cristina Rivera Garza urgió a combatir la impunidad en feminicidios y llamó a la sociedad civil a abandonar la indolencia ante la violencia de género.</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>Cristina Rivera Garza</t>
-  </si>
-  <si>
-    <t>La barbarie</t>
-  </si>
-  <si>
-    <t>En la revisión de los temas coyunturales encuentro algunos que resultan de sumo interés. Sin embargo, no me es posible abducirme del muy lamentable acontecimiento que cimbró a la sociedad mexicana en días pasados. Me refiero al multihomicidio que ocurrió en el estado de México presuntamente por el adeudo de una cantidad de dinero. Lo que desató la irracionalidad de una persona para cometer una barbaridad.</t>
-  </si>
-  <si>
-    <t>Edomex</t>
-  </si>
-  <si>
-    <t>Multihomicidio</t>
-  </si>
-  <si>
-    <t>Columna de opinión de Enrique López que analiza el brutal multihomicidio en el Estado de México derivado de deudas de dinero, llamando a la aplicación rigurosa de la ley.</t>
-  </si>
-  <si>
-    <t>Enrique López</t>
-  </si>
-  <si>
-    <t>Inversión para el Grito asciende a $20 millones</t>
-  </si>
-  <si>
-    <t>Pachuca.– El gobierno de Hidalgo gastó, hasta el momento, 20 millones de pesos para los festejos del 15 de Septiembre en plaza Juárez, de Pachuca, informó Édgar Orlando Ángeles Pérez, titular de la Oficialía Mayor. El gasto corresponde a distintos conceptos para la celebración del Grito de Independencia, desde el montaje hasta la contratación de los artistas que participarán en el programa de la noche del 15 de septiembre. Entre ellos, Carlos Rivera y los Cardenales de Nuevo León.</t>
-  </si>
-  <si>
-    <t>El oficial mayor Édgar Orlando Ángeles informó que los festejos patrios del 15 de septiembre en Plaza Juárez de Pachuca representarán un gasto de 20 mdp, incluyendo la contratación artística.</t>
-  </si>
-  <si>
-    <t>La entidad recibió a 19 millones de visitantes en cuatro años: Turismo</t>
-  </si>
-  <si>
-    <t>En cuatro años, Hidalgo ha recibido a más de 19 millones de visitantes, luego de que la afluencia de turistas pasara de 4.8 millones de 2022 a cerca de 6.5 millones en 2026, de acuerdo con la Secretaría de Turismo estatal. Este crecimiento, detalló la dependencia, se ha traducido en una derrama económica superior a los 9 mil 500 millones de pesos, además de alcanzar una ocupación hotelera promedio de 55.8 por ciento.</t>
-  </si>
-  <si>
-    <t>Afluencia Turística</t>
-  </si>
-  <si>
-    <t>La Secretaría de Turismo estatal reportó que Hidalgo recibió a más de 19 millones de visitantes durante los últimos cuatro años, generando una derrama económica de 9,500 mdp.</t>
-  </si>
-  <si>
     <t>Turismo</t>
   </si>
   <si>
-    <t>Contraloría impulsa la fiscalización digitial</t>
-  </si>
-  <si>
-    <t>La Contraloría estatal fortalece la transformación digital de los procesos de fiscalización, con herramientas que permiten elevar la transparencia, robustecer el control de los recursos públicos y detectar posibles riesgos de manera oportuna. Durante los cuatro años del gobierno de Julio Menchaca Salazar, la Contraloría consolidó la interconexión con la Plataforma Digital Nacional (PDN), con más de 396 mil 284 declaraciones patrimoniales.</t>
-  </si>
-  <si>
-    <t>Transparencia</t>
-  </si>
-  <si>
-    <t>La Secretaría de Contraloría del estado reportó la interconexión con la Plataforma Digital Nacional mediante más de 396 mil declaraciones patrimoniales bajo la plataforma Declara Hidalgo.</t>
-  </si>
-  <si>
-    <t>La STPSH realizó inspecciones a 5 mil 450 centros de empleo</t>
-  </si>
-  <si>
-    <t>Pachuca,- La Secretaría del Trabajo y Previsión Social de Hidalgo (STPSH) realizó 5 mil 450 visitas de inspección a centros de trabajo de competencia local en los cuatro años de la actual administración. Las inspecciones han permitido ampliar la presencia de la autoridad laboral en 55 municipios de Hidalgo, con una cobertura de 83 mil 222 personas trabajadoras. Además, la STPSH creó el Sistema Alterno de Inspección Laboral (SAIL).</t>
-  </si>
-  <si>
-    <t>Inspección laboral</t>
-  </si>
-  <si>
-    <t>La STPSH reportó 5,450 inspecciones laborales locales que cubren a más de 83 mil trabajadores, destacándose además la creación de la plataforma SAIL para regularizar empresas.</t>
-  </si>
-  <si>
-    <t>Anticipan dos años de obras y ayudas sociales</t>
-  </si>
-  <si>
-    <t>Pachuca.–Durante la conferencia semanal del gobierno estatal, el mandatario Julio Menchaca Salazar afirmó que su administración trabajará con mucha intensidad durante el resto del sexenio para seguir posicionando a Hidalgo en el contexto nacional, con obra pública en los 84 municipios y programas sociales que garanticen bienestar para las familias. Por otra parte, las tres nuevas obras de carretera anunciadas por el gobierno de Hidalgo arrancarán en 2026.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca y el secretario de Sipdus, Alejandro Sánchez, detalló que las tres megaobras carreteras (Pachuca-México, Río de las Avenidas y Actopan-Atotonilco) concluirán en junio de 2028.</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Alejandro Sánchez García</t>
-  </si>
-  <si>
-    <t>Escuelas de Huehuetla dañadas por vaguada mantendrán su sede</t>
-  </si>
-  <si>
-    <t>Huehuetla.- Las escuelas que resultaron afectadas por la vaguada monzónica en Huehuetla siguen operando y no serán reubicadas, como la secundaria general El Caudillo del Sur, que está a un costado del río Pantepec, indicó el titular de la Secretaría de Educación Pública de Hidalgo (SEPH), Natividad Castrejón Valdez, ya que Conagua construirá un muro más grande para evitar un nuevo desbordamiento. Además, el titular de Conagua, Félix Brambila Mendoza, indicó que los trabajos consisten en bordos de protección.</t>
-  </si>
-  <si>
-    <t>Huehuetla</t>
-  </si>
-  <si>
-    <t>Infraestructura escolar</t>
-  </si>
-  <si>
-    <t>El titular de la SEPH, Natividad Castrejón, aclaró que las escuelas dañadas por inundaciones en Huehuetla no se reubicarán, al coordinar Conagua obras de gaviones de protección por 36 mdp.</t>
-  </si>
-  <si>
-    <t>SEPH, Presidencia</t>
-  </si>
-  <si>
-    <t>Natividad Castrejón Valdez, Félix Brambila Mendoza</t>
-  </si>
-  <si>
-    <t>Prevé Hacienda $76 mil millones para el presupuesto anual de 2027</t>
-  </si>
-  <si>
-    <t>Pachuca.- La Secretaría de Hacienda de Hidalgo prevé un presupuesto de 76 mil millones de pesos para el ejercicio fiscal 2027, lo que representaría un incremento respecto a los 75 mil 343 millones 96 mil 742 pesos aprobados para 2026. De acuerdo con María Esther Ramírez Vargas, titular de la dependencia estatal, desde el 10 de mayo comenzaron las reuniones con los ejecutores del gasto para integrar el paquete hacendario de la siguiente anualidad.</t>
-  </si>
-  <si>
-    <t>La secretaria de Hacienda, María Esther Ramírez, proyectó un presupuesto de egresos de 76 mil mdp para 2027, reportando que bajo la actual gestión la recaudación estatal subió un 96%.</t>
-  </si>
-  <si>
-    <t>Hacienda, Congreso</t>
-  </si>
-  <si>
-    <t>María Esther Ramírez Vargas</t>
-  </si>
-  <si>
-    <t>¡PARA DAR EL GRITO! FESTEJOS PATRIOS COSTARÁN 20 MDP</t>
-  </si>
-  <si>
-    <t>Los festejos patrios de este año representarán una erogación de alrededor de 20 millones de pesos para el gobierno de Hidalgo, informó el Oficial Mayor, Orlando Ángeles Pérez, quien precisó que el monto contempla la contratación de artistas y los requerimientos necesarios para sus presentaciones. El funcionario explicó que entre estos servicios se encuentran los llamados “riders”; es decir, las necesidades técnicas y logísticas solicitadas por los artistas, como equipo de sonido, iluminación, montaje y distribución del escenario, además de camerinos y alimentación. El gobierno estatal anunció a Carlos Rivera y Los Cardenales de Nuevo León como los artistas principales de la celebración en Plaza Juárez. El año pasado, los festejos representaron un gasto de entre 13 y 14 millones de pesos, cuando se presentó Majo Aguilar, además de otros espectáculos y servicios. Ángeles Pérez también informó que la Oficialía Mayor destinó entre 2.3 y 2.5 millones de pesos para la organización y realización del Cuarto Informe de Gobierno.</t>
-  </si>
-  <si>
-    <t>El oficial mayor Édgar Orlando Ángeles Pérez informó que los festejos patrios del 15 de septiembre en Plaza Juárez costarán 20 mdp, incluyendo la cartelera de Carlos Rivera y Los Cardenales de Nuevo León.</t>
-  </si>
-  <si>
-    <t>Orlando Ángeles Pérez, Carlos Rivera, Julio Menchaca Salazar, Majo Aguilar</t>
-  </si>
-  <si>
-    <t>UBICAN TÚNEL CLANDESTINO DE HUACHICOL EN PACHUCA</t>
-  </si>
-  <si>
-    <t>El Gabinete de Seguridad llevó a cabo la destrucción de un túnel localizado en Santa Catarina, municipio de Pachuca. La excavación se dirigía desde unos locales comerciales hacia la zona de ductos y tenía una longitud de 8.90 metros, una altura aproximada de 2.40 metros y un acceso de 80 por 80 centímetros. De acuerdo con la información oficial, la intervención oportuna de las instituciones permitió detectar el túnel antes de que alcanzara el ducto de Pemex, con lo que se mitigaron riesgos para las familias, los establecimientos y las personas que transitan por el lugar, además de impedir que la excavación continuara avanzando. Entre junio y agosto de este año han sido destruidos 16 túneles en Hidalgo.</t>
-  </si>
-  <si>
-    <t>El Gabinete de Seguridad de Hidalgo y la FGR inhabilitaron un túnel de extracción ilegal de hidrocarburo de 9 metros de largo en la colonia Santa Catarina de Pachuca, sumando 16 ductos clandestinos destruidos.</t>
-  </si>
-  <si>
-    <t>HIDALGO TRIPLICÓ LA TASA DE DONACIÓN DE ÓRGANOS</t>
-  </si>
-  <si>
-    <t>La solidaridad de las y los hidalguenses y el fortalecimiento de los programas de donación permitieron ampliar las oportunidades de atención para pacientes que requieren tratamientos especializados, informó la Secretaría de Salud de Hidalgo (SSH). La dependencia puso en marcha la primera Unidad Móvil de Donación Voluntaria de Sangre en la entidad, para acercar estos servicios a la población y fortalecer la cultura de la donación altruista. La unidad móvil recorrió 49 localidades, brindó atención a más de 2 mil personas y permitió captar 674 donaciones altruistas, lo que representó un incremento de 140 por ciento respecto de años anteriores. Asimismo, durante la actual administración se registraron 175 donantes de órganos y tejidos, que hicieron posible la procuración de 493 órganos y tejidos con fines terapéuticos (13 trasplantes renales y 38 de córnea en beneficio de más de 40 pacientes). La secretaria de Salud, Vanesa Escalante, destacó el impacto del programa.</t>
-  </si>
-  <si>
-    <t>La Secretaría de Salud de Hidalgo reportó un incremento de 140% en donación altruista de sangre mediante su unidad móvil, registrando 13 trasplantes renales y 38 de córnea en cuatro años.</t>
-  </si>
-  <si>
-    <t>SSH, CETS, CEETRA</t>
-  </si>
-  <si>
-    <t>Vanesa Escalante</t>
-  </si>
-  <si>
-    <t>IMPUESTO A CERVEZA NO IMPACTARÁ A CEBADEROS</t>
-  </si>
-  <si>
-    <t>El secretario de Agricultura y Desarrollo Rural de Hidalgo (Saderh), Napoleón González Pérez, consideró que la propuesta para modificar el Impuesto Especial sobre Producción y Servicios (IEPS), que contempla un aumento de entre 60 centavos y un peso por unidad a la cerveza, no afectaría a los productores de cebada, ya que el precio de la materia prima ya está pactado. Expresó que el impacto directo será resentido únicamente por el consumidor final por el alza del producto. En otro tema, informó que hasta ahora no tiene conocimiento de casos de gusano barrenador en animales silvestres, manteniéndose estrecha vigilancia mediante cámaras trampa en coordinación con Semarnath.</t>
-  </si>
-  <si>
-    <t>El titular de la Saderh, Napoleón González, aclaró que un eventual incremento al IEPS de la cerveza no perjudicará a los productores de cebada de Hidalgo, ya que el precio del grano está preestablecido.</t>
-  </si>
-  <si>
-    <t>Saderh, Congreso, Semarnath</t>
-  </si>
-  <si>
-    <t>HIDALGO REGISTRA REPUNTE LABORAL EN CUATRO AÑOS</t>
-  </si>
-  <si>
-    <t>Al cuarto año de la administración del gobernador Julio Menchaca Salazar se han generado 39 mil 545 empleos formales, de los cuales 20 mil personas fueron colocadas mediante los servicios de vinculación y movilidad laboral de la Secretaría del Trabajo y Previsión Social de Hidalgo (STPSH). Esta cifra representa el 50 por ciento de los empleos registrados ante el Instituto Mexicano del Seguro Social (IMSS). Los mecanismos de movilidad laboral han permitido colocar a 4 mil 500 hidalguenses en empleos legales en países como Alemania, Estados Unidos, Canadá y España, e internamente en Baja California, Coahuila, Jalisco, Sinaloa, Sonora y San Luis Potosí. Se invirtieron más de 50 mdp en 7 mil 100 apoyos del programa "Primero el Pueblo".</t>
-  </si>
-  <si>
-    <t>La STPSH dio a conocer la generación de 39,545 empleos formales en cuatro años de gestión, logrando la colocación de la mitad de ellos mediante vinculación y movilidad.</t>
-  </si>
-  <si>
     <t>VAN A DEMOLER PRIMARIA EN TULANCINGO; EDIFICARÁN OTRA</t>
   </si>
   <si>
-    <t>La primaria Aquiles Serdán, de Tulancingo, deberá ser demolida y reconstruida debido a daños estructurales irreparables, proceso que podría extenderse durante todo el ciclo escolar 2026-2027, informó el titular de la Secretaría de Educación Pública de Hidalgo (SEPH), Natividad Castrejón. Castrejón indicó que los alumnos iniciarán clases con normalidad mientras se define una sede temporal presencial o híbrida. La propuesta contrasta con la información recibida por padres de familia en una reunión en el plantel, donde se les comunicó que se contemplaba la rehabilitación de cinco aulas y dos direcciones con actividades virtuales de manera temporal, rechazando la distribución en varias escuelas.</t>
-  </si>
-  <si>
     <t>La SEPH demolerá y reconstruirá el plantel de la escuela primaria Aquiles Serdán en Tulancingo por fallas estructurales graves, contemplando sedes temporales.</t>
   </si>
   <si>
-    <t>En la Mira: CHAT FILTRADO</t>
-  </si>
-  <si>
-    <t>Ante la filtración de la charla entre Cuauhtémoc Ochoa y Adán Augusto López, donde el senador habla de fortalecer su presencia en Hidalgo, Julio Menchaca soltó: “No opino de conversaciones privadas, me ocupo de cosas importantes”.</t>
-  </si>
-  <si>
-    <t>Trabajo partidista</t>
-  </si>
-  <si>
-    <t>Columna En la Mira que comenta la reacción del gobernador Julio Menchaca ante la filtración de un chat privado entre el senador Cuauhtémoc Ochoa y Adán Augusto López.</t>
-  </si>
-  <si>
-    <t>Gobernador, Congreso, Morena, Presidencia</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, Cuauhtémoc Ochoa, Adán Augusto López</t>
-  </si>
-  <si>
-    <t>En la Mira: TUZOBÚS</t>
-  </si>
-  <si>
-    <t>Aunque el gobierno estatal analiza una segunda ruta troncal del Tuzobús hacia Mineral de la Reforma, la prioridad será rehabilitar las estaciones de la línea actual, con una inversión cercana a 100 mdp, de acuerdo con el Gobernador Julio Menchaca Salazar.</t>
-  </si>
-  <si>
-    <t>Comentario de opinión sobre el plan estatal para rehabilitar las estaciones del Tuzobús por 100 mdp, aplazando el análisis de una segunda ruta troncal.</t>
-  </si>
-  <si>
-    <t>Semot, Gobernador</t>
-  </si>
-  <si>
-    <t>En la Mira: HUACHICOL</t>
-  </si>
-  <si>
-    <t>La estadística sigue apuntando a que Cuautepec y otros municipios aledaños al Valle de Tulancingo y al Altiplano se mantienen como los de mayor incidencia en cuanto a hallazgos de tomas clandestinas de hidrocarburo. Sin embargo, crecen los casos de huachitúneles o puntos de extracción más cercanos a la zona metropolitana: en las últimas semanas, operativos en Pachuca, Mineral de la Reforma, en Zempoala revelaron presencia de esta práctica. ¿Se expande el negocio o se aclaran otras rutas?</t>
-  </si>
-  <si>
-    <t>Cuautepec</t>
-  </si>
-  <si>
-    <t>La columna comenta la alta incidencia de tomas clandestinas en Cuautepec y el preocupante avance de los túneles clandestinos de huachicol en la zona metropolitana de Pachuca.</t>
-  </si>
-  <si>
     <t>SSPH, Presidencia</t>
   </si>
   <si>
-    <t>Anuncian inversión de 6 mil 451 MDP para obras de movilidad en Pachuca y Actopan</t>
-  </si>
-  <si>
-    <t>El Gobierno de Hidalgo destinará más de 6 mil 451 millones de pesos a tres proyectos estratégicos de infraestructura anunciados por el gobernador Julio Menchaca Salazar durante su Cuarto Informe de Gobierno, mismas que encabezarán el trabajo en materia de obra pública que se realizará en toda la entidad durante los dos últimos años del sexenio. Las obras contemplan la conclusión del eje carretero Actopan–Atotonilco el Grande, la ampliación y modernización de la carretera México–Pachuca, así como la continuación de las vialidades y el encauzamiento del Río de las Avenidas. Alejandro Sánchez García, titular de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (SIPDUS), explicó que los proyectos serán desarrollados en distintas etapas entre 2026 y 2028, con el objetivo de mejorar la conectividad carretera, agilizar la movilidad en la zona metropolitana de Pachuca y proteger a la población asentada junto al cauce.</t>
-  </si>
-  <si>
-    <t>El Gobierno de Hidalgo invertirá 6,451 mdp en tres proyectos estratégicos viales que se realizarán entre 2026 y 2028: Actopan-Atotonilco, ampliación de la México-Pachuca y encauzamiento del Río de las Avenidas.</t>
-  </si>
-  <si>
     <t>Oscar Raúl Pérez</t>
   </si>
   <si>
-    <t>En operativos caen en Hidalgo, 31 generadores de violencia</t>
-  </si>
-  <si>
-    <t>Durante las últimas horas se dio a conocer de manera oficial que, las denuncias ciudadanas y los operativos coordinados del Gabinete de Seguridad de Hidalgo derivaron en importantes resultados, destacando la detención de 31 personas señaladas por la comisión de diversos delitos, ello lo informó el gobernador Julio Menchaca Salazar. Fue durante la reunión semanal, donde se detalló que en la última semana las fuerzas de seguridad de Hidalgo, lograron arrestar a 15 hombres y tres mujeres en nueve municipios de la entidad. Así mismo se advirtió que, a los detenidos se les descubrió que presuntamente tenían en su posesión 3 mil 952 dosis de distintos estupefacientes, además de tres básculas grameras. En Tizayuca se logró la detención de tres hombres por robo a una tienda de conveniencia con armas cortas y réplicas. En la carretera México-Pachuca se capturaron a cuatro hombres con un inhibidor de señal, y en la México-Tuxpan a tres hombres más con un camión robado cargado con 24.8 toneladas de polímero.</t>
-  </si>
-  <si>
-    <t>Operativos del Gabinete de Seguridad de Hidalgo y denuncias anónimas al C5i derivaron en el arresto de 31 presuntos delincuentes, decomiso de dosis de droga, armas y vehículos de carga robados.</t>
-  </si>
-  <si>
-    <t>Ampliarán alertas para advertir de fenómenos naturales</t>
-  </si>
-  <si>
-    <t>Ampliarán alertas para advertir de fenómenos naturales. Estos avisos podrán emitirse con horas o días de anticipación. Las alertas se enviarán directamente a los teléfonos móviles de los ciudadanos con la finalidad de que la población en general tome las debidas precauciones con suficiente anticipación ante emergencias climatológicas, meteorológicas o desastres de tipo natural en el estado de Hidalgo.</t>
-  </si>
-  <si>
-    <t>El Gobierno de Hidalgo implementará un sistema de alertas tempranas vía teléfonos móviles para avisar con horas o días de anticipación sobre fenómenos climatológicos severos.</t>
-  </si>
-  <si>
-    <t>Desde la comodidad solo ven lo negativo</t>
-  </si>
-  <si>
-    <t>Julio Menchaca Salazar, gobernador de Hidalgo, aseguró que los cuestionamientos sobre la obra pública, principalmente por la construcción de edificios para oficinas gubernamentales, provienen de personajes que tuvieron la oportunidad de atender las necesidades de la población cuando ocuparon cargos públicos. El mandatario reconoció que todavía existen numerosos pendientes y negó que su administración pretenda asumir una postura triunfalista; sin embargo, consideró necesario comunicar los resultados alcanzados mediante el esfuerzo de servidores públicos y distintos sectores de la sociedad. "Es muy complicado tener satisfechos a todos, sobre todo a las personas a las que les guía el rencor, a quienes no les parece absolutamente nada", manifestó.</t>
-  </si>
-  <si>
-    <t>El gobernador Julio Menchaca descalificó las críticas contra la edificación de oficinas gubernamentales y defendió la inversión realizada en obra pública frente a cuestionamientos de la oposición.</t>
-  </si>
-  <si>
-    <t>Casi 40 mil familias cuentan con ingreso estable</t>
-  </si>
-  <si>
-    <t>El titular de la secretaría del Trabajo y Previsión Social de Hidalgo, Oscar Javier González Hernández, indicó que a cuatro años de administración se ha logrado que 40 mil familias cuenten con un ingreso estable para satisfacer sus necesidades. Apuntó que de este total, con base en indicadores del Instituto Mexicano del Seguro Social (IMSS), 20 mil fueron vinculados a través del Servicio Nacional de Empleo (SNE), con el cual se vincula al empleo formal con todas las prestaciones de ley. Manifestó que estas cifras también son posibles con las jornadas y días por el empleo, para que los hidalguenses se puedan incorporar al sector productivo de una manera segura y estable. Subrayó "no solamente vinculamos, sino también vigilamos que nuestras hermanas y hermanos hidalguenses estén en las mejores condiciones, seguros y con garantía".</t>
-  </si>
-  <si>
-    <t>El titular de la STPSH, Oscar Javier González, reportó que en cuatro años de gestión se logró que 40,000 familias tengan ingresos estables, vinculándose 20,000 mediante el SNE.</t>
-  </si>
-  <si>
     <t>Ana Luisa Vega</t>
   </si>
   <si>
-    <t>Oscar Javier González Hernández, Julio Menchaca Salazar</t>
-  </si>
-  <si>
-    <t>Anuncian cifras históricas en crecimiento económico</t>
-  </si>
-  <si>
-    <t>El titular de la Secretaría de Desarrollo Económico de Hidalgo (Sedeco), Carlos Henkel Escorza, precisó que en 4 años de gobierno, la entidad alcanzó cifras históricas en crecimiento económico, competitividad y actividad industrial. De igual forma, dijo que de acuerdo con el INEGI, IMSS e IMCO, Hidalgo ocupa el primer lugar nacional en crecimiento económico al alcanzar el 8.2 por ciento al primer trimestre del 2026. Asimismo tiene la primera posición en actividad industrial al registrar un crecimiento del 21 por ciento al mes de abril, por encima de la media nacional; y también subió 11 posiciones en competitividad al pasar del lugar 25 al 14 nacional. Además indicó que se alcanzó una inversión histórica superior a los 147 mil millones de pesos con 130 productos consolidados nacionales y extranjeros.</t>
-  </si>
-  <si>
-    <t>Crecimiento Económico</t>
-  </si>
-  <si>
-    <t>El secretario de la Sedeco, Carlos Henkel, dio a conocer que Hidalgo ocupa el primer lugar nacional en crecimiento económico (8.2%) y actividad industrial (21%), sumando inversiones por 147,000 mdp.</t>
-  </si>
-  <si>
-    <t>Sedeco, Gobernador, Otros</t>
-  </si>
-  <si>
-    <t>Carlos Henkel Escorza</t>
-  </si>
-  <si>
-    <t>Reabren espacio de alimentación para niños y adolescentes</t>
-  </si>
-  <si>
-    <t>Autoridades municipales dieron el banderazo de reapertura del Espacio de Alimentación, Encuentro y Desarrollo de la Escuela Martín Urrutia, el cual permaneció cerrado de noviembre de 2025 a julio de 2026, debido a daños ocasionados en su infraestructura por las lluvias y el paso del tiempo. Gracias a la gestión y participación de los padres de familia, fue posible realizar las acciones necesarias para recuperar su operatividad y volver a brindar este important servicio a las y los estudiantes. Se destacó que los Espacios de Alimentación, Encuentro y Desarrollo forman parte de un programa del Sistema DIF Hidalgo, cuyo objetivo es contribuir a que niñas, niños y adolescentes tengan acceso a una alimentación adecuada.</t>
-  </si>
-  <si>
-    <t>Espacios de alimentación</t>
-  </si>
-  <si>
-    <t>Autoridades locales de Tulancingo inauguraron la reapertura del Espacio de Alimentación de la escuela Martín Urrutia, cerrado por daños pluviales, gracias a esfuerzos conjuntos con el DIF Hidalgo.</t>
-  </si>
-  <si>
     <t>Jesús Riveros</t>
   </si>
   <si>
     <t>DIFH</t>
   </si>
   <si>
-    <t>DIFH, Ayuntamiento</t>
-  </si>
-  <si>
-    <t>Apareció un cadáver maniatado y con huellas de tortura</t>
-  </si>
-  <si>
-    <t>Intensa movilización se generó en las últimas horas, luego que al 911 de Emergencias se reportó sobre el hallazgo del cuerpo sin vida de una persona del género masculino, mismo que fue avistado a la orilla de un camino de terracería que va de la comunidad de la Estanzuela al poblado de Tilcuautla del municipio de San Agustín Tlaxiaca. Elementos policiacos corroboraron la existencia del masculino que carecía de signos vitales, el cual fue localizado maniatado, con los pies amarrados con un lazo y a simple vista se le apreciaron diversas huellas de tortura. Al lugar también asistieron socorristas y paramédicos, quienes realizaron la valoración del infortunado y procedieron a certificar su deceso. Al momento se desconoce la identidad de la víctima.</t>
-  </si>
-  <si>
-    <t>San Agustín Tlaxiaca</t>
-  </si>
-  <si>
-    <t>Levantamiento De Cuerpo</t>
-  </si>
-  <si>
-    <t>Cuerpos de auxilio y policías localizaron el cadáver maniatado y con severas huellas de tortura de un hombre de identidad desconocida en un camino de San Agustín Tlaxiaca.</t>
+    <t>LISTO, PROYECTO EJECUTIVO PARA REHABILITACIÓN DE 36 ESTACIONES DEL STM: ÁNGELES</t>
+  </si>
+  <si>
+    <t>Las licitaciones para la rehabilitación de todas las estaciones del Sistema de Transporte Metropolitano (STM), antes llamado Tuzobús, se emitirán este mes, y actualmente ya se terminó el proyecto ejecutivo, aseguró Orlando Ángeles Pérez, titular de la Oficialía Mayor. El funcionario estatal explicó que será mediante la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible (Sipdus) el medio en que se publicarán los procedimientos. Previamente, el funcionario había explicado que se les dará mantenimiento a las 36 estaciones durante este año, en un periodo de siete meses estimado, con un presupuesto estimado de 100 millones de pesos.</t>
+  </si>
+  <si>
+    <t>Rehabilitación estaciones Tuzobús</t>
+  </si>
+  <si>
+    <t>El oficial mayor Orlando Ángeles Pérez confirmó la conclusión del proyecto ejecutivo para rehabilitar las 36 estaciones del Tuzobús este año con un presupuesto de 100 mdp.</t>
+  </si>
+  <si>
+    <t>Oficialía Mayor, Sipdus, Semot, Gobernador</t>
+  </si>
+  <si>
+    <t>Orlando Ángeles Pérez</t>
+  </si>
+  <si>
+    <t>ASCIENDEN A $84 MIL LAS MULTAS POR INVADIR EL CARRIL CONFINADO</t>
+  </si>
+  <si>
+    <t>A casi un mes de haber iniciado las multas por invadir el carril confinado del Sistema de Transporte Metropolitano (STM), antes llamado Tuzobús, se han aplicado alrededor de 36 sanciones económicas a automovilistas y motociclistas, las cuales han dejado ingresos por más de 84 mil pesos. De acuerdo con la página oficial de la dependencia, los montos económicos se contabilizaron a partir del 16 de agosto, día en que iniciaron las sanciones. Según la Secretaría de Movilidad y Transporte de Hidalgo (Semot), las infracciones van de los 2 mil 346 a los 3 mil 519 pesos.</t>
+  </si>
+  <si>
+    <t>Carril confinado</t>
+  </si>
+  <si>
+    <t>La Semot reportó la aplicación de 36 infracciones económicas a automovilistas por invadir el carril confinado del Tuzobús en Pachuca, generando un recaudo de 84,456 pesos.</t>
+  </si>
+  <si>
+    <t>ENTREGAN 39 AYUDAS TÉCNICAS A PERSONAS CON DISCAPACIDADES</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo entregó 39 ayudas técnicas a personas con discapacidad de 13 municipios. Durante el acto, realizado en el Centro de Rehabilitación Integral de Hidalgo (CRIH), la presidenta del organismo, Edda Vite Ramos, explicó que cada beneficiario pasa por un proceso de valoración en distintas áreas para determinar el equipo más adecuado. Durante la actual administración, el DIF Hidalgo ha entregado más de 10 mil ayudas técnicas, con una inversión cercana a los 19 millones de pesos.</t>
+  </si>
+  <si>
+    <t>Apoyo a personas con discapacidad</t>
+  </si>
+  <si>
+    <t>El DIF Hidalgo entregó 39 ayudas técnicas adaptadas a personas con discapacidad de 13 municipios, acumulando más de 10 mil dispositivos entregados en la entidad con 19 mdp de inversión.</t>
+  </si>
+  <si>
+    <t>Lizania Zavala</t>
+  </si>
+  <si>
+    <t>DIFH, Gobernador</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos, Jesús Miguel, Isabel Mendoza Jiménez, Edwin Francisco Lina Hernández</t>
+  </si>
+  <si>
+    <t>FALTAN 45 PROCURADURÍAS DE PROTECCIÓN DE LA NIÑEZ</t>
+  </si>
+  <si>
+    <t>De los 84 municipios de Hidalgo, 45 aún no cuentan con una Procuraduría de Protección de Niñas, Niños y Adolescentes, mientras que 39 ya han concretado la instalación de estas instancias, informó la presidenta del Sistema DIF Hidalgo, Edda Vite Ramos. La titular mencionó que aproximadamente el 40 por ciento de los ayuntamientos cuenta actualmente con una procuraduría municipal, por lo que más de la mitad de los municipios permanecen pendientes de establecer estas áreas. Recordó que el decreto publicado en el POEH estableció un plazo de 180 días.</t>
+  </si>
+  <si>
+    <t>Protección del menor</t>
+  </si>
+  <si>
+    <t>La presidenta del DIF Hidalgo, Edda Vite Ramos, señaló que 45 ayuntamientos tienen pendiente la creación de su Procuraduría Municipal de Protección a la Niñez.</t>
+  </si>
+  <si>
+    <t>DIFH, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos</t>
+  </si>
+  <si>
+    <t>REMODELARÁ EL DIF HIDALGO TALLER DE ÓRTESIS Y PRÓTESIS; INVERTIRÁN 11.5 MDP</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo realizará la remodelación del Taller de Órtesis y Prótesis, ubicado cerca del Centro de Rehabilitación Integral de Hidalgo (CRIH), con una inversión de 11.5 millones de pesos y un plazo estimado de seis meses. La presidenta del DIF Hidalgo, Edda Vite Ramos, explicó que el proyecto contempla intervenir una parte del inmueble que presenta fisuras y un descenso en el nivel del piso, por lo que será necesario demolerla y realizar una remodelación completa.</t>
+  </si>
+  <si>
+    <t>Infraestructura hospitalaria</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo invertirá 11.5 mdp en la remodelación y demolición de áreas dañadas del Taller de Órtesis y Prótesis del CRIH en Pachuca.</t>
+  </si>
+  <si>
+    <t>ACUSAN FRENO A PROCESO PENAL CONTRA UN NOTARIO</t>
+  </si>
+  <si>
+    <t>La familia Arenas Rodríguez denunció públicamente un presunto freno en el proceso penal iniciado contra el notario público número 8 de Tulancingo, Juan Manuel Hinojosa Zamora, a quien señalan de haber facilitado un acto que derivó en la pérdida de un inmueble valuado en alrededor de 29 millones de pesos. Durante una conferencia de prensa en Pachuca, los denunciantes confirmaron que el fedatario es hermano de Juan Carlos Hinojosa Zamora, magistrado federal, por lo que temen favoritismos en la causa penal 117/2026.</t>
+  </si>
+  <si>
+    <t>Notarías</t>
+  </si>
+  <si>
+    <t>La familia Arenas Rodríguez acusó la paralización del proceso penal contra el notario No. 8 de Tulancingo, Juan Manuel Hinojosa, señalado por irregularidades que ocasionaron la pérdida de un bien de 29 mdp.</t>
+  </si>
+  <si>
+    <t>Luis Godínez</t>
+  </si>
+  <si>
+    <t>PGJEH, TSJEH, Notarías</t>
+  </si>
+  <si>
+    <t>Juan Manuel Hinojosa Zamora, Juan Carlos Hinojosa Zamora</t>
+  </si>
+  <si>
+    <t>COMIENZA RECONSTRUCCIÓN DE ESCUELAS AFECTADAS POR LA VAGUADA MONZÓNICA EN TIANGUISTENGO</t>
+  </si>
+  <si>
+    <t>A once meses del paso de la vaguada monzónica, en Tlacolula, Tianguistengo, comenzó este mes la reconstrucción de tres de las cuatro escuelas que registraron afectaciones, informó el delegado Luis Ángel Rodríguez Galindo. La intervención abarca la demolición y edificación de la primaria, la telesecundaria y el Cemsad Cobaeh, mientras el preescolar opera en instalaciones prestadas.</t>
+  </si>
+  <si>
+    <t>Tianguistengo</t>
+  </si>
+  <si>
+    <t>En Tlacolula, Tianguistengo, dio inicio la obra de reconstrucción de planteles escolares destruidos por la vaguada monzónica, como parte del paquete de 8 escuelas intervenidas por la SEPH.</t>
+  </si>
+  <si>
+    <t>SEPH, Gobernador, Conafe, Cobaeh</t>
+  </si>
+  <si>
+    <t>Luis Ángel Rodríguez Galindo, Julio Menchaca Salazar, Natividad Castrejón Valdez</t>
+  </si>
+  <si>
+    <t>Registra el estado 149 homicidios dolosos en 2026</t>
+  </si>
+  <si>
+    <t>De acuerdo con el reporte de incidencia delictiva presentado ayer durante la conferencia matutina de la presidenta Claudia Sheinbaum Pardo, Hidalgo registró 149 homicidios dolosos entre enero y agosto de 2026. Este número representó el 1.3% del total nacional, colocando al estado en el lugar 19 entre las 32 entidades federativas. El titular del Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública (SESNSP) presentó el reporte con fecha hasta el 31 de agosto de 2026.</t>
+  </si>
+  <si>
+    <t>Homicidios</t>
+  </si>
+  <si>
+    <t>El reporte nacional de incidencia delictiva del SESNSP ubica a Hidalgo en el lugar 19 del país con 149 homicidios dolosos registrados entre enero y agosto de 2026.</t>
+  </si>
+  <si>
+    <t>Claudia Sheinbaum Pardo</t>
+  </si>
+  <si>
+    <t>Impulsan el desarrollo científico</t>
+  </si>
+  <si>
+    <t>Más de 100 hidalguenses recibieron un apoyo por medio del Programa de Becas para Formación de Capital Humano Hidalguense en Estudios de Posgrado, impulsado por el gobierno de Hidalgo con el propósito de fortalecer la preparación de perfiles especializados. Entre los proyectos beneficiados destaca la obra civil del Laboratorio de Nuevos Alimentos (Lanua).</t>
+  </si>
+  <si>
+    <t>Becas De Posgrado</t>
+  </si>
+  <si>
+    <t>Más de 100 estudiantes e investigadores hidalguenses recibieron becas de posgrado del Gobierno estatal para fortalecer la formación científica especializada en la entidad.</t>
+  </si>
+  <si>
+    <t>Planeación</t>
+  </si>
+  <si>
+    <t>Planeación, Citnova, Gobernador</t>
+  </si>
+  <si>
+    <t>Hay menos reos de Hidalgo en Ceferesos</t>
+  </si>
+  <si>
+    <t>El número de personas originarias de Hidalgo en centros penitenciarios federales registró una disminución durante los primeros siete meses de 2026. De acuerdo con el Cuaderno Mensual de Información Estadística Penitenciaria Nacional, elaborado por Prevención y Reinserción Social, la población penal hidalguense pasó de 278 internos al cierre de 2025 a 267 en julio de este año, distribuidos en 12 Ceferesos del país.</t>
+  </si>
+  <si>
+    <t>Reinserción social</t>
+  </si>
+  <si>
+    <t>La población penitenciaria federal originaria de Hidalgo disminuyó a 267 reos al cierre de julio de 2026, concentrándose la mayoría en penales de Guanajuato, Durango y Veracruz.</t>
+  </si>
+  <si>
+    <t>Acusan retraso en proceso penal en contra de notario</t>
+  </si>
+  <si>
+    <t>Integrantes de la familia Arenas Rodríguez denunciaron un presunto retraso en el avance del proceso penal iniciado contra el notario público número 8 de Tulancingo de Bravo, Juan Manuel Hinojosa Zamora, por posibles delitos cometidos en el ejercicio de su actividad profesional, relacionados con la autorización de un poder notarial que habría derivado en la pérdida de un inmueble con valor aproximado de 29 millones de pesos.</t>
+  </si>
+  <si>
+    <t>La familia Arenas Rodríguez denunció el aplazamiento injustificado de la audiencia inicial en la causa penal 117/2026 contra el notario No. 8 de Tulancingo por presunta pérdida patrimonial de 29 mdp.</t>
+  </si>
+  <si>
+    <t>Juan Manuel Hinojosa Zamora</t>
+  </si>
+  <si>
+    <t>Conmemoración natalicio de Josefa Ortiz Téllez-Girón</t>
+  </si>
+  <si>
+    <t>La secretaria de Hacienda de Hidalgo, María Esther Ramírez Vargas, encabezó la ceremonia cívica en el Parque Hidalgo de Pachuca para conmemorar el natalicio de Josefa Ortiz Téllez-Girón, destacando el papel fundamental de las mujeres en la historia de la Independencia de México. Al acto asistieron legisladores, magistrados y mandos militares.</t>
+  </si>
+  <si>
+    <t>Aniversario natalicio</t>
+  </si>
+  <si>
+    <t>La secretaria de Hacienda, María Esther Ramírez Vargas, presidió el acto cívico por el natalicio de Josefa Ortiz Téllez-Girón en Pachuca, resaltando el valor de las mujeres en las causas nacionales.</t>
+  </si>
+  <si>
+    <t>Hacienda, Congreso, TSJEH, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>María Esther Ramírez Vargas, Andrés Velázquez Vázquez, Ariadna Maricela Martínez Austria</t>
+  </si>
+  <si>
+    <t>Dan a 105 proyectos apoyo económico</t>
+  </si>
+  <si>
+    <t>El Consejo de Ciencia, Tecnología e Innovación de Hidalgo (Citnova) otorgó 105 apoyos económicos individuales de hasta 250 mil pesos como parte del programa Fondo Hidalgo para proyectos de desarrollo científico, investigación e innovación social con base tecnológica, según informó su director Francisco Patiño Cardona.</t>
+  </si>
+  <si>
+    <t>Impulso A La Ciencia</t>
+  </si>
+  <si>
+    <t>El Citnova asignó apoyos económicos a 105 proyectos científicos y tecnológicos de Hidalgo con financiamientos individuales de hasta 250 mil pesos.</t>
+  </si>
+  <si>
+    <t>Sonia Nochebuena</t>
+  </si>
+  <si>
+    <t>Francisco Patiño Cardona</t>
+  </si>
+  <si>
+    <t>Piden más alimentadoras para acortar traslados</t>
+  </si>
+  <si>
+    <t>Habitantes de fraccionamientos ubicados en el sur de Pachuca y Zempoala solicitaron al Sistema de Transporte Metropolitano Tuzobús incrementar el número de unidades en rutas alimentadoras desde la terminal Téllez, ya que los tiempos de espera de hasta 25 minutos alargan sus trayectos diarios hasta dos horas.</t>
+  </si>
+  <si>
+    <t>Zempoala</t>
+  </si>
+  <si>
+    <t>Alimentadoras Tuzobús</t>
+  </si>
+  <si>
+    <t>Usuarios de la zona metropolitana sur recriminaron demoras en el paso de las alimentadoras del Tuzobús desde Téllez, señalando falta de iluminación y problemas de seguridad nocturna.</t>
+  </si>
+  <si>
+    <t>Semot, Sitmah</t>
+  </si>
+  <si>
+    <t>Humberto Cabrera Román</t>
+  </si>
+  <si>
+    <t>Otorgan apoyos a 5 elencos musicales</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura de Hidalgo ejerció un presupuesto de 6.5 millones de pesos en diversos programas de desarrollo artístico, permitiendo la entrega de 275 instrumentos musicales para conformar bandas tradicionales, orquestas de guitarras y ensambles en cinco municipios vulnerables.</t>
+  </si>
+  <si>
+    <t>Impulso a las artes</t>
+  </si>
+  <si>
+    <t>La Secretaría de Cultura estatal entregó 275 instrumentos a niños y jóvenes mediante el programa Semilleros Creativos de Hidalgo para impulsar la formación musical comunitaria.</t>
+  </si>
+  <si>
+    <t>Víctor Serrano</t>
+  </si>
+  <si>
+    <t>Cultura, Gobernador</t>
+  </si>
+  <si>
+    <t>Neyda Naranjo Baltazar, Julio Menchaca Salazar</t>
+  </si>
+  <si>
+    <t>Alumnos de la UTHH regresan al salón de clases</t>
+  </si>
+  <si>
+    <t>La Universidad Tecnológica de la Huasteca Hidalguense (UTHH) y el sindicato SUTUTEH acordaron la firma de las condiciones generales de trabajo, concluyendo una semana de paro laboral y permitiendo el regreso a aulas de más de 3 mil 300 estudiantes en Huejutla.</t>
+  </si>
+  <si>
+    <t>La rectoría de la UTHH y el gremio docente firmaron el acuerdo contractual, reactivando las labores académicas de 3,300 alumnos en la región Huasteca.</t>
+  </si>
+  <si>
+    <t>Rubén Juárez</t>
+  </si>
+  <si>
+    <t>Miguel Acosta Salazar</t>
+  </si>
+  <si>
+    <t>Participaron 305 alumnos de la entidad en la prueba PISA 2025</t>
+  </si>
+  <si>
+    <t>Participaron 305 estudiantes de Hidalgo en la prueba PISA 2025, cuyos resultados colocan a México como el penúltimo país de la Organización para la Cooperación y el Desarrollo Económico (OCDE) evaluado en ciencia y comprensión lectora, el antepenúltimo en matemáticas y el cuarto con desempeño más bajo en pensamiento computacional.</t>
+  </si>
+  <si>
+    <t>Cobertura educativa</t>
+  </si>
+  <si>
+    <t>Un total de 305 estudiantes de 15 años de nueve planteles de educación media superior en Hidalgo participaron en la prueba PISA 2025 de la OCDE.</t>
+  </si>
+  <si>
+    <t>SEPH, UAEH, Cobaeh, Cecyteh</t>
+  </si>
+  <si>
+    <t>HOMICIDIOS DISMINUYEN 53 POR CIENTO EN 2 AÑOS</t>
+  </si>
+  <si>
+    <t>El gobierno federal informó que los homicidios dolosos disminuyeron 53 por ciento en dos años, mientras que el promedio diario en Hidalgo cayó 28 por ciento de enero a agosto de 2026 en comparación al mismo periodo de 2025. El reporte del SESNSP ubica a la entidad en el lugar 19 nacional con 149 casos en ocho meses.</t>
+  </si>
+  <si>
+    <t>Cifras del SESNSP revelaron un descenso del 28% en el promedio diario de homicidios dolosos en Hidalgo entre enero y agosto de 2026, contabilizándose 149 carpetas de investigación.</t>
+  </si>
+  <si>
+    <t>Claudia Sheinbaum Pardo, Marcela Figueroa Franco</t>
+  </si>
+  <si>
+    <t>Madre pide avances en la búsqueda de su hijo de 23 años</t>
+  </si>
+  <si>
+    <t>Tras casi un año sin saber el paradero de su hijo mayor, Sandra López Tovar no pierde las esperanzas de encontrar a su familiar, Carlos López Tovar, visto por última vez en la comunidad Progreso, ubicada en Atotonilco de Tula, en diciembre de 2025. Exige mayor celeridad a las autoridades en la carpeta de investigación.</t>
+  </si>
+  <si>
+    <t>Atotonilco de Tula</t>
+  </si>
+  <si>
+    <t>La madre del joven Carlos López Tovar urgió a la Fiscalía agilizar las investigaciones para dar con el paradero de su hijo, desaparecido desde diciembre de 2025 en Atotonilco de Tula.</t>
+  </si>
+  <si>
+    <t>Segobh, PGJEH, Presidencia</t>
+  </si>
+  <si>
+    <t>Sandra López Tovar, Carlos López Tovar</t>
+  </si>
+  <si>
+    <t>Refuerzan estrategia contra el huachicol</t>
+  </si>
+  <si>
+    <t>El Gobierno de Hidalgo y Petróleos Mexicanos (Pemex) reinforced la coordinación institucional para atender con mayor eficacia el robo de hidrocarburo, prevenir riesgos y fortalecer la seguridad en las zonas por donde atraviesa la infraestructura de ductos.</t>
+  </si>
+  <si>
+    <t>Combate Al Huachicol</t>
+  </si>
+  <si>
+    <t>Gabinete de Seguridad de Hidalgo sostuvo reunión en la CDMX con directivos de Pemex para coordinar la inhabilitación acelerada de tomas clandestinas y túneles huachicoleros.</t>
+  </si>
+  <si>
+    <t>SSPH, Segobh, PGJEH, Presidencia</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares Reyna, Salvador Cruz Neri, Francisco Fernández Hasbum</t>
+  </si>
+  <si>
+    <t>Invertirán 11.5 mdp para reparar taller del DIFH</t>
+  </si>
+  <si>
+    <t>El Taller de Órtesis y Prótesis del Sistema para el Desarrollo Integral de la Familia Hidalgo (DIFH) será rehabilitado con una inversión estimada de 11.5 millones de pesos debido a fisuras en la estructura del inmueble, ocasionadas por deficiencias en el terreno y cimentación.</t>
+  </si>
+  <si>
+    <t>La presidenta del DIFH, Edda Vite Ramos, anunció la remodelación integral del Taller de Órtesis y Prótesis del CRIH por 11.5 mdp para corregir fallas de cimentación heredadas.</t>
+  </si>
+  <si>
+    <t>Acusan retraso en proceso contra notario de Tulancingo</t>
+  </si>
+  <si>
+    <t>Por hacer un poder notarial que propició que perdieran un inmueble valuado en 29 millones de pesos, la familia Arenas Rodríguez denunció a Juan Manuel Hinojosa Zamora, titular de la Notaría Pública 8 de Tulancingo, por delitos cometidos en el ejercicio de una actividad profesional; sin embargo, las víctimas acusaron que la causa penal 117/2026 no avanza.</t>
+  </si>
+  <si>
+    <t>La familia Arenas Rodríguez recriminó al Ministerio Público el diferimiento repetido de audiencias en la causa penal contra el notario No. 8 de Tulancingo por un fraude de 29 mdp.</t>
+  </si>
+  <si>
+    <t>Juan Manuel Hinojosa Zamora, José Antonio Arenas, Juan Carlos Hinojosa Zamora</t>
+  </si>
+  <si>
+    <t>La entidad acumula 22 casos de gusano barrenador en humanos</t>
+  </si>
+  <si>
+    <t>A finales de agosto, en Hidalgo incrementaron los casos de gusano barrenador en humanos a 22 pacientes, situando al estado en el octavo lugar nacional con más padecimientos de miasis, reportó la Secretaría de Salud federal.</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud confirmó un acumulado de 22 casos de miasis en humanos por gusano barrenador en Hidalgo, ubicándolo en la octava posición epidemiológica nacional.</t>
+  </si>
+  <si>
+    <t>SSH, Presidencia</t>
+  </si>
+  <si>
+    <t>REGRESAN A CLASES 3 MIL ALUMNOS DE UTHH</t>
+  </si>
+  <si>
+    <t>Luego de permanecer cinco días en paro laboral, este martes la Universidad Tecnológica de la Huasteca Hidalguense (UTHH) reanudó sus actividades académicas habituales tras la firma de acuerdos laborales entre la rectoría y el sindicato Sututeh.</t>
+  </si>
+  <si>
+    <t>La UTHH de Huejutla reactivó sus clases para más de 3,000 universitarios al pactar con el sindicato Sututeh la basificación y certidumbre salarial de la plantilla laboral.</t>
+  </si>
+  <si>
+    <t>Francisco Bautista</t>
+  </si>
+  <si>
+    <t>Efrén Juárez Castillo</t>
+  </si>
+  <si>
+    <t>Intensifican los operativos por una familia desaparecida</t>
+  </si>
+  <si>
+    <t>Autoridades de los tres órdenes de gobierno intensificaron las labores de búsqueda de cuatro integrantes de una familia en Tizayuca (sector El Pedregal) tras fichas activas emitidas por la Comisión de Búsqueda.</t>
+  </si>
+  <si>
+    <t>Corporaciones de seguridad y la Comisión de Búsqueda desplegaron operativos en la colonia El Pedregal de Tizayuca para dar con el paradero de cuatro miembros de una familia.</t>
+  </si>
+  <si>
+    <t>Javier Quezada</t>
+  </si>
+  <si>
+    <t>Segobh, Ayuntamientos, PGJEH</t>
+  </si>
+  <si>
+    <t>Por daños en estructura, DIF destinará 11.5 mdp para nuevo edificio</t>
+  </si>
+  <si>
+    <t>La presidenta del Patronato del Sistema para el Desarrollo Integral de la Familia (DIF) de Hidalgo, Edda Vite Ramos, informó que por daños estructurales, parte del Taller de Ortesis y Prótesis a cargo del Centro Integral de Rehabilitación de Hidalgo (CRIH) será demolido y se construirá un nuevo espacio con una inversión de 11.5 millones de pesos.</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo destinará 11.5 mdp a la demolición y reconstrucción de la segunda etapa del Taller de Órtesis y Prótesis del CRIH por fallas en la cimentación.</t>
+  </si>
+  <si>
+    <t>Socorro Ávila</t>
+  </si>
+  <si>
+    <t>DIFH, CRIH, Gobernador</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos, Héctor Alberto Villafuentes Téllez, Ricardo Alvizo Contreras</t>
+  </si>
+  <si>
+    <t>En cuatro años otorgan 19 mdp en ayudas técnicas</t>
+  </si>
+  <si>
+    <t>Durante los últimos cuatro años, el Sistema DIF Hidalgo ha realizado la entrega de más de 10 mil ayudas técnicas a personas en situación de vulnerabilidad y con alguna condición de discapacidad con una inversión cercana a los 19 millones de pesos. Edda Vite encabezó la más reciente entrega a 39 personas de 13 municipios.</t>
+  </si>
+  <si>
+    <t>La presidenta del DIF Hidalgo, Edda Vite, entregó 39 ayudas técnicas adaptadas a personas con discapacidad de 13 municipios, acumulando 10 mil apoyos en cuatro años.</t>
+  </si>
+  <si>
+    <t>DIFH, DIF Nacional, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos, Ricardo Alvizo Contreras</t>
+  </si>
+  <si>
+    <t>Inicia instalación de escenario para Grito de Independencia</t>
+  </si>
+  <si>
+    <t>Comenzaron los trabajos para la instalación del escenario en la explanada de Plaza Juárez, en Pachuca, donde se realizarán las presentaciones musicales de las fiestas patrias, destacando el concierto principal de Carlos Rivera y Los Cardenales de Nuevo León.</t>
+  </si>
+  <si>
+    <t>Arrancó el montaje de la infraestructura y escenario principal en Plaza Juárez para las presentaciones artísticas de las Fiestas Patrias en Pachuca.</t>
+  </si>
+  <si>
+    <t>Carlos Rivera</t>
+  </si>
+  <si>
+    <t>Busca IHE estudio para blindar el programa Vive saludable, vive feliz</t>
+  </si>
+  <si>
+    <t>Para realizar el estudio técnico operativo y diseñar el Plan de Aseguramiento de la Calidad (PAC) de la estrategia Vive saludable, vive feliz, el IHE emitió la licitación pública IHE-CGAyF-N56-2026 para la contratación de estudios de campo y gabinete.</t>
+  </si>
+  <si>
+    <t>Vida Saludable</t>
+  </si>
+  <si>
+    <t>El IHE licitó un estudio técnico y el Plan de Aseguramiento de la Calidad para fortalecer la operatividad y seguimiento de la estrategia de salud escolar en el estado.</t>
+  </si>
+  <si>
+    <t>Nathali González</t>
+  </si>
+  <si>
+    <t>SEPH, IHE, SSH, IMSS, IMSS-Bienestar, DIFH</t>
+  </si>
+  <si>
+    <t>Estudiantes de El Mexe exigen justicia por muerte de Antonio</t>
+  </si>
+  <si>
+    <t>Integrantes de la Escuela Normal Rural Luis Villarreal El Mexe solicitaron a la PGJEH una investigación rigurosa tras la localización del cuerpo sin vida de su compañero José Antonio Salgado Aparicio, de 22 años, quien presentaba heridas de arma blanca en Francisco I. Madero.</t>
+  </si>
+  <si>
+    <t>Francisco I. Madero</t>
+  </si>
+  <si>
+    <t>Exigen esclarecer homicidio</t>
+  </si>
+  <si>
+    <t>La comunidad estudiantil de El Mexe exigió el esclarecimiento del homicidio de José Antonio Salgado, cuyo cuerpo fue localizado en Francisco I. Madero.</t>
+  </si>
+  <si>
+    <t>Joselyn Sánchez</t>
+  </si>
+  <si>
+    <t>SEPH, PGJEH</t>
+  </si>
+  <si>
+    <t>José Antonio Salgado Aparicio</t>
+  </si>
+  <si>
+    <t>Lluvias colapsan línea de agua en Mineral del Monte</t>
+  </si>
+  <si>
+    <t>Los deslizamientos de tierra provocados por las lluvias del pasado fin de semana colapsaron un tramo de la línea de conducción de agua potable Pandola-Dificultad, en la zona de Peña Larga-Aviadero, en Mineral del Monte, por lo que el suministro será reforzado mediante mayor bombeo y carros cisterna. Personal de la Caasim inspeccionó la zona junto con autoridades municipales y Protección Civil. Se instalará de manera temporal un tramo de tubería de 12 metros para atender la afectación.</t>
+  </si>
+  <si>
+    <t>Mineral del Monte</t>
+  </si>
+  <si>
+    <t>Fuga De Agua</t>
+  </si>
+  <si>
+    <t>Deslizamientos de tierra colapsaron la línea de conducción de agua Pandola-Dificultad en Mineral del Monte, activando abasto emergente con pipas.</t>
+  </si>
+  <si>
+    <t>Sipdus, Caasim, Ayuntamiento, Segobh, Presidencia</t>
+  </si>
+  <si>
+    <t>Destinan más de 300 millones al campo</t>
+  </si>
+  <si>
+    <t>Recuperar la capacidad productiva de las tierras y contar con mejores insumos para sembrar son dos de las principales necesidades que enfrentan los productores de Hidalgo, donde se han canalizado 308 millones de pesos en varios apoyos.</t>
+  </si>
+  <si>
+    <t>Apoyo Al Agro</t>
+  </si>
+  <si>
+    <t>El Gobierno de Hidalgo ha canalizado 308 millones de pesos en apoyos agrícolas para recuperar la capacidad productiva de las tierras.</t>
+  </si>
+  <si>
+    <t>Saderh, Gobernador</t>
+  </si>
+  <si>
+    <t>10 mil comités vigilan obras</t>
+  </si>
+  <si>
+    <t>Cerca de 50 mil ciudadanas y ciudadanos participan en Hidalgo en la vigilancia de programas, obras y acciones públicas, mediante más de 10 mil Comités de Contraloría Social que dan seguimiento a los recursos.</t>
+  </si>
+  <si>
+    <t>Contraloría Social</t>
+  </si>
+  <si>
+    <t>Cerca de 50 mil ciudadanos participan en Hidalgo en la vigilancia de programas y obras mediante más de 10 mil Comités de Contraloría Social.</t>
+  </si>
+  <si>
+    <t>Conectan 358 comunidades con nuevas carreteras</t>
+  </si>
+  <si>
+    <t>Un total de 358 localidades de Hidalgo cuentan ahora con nuevas conexiones carreteras tras la construcción y pavimentación de 316 kilómetros de vías, como parte de las obras de infraestructura.</t>
+  </si>
+  <si>
+    <t>Obras De Infraestructura</t>
+  </si>
+  <si>
+    <t>Un total de 358 localidades de Hidalgo cuentan con nuevas conexiones carreteras tras la pavimentación de 316 kilómetros de vías.</t>
+  </si>
+  <si>
+    <t>Retraso en audiencia contra notario</t>
+  </si>
+  <si>
+    <t>La familia Arenas Rodríguez acusó retraso en la audiencia inicial en contra del titular de la notaría número 8 de Tulancingo, Juan Manuel Hinojosa Zamora, tras la carpeta de investigación iniciada en su contra por delitos cometidos en el ejercicio de una actividad profesional. En conferencia de prensa, José Antonio Arenas Daniels señaló que la carpeta de investigación ya fue judicializada pero el Ministerio Público solicitó en dos ocasiones el diferimiento.</t>
+  </si>
+  <si>
+    <t>La familia Arenas Rodríguez acusó el diferimiento repetido de la audiencia inicial contra el titular de la Notaría 8 de Tulancingo por presunto fraude.</t>
+  </si>
+  <si>
+    <t>PGJEH, Notarías</t>
+  </si>
+  <si>
+    <t>Juan Manuel Hinojosa Zamora, José Antonio Arenas Daniels</t>
+  </si>
+  <si>
+    <t>Resuelven 16 mil conflictos laborales</t>
+  </si>
+  <si>
+    <t>Más de 16 mil conflictos entre trabajadores y empleadores han sido resueltos mediante conciliación laboral en Hidalgo durante la actual administración, lo que ha permitido solucionar controversias sin que las partes tengan que llegar a juicio. El Centro de Conciliación Laboral de Hidalgo reportó 16 mil 535 controversias solucionadas mediante el diálogo.</t>
+  </si>
+  <si>
+    <t>Conciliación Laboral</t>
+  </si>
+  <si>
+    <t>El Centro de Conciliación Laboral de Hidalgo reportó la resolución de 16,535 controversias mediante acuerdos directos entre trabajadores y patrones.</t>
+  </si>
+  <si>
+    <t>STPSH, CCLEH, Gobernador</t>
+  </si>
+  <si>
+    <t>Hidalgo suma 2.5 millones de vacunas</t>
+  </si>
+  <si>
+    <t>Más de 2.5 millones de dosis de vacuna antirrábica han sido aplicadas en Hidalgo, mientras que las campañas de esterilización alcanzaron 139 mil 964 procedimientos en perros y gatos, como parte de las acciones de prevención sanitaria y control poblacional de animales de compañía.</t>
+  </si>
+  <si>
+    <t>Vacunación Antirrábica</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo aplicó más de 2.5 millones de dosis de vacuna antirrábica y realizó 139,964 esterilizaciones caninas y felinas.</t>
+  </si>
+  <si>
+    <t>Destacan papel de las mujeres en la Independencia</t>
+  </si>
+  <si>
+    <t>El papel de las mujeres en momentos decisivos de la historia de México fue destacado durante la conmemoración del 258 aniversario del natalicio de Josefa Ortiz Téllez-Girón.</t>
+  </si>
+  <si>
+    <t>Durante la conmemoración del 258 aniversario del natalicio de Josefa Ortiz Téllez-Girón, autoridades destacaron la participación decisiva de las mujeres en la historia patria.</t>
+  </si>
+  <si>
+    <t>Hacienda, Gobernador</t>
+  </si>
+  <si>
+    <t>Josefa Ortiz Téllez-Girón</t>
+  </si>
+  <si>
+    <t>Entregan 275 instrumentos a Semilleros Creativos</t>
+  </si>
+  <si>
+    <t>El programa Semilleros Creativos de Hidalgo entregó 275 instrumentos para integrar cinco agrupaciones en Cuautepec, San Bartolo, Metztitlán, Zacualtipán.</t>
+  </si>
+  <si>
+    <t>El programa Semilleros Creativos de Hidalgo entregó 275 instrumentos musicales para conformar cinco agrupaciones en Cuautepec, San Bartolo, Metztitlán y Zacualtipán.</t>
+  </si>
+  <si>
+    <t>Un total de 45 municipios están pendientes de formalizar su Procuraduría Municipal</t>
+  </si>
+  <si>
+    <t>Un total de 45 municipios están pendientes de formalizar su Procuraduría Municipal para la Atención de Niñas, Niños y Adolescentes, informó la presidenta del Patronato del Sistema DIFH, Edda Vite Ramos, quien señaló que hasta el momento se han instalado 39. Pese a que los ayuntamientos cuentan con un plazo de 180 días a partir del pasado 13 de abril, es decir, como límite el 10 de octubre, Vite Ramos señaló que, en caso de que haya ayuntamientos que no las formalicen, no se les va a obligar.</t>
+  </si>
+  <si>
+    <t>La presidenta del DIF Hidalgo, Edda Vite Ramos, informó que 45 municipios aún tienen pendiente la creación de su Procuraduría de Protección a la Niñez, descartando aplicar sanciones a los ayuntamientos omisos.</t>
+  </si>
+  <si>
+    <t>Veida Martínez Miranda</t>
+  </si>
+  <si>
+    <t>DIFH, Ayuntamientos, PPNNAF</t>
+  </si>
+  <si>
+    <t>Hidalgo suma 149 homicidios dolosos, 28% menos que en 2025</t>
+  </si>
+  <si>
+    <t>Durante el periodo de enero a agosto de 2026, Hidalgo registró un total de 149 homicidios dolosos, concentrando el 1.3% del total de los registros en el país, de acuerdo con datos del Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública (SESNSP). En comparación con el mismo periodo de 2025, la entidad obtuvo una disminución del 28% respecto a este delito. Por su parte, Omar García Harfuch informó sobre la detención en Pachuca de Jorge Luis N, líder del grupo delictivo 'Pueblos Unidos'.</t>
+  </si>
+  <si>
+    <t>Cifras del SESNSP ubican a Hidalgo en la posición 19 nacional con 149 homicidios dolosos registrados entre enero y agosto de 2026, lo que representa un descenso del 28% respecto al año anterior.</t>
+  </si>
+  <si>
+    <t>SSPH, Presidencia, SESNSP</t>
+  </si>
+  <si>
+    <t>Marcela Figueroa Franco, Omar García Harfuch</t>
+  </si>
+  <si>
+    <t>ENTREGA GOBIERNO UNIFORMES, ÚTILES Y CALZADO A ESTUDIANTES DE TULA-TEPEJI</t>
+  </si>
+  <si>
+    <t>El titular del Instituto Hidalguense de Educación y secretario de Educación Pública de Hidalgo, Natividad Castrejón Valdez, encabezó la entrega de uniformes, útiles escolares, libros de texto, calzado y equipamiento a estudiantes de educación básica de Tepeji del Río, Tula de Allende y Atotonilco de Tula, reafirmando el compromiso de la gestión estatal con la permanencia escolar.</t>
+  </si>
+  <si>
+    <t>Tepeji del Río</t>
+  </si>
+  <si>
+    <t>Paquete de apoyos escolares</t>
+  </si>
+  <si>
+    <t>El secretario de Educación Natividad Castrejón realizó una gira de trabajo por Tepeji, Tula y Atotonilco de Tula para entregar útiles, uniformes, libros y calzado a la comunidad estudiantil de nivel básico.</t>
+  </si>
+  <si>
+    <t>SEPH, IHE, Gobernador, Ayuntamientos</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez, Julio Menchaca Salazar, Laura Mendiola Pérez, Pedro Alfredo Olguín, Jenifer López Aguilar</t>
+  </si>
+  <si>
+    <t>Acusan a notario de Tulancingo de facilitar pérdida de inmueble valuado en 29 mdp</t>
+  </si>
+  <si>
+    <t>Integrantes de la familia Arenas Rodríguez denunciaron públicamente al notario número 8 de Tulancingo, Juan Manuel Hinojosa Zamora, ya que presuntamente realizó un poder notarial que facilitó la pérdida de un inmueble valuado en 29 millones de pesos. La carpeta con número 18-2024-005017 se encuentra judicializada ante la PGJEH, pero la audiencia inicial ha sido diferida en dos ocasiones.</t>
+  </si>
+  <si>
+    <t>La familia Arenas Rodríguez exigió la actuación del Ministerio Público contra el notario No. 8 de Tulancingo por avalar un poder irregular que ocasionó la pérdida patrimonial de un inmueble de 29 mdp.</t>
+  </si>
+  <si>
+    <t>Marco Cerón</t>
+  </si>
+  <si>
+    <t>PGJEH, Notarías, TSJEH</t>
+  </si>
+  <si>
+    <t>ONU Turismo pone la mirada en Hidalgo</t>
+  </si>
+  <si>
+    <t>En el marco de la Asamblea Ordinaria de la Asetur, la secretaria de Turismo de Hidalgo, Elizabeth Quintanar Gómez, sostuvo un encuentro con Shaikha Alnowais, secretaria general de ONU Turismo, para impulsar el turismo sostenible e incluyente, destacándose el nombramiento de Omitlán como Best Tourism Village 2023.</t>
+  </si>
+  <si>
+    <t>Omitlán</t>
+  </si>
+  <si>
+    <t>Impulso Al Turismo</t>
+  </si>
+  <si>
+    <t>La secretaria de Turismo de Hidalgo, Elizabeth Quintanar, se reunió con la secretaria general de ONU Turismo, Shaikha Alnowais, quien reconoció el modelo de turismo comunitario de Hidalgo.</t>
+  </si>
+  <si>
+    <t>Turismo, Presidencia</t>
+  </si>
+  <si>
+    <t>Elizabeth Quintanar Gómez, Shaikha Alnowais</t>
+  </si>
+  <si>
+    <t>Exhorta Semarnath a separar los residuos sólidos</t>
+  </si>
+  <si>
+    <t>La Secretaría de Medio Ambiente y Recursos Naturales de Hidalgo (Semarnath) exhortó a la población a contribuir al cuidado del medio ambiente al separar los residuos sólidos y llevarlos al Parque Ecológico de Cubitos (PEC), centro de acopio permanente, en un horario de atención de lunes a domingo.</t>
+  </si>
+  <si>
+    <t>Manejo de residuos</t>
+  </si>
+  <si>
+    <t>La Semarnath invitó a las familias hidalguenses a acudir al Parque Ecológico Cubitos para depositar residuos reciclables como papel, cartón, PET, aluminio y electrodomésticos.</t>
+  </si>
+  <si>
+    <t>Semarnath</t>
+  </si>
+  <si>
+    <t>Alertan sobre los signos y síntomas del cáncer infantil</t>
+  </si>
+  <si>
+    <t>En el marco de Septiembre Dorado, la Secretaría de Salud de Hidalgo (SSH) hizo un llamado a madres y padres de familia a estar atentos a signos de alerta como fiebre persistente, moretones inusuales, ganglios inflamados, palidez y dolor de huesos para lograr diagnósticos oportunos.</t>
+  </si>
+  <si>
+    <t>Cáncer Infantil</t>
+  </si>
+  <si>
+    <t>La Secretaría de Salud de Hidalgo exhortó a acudir a valoración médica inmediata ante cualquier síntoma sospechoso de cáncer infantil durante la campaña Septiembre Dorado.</t>
+  </si>
+  <si>
+    <t>Destinan más de 13 mil MDP a infraestructura carretera</t>
+  </si>
+  <si>
+    <t>A cuatro años del gobierno de Julio Menchaca, la Sipdus ha destinado más de 13 mil millones de pesos a infraestructura vial, logrando la construcción de 316 km de nuevas carreteras que conectan a 358 comunidades, la rehabilitación de 500 km estatales y 263 km de vialidades urbanas.</t>
+  </si>
+  <si>
+    <t>El secretario de Sipdus, Alejandro Sánchez García, detalló una inversión histórica de más de 13,000 mdp en carreteras, caminos rurales y bulevares metropolitanos en cuatro años.</t>
+  </si>
+  <si>
+    <t>Realizarán primer Recorrido Turístico para Personas con Discapacidad Visual</t>
+  </si>
+  <si>
+    <t>Del 10 al 13 de septiembre, Tulancingo albergará el primer Recorrido Turístico para Personas con Discapacidad Visual 'Recorriendo Realidades', reuniendo a 40 participantes de todo el país para promover el turismo accesible e inclusivo en sitios históricos y balnearios.</t>
+  </si>
+  <si>
+    <t>Turismo inclusivo</t>
+  </si>
+  <si>
+    <t>Activistas del colectivo Recorriendo Realidades organizan en Tulancingo una experiencia turística y gastronómica incluyente para personas con discapacidad visual de todo México.</t>
+  </si>
+  <si>
+    <t>Turismo, Ayuntamiento</t>
+  </si>
+  <si>
+    <t>Evelyn Ríos Estefes, Javier Orduña Ortega</t>
+  </si>
+  <si>
+    <t>Gobierno de Hidalgo y Pemex sostuvieron reunión de seguridad</t>
+  </si>
+  <si>
+    <t>Los titulares de Segobh, SSPH y PGJEH se reunieron en la CDMX con directivos de Pemex para acordar operativos semanales de inhabilitación de tomas clandestinas y clausura de túneles huachicoleros en Hidalgo.</t>
+  </si>
+  <si>
+    <t>El Gabinete de Seguridad de Hidalgo acordó con Pemex asignar maquinaria y personal especializado para sellar ductos clandestinos y 16 huachitúneles identificados.</t>
+  </si>
+  <si>
+    <t>Guillermo Olivares Reyna, Salvador Cruz Neri, Francisco Fernández Hasbum, Ana Cristina Maturano, Diego Hernández Pitta</t>
+  </si>
+  <si>
+    <t>Hidalgo baja en delito de alto impacto</t>
+  </si>
+  <si>
+    <t>Cifras del SESNSP ubican a Hidalgo en la posición 19 nacional con una reducción del 28% en el promedio diario de víctimas de homicidio doloso de enero a agosto de 2026 en comparación al mismo periodo del año pasado.</t>
+  </si>
+  <si>
+    <t>El reporte nacional de seguridad del SESNSP reveló un descenso de 10 casos en homicidios dolosos durante agosto en Hidalgo, concentrando solo el 1.3% del total nacional.</t>
+  </si>
+  <si>
+    <t>SSPH, Presidencia, SESNSP, Gobernador</t>
+  </si>
+  <si>
+    <t>Plaza Juárez se alista para el Grito</t>
+  </si>
+  <si>
+    <t>En Plaza Juárez, el escenario para la noche del Grito de Independencia comienza a tomar forma. Trabajadores montan la estructura que recibirá, el próximo 15 de septiembre, a Carlos Rivera y Los Cardenales de Nuevo León, artistas principales de la celebración organizada por el gobierno de Hidalgo. La Oficialía Mayor informó que el festejo tendrá un costo de alrededor de 20 millones de pesos, que contempla la contratación de los artistas y los requerimientos técnicos y logísticos para sus presentaciones. Entre estos se encuentran los llamados “riders”, que incluyen sonido, iluminación, montaje, escenario, camerinos y alimentación. En 2025, las actividades patrias costaron entre 13 y 14 millones de pesos, cuando se presentó Majo Aguilar.</t>
+  </si>
+  <si>
+    <t>En Plaza Juárez inició el montaje del escenario para las celebraciones del 15 de septiembre, las cuales tendrán un costo estimado de 20 mdp con las presentaciones de Carlos Rivera y Los Cardenales de Nuevo León.</t>
+  </si>
+  <si>
+    <t>Carlos Rivera, Majo Aguilar, Orlando Ángeles Pérez</t>
+  </si>
+  <si>
+    <t>RECONSTRUIRÁN TALLER DE DIFH CON 11.5 MDP</t>
+  </si>
+  <si>
+    <t>El Taller de Órtesis y Prótesis del Centro Integral de Rehabilitación de Hidalgo (CRIH) será intervenido este mes debido a fallas estructurales que obligarán a demoler una de sus áreas y reconstruirla, informó la presidenta del Patronato del DIF Hidalgo, Edda Vite Ramos. La funcionaria explicó que el inmueble fue construido en dos etapas y que los problemas se concentran en la segunda, edificada sobre un terreno que presentó inestabilidad y provocó fisuras en la estructura. Precisó que la primera parte se encuentra en buenas condiciones. Para permitir la intervención, ya comenzó la mudanza del taller y la búsqueda de bodegas provisionales. La nueva obra tendrá una inversión de 11.5 millones de pesos.</t>
+  </si>
+  <si>
+    <t>El Sistema DIF Hidalgo invertirá 11.5 mdp en la demolición y reconstrucción de la segunda etapa del Taller de Órtesis y Prótesis del CRIH por fallas en la cimentación.</t>
+  </si>
+  <si>
+    <t>Edda Vite Ramos, Héctor Alberto Villafuentes Téllez</t>
+  </si>
+  <si>
+    <t>En la Mira: EL MEXE</t>
+  </si>
+  <si>
+    <t>Estudiantes del Mexe condenaron el supuesto homicidio político en contra de uno de sus compañeros normalistas. Aunque poco se conoce hasta el momento, fuentes cercanas al plantel del Valle del Mezquital confirmaron a ADN que el joven sin vida fue localizado entre las milpas, en una zona donde solo aquel que conoce podría dejar un cuerpo. Ya veremos cómo se da solución y claridad al tema antes de que detone -nuevamente- en manifestaciones acaloradas que seguro llegarán a la capital hidalguense.</t>
+  </si>
+  <si>
+    <t>Normalistas de El Mexe exigieron justicia y celeridad a las investigaciones tras el hallazgo sin vida de un estudiante en el Valle del Mezquital.</t>
+  </si>
+  <si>
+    <t>En la Mira: PROCURADURÍAS INFANTILES</t>
+  </si>
+  <si>
+    <t>El reloj ya corre para los municipios de las 84 Procuradurías de Protección a Niñas, Niños y Adolescentes, pues apenas van 32 están instaladas, mientras el plazo de 180 días marcado en el POEH vence el 9 de diciembre. A los ayuntamientos les quedan poco más de tres meses para ponerse al corriente.</t>
+  </si>
+  <si>
+    <t>Comentario sobre el plazo legal que vence el 9 de diciembre para que los 84 ayuntamientos de Hidalgo instalen sus Procuradurías de Protección de Niñas, Niños y Adolescentes.</t>
+  </si>
+  <si>
+    <t>En la Mira: UTHH</t>
+  </si>
+  <si>
+    <t>Tras una semana sin clases, más de 3 mil estudiantes de la UTHH regresarían a las aulas luego de que finalmente se firmaran las condiciones generales de trabajo. Tres años de acuerdos gestionados y tuvo que llegar el paro para destrabar la firma.</t>
+  </si>
+  <si>
+    <t>La columna resalta la reanudación de actividades en la UTHH de Huejutla tras destrabarse la firma de las condiciones laborales del personal docente.</t>
+  </si>
+  <si>
+    <t>HIDALGO VA A LA BAJA EN DELITOS DE ALTO IMPACTO</t>
+  </si>
+  <si>
+    <t>Durante agosto, Hidalgo registró una disminución en los homicidios dolosos respecto a julio, con 10 casos menos, de acuerdo con cifras del Secretariado Ejecutivo del Sistema Nacional de Seguridad Pública (SESNSP). Con este resultado, la entidad se mantuvo entre las 16 entidades federativas con una incidencia inferior a la media nacional y se ubicó en el lugar 19 del país en este indicador. De enero a agosto de 2026, Hidalgo acumuló una reducción de 28 por ciento en este delito en comparación con el mismo periodo de 2025. Hidalgo representa 1.3 por ciento de la incidencia registrada en el país.</t>
+  </si>
+  <si>
+    <t>Cifras del SESNSP ubican a Hidalgo en el lugar 19 nacional con una reducción del 28% en el acumulado de homicidios dolosos de enero a agosto de 2026.</t>
+  </si>
+  <si>
+    <t>La primaria Aquiles Serdán, de Tulancingo, deberá ser demolida y reconstruida debido a daños estructurales irreparables, proceso que podría extenderse durante todo el ciclo escolar 2026-2027, informó el titular de la Secretaría de Educación Pública de Hidalgo (SEPH), Natividad Castrejón. Castrejón indicó que los alumnos iniciarán clases con normalidad mientras se define una sede temporal presencial o híbrida. La propuesta contrasta con la información recibida por padres de familia en una reunión en el plantel.</t>
+  </si>
+  <si>
+    <t>Natividad Castrejón Valdez</t>
   </si>
 </sst>
 </file>
@@ -1338,8 +1389,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ56" tableType="xml" totalsRowShown="0" connectionId="1">
-  <autoFilter ref="A1:AJ56" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}" name="Tabla1" displayName="Tabla1" ref="A1:AJ58" tableType="xml" totalsRowShown="0" connectionId="1">
+  <autoFilter ref="A1:AJ58" xr:uid="{9C9C4F43-DE86-4846-BF9E-6E01FFFDA369}"/>
   <tableColumns count="36">
     <tableColumn id="1" xr3:uid="{8F40C058-2FFC-41FE-8C1C-A4D19F52138F}" uniqueName="Canal" name="Canal" dataDxfId="20">
       <xmlColumnPr mapId="1" xpath="/NotasRadio/Nota/Canal" xmlDataType="string"/>
@@ -1771,7 +1822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C8D3BDD-1D0F-4C8C-BA65-EA33AD09B867}">
-  <dimension ref="A1:AJ56"/>
+  <dimension ref="A1:AJ58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -1921,25 +1972,25 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="F2" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>50</v>
@@ -1957,10 +2008,10 @@
         <v>37</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="Y2" s="2" t="s">
         <v>60</v>
@@ -1987,39 +2038,39 @@
         <v>40</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="F3" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -2034,69 +2085,67 @@
         <v>37</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Z3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA3">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="AB3" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD3" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="AG3" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>124</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="AJ3" s="2"/>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F4" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R4">
         <v>1</v>
@@ -2111,10 +2160,10 @@
         <v>37</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="Y4" s="2" t="s">
         <v>60</v>
@@ -2129,45 +2178,45 @@
         <v>61</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD4" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="AG4" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="AJ4" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F5" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>64</v>
@@ -2188,10 +2237,10 @@
         <v>37</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="Y5" s="2" t="s">
         <v>60</v>
@@ -2200,57 +2249,57 @@
         <v>43</v>
       </c>
       <c r="AA5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB5" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD5" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="AJ5" s="2" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F6" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R6">
         <v>1</v>
@@ -2265,19 +2314,19 @@
         <v>37</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Z6" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA6">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>61</v>
@@ -2289,45 +2338,45 @@
         <v>44</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="AJ6" s="2" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F7" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R7">
         <v>1</v>
@@ -2342,10 +2391,10 @@
         <v>37</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="Y7" s="2" t="s">
         <v>60</v>
@@ -2366,43 +2415,45 @@
         <v>44</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ7" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F8" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="R8">
         <v>1</v>
@@ -2417,10 +2468,10 @@
         <v>37</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>147</v>
+        <v>69</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="Y8" s="2" t="s">
         <v>60</v>
@@ -2441,42 +2492,42 @@
         <v>44</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="AG8" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="AJ8" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F9" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>42</v>
@@ -2494,61 +2545,63 @@
         <v>37</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="Y9" s="2" t="s">
         <v>60</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="AA9">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB9" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD9" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="AG9" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>156</v>
+        <v>45</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AJ9" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="AJ9" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F10" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>64</v>
@@ -2569,16 +2622,16 @@
         <v>37</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="Y10" s="2" t="s">
         <v>60</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="AA10">
         <v>24</v>
@@ -2593,45 +2646,45 @@
         <v>44</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>66</v>
+        <v>157</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>105</v>
+        <v>158</v>
       </c>
       <c r="AJ10" s="2" t="s">
-        <v>161</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F11" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>64</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -2646,19 +2699,19 @@
         <v>37</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="Y11" s="2" t="s">
         <v>60</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="AA11">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AB11" s="2" t="s">
         <v>61</v>
@@ -2670,7 +2723,7 @@
         <v>44</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="AG11" s="2" t="s">
         <v>40</v>
@@ -2679,31 +2732,31 @@
         <v>45</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="AJ11" s="2"/>
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F12" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G12">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>42</v>
@@ -2721,10 +2774,10 @@
         <v>37</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="Y12" s="2" t="s">
         <v>60</v>
@@ -2745,42 +2798,42 @@
         <v>44</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="AG12" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F13" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G13">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>50</v>
@@ -2798,10 +2851,10 @@
         <v>37</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="Y13" s="2" t="s">
         <v>60</v>
@@ -2816,45 +2869,45 @@
         <v>61</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD13" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AG13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="AJ13" s="2" t="s">
-        <v>59</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F14" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>64</v>
@@ -2875,19 +2928,19 @@
         <v>37</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="Y14" s="2" t="s">
         <v>60</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="AA14">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AB14" s="2" t="s">
         <v>61</v>
@@ -2899,45 +2952,45 @@
         <v>44</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>101</v>
+        <v>177</v>
       </c>
       <c r="AG14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>66</v>
+        <v>157</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>105</v>
+        <v>158</v>
       </c>
       <c r="AJ14" s="2" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F15" s="1">
+        <v>46274</v>
+      </c>
+      <c r="G15">
+        <v>8</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F15" s="1">
-        <v>46273</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="I15" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R15">
         <v>1</v>
@@ -2952,66 +3005,66 @@
         <v>37</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Z15" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA15">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB15" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD15" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>186</v>
+        <v>70</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AJ15" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F16" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G16">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>50</v>
@@ -3029,10 +3082,10 @@
         <v>37</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Y16" s="2" t="s">
         <v>60</v>
@@ -3047,48 +3100,48 @@
         <v>61</v>
       </c>
       <c r="AC16" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD16" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF16" s="2" t="s">
-        <v>101</v>
+        <v>190</v>
       </c>
       <c r="AG16" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AJ16" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F17" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G17">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>50</v>
@@ -3106,10 +3159,10 @@
         <v>37</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="Y17" s="2" t="s">
         <v>60</v>
@@ -3118,7 +3171,7 @@
         <v>43</v>
       </c>
       <c r="AA17">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AB17" s="2" t="s">
         <v>61</v>
@@ -3130,45 +3183,45 @@
         <v>44</v>
       </c>
       <c r="AF17" s="2" t="s">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="AG17" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH17" s="2" t="s">
-        <v>199</v>
+        <v>47</v>
       </c>
       <c r="AI17" s="2" t="s">
-        <v>200</v>
+        <v>47</v>
       </c>
       <c r="AJ17" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F18" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>64</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R18">
         <v>1</v>
@@ -3183,16 +3236,16 @@
         <v>37</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>87</v>
+        <v>200</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Y18" s="2" t="s">
         <v>60</v>
       </c>
       <c r="Z18" s="2" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="AA18">
         <v>24</v>
@@ -3207,45 +3260,43 @@
         <v>44</v>
       </c>
       <c r="AF18" s="2" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="AG18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH18" s="2" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="AJ18" s="2" t="s">
-        <v>206</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="AJ18" s="2"/>
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F19" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>64</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R19">
         <v>1</v>
@@ -3260,16 +3311,16 @@
         <v>37</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="Y19" s="2" t="s">
         <v>60</v>
       </c>
       <c r="Z19" s="2" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="AA19">
         <v>24</v>
@@ -3278,48 +3329,48 @@
         <v>61</v>
       </c>
       <c r="AC19" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD19" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF19" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AG19" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH19" s="2" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="AI19" s="2" t="s">
-        <v>210</v>
+        <v>103</v>
       </c>
       <c r="AJ19" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F20" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G20">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>42</v>
@@ -3337,10 +3388,10 @@
         <v>37</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="Y20" s="2" t="s">
         <v>60</v>
@@ -3361,45 +3412,45 @@
         <v>44</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="AG20" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH20" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AI20" s="2" t="s">
-        <v>108</v>
+        <v>211</v>
       </c>
       <c r="AJ20" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F21" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G21">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R21">
         <v>1</v>
@@ -3414,10 +3465,10 @@
         <v>37</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>127</v>
+        <v>215</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="Y21" s="2" t="s">
         <v>60</v>
@@ -3438,39 +3489,39 @@
         <v>44</v>
       </c>
       <c r="AF21" s="2" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="AG21" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>130</v>
+        <v>217</v>
       </c>
       <c r="AJ21" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="F22" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G22">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>46</v>
@@ -3491,10 +3542,10 @@
         <v>37</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>222</v>
+        <v>133</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Y22" s="2" t="s">
         <v>60</v>
@@ -3503,7 +3554,7 @@
         <v>43</v>
       </c>
       <c r="AA22">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB22" s="2" t="s">
         <v>61</v>
@@ -3515,43 +3566,45 @@
         <v>44</v>
       </c>
       <c r="AF22" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AG22" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH22" s="2" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="AJ22" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="AJ22" s="2" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F23" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R23">
         <v>1</v>
@@ -3566,10 +3619,10 @@
         <v>37</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>227</v>
+        <v>137</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="Y23" s="2" t="s">
         <v>60</v>
@@ -3578,55 +3631,57 @@
         <v>43</v>
       </c>
       <c r="AA23">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB23" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AC23" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD23" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF23" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="AG23" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH23" s="2" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ23" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="AJ23" s="2" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F24" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>64</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R24">
         <v>1</v>
@@ -3641,10 +3696,10 @@
         <v>37</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Y24" s="2" t="s">
         <v>60</v>
@@ -3665,40 +3720,40 @@
         <v>44</v>
       </c>
       <c r="AF24" s="2" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="AG24" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH24" s="2" t="s">
-        <v>156</v>
+        <v>48</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>156</v>
+        <v>229</v>
       </c>
       <c r="AJ24" s="2"/>
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F25" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G25">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>50</v>
@@ -3716,10 +3771,10 @@
         <v>37</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>222</v>
+        <v>75</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="Y25" s="2" t="s">
         <v>60</v>
@@ -3734,30 +3789,30 @@
         <v>61</v>
       </c>
       <c r="AC25" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD25" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF25" s="2" t="s">
-        <v>90</v>
+        <v>233</v>
       </c>
       <c r="AG25" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH25" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>224</v>
+        <v>47</v>
       </c>
       <c r="AJ25" s="2" t="s">
-        <v>98</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>53</v>
@@ -3769,16 +3824,16 @@
         <v>236</v>
       </c>
       <c r="F26" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R26">
         <v>1</v>
@@ -3793,7 +3848,7 @@
         <v>37</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>222</v>
+        <v>90</v>
       </c>
       <c r="X26" s="2" t="s">
         <v>237</v>
@@ -3802,10 +3857,10 @@
         <v>60</v>
       </c>
       <c r="Z26" s="2" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="AA26">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AB26" s="2" t="s">
         <v>61</v>
@@ -3817,39 +3872,37 @@
         <v>44</v>
       </c>
       <c r="AF26" s="2" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="AG26" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH26" s="2" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="AJ26" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="AJ26" s="2"/>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F27" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>46</v>
@@ -3870,19 +3923,19 @@
         <v>37</v>
       </c>
       <c r="W27" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="X27" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="Y27" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z27" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="X27" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="Y27" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z27" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="AA27">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AB27" s="2" t="s">
         <v>61</v>
@@ -3894,45 +3947,45 @@
         <v>44</v>
       </c>
       <c r="AF27" s="2" t="s">
-        <v>81</v>
+        <v>243</v>
       </c>
       <c r="AG27" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH27" s="2" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>85</v>
+        <v>244</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>59</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F28" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>64</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R28">
         <v>1</v>
@@ -3947,63 +4000,63 @@
         <v>37</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>243</v>
+        <v>120</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Y28" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Z28" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA28">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AB28" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AC28" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD28" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF28" s="2" t="s">
-        <v>58</v>
+        <v>243</v>
       </c>
       <c r="AG28" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH28" s="2" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="AI28" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AJ28" s="2" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F29" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>46</v>
@@ -4024,19 +4077,19 @@
         <v>37</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>222</v>
+        <v>93</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Y29" s="2" t="s">
         <v>60</v>
       </c>
       <c r="Z29" s="2" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="AA29">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB29" s="2" t="s">
         <v>61</v>
@@ -4048,37 +4101,39 @@
         <v>44</v>
       </c>
       <c r="AF29" s="2" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="AG29" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH29" s="2" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="AI29" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="AJ29" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="AJ29" s="2" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="F30" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>64</v>
@@ -4099,10 +4154,10 @@
         <v>37</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>175</v>
+        <v>257</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="Y30" s="2" t="s">
         <v>60</v>
@@ -4123,45 +4178,43 @@
         <v>44</v>
       </c>
       <c r="AF30" s="2" t="s">
-        <v>41</v>
+        <v>259</v>
       </c>
       <c r="AG30" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH30" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AI30" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="AJ30" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="AJ30" s="2"/>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="F31" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G31">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>46</v>
+        <v>263</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="R31">
         <v>1</v>
@@ -4176,10 +4229,10 @@
         <v>37</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="Y31" s="2" t="s">
         <v>60</v>
@@ -4194,48 +4247,48 @@
         <v>61</v>
       </c>
       <c r="AC31" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD31" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF31" s="2" t="s">
-        <v>58</v>
+        <v>266</v>
       </c>
       <c r="AG31" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH31" s="2" t="s">
-        <v>257</v>
+        <v>47</v>
       </c>
       <c r="AI31" s="2" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="F32" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>42</v>
@@ -4250,22 +4303,22 @@
         <v>63</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="Y32" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Z32" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA32">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AB32" s="2" t="s">
         <v>61</v>
@@ -4277,43 +4330,43 @@
         <v>44</v>
       </c>
       <c r="AF32" s="2" t="s">
-        <v>264</v>
+        <v>41</v>
       </c>
       <c r="AG32" s="2" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="AH32" s="2" t="s">
-        <v>257</v>
+        <v>66</v>
       </c>
       <c r="AI32" s="2" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="AJ32" s="2"/>
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="F33" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G33">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R33">
         <v>1</v>
@@ -4328,19 +4381,19 @@
         <v>37</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>127</v>
+        <v>277</v>
       </c>
       <c r="X33" s="2" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="Y33" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Z33" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA33">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB33" s="2" t="s">
         <v>61</v>
@@ -4352,39 +4405,37 @@
         <v>44</v>
       </c>
       <c r="AF33" s="2" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="AG33" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH33" s="2" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="AI33" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ33" s="2" t="s">
-        <v>131</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="AJ33" s="2"/>
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="F34" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>64</v>
@@ -4405,19 +4456,19 @@
         <v>37</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="X34" s="2" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="Y34" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Z34" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA34">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB34" s="2" t="s">
         <v>61</v>
@@ -4435,31 +4486,31 @@
         <v>41</v>
       </c>
       <c r="AH34" s="2" t="s">
-        <v>272</v>
+        <v>80</v>
       </c>
       <c r="AI34" s="2" t="s">
-        <v>272</v>
+        <v>84</v>
       </c>
       <c r="AJ34" s="2"/>
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="F35" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>64</v>
@@ -4480,19 +4531,19 @@
         <v>37</v>
       </c>
       <c r="W35" s="2" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="X35" s="2" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="Y35" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Z35" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA35">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AB35" s="2" t="s">
         <v>61</v>
@@ -4510,39 +4561,37 @@
         <v>41</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AJ35" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="AJ35" s="2"/>
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="F36" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R36">
         <v>1</v>
@@ -4557,19 +4606,19 @@
         <v>37</v>
       </c>
       <c r="W36" s="2" t="s">
-        <v>279</v>
+        <v>137</v>
       </c>
       <c r="X36" s="2" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="Y36" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Z36" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA36">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB36" s="2" t="s">
         <v>61</v>
@@ -4587,31 +4636,33 @@
         <v>41</v>
       </c>
       <c r="AH36" s="2" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AI36" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ36" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="AJ36" s="2" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="F37" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>64</v>
@@ -4632,66 +4683,64 @@
         <v>37</v>
       </c>
       <c r="W37" s="2" t="s">
-        <v>76</v>
+        <v>295</v>
       </c>
       <c r="X37" s="2" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="Y37" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Z37" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA37">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB37" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AC37" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD37" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF37" s="2" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="AG37" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AJ37" s="2" t="s">
-        <v>284</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="AJ37" s="2"/>
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="F38" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>287</v>
+        <v>64</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>50</v>
@@ -4709,66 +4758,64 @@
         <v>37</v>
       </c>
       <c r="W38" s="2" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="X38" s="2" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="Y38" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA38">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AC38" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD38" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF38" s="2" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="AG38" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="AJ38" s="2" t="s">
-        <v>291</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="AJ38" s="2"/>
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="F39" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>50</v>
@@ -4786,19 +4833,19 @@
         <v>37</v>
       </c>
       <c r="W39" s="2" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="X39" s="2" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="Y39" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Z39" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA39">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB39" s="2" t="s">
         <v>61</v>
@@ -4810,45 +4857,45 @@
         <v>44</v>
       </c>
       <c r="AF39" s="2" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="AG39" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="AJ39" s="2" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="F40" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R40">
         <v>1</v>
@@ -4863,19 +4910,19 @@
         <v>37</v>
       </c>
       <c r="W40" s="2" t="s">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="X40" s="2" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="Y40" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Z40" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA40">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB40" s="2" t="s">
         <v>61</v>
@@ -4887,45 +4934,43 @@
         <v>44</v>
       </c>
       <c r="AF40" s="2" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="AG40" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AJ40" s="2" t="s">
-        <v>300</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="AJ40" s="2"/>
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="F41" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R41">
         <v>1</v>
@@ -4940,10 +4985,10 @@
         <v>37</v>
       </c>
       <c r="W41" s="2" t="s">
-        <v>222</v>
+        <v>127</v>
       </c>
       <c r="X41" s="2" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="Y41" s="2" t="s">
         <v>60</v>
@@ -4952,7 +4997,7 @@
         <v>43</v>
       </c>
       <c r="AA41">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB41" s="2" t="s">
         <v>61</v>
@@ -4964,34 +5009,36 @@
         <v>44</v>
       </c>
       <c r="AF41" s="2" t="s">
-        <v>41</v>
+        <v>313</v>
       </c>
       <c r="AG41" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="AJ41" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="AJ41" s="2" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="F42" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -5015,16 +5062,16 @@
         <v>37</v>
       </c>
       <c r="W42" s="2" t="s">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="X42" s="2" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="Y42" s="2" t="s">
         <v>60</v>
       </c>
       <c r="Z42" s="2" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="AA42">
         <v>24</v>
@@ -5039,45 +5086,45 @@
         <v>44</v>
       </c>
       <c r="AF42" s="2" t="s">
-        <v>41</v>
+        <v>313</v>
       </c>
       <c r="AG42" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="AJ42" s="2" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="F43" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G43">
         <v>3</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>64</v>
+        <v>322</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R43">
         <v>1</v>
@@ -5092,10 +5139,10 @@
         <v>37</v>
       </c>
       <c r="W43" s="2" t="s">
-        <v>243</v>
+        <v>323</v>
       </c>
       <c r="X43" s="2" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="Y43" s="2" t="s">
         <v>60</v>
@@ -5104,7 +5151,7 @@
         <v>43</v>
       </c>
       <c r="AA43">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB43" s="2" t="s">
         <v>61</v>
@@ -5116,45 +5163,45 @@
         <v>44</v>
       </c>
       <c r="AF43" s="2" t="s">
-        <v>110</v>
+        <v>313</v>
       </c>
       <c r="AG43" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="AJ43" s="2" t="s">
-        <v>211</v>
+        <v>326</v>
       </c>
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="F44" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R44">
         <v>1</v>
@@ -5169,10 +5216,10 @@
         <v>37</v>
       </c>
       <c r="W44" s="2" t="s">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="X44" s="2" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="Y44" s="2" t="s">
         <v>60</v>
@@ -5181,7 +5228,7 @@
         <v>43</v>
       </c>
       <c r="AA44">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AB44" s="2" t="s">
         <v>61</v>
@@ -5193,45 +5240,45 @@
         <v>44</v>
       </c>
       <c r="AF44" s="2" t="s">
-        <v>41</v>
+        <v>330</v>
       </c>
       <c r="AG44" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>205</v>
+        <v>331</v>
       </c>
       <c r="AJ44" s="2" t="s">
-        <v>59</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="F45" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>49</v>
+        <v>334</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -5246,10 +5293,10 @@
         <v>37</v>
       </c>
       <c r="W45" s="2" t="s">
-        <v>69</v>
+        <v>335</v>
       </c>
       <c r="X45" s="2" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="Y45" s="2" t="s">
         <v>60</v>
@@ -5270,45 +5317,45 @@
         <v>44</v>
       </c>
       <c r="AF45" s="2" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="AG45" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>47</v>
+        <v>337</v>
       </c>
       <c r="AJ45" s="2" t="s">
-        <v>111</v>
+        <v>338</v>
       </c>
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="F46" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R46">
         <v>1</v>
@@ -5320,72 +5367,70 @@
         <v>63</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="X46" s="2" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="Y46" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Z46" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA46">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB46" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AC46" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD46" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF46" s="2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AG46" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>85</v>
+        <v>343</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="AJ46" s="2" t="s">
-        <v>324</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="AJ46" s="2"/>
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="F47" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R47">
         <v>1</v>
@@ -5397,72 +5442,70 @@
         <v>63</v>
       </c>
       <c r="V47" s="2" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="W47" s="2" t="s">
-        <v>116</v>
+        <v>346</v>
       </c>
       <c r="X47" s="2" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="Y47" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Z47" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA47">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AB47" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AC47" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD47" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF47" s="2" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AG47" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="AJ47" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="AJ47" s="2"/>
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="F48" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>331</v>
+        <v>64</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="R48">
         <v>1</v>
@@ -5474,67 +5517,69 @@
         <v>63</v>
       </c>
       <c r="V48" s="2" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="W48" s="2" t="s">
-        <v>102</v>
+        <v>286</v>
       </c>
       <c r="X48" s="2" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="Y48" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Z48" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA48">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AB48" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AC48" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AD48" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF48" s="2" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="AG48" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="AJ48" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AJ48" s="2" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="F49" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>50</v>
@@ -5552,19 +5597,19 @@
         <v>37</v>
       </c>
       <c r="W49" s="2" t="s">
-        <v>76</v>
+        <v>353</v>
       </c>
       <c r="X49" s="2" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="Y49" s="2" t="s">
         <v>60</v>
       </c>
       <c r="Z49" s="2" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="AA49">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AB49" s="2" t="s">
         <v>61</v>
@@ -5576,36 +5621,36 @@
         <v>44</v>
       </c>
       <c r="AF49" s="2" t="s">
-        <v>337</v>
+        <v>106</v>
       </c>
       <c r="AG49" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH49" s="2" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="AI49" s="2" t="s">
-        <v>105</v>
+        <v>355</v>
       </c>
       <c r="AJ49" s="2" t="s">
-        <v>284</v>
+        <v>356</v>
       </c>
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="F50" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G50">
         <v>8</v>
@@ -5629,16 +5674,16 @@
         <v>37</v>
       </c>
       <c r="W50" s="2" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="X50" s="2" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="Y50" s="2" t="s">
         <v>60</v>
       </c>
       <c r="Z50" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AA50">
         <v>24</v>
@@ -5662,36 +5707,36 @@
         <v>45</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="AJ50" s="2" t="s">
-        <v>59</v>
+        <v>360</v>
       </c>
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="F51" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G51">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>64</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R51">
         <v>1</v>
@@ -5706,19 +5751,19 @@
         <v>37</v>
       </c>
       <c r="W51" s="2" t="s">
-        <v>97</v>
+        <v>150</v>
       </c>
       <c r="X51" s="2" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="Y51" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Z51" s="2" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="AA51">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AB51" s="2" t="s">
         <v>61</v>
@@ -5736,31 +5781,31 @@
         <v>41</v>
       </c>
       <c r="AH51" s="2" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="AI51" s="2" t="s">
-        <v>95</v>
+        <v>364</v>
       </c>
       <c r="AJ51" s="2"/>
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="F52" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>46</v>
@@ -5781,19 +5826,19 @@
         <v>37</v>
       </c>
       <c r="W52" s="2" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="X52" s="2" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="Y52" s="2" t="s">
         <v>60</v>
       </c>
       <c r="Z52" s="2" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="AA52">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB52" s="2" t="s">
         <v>61</v>
@@ -5805,42 +5850,42 @@
         <v>44</v>
       </c>
       <c r="AF52" s="2" t="s">
-        <v>337</v>
+        <v>91</v>
       </c>
       <c r="AG52" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH52" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="AI52" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AJ52" s="2" t="s">
-        <v>59</v>
+        <v>368</v>
       </c>
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="F53" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>50</v>
@@ -5858,10 +5903,10 @@
         <v>37</v>
       </c>
       <c r="W53" s="2" t="s">
-        <v>87</v>
+        <v>133</v>
       </c>
       <c r="X53" s="2" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="Y53" s="2" t="s">
         <v>60</v>
@@ -5870,7 +5915,7 @@
         <v>43</v>
       </c>
       <c r="AA53">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AB53" s="2" t="s">
         <v>61</v>
@@ -5882,45 +5927,45 @@
         <v>44</v>
       </c>
       <c r="AF53" s="2" t="s">
-        <v>350</v>
+        <v>91</v>
       </c>
       <c r="AG53" s="2" t="s">
         <v>40</v>
       </c>
       <c r="AH53" s="2" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="AI53" s="2" t="s">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="AJ53" s="2" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="F54" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>64</v>
+        <v>263</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="R54">
         <v>1</v>
@@ -5932,72 +5977,70 @@
         <v>63</v>
       </c>
       <c r="V54" s="2" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="W54" s="2" t="s">
-        <v>354</v>
+        <v>264</v>
       </c>
       <c r="X54" s="2" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="Y54" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Z54" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA54">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB54" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AC54" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD54" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF54" s="2" t="s">
-        <v>350</v>
+        <v>78</v>
       </c>
       <c r="AG54" s="2" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c r="AI54" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="AJ54" s="2" t="s">
-        <v>357</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="AJ54" s="2"/>
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="F55" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G55">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R55">
         <v>1</v>
@@ -6009,70 +6052,70 @@
         <v>63</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="W55" s="2" t="s">
-        <v>360</v>
+        <v>127</v>
       </c>
       <c r="X55" s="2" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="Y55" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Z55" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA55">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB55" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AC55" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AD55" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AF55" s="2" t="s">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="AG55" s="2" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="AH55" s="2" t="s">
-        <v>363</v>
+        <v>107</v>
       </c>
       <c r="AI55" s="2" t="s">
-        <v>364</v>
+        <v>129</v>
       </c>
       <c r="AJ55" s="2"/>
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="F56" s="1">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G56">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>367</v>
+        <v>65</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -6084,45 +6127,197 @@
         <v>63</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="W56" s="2" t="s">
-        <v>368</v>
+        <v>75</v>
       </c>
       <c r="X56" s="2" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="Y56" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Z56" s="2" t="s">
         <v>43</v>
       </c>
       <c r="AA56">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AB56" s="2" t="s">
         <v>61</v>
       </c>
       <c r="AC56" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD56" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF56" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG56" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH56" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI56" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ56" s="2"/>
+    </row>
+    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F57" s="1">
+        <v>46274</v>
+      </c>
+      <c r="G57">
+        <v>4</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="R57">
+        <v>1</v>
+      </c>
+      <c r="S57">
+        <v>13262</v>
+      </c>
+      <c r="T57" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="V57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W57" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="X57" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="Y57" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z57" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA57">
+        <v>24</v>
+      </c>
+      <c r="AB57" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC57" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AD56" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF56" s="2" t="s">
+      <c r="AD57" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF57" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AG56" s="2" t="s">
+      <c r="AG57" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AH56" s="2" t="s">
+      <c r="AH57" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AI56" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="AJ56" s="2"/>
+      <c r="AI57" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="AJ57" s="2"/>
+    </row>
+    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="F58" s="1">
+        <v>46274</v>
+      </c>
+      <c r="G58">
+        <v>4</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="R58">
+        <v>1</v>
+      </c>
+      <c r="S58">
+        <v>13262</v>
+      </c>
+      <c r="T58" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W58" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="X58" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y58" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA58">
+        <v>20</v>
+      </c>
+      <c r="AB58" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC58" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD58" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF58" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG58" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH58" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI58" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ58" s="2" t="s">
+        <v>386</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
